--- a/arena_enrichment/output/arena_leaderboard_enriched.xlsx
+++ b/arena_enrichment/output/arena_leaderboard_enriched.xlsx
@@ -675,16 +675,16 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>1453.82</v>
+        <v>1455.43</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1446.14</v>
+        <v>1447.98</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1461.51</v>
+        <v>1462.89</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>6061</v>
+        <v>6466</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
@@ -826,16 +826,16 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>1450.54</v>
+        <v>1453.57</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1441.91</v>
+        <v>1445.27</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1459.18</v>
+        <v>1461.88</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>4541</v>
+        <v>4958</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
@@ -977,16 +977,16 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>1450.29</v>
+        <v>1451.66</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1443.98</v>
+        <v>1445.47</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1456.6</v>
+        <v>1457.85</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>10687</v>
+        <v>11075</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
@@ -1128,16 +1128,16 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>1440.85</v>
+        <v>1440.77</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1434.67</v>
+        <v>1434.59</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1447.03</v>
+        <v>1446.95</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>11936</v>
+        <v>11937</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
@@ -1279,16 +1279,16 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1435.15</v>
+        <v>1434.17</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1427.79</v>
+        <v>1427.04</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1442.5</v>
+        <v>1441.3</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>6722</v>
+        <v>7125</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
@@ -1430,16 +1430,16 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>1429.03</v>
+        <v>1428.7</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>1425.04</v>
+        <v>1424.73</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1433.02</v>
+        <v>1432.66</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>35751</v>
+        <v>36099</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
@@ -1587,10 +1587,10 @@
         <v>1421.04</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1429.04</v>
+        <v>1429.03</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>35129</v>
+        <v>35128</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
@@ -1732,16 +1732,16 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>1423.62</v>
+        <v>1423.66</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1417.13</v>
+        <v>1417.17</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1430.11</v>
+        <v>1430.15</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>11685</v>
+        <v>11680</v>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
@@ -1883,13 +1883,13 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>1423.3</v>
+        <v>1423.32</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>1416.72</v>
+        <v>1416.74</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1429.88</v>
+        <v>1429.9</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>8944</v>
@@ -2034,16 +2034,16 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>1422.22</v>
+        <v>1422.1</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>1419.17</v>
+        <v>1419.07</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1425.26</v>
+        <v>1425.13</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>71166</v>
+        <v>71551</v>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
@@ -2185,16 +2185,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1420.89</v>
+        <v>1420.12</v>
       </c>
       <c r="D12" t="n">
-        <v>1416.32</v>
+        <v>1415.58</v>
       </c>
       <c r="E12" t="n">
-        <v>1425.47</v>
+        <v>1424.66</v>
       </c>
       <c r="F12" t="n">
-        <v>25287</v>
+        <v>25692</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -2336,16 +2336,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1419.17</v>
+        <v>1419.83</v>
       </c>
       <c r="D13" t="n">
-        <v>1414.69</v>
+        <v>1415.4</v>
       </c>
       <c r="E13" t="n">
-        <v>1423.64</v>
+        <v>1424.26</v>
       </c>
       <c r="F13" t="n">
-        <v>30323</v>
+        <v>30709</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -2493,10 +2493,10 @@
         <v>1413.54</v>
       </c>
       <c r="E14" t="n">
-        <v>1424.75</v>
+        <v>1424.76</v>
       </c>
       <c r="F14" t="n">
-        <v>19178</v>
+        <v>19177</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -2638,16 +2638,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1418.28</v>
+        <v>1418.24</v>
       </c>
       <c r="D15" t="n">
-        <v>1412.28</v>
+        <v>1412.24</v>
       </c>
       <c r="E15" t="n">
-        <v>1424.28</v>
+        <v>1424.24</v>
       </c>
       <c r="F15" t="n">
-        <v>15198</v>
+        <v>15194</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -2785,36 +2785,36 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>kimi-k2-0905-preview</t>
+          <t>deepseek-v3.1-thinking</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1417.29</v>
+        <v>1417.23</v>
       </c>
       <c r="D16" t="n">
-        <v>1410.82</v>
+        <v>1410.64</v>
       </c>
       <c r="E16" t="n">
-        <v>1423.77</v>
+        <v>1423.82</v>
       </c>
       <c r="F16" t="n">
-        <v>11915</v>
+        <v>11918</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Moonshot</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Modified MIT</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1000</v>
+        <v>685</v>
       </c>
       <c r="J16" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -2823,26 +2823,26 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>artificial_analysis</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>2000</v>
+        <v>1370</v>
       </c>
       <c r="N16" t="n">
-        <v>2500</v>
+        <v>1712.5</v>
       </c>
       <c r="O16" t="n">
-        <v>1000</v>
+        <v>685</v>
       </c>
       <c r="P16" t="n">
-        <v>1250</v>
+        <v>856.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>500</v>
+        <v>342.5</v>
       </c>
       <c r="R16" t="n">
-        <v>625</v>
+        <v>428.1</v>
       </c>
       <c r="S16" s="5" t="inlineStr">
         <is>
@@ -2936,36 +2936,36 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>deepseek-v3.1-thinking</t>
+          <t>kimi-k2-0905-preview</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1417.27</v>
+        <v>1417.2</v>
       </c>
       <c r="D17" t="n">
-        <v>1410.68</v>
+        <v>1410.72</v>
       </c>
       <c r="E17" t="n">
-        <v>1423.86</v>
+        <v>1423.67</v>
       </c>
       <c r="F17" t="n">
-        <v>11919</v>
+        <v>11912</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>DeepSeek</t>
+          <t>Moonshot</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Modified MIT</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>685</v>
+        <v>1000</v>
       </c>
       <c r="J17" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -2974,26 +2974,26 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>artificial_analysis</t>
+          <t>override</t>
         </is>
       </c>
       <c r="M17" t="n">
-        <v>1370</v>
+        <v>2000</v>
       </c>
       <c r="N17" t="n">
-        <v>1712.5</v>
+        <v>2500</v>
       </c>
       <c r="O17" t="n">
-        <v>685</v>
+        <v>1000</v>
       </c>
       <c r="P17" t="n">
-        <v>856.2</v>
+        <v>1250</v>
       </c>
       <c r="Q17" t="n">
-        <v>342.5</v>
+        <v>500</v>
       </c>
       <c r="R17" t="n">
-        <v>428.1</v>
+        <v>625</v>
       </c>
       <c r="S17" s="5" t="inlineStr">
         <is>
@@ -3091,16 +3091,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1416.89</v>
+        <v>1416.8</v>
       </c>
       <c r="D18" t="n">
-        <v>1412.08</v>
+        <v>1411.98</v>
       </c>
       <c r="E18" t="n">
-        <v>1421.7</v>
+        <v>1421.61</v>
       </c>
       <c r="F18" t="n">
-        <v>28445</v>
+        <v>28440</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -3242,16 +3242,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1416.06</v>
+        <v>1416.1</v>
       </c>
       <c r="D19" t="n">
-        <v>1406.5</v>
+        <v>1406.53</v>
       </c>
       <c r="E19" t="n">
-        <v>1425.63</v>
+        <v>1425.67</v>
       </c>
       <c r="F19" t="n">
-        <v>3746</v>
+        <v>3743</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -3393,16 +3393,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1415.76</v>
+        <v>1415.77</v>
       </c>
       <c r="D20" t="n">
-        <v>1405.9</v>
+        <v>1405.91</v>
       </c>
       <c r="E20" t="n">
-        <v>1425.61</v>
+        <v>1425.64</v>
       </c>
       <c r="F20" t="n">
-        <v>3538</v>
+        <v>3536</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -3544,16 +3544,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1415.12</v>
+        <v>1414.85</v>
       </c>
       <c r="D21" t="n">
-        <v>1410.64</v>
+        <v>1410.41</v>
       </c>
       <c r="E21" t="n">
-        <v>1419.6</v>
+        <v>1419.29</v>
       </c>
       <c r="F21" t="n">
-        <v>26713</v>
+        <v>27128</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -3695,16 +3695,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1414.79</v>
+        <v>1414.74</v>
       </c>
       <c r="D22" t="n">
-        <v>1408.31</v>
+        <v>1408.26</v>
       </c>
       <c r="E22" t="n">
-        <v>1421.27</v>
+        <v>1421.22</v>
       </c>
       <c r="F22" t="n">
-        <v>11599</v>
+        <v>11598</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -3846,16 +3846,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1410.05</v>
+        <v>1410.09</v>
       </c>
       <c r="D23" t="n">
-        <v>1405.18</v>
+        <v>1405.21</v>
       </c>
       <c r="E23" t="n">
-        <v>1414.92</v>
+        <v>1414.96</v>
       </c>
       <c r="F23" t="n">
-        <v>24608</v>
+        <v>24600</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -3997,16 +3997,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1401.98</v>
+        <v>1401.95</v>
       </c>
       <c r="D24" t="n">
-        <v>1397.51</v>
+        <v>1397.49</v>
       </c>
       <c r="E24" t="n">
-        <v>1406.44</v>
+        <v>1406.42</v>
       </c>
       <c r="F24" t="n">
-        <v>39301</v>
+        <v>39295</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -4154,10 +4154,10 @@
         <v>1396.84</v>
       </c>
       <c r="E25" t="n">
-        <v>1406.47</v>
+        <v>1406.46</v>
       </c>
       <c r="F25" t="n">
-        <v>22675</v>
+        <v>22670</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -4295,36 +4295,36 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>longcat-flash-chat</t>
+          <t>minimax-m2.5</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1399.96</v>
+        <v>1401.47</v>
       </c>
       <c r="D26" t="n">
-        <v>1393.61</v>
+        <v>1393.65</v>
       </c>
       <c r="E26" t="n">
-        <v>1406.32</v>
+        <v>1409.29</v>
       </c>
       <c r="F26" t="n">
-        <v>11492</v>
+        <v>6065</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Meituan</t>
+          <t>MiniMax</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Modified MIT</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>560</v>
+        <v>230</v>
       </c>
       <c r="J26" t="n">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -4333,26 +4333,26 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>artificial_analysis</t>
         </is>
       </c>
       <c r="M26" t="n">
-        <v>1120</v>
+        <v>460</v>
       </c>
       <c r="N26" t="n">
-        <v>1400</v>
+        <v>575</v>
       </c>
       <c r="O26" t="n">
-        <v>560</v>
+        <v>230</v>
       </c>
       <c r="P26" t="n">
-        <v>700</v>
+        <v>287.5</v>
       </c>
       <c r="Q26" t="n">
-        <v>280</v>
+        <v>115</v>
       </c>
       <c r="R26" t="n">
-        <v>350</v>
+        <v>143.8</v>
       </c>
       <c r="S26" s="5" t="inlineStr">
         <is>
@@ -4409,9 +4409,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AD26" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AD26" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AE26" s="5" t="inlineStr">
@@ -4419,14 +4419,14 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AF26" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AG26" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AF26" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AG26" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AH26" t="inlineStr">
@@ -4436,7 +4436,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>B300 SXM</t>
         </is>
       </c>
     </row>
@@ -4446,36 +4446,36 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>minimax-m2.5</t>
+          <t>longcat-flash-chat</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1399.03</v>
+        <v>1399.96</v>
       </c>
       <c r="D27" t="n">
-        <v>1390.87</v>
+        <v>1393.61</v>
       </c>
       <c r="E27" t="n">
-        <v>1407.18</v>
+        <v>1406.31</v>
       </c>
       <c r="F27" t="n">
-        <v>5631</v>
+        <v>11486</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>MiniMax</t>
+          <t>Meituan</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Modified MIT</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>230</v>
+        <v>560</v>
       </c>
       <c r="J27" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -4484,26 +4484,26 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>artificial_analysis</t>
+          <t>override</t>
         </is>
       </c>
       <c r="M27" t="n">
-        <v>460</v>
+        <v>1120</v>
       </c>
       <c r="N27" t="n">
-        <v>575</v>
+        <v>1400</v>
       </c>
       <c r="O27" t="n">
-        <v>230</v>
+        <v>560</v>
       </c>
       <c r="P27" t="n">
-        <v>287.5</v>
+        <v>700</v>
       </c>
       <c r="Q27" t="n">
-        <v>115</v>
+        <v>280</v>
       </c>
       <c r="R27" t="n">
-        <v>143.8</v>
+        <v>350</v>
       </c>
       <c r="S27" s="5" t="inlineStr">
         <is>
@@ -4560,9 +4560,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AD27" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AD27" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AE27" s="5" t="inlineStr">
@@ -4570,14 +4570,14 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AF27" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AG27" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AF27" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AG27" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AH27" t="inlineStr">
@@ -4587,7 +4587,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>B300 SXM</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
     </row>
@@ -4601,16 +4601,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1398.58</v>
+        <v>1398.63</v>
       </c>
       <c r="D28" t="n">
-        <v>1392.1</v>
+        <v>1392.16</v>
       </c>
       <c r="E28" t="n">
-        <v>1405.05</v>
+        <v>1405.11</v>
       </c>
       <c r="F28" t="n">
-        <v>9189</v>
+        <v>9186</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -4752,13 +4752,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1397.68</v>
+        <v>1397.65</v>
       </c>
       <c r="D29" t="n">
-        <v>1392.84</v>
+        <v>1392.8</v>
       </c>
       <c r="E29" t="n">
-        <v>1402.52</v>
+        <v>1402.49</v>
       </c>
       <c r="F29" t="n">
         <v>18537</v>
@@ -4903,16 +4903,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1394.95</v>
+        <v>1395.02</v>
       </c>
       <c r="D30" t="n">
-        <v>1388.15</v>
+        <v>1388.22</v>
       </c>
       <c r="E30" t="n">
-        <v>1401.76</v>
+        <v>1401.82</v>
       </c>
       <c r="F30" t="n">
-        <v>7926</v>
+        <v>7924</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -5057,13 +5057,13 @@
         <v>1394.16</v>
       </c>
       <c r="D31" t="n">
-        <v>1390.3</v>
+        <v>1390.31</v>
       </c>
       <c r="E31" t="n">
-        <v>1398.01</v>
+        <v>1398.02</v>
       </c>
       <c r="F31" t="n">
-        <v>46442</v>
+        <v>46431</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -5201,68 +5201,148 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>step-3.5-flash</t>
+          <t>mimo-v2-flash (non-thinking)</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1390.95</v>
+        <v>1390.49</v>
       </c>
       <c r="D32" t="n">
-        <v>1384.1</v>
+        <v>1385.58</v>
       </c>
       <c r="E32" t="n">
-        <v>1397.81</v>
+        <v>1395.4</v>
       </c>
       <c r="F32" t="n">
-        <v>8214</v>
+        <v>19661</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>StepFun</t>
+          <t>Xiaomi</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>309</v>
+      </c>
+      <c r="J32" t="n">
+        <v>15</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr"/>
-      <c r="R32" t="inlineStr"/>
-      <c r="S32" t="inlineStr"/>
-      <c r="T32" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
-      <c r="V32" t="inlineStr"/>
-      <c r="W32" t="inlineStr"/>
-      <c r="X32" t="inlineStr"/>
-      <c r="Y32" t="inlineStr"/>
-      <c r="Z32" t="inlineStr"/>
-      <c r="AA32" t="inlineStr"/>
-      <c r="AB32" t="inlineStr"/>
-      <c r="AC32" t="inlineStr"/>
-      <c r="AD32" t="inlineStr"/>
-      <c r="AE32" t="inlineStr"/>
-      <c r="AF32" t="inlineStr"/>
-      <c r="AG32" t="inlineStr"/>
+          <t>artificial_analysis</t>
+        </is>
+      </c>
+      <c r="M32" t="n">
+        <v>618</v>
+      </c>
+      <c r="N32" t="n">
+        <v>772.5</v>
+      </c>
+      <c r="O32" t="n">
+        <v>309</v>
+      </c>
+      <c r="P32" t="n">
+        <v>386.2</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>154.5</v>
+      </c>
+      <c r="R32" t="n">
+        <v>193.1</v>
+      </c>
+      <c r="S32" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T32" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U32" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V32" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W32" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X32" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y32" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z32" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA32" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AB32" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AC32" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD32" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE32" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF32" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AG32" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
     </row>
@@ -5272,148 +5352,68 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>mimo-v2-flash (non-thinking)</t>
+          <t>step-3.5-flash</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1389.86</v>
+        <v>1389.7</v>
       </c>
       <c r="D33" t="n">
-        <v>1384.88</v>
+        <v>1383</v>
       </c>
       <c r="E33" t="n">
-        <v>1394.84</v>
+        <v>1396.4</v>
       </c>
       <c r="F33" t="n">
-        <v>19235</v>
+        <v>8624</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Xiaomi</t>
+          <t>StepFun</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="I33" t="n">
-        <v>309</v>
-      </c>
-      <c r="J33" t="n">
-        <v>15</v>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+          <t>Apache 2.0</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
-          <t>artificial_analysis</t>
-        </is>
-      </c>
-      <c r="M33" t="n">
-        <v>618</v>
-      </c>
-      <c r="N33" t="n">
-        <v>772.5</v>
-      </c>
-      <c r="O33" t="n">
-        <v>309</v>
-      </c>
-      <c r="P33" t="n">
-        <v>386.2</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>154.5</v>
-      </c>
-      <c r="R33" t="n">
-        <v>193.1</v>
-      </c>
-      <c r="S33" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T33" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U33" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="V33" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W33" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X33" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Y33" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z33" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AA33" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AB33" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AC33" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AD33" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AE33" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AF33" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AG33" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr"/>
+      <c r="W33" t="inlineStr"/>
+      <c r="X33" t="inlineStr"/>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr"/>
+      <c r="AA33" t="inlineStr"/>
+      <c r="AB33" t="inlineStr"/>
+      <c r="AC33" t="inlineStr"/>
+      <c r="AD33" t="inlineStr"/>
+      <c r="AE33" t="inlineStr"/>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="inlineStr"/>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -5427,16 +5427,16 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1386.78</v>
+        <v>1386.91</v>
       </c>
       <c r="D34" t="n">
-        <v>1380.44</v>
+        <v>1380.57</v>
       </c>
       <c r="E34" t="n">
-        <v>1393.12</v>
+        <v>1393.25</v>
       </c>
       <c r="F34" t="n">
-        <v>10877</v>
+        <v>10870</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -5578,16 +5578,16 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1386.57</v>
+        <v>1386.54</v>
       </c>
       <c r="D35" t="n">
-        <v>1381.67</v>
+        <v>1381.64</v>
       </c>
       <c r="E35" t="n">
-        <v>1391.47</v>
+        <v>1391.44</v>
       </c>
       <c r="F35" t="n">
-        <v>26414</v>
+        <v>26406</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -5729,16 +5729,16 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1385.54</v>
+        <v>1385.37</v>
       </c>
       <c r="D36" t="n">
-        <v>1380.21</v>
+        <v>1380.05</v>
       </c>
       <c r="E36" t="n">
-        <v>1390.86</v>
+        <v>1390.69</v>
       </c>
       <c r="F36" t="n">
-        <v>17099</v>
+        <v>17092</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -5880,16 +5880,16 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1383.77</v>
+        <v>1383.75</v>
       </c>
       <c r="D37" t="n">
-        <v>1378.9</v>
+        <v>1378.88</v>
       </c>
       <c r="E37" t="n">
-        <v>1388.64</v>
+        <v>1388.62</v>
       </c>
       <c r="F37" t="n">
-        <v>23952</v>
+        <v>23940</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -6031,13 +6031,13 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1377.82</v>
+        <v>1377.44</v>
       </c>
       <c r="D38" t="n">
-        <v>1366.53</v>
+        <v>1366.16</v>
       </c>
       <c r="E38" t="n">
-        <v>1389.1</v>
+        <v>1388.72</v>
       </c>
       <c r="F38" t="n">
         <v>2785</v>
@@ -6182,16 +6182,16 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1375.99</v>
+        <v>1375.1</v>
       </c>
       <c r="D39" t="n">
-        <v>1361.73</v>
+        <v>1362.39</v>
       </c>
       <c r="E39" t="n">
-        <v>1390.26</v>
+        <v>1387.8</v>
       </c>
       <c r="F39" t="n">
-        <v>1690</v>
+        <v>2166</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -6333,16 +6333,16 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1374.79</v>
+        <v>1374.77</v>
       </c>
       <c r="D40" t="n">
-        <v>1370.12</v>
+        <v>1370.1</v>
       </c>
       <c r="E40" t="n">
-        <v>1379.46</v>
+        <v>1379.44</v>
       </c>
       <c r="F40" t="n">
-        <v>27026</v>
+        <v>27019</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -6484,16 +6484,16 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1371.71</v>
+        <v>1371.75</v>
       </c>
       <c r="D41" t="n">
-        <v>1367.45</v>
+        <v>1367.48</v>
       </c>
       <c r="E41" t="n">
-        <v>1375.97</v>
+        <v>1376.01</v>
       </c>
       <c r="F41" t="n">
-        <v>31168</v>
+        <v>31154</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -6635,16 +6635,16 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1368.9</v>
+        <v>1368.86</v>
       </c>
       <c r="D42" t="n">
-        <v>1363.07</v>
+        <v>1363.03</v>
       </c>
       <c r="E42" t="n">
-        <v>1374.74</v>
+        <v>1374.7</v>
       </c>
       <c r="F42" t="n">
-        <v>13768</v>
+        <v>13767</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -6786,16 +6786,16 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1367.36</v>
+        <v>1367.33</v>
       </c>
       <c r="D43" t="n">
-        <v>1363.12</v>
+        <v>1363.09</v>
       </c>
       <c r="E43" t="n">
-        <v>1371.61</v>
+        <v>1371.58</v>
       </c>
       <c r="F43" t="n">
-        <v>36573</v>
+        <v>36564</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -6933,40 +6933,40 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>gemma-3-27b-it</t>
+          <t>glm-4.7-flash</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1365.13</v>
+        <v>1365.72</v>
       </c>
       <c r="D44" t="n">
-        <v>1361.49</v>
+        <v>1359.57</v>
       </c>
       <c r="E44" t="n">
-        <v>1368.78</v>
+        <v>1371.87</v>
       </c>
       <c r="F44" t="n">
-        <v>48462</v>
+        <v>10660</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Z.ai</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Gemma</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>27.4</v>
+        <v>31.2</v>
       </c>
       <c r="J44" t="n">
-        <v>27.4</v>
+        <v>3</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>dense</t>
+          <t>moe</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -6975,22 +6975,22 @@
         </is>
       </c>
       <c r="M44" t="n">
-        <v>54.8</v>
+        <v>62.4</v>
       </c>
       <c r="N44" t="n">
-        <v>68.5</v>
+        <v>78</v>
       </c>
       <c r="O44" t="n">
-        <v>27.4</v>
+        <v>31.2</v>
       </c>
       <c r="P44" t="n">
-        <v>34.2</v>
+        <v>39</v>
       </c>
       <c r="Q44" t="n">
-        <v>13.7</v>
+        <v>15.6</v>
       </c>
       <c r="R44" t="n">
-        <v>17.1</v>
+        <v>19.5</v>
       </c>
       <c r="S44" s="6" t="inlineStr">
         <is>
@@ -7084,40 +7084,40 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>glm-4.7-flash</t>
+          <t>gemma-3-27b-it</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1364.25</v>
+        <v>1365.18</v>
       </c>
       <c r="D45" t="n">
-        <v>1357.95</v>
+        <v>1361.53</v>
       </c>
       <c r="E45" t="n">
-        <v>1370.55</v>
+        <v>1368.83</v>
       </c>
       <c r="F45" t="n">
-        <v>10247</v>
+        <v>48453</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Z.ai</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Gemma</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>31.2</v>
+        <v>27.4</v>
       </c>
       <c r="J45" t="n">
-        <v>3</v>
+        <v>27.4</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>moe</t>
+          <t>dense</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -7126,22 +7126,22 @@
         </is>
       </c>
       <c r="M45" t="n">
-        <v>62.4</v>
+        <v>54.8</v>
       </c>
       <c r="N45" t="n">
-        <v>78</v>
+        <v>68.5</v>
       </c>
       <c r="O45" t="n">
-        <v>31.2</v>
+        <v>27.4</v>
       </c>
       <c r="P45" t="n">
-        <v>39</v>
+        <v>34.2</v>
       </c>
       <c r="Q45" t="n">
-        <v>15.6</v>
+        <v>13.7</v>
       </c>
       <c r="R45" t="n">
-        <v>19.5</v>
+        <v>17.1</v>
       </c>
       <c r="S45" s="6" t="inlineStr">
         <is>
@@ -7239,13 +7239,13 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1358.52</v>
+        <v>1358.47</v>
       </c>
       <c r="D46" t="n">
-        <v>1353.83</v>
+        <v>1353.77</v>
       </c>
       <c r="E46" t="n">
-        <v>1363.22</v>
+        <v>1363.16</v>
       </c>
       <c r="F46" t="n">
         <v>21788</v>
@@ -7390,16 +7390,16 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1356.09</v>
+        <v>1356.04</v>
       </c>
       <c r="D47" t="n">
-        <v>1347.68</v>
+        <v>1347.63</v>
       </c>
       <c r="E47" t="n">
-        <v>1364.51</v>
+        <v>1364.45</v>
       </c>
       <c r="F47" t="n">
-        <v>5289</v>
+        <v>5290</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -7541,16 +7541,16 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1356.06</v>
+        <v>1356.02</v>
       </c>
       <c r="D48" t="n">
-        <v>1350.9</v>
+        <v>1350.86</v>
       </c>
       <c r="E48" t="n">
-        <v>1361.22</v>
+        <v>1361.18</v>
       </c>
       <c r="F48" t="n">
-        <v>18240</v>
+        <v>18237</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -7692,16 +7692,16 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1354</v>
+        <v>1353.9</v>
       </c>
       <c r="D49" t="n">
-        <v>1349.64</v>
+        <v>1349.53</v>
       </c>
       <c r="E49" t="n">
-        <v>1358.37</v>
+        <v>1358.27</v>
       </c>
       <c r="F49" t="n">
-        <v>30767</v>
+        <v>30756</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -7843,16 +7843,16 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1353.16</v>
+        <v>1353.13</v>
       </c>
       <c r="D50" t="n">
-        <v>1344.79</v>
+        <v>1344.77</v>
       </c>
       <c r="E50" t="n">
-        <v>1361.52</v>
+        <v>1361.5</v>
       </c>
       <c r="F50" t="n">
-        <v>4954</v>
+        <v>4950</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -7994,16 +7994,16 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1353.1</v>
+        <v>1353.06</v>
       </c>
       <c r="D51" t="n">
-        <v>1349.67</v>
+        <v>1349.63</v>
       </c>
       <c r="E51" t="n">
-        <v>1356.54</v>
+        <v>1356.5</v>
       </c>
       <c r="F51" t="n">
-        <v>57108</v>
+        <v>57098</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -8145,13 +8145,13 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1347.27</v>
+        <v>1347.23</v>
       </c>
       <c r="D52" t="n">
-        <v>1335.55</v>
+        <v>1335.52</v>
       </c>
       <c r="E52" t="n">
-        <v>1358.98</v>
+        <v>1358.94</v>
       </c>
       <c r="F52" t="n">
         <v>2546</v>
@@ -8292,24 +8292,24 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>minimax-m2</t>
+          <t>qwen3-32b</t>
         </is>
       </c>
       <c r="C53" t="n">
         <v>1347</v>
       </c>
       <c r="D53" t="n">
-        <v>1339.18</v>
+        <v>1337.56</v>
       </c>
       <c r="E53" t="n">
-        <v>1354.83</v>
+        <v>1356.44</v>
       </c>
       <c r="F53" t="n">
-        <v>6688</v>
+        <v>3932</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>MiniMax</t>
+          <t>Alibaba</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -8318,14 +8318,14 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>230</v>
+        <v>32.8</v>
       </c>
       <c r="J53" t="n">
-        <v>10</v>
+        <v>32.8</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>moe</t>
+          <t>dense</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -8334,36 +8334,36 @@
         </is>
       </c>
       <c r="M53" t="n">
-        <v>460</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="N53" t="n">
-        <v>575</v>
+        <v>82</v>
       </c>
       <c r="O53" t="n">
-        <v>230</v>
+        <v>32.8</v>
       </c>
       <c r="P53" t="n">
-        <v>287.5</v>
+        <v>41</v>
       </c>
       <c r="Q53" t="n">
-        <v>115</v>
+        <v>16.4</v>
       </c>
       <c r="R53" t="n">
-        <v>143.8</v>
-      </c>
-      <c r="S53" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T53" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U53" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+        <v>20.5</v>
+      </c>
+      <c r="S53" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T53" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U53" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="V53" s="5" t="inlineStr">
@@ -8371,39 +8371,39 @@
           <t>No</t>
         </is>
       </c>
-      <c r="W53" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X53" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Y53" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z53" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AA53" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AB53" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AC53" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="W53" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X53" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y53" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z53" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AA53" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB53" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AC53" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AD53" s="6" t="inlineStr">
@@ -8411,9 +8411,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="AE53" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AE53" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AF53" s="6" t="inlineStr">
@@ -8428,12 +8428,12 @@
       </c>
       <c r="AH53" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>RTX PRO 6000</t>
         </is>
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>B300 SXM</t>
+          <t>H100 SXM</t>
         </is>
       </c>
     </row>
@@ -8443,24 +8443,24 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>qwen3-32b</t>
+          <t>minimax-m2</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1347</v>
+        <v>1346.97</v>
       </c>
       <c r="D54" t="n">
-        <v>1337.56</v>
+        <v>1339.14</v>
       </c>
       <c r="E54" t="n">
-        <v>1356.45</v>
+        <v>1354.8</v>
       </c>
       <c r="F54" t="n">
-        <v>3932</v>
+        <v>6688</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alibaba</t>
+          <t>MiniMax</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -8469,14 +8469,14 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>32.8</v>
+        <v>230</v>
       </c>
       <c r="J54" t="n">
-        <v>32.8</v>
+        <v>10</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>dense</t>
+          <t>moe</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -8485,36 +8485,36 @@
         </is>
       </c>
       <c r="M54" t="n">
-        <v>65.59999999999999</v>
+        <v>460</v>
       </c>
       <c r="N54" t="n">
-        <v>82</v>
+        <v>575</v>
       </c>
       <c r="O54" t="n">
-        <v>32.8</v>
+        <v>230</v>
       </c>
       <c r="P54" t="n">
-        <v>41</v>
+        <v>287.5</v>
       </c>
       <c r="Q54" t="n">
-        <v>16.4</v>
+        <v>115</v>
       </c>
       <c r="R54" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="S54" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="T54" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="U54" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+        <v>143.8</v>
+      </c>
+      <c r="S54" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T54" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U54" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="V54" s="5" t="inlineStr">
@@ -8522,39 +8522,39 @@
           <t>No</t>
         </is>
       </c>
-      <c r="W54" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X54" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Y54" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z54" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AA54" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB54" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AC54" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="W54" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X54" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y54" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z54" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA54" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AB54" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AC54" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AD54" s="6" t="inlineStr">
@@ -8562,9 +8562,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="AE54" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AE54" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AF54" s="6" t="inlineStr">
@@ -8579,12 +8579,12 @@
       </c>
       <c r="AH54" t="inlineStr">
         <is>
-          <t>RTX PRO 6000</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>B300 SXM</t>
         </is>
       </c>
     </row>
@@ -8598,16 +8598,16 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1346.87</v>
+        <v>1346.92</v>
       </c>
       <c r="D55" t="n">
-        <v>1339.61</v>
+        <v>1339.65</v>
       </c>
       <c r="E55" t="n">
-        <v>1354.14</v>
+        <v>1354.18</v>
       </c>
       <c r="F55" t="n">
-        <v>6998</v>
+        <v>6995</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -8749,16 +8749,16 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1346.46</v>
+        <v>1346.54</v>
       </c>
       <c r="D56" t="n">
-        <v>1339.07</v>
+        <v>1339.14</v>
       </c>
       <c r="E56" t="n">
-        <v>1353.86</v>
+        <v>1353.93</v>
       </c>
       <c r="F56" t="n">
-        <v>6568</v>
+        <v>6567</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -8971,16 +8971,16 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1341.51</v>
+        <v>1341.3</v>
       </c>
       <c r="D58" t="n">
-        <v>1331.6</v>
+        <v>1331.39</v>
       </c>
       <c r="E58" t="n">
-        <v>1351.41</v>
+        <v>1351.2</v>
       </c>
       <c r="F58" t="n">
-        <v>3402</v>
+        <v>3400</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -9131,7 +9131,7 @@
         <v>1340.17</v>
       </c>
       <c r="F59" t="n">
-        <v>26003</v>
+        <v>26000</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -9273,13 +9273,13 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1335.35</v>
+        <v>1335.21</v>
       </c>
       <c r="D60" t="n">
-        <v>1331.69</v>
+        <v>1331.56</v>
       </c>
       <c r="E60" t="n">
-        <v>1339</v>
+        <v>1338.87</v>
       </c>
       <c r="F60" t="n">
         <v>41392</v>
@@ -9424,13 +9424,13 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1333.53</v>
+        <v>1333.39</v>
       </c>
       <c r="D61" t="n">
-        <v>1329.98</v>
+        <v>1329.85</v>
       </c>
       <c r="E61" t="n">
-        <v>1337.07</v>
+        <v>1336.94</v>
       </c>
       <c r="F61" t="n">
         <v>59655</v>
@@ -9575,20 +9575,20 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1330.47</v>
+        <v>1330.45</v>
       </c>
       <c r="D62" t="n">
-        <v>1324.31</v>
+        <v>1324.3</v>
       </c>
       <c r="E62" t="n">
-        <v>1336.63</v>
+        <v>1336.61</v>
       </c>
       <c r="F62" t="n">
         <v>12252</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Allen AI</t>
+          <t>Ai2</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -9726,20 +9726,20 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1329.1</v>
+        <v>1329.22</v>
       </c>
       <c r="D63" t="n">
-        <v>1307.8</v>
+        <v>1307.93</v>
       </c>
       <c r="E63" t="n">
-        <v>1350.4</v>
+        <v>1350.52</v>
       </c>
       <c r="F63" t="n">
         <v>816</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>AI2</t>
+          <t>Ai2</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -9877,16 +9877,16 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1328.17</v>
+        <v>1328.13</v>
       </c>
       <c r="D64" t="n">
-        <v>1323.49</v>
+        <v>1323.44</v>
       </c>
       <c r="E64" t="n">
-        <v>1332.86</v>
+        <v>1332.81</v>
       </c>
       <c r="F64" t="n">
-        <v>27289</v>
+        <v>27282</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -10028,16 +10028,16 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1327.69</v>
+        <v>1327.62</v>
       </c>
       <c r="D65" t="n">
-        <v>1323.48</v>
+        <v>1323.41</v>
       </c>
       <c r="E65" t="n">
-        <v>1331.9</v>
+        <v>1331.83</v>
       </c>
       <c r="F65" t="n">
-        <v>40938</v>
+        <v>40932</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1327.09</v>
+        <v>1327.07</v>
       </c>
       <c r="D66" t="n">
-        <v>1314.95</v>
+        <v>1314.94</v>
       </c>
       <c r="E66" t="n">
-        <v>1339.22</v>
+        <v>1339.2</v>
       </c>
       <c r="F66" t="n">
         <v>2230</v>
@@ -10330,13 +10330,13 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1323.3</v>
+        <v>1323.24</v>
       </c>
       <c r="D67" t="n">
-        <v>1315.03</v>
+        <v>1314.97</v>
       </c>
       <c r="E67" t="n">
-        <v>1331.57</v>
+        <v>1331.5</v>
       </c>
       <c r="F67" t="n">
         <v>6793</v>
@@ -10481,16 +10481,16 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1322.51</v>
+        <v>1322.39</v>
       </c>
       <c r="D68" t="n">
-        <v>1317.84</v>
+        <v>1317.72</v>
       </c>
       <c r="E68" t="n">
-        <v>1327.19</v>
+        <v>1327.07</v>
       </c>
       <c r="F68" t="n">
-        <v>31061</v>
+        <v>31053</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -10632,16 +10632,16 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1320.39</v>
+        <v>1320.45</v>
       </c>
       <c r="D69" t="n">
-        <v>1313.17</v>
+        <v>1313.24</v>
       </c>
       <c r="E69" t="n">
-        <v>1327.6</v>
+        <v>1327.66</v>
       </c>
       <c r="F69" t="n">
-        <v>7149</v>
+        <v>7148</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -10783,16 +10783,16 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1319.45</v>
+        <v>1319.32</v>
       </c>
       <c r="D70" t="n">
-        <v>1316.05</v>
+        <v>1315.91</v>
       </c>
       <c r="E70" t="n">
-        <v>1322.86</v>
+        <v>1322.73</v>
       </c>
       <c r="F70" t="n">
-        <v>55456</v>
+        <v>55454</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -10934,16 +10934,16 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1319.3</v>
+        <v>1319.29</v>
       </c>
       <c r="D71" t="n">
-        <v>1314.2</v>
+        <v>1314.19</v>
       </c>
       <c r="E71" t="n">
-        <v>1324.39</v>
+        <v>1324.38</v>
       </c>
       <c r="F71" t="n">
-        <v>23197</v>
+        <v>23193</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -11085,13 +11085,13 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1318.13</v>
+        <v>1318.05</v>
       </c>
       <c r="D72" t="n">
-        <v>1312.45</v>
+        <v>1312.37</v>
       </c>
       <c r="E72" t="n">
-        <v>1323.8</v>
+        <v>1323.73</v>
       </c>
       <c r="F72" t="n">
         <v>16479</v>
@@ -11156,16 +11156,16 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1317.09</v>
+        <v>1317.02</v>
       </c>
       <c r="D73" t="n">
-        <v>1310.74</v>
+        <v>1310.67</v>
       </c>
       <c r="E73" t="n">
-        <v>1323.44</v>
+        <v>1323.37</v>
       </c>
       <c r="F73" t="n">
-        <v>10760</v>
+        <v>10758</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -11307,13 +11307,13 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1316.95</v>
+        <v>1317</v>
       </c>
       <c r="D74" t="n">
-        <v>1311.31</v>
+        <v>1311.37</v>
       </c>
       <c r="E74" t="n">
-        <v>1322.59</v>
+        <v>1322.64</v>
       </c>
       <c r="F74" t="n">
         <v>15408</v>
@@ -11458,13 +11458,13 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>1314.5</v>
+        <v>1314.44</v>
       </c>
       <c r="D75" t="n">
-        <v>1309.99</v>
+        <v>1309.93</v>
       </c>
       <c r="E75" t="n">
-        <v>1319.01</v>
+        <v>1318.95</v>
       </c>
       <c r="F75" t="n">
         <v>24746</v>
@@ -11609,13 +11609,13 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>1314.1</v>
+        <v>1314</v>
       </c>
       <c r="D76" t="n">
-        <v>1310.22</v>
+        <v>1310.12</v>
       </c>
       <c r="E76" t="n">
-        <v>1317.98</v>
+        <v>1317.88</v>
       </c>
       <c r="F76" t="n">
         <v>45460</v>
@@ -11760,13 +11760,13 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1307.06</v>
+        <v>1306.99</v>
       </c>
       <c r="D77" t="n">
-        <v>1302.39</v>
+        <v>1302.32</v>
       </c>
       <c r="E77" t="n">
-        <v>1311.73</v>
+        <v>1311.66</v>
       </c>
       <c r="F77" t="n">
         <v>24574</v>
@@ -11911,13 +11911,13 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1306.03</v>
+        <v>1305.96</v>
       </c>
       <c r="D78" t="n">
-        <v>1300.38</v>
+        <v>1300.31</v>
       </c>
       <c r="E78" t="n">
-        <v>1311.68</v>
+        <v>1311.61</v>
       </c>
       <c r="F78" t="n">
         <v>19622</v>
@@ -12062,20 +12062,20 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>1305.68</v>
+        <v>1305.64</v>
       </c>
       <c r="D79" t="n">
-        <v>1297.42</v>
+        <v>1297.37</v>
       </c>
       <c r="E79" t="n">
-        <v>1313.95</v>
+        <v>1313.9</v>
       </c>
       <c r="F79" t="n">
-        <v>5869</v>
+        <v>5868</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Allen AI</t>
+          <t>Ai2</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -12213,13 +12213,13 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1305.16</v>
+        <v>1305.07</v>
       </c>
       <c r="D80" t="n">
-        <v>1300.77</v>
+        <v>1300.69</v>
       </c>
       <c r="E80" t="n">
-        <v>1309.54</v>
+        <v>1309.46</v>
       </c>
       <c r="F80" t="n">
         <v>28081</v>
@@ -12364,16 +12364,16 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1304.41</v>
+        <v>1304.36</v>
       </c>
       <c r="D81" t="n">
-        <v>1299.93</v>
+        <v>1299.88</v>
       </c>
       <c r="E81" t="n">
-        <v>1308.89</v>
+        <v>1308.84</v>
       </c>
       <c r="F81" t="n">
-        <v>33907</v>
+        <v>33897</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -12515,13 +12515,13 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>1303.27</v>
+        <v>1303.26</v>
       </c>
       <c r="D82" t="n">
-        <v>1293.95</v>
+        <v>1293.94</v>
       </c>
       <c r="E82" t="n">
-        <v>1312.58</v>
+        <v>1312.57</v>
       </c>
       <c r="F82" t="n">
         <v>4177</v>
@@ -12666,13 +12666,13 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>1302.71</v>
+        <v>1302.64</v>
       </c>
       <c r="D83" t="n">
-        <v>1298.69</v>
+        <v>1298.62</v>
       </c>
       <c r="E83" t="n">
-        <v>1306.73</v>
+        <v>1306.66</v>
       </c>
       <c r="F83" t="n">
         <v>39409</v>
@@ -12817,13 +12817,13 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>1298.65</v>
+        <v>1298.63</v>
       </c>
       <c r="D84" t="n">
-        <v>1290.89</v>
+        <v>1290.88</v>
       </c>
       <c r="E84" t="n">
-        <v>1306.4</v>
+        <v>1306.38</v>
       </c>
       <c r="F84" t="n">
         <v>7136</v>
@@ -12968,13 +12968,13 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>1293.51</v>
+        <v>1293.43</v>
       </c>
       <c r="D85" t="n">
-        <v>1289.83</v>
+        <v>1289.75</v>
       </c>
       <c r="E85" t="n">
-        <v>1297.2</v>
+        <v>1297.12</v>
       </c>
       <c r="F85" t="n">
         <v>55234</v>
@@ -13119,13 +13119,13 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>1288.76</v>
+        <v>1288.66</v>
       </c>
       <c r="D86" t="n">
-        <v>1281.46</v>
+        <v>1281.36</v>
       </c>
       <c r="E86" t="n">
-        <v>1296.06</v>
+        <v>1295.96</v>
       </c>
       <c r="F86" t="n">
         <v>8659</v>
@@ -13270,13 +13270,13 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>1288.11</v>
+        <v>1288.04</v>
       </c>
       <c r="D87" t="n">
-        <v>1284.79</v>
+        <v>1284.71</v>
       </c>
       <c r="E87" t="n">
-        <v>1291.43</v>
+        <v>1291.36</v>
       </c>
       <c r="F87" t="n">
         <v>75764</v>
@@ -13421,13 +13421,13 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>1287.14</v>
+        <v>1287.04</v>
       </c>
       <c r="D88" t="n">
-        <v>1278.72</v>
+        <v>1278.62</v>
       </c>
       <c r="E88" t="n">
-        <v>1295.56</v>
+        <v>1295.46</v>
       </c>
       <c r="F88" t="n">
         <v>5622</v>
@@ -13572,13 +13572,13 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>1286.63</v>
+        <v>1286.53</v>
       </c>
       <c r="D89" t="n">
-        <v>1276.15</v>
+        <v>1276.06</v>
       </c>
       <c r="E89" t="n">
-        <v>1297.11</v>
+        <v>1297.01</v>
       </c>
       <c r="F89" t="n">
         <v>2846</v>
@@ -13723,13 +13723,13 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>1286.4</v>
+        <v>1286.25</v>
       </c>
       <c r="D90" t="n">
-        <v>1276.42</v>
+        <v>1276.28</v>
       </c>
       <c r="E90" t="n">
-        <v>1296.37</v>
+        <v>1296.23</v>
       </c>
       <c r="F90" t="n">
         <v>3749</v>
@@ -13874,20 +13874,20 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>1285.11</v>
+        <v>1285.07</v>
       </c>
       <c r="D91" t="n">
-        <v>1277.84</v>
+        <v>1277.81</v>
       </c>
       <c r="E91" t="n">
-        <v>1292.38</v>
+        <v>1292.34</v>
       </c>
       <c r="F91" t="n">
-        <v>8437</v>
+        <v>8442</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Allen AI</t>
+          <t>Ai2</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -14025,13 +14025,13 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>1279.47</v>
+        <v>1279.39</v>
       </c>
       <c r="D92" t="n">
-        <v>1272.62</v>
+        <v>1272.53</v>
       </c>
       <c r="E92" t="n">
-        <v>1286.32</v>
+        <v>1286.24</v>
       </c>
       <c r="F92" t="n">
         <v>10069</v>
@@ -14176,13 +14176,13 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>1277.54</v>
+        <v>1277.38</v>
       </c>
       <c r="D93" t="n">
-        <v>1272.22</v>
+        <v>1272.06</v>
       </c>
       <c r="E93" t="n">
-        <v>1282.86</v>
+        <v>1282.7</v>
       </c>
       <c r="F93" t="n">
         <v>19661</v>
@@ -14327,13 +14327,13 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1276.54</v>
+        <v>1276.4</v>
       </c>
       <c r="D94" t="n">
-        <v>1269.98</v>
+        <v>1269.84</v>
       </c>
       <c r="E94" t="n">
-        <v>1283.1</v>
+        <v>1282.96</v>
       </c>
       <c r="F94" t="n">
         <v>9869</v>
@@ -14478,13 +14478,13 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1276.07</v>
+        <v>1275.95</v>
       </c>
       <c r="D95" t="n">
-        <v>1272.51</v>
+        <v>1272.39</v>
       </c>
       <c r="E95" t="n">
-        <v>1279.63</v>
+        <v>1279.51</v>
       </c>
       <c r="F95" t="n">
         <v>156880</v>
@@ -14629,13 +14629,13 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>1273.93</v>
+        <v>1273.85</v>
       </c>
       <c r="D96" t="n">
-        <v>1268.05</v>
+        <v>1267.97</v>
       </c>
       <c r="E96" t="n">
-        <v>1279.8</v>
+        <v>1279.72</v>
       </c>
       <c r="F96" t="n">
         <v>14677</v>
@@ -14780,13 +14780,13 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1270.66</v>
+        <v>1270.57</v>
       </c>
       <c r="D97" t="n">
-        <v>1262.55</v>
+        <v>1262.45</v>
       </c>
       <c r="E97" t="n">
-        <v>1278.78</v>
+        <v>1278.68</v>
       </c>
       <c r="F97" t="n">
         <v>5430</v>
@@ -14931,13 +14931,13 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>1267.12</v>
+        <v>1267.03</v>
       </c>
       <c r="D98" t="n">
-        <v>1262.28</v>
+        <v>1262.18</v>
       </c>
       <c r="E98" t="n">
-        <v>1271.97</v>
+        <v>1271.88</v>
       </c>
       <c r="F98" t="n">
         <v>27123</v>
@@ -15082,13 +15082,13 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>1265.53</v>
+        <v>1265.46</v>
       </c>
       <c r="D99" t="n">
-        <v>1261.77</v>
+        <v>1261.69</v>
       </c>
       <c r="E99" t="n">
-        <v>1269.3</v>
+        <v>1269.22</v>
       </c>
       <c r="F99" t="n">
         <v>54615</v>
@@ -15233,13 +15233,13 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>1264.33</v>
+        <v>1264.19</v>
       </c>
       <c r="D100" t="n">
-        <v>1258.06</v>
+        <v>1257.92</v>
       </c>
       <c r="E100" t="n">
-        <v>1270.61</v>
+        <v>1270.47</v>
       </c>
       <c r="F100" t="n">
         <v>15147</v>
@@ -15384,13 +15384,13 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1262.07</v>
+        <v>1261.9</v>
       </c>
       <c r="D101" t="n">
-        <v>1257.76</v>
+        <v>1257.59</v>
       </c>
       <c r="E101" t="n">
-        <v>1266.38</v>
+        <v>1266.21</v>
       </c>
       <c r="F101" t="n">
         <v>77556</v>
@@ -15535,13 +15535,13 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>1261.95</v>
+        <v>1261.79</v>
       </c>
       <c r="D102" t="n">
-        <v>1257.03</v>
+        <v>1256.87</v>
       </c>
       <c r="E102" t="n">
-        <v>1266.88</v>
+        <v>1266.72</v>
       </c>
       <c r="F102" t="n">
         <v>37325</v>
@@ -15686,13 +15686,13 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>1256.16</v>
+        <v>1256.07</v>
       </c>
       <c r="D103" t="n">
-        <v>1251.61</v>
+        <v>1251.52</v>
       </c>
       <c r="E103" t="n">
-        <v>1260.71</v>
+        <v>1260.62</v>
       </c>
       <c r="F103" t="n">
         <v>24126</v>
@@ -15837,20 +15837,20 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>1252.09</v>
+        <v>1251.98</v>
       </c>
       <c r="D104" t="n">
-        <v>1241.3</v>
+        <v>1241.2</v>
       </c>
       <c r="E104" t="n">
-        <v>1262.87</v>
+        <v>1262.77</v>
       </c>
       <c r="F104" t="n">
         <v>3335</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Allen AI</t>
+          <t>Ai2</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -15988,13 +15988,13 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>1250.37</v>
+        <v>1250.21</v>
       </c>
       <c r="D105" t="n">
-        <v>1243.78</v>
+        <v>1243.62</v>
       </c>
       <c r="E105" t="n">
-        <v>1256.96</v>
+        <v>1256.8</v>
       </c>
       <c r="F105" t="n">
         <v>10141</v>
@@ -16139,13 +16139,13 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>1239</v>
+        <v>1238.91</v>
       </c>
       <c r="D106" t="n">
-        <v>1231.78</v>
+        <v>1231.69</v>
       </c>
       <c r="E106" t="n">
-        <v>1246.22</v>
+        <v>1246.13</v>
       </c>
       <c r="F106" t="n">
         <v>8854</v>
@@ -16290,13 +16290,13 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>1237.12</v>
+        <v>1237.03</v>
       </c>
       <c r="D107" t="n">
-        <v>1228.03</v>
+        <v>1227.94</v>
       </c>
       <c r="E107" t="n">
-        <v>1246.22</v>
+        <v>1246.13</v>
       </c>
       <c r="F107" t="n">
         <v>4780</v>
@@ -16441,13 +16441,13 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>1234.12</v>
+        <v>1233.96</v>
       </c>
       <c r="D108" t="n">
-        <v>1228.57</v>
+        <v>1228.42</v>
       </c>
       <c r="E108" t="n">
-        <v>1239.66</v>
+        <v>1239.51</v>
       </c>
       <c r="F108" t="n">
         <v>26191</v>
@@ -16592,13 +16592,13 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>1233.31</v>
+        <v>1233.14</v>
       </c>
       <c r="D109" t="n">
-        <v>1228.04</v>
+        <v>1227.87</v>
       </c>
       <c r="E109" t="n">
-        <v>1238.58</v>
+        <v>1238.41</v>
       </c>
       <c r="F109" t="n">
         <v>39296</v>
@@ -16743,13 +16743,13 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>1229.67</v>
+        <v>1229.48</v>
       </c>
       <c r="D110" t="n">
-        <v>1225.13</v>
+        <v>1224.94</v>
       </c>
       <c r="E110" t="n">
-        <v>1234.21</v>
+        <v>1234.02</v>
       </c>
       <c r="F110" t="n">
         <v>51417</v>
@@ -16894,13 +16894,13 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>1227.12</v>
+        <v>1226.94</v>
       </c>
       <c r="D111" t="n">
-        <v>1222.34</v>
+        <v>1222.16</v>
       </c>
       <c r="E111" t="n">
-        <v>1231.89</v>
+        <v>1231.71</v>
       </c>
       <c r="F111" t="n">
         <v>54038</v>
@@ -17045,13 +17045,13 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>1223.25</v>
+        <v>1223.12</v>
       </c>
       <c r="D112" t="n">
-        <v>1219.54</v>
+        <v>1219.41</v>
       </c>
       <c r="E112" t="n">
-        <v>1226.96</v>
+        <v>1226.83</v>
       </c>
       <c r="F112" t="n">
         <v>104636</v>
@@ -17196,13 +17196,13 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>1223.08</v>
+        <v>1223</v>
       </c>
       <c r="D113" t="n">
-        <v>1216.13</v>
+        <v>1216.05</v>
       </c>
       <c r="E113" t="n">
-        <v>1230.03</v>
+        <v>1229.95</v>
       </c>
       <c r="F113" t="n">
         <v>9827</v>
@@ -17347,13 +17347,13 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>1220.63</v>
+        <v>1220.55</v>
       </c>
       <c r="D114" t="n">
-        <v>1209.93</v>
+        <v>1209.84</v>
       </c>
       <c r="E114" t="n">
-        <v>1231.34</v>
+        <v>1231.25</v>
       </c>
       <c r="F114" t="n">
         <v>2895</v>
@@ -17498,13 +17498,13 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>1213.46</v>
+        <v>1213.33</v>
       </c>
       <c r="D115" t="n">
-        <v>1208.44</v>
+        <v>1208.31</v>
       </c>
       <c r="E115" t="n">
-        <v>1218.49</v>
+        <v>1218.36</v>
       </c>
       <c r="F115" t="n">
         <v>24142</v>
@@ -17649,13 +17649,13 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>1212.92</v>
+        <v>1212.74</v>
       </c>
       <c r="D116" t="n">
-        <v>1202.1</v>
+        <v>1201.93</v>
       </c>
       <c r="E116" t="n">
-        <v>1223.73</v>
+        <v>1223.55</v>
       </c>
       <c r="F116" t="n">
         <v>4653</v>
@@ -17800,13 +17800,13 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>1211.53</v>
+        <v>1211.47</v>
       </c>
       <c r="D117" t="n">
-        <v>1207.43</v>
+        <v>1207.37</v>
       </c>
       <c r="E117" t="n">
-        <v>1215.63</v>
+        <v>1215.57</v>
       </c>
       <c r="F117" t="n">
         <v>49605</v>
@@ -17951,13 +17951,13 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>1208.71</v>
+        <v>1208.56</v>
       </c>
       <c r="D118" t="n">
-        <v>1197.61</v>
+        <v>1197.45</v>
       </c>
       <c r="E118" t="n">
-        <v>1219.82</v>
+        <v>1219.66</v>
       </c>
       <c r="F118" t="n">
         <v>3092</v>
@@ -18102,13 +18102,13 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>1204.05</v>
+        <v>1203.87</v>
       </c>
       <c r="D119" t="n">
-        <v>1197.93</v>
+        <v>1197.76</v>
       </c>
       <c r="E119" t="n">
-        <v>1210.17</v>
+        <v>1209.99</v>
       </c>
       <c r="F119" t="n">
         <v>21744</v>
@@ -18253,13 +18253,13 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>1198.74</v>
+        <v>1198.7</v>
       </c>
       <c r="D120" t="n">
-        <v>1194.69</v>
+        <v>1194.65</v>
       </c>
       <c r="E120" t="n">
-        <v>1202.78</v>
+        <v>1202.75</v>
       </c>
       <c r="F120" t="n">
         <v>46618</v>
@@ -18404,13 +18404,13 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>1198.12</v>
+        <v>1197.96</v>
       </c>
       <c r="D121" t="n">
-        <v>1192.98</v>
+        <v>1192.81</v>
       </c>
       <c r="E121" t="n">
-        <v>1203.27</v>
+        <v>1203.1</v>
       </c>
       <c r="F121" t="n">
         <v>25055</v>
@@ -18555,13 +18555,13 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>1197.31</v>
+        <v>1197.12</v>
       </c>
       <c r="D122" t="n">
-        <v>1193.04</v>
+        <v>1192.86</v>
       </c>
       <c r="E122" t="n">
-        <v>1201.57</v>
+        <v>1201.39</v>
       </c>
       <c r="F122" t="n">
         <v>73505</v>
@@ -18706,13 +18706,13 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>1195.12</v>
+        <v>1194.93</v>
       </c>
       <c r="D123" t="n">
-        <v>1189.01</v>
+        <v>1188.82</v>
       </c>
       <c r="E123" t="n">
-        <v>1201.23</v>
+        <v>1201.04</v>
       </c>
       <c r="F123" t="n">
         <v>32196</v>
@@ -18857,13 +18857,13 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>1191.38</v>
+        <v>1191.28</v>
       </c>
       <c r="D124" t="n">
-        <v>1184.21</v>
+        <v>1184.1</v>
       </c>
       <c r="E124" t="n">
-        <v>1198.55</v>
+        <v>1198.45</v>
       </c>
       <c r="F124" t="n">
         <v>9902</v>
@@ -19008,13 +19008,13 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>1190.99</v>
+        <v>1190.83</v>
       </c>
       <c r="D125" t="n">
-        <v>1183.87</v>
+        <v>1183.7</v>
       </c>
       <c r="E125" t="n">
-        <v>1198.12</v>
+        <v>1197.95</v>
       </c>
       <c r="F125" t="n">
         <v>17841</v>
@@ -19159,13 +19159,13 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>1184.82</v>
+        <v>1184.64</v>
       </c>
       <c r="D126" t="n">
-        <v>1175.35</v>
+        <v>1175.18</v>
       </c>
       <c r="E126" t="n">
-        <v>1194.28</v>
+        <v>1194.1</v>
       </c>
       <c r="F126" t="n">
         <v>8214</v>
@@ -19310,13 +19310,13 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>1184.55</v>
+        <v>1184.35</v>
       </c>
       <c r="D127" t="n">
-        <v>1173.02</v>
+        <v>1172.83</v>
       </c>
       <c r="E127" t="n">
-        <v>1196.07</v>
+        <v>1195.87</v>
       </c>
       <c r="F127" t="n">
         <v>4933</v>
@@ -19461,13 +19461,13 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>1183.9</v>
+        <v>1183.75</v>
       </c>
       <c r="D128" t="n">
-        <v>1177.07</v>
+        <v>1176.93</v>
       </c>
       <c r="E128" t="n">
-        <v>1190.73</v>
+        <v>1190.58</v>
       </c>
       <c r="F128" t="n">
         <v>15483</v>
@@ -19612,13 +19612,13 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>1182.46</v>
+        <v>1182.27</v>
       </c>
       <c r="D129" t="n">
-        <v>1174.45</v>
+        <v>1174.27</v>
       </c>
       <c r="E129" t="n">
-        <v>1190.46</v>
+        <v>1190.28</v>
       </c>
       <c r="F129" t="n">
         <v>12636</v>
@@ -19763,13 +19763,13 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>1182.4</v>
+        <v>1182.2</v>
       </c>
       <c r="D130" t="n">
-        <v>1172.71</v>
+        <v>1172.52</v>
       </c>
       <c r="E130" t="n">
-        <v>1192.08</v>
+        <v>1191.89</v>
       </c>
       <c r="F130" t="n">
         <v>7967</v>
@@ -19914,13 +19914,13 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>1182.1</v>
+        <v>1181.92</v>
       </c>
       <c r="D131" t="n">
-        <v>1173.42</v>
+        <v>1173.23</v>
       </c>
       <c r="E131" t="n">
-        <v>1190.78</v>
+        <v>1190.6</v>
       </c>
       <c r="F131" t="n">
         <v>6643</v>
@@ -20065,13 +20065,13 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>1180.25</v>
+        <v>1180.13</v>
       </c>
       <c r="D132" t="n">
-        <v>1174.18</v>
+        <v>1174.07</v>
       </c>
       <c r="E132" t="n">
-        <v>1186.32</v>
+        <v>1186.2</v>
       </c>
       <c r="F132" t="n">
         <v>23893</v>
@@ -20216,13 +20216,13 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>1179.65</v>
+        <v>1179.46</v>
       </c>
       <c r="D133" t="n">
-        <v>1173.74</v>
+        <v>1173.55</v>
       </c>
       <c r="E133" t="n">
-        <v>1185.56</v>
+        <v>1185.37</v>
       </c>
       <c r="F133" t="n">
         <v>32836</v>
@@ -20367,13 +20367,13 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>1179.44</v>
+        <v>1179.3</v>
       </c>
       <c r="D134" t="n">
-        <v>1168.24</v>
+        <v>1168.1</v>
       </c>
       <c r="E134" t="n">
-        <v>1190.64</v>
+        <v>1190.5</v>
       </c>
       <c r="F134" t="n">
         <v>3191</v>
@@ -20518,13 +20518,13 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>1178.18</v>
+        <v>1178.01</v>
       </c>
       <c r="D135" t="n">
-        <v>1168.36</v>
+        <v>1168.18</v>
       </c>
       <c r="E135" t="n">
-        <v>1188.01</v>
+        <v>1187.84</v>
       </c>
       <c r="F135" t="n">
         <v>6534</v>
@@ -20669,13 +20669,13 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>1175.32</v>
+        <v>1175.12</v>
       </c>
       <c r="D136" t="n">
-        <v>1164.88</v>
+        <v>1164.69</v>
       </c>
       <c r="E136" t="n">
-        <v>1185.75</v>
+        <v>1185.56</v>
       </c>
       <c r="F136" t="n">
         <v>5006</v>
@@ -20820,13 +20820,13 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>1172.96</v>
+        <v>1172.78</v>
       </c>
       <c r="D137" t="n">
-        <v>1166.75</v>
+        <v>1166.57</v>
       </c>
       <c r="E137" t="n">
-        <v>1179.17</v>
+        <v>1178.99</v>
       </c>
       <c r="F137" t="n">
         <v>22479</v>
@@ -20971,13 +20971,13 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>1171.73</v>
+        <v>1171.59</v>
       </c>
       <c r="D138" t="n">
-        <v>1164.31</v>
+        <v>1164.18</v>
       </c>
       <c r="E138" t="n">
-        <v>1179.14</v>
+        <v>1179.01</v>
       </c>
       <c r="F138" t="n">
         <v>16057</v>
@@ -21122,13 +21122,13 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>1171.32</v>
+        <v>1171.16</v>
       </c>
       <c r="D139" t="n">
-        <v>1165.41</v>
+        <v>1165.25</v>
       </c>
       <c r="E139" t="n">
-        <v>1177.23</v>
+        <v>1177.07</v>
       </c>
       <c r="F139" t="n">
         <v>17763</v>
@@ -21273,13 +21273,13 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>1170.95</v>
+        <v>1170.79</v>
       </c>
       <c r="D140" t="n">
-        <v>1165.44</v>
+        <v>1165.29</v>
       </c>
       <c r="E140" t="n">
-        <v>1176.45</v>
+        <v>1176.29</v>
       </c>
       <c r="F140" t="n">
         <v>38491</v>
@@ -21424,13 +21424,13 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>1167.68</v>
+        <v>1167.52</v>
       </c>
       <c r="D141" t="n">
-        <v>1159.61</v>
+        <v>1159.44</v>
       </c>
       <c r="E141" t="n">
-        <v>1175.76</v>
+        <v>1175.59</v>
       </c>
       <c r="F141" t="n">
         <v>10224</v>
@@ -21575,13 +21575,13 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>1166.75</v>
+        <v>1166.61</v>
       </c>
       <c r="D142" t="n">
-        <v>1159.06</v>
+        <v>1158.92</v>
       </c>
       <c r="E142" t="n">
-        <v>1174.44</v>
+        <v>1174.3</v>
       </c>
       <c r="F142" t="n">
         <v>7936</v>
@@ -21726,13 +21726,13 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>1164.82</v>
+        <v>1164.66</v>
       </c>
       <c r="D143" t="n">
-        <v>1152.87</v>
+        <v>1152.71</v>
       </c>
       <c r="E143" t="n">
-        <v>1176.77</v>
+        <v>1176.62</v>
       </c>
       <c r="F143" t="n">
         <v>3776</v>
@@ -21877,13 +21877,13 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>1157.09</v>
+        <v>1157</v>
       </c>
       <c r="D144" t="n">
-        <v>1145.58</v>
+        <v>1145.49</v>
       </c>
       <c r="E144" t="n">
-        <v>1168.6</v>
+        <v>1168.51</v>
       </c>
       <c r="F144" t="n">
         <v>3233</v>
@@ -22028,13 +22028,13 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>1156.11</v>
+        <v>1155.93</v>
       </c>
       <c r="D145" t="n">
-        <v>1147.71</v>
+        <v>1147.54</v>
       </c>
       <c r="E145" t="n">
-        <v>1164.5</v>
+        <v>1164.32</v>
       </c>
       <c r="F145" t="n">
         <v>6837</v>
@@ -22179,13 +22179,13 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>1155.48</v>
+        <v>1155.29</v>
       </c>
       <c r="D146" t="n">
-        <v>1142.85</v>
+        <v>1142.66</v>
       </c>
       <c r="E146" t="n">
-        <v>1168.12</v>
+        <v>1167.93</v>
       </c>
       <c r="F146" t="n">
         <v>3584</v>
@@ -22330,13 +22330,13 @@
         </is>
       </c>
       <c r="C147" t="n">
-        <v>1152.53</v>
+        <v>1152.34</v>
       </c>
       <c r="D147" t="n">
-        <v>1139.3</v>
+        <v>1139.11</v>
       </c>
       <c r="E147" t="n">
-        <v>1165.75</v>
+        <v>1165.56</v>
       </c>
       <c r="F147" t="n">
         <v>4155</v>
@@ -22481,13 +22481,13 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>1152.13</v>
+        <v>1151.95</v>
       </c>
       <c r="D148" t="n">
-        <v>1136.72</v>
+        <v>1136.54</v>
       </c>
       <c r="E148" t="n">
-        <v>1167.55</v>
+        <v>1167.37</v>
       </c>
       <c r="F148" t="n">
         <v>1679</v>
@@ -22632,13 +22632,13 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>1150.28</v>
+        <v>1150.09</v>
       </c>
       <c r="D149" t="n">
-        <v>1137.97</v>
+        <v>1137.78</v>
       </c>
       <c r="E149" t="n">
-        <v>1162.6</v>
+        <v>1162.41</v>
       </c>
       <c r="F149" t="n">
         <v>2571</v>
@@ -22783,13 +22783,13 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>1149.78</v>
+        <v>1149.61</v>
       </c>
       <c r="D150" t="n">
-        <v>1143.13</v>
+        <v>1142.96</v>
       </c>
       <c r="E150" t="n">
-        <v>1156.44</v>
+        <v>1156.26</v>
       </c>
       <c r="F150" t="n">
         <v>19402</v>
@@ -22934,13 +22934,13 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>1149.3</v>
+        <v>1149.12</v>
       </c>
       <c r="D151" t="n">
-        <v>1140.03</v>
+        <v>1139.85</v>
       </c>
       <c r="E151" t="n">
-        <v>1158.58</v>
+        <v>1158.39</v>
       </c>
       <c r="F151" t="n">
         <v>7046</v>
@@ -23085,13 +23085,13 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>1147.16</v>
+        <v>1146.96</v>
       </c>
       <c r="D152" t="n">
-        <v>1130.01</v>
+        <v>1129.81</v>
       </c>
       <c r="E152" t="n">
-        <v>1164.32</v>
+        <v>1164.11</v>
       </c>
       <c r="F152" t="n">
         <v>1295</v>
@@ -23236,13 +23236,13 @@
         </is>
       </c>
       <c r="C153" t="n">
-        <v>1144.02</v>
+        <v>1143.86</v>
       </c>
       <c r="D153" t="n">
-        <v>1134.11</v>
+        <v>1133.96</v>
       </c>
       <c r="E153" t="n">
-        <v>1153.92</v>
+        <v>1153.76</v>
       </c>
       <c r="F153" t="n">
         <v>4735</v>
@@ -23387,13 +23387,13 @@
         </is>
       </c>
       <c r="C154" t="n">
-        <v>1143.16</v>
+        <v>1142.99</v>
       </c>
       <c r="D154" t="n">
-        <v>1136.72</v>
+        <v>1136.56</v>
       </c>
       <c r="E154" t="n">
-        <v>1149.59</v>
+        <v>1149.42</v>
       </c>
       <c r="F154" t="n">
         <v>12296</v>
@@ -23538,13 +23538,13 @@
         </is>
       </c>
       <c r="C155" t="n">
-        <v>1141.61</v>
+        <v>1141.46</v>
       </c>
       <c r="D155" t="n">
-        <v>1134.88</v>
+        <v>1134.73</v>
       </c>
       <c r="E155" t="n">
-        <v>1148.34</v>
+        <v>1148.18</v>
       </c>
       <c r="F155" t="n">
         <v>19171</v>
@@ -23689,13 +23689,13 @@
         </is>
       </c>
       <c r="C156" t="n">
-        <v>1141.06</v>
+        <v>1140.86</v>
       </c>
       <c r="D156" t="n">
-        <v>1134.34</v>
+        <v>1134.14</v>
       </c>
       <c r="E156" t="n">
-        <v>1147.77</v>
+        <v>1147.58</v>
       </c>
       <c r="F156" t="n">
         <v>19366</v>
@@ -23840,13 +23840,13 @@
         </is>
       </c>
       <c r="C157" t="n">
-        <v>1138.71</v>
+        <v>1138.51</v>
       </c>
       <c r="D157" t="n">
-        <v>1127.74</v>
+        <v>1127.53</v>
       </c>
       <c r="E157" t="n">
-        <v>1149.69</v>
+        <v>1149.48</v>
       </c>
       <c r="F157" t="n">
         <v>4964</v>
@@ -23991,13 +23991,13 @@
         </is>
       </c>
       <c r="C158" t="n">
-        <v>1136.73</v>
+        <v>1136.55</v>
       </c>
       <c r="D158" t="n">
-        <v>1127.82</v>
+        <v>1127.64</v>
       </c>
       <c r="E158" t="n">
-        <v>1145.64</v>
+        <v>1145.46</v>
       </c>
       <c r="F158" t="n">
         <v>7363</v>
@@ -24142,13 +24142,13 @@
         </is>
       </c>
       <c r="C159" t="n">
-        <v>1136.04</v>
+        <v>1135.91</v>
       </c>
       <c r="D159" t="n">
-        <v>1126.53</v>
+        <v>1126.4</v>
       </c>
       <c r="E159" t="n">
-        <v>1145.55</v>
+        <v>1145.43</v>
       </c>
       <c r="F159" t="n">
         <v>8925</v>
@@ -24293,13 +24293,13 @@
         </is>
       </c>
       <c r="C160" t="n">
-        <v>1131.22</v>
+        <v>1131.04</v>
       </c>
       <c r="D160" t="n">
-        <v>1122.37</v>
+        <v>1122.19</v>
       </c>
       <c r="E160" t="n">
-        <v>1140.07</v>
+        <v>1139.9</v>
       </c>
       <c r="F160" t="n">
         <v>11116</v>
@@ -24444,13 +24444,13 @@
         </is>
       </c>
       <c r="C161" t="n">
-        <v>1129.34</v>
+        <v>1129.15</v>
       </c>
       <c r="D161" t="n">
-        <v>1121.91</v>
+        <v>1121.73</v>
       </c>
       <c r="E161" t="n">
-        <v>1136.76</v>
+        <v>1136.58</v>
       </c>
       <c r="F161" t="n">
         <v>20691</v>
@@ -24595,13 +24595,13 @@
         </is>
       </c>
       <c r="C162" t="n">
-        <v>1128.5</v>
+        <v>1128.34</v>
       </c>
       <c r="D162" t="n">
-        <v>1122.1</v>
+        <v>1121.94</v>
       </c>
       <c r="E162" t="n">
-        <v>1134.89</v>
+        <v>1134.73</v>
       </c>
       <c r="F162" t="n">
         <v>20115</v>
@@ -24746,13 +24746,13 @@
         </is>
       </c>
       <c r="C163" t="n">
-        <v>1127.45</v>
+        <v>1127.26</v>
       </c>
       <c r="D163" t="n">
-        <v>1115.28</v>
+        <v>1115.09</v>
       </c>
       <c r="E163" t="n">
-        <v>1139.62</v>
+        <v>1139.43</v>
       </c>
       <c r="F163" t="n">
         <v>2921</v>
@@ -24897,13 +24897,13 @@
         </is>
       </c>
       <c r="C164" t="n">
-        <v>1127.05</v>
+        <v>1126.87</v>
       </c>
       <c r="D164" t="n">
-        <v>1111.36</v>
+        <v>1111.17</v>
       </c>
       <c r="E164" t="n">
-        <v>1142.74</v>
+        <v>1142.56</v>
       </c>
       <c r="F164" t="n">
         <v>1785</v>
@@ -25048,13 +25048,13 @@
         </is>
       </c>
       <c r="C165" t="n">
-        <v>1121.1</v>
+        <v>1120.9</v>
       </c>
       <c r="D165" t="n">
-        <v>1110.09</v>
+        <v>1109.9</v>
       </c>
       <c r="E165" t="n">
-        <v>1132.1</v>
+        <v>1131.91</v>
       </c>
       <c r="F165" t="n">
         <v>5184</v>
@@ -25199,13 +25199,13 @@
         </is>
       </c>
       <c r="C166" t="n">
-        <v>1119.1</v>
+        <v>1118.94</v>
       </c>
       <c r="D166" t="n">
-        <v>1100.86</v>
+        <v>1100.71</v>
       </c>
       <c r="E166" t="n">
-        <v>1137.33</v>
+        <v>1137.18</v>
       </c>
       <c r="F166" t="n">
         <v>1143</v>
@@ -25350,13 +25350,13 @@
         </is>
       </c>
       <c r="C167" t="n">
-        <v>1114.77</v>
+        <v>1114.57</v>
       </c>
       <c r="D167" t="n">
-        <v>1105.57</v>
+        <v>1105.38</v>
       </c>
       <c r="E167" t="n">
-        <v>1123.96</v>
+        <v>1123.76</v>
       </c>
       <c r="F167" t="n">
         <v>6923</v>
@@ -25501,13 +25501,13 @@
         </is>
       </c>
       <c r="C168" t="n">
-        <v>1114.44</v>
+        <v>1114.26</v>
       </c>
       <c r="D168" t="n">
-        <v>1100.01</v>
+        <v>1099.83</v>
       </c>
       <c r="E168" t="n">
-        <v>1128.86</v>
+        <v>1128.69</v>
       </c>
       <c r="F168" t="n">
         <v>2201</v>
@@ -25652,13 +25652,13 @@
         </is>
       </c>
       <c r="C169" t="n">
-        <v>1114.19</v>
+        <v>1114.08</v>
       </c>
       <c r="D169" t="n">
-        <v>1106.46</v>
+        <v>1106.34</v>
       </c>
       <c r="E169" t="n">
-        <v>1121.93</v>
+        <v>1121.81</v>
       </c>
       <c r="F169" t="n">
         <v>10853</v>
@@ -25803,13 +25803,13 @@
         </is>
       </c>
       <c r="C170" t="n">
-        <v>1111.33</v>
+        <v>1111.19</v>
       </c>
       <c r="D170" t="n">
-        <v>1103.46</v>
+        <v>1103.32</v>
       </c>
       <c r="E170" t="n">
-        <v>1119.21</v>
+        <v>1119.06</v>
       </c>
       <c r="F170" t="n">
         <v>8045</v>
@@ -25954,13 +25954,13 @@
         </is>
       </c>
       <c r="C171" t="n">
-        <v>1109.78</v>
+        <v>1109.58</v>
       </c>
       <c r="D171" t="n">
-        <v>1100.47</v>
+        <v>1100.27</v>
       </c>
       <c r="E171" t="n">
-        <v>1119.08</v>
+        <v>1118.88</v>
       </c>
       <c r="F171" t="n">
         <v>8977</v>
@@ -26105,13 +26105,13 @@
         </is>
       </c>
       <c r="C172" t="n">
-        <v>1108.29</v>
+        <v>1108.14</v>
       </c>
       <c r="D172" t="n">
-        <v>1101.24</v>
+        <v>1101.08</v>
       </c>
       <c r="E172" t="n">
-        <v>1115.35</v>
+        <v>1115.2</v>
       </c>
       <c r="F172" t="n">
         <v>14148</v>
@@ -26256,13 +26256,13 @@
         </is>
       </c>
       <c r="C173" t="n">
-        <v>1091.68</v>
+        <v>1091.54</v>
       </c>
       <c r="D173" t="n">
-        <v>1080.15</v>
+        <v>1080.02</v>
       </c>
       <c r="E173" t="n">
-        <v>1103.2</v>
+        <v>1103.07</v>
       </c>
       <c r="F173" t="n">
         <v>4779</v>
@@ -26407,13 +26407,13 @@
         </is>
       </c>
       <c r="C174" t="n">
-        <v>1090.27</v>
+        <v>1090.06</v>
       </c>
       <c r="D174" t="n">
-        <v>1080.92</v>
+        <v>1080.71</v>
       </c>
       <c r="E174" t="n">
-        <v>1099.63</v>
+        <v>1099.42</v>
       </c>
       <c r="F174" t="n">
         <v>7598</v>
@@ -26558,20 +26558,20 @@
         </is>
       </c>
       <c r="C175" t="n">
-        <v>1074.72</v>
+        <v>1074.57</v>
       </c>
       <c r="D175" t="n">
-        <v>1063.52</v>
+        <v>1063.37</v>
       </c>
       <c r="E175" t="n">
-        <v>1085.92</v>
+        <v>1085.77</v>
       </c>
       <c r="F175" t="n">
         <v>6329</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Allen AI</t>
+          <t>Ai2</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -26709,13 +26709,13 @@
         </is>
       </c>
       <c r="C176" t="n">
-        <v>1070.54</v>
+        <v>1070.35</v>
       </c>
       <c r="D176" t="n">
-        <v>1060.57</v>
+        <v>1060.38</v>
       </c>
       <c r="E176" t="n">
-        <v>1080.51</v>
+        <v>1080.32</v>
       </c>
       <c r="F176" t="n">
         <v>6964</v>
@@ -26860,13 +26860,13 @@
         </is>
       </c>
       <c r="C177" t="n">
-        <v>1067.52</v>
+        <v>1067.28</v>
       </c>
       <c r="D177" t="n">
-        <v>1055.97</v>
+        <v>1055.74</v>
       </c>
       <c r="E177" t="n">
-        <v>1079.06</v>
+        <v>1078.83</v>
       </c>
       <c r="F177" t="n">
         <v>5745</v>
@@ -27011,13 +27011,13 @@
         </is>
       </c>
       <c r="C178" t="n">
-        <v>1066.06</v>
+        <v>1065.85</v>
       </c>
       <c r="D178" t="n">
-        <v>1050.75</v>
+        <v>1050.54</v>
       </c>
       <c r="E178" t="n">
-        <v>1081.38</v>
+        <v>1081.16</v>
       </c>
       <c r="F178" t="n">
         <v>1743</v>
@@ -27162,13 +27162,13 @@
         </is>
       </c>
       <c r="C179" t="n">
-        <v>1061.94</v>
+        <v>1061.73</v>
       </c>
       <c r="D179" t="n">
-        <v>1049.89</v>
+        <v>1049.68</v>
       </c>
       <c r="E179" t="n">
-        <v>1073.99</v>
+        <v>1073.78</v>
       </c>
       <c r="F179" t="n">
         <v>3925</v>
@@ -27313,13 +27313,13 @@
         </is>
       </c>
       <c r="C180" t="n">
-        <v>1056.17</v>
+        <v>1055.97</v>
       </c>
       <c r="D180" t="n">
-        <v>1044.47</v>
+        <v>1044.27</v>
       </c>
       <c r="E180" t="n">
-        <v>1067.86</v>
+        <v>1067.66</v>
       </c>
       <c r="F180" t="n">
         <v>4658</v>
@@ -27464,13 +27464,13 @@
         </is>
       </c>
       <c r="C181" t="n">
-        <v>1041.4</v>
+        <v>1041.2</v>
       </c>
       <c r="D181" t="n">
-        <v>1029.93</v>
+        <v>1029.73</v>
       </c>
       <c r="E181" t="n">
-        <v>1052.87</v>
+        <v>1052.67</v>
       </c>
       <c r="F181" t="n">
         <v>4845</v>
@@ -27615,13 +27615,13 @@
         </is>
       </c>
       <c r="C182" t="n">
-        <v>1024.3</v>
+        <v>1024.11</v>
       </c>
       <c r="D182" t="n">
-        <v>1010.65</v>
+        <v>1010.46</v>
       </c>
       <c r="E182" t="n">
-        <v>1037.95</v>
+        <v>1037.76</v>
       </c>
       <c r="F182" t="n">
         <v>2657</v>
@@ -27766,13 +27766,13 @@
         </is>
       </c>
       <c r="C183" t="n">
-        <v>1022.21</v>
+        <v>1022</v>
       </c>
       <c r="D183" t="n">
-        <v>1011.26</v>
+        <v>1011.05</v>
       </c>
       <c r="E183" t="n">
-        <v>1033.16</v>
+        <v>1032.95</v>
       </c>
       <c r="F183" t="n">
         <v>6311</v>
@@ -27917,13 +27917,13 @@
         </is>
       </c>
       <c r="C184" t="n">
-        <v>995.679</v>
+        <v>995.492</v>
       </c>
       <c r="D184" t="n">
-        <v>983.0309999999999</v>
+        <v>982.845</v>
       </c>
       <c r="E184" t="n">
-        <v>1008.33</v>
+        <v>1008.14</v>
       </c>
       <c r="F184" t="n">
         <v>4914</v>
@@ -28068,13 +28068,13 @@
         </is>
       </c>
       <c r="C185" t="n">
-        <v>991.39</v>
+        <v>991.198</v>
       </c>
       <c r="D185" t="n">
-        <v>978.929</v>
+        <v>978.739</v>
       </c>
       <c r="E185" t="n">
-        <v>1003.85</v>
+        <v>1003.66</v>
       </c>
       <c r="F185" t="n">
         <v>4203</v>
@@ -28219,13 +28219,13 @@
         </is>
       </c>
       <c r="C186" t="n">
-        <v>980.169</v>
+        <v>979.9400000000001</v>
       </c>
       <c r="D186" t="n">
-        <v>966.524</v>
+        <v>966.297</v>
       </c>
       <c r="E186" t="n">
-        <v>993.814</v>
+        <v>993.583</v>
       </c>
       <c r="F186" t="n">
         <v>3412</v>
@@ -28370,13 +28370,13 @@
         </is>
       </c>
       <c r="C187" t="n">
-        <v>972.227</v>
+        <v>972.002</v>
       </c>
       <c r="D187" t="n">
-        <v>956.271</v>
+        <v>956.048</v>
       </c>
       <c r="E187" t="n">
-        <v>988.182</v>
+        <v>987.955</v>
       </c>
       <c r="F187" t="n">
         <v>2391</v>
@@ -28521,13 +28521,13 @@
         </is>
       </c>
       <c r="C188" t="n">
-        <v>952.696</v>
+        <v>952.506</v>
       </c>
       <c r="D188" t="n">
-        <v>939.847</v>
+        <v>939.659</v>
       </c>
       <c r="E188" t="n">
-        <v>965.546</v>
+        <v>965.354</v>
       </c>
       <c r="F188" t="n">
         <v>3287</v>
@@ -29636,14 +29636,14 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>kimi-k2-0905-preview</t>
+          <t>deepseek-v3.1-thinking</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1000</v>
+        <v>685</v>
       </c>
       <c r="C16" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -29652,21 +29652,21 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>artificial_analysis</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>deepseek-v3.1-thinking</t>
+          <t>kimi-k2-0905-preview</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>685</v>
+        <v>1000</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -29675,7 +29675,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>artificial_analysis</t>
+          <t>override</t>
         </is>
       </c>
     </row>
@@ -29866,14 +29866,14 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>longcat-flash-chat</t>
+          <t>minimax-m2.5</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>560</v>
+        <v>230</v>
       </c>
       <c r="C26" t="n">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -29882,21 +29882,21 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>artificial_analysis</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>minimax-m2.5</t>
+          <t>longcat-flash-chat</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>230</v>
+        <v>560</v>
       </c>
       <c r="C27" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -29905,7 +29905,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>artificial_analysis</t>
+          <t>override</t>
         </is>
       </c>
     </row>
@@ -30004,38 +30004,38 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>step-3.5-flash</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
+          <t>mimo-v2-flash (non-thinking)</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>309</v>
+      </c>
+      <c r="C32" t="n">
+        <v>15</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>artificial_analysis</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>mimo-v2-flash (non-thinking)</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>309</v>
-      </c>
-      <c r="C33" t="n">
-        <v>15</v>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+          <t>step-3.5-flash</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>artificial_analysis</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -30272,18 +30272,18 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>gemma-3-27b-it</t>
+          <t>glm-4.7-flash</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>27.4</v>
+        <v>31.2</v>
       </c>
       <c r="C44" t="n">
-        <v>27.4</v>
+        <v>3</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>dense</t>
+          <t>moe</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -30295,18 +30295,18 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>glm-4.7-flash</t>
+          <t>gemma-3-27b-it</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>31.2</v>
+        <v>27.4</v>
       </c>
       <c r="C45" t="n">
-        <v>3</v>
+        <v>27.4</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>moe</t>
+          <t>dense</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -30479,18 +30479,18 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>minimax-m2</t>
+          <t>qwen3-32b</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>230</v>
+        <v>32.8</v>
       </c>
       <c r="C53" t="n">
-        <v>10</v>
+        <v>32.8</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>moe</t>
+          <t>dense</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -30502,18 +30502,18 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>qwen3-32b</t>
+          <t>minimax-m2</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>32.8</v>
+        <v>230</v>
       </c>
       <c r="C54" t="n">
-        <v>32.8</v>
+        <v>10</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>dense</t>
+          <t>moe</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">

--- a/arena_enrichment/output/arena_leaderboard_enriched.xlsx
+++ b/arena_enrichment/output/arena_leaderboard_enriched.xlsx
@@ -19633,123 +19633,43 @@
           <t>Apache-2.0</t>
         </is>
       </c>
-      <c r="I129" t="n">
-        <v>7</v>
-      </c>
-      <c r="J129" t="n">
-        <v>7</v>
-      </c>
-      <c r="K129" t="inlineStr">
-        <is>
-          <t>dense</t>
-        </is>
-      </c>
+      <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
       <c r="L129" t="inlineStr">
         <is>
-          <t>artificial_analysis</t>
-        </is>
-      </c>
-      <c r="M129" t="n">
-        <v>14</v>
-      </c>
-      <c r="N129" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="O129" t="n">
-        <v>7</v>
-      </c>
-      <c r="P129" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="Q129" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R129" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="S129" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="T129" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="U129" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="V129" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W129" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X129" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Y129" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z129" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AA129" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB129" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AC129" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AD129" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AE129" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AF129" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AG129" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr"/>
+      <c r="N129" t="inlineStr"/>
+      <c r="O129" t="inlineStr"/>
+      <c r="P129" t="inlineStr"/>
+      <c r="Q129" t="inlineStr"/>
+      <c r="R129" t="inlineStr"/>
+      <c r="S129" t="inlineStr"/>
+      <c r="T129" t="inlineStr"/>
+      <c r="U129" t="inlineStr"/>
+      <c r="V129" t="inlineStr"/>
+      <c r="W129" t="inlineStr"/>
+      <c r="X129" t="inlineStr"/>
+      <c r="Y129" t="inlineStr"/>
+      <c r="Z129" t="inlineStr"/>
+      <c r="AA129" t="inlineStr"/>
+      <c r="AB129" t="inlineStr"/>
+      <c r="AC129" t="inlineStr"/>
+      <c r="AD129" t="inlineStr"/>
+      <c r="AE129" t="inlineStr"/>
+      <c r="AF129" t="inlineStr"/>
+      <c r="AG129" t="inlineStr"/>
       <c r="AH129" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="AI129" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -19784,123 +19704,43 @@
           <t>Apache-2.0</t>
         </is>
       </c>
-      <c r="I130" t="n">
-        <v>7</v>
-      </c>
-      <c r="J130" t="n">
-        <v>7</v>
-      </c>
-      <c r="K130" t="inlineStr">
-        <is>
-          <t>dense</t>
-        </is>
-      </c>
+      <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
       <c r="L130" t="inlineStr">
         <is>
-          <t>artificial_analysis</t>
-        </is>
-      </c>
-      <c r="M130" t="n">
-        <v>14</v>
-      </c>
-      <c r="N130" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="O130" t="n">
-        <v>7</v>
-      </c>
-      <c r="P130" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="Q130" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R130" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="S130" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="T130" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="U130" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="V130" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W130" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X130" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Y130" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z130" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AA130" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB130" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AC130" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AD130" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AE130" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AF130" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AG130" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr"/>
+      <c r="N130" t="inlineStr"/>
+      <c r="O130" t="inlineStr"/>
+      <c r="P130" t="inlineStr"/>
+      <c r="Q130" t="inlineStr"/>
+      <c r="R130" t="inlineStr"/>
+      <c r="S130" t="inlineStr"/>
+      <c r="T130" t="inlineStr"/>
+      <c r="U130" t="inlineStr"/>
+      <c r="V130" t="inlineStr"/>
+      <c r="W130" t="inlineStr"/>
+      <c r="X130" t="inlineStr"/>
+      <c r="Y130" t="inlineStr"/>
+      <c r="Z130" t="inlineStr"/>
+      <c r="AA130" t="inlineStr"/>
+      <c r="AB130" t="inlineStr"/>
+      <c r="AC130" t="inlineStr"/>
+      <c r="AD130" t="inlineStr"/>
+      <c r="AE130" t="inlineStr"/>
+      <c r="AF130" t="inlineStr"/>
+      <c r="AG130" t="inlineStr"/>
       <c r="AH130" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="AI130" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -20237,123 +20077,43 @@
           <t>Apache 2.0</t>
         </is>
       </c>
-      <c r="I133" t="n">
-        <v>480</v>
-      </c>
-      <c r="J133" t="n">
-        <v>17</v>
-      </c>
-      <c r="K133" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+      <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr"/>
+      <c r="K133" t="inlineStr"/>
       <c r="L133" t="inlineStr">
         <is>
-          <t>artificial_analysis</t>
-        </is>
-      </c>
-      <c r="M133" t="n">
-        <v>960</v>
-      </c>
-      <c r="N133" t="n">
-        <v>1200</v>
-      </c>
-      <c r="O133" t="n">
-        <v>480</v>
-      </c>
-      <c r="P133" t="n">
-        <v>600</v>
-      </c>
-      <c r="Q133" t="n">
-        <v>240</v>
-      </c>
-      <c r="R133" t="n">
-        <v>300</v>
-      </c>
-      <c r="S133" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T133" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U133" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="V133" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W133" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X133" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Y133" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z133" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AA133" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AB133" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AC133" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AD133" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AE133" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AF133" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AG133" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr"/>
+      <c r="N133" t="inlineStr"/>
+      <c r="O133" t="inlineStr"/>
+      <c r="P133" t="inlineStr"/>
+      <c r="Q133" t="inlineStr"/>
+      <c r="R133" t="inlineStr"/>
+      <c r="S133" t="inlineStr"/>
+      <c r="T133" t="inlineStr"/>
+      <c r="U133" t="inlineStr"/>
+      <c r="V133" t="inlineStr"/>
+      <c r="W133" t="inlineStr"/>
+      <c r="X133" t="inlineStr"/>
+      <c r="Y133" t="inlineStr"/>
+      <c r="Z133" t="inlineStr"/>
+      <c r="AA133" t="inlineStr"/>
+      <c r="AB133" t="inlineStr"/>
+      <c r="AC133" t="inlineStr"/>
+      <c r="AD133" t="inlineStr"/>
+      <c r="AE133" t="inlineStr"/>
+      <c r="AF133" t="inlineStr"/>
+      <c r="AG133" t="inlineStr"/>
       <c r="AH133" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="AI133" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -22817,7 +22577,7 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>artificial_analysis</t>
+          <t>name_parsing</t>
         </is>
       </c>
       <c r="M150" t="n">
@@ -25988,7 +25748,7 @@
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>artificial_analysis</t>
+          <t>name_parsing</t>
         </is>
       </c>
       <c r="M171" t="n">
@@ -32214,20 +31974,12 @@
           <t>openchat-3.5-0106</t>
         </is>
       </c>
-      <c r="B129" t="n">
-        <v>7</v>
-      </c>
-      <c r="C129" t="n">
-        <v>7</v>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>dense</t>
-        </is>
-      </c>
+      <c r="B129" t="inlineStr"/>
+      <c r="C129" t="inlineStr"/>
+      <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr">
         <is>
-          <t>artificial_analysis</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -32237,20 +31989,12 @@
           <t>openchat-3.5</t>
         </is>
       </c>
-      <c r="B130" t="n">
-        <v>7</v>
-      </c>
-      <c r="C130" t="n">
-        <v>7</v>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>dense</t>
-        </is>
-      </c>
+      <c r="B130" t="inlineStr"/>
+      <c r="C130" t="inlineStr"/>
+      <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr">
         <is>
-          <t>artificial_analysis</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -32306,20 +32050,12 @@
           <t>snowflake-arctic-instruct</t>
         </is>
       </c>
-      <c r="B133" t="n">
-        <v>480</v>
-      </c>
-      <c r="C133" t="n">
-        <v>17</v>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+      <c r="B133" t="inlineStr"/>
+      <c r="C133" t="inlineStr"/>
+      <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr">
         <is>
-          <t>artificial_analysis</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -32710,7 +32446,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>artificial_analysis</t>
+          <t>name_parsing</t>
         </is>
       </c>
     </row>
@@ -33193,7 +32929,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>artificial_analysis</t>
+          <t>name_parsing</t>
         </is>
       </c>
     </row>

--- a/arena_enrichment/output/arena_leaderboard_enriched.xlsx
+++ b/arena_enrichment/output/arena_leaderboard_enriched.xlsx
@@ -675,16 +675,16 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>1454.42</v>
+        <v>1453.22</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1447.43</v>
+        <v>1446.27</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1461.4</v>
+        <v>1460.16</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>7429</v>
+        <v>7632</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
@@ -822,36 +822,36 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>qwen3.5-397b-a17b</t>
+          <t>kimi-k2.5-thinking</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>1451.88</v>
+        <v>1450.61</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1444.29</v>
+        <v>1444.72</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1459.48</v>
+        <v>1456.51</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>6056</v>
+        <v>12263</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Alibaba</t>
+          <t>Moonshot</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
+          <t>Modified MIT</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>397</v>
+        <v>1000</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
@@ -860,26 +860,26 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>artificial_analysis</t>
+          <t>override</t>
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>794</v>
+        <v>2000</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>992.5</v>
+        <v>2500</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>397</v>
+        <v>1000</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>496.2</v>
+        <v>1250</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>198.5</v>
+        <v>500</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>248.1</v>
+        <v>625</v>
       </c>
       <c r="S3" s="3" t="inlineStr">
         <is>
@@ -951,9 +951,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AG3" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AG3" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AH3" s="2" t="inlineStr">
@@ -973,36 +973,36 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>kimi-k2.5-thinking</t>
+          <t>qwen3.5-397b-a17b</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>1451.05</v>
+        <v>1449.8</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1445.11</v>
+        <v>1442.3</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1456.99</v>
+        <v>1457.3</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>12046</v>
+        <v>6296</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Moonshot</t>
+          <t>Alibaba</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Modified MIT</t>
+          <t>Apache 2.0</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>1000</v>
+        <v>397</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
@@ -1011,26 +1011,26 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>artificial_analysis</t>
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>2000</v>
+        <v>794</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>2500</v>
+        <v>992.5</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>1000</v>
+        <v>397</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>1250</v>
+        <v>496.2</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>500</v>
+        <v>198.5</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>625</v>
+        <v>248.1</v>
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
@@ -1102,9 +1102,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AG4" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AG4" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AH4" s="2" t="inlineStr">
@@ -1128,16 +1128,16 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>1440.76</v>
+        <v>1440.77</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1434.58</v>
+        <v>1434.59</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>1446.94</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>11934</v>
+        <v>11933</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
@@ -1279,16 +1279,16 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1433.32</v>
+        <v>1431.95</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1426.62</v>
+        <v>1425.35</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1440.01</v>
+        <v>1438.55</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>8101</v>
+        <v>8355</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
@@ -1430,16 +1430,16 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>1428.42</v>
+        <v>1428.93</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>1424.52</v>
+        <v>1425.04</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1432.32</v>
+        <v>1432.82</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>37080</v>
+        <v>37329</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
@@ -1581,16 +1581,16 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>1425.1</v>
+        <v>1425.07</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>1421.11</v>
+        <v>1421.08</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1429.09</v>
+        <v>1429.06</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>35097</v>
+        <v>35096</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
@@ -1732,16 +1732,16 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>1423.65</v>
+        <v>1423.64</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1417.16</v>
+        <v>1417.15</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1430.14</v>
+        <v>1430.13</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>11675</v>
+        <v>11674</v>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
@@ -1883,13 +1883,13 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>1423.31</v>
+        <v>1423.28</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>1416.72</v>
+        <v>1416.7</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1429.89</v>
+        <v>1429.86</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>8943</v>
@@ -2030,20 +2030,20 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>qwen3.5-122b-a10b</t>
+          <t>qwen3-235b-a22b-instruct-2507</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>1423.14</v>
+        <v>1422.3</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>1410.98</v>
+        <v>1419.3</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1435.3</v>
+        <v>1425.3</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>2221</v>
+        <v>72786</v>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
@@ -2056,10 +2056,10 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>125</v>
+        <v>235</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
@@ -2072,22 +2072,22 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>250</v>
+        <v>470</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>312.5</v>
+        <v>587.5</v>
       </c>
       <c r="O11" s="2" t="n">
-        <v>125</v>
+        <v>235</v>
       </c>
       <c r="P11" s="2" t="n">
-        <v>156.2</v>
+        <v>293.8</v>
       </c>
       <c r="Q11" s="2" t="n">
-        <v>62.5</v>
+        <v>117.5</v>
       </c>
       <c r="R11" s="2" t="n">
-        <v>78.09999999999999</v>
+        <v>146.9</v>
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
@@ -2099,9 +2099,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="U11" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="U11" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="V11" s="3" t="inlineStr">
@@ -2114,9 +2114,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="X11" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="X11" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
@@ -2129,9 +2129,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AA11" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AA11" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AB11" s="3" t="inlineStr">
@@ -2139,9 +2139,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AC11" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AC11" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AD11" s="4" t="inlineStr">
@@ -2154,9 +2154,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AF11" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AF11" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AG11" s="4" t="inlineStr">
@@ -2171,7 +2171,7 @@
       </c>
       <c r="AI11" s="2" t="inlineStr">
         <is>
-          <t>B200 SXM</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
     </row>
@@ -2181,36 +2181,36 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>qwen3-235b-a22b-instruct-2507</t>
+          <t>deepseek-v3.2</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1422.46</v>
+        <v>1421</v>
       </c>
       <c r="D12" t="n">
-        <v>1419.45</v>
+        <v>1416.68</v>
       </c>
       <c r="E12" t="n">
-        <v>1425.47</v>
+        <v>1425.32</v>
       </c>
       <c r="F12" t="n">
-        <v>72533</v>
+        <v>32019</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alibaba</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>235</v>
+        <v>685</v>
       </c>
       <c r="J12" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -2223,22 +2223,22 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>470</v>
+        <v>1370</v>
       </c>
       <c r="N12" t="n">
-        <v>587.5</v>
+        <v>1712.5</v>
       </c>
       <c r="O12" t="n">
-        <v>235</v>
+        <v>685</v>
       </c>
       <c r="P12" t="n">
-        <v>293.8</v>
+        <v>856.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>117.5</v>
+        <v>342.5</v>
       </c>
       <c r="R12" t="n">
-        <v>146.9</v>
+        <v>428.1</v>
       </c>
       <c r="S12" s="5" t="inlineStr">
         <is>
@@ -2295,9 +2295,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AD12" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AD12" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AE12" s="5" t="inlineStr">
@@ -2310,9 +2310,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AG12" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AG12" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
@@ -2332,36 +2332,36 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>deepseek-v3.2</t>
+          <t>qwen3.5-122b-a10b</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1420.73</v>
+        <v>1419.86</v>
       </c>
       <c r="D13" t="n">
-        <v>1416.4</v>
+        <v>1408.87</v>
       </c>
       <c r="E13" t="n">
-        <v>1425.07</v>
+        <v>1430.84</v>
       </c>
       <c r="F13" t="n">
-        <v>31778</v>
+        <v>2743</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>DeepSeek</t>
+          <t>Alibaba</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Apache 2.0</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>685</v>
+        <v>125</v>
       </c>
       <c r="J13" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -2374,22 +2374,22 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>1370</v>
+        <v>250</v>
       </c>
       <c r="N13" t="n">
-        <v>1712.5</v>
+        <v>312.5</v>
       </c>
       <c r="O13" t="n">
-        <v>685</v>
+        <v>125</v>
       </c>
       <c r="P13" t="n">
-        <v>856.2</v>
+        <v>156.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>342.5</v>
+        <v>62.5</v>
       </c>
       <c r="R13" t="n">
-        <v>428.1</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="S13" s="5" t="inlineStr">
         <is>
@@ -2401,9 +2401,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="U13" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="U13" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="V13" s="5" t="inlineStr">
@@ -2416,9 +2416,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="X13" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="X13" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Y13" s="5" t="inlineStr">
@@ -2431,9 +2431,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AA13" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AA13" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AB13" s="5" t="inlineStr">
@@ -2441,14 +2441,14 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AC13" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AD13" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AC13" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AD13" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AE13" s="5" t="inlineStr">
@@ -2456,14 +2456,14 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AF13" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AG13" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AF13" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AG13" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
@@ -2473,7 +2473,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>B200 SXM</t>
         </is>
       </c>
     </row>
@@ -2487,16 +2487,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1419.77</v>
+        <v>1419.78</v>
       </c>
       <c r="D14" t="n">
-        <v>1415.32</v>
+        <v>1415.35</v>
       </c>
       <c r="E14" t="n">
         <v>1424.22</v>
       </c>
       <c r="F14" t="n">
-        <v>26665</v>
+        <v>26885</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1419.27</v>
+        <v>1419.28</v>
       </c>
       <c r="D15" t="n">
         <v>1413.67</v>
@@ -2647,7 +2647,7 @@
         <v>1424.88</v>
       </c>
       <c r="F15" t="n">
-        <v>19155</v>
+        <v>19154</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -2789,16 +2789,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1418.17</v>
+        <v>1418.14</v>
       </c>
       <c r="D16" t="n">
-        <v>1412.18</v>
+        <v>1412.14</v>
       </c>
       <c r="E16" t="n">
-        <v>1424.17</v>
+        <v>1424.13</v>
       </c>
       <c r="F16" t="n">
-        <v>15195</v>
+        <v>15194</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -2936,36 +2936,36 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>deepseek-v3.1-thinking</t>
+          <t>kimi-k2-0905-preview</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1417.12</v>
+        <v>1417.1</v>
       </c>
       <c r="D17" t="n">
-        <v>1410.53</v>
+        <v>1410.63</v>
       </c>
       <c r="E17" t="n">
-        <v>1423.71</v>
+        <v>1423.58</v>
       </c>
       <c r="F17" t="n">
-        <v>11918</v>
+        <v>11909</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>DeepSeek</t>
+          <t>Moonshot</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Modified MIT</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>685</v>
+        <v>1000</v>
       </c>
       <c r="J17" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -2974,26 +2974,26 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>artificial_analysis</t>
+          <t>override</t>
         </is>
       </c>
       <c r="M17" t="n">
-        <v>1370</v>
+        <v>2000</v>
       </c>
       <c r="N17" t="n">
-        <v>1712.5</v>
+        <v>2500</v>
       </c>
       <c r="O17" t="n">
-        <v>685</v>
+        <v>1000</v>
       </c>
       <c r="P17" t="n">
-        <v>856.2</v>
+        <v>1250</v>
       </c>
       <c r="Q17" t="n">
-        <v>342.5</v>
+        <v>500</v>
       </c>
       <c r="R17" t="n">
-        <v>428.1</v>
+        <v>625</v>
       </c>
       <c r="S17" s="5" t="inlineStr">
         <is>
@@ -3087,36 +3087,36 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>kimi-k2-0905-preview</t>
+          <t>deepseek-v3.1-thinking</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1417.08</v>
+        <v>1417.1</v>
       </c>
       <c r="D18" t="n">
-        <v>1410.6</v>
+        <v>1410.51</v>
       </c>
       <c r="E18" t="n">
-        <v>1423.55</v>
+        <v>1423.68</v>
       </c>
       <c r="F18" t="n">
-        <v>11910</v>
+        <v>11918</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Moonshot</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Modified MIT</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1000</v>
+        <v>685</v>
       </c>
       <c r="J18" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -3125,26 +3125,26 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>artificial_analysis</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>2000</v>
+        <v>1370</v>
       </c>
       <c r="N18" t="n">
-        <v>2500</v>
+        <v>1712.5</v>
       </c>
       <c r="O18" t="n">
-        <v>1000</v>
+        <v>685</v>
       </c>
       <c r="P18" t="n">
-        <v>1250</v>
+        <v>856.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>500</v>
+        <v>342.5</v>
       </c>
       <c r="R18" t="n">
-        <v>625</v>
+        <v>428.1</v>
       </c>
       <c r="S18" s="5" t="inlineStr">
         <is>
@@ -3242,16 +3242,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1416.6</v>
+        <v>1416.62</v>
       </c>
       <c r="D19" t="n">
-        <v>1411.78</v>
+        <v>1411.81</v>
       </c>
       <c r="E19" t="n">
-        <v>1421.41</v>
+        <v>1421.43</v>
       </c>
       <c r="F19" t="n">
-        <v>28432</v>
+        <v>28429</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -3393,13 +3393,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1416.12</v>
+        <v>1416.1</v>
       </c>
       <c r="D20" t="n">
-        <v>1406.55</v>
+        <v>1406.53</v>
       </c>
       <c r="E20" t="n">
-        <v>1425.69</v>
+        <v>1425.67</v>
       </c>
       <c r="F20" t="n">
         <v>3743</v>
@@ -3544,13 +3544,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1415.53</v>
+        <v>1415.5</v>
       </c>
       <c r="D21" t="n">
-        <v>1405.66</v>
+        <v>1405.64</v>
       </c>
       <c r="E21" t="n">
-        <v>1425.39</v>
+        <v>1425.37</v>
       </c>
       <c r="F21" t="n">
         <v>3536</v>
@@ -3691,24 +3691,24 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>mistral-large-3</t>
+          <t>qwen3-vl-235b-a22b-instruct</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1415.16</v>
+        <v>1414.66</v>
       </c>
       <c r="D22" t="n">
-        <v>1410.81</v>
+        <v>1408.18</v>
       </c>
       <c r="E22" t="n">
-        <v>1419.51</v>
+        <v>1421.13</v>
       </c>
       <c r="F22" t="n">
-        <v>28268</v>
+        <v>11594</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Mistral</t>
+          <t>Alibaba</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3717,10 +3717,10 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>675</v>
+        <v>235</v>
       </c>
       <c r="J22" t="n">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -3733,22 +3733,22 @@
         </is>
       </c>
       <c r="M22" t="n">
-        <v>1350</v>
+        <v>470</v>
       </c>
       <c r="N22" t="n">
-        <v>1687.5</v>
+        <v>587.5</v>
       </c>
       <c r="O22" t="n">
-        <v>675</v>
+        <v>235</v>
       </c>
       <c r="P22" t="n">
-        <v>843.8</v>
+        <v>293.8</v>
       </c>
       <c r="Q22" t="n">
-        <v>337.5</v>
+        <v>117.5</v>
       </c>
       <c r="R22" t="n">
-        <v>421.9</v>
+        <v>146.9</v>
       </c>
       <c r="S22" s="5" t="inlineStr">
         <is>
@@ -3805,9 +3805,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AD22" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AD22" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AE22" s="5" t="inlineStr">
@@ -3820,9 +3820,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AG22" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AG22" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
@@ -3842,24 +3842,24 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>qwen3-vl-235b-a22b-instruct</t>
+          <t>mistral-large-3</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1414.69</v>
+        <v>1414.63</v>
       </c>
       <c r="D23" t="n">
-        <v>1408.21</v>
+        <v>1410.3</v>
       </c>
       <c r="E23" t="n">
-        <v>1421.17</v>
+        <v>1418.96</v>
       </c>
       <c r="F23" t="n">
-        <v>11594</v>
+        <v>28519</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alibaba</t>
+          <t>Mistral</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3868,10 +3868,10 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>235</v>
+        <v>675</v>
       </c>
       <c r="J23" t="n">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -3884,22 +3884,22 @@
         </is>
       </c>
       <c r="M23" t="n">
-        <v>470</v>
+        <v>1350</v>
       </c>
       <c r="N23" t="n">
-        <v>587.5</v>
+        <v>1687.5</v>
       </c>
       <c r="O23" t="n">
-        <v>235</v>
+        <v>675</v>
       </c>
       <c r="P23" t="n">
-        <v>293.8</v>
+        <v>843.8</v>
       </c>
       <c r="Q23" t="n">
-        <v>117.5</v>
+        <v>337.5</v>
       </c>
       <c r="R23" t="n">
-        <v>146.9</v>
+        <v>421.9</v>
       </c>
       <c r="S23" s="5" t="inlineStr">
         <is>
@@ -3956,9 +3956,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AD23" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AD23" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AE23" s="5" t="inlineStr">
@@ -3971,9 +3971,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AG23" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AG23" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
@@ -3993,40 +3993,40 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>glm-4.5</t>
+          <t>qwen3.5-27b</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1410.12</v>
+        <v>1410.21</v>
       </c>
       <c r="D24" t="n">
-        <v>1405.25</v>
+        <v>1399.51</v>
       </c>
       <c r="E24" t="n">
-        <v>1415</v>
+        <v>1420.91</v>
       </c>
       <c r="F24" t="n">
-        <v>24593</v>
+        <v>2848</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Z.ai</t>
+          <t>Alibaba</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Apache 2.0</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>355</v>
+        <v>27.8</v>
       </c>
       <c r="J24" t="n">
-        <v>32</v>
+        <v>27.8</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>moe</t>
+          <t>dense</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -4035,91 +4035,91 @@
         </is>
       </c>
       <c r="M24" t="n">
-        <v>710</v>
+        <v>55.6</v>
       </c>
       <c r="N24" t="n">
-        <v>887.5</v>
+        <v>69.5</v>
       </c>
       <c r="O24" t="n">
-        <v>355</v>
+        <v>27.8</v>
       </c>
       <c r="P24" t="n">
-        <v>443.8</v>
+        <v>34.8</v>
       </c>
       <c r="Q24" t="n">
-        <v>177.5</v>
+        <v>13.9</v>
       </c>
       <c r="R24" t="n">
-        <v>221.9</v>
-      </c>
-      <c r="S24" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T24" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U24" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="V24" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W24" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X24" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Y24" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z24" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AA24" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AB24" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AC24" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AD24" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AE24" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AF24" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+        <v>17.4</v>
+      </c>
+      <c r="S24" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T24" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U24" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V24" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W24" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X24" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y24" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z24" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AA24" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB24" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AC24" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AD24" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE24" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AF24" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AG24" s="6" t="inlineStr">
@@ -4129,12 +4129,12 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>H100 SXM</t>
         </is>
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>H100 SXM</t>
         </is>
       </c>
     </row>
@@ -4144,40 +4144,40 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>qwen3.5-27b</t>
+          <t>glm-4.5</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1409.46</v>
+        <v>1410.08</v>
       </c>
       <c r="D25" t="n">
-        <v>1397.53</v>
+        <v>1405.21</v>
       </c>
       <c r="E25" t="n">
-        <v>1421.38</v>
+        <v>1414.95</v>
       </c>
       <c r="F25" t="n">
-        <v>2279</v>
+        <v>24594</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alibaba</t>
+          <t>Z.ai</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>27.8</v>
+        <v>355</v>
       </c>
       <c r="J25" t="n">
-        <v>27.8</v>
+        <v>32</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>dense</t>
+          <t>moe</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -4186,91 +4186,91 @@
         </is>
       </c>
       <c r="M25" t="n">
-        <v>55.6</v>
+        <v>710</v>
       </c>
       <c r="N25" t="n">
-        <v>69.5</v>
+        <v>887.5</v>
       </c>
       <c r="O25" t="n">
-        <v>27.8</v>
+        <v>355</v>
       </c>
       <c r="P25" t="n">
-        <v>34.8</v>
+        <v>443.8</v>
       </c>
       <c r="Q25" t="n">
-        <v>13.9</v>
+        <v>177.5</v>
       </c>
       <c r="R25" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="S25" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="T25" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="U25" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="V25" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W25" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X25" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Y25" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z25" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AA25" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB25" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AC25" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AD25" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AE25" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AF25" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+        <v>221.9</v>
+      </c>
+      <c r="S25" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T25" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U25" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V25" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W25" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X25" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y25" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z25" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA25" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AB25" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AC25" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD25" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE25" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF25" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AG25" s="6" t="inlineStr">
@@ -4280,12 +4280,12 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
     </row>
@@ -4299,16 +4299,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1401.88</v>
+        <v>1401.86</v>
       </c>
       <c r="D26" t="n">
-        <v>1397.42</v>
+        <v>1397.4</v>
       </c>
       <c r="E26" t="n">
-        <v>1406.35</v>
+        <v>1406.33</v>
       </c>
       <c r="F26" t="n">
-        <v>39274</v>
+        <v>39272</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -4450,16 +4450,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1401.78</v>
+        <v>1401.72</v>
       </c>
       <c r="D27" t="n">
-        <v>1396.96</v>
+        <v>1396.91</v>
       </c>
       <c r="E27" t="n">
-        <v>1406.59</v>
+        <v>1406.53</v>
       </c>
       <c r="F27" t="n">
-        <v>22667</v>
+        <v>22666</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -4601,16 +4601,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1400.47</v>
+        <v>1400.89</v>
       </c>
       <c r="D28" t="n">
-        <v>1393.24</v>
+        <v>1393.8</v>
       </c>
       <c r="E28" t="n">
-        <v>1407.7</v>
+        <v>1407.99</v>
       </c>
       <c r="F28" t="n">
-        <v>7188</v>
+        <v>7466</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -4752,16 +4752,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1400.09</v>
+        <v>1400.07</v>
       </c>
       <c r="D29" t="n">
-        <v>1393.73</v>
+        <v>1393.72</v>
       </c>
       <c r="E29" t="n">
-        <v>1406.44</v>
+        <v>1406.42</v>
       </c>
       <c r="F29" t="n">
-        <v>11486</v>
+        <v>11485</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -4912,7 +4912,7 @@
         <v>1405.06</v>
       </c>
       <c r="F30" t="n">
-        <v>9181</v>
+        <v>9179</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -5205,16 +5205,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1394.99</v>
+        <v>1395</v>
       </c>
       <c r="D32" t="n">
-        <v>1388.19</v>
+        <v>1388.2</v>
       </c>
       <c r="E32" t="n">
         <v>1401.8</v>
       </c>
       <c r="F32" t="n">
-        <v>7920</v>
+        <v>7919</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -5356,13 +5356,13 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1394.06</v>
+        <v>1394.05</v>
       </c>
       <c r="D33" t="n">
-        <v>1390.21</v>
+        <v>1390.2</v>
       </c>
       <c r="E33" t="n">
-        <v>1397.92</v>
+        <v>1397.91</v>
       </c>
       <c r="F33" t="n">
         <v>46412</v>
@@ -5507,16 +5507,16 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1393.05</v>
+        <v>1392.39</v>
       </c>
       <c r="D34" t="n">
-        <v>1381.02</v>
+        <v>1381.51</v>
       </c>
       <c r="E34" t="n">
-        <v>1405.07</v>
+        <v>1403.28</v>
       </c>
       <c r="F34" t="n">
-        <v>2315</v>
+        <v>2876</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -5658,16 +5658,16 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1390.61</v>
+        <v>1391.05</v>
       </c>
       <c r="D35" t="n">
-        <v>1385.82</v>
+        <v>1386.29</v>
       </c>
       <c r="E35" t="n">
-        <v>1395.4</v>
+        <v>1395.82</v>
       </c>
       <c r="F35" t="n">
-        <v>20736</v>
+        <v>20996</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -5809,16 +5809,16 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1387.49</v>
+        <v>1386.91</v>
       </c>
       <c r="D36" t="n">
-        <v>1381.12</v>
+        <v>1380.6</v>
       </c>
       <c r="E36" t="n">
-        <v>1393.85</v>
+        <v>1393.22</v>
       </c>
       <c r="F36" t="n">
-        <v>9652</v>
+        <v>9917</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -5880,13 +5880,13 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1386.51</v>
+        <v>1386.54</v>
       </c>
       <c r="D37" t="n">
-        <v>1380.18</v>
+        <v>1380.2</v>
       </c>
       <c r="E37" t="n">
-        <v>1392.85</v>
+        <v>1392.87</v>
       </c>
       <c r="F37" t="n">
         <v>10864</v>
@@ -6040,7 +6040,7 @@
         <v>1391.35</v>
       </c>
       <c r="F38" t="n">
-        <v>26402</v>
+        <v>26400</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -6182,16 +6182,16 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1385.09</v>
+        <v>1385.15</v>
       </c>
       <c r="D39" t="n">
-        <v>1379.77</v>
+        <v>1379.83</v>
       </c>
       <c r="E39" t="n">
-        <v>1390.41</v>
+        <v>1390.46</v>
       </c>
       <c r="F39" t="n">
-        <v>17069</v>
+        <v>17068</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -6333,13 +6333,13 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1383.64</v>
+        <v>1383.61</v>
       </c>
       <c r="D40" t="n">
-        <v>1378.77</v>
+        <v>1378.74</v>
       </c>
       <c r="E40" t="n">
-        <v>1388.51</v>
+        <v>1388.48</v>
       </c>
       <c r="F40" t="n">
         <v>23936</v>
@@ -6484,13 +6484,13 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1377.79</v>
+        <v>1377.81</v>
       </c>
       <c r="D41" t="n">
-        <v>1366.51</v>
+        <v>1366.53</v>
       </c>
       <c r="E41" t="n">
-        <v>1389.07</v>
+        <v>1389.09</v>
       </c>
       <c r="F41" t="n">
         <v>2785</v>
@@ -6635,16 +6635,16 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1375.92</v>
+        <v>1375.47</v>
       </c>
       <c r="D42" t="n">
-        <v>1365.49</v>
+        <v>1365.46</v>
       </c>
       <c r="E42" t="n">
-        <v>1386.36</v>
+        <v>1385.48</v>
       </c>
       <c r="F42" t="n">
-        <v>3340</v>
+        <v>3646</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -6786,16 +6786,16 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1374.65</v>
+        <v>1374.62</v>
       </c>
       <c r="D43" t="n">
-        <v>1369.98</v>
+        <v>1369.95</v>
       </c>
       <c r="E43" t="n">
-        <v>1379.32</v>
+        <v>1379.29</v>
       </c>
       <c r="F43" t="n">
-        <v>27003</v>
+        <v>27001</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -6937,16 +6937,16 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1371.72</v>
+        <v>1371.68</v>
       </c>
       <c r="D44" t="n">
-        <v>1367.46</v>
+        <v>1367.42</v>
       </c>
       <c r="E44" t="n">
-        <v>1375.98</v>
+        <v>1375.94</v>
       </c>
       <c r="F44" t="n">
-        <v>31142</v>
+        <v>31140</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -7088,13 +7088,13 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1368.84</v>
+        <v>1368.81</v>
       </c>
       <c r="D45" t="n">
-        <v>1363</v>
+        <v>1362.98</v>
       </c>
       <c r="E45" t="n">
-        <v>1374.67</v>
+        <v>1374.65</v>
       </c>
       <c r="F45" t="n">
         <v>13768</v>
@@ -7239,16 +7239,16 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1366.96</v>
+        <v>1366.91</v>
       </c>
       <c r="D46" t="n">
-        <v>1361.07</v>
+        <v>1361.02</v>
       </c>
       <c r="E46" t="n">
-        <v>1372.85</v>
+        <v>1372.79</v>
       </c>
       <c r="F46" t="n">
-        <v>11754</v>
+        <v>11752</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -7390,16 +7390,16 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1366.52</v>
+        <v>1366.56</v>
       </c>
       <c r="D47" t="n">
-        <v>1362.27</v>
+        <v>1362.31</v>
       </c>
       <c r="E47" t="n">
-        <v>1370.77</v>
+        <v>1370.81</v>
       </c>
       <c r="F47" t="n">
-        <v>36434</v>
+        <v>36433</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -7547,10 +7547,10 @@
         <v>1361.52</v>
       </c>
       <c r="E48" t="n">
-        <v>1368.82</v>
+        <v>1368.81</v>
       </c>
       <c r="F48" t="n">
-        <v>48424</v>
+        <v>48423</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -7843,13 +7843,13 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1356.14</v>
+        <v>1356.15</v>
       </c>
       <c r="D50" t="n">
-        <v>1347.73</v>
+        <v>1347.75</v>
       </c>
       <c r="E50" t="n">
-        <v>1364.55</v>
+        <v>1364.56</v>
       </c>
       <c r="F50" t="n">
         <v>5285</v>
@@ -7994,13 +7994,13 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1356.01</v>
+        <v>1356.06</v>
       </c>
       <c r="D51" t="n">
-        <v>1350.85</v>
+        <v>1350.9</v>
       </c>
       <c r="E51" t="n">
-        <v>1361.17</v>
+        <v>1361.22</v>
       </c>
       <c r="F51" t="n">
         <v>18223</v>
@@ -8145,13 +8145,13 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1353.98</v>
+        <v>1353.99</v>
       </c>
       <c r="D52" t="n">
-        <v>1349.61</v>
+        <v>1349.62</v>
       </c>
       <c r="E52" t="n">
-        <v>1358.34</v>
+        <v>1358.35</v>
       </c>
       <c r="F52" t="n">
         <v>30749</v>
@@ -8292,40 +8292,40 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>glm-4.5v</t>
+          <t>command-a-03-2025</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1352.96</v>
+        <v>1352.97</v>
       </c>
       <c r="D53" t="n">
-        <v>1344.6</v>
+        <v>1349.53</v>
       </c>
       <c r="E53" t="n">
-        <v>1361.33</v>
+        <v>1356.4</v>
       </c>
       <c r="F53" t="n">
-        <v>4949</v>
+        <v>57068</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Z.ai</t>
+          <t>Cohere</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>CC-BY-NC-4.0</t>
         </is>
       </c>
       <c r="I53" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="J53" t="n">
-        <v>12</v>
+        <v>111</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>moe</t>
+          <t>dense</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -8334,22 +8334,22 @@
         </is>
       </c>
       <c r="M53" t="n">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="N53" t="n">
-        <v>270</v>
+        <v>277.5</v>
       </c>
       <c r="O53" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="P53" t="n">
-        <v>135</v>
+        <v>138.8</v>
       </c>
       <c r="Q53" t="n">
-        <v>54</v>
+        <v>55.5</v>
       </c>
       <c r="R53" t="n">
-        <v>67.5</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="S53" s="5" t="inlineStr">
         <is>
@@ -8443,40 +8443,40 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>command-a-03-2025</t>
+          <t>glm-4.5v</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1352.94</v>
+        <v>1352.96</v>
       </c>
       <c r="D54" t="n">
-        <v>1349.51</v>
+        <v>1344.59</v>
       </c>
       <c r="E54" t="n">
-        <v>1356.38</v>
+        <v>1361.32</v>
       </c>
       <c r="F54" t="n">
-        <v>57071</v>
+        <v>4949</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cohere</t>
+          <t>Z.ai</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>CC-BY-NC-4.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="I54" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="J54" t="n">
-        <v>111</v>
+        <v>12</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>dense</t>
+          <t>moe</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -8485,22 +8485,22 @@
         </is>
       </c>
       <c r="M54" t="n">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="N54" t="n">
-        <v>277.5</v>
+        <v>270</v>
       </c>
       <c r="O54" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="P54" t="n">
-        <v>138.8</v>
+        <v>135</v>
       </c>
       <c r="Q54" t="n">
-        <v>55.5</v>
+        <v>54</v>
       </c>
       <c r="R54" t="n">
-        <v>69.40000000000001</v>
+        <v>67.5</v>
       </c>
       <c r="S54" s="5" t="inlineStr">
         <is>
@@ -8598,10 +8598,10 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1347.16</v>
+        <v>1347.17</v>
       </c>
       <c r="D55" t="n">
-        <v>1335.45</v>
+        <v>1335.46</v>
       </c>
       <c r="E55" t="n">
         <v>1358.87</v>
@@ -8749,13 +8749,13 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1347.04</v>
+        <v>1347</v>
       </c>
       <c r="D56" t="n">
-        <v>1339.78</v>
+        <v>1339.74</v>
       </c>
       <c r="E56" t="n">
-        <v>1354.31</v>
+        <v>1354.27</v>
       </c>
       <c r="F56" t="n">
         <v>6991</v>
@@ -8900,13 +8900,13 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1346.98</v>
+        <v>1346.96</v>
       </c>
       <c r="D57" t="n">
-        <v>1337.54</v>
+        <v>1337.52</v>
       </c>
       <c r="E57" t="n">
-        <v>1356.42</v>
+        <v>1356.4</v>
       </c>
       <c r="F57" t="n">
         <v>3932</v>
@@ -9051,13 +9051,13 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1346.75</v>
+        <v>1346.73</v>
       </c>
       <c r="D58" t="n">
-        <v>1338.92</v>
+        <v>1338.9</v>
       </c>
       <c r="E58" t="n">
-        <v>1354.58</v>
+        <v>1354.55</v>
       </c>
       <c r="F58" t="n">
         <v>6686</v>
@@ -9202,16 +9202,16 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1346.56</v>
+        <v>1346.53</v>
       </c>
       <c r="D59" t="n">
-        <v>1339.16</v>
+        <v>1339.13</v>
       </c>
       <c r="E59" t="n">
-        <v>1353.95</v>
+        <v>1353.92</v>
       </c>
       <c r="F59" t="n">
-        <v>6567</v>
+        <v>6566</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -9424,13 +9424,13 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1341.03</v>
+        <v>1341.02</v>
       </c>
       <c r="D61" t="n">
-        <v>1331.12</v>
+        <v>1331.11</v>
       </c>
       <c r="E61" t="n">
-        <v>1350.94</v>
+        <v>1350.93</v>
       </c>
       <c r="F61" t="n">
         <v>3398</v>
@@ -9575,16 +9575,16 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1335.77</v>
+        <v>1335.75</v>
       </c>
       <c r="D62" t="n">
-        <v>1331.38</v>
+        <v>1331.36</v>
       </c>
       <c r="E62" t="n">
-        <v>1340.16</v>
+        <v>1340.14</v>
       </c>
       <c r="F62" t="n">
-        <v>25987</v>
+        <v>25986</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -9726,13 +9726,13 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1334.96</v>
+        <v>1334.98</v>
       </c>
       <c r="D63" t="n">
-        <v>1331.3</v>
+        <v>1331.32</v>
       </c>
       <c r="E63" t="n">
-        <v>1338.62</v>
+        <v>1338.64</v>
       </c>
       <c r="F63" t="n">
         <v>41392</v>
@@ -9877,13 +9877,13 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1333.15</v>
+        <v>1333.17</v>
       </c>
       <c r="D64" t="n">
-        <v>1329.6</v>
+        <v>1329.62</v>
       </c>
       <c r="E64" t="n">
-        <v>1336.69</v>
+        <v>1336.72</v>
       </c>
       <c r="F64" t="n">
         <v>59655</v>
@@ -10028,7 +10028,7 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1330.5</v>
+        <v>1330.51</v>
       </c>
       <c r="D65" t="n">
         <v>1324.35</v>
@@ -10037,7 +10037,7 @@
         <v>1336.66</v>
       </c>
       <c r="F65" t="n">
-        <v>12238</v>
+        <v>12234</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -10179,16 +10179,16 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1328.65</v>
+        <v>1328.83</v>
       </c>
       <c r="D66" t="n">
-        <v>1307.23</v>
+        <v>1307.44</v>
       </c>
       <c r="E66" t="n">
-        <v>1350.06</v>
+        <v>1350.22</v>
       </c>
       <c r="F66" t="n">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -10330,13 +10330,13 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1328.08</v>
+        <v>1328.07</v>
       </c>
       <c r="D67" t="n">
-        <v>1323.39</v>
+        <v>1323.38</v>
       </c>
       <c r="E67" t="n">
-        <v>1332.77</v>
+        <v>1332.75</v>
       </c>
       <c r="F67" t="n">
         <v>27264</v>
@@ -10481,13 +10481,13 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1327.42</v>
+        <v>1327.44</v>
       </c>
       <c r="D68" t="n">
-        <v>1323.22</v>
+        <v>1323.23</v>
       </c>
       <c r="E68" t="n">
-        <v>1331.63</v>
+        <v>1331.65</v>
       </c>
       <c r="F68" t="n">
         <v>40914</v>
@@ -10934,16 +10934,16 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1322.24</v>
+        <v>1322.25</v>
       </c>
       <c r="D71" t="n">
-        <v>1317.57</v>
+        <v>1317.58</v>
       </c>
       <c r="E71" t="n">
-        <v>1326.91</v>
+        <v>1326.93</v>
       </c>
       <c r="F71" t="n">
-        <v>31030</v>
+        <v>31029</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -11085,13 +11085,13 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1320.35</v>
+        <v>1320.32</v>
       </c>
       <c r="D72" t="n">
-        <v>1313.14</v>
+        <v>1313.1</v>
       </c>
       <c r="E72" t="n">
-        <v>1327.56</v>
+        <v>1327.53</v>
       </c>
       <c r="F72" t="n">
         <v>7148</v>
@@ -11236,16 +11236,16 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1319.25</v>
+        <v>1319.24</v>
       </c>
       <c r="D73" t="n">
-        <v>1314.15</v>
+        <v>1314.14</v>
       </c>
       <c r="E73" t="n">
         <v>1324.34</v>
       </c>
       <c r="F73" t="n">
-        <v>23181</v>
+        <v>23179</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -11387,16 +11387,16 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1319.02</v>
+        <v>1319.04</v>
       </c>
       <c r="D74" t="n">
-        <v>1315.61</v>
+        <v>1315.63</v>
       </c>
       <c r="E74" t="n">
-        <v>1322.43</v>
+        <v>1322.45</v>
       </c>
       <c r="F74" t="n">
-        <v>55438</v>
+        <v>55436</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -11538,13 +11538,13 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>1317.89</v>
+        <v>1317.9</v>
       </c>
       <c r="D75" t="n">
         <v>1312.22</v>
       </c>
       <c r="E75" t="n">
-        <v>1323.57</v>
+        <v>1323.58</v>
       </c>
       <c r="F75" t="n">
         <v>16479</v>
@@ -11609,16 +11609,16 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>1317.23</v>
+        <v>1317.24</v>
       </c>
       <c r="D76" t="n">
-        <v>1311.6</v>
+        <v>1311.61</v>
       </c>
       <c r="E76" t="n">
-        <v>1322.87</v>
+        <v>1322.88</v>
       </c>
       <c r="F76" t="n">
-        <v>15394</v>
+        <v>15393</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -11760,10 +11760,10 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1316.99</v>
+        <v>1317</v>
       </c>
       <c r="D77" t="n">
-        <v>1310.64</v>
+        <v>1310.65</v>
       </c>
       <c r="E77" t="n">
         <v>1323.34</v>
@@ -11911,13 +11911,13 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1314.34</v>
+        <v>1314.33</v>
       </c>
       <c r="D78" t="n">
-        <v>1309.83</v>
+        <v>1309.82</v>
       </c>
       <c r="E78" t="n">
-        <v>1318.85</v>
+        <v>1318.84</v>
       </c>
       <c r="F78" t="n">
         <v>24746</v>
@@ -12062,13 +12062,13 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>1313.8</v>
+        <v>1313.82</v>
       </c>
       <c r="D79" t="n">
-        <v>1309.92</v>
+        <v>1309.94</v>
       </c>
       <c r="E79" t="n">
-        <v>1317.69</v>
+        <v>1317.71</v>
       </c>
       <c r="F79" t="n">
         <v>45460</v>
@@ -12213,13 +12213,13 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1306.86</v>
+        <v>1306.87</v>
       </c>
       <c r="D80" t="n">
-        <v>1302.19</v>
+        <v>1302.2</v>
       </c>
       <c r="E80" t="n">
-        <v>1311.53</v>
+        <v>1311.54</v>
       </c>
       <c r="F80" t="n">
         <v>24574</v>
@@ -12364,13 +12364,13 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1305.86</v>
+        <v>1305.89</v>
       </c>
       <c r="D81" t="n">
-        <v>1300.21</v>
+        <v>1300.24</v>
       </c>
       <c r="E81" t="n">
-        <v>1311.51</v>
+        <v>1311.54</v>
       </c>
       <c r="F81" t="n">
         <v>19622</v>
@@ -12515,16 +12515,16 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>1305.73</v>
+        <v>1305.77</v>
       </c>
       <c r="D82" t="n">
-        <v>1297.46</v>
+        <v>1297.5</v>
       </c>
       <c r="E82" t="n">
-        <v>1313.99</v>
+        <v>1314.03</v>
       </c>
       <c r="F82" t="n">
-        <v>5864</v>
+        <v>5863</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -12666,13 +12666,13 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>1304.9</v>
+        <v>1304.91</v>
       </c>
       <c r="D83" t="n">
         <v>1300.52</v>
       </c>
       <c r="E83" t="n">
-        <v>1309.29</v>
+        <v>1309.3</v>
       </c>
       <c r="F83" t="n">
         <v>28081</v>
@@ -12971,7 +12971,7 @@
         <v>1303.19</v>
       </c>
       <c r="D85" t="n">
-        <v>1293.87</v>
+        <v>1293.88</v>
       </c>
       <c r="E85" t="n">
         <v>1312.5</v>
@@ -13125,7 +13125,7 @@
         <v>1298.48</v>
       </c>
       <c r="E86" t="n">
-        <v>1306.52</v>
+        <v>1306.53</v>
       </c>
       <c r="F86" t="n">
         <v>39409</v>
@@ -13421,13 +13421,13 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>1293.32</v>
+        <v>1293.33</v>
       </c>
       <c r="D88" t="n">
-        <v>1289.63</v>
+        <v>1289.64</v>
       </c>
       <c r="E88" t="n">
-        <v>1297</v>
+        <v>1297.02</v>
       </c>
       <c r="F88" t="n">
         <v>55234</v>
@@ -13572,13 +13572,13 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>1288.48</v>
+        <v>1288.5</v>
       </c>
       <c r="D89" t="n">
-        <v>1281.18</v>
+        <v>1281.2</v>
       </c>
       <c r="E89" t="n">
-        <v>1295.78</v>
+        <v>1295.8</v>
       </c>
       <c r="F89" t="n">
         <v>8659</v>
@@ -13723,13 +13723,13 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>1287.9</v>
+        <v>1287.94</v>
       </c>
       <c r="D90" t="n">
-        <v>1284.58</v>
+        <v>1284.61</v>
       </c>
       <c r="E90" t="n">
-        <v>1291.23</v>
+        <v>1291.27</v>
       </c>
       <c r="F90" t="n">
         <v>75764</v>
@@ -13874,16 +13874,16 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>1286.87</v>
+        <v>1286.92</v>
       </c>
       <c r="D91" t="n">
-        <v>1278.46</v>
+        <v>1278.5</v>
       </c>
       <c r="E91" t="n">
-        <v>1295.29</v>
+        <v>1295.34</v>
       </c>
       <c r="F91" t="n">
-        <v>5621</v>
+        <v>5620</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -14025,13 +14025,13 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>1286.37</v>
+        <v>1286.38</v>
       </c>
       <c r="D92" t="n">
-        <v>1275.89</v>
+        <v>1275.9</v>
       </c>
       <c r="E92" t="n">
-        <v>1296.84</v>
+        <v>1296.85</v>
       </c>
       <c r="F92" t="n">
         <v>2846</v>
@@ -14176,13 +14176,13 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>1286</v>
+        <v>1286.03</v>
       </c>
       <c r="D93" t="n">
-        <v>1276.03</v>
+        <v>1276.06</v>
       </c>
       <c r="E93" t="n">
-        <v>1295.98</v>
+        <v>1296.01</v>
       </c>
       <c r="F93" t="n">
         <v>3749</v>
@@ -14327,13 +14327,13 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1284.86</v>
+        <v>1284.88</v>
       </c>
       <c r="D94" t="n">
-        <v>1277.59</v>
+        <v>1277.62</v>
       </c>
       <c r="E94" t="n">
-        <v>1292.12</v>
+        <v>1292.15</v>
       </c>
       <c r="F94" t="n">
         <v>8435</v>
@@ -14478,13 +14478,13 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1279.29</v>
+        <v>1279.33</v>
       </c>
       <c r="D95" t="n">
-        <v>1272.44</v>
+        <v>1272.47</v>
       </c>
       <c r="E95" t="n">
-        <v>1286.14</v>
+        <v>1286.18</v>
       </c>
       <c r="F95" t="n">
         <v>10069</v>
@@ -14629,13 +14629,13 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>1277.1</v>
+        <v>1277.12</v>
       </c>
       <c r="D96" t="n">
-        <v>1271.78</v>
+        <v>1271.8</v>
       </c>
       <c r="E96" t="n">
-        <v>1282.42</v>
+        <v>1282.44</v>
       </c>
       <c r="F96" t="n">
         <v>19661</v>
@@ -14780,13 +14780,13 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1276.15</v>
+        <v>1276.17</v>
       </c>
       <c r="D97" t="n">
-        <v>1269.59</v>
+        <v>1269.61</v>
       </c>
       <c r="E97" t="n">
-        <v>1282.71</v>
+        <v>1282.73</v>
       </c>
       <c r="F97" t="n">
         <v>9869</v>
@@ -14931,13 +14931,13 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>1275.73</v>
+        <v>1275.76</v>
       </c>
       <c r="D98" t="n">
-        <v>1272.17</v>
+        <v>1272.2</v>
       </c>
       <c r="E98" t="n">
-        <v>1279.29</v>
+        <v>1279.32</v>
       </c>
       <c r="F98" t="n">
         <v>156880</v>
@@ -15082,13 +15082,13 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>1273.68</v>
+        <v>1273.69</v>
       </c>
       <c r="D99" t="n">
-        <v>1267.8</v>
+        <v>1267.81</v>
       </c>
       <c r="E99" t="n">
-        <v>1279.56</v>
+        <v>1279.57</v>
       </c>
       <c r="F99" t="n">
         <v>14677</v>
@@ -15233,13 +15233,13 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>1270.39</v>
+        <v>1270.4</v>
       </c>
       <c r="D100" t="n">
-        <v>1262.28</v>
+        <v>1262.29</v>
       </c>
       <c r="E100" t="n">
-        <v>1278.5</v>
+        <v>1278.51</v>
       </c>
       <c r="F100" t="n">
         <v>5430</v>
@@ -15384,13 +15384,13 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1266.87</v>
+        <v>1266.89</v>
       </c>
       <c r="D101" t="n">
-        <v>1262.02</v>
+        <v>1262.04</v>
       </c>
       <c r="E101" t="n">
-        <v>1271.71</v>
+        <v>1271.74</v>
       </c>
       <c r="F101" t="n">
         <v>27123</v>
@@ -15535,13 +15535,13 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>1265.32</v>
+        <v>1265.36</v>
       </c>
       <c r="D102" t="n">
-        <v>1261.56</v>
+        <v>1261.59</v>
       </c>
       <c r="E102" t="n">
-        <v>1269.09</v>
+        <v>1269.13</v>
       </c>
       <c r="F102" t="n">
         <v>54615</v>
@@ -15686,13 +15686,13 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>1263.95</v>
+        <v>1263.99</v>
       </c>
       <c r="D103" t="n">
-        <v>1257.68</v>
+        <v>1257.71</v>
       </c>
       <c r="E103" t="n">
-        <v>1270.23</v>
+        <v>1270.27</v>
       </c>
       <c r="F103" t="n">
         <v>15147</v>
@@ -15837,13 +15837,13 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>1261.6</v>
+        <v>1261.63</v>
       </c>
       <c r="D104" t="n">
-        <v>1257.29</v>
+        <v>1257.32</v>
       </c>
       <c r="E104" t="n">
-        <v>1265.91</v>
+        <v>1265.94</v>
       </c>
       <c r="F104" t="n">
         <v>77556</v>
@@ -15988,13 +15988,13 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>1261.53</v>
+        <v>1261.56</v>
       </c>
       <c r="D105" t="n">
-        <v>1256.6</v>
+        <v>1256.63</v>
       </c>
       <c r="E105" t="n">
-        <v>1266.46</v>
+        <v>1266.49</v>
       </c>
       <c r="F105" t="n">
         <v>37325</v>
@@ -16139,13 +16139,13 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>1255.91</v>
+        <v>1255.92</v>
       </c>
       <c r="D106" t="n">
-        <v>1251.36</v>
+        <v>1251.37</v>
       </c>
       <c r="E106" t="n">
-        <v>1260.46</v>
+        <v>1260.47</v>
       </c>
       <c r="F106" t="n">
         <v>24126</v>
@@ -16290,13 +16290,13 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>1251.8</v>
+        <v>1251.82</v>
       </c>
       <c r="D107" t="n">
-        <v>1241.02</v>
+        <v>1241.03</v>
       </c>
       <c r="E107" t="n">
-        <v>1262.59</v>
+        <v>1262.6</v>
       </c>
       <c r="F107" t="n">
         <v>3335</v>
@@ -16441,13 +16441,13 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>1249.92</v>
+        <v>1249.95</v>
       </c>
       <c r="D108" t="n">
-        <v>1243.33</v>
+        <v>1243.36</v>
       </c>
       <c r="E108" t="n">
-        <v>1256.51</v>
+        <v>1256.54</v>
       </c>
       <c r="F108" t="n">
         <v>10141</v>
@@ -16592,13 +16592,13 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>1238.74</v>
+        <v>1238.77</v>
       </c>
       <c r="D109" t="n">
-        <v>1231.53</v>
+        <v>1231.55</v>
       </c>
       <c r="E109" t="n">
-        <v>1245.96</v>
+        <v>1245.98</v>
       </c>
       <c r="F109" t="n">
         <v>8854</v>
@@ -16743,13 +16743,13 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>1236.86</v>
+        <v>1236.87</v>
       </c>
       <c r="D110" t="n">
-        <v>1227.76</v>
+        <v>1227.78</v>
       </c>
       <c r="E110" t="n">
-        <v>1245.95</v>
+        <v>1245.97</v>
       </c>
       <c r="F110" t="n">
         <v>4780</v>
@@ -16894,13 +16894,13 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>1233.72</v>
+        <v>1233.75</v>
       </c>
       <c r="D111" t="n">
-        <v>1228.17</v>
+        <v>1228.2</v>
       </c>
       <c r="E111" t="n">
-        <v>1239.26</v>
+        <v>1239.3</v>
       </c>
       <c r="F111" t="n">
         <v>26191</v>
@@ -17045,13 +17045,13 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>1232.85</v>
+        <v>1232.88</v>
       </c>
       <c r="D112" t="n">
-        <v>1227.58</v>
+        <v>1227.61</v>
       </c>
       <c r="E112" t="n">
-        <v>1238.12</v>
+        <v>1238.15</v>
       </c>
       <c r="F112" t="n">
         <v>39296</v>
@@ -17196,13 +17196,13 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>1229.17</v>
+        <v>1229.2</v>
       </c>
       <c r="D113" t="n">
-        <v>1224.63</v>
+        <v>1224.66</v>
       </c>
       <c r="E113" t="n">
-        <v>1233.71</v>
+        <v>1233.74</v>
       </c>
       <c r="F113" t="n">
         <v>51417</v>
@@ -17347,13 +17347,13 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>1226.62</v>
+        <v>1226.65</v>
       </c>
       <c r="D114" t="n">
-        <v>1221.85</v>
+        <v>1221.88</v>
       </c>
       <c r="E114" t="n">
-        <v>1231.4</v>
+        <v>1231.43</v>
       </c>
       <c r="F114" t="n">
         <v>54038</v>
@@ -17498,13 +17498,13 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>1222.88</v>
+        <v>1222.91</v>
       </c>
       <c r="D115" t="n">
-        <v>1219.17</v>
+        <v>1219.19</v>
       </c>
       <c r="E115" t="n">
-        <v>1226.59</v>
+        <v>1226.62</v>
       </c>
       <c r="F115" t="n">
         <v>104636</v>
@@ -17649,13 +17649,13 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>1222.85</v>
+        <v>1222.87</v>
       </c>
       <c r="D116" t="n">
-        <v>1215.9</v>
+        <v>1215.92</v>
       </c>
       <c r="E116" t="n">
-        <v>1229.8</v>
+        <v>1229.82</v>
       </c>
       <c r="F116" t="n">
         <v>9827</v>
@@ -17803,10 +17803,10 @@
         <v>1220.41</v>
       </c>
       <c r="D117" t="n">
-        <v>1209.7</v>
+        <v>1209.71</v>
       </c>
       <c r="E117" t="n">
-        <v>1231.11</v>
+        <v>1231.12</v>
       </c>
       <c r="F117" t="n">
         <v>2895</v>
@@ -17951,13 +17951,13 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>1213.1</v>
+        <v>1213.12</v>
       </c>
       <c r="D118" t="n">
-        <v>1208.08</v>
+        <v>1208.09</v>
       </c>
       <c r="E118" t="n">
-        <v>1218.13</v>
+        <v>1218.15</v>
       </c>
       <c r="F118" t="n">
         <v>24142</v>
@@ -18102,13 +18102,13 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>1212.42</v>
+        <v>1212.45</v>
       </c>
       <c r="D119" t="n">
-        <v>1201.6</v>
+        <v>1201.64</v>
       </c>
       <c r="E119" t="n">
-        <v>1223.23</v>
+        <v>1223.26</v>
       </c>
       <c r="F119" t="n">
         <v>4653</v>
@@ -18259,7 +18259,7 @@
         <v>1207.28</v>
       </c>
       <c r="E120" t="n">
-        <v>1215.48</v>
+        <v>1215.49</v>
       </c>
       <c r="F120" t="n">
         <v>49605</v>
@@ -18404,13 +18404,13 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>1208.27</v>
+        <v>1208.29</v>
       </c>
       <c r="D121" t="n">
-        <v>1197.16</v>
+        <v>1197.19</v>
       </c>
       <c r="E121" t="n">
-        <v>1219.37</v>
+        <v>1219.4</v>
       </c>
       <c r="F121" t="n">
         <v>3092</v>
@@ -18555,13 +18555,13 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>1203.56</v>
+        <v>1203.59</v>
       </c>
       <c r="D122" t="n">
-        <v>1197.45</v>
+        <v>1197.48</v>
       </c>
       <c r="E122" t="n">
-        <v>1209.68</v>
+        <v>1209.71</v>
       </c>
       <c r="F122" t="n">
         <v>21744</v>
@@ -18706,13 +18706,13 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>1198.62</v>
+        <v>1198.64</v>
       </c>
       <c r="D123" t="n">
-        <v>1194.57</v>
+        <v>1194.59</v>
       </c>
       <c r="E123" t="n">
-        <v>1202.67</v>
+        <v>1202.69</v>
       </c>
       <c r="F123" t="n">
         <v>46618</v>
@@ -18857,13 +18857,13 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>1197.65</v>
+        <v>1197.68</v>
       </c>
       <c r="D124" t="n">
-        <v>1192.51</v>
+        <v>1192.53</v>
       </c>
       <c r="E124" t="n">
-        <v>1202.8</v>
+        <v>1202.82</v>
       </c>
       <c r="F124" t="n">
         <v>25055</v>
@@ -19008,13 +19008,13 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>1196.81</v>
+        <v>1196.84</v>
       </c>
       <c r="D125" t="n">
-        <v>1192.55</v>
+        <v>1192.57</v>
       </c>
       <c r="E125" t="n">
-        <v>1201.07</v>
+        <v>1201.1</v>
       </c>
       <c r="F125" t="n">
         <v>73505</v>
@@ -19159,13 +19159,13 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>1194.61</v>
+        <v>1194.65</v>
       </c>
       <c r="D126" t="n">
-        <v>1188.5</v>
+        <v>1188.54</v>
       </c>
       <c r="E126" t="n">
-        <v>1200.72</v>
+        <v>1200.76</v>
       </c>
       <c r="F126" t="n">
         <v>32196</v>
@@ -19310,13 +19310,13 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>1191.09</v>
+        <v>1191.1</v>
       </c>
       <c r="D127" t="n">
-        <v>1183.92</v>
+        <v>1183.93</v>
       </c>
       <c r="E127" t="n">
-        <v>1198.26</v>
+        <v>1198.27</v>
       </c>
       <c r="F127" t="n">
         <v>9902</v>
@@ -19461,13 +19461,13 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>1190.53</v>
+        <v>1190.56</v>
       </c>
       <c r="D128" t="n">
-        <v>1183.41</v>
+        <v>1183.44</v>
       </c>
       <c r="E128" t="n">
-        <v>1197.66</v>
+        <v>1197.69</v>
       </c>
       <c r="F128" t="n">
         <v>17841</v>
@@ -19612,13 +19612,13 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>1184.32</v>
+        <v>1184.35</v>
       </c>
       <c r="D129" t="n">
-        <v>1174.86</v>
+        <v>1174.89</v>
       </c>
       <c r="E129" t="n">
-        <v>1193.78</v>
+        <v>1193.81</v>
       </c>
       <c r="F129" t="n">
         <v>8214</v>
@@ -19763,13 +19763,13 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>1184.02</v>
+        <v>1184.06</v>
       </c>
       <c r="D130" t="n">
-        <v>1172.5</v>
+        <v>1172.54</v>
       </c>
       <c r="E130" t="n">
-        <v>1195.54</v>
+        <v>1195.58</v>
       </c>
       <c r="F130" t="n">
         <v>4933</v>
@@ -19914,13 +19914,13 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>1183.5</v>
+        <v>1183.52</v>
       </c>
       <c r="D131" t="n">
-        <v>1176.67</v>
+        <v>1176.69</v>
       </c>
       <c r="E131" t="n">
-        <v>1190.32</v>
+        <v>1190.35</v>
       </c>
       <c r="F131" t="n">
         <v>15483</v>
@@ -20065,13 +20065,13 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>1181.94</v>
+        <v>1181.98</v>
       </c>
       <c r="D132" t="n">
-        <v>1173.93</v>
+        <v>1173.97</v>
       </c>
       <c r="E132" t="n">
-        <v>1189.95</v>
+        <v>1189.98</v>
       </c>
       <c r="F132" t="n">
         <v>12636</v>
@@ -20136,13 +20136,13 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>1181.87</v>
+        <v>1181.91</v>
       </c>
       <c r="D133" t="n">
-        <v>1172.18</v>
+        <v>1172.23</v>
       </c>
       <c r="E133" t="n">
-        <v>1191.55</v>
+        <v>1191.6</v>
       </c>
       <c r="F133" t="n">
         <v>7967</v>
@@ -20207,13 +20207,13 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>1181.6</v>
+        <v>1181.64</v>
       </c>
       <c r="D134" t="n">
-        <v>1172.91</v>
+        <v>1172.96</v>
       </c>
       <c r="E134" t="n">
-        <v>1190.28</v>
+        <v>1190.33</v>
       </c>
       <c r="F134" t="n">
         <v>6643</v>
@@ -20358,13 +20358,13 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>1179.94</v>
+        <v>1180</v>
       </c>
       <c r="D135" t="n">
-        <v>1173.87</v>
+        <v>1173.93</v>
       </c>
       <c r="E135" t="n">
-        <v>1186.01</v>
+        <v>1186.07</v>
       </c>
       <c r="F135" t="n">
         <v>23893</v>
@@ -20509,13 +20509,13 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>1179.12</v>
+        <v>1179.16</v>
       </c>
       <c r="D136" t="n">
-        <v>1173.21</v>
+        <v>1173.25</v>
       </c>
       <c r="E136" t="n">
-        <v>1185.03</v>
+        <v>1185.07</v>
       </c>
       <c r="F136" t="n">
         <v>32836</v>
@@ -20580,13 +20580,13 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>1179.03</v>
+        <v>1179.05</v>
       </c>
       <c r="D137" t="n">
-        <v>1167.83</v>
+        <v>1167.85</v>
       </c>
       <c r="E137" t="n">
-        <v>1190.22</v>
+        <v>1190.24</v>
       </c>
       <c r="F137" t="n">
         <v>3191</v>
@@ -20731,13 +20731,13 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>1177.7</v>
+        <v>1177.72</v>
       </c>
       <c r="D138" t="n">
-        <v>1167.87</v>
+        <v>1167.89</v>
       </c>
       <c r="E138" t="n">
-        <v>1187.53</v>
+        <v>1187.55</v>
       </c>
       <c r="F138" t="n">
         <v>6534</v>
@@ -20882,13 +20882,13 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>1174.79</v>
+        <v>1174.83</v>
       </c>
       <c r="D139" t="n">
-        <v>1164.35</v>
+        <v>1164.4</v>
       </c>
       <c r="E139" t="n">
-        <v>1185.22</v>
+        <v>1185.26</v>
       </c>
       <c r="F139" t="n">
         <v>5006</v>
@@ -21033,13 +21033,13 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>1172.45</v>
+        <v>1172.48</v>
       </c>
       <c r="D140" t="n">
-        <v>1166.24</v>
+        <v>1166.27</v>
       </c>
       <c r="E140" t="n">
-        <v>1178.66</v>
+        <v>1178.69</v>
       </c>
       <c r="F140" t="n">
         <v>22479</v>
@@ -21335,13 +21335,13 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>1170.86</v>
+        <v>1170.89</v>
       </c>
       <c r="D142" t="n">
-        <v>1164.95</v>
+        <v>1164.98</v>
       </c>
       <c r="E142" t="n">
-        <v>1176.77</v>
+        <v>1176.8</v>
       </c>
       <c r="F142" t="n">
         <v>17763</v>
@@ -21486,13 +21486,13 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>1170.47</v>
+        <v>1170.49</v>
       </c>
       <c r="D143" t="n">
-        <v>1164.97</v>
+        <v>1164.99</v>
       </c>
       <c r="E143" t="n">
-        <v>1175.98</v>
+        <v>1176</v>
       </c>
       <c r="F143" t="n">
         <v>38491</v>
@@ -21637,13 +21637,13 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>1167.19</v>
+        <v>1167.22</v>
       </c>
       <c r="D144" t="n">
-        <v>1159.12</v>
+        <v>1159.14</v>
       </c>
       <c r="E144" t="n">
-        <v>1175.27</v>
+        <v>1175.29</v>
       </c>
       <c r="F144" t="n">
         <v>10224</v>
@@ -21788,13 +21788,13 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>1166.38</v>
+        <v>1166.4</v>
       </c>
       <c r="D145" t="n">
-        <v>1158.69</v>
+        <v>1158.71</v>
       </c>
       <c r="E145" t="n">
-        <v>1174.07</v>
+        <v>1174.1</v>
       </c>
       <c r="F145" t="n">
         <v>7936</v>
@@ -21939,13 +21939,13 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>1164.36</v>
+        <v>1164.38</v>
       </c>
       <c r="D146" t="n">
-        <v>1152.41</v>
+        <v>1152.43</v>
       </c>
       <c r="E146" t="n">
-        <v>1176.31</v>
+        <v>1176.33</v>
       </c>
       <c r="F146" t="n">
         <v>3776</v>
@@ -22090,13 +22090,13 @@
         </is>
       </c>
       <c r="C147" t="n">
-        <v>1156.84</v>
+        <v>1156.82</v>
       </c>
       <c r="D147" t="n">
-        <v>1145.33</v>
+        <v>1145.31</v>
       </c>
       <c r="E147" t="n">
-        <v>1168.35</v>
+        <v>1168.32</v>
       </c>
       <c r="F147" t="n">
         <v>3233</v>
@@ -22241,13 +22241,13 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>1155.61</v>
+        <v>1155.65</v>
       </c>
       <c r="D148" t="n">
-        <v>1147.22</v>
+        <v>1147.26</v>
       </c>
       <c r="E148" t="n">
-        <v>1164.01</v>
+        <v>1164.04</v>
       </c>
       <c r="F148" t="n">
         <v>6837</v>
@@ -22392,13 +22392,13 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>1155</v>
+        <v>1155.02</v>
       </c>
       <c r="D149" t="n">
-        <v>1142.37</v>
+        <v>1142.39</v>
       </c>
       <c r="E149" t="n">
-        <v>1167.63</v>
+        <v>1167.65</v>
       </c>
       <c r="F149" t="n">
         <v>3584</v>
@@ -22543,13 +22543,13 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>1152.02</v>
+        <v>1152.05</v>
       </c>
       <c r="D150" t="n">
-        <v>1138.8</v>
+        <v>1138.83</v>
       </c>
       <c r="E150" t="n">
-        <v>1165.24</v>
+        <v>1165.27</v>
       </c>
       <c r="F150" t="n">
         <v>4155</v>
@@ -22694,13 +22694,13 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>1151.63</v>
+        <v>1151.66</v>
       </c>
       <c r="D151" t="n">
-        <v>1136.22</v>
+        <v>1136.25</v>
       </c>
       <c r="E151" t="n">
-        <v>1167.04</v>
+        <v>1167.08</v>
       </c>
       <c r="F151" t="n">
         <v>1679</v>
@@ -22845,13 +22845,13 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>1149.76</v>
+        <v>1149.8</v>
       </c>
       <c r="D152" t="n">
-        <v>1137.45</v>
+        <v>1137.49</v>
       </c>
       <c r="E152" t="n">
-        <v>1162.08</v>
+        <v>1162.12</v>
       </c>
       <c r="F152" t="n">
         <v>2571</v>
@@ -22996,13 +22996,13 @@
         </is>
       </c>
       <c r="C153" t="n">
-        <v>1149.3</v>
+        <v>1149.32</v>
       </c>
       <c r="D153" t="n">
-        <v>1142.64</v>
+        <v>1142.67</v>
       </c>
       <c r="E153" t="n">
-        <v>1155.95</v>
+        <v>1155.97</v>
       </c>
       <c r="F153" t="n">
         <v>19402</v>
@@ -23147,13 +23147,13 @@
         </is>
       </c>
       <c r="C154" t="n">
-        <v>1148.79</v>
+        <v>1148.83</v>
       </c>
       <c r="D154" t="n">
-        <v>1139.52</v>
+        <v>1139.56</v>
       </c>
       <c r="E154" t="n">
-        <v>1158.06</v>
+        <v>1158.1</v>
       </c>
       <c r="F154" t="n">
         <v>7046</v>
@@ -23298,13 +23298,13 @@
         </is>
       </c>
       <c r="C155" t="n">
-        <v>1146.62</v>
+        <v>1146.67</v>
       </c>
       <c r="D155" t="n">
-        <v>1129.48</v>
+        <v>1129.53</v>
       </c>
       <c r="E155" t="n">
-        <v>1163.77</v>
+        <v>1163.82</v>
       </c>
       <c r="F155" t="n">
         <v>1295</v>
@@ -23449,13 +23449,13 @@
         </is>
       </c>
       <c r="C156" t="n">
-        <v>1143.56</v>
+        <v>1143.59</v>
       </c>
       <c r="D156" t="n">
-        <v>1133.66</v>
+        <v>1133.69</v>
       </c>
       <c r="E156" t="n">
-        <v>1153.46</v>
+        <v>1153.49</v>
       </c>
       <c r="F156" t="n">
         <v>4735</v>
@@ -23600,13 +23600,13 @@
         </is>
       </c>
       <c r="C157" t="n">
-        <v>1142.7</v>
+        <v>1142.73</v>
       </c>
       <c r="D157" t="n">
-        <v>1136.27</v>
+        <v>1136.29</v>
       </c>
       <c r="E157" t="n">
-        <v>1149.13</v>
+        <v>1149.16</v>
       </c>
       <c r="F157" t="n">
         <v>12296</v>
@@ -23751,13 +23751,13 @@
         </is>
       </c>
       <c r="C158" t="n">
-        <v>1141.14</v>
+        <v>1141.16</v>
       </c>
       <c r="D158" t="n">
-        <v>1134.41</v>
+        <v>1134.43</v>
       </c>
       <c r="E158" t="n">
-        <v>1147.87</v>
+        <v>1147.89</v>
       </c>
       <c r="F158" t="n">
         <v>19171</v>
@@ -23902,13 +23902,13 @@
         </is>
       </c>
       <c r="C159" t="n">
-        <v>1140.53</v>
+        <v>1140.57</v>
       </c>
       <c r="D159" t="n">
-        <v>1133.81</v>
+        <v>1133.85</v>
       </c>
       <c r="E159" t="n">
-        <v>1147.24</v>
+        <v>1147.29</v>
       </c>
       <c r="F159" t="n">
         <v>19366</v>
@@ -24053,13 +24053,13 @@
         </is>
       </c>
       <c r="C160" t="n">
-        <v>1138.18</v>
+        <v>1138.23</v>
       </c>
       <c r="D160" t="n">
-        <v>1127.2</v>
+        <v>1127.25</v>
       </c>
       <c r="E160" t="n">
-        <v>1149.15</v>
+        <v>1149.2</v>
       </c>
       <c r="F160" t="n">
         <v>4964</v>
@@ -24204,13 +24204,13 @@
         </is>
       </c>
       <c r="C161" t="n">
-        <v>1136.22</v>
+        <v>1136.25</v>
       </c>
       <c r="D161" t="n">
-        <v>1127.31</v>
+        <v>1127.34</v>
       </c>
       <c r="E161" t="n">
-        <v>1145.13</v>
+        <v>1145.16</v>
       </c>
       <c r="F161" t="n">
         <v>7363</v>
@@ -24355,13 +24355,13 @@
         </is>
       </c>
       <c r="C162" t="n">
-        <v>1135.72</v>
+        <v>1135.77</v>
       </c>
       <c r="D162" t="n">
-        <v>1126.21</v>
+        <v>1126.26</v>
       </c>
       <c r="E162" t="n">
-        <v>1145.23</v>
+        <v>1145.28</v>
       </c>
       <c r="F162" t="n">
         <v>8925</v>
@@ -24506,13 +24506,13 @@
         </is>
       </c>
       <c r="C163" t="n">
-        <v>1130.73</v>
+        <v>1130.75</v>
       </c>
       <c r="D163" t="n">
-        <v>1121.88</v>
+        <v>1121.9</v>
       </c>
       <c r="E163" t="n">
-        <v>1139.58</v>
+        <v>1139.6</v>
       </c>
       <c r="F163" t="n">
         <v>11116</v>
@@ -24657,13 +24657,13 @@
         </is>
       </c>
       <c r="C164" t="n">
-        <v>1128.83</v>
+        <v>1128.87</v>
       </c>
       <c r="D164" t="n">
-        <v>1121.4</v>
+        <v>1121.44</v>
       </c>
       <c r="E164" t="n">
-        <v>1136.25</v>
+        <v>1136.29</v>
       </c>
       <c r="F164" t="n">
         <v>20691</v>
@@ -24808,13 +24808,13 @@
         </is>
       </c>
       <c r="C165" t="n">
-        <v>1128.04</v>
+        <v>1128.06</v>
       </c>
       <c r="D165" t="n">
-        <v>1121.64</v>
+        <v>1121.66</v>
       </c>
       <c r="E165" t="n">
-        <v>1134.43</v>
+        <v>1134.45</v>
       </c>
       <c r="F165" t="n">
         <v>20115</v>
@@ -24959,13 +24959,13 @@
         </is>
       </c>
       <c r="C166" t="n">
-        <v>1126.94</v>
+        <v>1126.98</v>
       </c>
       <c r="D166" t="n">
-        <v>1114.77</v>
+        <v>1114.81</v>
       </c>
       <c r="E166" t="n">
-        <v>1139.11</v>
+        <v>1139.15</v>
       </c>
       <c r="F166" t="n">
         <v>2921</v>
@@ -25110,13 +25110,13 @@
         </is>
       </c>
       <c r="C167" t="n">
-        <v>1126.54</v>
+        <v>1126.58</v>
       </c>
       <c r="D167" t="n">
-        <v>1110.86</v>
+        <v>1110.89</v>
       </c>
       <c r="E167" t="n">
-        <v>1142.23</v>
+        <v>1142.26</v>
       </c>
       <c r="F167" t="n">
         <v>1785</v>
@@ -25261,13 +25261,13 @@
         </is>
       </c>
       <c r="C168" t="n">
-        <v>1120.57</v>
+        <v>1120.61</v>
       </c>
       <c r="D168" t="n">
-        <v>1109.57</v>
+        <v>1109.61</v>
       </c>
       <c r="E168" t="n">
-        <v>1131.57</v>
+        <v>1131.62</v>
       </c>
       <c r="F168" t="n">
         <v>5184</v>
@@ -25412,13 +25412,13 @@
         </is>
       </c>
       <c r="C169" t="n">
-        <v>1118.68</v>
+        <v>1118.71</v>
       </c>
       <c r="D169" t="n">
-        <v>1100.45</v>
+        <v>1100.48</v>
       </c>
       <c r="E169" t="n">
-        <v>1136.91</v>
+        <v>1136.94</v>
       </c>
       <c r="F169" t="n">
         <v>1143</v>
@@ -25563,13 +25563,13 @@
         </is>
       </c>
       <c r="C170" t="n">
-        <v>1114.24</v>
+        <v>1114.28</v>
       </c>
       <c r="D170" t="n">
-        <v>1105.05</v>
+        <v>1105.09</v>
       </c>
       <c r="E170" t="n">
-        <v>1123.43</v>
+        <v>1123.47</v>
       </c>
       <c r="F170" t="n">
         <v>6923</v>
@@ -25714,13 +25714,13 @@
         </is>
       </c>
       <c r="C171" t="n">
-        <v>1113.96</v>
+        <v>1114</v>
       </c>
       <c r="D171" t="n">
-        <v>1099.54</v>
+        <v>1099.57</v>
       </c>
       <c r="E171" t="n">
-        <v>1128.39</v>
+        <v>1128.42</v>
       </c>
       <c r="F171" t="n">
         <v>2201</v>
@@ -25865,13 +25865,13 @@
         </is>
       </c>
       <c r="C172" t="n">
-        <v>1113.86</v>
+        <v>1113.92</v>
       </c>
       <c r="D172" t="n">
-        <v>1106.13</v>
+        <v>1106.18</v>
       </c>
       <c r="E172" t="n">
-        <v>1121.6</v>
+        <v>1121.66</v>
       </c>
       <c r="F172" t="n">
         <v>10853</v>
@@ -26016,13 +26016,13 @@
         </is>
       </c>
       <c r="C173" t="n">
-        <v>1110.96</v>
+        <v>1110.98</v>
       </c>
       <c r="D173" t="n">
-        <v>1103.08</v>
+        <v>1103.11</v>
       </c>
       <c r="E173" t="n">
-        <v>1118.83</v>
+        <v>1118.85</v>
       </c>
       <c r="F173" t="n">
         <v>8045</v>
@@ -26167,13 +26167,13 @@
         </is>
       </c>
       <c r="C174" t="n">
-        <v>1109.24</v>
+        <v>1109.29</v>
       </c>
       <c r="D174" t="n">
-        <v>1099.94</v>
+        <v>1099.99</v>
       </c>
       <c r="E174" t="n">
-        <v>1118.55</v>
+        <v>1118.59</v>
       </c>
       <c r="F174" t="n">
         <v>8977</v>
@@ -26318,13 +26318,13 @@
         </is>
       </c>
       <c r="C175" t="n">
-        <v>1107.81</v>
+        <v>1107.83</v>
       </c>
       <c r="D175" t="n">
-        <v>1100.75</v>
+        <v>1100.77</v>
       </c>
       <c r="E175" t="n">
-        <v>1114.87</v>
+        <v>1114.88</v>
       </c>
       <c r="F175" t="n">
         <v>14148</v>
@@ -26469,13 +26469,13 @@
         </is>
       </c>
       <c r="C176" t="n">
-        <v>1091.32</v>
+        <v>1091.38</v>
       </c>
       <c r="D176" t="n">
-        <v>1079.8</v>
+        <v>1079.86</v>
       </c>
       <c r="E176" t="n">
-        <v>1102.85</v>
+        <v>1102.9</v>
       </c>
       <c r="F176" t="n">
         <v>4779</v>
@@ -26620,13 +26620,13 @@
         </is>
       </c>
       <c r="C177" t="n">
-        <v>1089.73</v>
+        <v>1089.78</v>
       </c>
       <c r="D177" t="n">
-        <v>1080.37</v>
+        <v>1080.42</v>
       </c>
       <c r="E177" t="n">
-        <v>1099.08</v>
+        <v>1099.13</v>
       </c>
       <c r="F177" t="n">
         <v>7598</v>
@@ -26771,13 +26771,13 @@
         </is>
       </c>
       <c r="C178" t="n">
-        <v>1074.27</v>
+        <v>1074.28</v>
       </c>
       <c r="D178" t="n">
-        <v>1063.07</v>
+        <v>1063.08</v>
       </c>
       <c r="E178" t="n">
-        <v>1085.46</v>
+        <v>1085.47</v>
       </c>
       <c r="F178" t="n">
         <v>6329</v>
@@ -26922,13 +26922,13 @@
         </is>
       </c>
       <c r="C179" t="n">
-        <v>1070.02</v>
+        <v>1070.06</v>
       </c>
       <c r="D179" t="n">
-        <v>1060.05</v>
+        <v>1060.09</v>
       </c>
       <c r="E179" t="n">
-        <v>1079.99</v>
+        <v>1080.02</v>
       </c>
       <c r="F179" t="n">
         <v>6964</v>
@@ -27073,13 +27073,13 @@
         </is>
       </c>
       <c r="C180" t="n">
-        <v>1066.92</v>
+        <v>1067</v>
       </c>
       <c r="D180" t="n">
-        <v>1055.38</v>
+        <v>1055.46</v>
       </c>
       <c r="E180" t="n">
-        <v>1078.45</v>
+        <v>1078.54</v>
       </c>
       <c r="F180" t="n">
         <v>5745</v>
@@ -27224,13 +27224,13 @@
         </is>
       </c>
       <c r="C181" t="n">
-        <v>1065.5</v>
+        <v>1065.56</v>
       </c>
       <c r="D181" t="n">
-        <v>1050.19</v>
+        <v>1050.25</v>
       </c>
       <c r="E181" t="n">
-        <v>1080.81</v>
+        <v>1080.87</v>
       </c>
       <c r="F181" t="n">
         <v>1743</v>
@@ -27375,13 +27375,13 @@
         </is>
       </c>
       <c r="C182" t="n">
-        <v>1061.38</v>
+        <v>1061.44</v>
       </c>
       <c r="D182" t="n">
-        <v>1049.33</v>
+        <v>1049.39</v>
       </c>
       <c r="E182" t="n">
-        <v>1073.42</v>
+        <v>1073.48</v>
       </c>
       <c r="F182" t="n">
         <v>3925</v>
@@ -27526,13 +27526,13 @@
         </is>
       </c>
       <c r="C183" t="n">
-        <v>1055.64</v>
+        <v>1055.68</v>
       </c>
       <c r="D183" t="n">
-        <v>1043.95</v>
+        <v>1043.99</v>
       </c>
       <c r="E183" t="n">
-        <v>1067.33</v>
+        <v>1067.38</v>
       </c>
       <c r="F183" t="n">
         <v>4658</v>
@@ -27677,13 +27677,13 @@
         </is>
       </c>
       <c r="C184" t="n">
-        <v>1040.86</v>
+        <v>1040.91</v>
       </c>
       <c r="D184" t="n">
-        <v>1029.4</v>
+        <v>1029.44</v>
       </c>
       <c r="E184" t="n">
-        <v>1052.33</v>
+        <v>1052.38</v>
       </c>
       <c r="F184" t="n">
         <v>4845</v>
@@ -27828,13 +27828,13 @@
         </is>
       </c>
       <c r="C185" t="n">
-        <v>1023.78</v>
+        <v>1023.82</v>
       </c>
       <c r="D185" t="n">
-        <v>1010.13</v>
+        <v>1010.17</v>
       </c>
       <c r="E185" t="n">
-        <v>1037.42</v>
+        <v>1037.47</v>
       </c>
       <c r="F185" t="n">
         <v>2657</v>
@@ -27979,13 +27979,13 @@
         </is>
       </c>
       <c r="C186" t="n">
-        <v>1021.65</v>
+        <v>1021.71</v>
       </c>
       <c r="D186" t="n">
-        <v>1010.71</v>
+        <v>1010.77</v>
       </c>
       <c r="E186" t="n">
-        <v>1032.6</v>
+        <v>1032.65</v>
       </c>
       <c r="F186" t="n">
         <v>6311</v>
@@ -28130,13 +28130,13 @@
         </is>
       </c>
       <c r="C187" t="n">
-        <v>995.165</v>
+        <v>995.199</v>
       </c>
       <c r="D187" t="n">
-        <v>982.522</v>
+        <v>982.557</v>
       </c>
       <c r="E187" t="n">
-        <v>1007.81</v>
+        <v>1007.84</v>
       </c>
       <c r="F187" t="n">
         <v>4914</v>
@@ -28281,13 +28281,13 @@
         </is>
       </c>
       <c r="C188" t="n">
-        <v>990.847</v>
+        <v>990.895</v>
       </c>
       <c r="D188" t="n">
-        <v>978.3920000000001</v>
+        <v>978.4400000000001</v>
       </c>
       <c r="E188" t="n">
-        <v>1003.3</v>
+        <v>1003.35</v>
       </c>
       <c r="F188" t="n">
         <v>4203</v>
@@ -28432,13 +28432,13 @@
         </is>
       </c>
       <c r="C189" t="n">
-        <v>979.579</v>
+        <v>979.655</v>
       </c>
       <c r="D189" t="n">
-        <v>965.941</v>
+        <v>966.018</v>
       </c>
       <c r="E189" t="n">
-        <v>993.216</v>
+        <v>993.292</v>
       </c>
       <c r="F189" t="n">
         <v>3412</v>
@@ -28583,13 +28583,13 @@
         </is>
       </c>
       <c r="C190" t="n">
-        <v>971.623</v>
+        <v>971.705</v>
       </c>
       <c r="D190" t="n">
-        <v>955.677</v>
+        <v>955.76</v>
       </c>
       <c r="E190" t="n">
-        <v>987.568</v>
+        <v>987.649</v>
       </c>
       <c r="F190" t="n">
         <v>2391</v>
@@ -28734,13 +28734,13 @@
         </is>
       </c>
       <c r="C191" t="n">
-        <v>952.171</v>
+        <v>952.21</v>
       </c>
       <c r="D191" t="n">
-        <v>939.329</v>
+        <v>939.369</v>
       </c>
       <c r="E191" t="n">
-        <v>965.013</v>
+        <v>965.052</v>
       </c>
       <c r="F191" t="n">
         <v>3287</v>
@@ -28892,7 +28892,7 @@
     <col width="23" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
@@ -28959,7 +28959,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -28994,7 +28994,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -29029,7 +29029,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -29064,7 +29064,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -29099,7 +29099,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -29138,7 +29138,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -29173,7 +29173,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -29208,7 +29208,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -29243,7 +29243,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -29278,7 +29278,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -29313,7 +29313,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -29352,14 +29352,14 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>qwen3.5-122b-a10b</t>
+          <t>qwen3-235b-a22b-instruct-2507</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>125</v>
+        <v>235</v>
       </c>
       <c r="F13" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -29367,7 +29367,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>78.09999999999999</v>
+        <v>146.9</v>
       </c>
       <c r="I13" t="inlineStr"/>
     </row>
@@ -29383,7 +29383,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -29418,7 +29418,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -29453,7 +29453,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -29550,14 +29550,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>qwen3.5-397b-a17b</t>
+          <t>kimi-k2.5-thinking</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>397</v>
+        <v>1000</v>
       </c>
       <c r="C3" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -29566,21 +29566,21 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>artificial_analysis</t>
+          <t>override</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>kimi-k2.5-thinking</t>
+          <t>qwen3.5-397b-a17b</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1000</v>
+        <v>397</v>
       </c>
       <c r="C4" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -29589,7 +29589,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>artificial_analysis</t>
         </is>
       </c>
     </row>
@@ -29734,14 +29734,14 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>qwen3.5-122b-a10b</t>
+          <t>qwen3-235b-a22b-instruct-2507</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>125</v>
+        <v>235</v>
       </c>
       <c r="C11" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -29757,14 +29757,14 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>qwen3-235b-a22b-instruct-2507</t>
+          <t>deepseek-v3.2</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>235</v>
+        <v>685</v>
       </c>
       <c r="C12" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -29780,14 +29780,14 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>deepseek-v3.2</t>
+          <t>qwen3.5-122b-a10b</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>685</v>
+        <v>125</v>
       </c>
       <c r="C13" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -29872,14 +29872,14 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>deepseek-v3.1-thinking</t>
+          <t>kimi-k2-0905-preview</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>685</v>
+        <v>1000</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -29888,21 +29888,21 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>artificial_analysis</t>
+          <t>override</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>kimi-k2-0905-preview</t>
+          <t>deepseek-v3.1-thinking</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1000</v>
+        <v>685</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -29911,7 +29911,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>artificial_analysis</t>
         </is>
       </c>
     </row>
@@ -29987,14 +29987,14 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>mistral-large-3</t>
+          <t>qwen3-vl-235b-a22b-instruct</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>675</v>
+        <v>235</v>
       </c>
       <c r="C22" t="n">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -30010,14 +30010,14 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>qwen3-vl-235b-a22b-instruct</t>
+          <t>mistral-large-3</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>235</v>
+        <v>675</v>
       </c>
       <c r="C23" t="n">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -30033,18 +30033,18 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>glm-4.5</t>
+          <t>qwen3.5-27b</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>355</v>
+        <v>27.8</v>
       </c>
       <c r="C24" t="n">
-        <v>32</v>
+        <v>27.8</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>moe</t>
+          <t>dense</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -30056,18 +30056,18 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>qwen3.5-27b</t>
+          <t>glm-4.5</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>27.8</v>
+        <v>355</v>
       </c>
       <c r="C25" t="n">
-        <v>27.8</v>
+        <v>32</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>dense</t>
+          <t>moe</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -30692,18 +30692,18 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>glm-4.5v</t>
+          <t>command-a-03-2025</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C53" t="n">
-        <v>12</v>
+        <v>111</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>moe</t>
+          <t>dense</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -30715,18 +30715,18 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>command-a-03-2025</t>
+          <t>glm-4.5v</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C54" t="n">
-        <v>111</v>
+        <v>12</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>dense</t>
+          <t>moe</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">

--- a/arena_enrichment/output/arena_leaderboard_enriched.xlsx
+++ b/arena_enrichment/output/arena_leaderboard_enriched.xlsx
@@ -675,16 +675,16 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>1453.22</v>
+        <v>1452.62</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1446.27</v>
+        <v>1445.74</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1460.16</v>
+        <v>1459.51</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>7632</v>
+        <v>7875</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
@@ -822,36 +822,36 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>kimi-k2.5-thinking</t>
+          <t>qwen3.5-397b-a17b</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>1450.61</v>
+        <v>1451.39</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1444.72</v>
+        <v>1444.03</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1456.51</v>
+        <v>1458.76</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>12263</v>
+        <v>6576</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Moonshot</t>
+          <t>Alibaba</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Modified MIT</t>
+          <t>Apache 2.0</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>1000</v>
+        <v>397</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
@@ -860,26 +860,26 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>artificial_analysis</t>
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>2000</v>
+        <v>794</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>2500</v>
+        <v>992.5</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>1000</v>
+        <v>397</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>1250</v>
+        <v>496.2</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>500</v>
+        <v>198.5</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>625</v>
+        <v>248.1</v>
       </c>
       <c r="S3" s="3" t="inlineStr">
         <is>
@@ -951,9 +951,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AG3" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AG3" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AH3" s="2" t="inlineStr">
@@ -973,36 +973,36 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>qwen3.5-397b-a17b</t>
+          <t>kimi-k2.5-thinking</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>1449.8</v>
+        <v>1450.37</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1442.3</v>
+        <v>1444.49</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1457.3</v>
+        <v>1456.25</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>6296</v>
+        <v>12488</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Alibaba</t>
+          <t>Moonshot</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
+          <t>Modified MIT</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>397</v>
+        <v>1000</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
@@ -1011,26 +1011,26 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>artificial_analysis</t>
+          <t>override</t>
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>794</v>
+        <v>2000</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>992.5</v>
+        <v>2500</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>397</v>
+        <v>1000</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>496.2</v>
+        <v>1250</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>198.5</v>
+        <v>500</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>248.1</v>
+        <v>625</v>
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
@@ -1102,9 +1102,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AG4" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AG4" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AH4" s="2" t="inlineStr">
@@ -1128,13 +1128,13 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>1440.77</v>
+        <v>1440.88</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1434.59</v>
+        <v>1434.71</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1446.94</v>
+        <v>1447.06</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>11933</v>
@@ -1279,16 +1279,16 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1431.95</v>
+        <v>1434.6</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1425.35</v>
+        <v>1428.08</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1438.55</v>
+        <v>1441.12</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>8355</v>
+        <v>8596</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
@@ -1430,16 +1430,16 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>1428.93</v>
+        <v>1429.19</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>1425.04</v>
+        <v>1425.31</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1432.82</v>
+        <v>1433.07</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>37329</v>
+        <v>37587</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
@@ -1581,16 +1581,16 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>1425.07</v>
+        <v>1425.11</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>1421.08</v>
+        <v>1421.12</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1429.06</v>
+        <v>1429.09</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>35096</v>
+        <v>35097</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
@@ -1732,13 +1732,13 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>1423.64</v>
+        <v>1423.71</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1417.15</v>
+        <v>1417.22</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1430.13</v>
+        <v>1430.2</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>11674</v>
@@ -1883,16 +1883,16 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>1423.28</v>
+        <v>1423.33</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>1416.7</v>
+        <v>1416.75</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1429.86</v>
+        <v>1429.91</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>8943</v>
+        <v>8942</v>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
@@ -2034,16 +2034,16 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>1422.3</v>
+        <v>1422.29</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>1419.3</v>
+        <v>1419.29</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1425.3</v>
+        <v>1425.28</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>72786</v>
+        <v>73052</v>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
@@ -2185,16 +2185,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1421</v>
+        <v>1420.96</v>
       </c>
       <c r="D12" t="n">
-        <v>1416.68</v>
+        <v>1416.66</v>
       </c>
       <c r="E12" t="n">
-        <v>1425.32</v>
+        <v>1425.27</v>
       </c>
       <c r="F12" t="n">
-        <v>32019</v>
+        <v>32274</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -2332,36 +2332,36 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>qwen3.5-122b-a10b</t>
+          <t>deepseek-v3.2-thinking</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1419.86</v>
+        <v>1419.44</v>
       </c>
       <c r="D13" t="n">
-        <v>1408.87</v>
+        <v>1415.02</v>
       </c>
       <c r="E13" t="n">
-        <v>1430.84</v>
+        <v>1423.86</v>
       </c>
       <c r="F13" t="n">
-        <v>2743</v>
+        <v>27113</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alibaba</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>125</v>
+        <v>685</v>
       </c>
       <c r="J13" t="n">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -2374,22 +2374,22 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>250</v>
+        <v>1370</v>
       </c>
       <c r="N13" t="n">
-        <v>312.5</v>
+        <v>1712.5</v>
       </c>
       <c r="O13" t="n">
-        <v>125</v>
+        <v>685</v>
       </c>
       <c r="P13" t="n">
-        <v>156.2</v>
+        <v>856.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>62.5</v>
+        <v>342.5</v>
       </c>
       <c r="R13" t="n">
-        <v>78.09999999999999</v>
+        <v>428.1</v>
       </c>
       <c r="S13" s="5" t="inlineStr">
         <is>
@@ -2401,9 +2401,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="U13" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="U13" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="V13" s="5" t="inlineStr">
@@ -2416,9 +2416,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="X13" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="X13" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="Y13" s="5" t="inlineStr">
@@ -2431,9 +2431,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AA13" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AA13" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AB13" s="5" t="inlineStr">
@@ -2441,14 +2441,14 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AC13" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AD13" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AC13" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD13" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AE13" s="5" t="inlineStr">
@@ -2456,14 +2456,14 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AF13" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AG13" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AF13" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AG13" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
@@ -2473,7 +2473,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>B200 SXM</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
     </row>
@@ -2483,36 +2483,36 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>deepseek-v3.2-thinking</t>
+          <t>qwen3.5-122b-a10b</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1419.78</v>
+        <v>1419.32</v>
       </c>
       <c r="D14" t="n">
-        <v>1415.35</v>
+        <v>1408.76</v>
       </c>
       <c r="E14" t="n">
-        <v>1424.22</v>
+        <v>1429.87</v>
       </c>
       <c r="F14" t="n">
-        <v>26885</v>
+        <v>3003</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>DeepSeek</t>
+          <t>Alibaba</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Apache 2.0</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>685</v>
+        <v>125</v>
       </c>
       <c r="J14" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -2525,22 +2525,22 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>1370</v>
+        <v>250</v>
       </c>
       <c r="N14" t="n">
-        <v>1712.5</v>
+        <v>312.5</v>
       </c>
       <c r="O14" t="n">
-        <v>685</v>
+        <v>125</v>
       </c>
       <c r="P14" t="n">
-        <v>856.2</v>
+        <v>156.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>342.5</v>
+        <v>62.5</v>
       </c>
       <c r="R14" t="n">
-        <v>428.1</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="S14" s="5" t="inlineStr">
         <is>
@@ -2552,9 +2552,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="U14" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="U14" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="V14" s="5" t="inlineStr">
@@ -2567,9 +2567,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="X14" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="X14" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Y14" s="5" t="inlineStr">
@@ -2582,9 +2582,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AA14" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AA14" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AB14" s="5" t="inlineStr">
@@ -2592,14 +2592,14 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AC14" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AD14" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AC14" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AD14" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AE14" s="5" t="inlineStr">
@@ -2607,14 +2607,14 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AF14" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AG14" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AF14" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AG14" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
@@ -2624,7 +2624,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>B200 SXM</t>
         </is>
       </c>
     </row>
@@ -2638,16 +2638,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1419.28</v>
+        <v>1419.3</v>
       </c>
       <c r="D15" t="n">
-        <v>1413.67</v>
+        <v>1413.7</v>
       </c>
       <c r="E15" t="n">
-        <v>1424.88</v>
+        <v>1424.91</v>
       </c>
       <c r="F15" t="n">
-        <v>19154</v>
+        <v>19155</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1418.14</v>
+        <v>1418.13</v>
       </c>
       <c r="D16" t="n">
         <v>1412.14</v>
@@ -2798,7 +2798,7 @@
         <v>1424.13</v>
       </c>
       <c r="F16" t="n">
-        <v>15194</v>
+        <v>15193</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -2936,36 +2936,36 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>kimi-k2-0905-preview</t>
+          <t>deepseek-v3.1-thinking</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1417.1</v>
+        <v>1417.12</v>
       </c>
       <c r="D17" t="n">
-        <v>1410.63</v>
+        <v>1410.54</v>
       </c>
       <c r="E17" t="n">
-        <v>1423.58</v>
+        <v>1423.71</v>
       </c>
       <c r="F17" t="n">
-        <v>11909</v>
+        <v>11918</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Moonshot</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Modified MIT</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1000</v>
+        <v>685</v>
       </c>
       <c r="J17" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -2974,26 +2974,26 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>artificial_analysis</t>
         </is>
       </c>
       <c r="M17" t="n">
-        <v>2000</v>
+        <v>1370</v>
       </c>
       <c r="N17" t="n">
-        <v>2500</v>
+        <v>1712.5</v>
       </c>
       <c r="O17" t="n">
-        <v>1000</v>
+        <v>685</v>
       </c>
       <c r="P17" t="n">
-        <v>1250</v>
+        <v>856.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>500</v>
+        <v>342.5</v>
       </c>
       <c r="R17" t="n">
-        <v>625</v>
+        <v>428.1</v>
       </c>
       <c r="S17" s="5" t="inlineStr">
         <is>
@@ -3087,36 +3087,36 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>deepseek-v3.1-thinking</t>
+          <t>kimi-k2-0905-preview</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>1417.1</v>
       </c>
       <c r="D18" t="n">
-        <v>1410.51</v>
+        <v>1410.62</v>
       </c>
       <c r="E18" t="n">
-        <v>1423.68</v>
+        <v>1423.57</v>
       </c>
       <c r="F18" t="n">
-        <v>11918</v>
+        <v>11909</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>DeepSeek</t>
+          <t>Moonshot</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Modified MIT</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>685</v>
+        <v>1000</v>
       </c>
       <c r="J18" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -3125,26 +3125,26 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>artificial_analysis</t>
+          <t>override</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>1370</v>
+        <v>2000</v>
       </c>
       <c r="N18" t="n">
-        <v>1712.5</v>
+        <v>2500</v>
       </c>
       <c r="O18" t="n">
-        <v>685</v>
+        <v>1000</v>
       </c>
       <c r="P18" t="n">
-        <v>856.2</v>
+        <v>1250</v>
       </c>
       <c r="Q18" t="n">
-        <v>342.5</v>
+        <v>500</v>
       </c>
       <c r="R18" t="n">
-        <v>428.1</v>
+        <v>625</v>
       </c>
       <c r="S18" s="5" t="inlineStr">
         <is>
@@ -3242,16 +3242,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1416.62</v>
+        <v>1416.6</v>
       </c>
       <c r="D19" t="n">
-        <v>1411.81</v>
+        <v>1411.79</v>
       </c>
       <c r="E19" t="n">
-        <v>1421.43</v>
+        <v>1421.41</v>
       </c>
       <c r="F19" t="n">
-        <v>28429</v>
+        <v>28425</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -3393,16 +3393,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1416.1</v>
+        <v>1415.91</v>
       </c>
       <c r="D20" t="n">
-        <v>1406.53</v>
+        <v>1406.34</v>
       </c>
       <c r="E20" t="n">
-        <v>1425.67</v>
+        <v>1425.48</v>
       </c>
       <c r="F20" t="n">
-        <v>3743</v>
+        <v>3745</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -3544,13 +3544,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1415.5</v>
+        <v>1415.53</v>
       </c>
       <c r="D21" t="n">
-        <v>1405.64</v>
+        <v>1405.67</v>
       </c>
       <c r="E21" t="n">
-        <v>1425.37</v>
+        <v>1425.4</v>
       </c>
       <c r="F21" t="n">
         <v>3536</v>
@@ -3695,16 +3695,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1414.66</v>
+        <v>1414.74</v>
       </c>
       <c r="D22" t="n">
-        <v>1408.18</v>
+        <v>1408.26</v>
       </c>
       <c r="E22" t="n">
-        <v>1421.13</v>
+        <v>1421.21</v>
       </c>
       <c r="F22" t="n">
-        <v>11594</v>
+        <v>11596</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -3846,16 +3846,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1414.63</v>
+        <v>1414.68</v>
       </c>
       <c r="D23" t="n">
-        <v>1410.3</v>
+        <v>1410.37</v>
       </c>
       <c r="E23" t="n">
-        <v>1418.96</v>
+        <v>1419</v>
       </c>
       <c r="F23" t="n">
-        <v>28519</v>
+        <v>28787</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -3993,40 +3993,40 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>qwen3.5-27b</t>
+          <t>glm-4.5</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1410.21</v>
+        <v>1410.14</v>
       </c>
       <c r="D24" t="n">
-        <v>1399.51</v>
+        <v>1405.26</v>
       </c>
       <c r="E24" t="n">
-        <v>1420.91</v>
+        <v>1415.01</v>
       </c>
       <c r="F24" t="n">
-        <v>2848</v>
+        <v>24596</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alibaba</t>
+          <t>Z.ai</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>27.8</v>
+        <v>355</v>
       </c>
       <c r="J24" t="n">
-        <v>27.8</v>
+        <v>32</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>dense</t>
+          <t>moe</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -4035,91 +4035,91 @@
         </is>
       </c>
       <c r="M24" t="n">
-        <v>55.6</v>
+        <v>710</v>
       </c>
       <c r="N24" t="n">
-        <v>69.5</v>
+        <v>887.5</v>
       </c>
       <c r="O24" t="n">
-        <v>27.8</v>
+        <v>355</v>
       </c>
       <c r="P24" t="n">
-        <v>34.8</v>
+        <v>443.8</v>
       </c>
       <c r="Q24" t="n">
-        <v>13.9</v>
+        <v>177.5</v>
       </c>
       <c r="R24" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="S24" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="T24" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="U24" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="V24" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W24" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X24" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Y24" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z24" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AA24" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB24" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AC24" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AD24" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AE24" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AF24" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+        <v>221.9</v>
+      </c>
+      <c r="S24" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T24" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U24" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V24" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W24" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X24" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y24" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z24" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA24" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AB24" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AC24" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD24" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE24" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF24" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AG24" s="6" t="inlineStr">
@@ -4129,12 +4129,12 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
     </row>
@@ -4144,40 +4144,40 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>glm-4.5</t>
+          <t>qwen3.5-27b</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1410.08</v>
+        <v>1409.63</v>
       </c>
       <c r="D25" t="n">
-        <v>1405.21</v>
+        <v>1399.32</v>
       </c>
       <c r="E25" t="n">
-        <v>1414.95</v>
+        <v>1419.94</v>
       </c>
       <c r="F25" t="n">
-        <v>24594</v>
+        <v>3104</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Z.ai</t>
+          <t>Alibaba</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Apache 2.0</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>355</v>
+        <v>27.8</v>
       </c>
       <c r="J25" t="n">
-        <v>32</v>
+        <v>27.8</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>moe</t>
+          <t>dense</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -4186,91 +4186,91 @@
         </is>
       </c>
       <c r="M25" t="n">
-        <v>710</v>
+        <v>55.6</v>
       </c>
       <c r="N25" t="n">
-        <v>887.5</v>
+        <v>69.5</v>
       </c>
       <c r="O25" t="n">
-        <v>355</v>
+        <v>27.8</v>
       </c>
       <c r="P25" t="n">
-        <v>443.8</v>
+        <v>34.8</v>
       </c>
       <c r="Q25" t="n">
-        <v>177.5</v>
+        <v>13.9</v>
       </c>
       <c r="R25" t="n">
-        <v>221.9</v>
-      </c>
-      <c r="S25" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T25" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U25" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="V25" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W25" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X25" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Y25" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z25" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AA25" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AB25" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AC25" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AD25" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AE25" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AF25" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+        <v>17.4</v>
+      </c>
+      <c r="S25" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T25" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U25" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V25" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W25" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X25" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y25" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z25" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AA25" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB25" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AC25" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AD25" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE25" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AF25" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AG25" s="6" t="inlineStr">
@@ -4280,12 +4280,12 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>H100 SXM</t>
         </is>
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>H100 SXM</t>
         </is>
       </c>
     </row>
@@ -4299,16 +4299,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1401.86</v>
+        <v>1401.93</v>
       </c>
       <c r="D26" t="n">
-        <v>1397.4</v>
+        <v>1397.46</v>
       </c>
       <c r="E26" t="n">
-        <v>1406.33</v>
+        <v>1406.39</v>
       </c>
       <c r="F26" t="n">
-        <v>39272</v>
+        <v>39270</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -4450,16 +4450,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1401.72</v>
+        <v>1401.79</v>
       </c>
       <c r="D27" t="n">
-        <v>1396.91</v>
+        <v>1396.98</v>
       </c>
       <c r="E27" t="n">
-        <v>1406.53</v>
+        <v>1406.6</v>
       </c>
       <c r="F27" t="n">
-        <v>22666</v>
+        <v>22667</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -4601,16 +4601,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1400.89</v>
+        <v>1401.13</v>
       </c>
       <c r="D28" t="n">
-        <v>1393.8</v>
+        <v>1394.12</v>
       </c>
       <c r="E28" t="n">
-        <v>1407.99</v>
+        <v>1408.15</v>
       </c>
       <c r="F28" t="n">
-        <v>7466</v>
+        <v>7745</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -4752,16 +4752,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1400.07</v>
+        <v>1400.11</v>
       </c>
       <c r="D29" t="n">
-        <v>1393.72</v>
+        <v>1393.76</v>
       </c>
       <c r="E29" t="n">
-        <v>1406.42</v>
+        <v>1406.46</v>
       </c>
       <c r="F29" t="n">
-        <v>11485</v>
+        <v>11487</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -4903,13 +4903,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1398.58</v>
+        <v>1398.63</v>
       </c>
       <c r="D30" t="n">
-        <v>1392.11</v>
+        <v>1392.15</v>
       </c>
       <c r="E30" t="n">
-        <v>1405.06</v>
+        <v>1405.1</v>
       </c>
       <c r="F30" t="n">
         <v>9179</v>
@@ -5205,16 +5205,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1395</v>
+        <v>1395.05</v>
       </c>
       <c r="D32" t="n">
-        <v>1388.2</v>
+        <v>1388.24</v>
       </c>
       <c r="E32" t="n">
-        <v>1401.8</v>
+        <v>1401.85</v>
       </c>
       <c r="F32" t="n">
-        <v>7919</v>
+        <v>7918</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -5352,36 +5352,36 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>deepseek-v3-0324</t>
+          <t>qwen3.5-35b-a3b</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1394.05</v>
+        <v>1395.04</v>
       </c>
       <c r="D33" t="n">
-        <v>1390.2</v>
+        <v>1384.62</v>
       </c>
       <c r="E33" t="n">
-        <v>1397.91</v>
+        <v>1405.46</v>
       </c>
       <c r="F33" t="n">
-        <v>46412</v>
+        <v>3145</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>DeepSeek</t>
+          <t>Alibaba</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Apache 2.0</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>671</v>
+        <v>36</v>
       </c>
       <c r="J33" t="n">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -5394,36 +5394,36 @@
         </is>
       </c>
       <c r="M33" t="n">
-        <v>1342</v>
+        <v>72</v>
       </c>
       <c r="N33" t="n">
-        <v>1677.5</v>
+        <v>90</v>
       </c>
       <c r="O33" t="n">
-        <v>671</v>
+        <v>36</v>
       </c>
       <c r="P33" t="n">
-        <v>838.8</v>
+        <v>45</v>
       </c>
       <c r="Q33" t="n">
-        <v>335.5</v>
+        <v>18</v>
       </c>
       <c r="R33" t="n">
-        <v>419.4</v>
-      </c>
-      <c r="S33" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T33" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U33" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+        <v>22.5</v>
+      </c>
+      <c r="S33" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T33" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U33" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="V33" s="5" t="inlineStr">
@@ -5431,69 +5431,69 @@
           <t>No</t>
         </is>
       </c>
-      <c r="W33" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X33" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Y33" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z33" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AA33" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AB33" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AC33" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AD33" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AE33" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AF33" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AG33" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="W33" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X33" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y33" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z33" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AA33" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB33" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AC33" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AD33" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE33" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AF33" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AG33" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>RTX PRO 6000</t>
         </is>
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>H100 SXM</t>
         </is>
       </c>
     </row>
@@ -5503,36 +5503,36 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>qwen3.5-35b-a3b</t>
+          <t>deepseek-v3-0324</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1392.39</v>
+        <v>1394.07</v>
       </c>
       <c r="D34" t="n">
-        <v>1381.51</v>
+        <v>1390.22</v>
       </c>
       <c r="E34" t="n">
-        <v>1403.28</v>
+        <v>1397.92</v>
       </c>
       <c r="F34" t="n">
-        <v>2876</v>
+        <v>46411</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alibaba</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>36</v>
+        <v>671</v>
       </c>
       <c r="J34" t="n">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -5545,36 +5545,36 @@
         </is>
       </c>
       <c r="M34" t="n">
-        <v>72</v>
+        <v>1342</v>
       </c>
       <c r="N34" t="n">
-        <v>90</v>
+        <v>1677.5</v>
       </c>
       <c r="O34" t="n">
-        <v>36</v>
+        <v>671</v>
       </c>
       <c r="P34" t="n">
-        <v>45</v>
+        <v>838.8</v>
       </c>
       <c r="Q34" t="n">
-        <v>18</v>
+        <v>335.5</v>
       </c>
       <c r="R34" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="S34" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="T34" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="U34" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+        <v>419.4</v>
+      </c>
+      <c r="S34" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T34" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U34" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="V34" s="5" t="inlineStr">
@@ -5582,69 +5582,69 @@
           <t>No</t>
         </is>
       </c>
-      <c r="W34" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X34" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Y34" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z34" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AA34" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB34" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AC34" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AD34" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AE34" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AF34" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AG34" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="W34" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X34" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y34" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z34" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA34" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AB34" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AC34" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD34" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE34" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF34" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AG34" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>RTX PRO 6000</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
     </row>
@@ -5658,16 +5658,16 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1391.05</v>
+        <v>1390.93</v>
       </c>
       <c r="D35" t="n">
-        <v>1386.29</v>
+        <v>1386.18</v>
       </c>
       <c r="E35" t="n">
-        <v>1395.82</v>
+        <v>1395.68</v>
       </c>
       <c r="F35" t="n">
-        <v>20996</v>
+        <v>21281</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -5809,16 +5809,16 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1386.91</v>
+        <v>1386.92</v>
       </c>
       <c r="D36" t="n">
-        <v>1380.6</v>
+        <v>1380.67</v>
       </c>
       <c r="E36" t="n">
-        <v>1393.22</v>
+        <v>1393.18</v>
       </c>
       <c r="F36" t="n">
-        <v>9917</v>
+        <v>10176</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -5830,43 +5830,123 @@
           <t>Apache 2.0</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
+      <c r="I36" t="n">
+        <v>196</v>
+      </c>
+      <c r="J36" t="n">
+        <v>11</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="inlineStr"/>
-      <c r="S36" t="inlineStr"/>
-      <c r="T36" t="inlineStr"/>
-      <c r="U36" t="inlineStr"/>
-      <c r="V36" t="inlineStr"/>
-      <c r="W36" t="inlineStr"/>
-      <c r="X36" t="inlineStr"/>
-      <c r="Y36" t="inlineStr"/>
-      <c r="Z36" t="inlineStr"/>
-      <c r="AA36" t="inlineStr"/>
-      <c r="AB36" t="inlineStr"/>
-      <c r="AC36" t="inlineStr"/>
-      <c r="AD36" t="inlineStr"/>
-      <c r="AE36" t="inlineStr"/>
-      <c r="AF36" t="inlineStr"/>
-      <c r="AG36" t="inlineStr"/>
+          <t>artificial_analysis</t>
+        </is>
+      </c>
+      <c r="M36" t="n">
+        <v>392</v>
+      </c>
+      <c r="N36" t="n">
+        <v>490</v>
+      </c>
+      <c r="O36" t="n">
+        <v>196</v>
+      </c>
+      <c r="P36" t="n">
+        <v>245</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>98</v>
+      </c>
+      <c r="R36" t="n">
+        <v>122.5</v>
+      </c>
+      <c r="S36" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T36" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U36" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V36" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W36" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X36" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y36" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z36" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA36" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB36" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AC36" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD36" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE36" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF36" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AG36" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>B300 SXM</t>
         </is>
       </c>
     </row>
@@ -5880,13 +5960,13 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1386.54</v>
+        <v>1386.69</v>
       </c>
       <c r="D37" t="n">
-        <v>1380.2</v>
+        <v>1380.35</v>
       </c>
       <c r="E37" t="n">
-        <v>1392.87</v>
+        <v>1393.02</v>
       </c>
       <c r="F37" t="n">
         <v>10864</v>
@@ -6031,13 +6111,13 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1386.46</v>
+        <v>1386.47</v>
       </c>
       <c r="D38" t="n">
-        <v>1381.56</v>
+        <v>1381.58</v>
       </c>
       <c r="E38" t="n">
-        <v>1391.35</v>
+        <v>1391.36</v>
       </c>
       <c r="F38" t="n">
         <v>26400</v>
@@ -6182,16 +6262,16 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1385.15</v>
+        <v>1385.3</v>
       </c>
       <c r="D39" t="n">
-        <v>1379.83</v>
+        <v>1379.99</v>
       </c>
       <c r="E39" t="n">
-        <v>1390.46</v>
+        <v>1390.62</v>
       </c>
       <c r="F39" t="n">
-        <v>17068</v>
+        <v>17070</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -6333,13 +6413,13 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1383.61</v>
+        <v>1383.65</v>
       </c>
       <c r="D40" t="n">
-        <v>1378.74</v>
+        <v>1378.78</v>
       </c>
       <c r="E40" t="n">
-        <v>1388.48</v>
+        <v>1388.52</v>
       </c>
       <c r="F40" t="n">
         <v>23936</v>
@@ -6484,13 +6564,13 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1377.81</v>
+        <v>1377.87</v>
       </c>
       <c r="D41" t="n">
-        <v>1366.53</v>
+        <v>1366.6</v>
       </c>
       <c r="E41" t="n">
-        <v>1389.09</v>
+        <v>1389.15</v>
       </c>
       <c r="F41" t="n">
         <v>2785</v>
@@ -6631,24 +6711,24 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>trinity-large</t>
+          <t>qwen3-235b-a22b</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1375.47</v>
+        <v>1374.64</v>
       </c>
       <c r="D42" t="n">
-        <v>1365.46</v>
+        <v>1369.98</v>
       </c>
       <c r="E42" t="n">
-        <v>1385.48</v>
+        <v>1379.31</v>
       </c>
       <c r="F42" t="n">
-        <v>3646</v>
+        <v>27001</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Arcee AI</t>
+          <t>Alibaba</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -6657,52 +6737,52 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>70</v>
+        <v>235</v>
       </c>
       <c r="J42" t="n">
-        <v>70</v>
+        <v>22</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>dense</t>
+          <t>moe</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>artificial_analysis</t>
         </is>
       </c>
       <c r="M42" t="n">
-        <v>140</v>
+        <v>470</v>
       </c>
       <c r="N42" t="n">
-        <v>175</v>
+        <v>587.5</v>
       </c>
       <c r="O42" t="n">
-        <v>70</v>
+        <v>235</v>
       </c>
       <c r="P42" t="n">
-        <v>87.5</v>
+        <v>293.8</v>
       </c>
       <c r="Q42" t="n">
-        <v>35</v>
+        <v>117.5</v>
       </c>
       <c r="R42" t="n">
-        <v>43.8</v>
+        <v>146.9</v>
       </c>
       <c r="S42" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="T42" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="U42" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="T42" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U42" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="V42" s="5" t="inlineStr">
@@ -6715,9 +6795,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="X42" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="X42" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="Y42" s="5" t="inlineStr">
@@ -6725,24 +6805,24 @@
           <t>No</t>
         </is>
       </c>
-      <c r="Z42" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AA42" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB42" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AC42" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="Z42" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA42" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AB42" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AC42" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AD42" s="6" t="inlineStr">
@@ -6750,14 +6830,14 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="AE42" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AF42" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AE42" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF42" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AG42" s="6" t="inlineStr">
@@ -6767,12 +6847,12 @@
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>B200 SXM</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>RTX PRO 6000</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
     </row>
@@ -6782,24 +6862,24 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>qwen3-235b-a22b</t>
+          <t>trinity-large</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1374.62</v>
+        <v>1374.03</v>
       </c>
       <c r="D43" t="n">
-        <v>1369.95</v>
+        <v>1364.31</v>
       </c>
       <c r="E43" t="n">
-        <v>1379.29</v>
+        <v>1383.74</v>
       </c>
       <c r="F43" t="n">
-        <v>27001</v>
+        <v>3917</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alibaba</t>
+          <t>Arcee AI</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -6808,52 +6888,52 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>235</v>
+        <v>70</v>
       </c>
       <c r="J43" t="n">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>moe</t>
+          <t>dense</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>artificial_analysis</t>
+          <t>override</t>
         </is>
       </c>
       <c r="M43" t="n">
-        <v>470</v>
+        <v>140</v>
       </c>
       <c r="N43" t="n">
-        <v>587.5</v>
+        <v>175</v>
       </c>
       <c r="O43" t="n">
-        <v>235</v>
+        <v>70</v>
       </c>
       <c r="P43" t="n">
-        <v>293.8</v>
+        <v>87.5</v>
       </c>
       <c r="Q43" t="n">
-        <v>117.5</v>
+        <v>35</v>
       </c>
       <c r="R43" t="n">
-        <v>146.9</v>
+        <v>43.8</v>
       </c>
       <c r="S43" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="T43" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U43" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="T43" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U43" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="V43" s="5" t="inlineStr">
@@ -6866,9 +6946,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="X43" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="X43" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Y43" s="5" t="inlineStr">
@@ -6876,24 +6956,24 @@
           <t>No</t>
         </is>
       </c>
-      <c r="Z43" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AA43" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AB43" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AC43" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="Z43" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AA43" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB43" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AC43" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AD43" s="6" t="inlineStr">
@@ -6901,14 +6981,14 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="AE43" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AF43" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AE43" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AF43" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AG43" s="6" t="inlineStr">
@@ -6918,12 +6998,12 @@
       </c>
       <c r="AH43" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>B200 SXM</t>
         </is>
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>RTX PRO 6000</t>
         </is>
       </c>
     </row>
@@ -6937,16 +7017,16 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1371.68</v>
+        <v>1371.73</v>
       </c>
       <c r="D44" t="n">
-        <v>1367.42</v>
+        <v>1367.47</v>
       </c>
       <c r="E44" t="n">
-        <v>1375.94</v>
+        <v>1375.99</v>
       </c>
       <c r="F44" t="n">
-        <v>31140</v>
+        <v>31137</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -7088,13 +7168,13 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1368.81</v>
+        <v>1368.85</v>
       </c>
       <c r="D45" t="n">
-        <v>1362.98</v>
+        <v>1363.01</v>
       </c>
       <c r="E45" t="n">
-        <v>1374.65</v>
+        <v>1374.68</v>
       </c>
       <c r="F45" t="n">
         <v>13768</v>
@@ -7239,16 +7319,16 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1366.91</v>
+        <v>1367.08</v>
       </c>
       <c r="D46" t="n">
-        <v>1361.02</v>
+        <v>1361.19</v>
       </c>
       <c r="E46" t="n">
-        <v>1372.79</v>
+        <v>1372.96</v>
       </c>
       <c r="F46" t="n">
-        <v>11752</v>
+        <v>11756</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -7390,16 +7470,16 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1366.56</v>
+        <v>1366.58</v>
       </c>
       <c r="D47" t="n">
-        <v>1362.31</v>
+        <v>1362.33</v>
       </c>
       <c r="E47" t="n">
-        <v>1370.81</v>
+        <v>1370.83</v>
       </c>
       <c r="F47" t="n">
-        <v>36433</v>
+        <v>36431</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -7541,10 +7621,10 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1365.17</v>
+        <v>1365.16</v>
       </c>
       <c r="D48" t="n">
-        <v>1361.52</v>
+        <v>1361.51</v>
       </c>
       <c r="E48" t="n">
         <v>1368.81</v>
@@ -7698,7 +7778,7 @@
         <v>1353.67</v>
       </c>
       <c r="E49" t="n">
-        <v>1363.07</v>
+        <v>1363.08</v>
       </c>
       <c r="F49" t="n">
         <v>21788</v>
@@ -7843,13 +7923,13 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1356.15</v>
+        <v>1356.21</v>
       </c>
       <c r="D50" t="n">
-        <v>1347.75</v>
+        <v>1347.8</v>
       </c>
       <c r="E50" t="n">
-        <v>1364.56</v>
+        <v>1364.61</v>
       </c>
       <c r="F50" t="n">
         <v>5285</v>
@@ -7994,13 +8074,13 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1356.06</v>
+        <v>1356.07</v>
       </c>
       <c r="D51" t="n">
-        <v>1350.9</v>
+        <v>1350.91</v>
       </c>
       <c r="E51" t="n">
-        <v>1361.22</v>
+        <v>1361.23</v>
       </c>
       <c r="F51" t="n">
         <v>18223</v>
@@ -8145,16 +8225,16 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1353.99</v>
+        <v>1354.07</v>
       </c>
       <c r="D52" t="n">
-        <v>1349.62</v>
+        <v>1349.7</v>
       </c>
       <c r="E52" t="n">
-        <v>1358.35</v>
+        <v>1358.43</v>
       </c>
       <c r="F52" t="n">
-        <v>30749</v>
+        <v>30747</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -8296,16 +8376,16 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1352.97</v>
+        <v>1352.98</v>
       </c>
       <c r="D53" t="n">
-        <v>1349.53</v>
+        <v>1349.54</v>
       </c>
       <c r="E53" t="n">
-        <v>1356.4</v>
+        <v>1356.41</v>
       </c>
       <c r="F53" t="n">
-        <v>57068</v>
+        <v>57067</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -8447,7 +8527,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1352.96</v>
+        <v>1352.95</v>
       </c>
       <c r="D54" t="n">
         <v>1344.59</v>
@@ -8456,7 +8536,7 @@
         <v>1361.32</v>
       </c>
       <c r="F54" t="n">
-        <v>4949</v>
+        <v>4948</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -8594,40 +8674,40 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>llama-3.1-nemotron-ultra-253b-v1</t>
+          <t>ling-flash-2.0</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1347.17</v>
+        <v>1347.2</v>
       </c>
       <c r="D55" t="n">
-        <v>1335.46</v>
+        <v>1339.94</v>
       </c>
       <c r="E55" t="n">
-        <v>1358.87</v>
+        <v>1354.47</v>
       </c>
       <c r="F55" t="n">
-        <v>2546</v>
+        <v>6988</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Ant Group</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Nvidia Open Model</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="I55" t="n">
-        <v>253</v>
+        <v>103</v>
       </c>
       <c r="J55" t="n">
-        <v>253</v>
+        <v>6.1</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>dense</t>
+          <t>moe</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -8636,22 +8716,22 @@
         </is>
       </c>
       <c r="M55" t="n">
-        <v>506</v>
+        <v>206</v>
       </c>
       <c r="N55" t="n">
-        <v>632.5</v>
+        <v>257.5</v>
       </c>
       <c r="O55" t="n">
-        <v>253</v>
+        <v>103</v>
       </c>
       <c r="P55" t="n">
-        <v>316.2</v>
+        <v>128.8</v>
       </c>
       <c r="Q55" t="n">
-        <v>126.5</v>
+        <v>51.5</v>
       </c>
       <c r="R55" t="n">
-        <v>158.1</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="S55" s="5" t="inlineStr">
         <is>
@@ -8663,9 +8743,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="U55" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="U55" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="V55" s="5" t="inlineStr">
@@ -8678,9 +8758,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="X55" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="X55" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Y55" s="5" t="inlineStr">
@@ -8688,14 +8768,14 @@
           <t>No</t>
         </is>
       </c>
-      <c r="Z55" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AA55" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="Z55" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AA55" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AB55" s="5" t="inlineStr">
@@ -8703,9 +8783,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AC55" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AC55" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AD55" s="6" t="inlineStr">
@@ -8713,14 +8793,14 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="AE55" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AF55" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AE55" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AF55" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AG55" s="6" t="inlineStr">
@@ -8730,12 +8810,12 @@
       </c>
       <c r="AH55" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>B300 SXM</t>
         </is>
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>H200 SXM</t>
         </is>
       </c>
     </row>
@@ -8745,40 +8825,40 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ling-flash-2.0</t>
+          <t>llama-3.1-nemotron-ultra-253b-v1</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1347</v>
+        <v>1347.16</v>
       </c>
       <c r="D56" t="n">
-        <v>1339.74</v>
+        <v>1335.46</v>
       </c>
       <c r="E56" t="n">
-        <v>1354.27</v>
+        <v>1358.87</v>
       </c>
       <c r="F56" t="n">
-        <v>6991</v>
+        <v>2546</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Ant Group</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Nvidia Open Model</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>103</v>
+        <v>253</v>
       </c>
       <c r="J56" t="n">
-        <v>6.1</v>
+        <v>253</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>moe</t>
+          <t>dense</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -8787,22 +8867,22 @@
         </is>
       </c>
       <c r="M56" t="n">
-        <v>206</v>
+        <v>506</v>
       </c>
       <c r="N56" t="n">
-        <v>257.5</v>
+        <v>632.5</v>
       </c>
       <c r="O56" t="n">
-        <v>103</v>
+        <v>253</v>
       </c>
       <c r="P56" t="n">
-        <v>128.8</v>
+        <v>316.2</v>
       </c>
       <c r="Q56" t="n">
-        <v>51.5</v>
+        <v>126.5</v>
       </c>
       <c r="R56" t="n">
-        <v>64.40000000000001</v>
+        <v>158.1</v>
       </c>
       <c r="S56" s="5" t="inlineStr">
         <is>
@@ -8814,9 +8894,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="U56" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="U56" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="V56" s="5" t="inlineStr">
@@ -8829,9 +8909,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="X56" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="X56" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="Y56" s="5" t="inlineStr">
@@ -8839,14 +8919,14 @@
           <t>No</t>
         </is>
       </c>
-      <c r="Z56" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AA56" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="Z56" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA56" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AB56" s="5" t="inlineStr">
@@ -8854,9 +8934,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AC56" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AC56" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AD56" s="6" t="inlineStr">
@@ -8864,14 +8944,14 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="AE56" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AF56" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AE56" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF56" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AG56" s="6" t="inlineStr">
@@ -8881,12 +8961,12 @@
       </c>
       <c r="AH56" t="inlineStr">
         <is>
-          <t>B300 SXM</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>H200 SXM</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
     </row>
@@ -8900,13 +8980,13 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1346.96</v>
+        <v>1346.99</v>
       </c>
       <c r="D57" t="n">
-        <v>1337.52</v>
+        <v>1337.55</v>
       </c>
       <c r="E57" t="n">
-        <v>1356.4</v>
+        <v>1356.43</v>
       </c>
       <c r="F57" t="n">
         <v>3932</v>
@@ -9051,16 +9131,16 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1346.73</v>
+        <v>1346.84</v>
       </c>
       <c r="D58" t="n">
-        <v>1338.9</v>
+        <v>1339.01</v>
       </c>
       <c r="E58" t="n">
-        <v>1354.55</v>
+        <v>1354.67</v>
       </c>
       <c r="F58" t="n">
-        <v>6686</v>
+        <v>6683</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -9202,13 +9282,13 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1346.53</v>
+        <v>1346.55</v>
       </c>
       <c r="D59" t="n">
-        <v>1339.13</v>
+        <v>1339.16</v>
       </c>
       <c r="E59" t="n">
-        <v>1353.92</v>
+        <v>1353.95</v>
       </c>
       <c r="F59" t="n">
         <v>6566</v>
@@ -9273,13 +9353,13 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1341.56</v>
+        <v>1341.55</v>
       </c>
       <c r="D60" t="n">
         <v>1332.04</v>
       </c>
       <c r="E60" t="n">
-        <v>1351.08</v>
+        <v>1351.07</v>
       </c>
       <c r="F60" t="n">
         <v>3829</v>
@@ -9424,13 +9504,13 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1341.02</v>
+        <v>1341.04</v>
       </c>
       <c r="D61" t="n">
-        <v>1331.11</v>
+        <v>1331.13</v>
       </c>
       <c r="E61" t="n">
-        <v>1350.93</v>
+        <v>1350.95</v>
       </c>
       <c r="F61" t="n">
         <v>3398</v>
@@ -9575,16 +9655,16 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1335.75</v>
+        <v>1335.8</v>
       </c>
       <c r="D62" t="n">
-        <v>1331.36</v>
+        <v>1331.41</v>
       </c>
       <c r="E62" t="n">
-        <v>1340.14</v>
+        <v>1340.2</v>
       </c>
       <c r="F62" t="n">
-        <v>25986</v>
+        <v>25985</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -9726,13 +9806,13 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1334.98</v>
+        <v>1334.95</v>
       </c>
       <c r="D63" t="n">
-        <v>1331.32</v>
+        <v>1331.28</v>
       </c>
       <c r="E63" t="n">
-        <v>1338.64</v>
+        <v>1338.61</v>
       </c>
       <c r="F63" t="n">
         <v>41392</v>
@@ -9877,13 +9957,13 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1333.17</v>
+        <v>1333.14</v>
       </c>
       <c r="D64" t="n">
-        <v>1329.62</v>
+        <v>1329.59</v>
       </c>
       <c r="E64" t="n">
-        <v>1336.72</v>
+        <v>1336.69</v>
       </c>
       <c r="F64" t="n">
         <v>59655</v>
@@ -10028,16 +10108,16 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1330.51</v>
+        <v>1330.56</v>
       </c>
       <c r="D65" t="n">
-        <v>1324.35</v>
+        <v>1324.41</v>
       </c>
       <c r="E65" t="n">
-        <v>1336.66</v>
+        <v>1336.72</v>
       </c>
       <c r="F65" t="n">
-        <v>12234</v>
+        <v>12237</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -10179,13 +10259,13 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1328.83</v>
+        <v>1328.55</v>
       </c>
       <c r="D66" t="n">
-        <v>1307.44</v>
+        <v>1307.16</v>
       </c>
       <c r="E66" t="n">
-        <v>1350.22</v>
+        <v>1349.95</v>
       </c>
       <c r="F66" t="n">
         <v>812</v>
@@ -10330,13 +10410,13 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1328.07</v>
+        <v>1328.08</v>
       </c>
       <c r="D67" t="n">
-        <v>1323.38</v>
+        <v>1323.39</v>
       </c>
       <c r="E67" t="n">
-        <v>1332.75</v>
+        <v>1332.77</v>
       </c>
       <c r="F67" t="n">
         <v>27264</v>
@@ -10481,13 +10561,13 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1327.44</v>
+        <v>1327.42</v>
       </c>
       <c r="D68" t="n">
-        <v>1323.23</v>
+        <v>1323.21</v>
       </c>
       <c r="E68" t="n">
-        <v>1331.65</v>
+        <v>1331.63</v>
       </c>
       <c r="F68" t="n">
         <v>40914</v>
@@ -10635,7 +10715,7 @@
         <v>1327.04</v>
       </c>
       <c r="D69" t="n">
-        <v>1314.91</v>
+        <v>1314.92</v>
       </c>
       <c r="E69" t="n">
         <v>1339.17</v>
@@ -10786,10 +10866,10 @@
         <v>1323.13</v>
       </c>
       <c r="D70" t="n">
-        <v>1314.86</v>
+        <v>1314.87</v>
       </c>
       <c r="E70" t="n">
-        <v>1331.39</v>
+        <v>1331.4</v>
       </c>
       <c r="F70" t="n">
         <v>6793</v>
@@ -10934,16 +11014,16 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1322.25</v>
+        <v>1322.19</v>
       </c>
       <c r="D71" t="n">
-        <v>1317.58</v>
+        <v>1317.52</v>
       </c>
       <c r="E71" t="n">
-        <v>1326.93</v>
+        <v>1326.86</v>
       </c>
       <c r="F71" t="n">
-        <v>31029</v>
+        <v>31026</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -11085,16 +11165,16 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1320.32</v>
+        <v>1320.36</v>
       </c>
       <c r="D72" t="n">
-        <v>1313.1</v>
+        <v>1313.14</v>
       </c>
       <c r="E72" t="n">
-        <v>1327.53</v>
+        <v>1327.57</v>
       </c>
       <c r="F72" t="n">
-        <v>7148</v>
+        <v>7147</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -11245,7 +11325,7 @@
         <v>1324.34</v>
       </c>
       <c r="F73" t="n">
-        <v>23179</v>
+        <v>23177</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -11387,16 +11467,16 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1319.04</v>
+        <v>1319.02</v>
       </c>
       <c r="D74" t="n">
-        <v>1315.63</v>
+        <v>1315.6</v>
       </c>
       <c r="E74" t="n">
-        <v>1322.45</v>
+        <v>1322.43</v>
       </c>
       <c r="F74" t="n">
-        <v>55436</v>
+        <v>55437</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -11538,13 +11618,13 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>1317.9</v>
+        <v>1317.89</v>
       </c>
       <c r="D75" t="n">
-        <v>1312.22</v>
+        <v>1312.21</v>
       </c>
       <c r="E75" t="n">
-        <v>1323.58</v>
+        <v>1323.57</v>
       </c>
       <c r="F75" t="n">
         <v>16479</v>
@@ -11609,16 +11689,16 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>1317.24</v>
+        <v>1317.35</v>
       </c>
       <c r="D76" t="n">
-        <v>1311.61</v>
+        <v>1311.72</v>
       </c>
       <c r="E76" t="n">
-        <v>1322.88</v>
+        <v>1322.98</v>
       </c>
       <c r="F76" t="n">
-        <v>15393</v>
+        <v>15394</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -11760,16 +11840,16 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1317</v>
+        <v>1316.99</v>
       </c>
       <c r="D77" t="n">
-        <v>1310.65</v>
+        <v>1310.64</v>
       </c>
       <c r="E77" t="n">
-        <v>1323.34</v>
+        <v>1323.33</v>
       </c>
       <c r="F77" t="n">
-        <v>10752</v>
+        <v>10751</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -11911,13 +11991,13 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1314.33</v>
+        <v>1314.34</v>
       </c>
       <c r="D78" t="n">
-        <v>1309.82</v>
+        <v>1309.83</v>
       </c>
       <c r="E78" t="n">
-        <v>1318.84</v>
+        <v>1318.86</v>
       </c>
       <c r="F78" t="n">
         <v>24746</v>
@@ -12062,13 +12142,13 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>1313.82</v>
+        <v>1313.8</v>
       </c>
       <c r="D79" t="n">
-        <v>1309.94</v>
+        <v>1309.91</v>
       </c>
       <c r="E79" t="n">
-        <v>1317.71</v>
+        <v>1317.69</v>
       </c>
       <c r="F79" t="n">
         <v>45460</v>
@@ -12216,7 +12296,7 @@
         <v>1306.87</v>
       </c>
       <c r="D80" t="n">
-        <v>1302.2</v>
+        <v>1302.19</v>
       </c>
       <c r="E80" t="n">
         <v>1311.54</v>
@@ -12364,13 +12444,13 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1305.89</v>
+        <v>1305.86</v>
       </c>
       <c r="D81" t="n">
-        <v>1300.24</v>
+        <v>1300.21</v>
       </c>
       <c r="E81" t="n">
-        <v>1311.54</v>
+        <v>1311.52</v>
       </c>
       <c r="F81" t="n">
         <v>19622</v>
@@ -12515,13 +12595,13 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>1305.77</v>
+        <v>1305.83</v>
       </c>
       <c r="D82" t="n">
-        <v>1297.5</v>
+        <v>1297.57</v>
       </c>
       <c r="E82" t="n">
-        <v>1314.03</v>
+        <v>1314.1</v>
       </c>
       <c r="F82" t="n">
         <v>5863</v>
@@ -12666,13 +12746,13 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>1304.91</v>
+        <v>1304.9</v>
       </c>
       <c r="D83" t="n">
-        <v>1300.52</v>
+        <v>1300.51</v>
       </c>
       <c r="E83" t="n">
-        <v>1309.3</v>
+        <v>1309.29</v>
       </c>
       <c r="F83" t="n">
         <v>28081</v>
@@ -12823,10 +12903,10 @@
         <v>1299.75</v>
       </c>
       <c r="E84" t="n">
-        <v>1308.71</v>
+        <v>1308.7</v>
       </c>
       <c r="F84" t="n">
-        <v>33879</v>
+        <v>33878</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -12968,13 +13048,13 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>1303.19</v>
+        <v>1303.18</v>
       </c>
       <c r="D85" t="n">
-        <v>1293.88</v>
+        <v>1293.87</v>
       </c>
       <c r="E85" t="n">
-        <v>1312.5</v>
+        <v>1312.49</v>
       </c>
       <c r="F85" t="n">
         <v>4177</v>
@@ -13270,7 +13350,7 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>1298.58</v>
+        <v>1298.59</v>
       </c>
       <c r="D87" t="n">
         <v>1290.83</v>
@@ -13421,13 +13501,13 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>1293.33</v>
+        <v>1293.32</v>
       </c>
       <c r="D88" t="n">
-        <v>1289.64</v>
+        <v>1289.63</v>
       </c>
       <c r="E88" t="n">
-        <v>1297.02</v>
+        <v>1297.01</v>
       </c>
       <c r="F88" t="n">
         <v>55234</v>
@@ -13572,13 +13652,13 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>1288.5</v>
+        <v>1288.48</v>
       </c>
       <c r="D89" t="n">
-        <v>1281.2</v>
+        <v>1281.17</v>
       </c>
       <c r="E89" t="n">
-        <v>1295.8</v>
+        <v>1295.78</v>
       </c>
       <c r="F89" t="n">
         <v>8659</v>
@@ -13723,13 +13803,13 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>1287.94</v>
+        <v>1287.9</v>
       </c>
       <c r="D90" t="n">
-        <v>1284.61</v>
+        <v>1284.57</v>
       </c>
       <c r="E90" t="n">
-        <v>1291.27</v>
+        <v>1291.23</v>
       </c>
       <c r="F90" t="n">
         <v>75764</v>
@@ -13874,16 +13954,16 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>1286.92</v>
+        <v>1286.58</v>
       </c>
       <c r="D91" t="n">
-        <v>1278.5</v>
+        <v>1278.16</v>
       </c>
       <c r="E91" t="n">
-        <v>1295.34</v>
+        <v>1295</v>
       </c>
       <c r="F91" t="n">
-        <v>5620</v>
+        <v>5618</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -14025,13 +14105,13 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>1286.38</v>
+        <v>1286.37</v>
       </c>
       <c r="D92" t="n">
-        <v>1275.9</v>
+        <v>1275.89</v>
       </c>
       <c r="E92" t="n">
-        <v>1296.85</v>
+        <v>1296.84</v>
       </c>
       <c r="F92" t="n">
         <v>2846</v>
@@ -14176,13 +14256,13 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>1286.03</v>
+        <v>1286</v>
       </c>
       <c r="D93" t="n">
-        <v>1276.06</v>
+        <v>1276.02</v>
       </c>
       <c r="E93" t="n">
-        <v>1296.01</v>
+        <v>1295.97</v>
       </c>
       <c r="F93" t="n">
         <v>3749</v>
@@ -14327,16 +14407,16 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1284.88</v>
+        <v>1285</v>
       </c>
       <c r="D94" t="n">
-        <v>1277.62</v>
+        <v>1277.74</v>
       </c>
       <c r="E94" t="n">
-        <v>1292.15</v>
+        <v>1292.26</v>
       </c>
       <c r="F94" t="n">
-        <v>8435</v>
+        <v>8441</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -14478,13 +14558,13 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1279.33</v>
+        <v>1279.29</v>
       </c>
       <c r="D95" t="n">
-        <v>1272.47</v>
+        <v>1272.44</v>
       </c>
       <c r="E95" t="n">
-        <v>1286.18</v>
+        <v>1286.15</v>
       </c>
       <c r="F95" t="n">
         <v>10069</v>
@@ -14629,13 +14709,13 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>1277.12</v>
+        <v>1277.09</v>
       </c>
       <c r="D96" t="n">
-        <v>1271.8</v>
+        <v>1271.77</v>
       </c>
       <c r="E96" t="n">
-        <v>1282.44</v>
+        <v>1282.41</v>
       </c>
       <c r="F96" t="n">
         <v>19661</v>
@@ -14780,13 +14860,13 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1276.17</v>
+        <v>1276.15</v>
       </c>
       <c r="D97" t="n">
-        <v>1269.61</v>
+        <v>1269.58</v>
       </c>
       <c r="E97" t="n">
-        <v>1282.73</v>
+        <v>1282.71</v>
       </c>
       <c r="F97" t="n">
         <v>9869</v>
@@ -14931,13 +15011,13 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>1275.76</v>
+        <v>1275.72</v>
       </c>
       <c r="D98" t="n">
-        <v>1272.2</v>
+        <v>1272.16</v>
       </c>
       <c r="E98" t="n">
-        <v>1279.32</v>
+        <v>1279.28</v>
       </c>
       <c r="F98" t="n">
         <v>156880</v>
@@ -15082,13 +15162,13 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>1273.69</v>
+        <v>1273.68</v>
       </c>
       <c r="D99" t="n">
-        <v>1267.81</v>
+        <v>1267.8</v>
       </c>
       <c r="E99" t="n">
-        <v>1279.57</v>
+        <v>1279.56</v>
       </c>
       <c r="F99" t="n">
         <v>14677</v>
@@ -15233,13 +15313,13 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>1270.4</v>
+        <v>1270.39</v>
       </c>
       <c r="D100" t="n">
-        <v>1262.29</v>
+        <v>1262.28</v>
       </c>
       <c r="E100" t="n">
-        <v>1278.51</v>
+        <v>1278.5</v>
       </c>
       <c r="F100" t="n">
         <v>5430</v>
@@ -15384,13 +15464,13 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1266.89</v>
+        <v>1266.86</v>
       </c>
       <c r="D101" t="n">
-        <v>1262.04</v>
+        <v>1262.01</v>
       </c>
       <c r="E101" t="n">
-        <v>1271.74</v>
+        <v>1271.71</v>
       </c>
       <c r="F101" t="n">
         <v>27123</v>
@@ -15535,13 +15615,13 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>1265.36</v>
+        <v>1265.32</v>
       </c>
       <c r="D102" t="n">
-        <v>1261.59</v>
+        <v>1261.55</v>
       </c>
       <c r="E102" t="n">
-        <v>1269.13</v>
+        <v>1269.09</v>
       </c>
       <c r="F102" t="n">
         <v>54615</v>
@@ -15686,13 +15766,13 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>1263.99</v>
+        <v>1263.94</v>
       </c>
       <c r="D103" t="n">
-        <v>1257.71</v>
+        <v>1257.67</v>
       </c>
       <c r="E103" t="n">
-        <v>1270.27</v>
+        <v>1270.22</v>
       </c>
       <c r="F103" t="n">
         <v>15147</v>
@@ -15837,13 +15917,13 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>1261.63</v>
+        <v>1261.6</v>
       </c>
       <c r="D104" t="n">
-        <v>1257.32</v>
+        <v>1257.28</v>
       </c>
       <c r="E104" t="n">
-        <v>1265.94</v>
+        <v>1265.91</v>
       </c>
       <c r="F104" t="n">
         <v>77556</v>
@@ -15988,13 +16068,13 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>1261.56</v>
+        <v>1261.53</v>
       </c>
       <c r="D105" t="n">
-        <v>1256.63</v>
+        <v>1256.6</v>
       </c>
       <c r="E105" t="n">
-        <v>1266.49</v>
+        <v>1266.46</v>
       </c>
       <c r="F105" t="n">
         <v>37325</v>
@@ -16139,13 +16219,13 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>1255.92</v>
+        <v>1255.91</v>
       </c>
       <c r="D106" t="n">
-        <v>1251.37</v>
+        <v>1251.35</v>
       </c>
       <c r="E106" t="n">
-        <v>1260.47</v>
+        <v>1260.46</v>
       </c>
       <c r="F106" t="n">
         <v>24126</v>
@@ -16290,13 +16370,13 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>1251.82</v>
+        <v>1251.81</v>
       </c>
       <c r="D107" t="n">
-        <v>1241.03</v>
+        <v>1241.02</v>
       </c>
       <c r="E107" t="n">
-        <v>1262.6</v>
+        <v>1262.59</v>
       </c>
       <c r="F107" t="n">
         <v>3335</v>
@@ -16441,13 +16521,13 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>1249.95</v>
+        <v>1249.91</v>
       </c>
       <c r="D108" t="n">
-        <v>1243.36</v>
+        <v>1243.32</v>
       </c>
       <c r="E108" t="n">
-        <v>1256.54</v>
+        <v>1256.5</v>
       </c>
       <c r="F108" t="n">
         <v>10141</v>
@@ -16592,13 +16672,13 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>1238.77</v>
+        <v>1238.74</v>
       </c>
       <c r="D109" t="n">
-        <v>1231.55</v>
+        <v>1231.52</v>
       </c>
       <c r="E109" t="n">
-        <v>1245.98</v>
+        <v>1245.96</v>
       </c>
       <c r="F109" t="n">
         <v>8854</v>
@@ -16743,13 +16823,13 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>1236.87</v>
+        <v>1236.85</v>
       </c>
       <c r="D110" t="n">
-        <v>1227.78</v>
+        <v>1227.76</v>
       </c>
       <c r="E110" t="n">
-        <v>1245.97</v>
+        <v>1245.95</v>
       </c>
       <c r="F110" t="n">
         <v>4780</v>
@@ -16894,13 +16974,13 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>1233.75</v>
+        <v>1233.72</v>
       </c>
       <c r="D111" t="n">
-        <v>1228.2</v>
+        <v>1228.17</v>
       </c>
       <c r="E111" t="n">
-        <v>1239.3</v>
+        <v>1239.26</v>
       </c>
       <c r="F111" t="n">
         <v>26191</v>
@@ -17045,13 +17125,13 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>1232.88</v>
+        <v>1232.84</v>
       </c>
       <c r="D112" t="n">
-        <v>1227.61</v>
+        <v>1227.57</v>
       </c>
       <c r="E112" t="n">
-        <v>1238.15</v>
+        <v>1238.11</v>
       </c>
       <c r="F112" t="n">
         <v>39296</v>
@@ -17196,13 +17276,13 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>1229.2</v>
+        <v>1229.16</v>
       </c>
       <c r="D113" t="n">
-        <v>1224.66</v>
+        <v>1224.62</v>
       </c>
       <c r="E113" t="n">
-        <v>1233.74</v>
+        <v>1233.7</v>
       </c>
       <c r="F113" t="n">
         <v>51417</v>
@@ -17347,13 +17427,13 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>1226.65</v>
+        <v>1226.62</v>
       </c>
       <c r="D114" t="n">
-        <v>1221.88</v>
+        <v>1221.84</v>
       </c>
       <c r="E114" t="n">
-        <v>1231.43</v>
+        <v>1231.39</v>
       </c>
       <c r="F114" t="n">
         <v>54038</v>
@@ -17498,13 +17578,13 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>1222.91</v>
+        <v>1222.87</v>
       </c>
       <c r="D115" t="n">
-        <v>1219.19</v>
+        <v>1219.15</v>
       </c>
       <c r="E115" t="n">
-        <v>1226.62</v>
+        <v>1226.58</v>
       </c>
       <c r="F115" t="n">
         <v>104636</v>
@@ -17649,13 +17729,13 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>1222.87</v>
+        <v>1222.85</v>
       </c>
       <c r="D116" t="n">
-        <v>1215.92</v>
+        <v>1215.9</v>
       </c>
       <c r="E116" t="n">
-        <v>1229.82</v>
+        <v>1229.8</v>
       </c>
       <c r="F116" t="n">
         <v>9827</v>
@@ -17951,13 +18031,13 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>1213.12</v>
+        <v>1213.1</v>
       </c>
       <c r="D118" t="n">
-        <v>1208.09</v>
+        <v>1208.07</v>
       </c>
       <c r="E118" t="n">
-        <v>1218.15</v>
+        <v>1218.13</v>
       </c>
       <c r="F118" t="n">
         <v>24142</v>
@@ -18102,13 +18182,13 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>1212.45</v>
+        <v>1212.4</v>
       </c>
       <c r="D119" t="n">
-        <v>1201.64</v>
+        <v>1201.59</v>
       </c>
       <c r="E119" t="n">
-        <v>1223.26</v>
+        <v>1223.22</v>
       </c>
       <c r="F119" t="n">
         <v>4653</v>
@@ -18253,7 +18333,7 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>1211.38</v>
+        <v>1211.39</v>
       </c>
       <c r="D120" t="n">
         <v>1207.28</v>
@@ -18404,13 +18484,13 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>1208.29</v>
+        <v>1208.25</v>
       </c>
       <c r="D121" t="n">
-        <v>1197.19</v>
+        <v>1197.15</v>
       </c>
       <c r="E121" t="n">
-        <v>1219.4</v>
+        <v>1219.36</v>
       </c>
       <c r="F121" t="n">
         <v>3092</v>
@@ -18555,13 +18635,13 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>1203.59</v>
+        <v>1203.55</v>
       </c>
       <c r="D122" t="n">
-        <v>1197.48</v>
+        <v>1197.44</v>
       </c>
       <c r="E122" t="n">
-        <v>1209.71</v>
+        <v>1209.67</v>
       </c>
       <c r="F122" t="n">
         <v>21744</v>
@@ -18706,13 +18786,13 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>1198.64</v>
+        <v>1198.61</v>
       </c>
       <c r="D123" t="n">
-        <v>1194.59</v>
+        <v>1194.56</v>
       </c>
       <c r="E123" t="n">
-        <v>1202.69</v>
+        <v>1202.66</v>
       </c>
       <c r="F123" t="n">
         <v>46618</v>
@@ -18857,13 +18937,13 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>1197.68</v>
+        <v>1197.64</v>
       </c>
       <c r="D124" t="n">
-        <v>1192.53</v>
+        <v>1192.5</v>
       </c>
       <c r="E124" t="n">
-        <v>1202.82</v>
+        <v>1202.79</v>
       </c>
       <c r="F124" t="n">
         <v>25055</v>
@@ -19008,13 +19088,13 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>1196.84</v>
+        <v>1196.8</v>
       </c>
       <c r="D125" t="n">
-        <v>1192.57</v>
+        <v>1192.54</v>
       </c>
       <c r="E125" t="n">
-        <v>1201.1</v>
+        <v>1201.06</v>
       </c>
       <c r="F125" t="n">
         <v>73505</v>
@@ -19159,13 +19239,13 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>1194.65</v>
+        <v>1194.6</v>
       </c>
       <c r="D126" t="n">
-        <v>1188.54</v>
+        <v>1188.49</v>
       </c>
       <c r="E126" t="n">
-        <v>1200.76</v>
+        <v>1200.72</v>
       </c>
       <c r="F126" t="n">
         <v>32196</v>
@@ -19310,13 +19390,13 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>1191.1</v>
+        <v>1191.09</v>
       </c>
       <c r="D127" t="n">
-        <v>1183.93</v>
+        <v>1183.92</v>
       </c>
       <c r="E127" t="n">
-        <v>1198.27</v>
+        <v>1198.26</v>
       </c>
       <c r="F127" t="n">
         <v>9902</v>
@@ -19461,13 +19541,13 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>1190.56</v>
+        <v>1190.53</v>
       </c>
       <c r="D128" t="n">
-        <v>1183.44</v>
+        <v>1183.4</v>
       </c>
       <c r="E128" t="n">
-        <v>1197.69</v>
+        <v>1197.65</v>
       </c>
       <c r="F128" t="n">
         <v>17841</v>
@@ -19612,13 +19692,13 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>1184.35</v>
+        <v>1184.31</v>
       </c>
       <c r="D129" t="n">
-        <v>1174.89</v>
+        <v>1174.85</v>
       </c>
       <c r="E129" t="n">
-        <v>1193.81</v>
+        <v>1193.77</v>
       </c>
       <c r="F129" t="n">
         <v>8214</v>
@@ -19763,13 +19843,13 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>1184.06</v>
+        <v>1184.01</v>
       </c>
       <c r="D130" t="n">
-        <v>1172.54</v>
+        <v>1172.49</v>
       </c>
       <c r="E130" t="n">
-        <v>1195.58</v>
+        <v>1195.53</v>
       </c>
       <c r="F130" t="n">
         <v>4933</v>
@@ -19914,13 +19994,13 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>1183.52</v>
+        <v>1183.49</v>
       </c>
       <c r="D131" t="n">
-        <v>1176.69</v>
+        <v>1176.66</v>
       </c>
       <c r="E131" t="n">
-        <v>1190.35</v>
+        <v>1190.32</v>
       </c>
       <c r="F131" t="n">
         <v>15483</v>
@@ -20065,13 +20145,13 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>1181.98</v>
+        <v>1181.93</v>
       </c>
       <c r="D132" t="n">
-        <v>1173.97</v>
+        <v>1173.92</v>
       </c>
       <c r="E132" t="n">
-        <v>1189.98</v>
+        <v>1189.93</v>
       </c>
       <c r="F132" t="n">
         <v>12636</v>
@@ -20136,13 +20216,13 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>1181.91</v>
+        <v>1181.86</v>
       </c>
       <c r="D133" t="n">
-        <v>1172.23</v>
+        <v>1172.17</v>
       </c>
       <c r="E133" t="n">
-        <v>1191.6</v>
+        <v>1191.54</v>
       </c>
       <c r="F133" t="n">
         <v>7967</v>
@@ -20207,13 +20287,13 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>1181.64</v>
+        <v>1181.58</v>
       </c>
       <c r="D134" t="n">
-        <v>1172.96</v>
+        <v>1172.9</v>
       </c>
       <c r="E134" t="n">
-        <v>1190.33</v>
+        <v>1190.27</v>
       </c>
       <c r="F134" t="n">
         <v>6643</v>
@@ -20358,13 +20438,13 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>1180</v>
+        <v>1179.93</v>
       </c>
       <c r="D135" t="n">
-        <v>1173.93</v>
+        <v>1173.86</v>
       </c>
       <c r="E135" t="n">
-        <v>1186.07</v>
+        <v>1186</v>
       </c>
       <c r="F135" t="n">
         <v>23893</v>
@@ -20509,13 +20589,13 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>1179.16</v>
+        <v>1179.11</v>
       </c>
       <c r="D136" t="n">
-        <v>1173.25</v>
+        <v>1173.2</v>
       </c>
       <c r="E136" t="n">
-        <v>1185.07</v>
+        <v>1185.02</v>
       </c>
       <c r="F136" t="n">
         <v>32836</v>
@@ -20580,13 +20660,13 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>1179.05</v>
+        <v>1179.02</v>
       </c>
       <c r="D137" t="n">
-        <v>1167.85</v>
+        <v>1167.82</v>
       </c>
       <c r="E137" t="n">
-        <v>1190.24</v>
+        <v>1190.21</v>
       </c>
       <c r="F137" t="n">
         <v>3191</v>
@@ -20731,13 +20811,13 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>1177.72</v>
+        <v>1177.69</v>
       </c>
       <c r="D138" t="n">
-        <v>1167.89</v>
+        <v>1167.86</v>
       </c>
       <c r="E138" t="n">
-        <v>1187.55</v>
+        <v>1187.52</v>
       </c>
       <c r="F138" t="n">
         <v>6534</v>
@@ -20882,13 +20962,13 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>1174.83</v>
+        <v>1174.77</v>
       </c>
       <c r="D139" t="n">
-        <v>1164.4</v>
+        <v>1164.34</v>
       </c>
       <c r="E139" t="n">
-        <v>1185.26</v>
+        <v>1185.2</v>
       </c>
       <c r="F139" t="n">
         <v>5006</v>
@@ -21033,13 +21113,13 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>1172.48</v>
+        <v>1172.44</v>
       </c>
       <c r="D140" t="n">
-        <v>1166.27</v>
+        <v>1166.23</v>
       </c>
       <c r="E140" t="n">
-        <v>1178.69</v>
+        <v>1178.65</v>
       </c>
       <c r="F140" t="n">
         <v>22479</v>
@@ -21184,13 +21264,13 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>1171.27</v>
+        <v>1171.25</v>
       </c>
       <c r="D141" t="n">
-        <v>1163.86</v>
+        <v>1163.83</v>
       </c>
       <c r="E141" t="n">
-        <v>1178.69</v>
+        <v>1178.66</v>
       </c>
       <c r="F141" t="n">
         <v>16057</v>
@@ -21335,13 +21415,13 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>1170.89</v>
+        <v>1170.86</v>
       </c>
       <c r="D142" t="n">
-        <v>1164.98</v>
+        <v>1164.95</v>
       </c>
       <c r="E142" t="n">
-        <v>1176.8</v>
+        <v>1176.77</v>
       </c>
       <c r="F142" t="n">
         <v>17763</v>
@@ -21486,13 +21566,13 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>1170.49</v>
+        <v>1170.46</v>
       </c>
       <c r="D143" t="n">
-        <v>1164.99</v>
+        <v>1164.96</v>
       </c>
       <c r="E143" t="n">
-        <v>1176</v>
+        <v>1175.96</v>
       </c>
       <c r="F143" t="n">
         <v>38491</v>
@@ -21637,13 +21717,13 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>1167.22</v>
+        <v>1167.18</v>
       </c>
       <c r="D144" t="n">
-        <v>1159.14</v>
+        <v>1159.11</v>
       </c>
       <c r="E144" t="n">
-        <v>1175.29</v>
+        <v>1175.26</v>
       </c>
       <c r="F144" t="n">
         <v>10224</v>
@@ -21788,13 +21868,13 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>1166.4</v>
+        <v>1166.37</v>
       </c>
       <c r="D145" t="n">
-        <v>1158.71</v>
+        <v>1158.68</v>
       </c>
       <c r="E145" t="n">
-        <v>1174.1</v>
+        <v>1174.07</v>
       </c>
       <c r="F145" t="n">
         <v>7936</v>
@@ -21939,13 +22019,13 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>1164.38</v>
+        <v>1164.35</v>
       </c>
       <c r="D146" t="n">
-        <v>1152.43</v>
+        <v>1152.4</v>
       </c>
       <c r="E146" t="n">
-        <v>1176.33</v>
+        <v>1176.3</v>
       </c>
       <c r="F146" t="n">
         <v>3776</v>
@@ -22090,13 +22170,13 @@
         </is>
       </c>
       <c r="C147" t="n">
-        <v>1156.82</v>
+        <v>1156.85</v>
       </c>
       <c r="D147" t="n">
-        <v>1145.31</v>
+        <v>1145.34</v>
       </c>
       <c r="E147" t="n">
-        <v>1168.32</v>
+        <v>1168.36</v>
       </c>
       <c r="F147" t="n">
         <v>3233</v>
@@ -22241,13 +22321,13 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>1155.65</v>
+        <v>1155.6</v>
       </c>
       <c r="D148" t="n">
-        <v>1147.26</v>
+        <v>1147.21</v>
       </c>
       <c r="E148" t="n">
-        <v>1164.04</v>
+        <v>1163.99</v>
       </c>
       <c r="F148" t="n">
         <v>6837</v>
@@ -22392,13 +22472,13 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>1155.02</v>
+        <v>1155</v>
       </c>
       <c r="D149" t="n">
-        <v>1142.39</v>
+        <v>1142.37</v>
       </c>
       <c r="E149" t="n">
-        <v>1167.65</v>
+        <v>1167.63</v>
       </c>
       <c r="F149" t="n">
         <v>3584</v>
@@ -22543,13 +22623,13 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>1152.05</v>
+        <v>1152.01</v>
       </c>
       <c r="D150" t="n">
-        <v>1138.83</v>
+        <v>1138.79</v>
       </c>
       <c r="E150" t="n">
-        <v>1165.27</v>
+        <v>1165.23</v>
       </c>
       <c r="F150" t="n">
         <v>4155</v>
@@ -22694,13 +22774,13 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>1151.66</v>
+        <v>1151.62</v>
       </c>
       <c r="D151" t="n">
-        <v>1136.25</v>
+        <v>1136.21</v>
       </c>
       <c r="E151" t="n">
-        <v>1167.08</v>
+        <v>1167.03</v>
       </c>
       <c r="F151" t="n">
         <v>1679</v>
@@ -22845,13 +22925,13 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>1149.8</v>
+        <v>1149.75</v>
       </c>
       <c r="D152" t="n">
-        <v>1137.49</v>
+        <v>1137.44</v>
       </c>
       <c r="E152" t="n">
-        <v>1162.12</v>
+        <v>1162.06</v>
       </c>
       <c r="F152" t="n">
         <v>2571</v>
@@ -22996,13 +23076,13 @@
         </is>
       </c>
       <c r="C153" t="n">
-        <v>1149.32</v>
+        <v>1149.29</v>
       </c>
       <c r="D153" t="n">
-        <v>1142.67</v>
+        <v>1142.63</v>
       </c>
       <c r="E153" t="n">
-        <v>1155.97</v>
+        <v>1155.94</v>
       </c>
       <c r="F153" t="n">
         <v>19402</v>
@@ -23147,13 +23227,13 @@
         </is>
       </c>
       <c r="C154" t="n">
-        <v>1148.83</v>
+        <v>1148.78</v>
       </c>
       <c r="D154" t="n">
-        <v>1139.56</v>
+        <v>1139.51</v>
       </c>
       <c r="E154" t="n">
-        <v>1158.1</v>
+        <v>1158.05</v>
       </c>
       <c r="F154" t="n">
         <v>7046</v>
@@ -23298,13 +23378,13 @@
         </is>
       </c>
       <c r="C155" t="n">
-        <v>1146.67</v>
+        <v>1146.61</v>
       </c>
       <c r="D155" t="n">
-        <v>1129.53</v>
+        <v>1129.47</v>
       </c>
       <c r="E155" t="n">
-        <v>1163.82</v>
+        <v>1163.76</v>
       </c>
       <c r="F155" t="n">
         <v>1295</v>
@@ -23449,13 +23529,13 @@
         </is>
       </c>
       <c r="C156" t="n">
-        <v>1143.59</v>
+        <v>1143.55</v>
       </c>
       <c r="D156" t="n">
-        <v>1133.69</v>
+        <v>1133.65</v>
       </c>
       <c r="E156" t="n">
-        <v>1153.49</v>
+        <v>1153.45</v>
       </c>
       <c r="F156" t="n">
         <v>4735</v>
@@ -23600,13 +23680,13 @@
         </is>
       </c>
       <c r="C157" t="n">
-        <v>1142.73</v>
+        <v>1142.69</v>
       </c>
       <c r="D157" t="n">
-        <v>1136.29</v>
+        <v>1136.26</v>
       </c>
       <c r="E157" t="n">
-        <v>1149.16</v>
+        <v>1149.13</v>
       </c>
       <c r="F157" t="n">
         <v>12296</v>
@@ -23751,13 +23831,13 @@
         </is>
       </c>
       <c r="C158" t="n">
-        <v>1141.16</v>
+        <v>1141.12</v>
       </c>
       <c r="D158" t="n">
-        <v>1134.43</v>
+        <v>1134.39</v>
       </c>
       <c r="E158" t="n">
-        <v>1147.89</v>
+        <v>1147.85</v>
       </c>
       <c r="F158" t="n">
         <v>19171</v>
@@ -23902,13 +23982,13 @@
         </is>
       </c>
       <c r="C159" t="n">
-        <v>1140.57</v>
+        <v>1140.52</v>
       </c>
       <c r="D159" t="n">
-        <v>1133.85</v>
+        <v>1133.8</v>
       </c>
       <c r="E159" t="n">
-        <v>1147.29</v>
+        <v>1147.23</v>
       </c>
       <c r="F159" t="n">
         <v>19366</v>
@@ -24053,13 +24133,13 @@
         </is>
       </c>
       <c r="C160" t="n">
-        <v>1138.23</v>
+        <v>1138.17</v>
       </c>
       <c r="D160" t="n">
-        <v>1127.25</v>
+        <v>1127.2</v>
       </c>
       <c r="E160" t="n">
-        <v>1149.2</v>
+        <v>1149.14</v>
       </c>
       <c r="F160" t="n">
         <v>4964</v>
@@ -24204,13 +24284,13 @@
         </is>
       </c>
       <c r="C161" t="n">
-        <v>1136.25</v>
+        <v>1136.21</v>
       </c>
       <c r="D161" t="n">
-        <v>1127.34</v>
+        <v>1127.3</v>
       </c>
       <c r="E161" t="n">
-        <v>1145.16</v>
+        <v>1145.12</v>
       </c>
       <c r="F161" t="n">
         <v>7363</v>
@@ -24355,13 +24435,13 @@
         </is>
       </c>
       <c r="C162" t="n">
-        <v>1135.77</v>
+        <v>1135.71</v>
       </c>
       <c r="D162" t="n">
-        <v>1126.26</v>
+        <v>1126.2</v>
       </c>
       <c r="E162" t="n">
-        <v>1145.28</v>
+        <v>1145.22</v>
       </c>
       <c r="F162" t="n">
         <v>8925</v>
@@ -24506,13 +24586,13 @@
         </is>
       </c>
       <c r="C163" t="n">
-        <v>1130.75</v>
+        <v>1130.72</v>
       </c>
       <c r="D163" t="n">
-        <v>1121.9</v>
+        <v>1121.87</v>
       </c>
       <c r="E163" t="n">
-        <v>1139.6</v>
+        <v>1139.57</v>
       </c>
       <c r="F163" t="n">
         <v>11116</v>
@@ -24657,13 +24737,13 @@
         </is>
       </c>
       <c r="C164" t="n">
-        <v>1128.87</v>
+        <v>1128.82</v>
       </c>
       <c r="D164" t="n">
-        <v>1121.44</v>
+        <v>1121.39</v>
       </c>
       <c r="E164" t="n">
-        <v>1136.29</v>
+        <v>1136.24</v>
       </c>
       <c r="F164" t="n">
         <v>20691</v>
@@ -24808,13 +24888,13 @@
         </is>
       </c>
       <c r="C165" t="n">
-        <v>1128.06</v>
+        <v>1128.03</v>
       </c>
       <c r="D165" t="n">
-        <v>1121.66</v>
+        <v>1121.63</v>
       </c>
       <c r="E165" t="n">
-        <v>1134.45</v>
+        <v>1134.42</v>
       </c>
       <c r="F165" t="n">
         <v>20115</v>
@@ -24959,13 +25039,13 @@
         </is>
       </c>
       <c r="C166" t="n">
-        <v>1126.98</v>
+        <v>1126.94</v>
       </c>
       <c r="D166" t="n">
-        <v>1114.81</v>
+        <v>1114.77</v>
       </c>
       <c r="E166" t="n">
-        <v>1139.15</v>
+        <v>1139.11</v>
       </c>
       <c r="F166" t="n">
         <v>2921</v>
@@ -25110,13 +25190,13 @@
         </is>
       </c>
       <c r="C167" t="n">
-        <v>1126.58</v>
+        <v>1126.54</v>
       </c>
       <c r="D167" t="n">
-        <v>1110.89</v>
+        <v>1110.85</v>
       </c>
       <c r="E167" t="n">
-        <v>1142.26</v>
+        <v>1142.22</v>
       </c>
       <c r="F167" t="n">
         <v>1785</v>
@@ -25261,13 +25341,13 @@
         </is>
       </c>
       <c r="C168" t="n">
-        <v>1120.61</v>
+        <v>1120.56</v>
       </c>
       <c r="D168" t="n">
-        <v>1109.61</v>
+        <v>1109.56</v>
       </c>
       <c r="E168" t="n">
-        <v>1131.62</v>
+        <v>1131.56</v>
       </c>
       <c r="F168" t="n">
         <v>5184</v>
@@ -25412,13 +25492,13 @@
         </is>
       </c>
       <c r="C169" t="n">
-        <v>1118.71</v>
+        <v>1118.67</v>
       </c>
       <c r="D169" t="n">
-        <v>1100.48</v>
+        <v>1100.44</v>
       </c>
       <c r="E169" t="n">
-        <v>1136.94</v>
+        <v>1136.9</v>
       </c>
       <c r="F169" t="n">
         <v>1143</v>
@@ -25563,13 +25643,13 @@
         </is>
       </c>
       <c r="C170" t="n">
-        <v>1114.28</v>
+        <v>1114.23</v>
       </c>
       <c r="D170" t="n">
-        <v>1105.09</v>
+        <v>1105.04</v>
       </c>
       <c r="E170" t="n">
-        <v>1123.47</v>
+        <v>1123.42</v>
       </c>
       <c r="F170" t="n">
         <v>6923</v>
@@ -25714,13 +25794,13 @@
         </is>
       </c>
       <c r="C171" t="n">
-        <v>1114</v>
+        <v>1113.95</v>
       </c>
       <c r="D171" t="n">
-        <v>1099.57</v>
+        <v>1099.53</v>
       </c>
       <c r="E171" t="n">
-        <v>1128.42</v>
+        <v>1128.38</v>
       </c>
       <c r="F171" t="n">
         <v>2201</v>
@@ -25865,13 +25945,13 @@
         </is>
       </c>
       <c r="C172" t="n">
-        <v>1113.92</v>
+        <v>1113.84</v>
       </c>
       <c r="D172" t="n">
-        <v>1106.18</v>
+        <v>1106.11</v>
       </c>
       <c r="E172" t="n">
-        <v>1121.66</v>
+        <v>1121.58</v>
       </c>
       <c r="F172" t="n">
         <v>10853</v>
@@ -26016,13 +26096,13 @@
         </is>
       </c>
       <c r="C173" t="n">
-        <v>1110.98</v>
+        <v>1110.95</v>
       </c>
       <c r="D173" t="n">
-        <v>1103.11</v>
+        <v>1103.08</v>
       </c>
       <c r="E173" t="n">
-        <v>1118.85</v>
+        <v>1118.83</v>
       </c>
       <c r="F173" t="n">
         <v>8045</v>
@@ -26167,13 +26247,13 @@
         </is>
       </c>
       <c r="C174" t="n">
-        <v>1109.29</v>
+        <v>1109.24</v>
       </c>
       <c r="D174" t="n">
-        <v>1099.99</v>
+        <v>1099.93</v>
       </c>
       <c r="E174" t="n">
-        <v>1118.59</v>
+        <v>1118.54</v>
       </c>
       <c r="F174" t="n">
         <v>8977</v>
@@ -26318,13 +26398,13 @@
         </is>
       </c>
       <c r="C175" t="n">
-        <v>1107.83</v>
+        <v>1107.79</v>
       </c>
       <c r="D175" t="n">
-        <v>1100.77</v>
+        <v>1100.73</v>
       </c>
       <c r="E175" t="n">
-        <v>1114.88</v>
+        <v>1114.85</v>
       </c>
       <c r="F175" t="n">
         <v>14148</v>
@@ -26469,13 +26549,13 @@
         </is>
       </c>
       <c r="C176" t="n">
-        <v>1091.38</v>
+        <v>1091.31</v>
       </c>
       <c r="D176" t="n">
-        <v>1079.86</v>
+        <v>1079.79</v>
       </c>
       <c r="E176" t="n">
-        <v>1102.9</v>
+        <v>1102.84</v>
       </c>
       <c r="F176" t="n">
         <v>4779</v>
@@ -26620,13 +26700,13 @@
         </is>
       </c>
       <c r="C177" t="n">
-        <v>1089.78</v>
+        <v>1089.72</v>
       </c>
       <c r="D177" t="n">
-        <v>1080.42</v>
+        <v>1080.36</v>
       </c>
       <c r="E177" t="n">
-        <v>1099.13</v>
+        <v>1099.07</v>
       </c>
       <c r="F177" t="n">
         <v>7598</v>
@@ -26771,13 +26851,13 @@
         </is>
       </c>
       <c r="C178" t="n">
-        <v>1074.28</v>
+        <v>1074.26</v>
       </c>
       <c r="D178" t="n">
-        <v>1063.08</v>
+        <v>1063.06</v>
       </c>
       <c r="E178" t="n">
-        <v>1085.47</v>
+        <v>1085.45</v>
       </c>
       <c r="F178" t="n">
         <v>6329</v>
@@ -26922,13 +27002,13 @@
         </is>
       </c>
       <c r="C179" t="n">
-        <v>1070.06</v>
+        <v>1070.01</v>
       </c>
       <c r="D179" t="n">
-        <v>1060.09</v>
+        <v>1060.05</v>
       </c>
       <c r="E179" t="n">
-        <v>1080.02</v>
+        <v>1079.97</v>
       </c>
       <c r="F179" t="n">
         <v>6964</v>
@@ -27073,13 +27153,13 @@
         </is>
       </c>
       <c r="C180" t="n">
-        <v>1067</v>
+        <v>1066.9</v>
       </c>
       <c r="D180" t="n">
-        <v>1055.46</v>
+        <v>1055.36</v>
       </c>
       <c r="E180" t="n">
-        <v>1078.54</v>
+        <v>1078.44</v>
       </c>
       <c r="F180" t="n">
         <v>5745</v>
@@ -27224,13 +27304,13 @@
         </is>
       </c>
       <c r="C181" t="n">
-        <v>1065.56</v>
+        <v>1065.49</v>
       </c>
       <c r="D181" t="n">
-        <v>1050.25</v>
+        <v>1050.18</v>
       </c>
       <c r="E181" t="n">
-        <v>1080.87</v>
+        <v>1080.79</v>
       </c>
       <c r="F181" t="n">
         <v>1743</v>
@@ -27375,13 +27455,13 @@
         </is>
       </c>
       <c r="C182" t="n">
-        <v>1061.44</v>
+        <v>1061.36</v>
       </c>
       <c r="D182" t="n">
-        <v>1049.39</v>
+        <v>1049.32</v>
       </c>
       <c r="E182" t="n">
-        <v>1073.48</v>
+        <v>1073.41</v>
       </c>
       <c r="F182" t="n">
         <v>3925</v>
@@ -27526,13 +27606,13 @@
         </is>
       </c>
       <c r="C183" t="n">
-        <v>1055.68</v>
+        <v>1055.63</v>
       </c>
       <c r="D183" t="n">
-        <v>1043.99</v>
+        <v>1043.94</v>
       </c>
       <c r="E183" t="n">
-        <v>1067.38</v>
+        <v>1067.33</v>
       </c>
       <c r="F183" t="n">
         <v>4658</v>
@@ -27677,13 +27757,13 @@
         </is>
       </c>
       <c r="C184" t="n">
-        <v>1040.91</v>
+        <v>1040.85</v>
       </c>
       <c r="D184" t="n">
-        <v>1029.44</v>
+        <v>1029.38</v>
       </c>
       <c r="E184" t="n">
-        <v>1052.38</v>
+        <v>1052.31</v>
       </c>
       <c r="F184" t="n">
         <v>4845</v>
@@ -27828,13 +27908,13 @@
         </is>
       </c>
       <c r="C185" t="n">
-        <v>1023.82</v>
+        <v>1023.77</v>
       </c>
       <c r="D185" t="n">
-        <v>1010.17</v>
+        <v>1010.12</v>
       </c>
       <c r="E185" t="n">
-        <v>1037.47</v>
+        <v>1037.41</v>
       </c>
       <c r="F185" t="n">
         <v>2657</v>
@@ -27979,13 +28059,13 @@
         </is>
       </c>
       <c r="C186" t="n">
-        <v>1021.71</v>
+        <v>1021.64</v>
       </c>
       <c r="D186" t="n">
-        <v>1010.77</v>
+        <v>1010.7</v>
       </c>
       <c r="E186" t="n">
-        <v>1032.65</v>
+        <v>1032.58</v>
       </c>
       <c r="F186" t="n">
         <v>6311</v>
@@ -28130,13 +28210,13 @@
         </is>
       </c>
       <c r="C187" t="n">
-        <v>995.199</v>
+        <v>995.155</v>
       </c>
       <c r="D187" t="n">
-        <v>982.557</v>
+        <v>982.515</v>
       </c>
       <c r="E187" t="n">
-        <v>1007.84</v>
+        <v>1007.8</v>
       </c>
       <c r="F187" t="n">
         <v>4914</v>
@@ -28281,13 +28361,13 @@
         </is>
       </c>
       <c r="C188" t="n">
-        <v>990.895</v>
+        <v>990.83</v>
       </c>
       <c r="D188" t="n">
-        <v>978.4400000000001</v>
+        <v>978.376</v>
       </c>
       <c r="E188" t="n">
-        <v>1003.35</v>
+        <v>1003.28</v>
       </c>
       <c r="F188" t="n">
         <v>4203</v>
@@ -28432,13 +28512,13 @@
         </is>
       </c>
       <c r="C189" t="n">
-        <v>979.655</v>
+        <v>979.566</v>
       </c>
       <c r="D189" t="n">
-        <v>966.018</v>
+        <v>965.932</v>
       </c>
       <c r="E189" t="n">
-        <v>993.292</v>
+        <v>993.201</v>
       </c>
       <c r="F189" t="n">
         <v>3412</v>
@@ -28583,13 +28663,13 @@
         </is>
       </c>
       <c r="C190" t="n">
-        <v>971.705</v>
+        <v>971.601</v>
       </c>
       <c r="D190" t="n">
-        <v>955.76</v>
+        <v>955.659</v>
       </c>
       <c r="E190" t="n">
-        <v>987.649</v>
+        <v>987.542</v>
       </c>
       <c r="F190" t="n">
         <v>2391</v>
@@ -28734,13 +28814,13 @@
         </is>
       </c>
       <c r="C191" t="n">
-        <v>952.21</v>
+        <v>952.16</v>
       </c>
       <c r="D191" t="n">
-        <v>939.369</v>
+        <v>939.321</v>
       </c>
       <c r="E191" t="n">
-        <v>965.052</v>
+        <v>964.999</v>
       </c>
       <c r="F191" t="n">
         <v>3287</v>
@@ -28959,7 +29039,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -28994,7 +29074,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -29029,7 +29109,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -29064,7 +29144,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -29099,7 +29179,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -29138,7 +29218,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -29173,7 +29253,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -29208,7 +29288,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -29243,7 +29323,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -29278,7 +29358,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -29313,7 +29393,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -29383,7 +29463,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -29418,7 +29498,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -29453,7 +29533,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -29550,14 +29630,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>kimi-k2.5-thinking</t>
+          <t>qwen3.5-397b-a17b</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1000</v>
+        <v>397</v>
       </c>
       <c r="C3" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -29566,21 +29646,21 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>artificial_analysis</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>qwen3.5-397b-a17b</t>
+          <t>kimi-k2.5-thinking</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>397</v>
+        <v>1000</v>
       </c>
       <c r="C4" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -29589,7 +29669,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>artificial_analysis</t>
+          <t>override</t>
         </is>
       </c>
     </row>
@@ -29780,14 +29860,14 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>qwen3.5-122b-a10b</t>
+          <t>deepseek-v3.2-thinking</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>125</v>
+        <v>685</v>
       </c>
       <c r="C13" t="n">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -29803,14 +29883,14 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>deepseek-v3.2-thinking</t>
+          <t>qwen3.5-122b-a10b</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>685</v>
+        <v>125</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -29872,14 +29952,14 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>kimi-k2-0905-preview</t>
+          <t>deepseek-v3.1-thinking</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1000</v>
+        <v>685</v>
       </c>
       <c r="C17" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -29888,21 +29968,21 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>artificial_analysis</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>deepseek-v3.1-thinking</t>
+          <t>kimi-k2-0905-preview</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>685</v>
+        <v>1000</v>
       </c>
       <c r="C18" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -29911,7 +29991,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>artificial_analysis</t>
+          <t>override</t>
         </is>
       </c>
     </row>
@@ -30033,18 +30113,18 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>qwen3.5-27b</t>
+          <t>glm-4.5</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>27.8</v>
+        <v>355</v>
       </c>
       <c r="C24" t="n">
-        <v>27.8</v>
+        <v>32</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>dense</t>
+          <t>moe</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -30056,18 +30136,18 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>glm-4.5</t>
+          <t>qwen3.5-27b</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>355</v>
+        <v>27.8</v>
       </c>
       <c r="C25" t="n">
-        <v>32</v>
+        <v>27.8</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>moe</t>
+          <t>dense</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -30240,14 +30320,14 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>deepseek-v3-0324</t>
+          <t>qwen3.5-35b-a3b</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>671</v>
+        <v>36</v>
       </c>
       <c r="C33" t="n">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -30263,14 +30343,14 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>qwen3.5-35b-a3b</t>
+          <t>deepseek-v3-0324</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>36</v>
+        <v>671</v>
       </c>
       <c r="C34" t="n">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -30312,12 +30392,20 @@
           <t>step-3.5-flash</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr"/>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
+      <c r="B36" t="n">
+        <v>196</v>
+      </c>
+      <c r="C36" t="n">
+        <v>11</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>artificial_analysis</t>
         </is>
       </c>
     </row>
@@ -30439,46 +30527,46 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>trinity-large</t>
+          <t>qwen3-235b-a22b</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>70</v>
+        <v>235</v>
       </c>
       <c r="C42" t="n">
-        <v>70</v>
+        <v>22</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>dense</t>
+          <t>moe</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>artificial_analysis</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>qwen3-235b-a22b</t>
+          <t>trinity-large</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>235</v>
+        <v>70</v>
       </c>
       <c r="C43" t="n">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>moe</t>
+          <t>dense</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>artificial_analysis</t>
+          <t>override</t>
         </is>
       </c>
     </row>
@@ -30738,18 +30826,18 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>llama-3.1-nemotron-ultra-253b-v1</t>
+          <t>ling-flash-2.0</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>253</v>
+        <v>103</v>
       </c>
       <c r="C55" t="n">
-        <v>253</v>
+        <v>6.1</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>dense</t>
+          <t>moe</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -30761,18 +30849,18 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ling-flash-2.0</t>
+          <t>llama-3.1-nemotron-ultra-253b-v1</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>103</v>
+        <v>253</v>
       </c>
       <c r="C56" t="n">
-        <v>6.1</v>
+        <v>253</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>moe</t>
+          <t>dense</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">

--- a/arena_enrichment/output/arena_leaderboard_enriched.xlsx
+++ b/arena_enrichment/output/arena_leaderboard_enriched.xlsx
@@ -675,16 +675,16 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>1452.62</v>
+        <v>1451.66</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1445.74</v>
+        <v>1444.84</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1459.51</v>
+        <v>1458.48</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>7875</v>
+        <v>8095</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
@@ -822,36 +822,36 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>qwen3.5-397b-a17b</t>
+          <t>kimi-k2.5-thinking</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>1451.39</v>
+        <v>1451.33</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1444.03</v>
+        <v>1445.51</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1458.76</v>
+        <v>1457.14</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>6576</v>
+        <v>12710</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Alibaba</t>
+          <t>Moonshot</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
+          <t>Modified MIT</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>397</v>
+        <v>1000</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
@@ -860,26 +860,26 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>artificial_analysis</t>
+          <t>override</t>
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>794</v>
+        <v>2000</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>992.5</v>
+        <v>2500</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>397</v>
+        <v>1000</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>496.2</v>
+        <v>1250</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>198.5</v>
+        <v>500</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>248.1</v>
+        <v>625</v>
       </c>
       <c r="S3" s="3" t="inlineStr">
         <is>
@@ -951,9 +951,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AG3" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AG3" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AH3" s="2" t="inlineStr">
@@ -973,36 +973,36 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>kimi-k2.5-thinking</t>
+          <t>qwen3.5-397b-a17b</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>1450.37</v>
+        <v>1450.5</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1444.49</v>
+        <v>1443.26</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1456.25</v>
+        <v>1457.74</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>12488</v>
+        <v>6836</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Moonshot</t>
+          <t>Alibaba</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Modified MIT</t>
+          <t>Apache 2.0</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>1000</v>
+        <v>397</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
@@ -1011,26 +1011,26 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>artificial_analysis</t>
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>2000</v>
+        <v>794</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>2500</v>
+        <v>992.5</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>1000</v>
+        <v>397</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>1250</v>
+        <v>496.2</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>500</v>
+        <v>198.5</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>625</v>
+        <v>248.1</v>
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
@@ -1102,9 +1102,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AG4" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AG4" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AH4" s="2" t="inlineStr">
@@ -1128,16 +1128,16 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>1440.88</v>
+        <v>1440.97</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1434.71</v>
+        <v>1434.8</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1447.06</v>
+        <v>1447.14</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>11933</v>
+        <v>11936</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
@@ -1279,16 +1279,16 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1434.6</v>
+        <v>1433.69</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1428.08</v>
+        <v>1427.25</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1441.12</v>
+        <v>1440.13</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>8596</v>
+        <v>8823</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
@@ -1430,16 +1430,16 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>1429.19</v>
+        <v>1429.22</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>1425.31</v>
+        <v>1425.36</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1433.07</v>
+        <v>1433.09</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>37587</v>
+        <v>37861</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
@@ -1581,16 +1581,16 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>1425.11</v>
+        <v>1425.1</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>1421.12</v>
+        <v>1421.11</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1429.09</v>
+        <v>1429.08</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>35097</v>
+        <v>35102</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
@@ -1732,16 +1732,16 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>1423.71</v>
+        <v>1423.79</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1417.22</v>
+        <v>1417.3</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1430.2</v>
+        <v>1430.28</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>11674</v>
+        <v>11672</v>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
@@ -1883,13 +1883,13 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>1423.33</v>
+        <v>1423.37</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>1416.75</v>
+        <v>1416.8</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1429.91</v>
+        <v>1429.95</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>8942</v>
@@ -2034,16 +2034,16 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>1422.29</v>
+        <v>1422.36</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>1419.29</v>
+        <v>1419.38</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1425.28</v>
+        <v>1425.35</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>73052</v>
+        <v>73293</v>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
@@ -2185,16 +2185,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1420.96</v>
+        <v>1420.9</v>
       </c>
       <c r="D12" t="n">
-        <v>1416.66</v>
+        <v>1416.62</v>
       </c>
       <c r="E12" t="n">
-        <v>1425.27</v>
+        <v>1425.19</v>
       </c>
       <c r="F12" t="n">
-        <v>32274</v>
+        <v>32541</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -2336,16 +2336,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1419.44</v>
+        <v>1419.98</v>
       </c>
       <c r="D13" t="n">
-        <v>1415.02</v>
+        <v>1415.59</v>
       </c>
       <c r="E13" t="n">
-        <v>1423.86</v>
+        <v>1424.38</v>
       </c>
       <c r="F13" t="n">
-        <v>27113</v>
+        <v>27370</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -2483,36 +2483,36 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>qwen3.5-122b-a10b</t>
+          <t>deepseek-r1-0528</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1419.32</v>
+        <v>1419.36</v>
       </c>
       <c r="D14" t="n">
-        <v>1408.76</v>
+        <v>1413.75</v>
       </c>
       <c r="E14" t="n">
-        <v>1429.87</v>
+        <v>1424.96</v>
       </c>
       <c r="F14" t="n">
-        <v>3003</v>
+        <v>19153</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alibaba</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>125</v>
+        <v>685</v>
       </c>
       <c r="J14" t="n">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -2525,22 +2525,22 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>250</v>
+        <v>1370</v>
       </c>
       <c r="N14" t="n">
-        <v>312.5</v>
+        <v>1712.5</v>
       </c>
       <c r="O14" t="n">
-        <v>125</v>
+        <v>685</v>
       </c>
       <c r="P14" t="n">
-        <v>156.2</v>
+        <v>856.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>62.5</v>
+        <v>342.5</v>
       </c>
       <c r="R14" t="n">
-        <v>78.09999999999999</v>
+        <v>428.1</v>
       </c>
       <c r="S14" s="5" t="inlineStr">
         <is>
@@ -2552,9 +2552,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="U14" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="U14" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="V14" s="5" t="inlineStr">
@@ -2567,9 +2567,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="X14" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="X14" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="Y14" s="5" t="inlineStr">
@@ -2582,9 +2582,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AA14" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AA14" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AB14" s="5" t="inlineStr">
@@ -2592,14 +2592,14 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AC14" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AD14" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AC14" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD14" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AE14" s="5" t="inlineStr">
@@ -2607,14 +2607,14 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AF14" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AG14" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AF14" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AG14" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
@@ -2624,7 +2624,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>B200 SXM</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
     </row>
@@ -2634,20 +2634,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>deepseek-r1-0528</t>
+          <t>deepseek-v3.1</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1419.3</v>
+        <v>1418.15</v>
       </c>
       <c r="D15" t="n">
-        <v>1413.7</v>
+        <v>1412.16</v>
       </c>
       <c r="E15" t="n">
-        <v>1424.91</v>
+        <v>1424.15</v>
       </c>
       <c r="F15" t="n">
-        <v>19155</v>
+        <v>15192</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -2785,36 +2785,36 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>deepseek-v3.1</t>
+          <t>qwen3.5-122b-a10b</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1418.13</v>
+        <v>1418.02</v>
       </c>
       <c r="D16" t="n">
-        <v>1412.14</v>
+        <v>1407.85</v>
       </c>
       <c r="E16" t="n">
-        <v>1424.13</v>
+        <v>1428.19</v>
       </c>
       <c r="F16" t="n">
-        <v>15193</v>
+        <v>3251</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>DeepSeek</t>
+          <t>Alibaba</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Apache 2.0</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>685</v>
+        <v>125</v>
       </c>
       <c r="J16" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -2827,22 +2827,22 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>1370</v>
+        <v>250</v>
       </c>
       <c r="N16" t="n">
-        <v>1712.5</v>
+        <v>312.5</v>
       </c>
       <c r="O16" t="n">
-        <v>685</v>
+        <v>125</v>
       </c>
       <c r="P16" t="n">
-        <v>856.2</v>
+        <v>156.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>342.5</v>
+        <v>62.5</v>
       </c>
       <c r="R16" t="n">
-        <v>428.1</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="S16" s="5" t="inlineStr">
         <is>
@@ -2854,9 +2854,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="U16" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="U16" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="V16" s="5" t="inlineStr">
@@ -2869,9 +2869,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="X16" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="X16" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Y16" s="5" t="inlineStr">
@@ -2884,9 +2884,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AA16" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AA16" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AB16" s="5" t="inlineStr">
@@ -2894,14 +2894,14 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AC16" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AD16" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AC16" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AD16" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AE16" s="5" t="inlineStr">
@@ -2909,14 +2909,14 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AF16" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AG16" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AF16" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AG16" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
@@ -2926,7 +2926,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>B200 SXM</t>
         </is>
       </c>
     </row>
@@ -2940,16 +2940,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1417.12</v>
+        <v>1417.13</v>
       </c>
       <c r="D17" t="n">
         <v>1410.54</v>
       </c>
       <c r="E17" t="n">
-        <v>1423.71</v>
+        <v>1423.72</v>
       </c>
       <c r="F17" t="n">
-        <v>11918</v>
+        <v>11916</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -3091,16 +3091,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1417.1</v>
+        <v>1417.08</v>
       </c>
       <c r="D18" t="n">
-        <v>1410.62</v>
+        <v>1410.6</v>
       </c>
       <c r="E18" t="n">
-        <v>1423.57</v>
+        <v>1423.55</v>
       </c>
       <c r="F18" t="n">
-        <v>11909</v>
+        <v>11907</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -3242,16 +3242,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1416.6</v>
+        <v>1416.59</v>
       </c>
       <c r="D19" t="n">
-        <v>1411.79</v>
+        <v>1411.78</v>
       </c>
       <c r="E19" t="n">
-        <v>1421.41</v>
+        <v>1421.4</v>
       </c>
       <c r="F19" t="n">
-        <v>28425</v>
+        <v>28423</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -3393,16 +3393,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1415.91</v>
+        <v>1415.86</v>
       </c>
       <c r="D20" t="n">
-        <v>1406.34</v>
+        <v>1406.29</v>
       </c>
       <c r="E20" t="n">
-        <v>1425.48</v>
+        <v>1425.43</v>
       </c>
       <c r="F20" t="n">
-        <v>3745</v>
+        <v>3744</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -3544,16 +3544,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1415.53</v>
+        <v>1415.64</v>
       </c>
       <c r="D21" t="n">
-        <v>1405.67</v>
+        <v>1405.78</v>
       </c>
       <c r="E21" t="n">
-        <v>1425.4</v>
+        <v>1425.5</v>
       </c>
       <c r="F21" t="n">
-        <v>3536</v>
+        <v>3535</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -3695,13 +3695,13 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1414.74</v>
+        <v>1414.78</v>
       </c>
       <c r="D22" t="n">
-        <v>1408.26</v>
+        <v>1408.3</v>
       </c>
       <c r="E22" t="n">
-        <v>1421.21</v>
+        <v>1421.25</v>
       </c>
       <c r="F22" t="n">
         <v>11596</v>
@@ -3846,16 +3846,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1414.68</v>
+        <v>1414.38</v>
       </c>
       <c r="D23" t="n">
-        <v>1410.37</v>
+        <v>1410.09</v>
       </c>
       <c r="E23" t="n">
-        <v>1419</v>
+        <v>1418.66</v>
       </c>
       <c r="F23" t="n">
-        <v>28787</v>
+        <v>29075</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -3993,40 +3993,40 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>glm-4.5</t>
+          <t>qwen3.5-27b</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1410.14</v>
+        <v>1410.57</v>
       </c>
       <c r="D24" t="n">
-        <v>1405.26</v>
+        <v>1400.65</v>
       </c>
       <c r="E24" t="n">
-        <v>1415.01</v>
+        <v>1420.49</v>
       </c>
       <c r="F24" t="n">
-        <v>24596</v>
+        <v>3368</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Z.ai</t>
+          <t>Alibaba</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Apache 2.0</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>355</v>
+        <v>27.8</v>
       </c>
       <c r="J24" t="n">
-        <v>32</v>
+        <v>27.8</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>moe</t>
+          <t>dense</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -4035,91 +4035,91 @@
         </is>
       </c>
       <c r="M24" t="n">
-        <v>710</v>
+        <v>55.6</v>
       </c>
       <c r="N24" t="n">
-        <v>887.5</v>
+        <v>69.5</v>
       </c>
       <c r="O24" t="n">
-        <v>355</v>
+        <v>27.8</v>
       </c>
       <c r="P24" t="n">
-        <v>443.8</v>
+        <v>34.8</v>
       </c>
       <c r="Q24" t="n">
-        <v>177.5</v>
+        <v>13.9</v>
       </c>
       <c r="R24" t="n">
-        <v>221.9</v>
-      </c>
-      <c r="S24" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T24" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U24" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="V24" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W24" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X24" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Y24" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z24" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AA24" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AB24" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AC24" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AD24" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AE24" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AF24" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+        <v>17.4</v>
+      </c>
+      <c r="S24" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T24" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U24" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V24" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W24" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X24" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y24" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z24" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AA24" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB24" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AC24" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AD24" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE24" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AF24" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AG24" s="6" t="inlineStr">
@@ -4129,12 +4129,12 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>H100 SXM</t>
         </is>
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>H100 SXM</t>
         </is>
       </c>
     </row>
@@ -4144,40 +4144,40 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>qwen3.5-27b</t>
+          <t>glm-4.5</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1409.63</v>
+        <v>1410.2</v>
       </c>
       <c r="D25" t="n">
-        <v>1399.32</v>
+        <v>1405.33</v>
       </c>
       <c r="E25" t="n">
-        <v>1419.94</v>
+        <v>1415.07</v>
       </c>
       <c r="F25" t="n">
-        <v>3104</v>
+        <v>24595</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alibaba</t>
+          <t>Z.ai</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>27.8</v>
+        <v>355</v>
       </c>
       <c r="J25" t="n">
-        <v>27.8</v>
+        <v>32</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>dense</t>
+          <t>moe</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -4186,91 +4186,91 @@
         </is>
       </c>
       <c r="M25" t="n">
-        <v>55.6</v>
+        <v>710</v>
       </c>
       <c r="N25" t="n">
-        <v>69.5</v>
+        <v>887.5</v>
       </c>
       <c r="O25" t="n">
-        <v>27.8</v>
+        <v>355</v>
       </c>
       <c r="P25" t="n">
-        <v>34.8</v>
+        <v>443.8</v>
       </c>
       <c r="Q25" t="n">
-        <v>13.9</v>
+        <v>177.5</v>
       </c>
       <c r="R25" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="S25" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="T25" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="U25" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="V25" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W25" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X25" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Y25" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z25" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AA25" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB25" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AC25" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AD25" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AE25" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AF25" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+        <v>221.9</v>
+      </c>
+      <c r="S25" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T25" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U25" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V25" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W25" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X25" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y25" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z25" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA25" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AB25" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AC25" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD25" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE25" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF25" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AG25" s="6" t="inlineStr">
@@ -4280,12 +4280,12 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
     </row>
@@ -4295,36 +4295,36 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>qwen3-235b-a22b-no-thinking</t>
+          <t>minimax-m2.5</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1401.93</v>
+        <v>1401.94</v>
       </c>
       <c r="D26" t="n">
-        <v>1397.46</v>
+        <v>1395.03</v>
       </c>
       <c r="E26" t="n">
-        <v>1406.39</v>
+        <v>1408.85</v>
       </c>
       <c r="F26" t="n">
-        <v>39270</v>
+        <v>8017</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alibaba</t>
+          <t>MiniMax</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
+          <t>Modified MIT</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="J26" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -4333,26 +4333,26 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>artificial_analysis</t>
         </is>
       </c>
       <c r="M26" t="n">
-        <v>470</v>
+        <v>460</v>
       </c>
       <c r="N26" t="n">
-        <v>587.5</v>
+        <v>575</v>
       </c>
       <c r="O26" t="n">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="P26" t="n">
-        <v>293.8</v>
+        <v>287.5</v>
       </c>
       <c r="Q26" t="n">
-        <v>117.5</v>
+        <v>115</v>
       </c>
       <c r="R26" t="n">
-        <v>146.9</v>
+        <v>143.8</v>
       </c>
       <c r="S26" s="5" t="inlineStr">
         <is>
@@ -4419,9 +4419,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AF26" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AF26" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AG26" s="6" t="inlineStr">
@@ -4436,7 +4436,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>B300 SXM</t>
         </is>
       </c>
     </row>
@@ -4446,20 +4446,20 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>qwen3-next-80b-a3b-instruct</t>
+          <t>qwen3-235b-a22b-no-thinking</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1401.79</v>
+        <v>1401.92</v>
       </c>
       <c r="D27" t="n">
-        <v>1396.98</v>
+        <v>1397.46</v>
       </c>
       <c r="E27" t="n">
-        <v>1406.6</v>
+        <v>1406.39</v>
       </c>
       <c r="F27" t="n">
-        <v>22667</v>
+        <v>39264</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -4472,10 +4472,10 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>80</v>
+        <v>235</v>
       </c>
       <c r="J27" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -4484,26 +4484,26 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>artificial_analysis</t>
+          <t>name_parsing</t>
         </is>
       </c>
       <c r="M27" t="n">
-        <v>160</v>
+        <v>470</v>
       </c>
       <c r="N27" t="n">
-        <v>200</v>
+        <v>587.5</v>
       </c>
       <c r="O27" t="n">
-        <v>80</v>
+        <v>235</v>
       </c>
       <c r="P27" t="n">
-        <v>100</v>
+        <v>293.8</v>
       </c>
       <c r="Q27" t="n">
-        <v>40</v>
+        <v>117.5</v>
       </c>
       <c r="R27" t="n">
-        <v>50</v>
+        <v>146.9</v>
       </c>
       <c r="S27" s="5" t="inlineStr">
         <is>
@@ -4515,9 +4515,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="U27" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="U27" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="V27" s="5" t="inlineStr">
@@ -4530,9 +4530,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="X27" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="X27" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="Y27" s="5" t="inlineStr">
@@ -4540,14 +4540,14 @@
           <t>No</t>
         </is>
       </c>
-      <c r="Z27" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AA27" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="Z27" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA27" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AB27" s="5" t="inlineStr">
@@ -4555,9 +4555,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AC27" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AC27" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AD27" s="6" t="inlineStr">
@@ -4565,14 +4565,14 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="AE27" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AF27" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AE27" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF27" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AG27" s="6" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>B300 SXM</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>H200 SXM</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
     </row>
@@ -4597,36 +4597,36 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>minimax-m2.5</t>
+          <t>qwen3-next-80b-a3b-instruct</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1401.13</v>
+        <v>1401.82</v>
       </c>
       <c r="D28" t="n">
-        <v>1394.12</v>
+        <v>1397.01</v>
       </c>
       <c r="E28" t="n">
-        <v>1408.15</v>
+        <v>1406.63</v>
       </c>
       <c r="F28" t="n">
-        <v>7745</v>
+        <v>22670</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>MiniMax</t>
+          <t>Alibaba</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Modified MIT</t>
+          <t>Apache 2.0</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>230</v>
+        <v>80</v>
       </c>
       <c r="J28" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -4639,22 +4639,22 @@
         </is>
       </c>
       <c r="M28" t="n">
-        <v>460</v>
+        <v>160</v>
       </c>
       <c r="N28" t="n">
-        <v>575</v>
+        <v>200</v>
       </c>
       <c r="O28" t="n">
-        <v>230</v>
+        <v>80</v>
       </c>
       <c r="P28" t="n">
-        <v>287.5</v>
+        <v>100</v>
       </c>
       <c r="Q28" t="n">
-        <v>115</v>
+        <v>40</v>
       </c>
       <c r="R28" t="n">
-        <v>143.8</v>
+        <v>50</v>
       </c>
       <c r="S28" s="5" t="inlineStr">
         <is>
@@ -4666,9 +4666,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="U28" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="U28" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="V28" s="5" t="inlineStr">
@@ -4681,9 +4681,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="X28" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="X28" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Y28" s="5" t="inlineStr">
@@ -4691,14 +4691,14 @@
           <t>No</t>
         </is>
       </c>
-      <c r="Z28" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AA28" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="Z28" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AA28" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AB28" s="5" t="inlineStr">
@@ -4706,9 +4706,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AC28" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AC28" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AD28" s="6" t="inlineStr">
@@ -4716,9 +4716,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="AE28" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AE28" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AF28" s="6" t="inlineStr">
@@ -4733,12 +4733,12 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>B300 SXM</t>
         </is>
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>B300 SXM</t>
+          <t>H200 SXM</t>
         </is>
       </c>
     </row>
@@ -4752,16 +4752,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1400.11</v>
+        <v>1400.09</v>
       </c>
       <c r="D29" t="n">
-        <v>1393.76</v>
+        <v>1393.74</v>
       </c>
       <c r="E29" t="n">
-        <v>1406.46</v>
+        <v>1406.45</v>
       </c>
       <c r="F29" t="n">
-        <v>11487</v>
+        <v>11486</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -4903,16 +4903,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1398.63</v>
+        <v>1398.69</v>
       </c>
       <c r="D30" t="n">
-        <v>1392.15</v>
+        <v>1392.21</v>
       </c>
       <c r="E30" t="n">
-        <v>1405.1</v>
+        <v>1405.16</v>
       </c>
       <c r="F30" t="n">
-        <v>9179</v>
+        <v>9177</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -5054,13 +5054,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1397.57</v>
+        <v>1397.59</v>
       </c>
       <c r="D31" t="n">
-        <v>1392.73</v>
+        <v>1392.75</v>
       </c>
       <c r="E31" t="n">
-        <v>1402.41</v>
+        <v>1402.44</v>
       </c>
       <c r="F31" t="n">
         <v>18537</v>
@@ -5201,20 +5201,20 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>qwen3-vl-235b-a22b-thinking</t>
+          <t>qwen3.5-35b-a3b</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1395.05</v>
+        <v>1395.41</v>
       </c>
       <c r="D32" t="n">
-        <v>1388.24</v>
+        <v>1385.4</v>
       </c>
       <c r="E32" t="n">
-        <v>1401.85</v>
+        <v>1405.42</v>
       </c>
       <c r="F32" t="n">
-        <v>7918</v>
+        <v>3427</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -5227,10 +5227,10 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>235</v>
+        <v>36</v>
       </c>
       <c r="J32" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -5239,40 +5239,40 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>artificial_analysis</t>
         </is>
       </c>
       <c r="M32" t="n">
-        <v>470</v>
+        <v>72</v>
       </c>
       <c r="N32" t="n">
-        <v>587.5</v>
+        <v>90</v>
       </c>
       <c r="O32" t="n">
-        <v>235</v>
+        <v>36</v>
       </c>
       <c r="P32" t="n">
-        <v>293.8</v>
+        <v>45</v>
       </c>
       <c r="Q32" t="n">
-        <v>117.5</v>
+        <v>18</v>
       </c>
       <c r="R32" t="n">
-        <v>146.9</v>
-      </c>
-      <c r="S32" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T32" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U32" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+        <v>22.5</v>
+      </c>
+      <c r="S32" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T32" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U32" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="V32" s="5" t="inlineStr">
@@ -5280,39 +5280,39 @@
           <t>No</t>
         </is>
       </c>
-      <c r="W32" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X32" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Y32" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z32" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AA32" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AB32" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AC32" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="W32" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X32" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y32" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z32" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AA32" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB32" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AC32" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AD32" s="6" t="inlineStr">
@@ -5320,14 +5320,14 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="AE32" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AF32" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AE32" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AF32" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AG32" s="6" t="inlineStr">
@@ -5337,12 +5337,12 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>RTX PRO 6000</t>
         </is>
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>H100 SXM</t>
         </is>
       </c>
     </row>
@@ -5352,20 +5352,20 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>qwen3.5-35b-a3b</t>
+          <t>qwen3-vl-235b-a22b-thinking</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1395.04</v>
+        <v>1395.13</v>
       </c>
       <c r="D33" t="n">
-        <v>1384.62</v>
+        <v>1388.32</v>
       </c>
       <c r="E33" t="n">
-        <v>1405.46</v>
+        <v>1401.93</v>
       </c>
       <c r="F33" t="n">
-        <v>3145</v>
+        <v>7919</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -5378,10 +5378,10 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>36</v>
+        <v>235</v>
       </c>
       <c r="J33" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -5390,40 +5390,40 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>artificial_analysis</t>
+          <t>name_parsing</t>
         </is>
       </c>
       <c r="M33" t="n">
-        <v>72</v>
+        <v>470</v>
       </c>
       <c r="N33" t="n">
-        <v>90</v>
+        <v>587.5</v>
       </c>
       <c r="O33" t="n">
-        <v>36</v>
+        <v>235</v>
       </c>
       <c r="P33" t="n">
-        <v>45</v>
+        <v>293.8</v>
       </c>
       <c r="Q33" t="n">
-        <v>18</v>
+        <v>117.5</v>
       </c>
       <c r="R33" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="S33" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="T33" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="U33" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+        <v>146.9</v>
+      </c>
+      <c r="S33" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T33" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U33" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="V33" s="5" t="inlineStr">
@@ -5431,39 +5431,39 @@
           <t>No</t>
         </is>
       </c>
-      <c r="W33" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X33" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Y33" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z33" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AA33" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB33" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AC33" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="W33" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X33" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y33" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z33" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA33" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AB33" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AC33" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AD33" s="6" t="inlineStr">
@@ -5471,14 +5471,14 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="AE33" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AF33" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AE33" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF33" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AG33" s="6" t="inlineStr">
@@ -5488,12 +5488,12 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>RTX PRO 6000</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
     </row>
@@ -5507,16 +5507,16 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1394.07</v>
+        <v>1394.11</v>
       </c>
       <c r="D34" t="n">
-        <v>1390.22</v>
+        <v>1390.26</v>
       </c>
       <c r="E34" t="n">
-        <v>1397.92</v>
+        <v>1397.96</v>
       </c>
       <c r="F34" t="n">
-        <v>46411</v>
+        <v>46409</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -5658,16 +5658,16 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1390.93</v>
+        <v>1391.72</v>
       </c>
       <c r="D35" t="n">
-        <v>1386.18</v>
+        <v>1387.01</v>
       </c>
       <c r="E35" t="n">
-        <v>1395.68</v>
+        <v>1396.44</v>
       </c>
       <c r="F35" t="n">
-        <v>21281</v>
+        <v>21546</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -5809,16 +5809,16 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1386.92</v>
+        <v>1388.91</v>
       </c>
       <c r="D36" t="n">
-        <v>1380.67</v>
+        <v>1382.73</v>
       </c>
       <c r="E36" t="n">
-        <v>1393.18</v>
+        <v>1395.1</v>
       </c>
       <c r="F36" t="n">
-        <v>10176</v>
+        <v>10401</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -5960,16 +5960,16 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1386.69</v>
+        <v>1386.76</v>
       </c>
       <c r="D37" t="n">
-        <v>1380.35</v>
+        <v>1380.42</v>
       </c>
       <c r="E37" t="n">
-        <v>1393.02</v>
+        <v>1393.09</v>
       </c>
       <c r="F37" t="n">
-        <v>10864</v>
+        <v>10861</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -6111,16 +6111,16 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1386.47</v>
+        <v>1386.43</v>
       </c>
       <c r="D38" t="n">
-        <v>1381.58</v>
+        <v>1381.53</v>
       </c>
       <c r="E38" t="n">
-        <v>1391.36</v>
+        <v>1391.32</v>
       </c>
       <c r="F38" t="n">
-        <v>26400</v>
+        <v>26393</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -6262,16 +6262,16 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1385.3</v>
+        <v>1385.35</v>
       </c>
       <c r="D39" t="n">
-        <v>1379.99</v>
+        <v>1380.04</v>
       </c>
       <c r="E39" t="n">
-        <v>1390.62</v>
+        <v>1390.66</v>
       </c>
       <c r="F39" t="n">
-        <v>17070</v>
+        <v>17078</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -6413,16 +6413,16 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1383.65</v>
+        <v>1383.69</v>
       </c>
       <c r="D40" t="n">
-        <v>1378.78</v>
+        <v>1378.82</v>
       </c>
       <c r="E40" t="n">
-        <v>1388.52</v>
+        <v>1388.56</v>
       </c>
       <c r="F40" t="n">
-        <v>23936</v>
+        <v>23933</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -6567,13 +6567,13 @@
         <v>1377.87</v>
       </c>
       <c r="D41" t="n">
-        <v>1366.6</v>
+        <v>1366.59</v>
       </c>
       <c r="E41" t="n">
-        <v>1389.15</v>
+        <v>1389.16</v>
       </c>
       <c r="F41" t="n">
-        <v>2785</v>
+        <v>2784</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -6715,16 +6715,16 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1374.64</v>
+        <v>1374.68</v>
       </c>
       <c r="D42" t="n">
-        <v>1369.98</v>
+        <v>1370.01</v>
       </c>
       <c r="E42" t="n">
-        <v>1379.31</v>
+        <v>1379.35</v>
       </c>
       <c r="F42" t="n">
-        <v>27001</v>
+        <v>27000</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -6866,16 +6866,16 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1374.03</v>
+        <v>1374.19</v>
       </c>
       <c r="D43" t="n">
-        <v>1364.31</v>
+        <v>1364.82</v>
       </c>
       <c r="E43" t="n">
-        <v>1383.74</v>
+        <v>1383.56</v>
       </c>
       <c r="F43" t="n">
-        <v>3917</v>
+        <v>4191</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -7017,16 +7017,16 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1371.73</v>
+        <v>1371.84</v>
       </c>
       <c r="D44" t="n">
-        <v>1367.47</v>
+        <v>1367.58</v>
       </c>
       <c r="E44" t="n">
-        <v>1375.99</v>
+        <v>1376.1</v>
       </c>
       <c r="F44" t="n">
-        <v>31137</v>
+        <v>31132</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -7168,16 +7168,16 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1368.85</v>
+        <v>1368.83</v>
       </c>
       <c r="D45" t="n">
-        <v>1363.01</v>
+        <v>1362.99</v>
       </c>
       <c r="E45" t="n">
-        <v>1374.68</v>
+        <v>1374.66</v>
       </c>
       <c r="F45" t="n">
-        <v>13768</v>
+        <v>13767</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -7319,16 +7319,16 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1367.08</v>
+        <v>1366.99</v>
       </c>
       <c r="D46" t="n">
-        <v>1361.19</v>
+        <v>1361.1</v>
       </c>
       <c r="E46" t="n">
-        <v>1372.96</v>
+        <v>1372.87</v>
       </c>
       <c r="F46" t="n">
-        <v>11756</v>
+        <v>11734</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -7470,16 +7470,16 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1366.58</v>
+        <v>1366.61</v>
       </c>
       <c r="D47" t="n">
-        <v>1362.33</v>
+        <v>1362.36</v>
       </c>
       <c r="E47" t="n">
-        <v>1370.83</v>
+        <v>1370.86</v>
       </c>
       <c r="F47" t="n">
-        <v>36431</v>
+        <v>36424</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -7621,16 +7621,16 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1365.16</v>
+        <v>1365.15</v>
       </c>
       <c r="D48" t="n">
-        <v>1361.51</v>
+        <v>1361.5</v>
       </c>
       <c r="E48" t="n">
-        <v>1368.81</v>
+        <v>1368.8</v>
       </c>
       <c r="F48" t="n">
-        <v>48423</v>
+        <v>48420</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -7772,13 +7772,13 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1358.37</v>
+        <v>1358.39</v>
       </c>
       <c r="D49" t="n">
-        <v>1353.67</v>
+        <v>1353.69</v>
       </c>
       <c r="E49" t="n">
-        <v>1363.08</v>
+        <v>1363.09</v>
       </c>
       <c r="F49" t="n">
         <v>21788</v>
@@ -7923,13 +7923,13 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1356.21</v>
+        <v>1356.23</v>
       </c>
       <c r="D50" t="n">
-        <v>1347.8</v>
+        <v>1347.83</v>
       </c>
       <c r="E50" t="n">
-        <v>1364.61</v>
+        <v>1364.64</v>
       </c>
       <c r="F50" t="n">
         <v>5285</v>
@@ -8074,16 +8074,16 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1356.07</v>
+        <v>1356.11</v>
       </c>
       <c r="D51" t="n">
-        <v>1350.91</v>
+        <v>1350.95</v>
       </c>
       <c r="E51" t="n">
-        <v>1361.23</v>
+        <v>1361.27</v>
       </c>
       <c r="F51" t="n">
-        <v>18223</v>
+        <v>18219</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -8228,10 +8228,10 @@
         <v>1354.07</v>
       </c>
       <c r="D52" t="n">
-        <v>1349.7</v>
+        <v>1349.71</v>
       </c>
       <c r="E52" t="n">
-        <v>1358.43</v>
+        <v>1358.44</v>
       </c>
       <c r="F52" t="n">
         <v>30747</v>
@@ -8376,16 +8376,16 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1352.98</v>
+        <v>1353.03</v>
       </c>
       <c r="D53" t="n">
-        <v>1349.54</v>
+        <v>1349.59</v>
       </c>
       <c r="E53" t="n">
-        <v>1356.41</v>
+        <v>1356.46</v>
       </c>
       <c r="F53" t="n">
-        <v>57067</v>
+        <v>57059</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -8530,13 +8530,13 @@
         <v>1352.95</v>
       </c>
       <c r="D54" t="n">
-        <v>1344.59</v>
+        <v>1344.58</v>
       </c>
       <c r="E54" t="n">
-        <v>1361.32</v>
+        <v>1361.31</v>
       </c>
       <c r="F54" t="n">
-        <v>4948</v>
+        <v>4947</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -8678,13 +8678,13 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1347.2</v>
+        <v>1347.26</v>
       </c>
       <c r="D55" t="n">
-        <v>1339.94</v>
+        <v>1339.99</v>
       </c>
       <c r="E55" t="n">
-        <v>1354.47</v>
+        <v>1354.52</v>
       </c>
       <c r="F55" t="n">
         <v>6988</v>
@@ -8829,13 +8829,13 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1347.16</v>
+        <v>1347.18</v>
       </c>
       <c r="D56" t="n">
-        <v>1335.46</v>
+        <v>1335.47</v>
       </c>
       <c r="E56" t="n">
-        <v>1358.87</v>
+        <v>1358.89</v>
       </c>
       <c r="F56" t="n">
         <v>2546</v>
@@ -8980,13 +8980,13 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1346.99</v>
+        <v>1347.03</v>
       </c>
       <c r="D57" t="n">
-        <v>1337.55</v>
+        <v>1337.58</v>
       </c>
       <c r="E57" t="n">
-        <v>1356.43</v>
+        <v>1356.47</v>
       </c>
       <c r="F57" t="n">
         <v>3932</v>
@@ -9131,16 +9131,16 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1346.84</v>
+        <v>1346.88</v>
       </c>
       <c r="D58" t="n">
-        <v>1339.01</v>
+        <v>1339.05</v>
       </c>
       <c r="E58" t="n">
-        <v>1354.67</v>
+        <v>1354.71</v>
       </c>
       <c r="F58" t="n">
-        <v>6683</v>
+        <v>6684</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -9282,16 +9282,16 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1346.55</v>
+        <v>1346.66</v>
       </c>
       <c r="D59" t="n">
-        <v>1339.16</v>
+        <v>1339.26</v>
       </c>
       <c r="E59" t="n">
-        <v>1353.95</v>
+        <v>1354.05</v>
       </c>
       <c r="F59" t="n">
-        <v>6566</v>
+        <v>6565</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -9353,13 +9353,13 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1341.55</v>
+        <v>1341.56</v>
       </c>
       <c r="D60" t="n">
-        <v>1332.04</v>
+        <v>1332.05</v>
       </c>
       <c r="E60" t="n">
-        <v>1351.07</v>
+        <v>1351.08</v>
       </c>
       <c r="F60" t="n">
         <v>3829</v>
@@ -9504,13 +9504,13 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1341.04</v>
+        <v>1341.09</v>
       </c>
       <c r="D61" t="n">
-        <v>1331.13</v>
+        <v>1331.18</v>
       </c>
       <c r="E61" t="n">
-        <v>1350.95</v>
+        <v>1351</v>
       </c>
       <c r="F61" t="n">
         <v>3398</v>
@@ -9655,13 +9655,13 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1335.8</v>
+        <v>1335.83</v>
       </c>
       <c r="D62" t="n">
-        <v>1331.41</v>
+        <v>1331.44</v>
       </c>
       <c r="E62" t="n">
-        <v>1340.2</v>
+        <v>1340.22</v>
       </c>
       <c r="F62" t="n">
         <v>25985</v>
@@ -9806,13 +9806,13 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1334.95</v>
+        <v>1334.93</v>
       </c>
       <c r="D63" t="n">
-        <v>1331.28</v>
+        <v>1331.26</v>
       </c>
       <c r="E63" t="n">
-        <v>1338.61</v>
+        <v>1338.59</v>
       </c>
       <c r="F63" t="n">
         <v>41392</v>
@@ -9957,13 +9957,13 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1333.14</v>
+        <v>1333.11</v>
       </c>
       <c r="D64" t="n">
-        <v>1329.59</v>
+        <v>1329.56</v>
       </c>
       <c r="E64" t="n">
-        <v>1336.69</v>
+        <v>1336.67</v>
       </c>
       <c r="F64" t="n">
         <v>59655</v>
@@ -10108,16 +10108,16 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1330.56</v>
+        <v>1330.62</v>
       </c>
       <c r="D65" t="n">
-        <v>1324.41</v>
+        <v>1324.47</v>
       </c>
       <c r="E65" t="n">
-        <v>1336.72</v>
+        <v>1336.77</v>
       </c>
       <c r="F65" t="n">
-        <v>12237</v>
+        <v>12238</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -10259,13 +10259,13 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1328.55</v>
+        <v>1328.67</v>
       </c>
       <c r="D66" t="n">
-        <v>1307.16</v>
+        <v>1307.28</v>
       </c>
       <c r="E66" t="n">
-        <v>1349.95</v>
+        <v>1350.07</v>
       </c>
       <c r="F66" t="n">
         <v>812</v>
@@ -10410,16 +10410,16 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1328.08</v>
+        <v>1328.1</v>
       </c>
       <c r="D67" t="n">
-        <v>1323.39</v>
+        <v>1323.42</v>
       </c>
       <c r="E67" t="n">
-        <v>1332.77</v>
+        <v>1332.79</v>
       </c>
       <c r="F67" t="n">
-        <v>27264</v>
+        <v>27260</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -10561,16 +10561,16 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1327.42</v>
+        <v>1327.43</v>
       </c>
       <c r="D68" t="n">
-        <v>1323.21</v>
+        <v>1323.22</v>
       </c>
       <c r="E68" t="n">
-        <v>1331.63</v>
+        <v>1331.64</v>
       </c>
       <c r="F68" t="n">
-        <v>40914</v>
+        <v>40913</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -10712,13 +10712,13 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1327.04</v>
+        <v>1327.08</v>
       </c>
       <c r="D69" t="n">
-        <v>1314.92</v>
+        <v>1314.95</v>
       </c>
       <c r="E69" t="n">
-        <v>1339.17</v>
+        <v>1339.21</v>
       </c>
       <c r="F69" t="n">
         <v>2230</v>
@@ -10863,13 +10863,13 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1323.13</v>
+        <v>1323.15</v>
       </c>
       <c r="D70" t="n">
-        <v>1314.87</v>
+        <v>1314.88</v>
       </c>
       <c r="E70" t="n">
-        <v>1331.4</v>
+        <v>1331.42</v>
       </c>
       <c r="F70" t="n">
         <v>6793</v>
@@ -11014,16 +11014,16 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1322.19</v>
+        <v>1322.18</v>
       </c>
       <c r="D71" t="n">
-        <v>1317.52</v>
+        <v>1317.51</v>
       </c>
       <c r="E71" t="n">
-        <v>1326.86</v>
+        <v>1326.85</v>
       </c>
       <c r="F71" t="n">
-        <v>31026</v>
+        <v>31023</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -11165,13 +11165,13 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1320.36</v>
+        <v>1320.4</v>
       </c>
       <c r="D72" t="n">
-        <v>1313.14</v>
+        <v>1313.19</v>
       </c>
       <c r="E72" t="n">
-        <v>1327.57</v>
+        <v>1327.62</v>
       </c>
       <c r="F72" t="n">
         <v>7147</v>
@@ -11316,16 +11316,16 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1319.24</v>
+        <v>1319.28</v>
       </c>
       <c r="D73" t="n">
-        <v>1314.14</v>
+        <v>1314.18</v>
       </c>
       <c r="E73" t="n">
-        <v>1324.34</v>
+        <v>1324.37</v>
       </c>
       <c r="F73" t="n">
-        <v>23177</v>
+        <v>23170</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -11467,16 +11467,16 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1319.02</v>
+        <v>1318.98</v>
       </c>
       <c r="D74" t="n">
-        <v>1315.6</v>
+        <v>1315.57</v>
       </c>
       <c r="E74" t="n">
-        <v>1322.43</v>
+        <v>1322.39</v>
       </c>
       <c r="F74" t="n">
-        <v>55437</v>
+        <v>55436</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -11618,13 +11618,13 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>1317.89</v>
+        <v>1317.9</v>
       </c>
       <c r="D75" t="n">
-        <v>1312.21</v>
+        <v>1312.23</v>
       </c>
       <c r="E75" t="n">
-        <v>1323.57</v>
+        <v>1323.58</v>
       </c>
       <c r="F75" t="n">
         <v>16479</v>
@@ -11689,13 +11689,13 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>1317.35</v>
+        <v>1317.23</v>
       </c>
       <c r="D76" t="n">
-        <v>1311.72</v>
+        <v>1311.6</v>
       </c>
       <c r="E76" t="n">
-        <v>1322.98</v>
+        <v>1322.85</v>
       </c>
       <c r="F76" t="n">
         <v>15394</v>
@@ -11840,13 +11840,13 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1316.99</v>
+        <v>1317.07</v>
       </c>
       <c r="D77" t="n">
-        <v>1310.64</v>
+        <v>1310.72</v>
       </c>
       <c r="E77" t="n">
-        <v>1323.33</v>
+        <v>1323.41</v>
       </c>
       <c r="F77" t="n">
         <v>10751</v>
@@ -11991,13 +11991,13 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1314.34</v>
+        <v>1314.36</v>
       </c>
       <c r="D78" t="n">
-        <v>1309.83</v>
+        <v>1309.85</v>
       </c>
       <c r="E78" t="n">
-        <v>1318.86</v>
+        <v>1318.88</v>
       </c>
       <c r="F78" t="n">
         <v>24746</v>
@@ -12293,13 +12293,13 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1306.87</v>
+        <v>1306.88</v>
       </c>
       <c r="D80" t="n">
-        <v>1302.19</v>
+        <v>1302.21</v>
       </c>
       <c r="E80" t="n">
-        <v>1311.54</v>
+        <v>1311.55</v>
       </c>
       <c r="F80" t="n">
         <v>24574</v>
@@ -12440,36 +12440,36 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>athene-70b-0725</t>
+          <t>olmo-3-32b-think</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1305.86</v>
+        <v>1305.95</v>
       </c>
       <c r="D81" t="n">
-        <v>1300.21</v>
+        <v>1297.69</v>
       </c>
       <c r="E81" t="n">
-        <v>1311.52</v>
+        <v>1314.21</v>
       </c>
       <c r="F81" t="n">
-        <v>19622</v>
+        <v>5863</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>NexusFlow</t>
+          <t>Ai2</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>CC-BY-NC-4.0</t>
+          <t>Apache 2.0</t>
         </is>
       </c>
       <c r="I81" t="n">
-        <v>70</v>
+        <v>32.2</v>
       </c>
       <c r="J81" t="n">
-        <v>70</v>
+        <v>32.2</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
@@ -12478,30 +12478,30 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>artificial_analysis</t>
         </is>
       </c>
       <c r="M81" t="n">
-        <v>140</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="N81" t="n">
-        <v>175</v>
+        <v>80.5</v>
       </c>
       <c r="O81" t="n">
-        <v>70</v>
+        <v>32.2</v>
       </c>
       <c r="P81" t="n">
-        <v>87.5</v>
+        <v>40.2</v>
       </c>
       <c r="Q81" t="n">
-        <v>35</v>
+        <v>16.1</v>
       </c>
       <c r="R81" t="n">
-        <v>43.8</v>
-      </c>
-      <c r="S81" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+        <v>20.1</v>
+      </c>
+      <c r="S81" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="T81" s="6" t="inlineStr">
@@ -12519,9 +12519,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="W81" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="W81" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="X81" s="6" t="inlineStr">
@@ -12529,9 +12529,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="Y81" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="Y81" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Z81" s="6" t="inlineStr">
@@ -12576,12 +12576,12 @@
       </c>
       <c r="AH81" t="inlineStr">
         <is>
-          <t>B200 SXM</t>
+          <t>RTX PRO 6000</t>
         </is>
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>RTX PRO 6000</t>
+          <t>H100 SXM</t>
         </is>
       </c>
     </row>
@@ -12591,36 +12591,36 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>olmo-3-32b-think</t>
+          <t>athene-70b-0725</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>1305.83</v>
+        <v>1305.85</v>
       </c>
       <c r="D82" t="n">
-        <v>1297.57</v>
+        <v>1300.19</v>
       </c>
       <c r="E82" t="n">
-        <v>1314.1</v>
+        <v>1311.5</v>
       </c>
       <c r="F82" t="n">
-        <v>5863</v>
+        <v>19622</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Ai2</t>
+          <t>NexusFlow</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
+          <t>CC-BY-NC-4.0</t>
         </is>
       </c>
       <c r="I82" t="n">
-        <v>32.2</v>
+        <v>70</v>
       </c>
       <c r="J82" t="n">
-        <v>32.2</v>
+        <v>70</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
@@ -12629,30 +12629,30 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>artificial_analysis</t>
+          <t>name_parsing</t>
         </is>
       </c>
       <c r="M82" t="n">
-        <v>64.40000000000001</v>
+        <v>140</v>
       </c>
       <c r="N82" t="n">
-        <v>80.5</v>
+        <v>175</v>
       </c>
       <c r="O82" t="n">
-        <v>32.2</v>
+        <v>70</v>
       </c>
       <c r="P82" t="n">
-        <v>40.2</v>
+        <v>87.5</v>
       </c>
       <c r="Q82" t="n">
-        <v>16.1</v>
+        <v>35</v>
       </c>
       <c r="R82" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="S82" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+        <v>43.8</v>
+      </c>
+      <c r="S82" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="T82" s="6" t="inlineStr">
@@ -12670,9 +12670,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="W82" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="W82" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="X82" s="6" t="inlineStr">
@@ -12680,9 +12680,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="Y82" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="Y82" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="Z82" s="6" t="inlineStr">
@@ -12727,12 +12727,12 @@
       </c>
       <c r="AH82" t="inlineStr">
         <is>
+          <t>B200 SXM</t>
+        </is>
+      </c>
+      <c r="AI82" t="inlineStr">
+        <is>
           <t>RTX PRO 6000</t>
-        </is>
-      </c>
-      <c r="AI82" t="inlineStr">
-        <is>
-          <t>H100 SXM</t>
         </is>
       </c>
     </row>
@@ -12746,13 +12746,13 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>1304.9</v>
+        <v>1304.91</v>
       </c>
       <c r="D83" t="n">
-        <v>1300.51</v>
+        <v>1300.52</v>
       </c>
       <c r="E83" t="n">
-        <v>1309.29</v>
+        <v>1309.3</v>
       </c>
       <c r="F83" t="n">
         <v>28081</v>
@@ -12897,16 +12897,16 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>1304.23</v>
+        <v>1304.27</v>
       </c>
       <c r="D84" t="n">
-        <v>1299.75</v>
+        <v>1299.79</v>
       </c>
       <c r="E84" t="n">
-        <v>1308.7</v>
+        <v>1308.75</v>
       </c>
       <c r="F84" t="n">
-        <v>33878</v>
+        <v>33870</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -13048,13 +13048,13 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>1303.18</v>
+        <v>1303.19</v>
       </c>
       <c r="D85" t="n">
         <v>1293.87</v>
       </c>
       <c r="E85" t="n">
-        <v>1312.49</v>
+        <v>1312.5</v>
       </c>
       <c r="F85" t="n">
         <v>4177</v>
@@ -13199,13 +13199,13 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>1302.5</v>
+        <v>1302.52</v>
       </c>
       <c r="D86" t="n">
-        <v>1298.48</v>
+        <v>1298.49</v>
       </c>
       <c r="E86" t="n">
-        <v>1306.53</v>
+        <v>1306.55</v>
       </c>
       <c r="F86" t="n">
         <v>39409</v>
@@ -13350,13 +13350,13 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>1298.59</v>
+        <v>1298.6</v>
       </c>
       <c r="D87" t="n">
-        <v>1290.83</v>
+        <v>1290.85</v>
       </c>
       <c r="E87" t="n">
-        <v>1306.34</v>
+        <v>1306.35</v>
       </c>
       <c r="F87" t="n">
         <v>7136</v>
@@ -13501,13 +13501,13 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>1293.32</v>
+        <v>1293.3</v>
       </c>
       <c r="D88" t="n">
-        <v>1289.63</v>
+        <v>1289.61</v>
       </c>
       <c r="E88" t="n">
-        <v>1297.01</v>
+        <v>1296.99</v>
       </c>
       <c r="F88" t="n">
         <v>55234</v>
@@ -13655,10 +13655,10 @@
         <v>1288.48</v>
       </c>
       <c r="D89" t="n">
-        <v>1281.17</v>
+        <v>1281.18</v>
       </c>
       <c r="E89" t="n">
-        <v>1295.78</v>
+        <v>1295.79</v>
       </c>
       <c r="F89" t="n">
         <v>8659</v>
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>1287.9</v>
+        <v>1287.89</v>
       </c>
       <c r="D90" t="n">
         <v>1284.57</v>
       </c>
       <c r="E90" t="n">
-        <v>1291.23</v>
+        <v>1291.22</v>
       </c>
       <c r="F90" t="n">
         <v>75764</v>
@@ -13954,16 +13954,16 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>1286.58</v>
+        <v>1286.66</v>
       </c>
       <c r="D91" t="n">
-        <v>1278.16</v>
+        <v>1278.24</v>
       </c>
       <c r="E91" t="n">
-        <v>1295</v>
+        <v>1295.08</v>
       </c>
       <c r="F91" t="n">
-        <v>5618</v>
+        <v>5619</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -14105,13 +14105,13 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>1286.37</v>
+        <v>1286.35</v>
       </c>
       <c r="D92" t="n">
-        <v>1275.89</v>
+        <v>1275.88</v>
       </c>
       <c r="E92" t="n">
-        <v>1296.84</v>
+        <v>1296.83</v>
       </c>
       <c r="F92" t="n">
         <v>2846</v>
@@ -14256,13 +14256,13 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>1286</v>
+        <v>1285.97</v>
       </c>
       <c r="D93" t="n">
-        <v>1276.02</v>
+        <v>1276</v>
       </c>
       <c r="E93" t="n">
-        <v>1295.97</v>
+        <v>1295.94</v>
       </c>
       <c r="F93" t="n">
         <v>3749</v>
@@ -14407,13 +14407,13 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1285</v>
+        <v>1284.9</v>
       </c>
       <c r="D94" t="n">
-        <v>1277.74</v>
+        <v>1277.64</v>
       </c>
       <c r="E94" t="n">
-        <v>1292.26</v>
+        <v>1292.16</v>
       </c>
       <c r="F94" t="n">
         <v>8441</v>
@@ -14558,13 +14558,13 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1279.29</v>
+        <v>1279.28</v>
       </c>
       <c r="D95" t="n">
-        <v>1272.44</v>
+        <v>1272.42</v>
       </c>
       <c r="E95" t="n">
-        <v>1286.15</v>
+        <v>1286.13</v>
       </c>
       <c r="F95" t="n">
         <v>10069</v>
@@ -14709,13 +14709,13 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>1277.09</v>
+        <v>1277.06</v>
       </c>
       <c r="D96" t="n">
-        <v>1271.77</v>
+        <v>1271.74</v>
       </c>
       <c r="E96" t="n">
-        <v>1282.41</v>
+        <v>1282.38</v>
       </c>
       <c r="F96" t="n">
         <v>19661</v>
@@ -14860,13 +14860,13 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1276.15</v>
+        <v>1276.12</v>
       </c>
       <c r="D97" t="n">
-        <v>1269.58</v>
+        <v>1269.56</v>
       </c>
       <c r="E97" t="n">
-        <v>1282.71</v>
+        <v>1282.69</v>
       </c>
       <c r="F97" t="n">
         <v>9869</v>
@@ -15011,13 +15011,13 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>1275.72</v>
+        <v>1275.7</v>
       </c>
       <c r="D98" t="n">
-        <v>1272.16</v>
+        <v>1272.14</v>
       </c>
       <c r="E98" t="n">
-        <v>1279.28</v>
+        <v>1279.26</v>
       </c>
       <c r="F98" t="n">
         <v>156880</v>
@@ -15162,13 +15162,13 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>1273.68</v>
+        <v>1273.69</v>
       </c>
       <c r="D99" t="n">
-        <v>1267.8</v>
+        <v>1267.81</v>
       </c>
       <c r="E99" t="n">
-        <v>1279.56</v>
+        <v>1279.57</v>
       </c>
       <c r="F99" t="n">
         <v>14677</v>
@@ -15319,7 +15319,7 @@
         <v>1262.28</v>
       </c>
       <c r="E100" t="n">
-        <v>1278.5</v>
+        <v>1278.51</v>
       </c>
       <c r="F100" t="n">
         <v>5430</v>
@@ -15464,13 +15464,13 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1266.86</v>
+        <v>1266.85</v>
       </c>
       <c r="D101" t="n">
-        <v>1262.01</v>
+        <v>1262</v>
       </c>
       <c r="E101" t="n">
-        <v>1271.71</v>
+        <v>1271.7</v>
       </c>
       <c r="F101" t="n">
         <v>27123</v>
@@ -15618,7 +15618,7 @@
         <v>1265.32</v>
       </c>
       <c r="D102" t="n">
-        <v>1261.55</v>
+        <v>1261.54</v>
       </c>
       <c r="E102" t="n">
         <v>1269.09</v>
@@ -15766,13 +15766,13 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>1263.94</v>
+        <v>1263.93</v>
       </c>
       <c r="D103" t="n">
-        <v>1257.67</v>
+        <v>1257.65</v>
       </c>
       <c r="E103" t="n">
-        <v>1270.22</v>
+        <v>1270.21</v>
       </c>
       <c r="F103" t="n">
         <v>15147</v>
@@ -15917,13 +15917,13 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>1261.6</v>
+        <v>1261.56</v>
       </c>
       <c r="D104" t="n">
-        <v>1257.28</v>
+        <v>1257.25</v>
       </c>
       <c r="E104" t="n">
-        <v>1265.91</v>
+        <v>1265.87</v>
       </c>
       <c r="F104" t="n">
         <v>77556</v>
@@ -16068,13 +16068,13 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>1261.53</v>
+        <v>1261.49</v>
       </c>
       <c r="D105" t="n">
-        <v>1256.6</v>
+        <v>1256.56</v>
       </c>
       <c r="E105" t="n">
-        <v>1266.46</v>
+        <v>1266.42</v>
       </c>
       <c r="F105" t="n">
         <v>37325</v>
@@ -16370,13 +16370,13 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>1251.81</v>
+        <v>1251.78</v>
       </c>
       <c r="D107" t="n">
-        <v>1241.02</v>
+        <v>1241</v>
       </c>
       <c r="E107" t="n">
-        <v>1262.59</v>
+        <v>1262.57</v>
       </c>
       <c r="F107" t="n">
         <v>3335</v>
@@ -16521,13 +16521,13 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>1249.91</v>
+        <v>1249.89</v>
       </c>
       <c r="D108" t="n">
-        <v>1243.32</v>
+        <v>1243.3</v>
       </c>
       <c r="E108" t="n">
-        <v>1256.5</v>
+        <v>1256.47</v>
       </c>
       <c r="F108" t="n">
         <v>10141</v>
@@ -16823,13 +16823,13 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>1236.85</v>
+        <v>1236.86</v>
       </c>
       <c r="D110" t="n">
-        <v>1227.76</v>
+        <v>1227.77</v>
       </c>
       <c r="E110" t="n">
-        <v>1245.95</v>
+        <v>1245.96</v>
       </c>
       <c r="F110" t="n">
         <v>4780</v>
@@ -16974,13 +16974,13 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>1233.72</v>
+        <v>1233.68</v>
       </c>
       <c r="D111" t="n">
-        <v>1228.17</v>
+        <v>1228.13</v>
       </c>
       <c r="E111" t="n">
-        <v>1239.26</v>
+        <v>1239.23</v>
       </c>
       <c r="F111" t="n">
         <v>26191</v>
@@ -17125,13 +17125,13 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>1232.84</v>
+        <v>1232.81</v>
       </c>
       <c r="D112" t="n">
-        <v>1227.57</v>
+        <v>1227.54</v>
       </c>
       <c r="E112" t="n">
-        <v>1238.11</v>
+        <v>1238.08</v>
       </c>
       <c r="F112" t="n">
         <v>39296</v>
@@ -17276,13 +17276,13 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>1229.16</v>
+        <v>1229.12</v>
       </c>
       <c r="D113" t="n">
-        <v>1224.62</v>
+        <v>1224.58</v>
       </c>
       <c r="E113" t="n">
-        <v>1233.7</v>
+        <v>1233.67</v>
       </c>
       <c r="F113" t="n">
         <v>51417</v>
@@ -17427,13 +17427,13 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>1226.62</v>
+        <v>1226.58</v>
       </c>
       <c r="D114" t="n">
-        <v>1221.84</v>
+        <v>1221.8</v>
       </c>
       <c r="E114" t="n">
-        <v>1231.39</v>
+        <v>1231.35</v>
       </c>
       <c r="F114" t="n">
         <v>54038</v>
@@ -17578,13 +17578,13 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>1222.87</v>
+        <v>1222.85</v>
       </c>
       <c r="D115" t="n">
-        <v>1219.15</v>
+        <v>1219.13</v>
       </c>
       <c r="E115" t="n">
-        <v>1226.58</v>
+        <v>1226.56</v>
       </c>
       <c r="F115" t="n">
         <v>104636</v>
@@ -17729,13 +17729,13 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>1222.85</v>
+        <v>1222.84</v>
       </c>
       <c r="D116" t="n">
-        <v>1215.9</v>
+        <v>1215.89</v>
       </c>
       <c r="E116" t="n">
-        <v>1229.8</v>
+        <v>1229.79</v>
       </c>
       <c r="F116" t="n">
         <v>9827</v>
@@ -17880,13 +17880,13 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>1220.41</v>
+        <v>1220.4</v>
       </c>
       <c r="D117" t="n">
-        <v>1209.71</v>
+        <v>1209.69</v>
       </c>
       <c r="E117" t="n">
-        <v>1231.12</v>
+        <v>1231.1</v>
       </c>
       <c r="F117" t="n">
         <v>2895</v>
@@ -18031,13 +18031,13 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>1213.1</v>
+        <v>1213.08</v>
       </c>
       <c r="D118" t="n">
-        <v>1208.07</v>
+        <v>1208.05</v>
       </c>
       <c r="E118" t="n">
-        <v>1218.13</v>
+        <v>1218.11</v>
       </c>
       <c r="F118" t="n">
         <v>24142</v>
@@ -18182,13 +18182,13 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>1212.4</v>
+        <v>1212.38</v>
       </c>
       <c r="D119" t="n">
-        <v>1201.59</v>
+        <v>1201.56</v>
       </c>
       <c r="E119" t="n">
-        <v>1223.22</v>
+        <v>1223.19</v>
       </c>
       <c r="F119" t="n">
         <v>4653</v>
@@ -18333,7 +18333,7 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>1211.39</v>
+        <v>1211.38</v>
       </c>
       <c r="D120" t="n">
         <v>1207.28</v>
@@ -18484,13 +18484,13 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>1208.25</v>
+        <v>1208.23</v>
       </c>
       <c r="D121" t="n">
-        <v>1197.15</v>
+        <v>1197.12</v>
       </c>
       <c r="E121" t="n">
-        <v>1219.36</v>
+        <v>1219.33</v>
       </c>
       <c r="F121" t="n">
         <v>3092</v>
@@ -18635,13 +18635,13 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>1203.55</v>
+        <v>1203.52</v>
       </c>
       <c r="D122" t="n">
-        <v>1197.44</v>
+        <v>1197.4</v>
       </c>
       <c r="E122" t="n">
-        <v>1209.67</v>
+        <v>1209.64</v>
       </c>
       <c r="F122" t="n">
         <v>21744</v>
@@ -18786,13 +18786,13 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>1198.61</v>
+        <v>1198.62</v>
       </c>
       <c r="D123" t="n">
         <v>1194.56</v>
       </c>
       <c r="E123" t="n">
-        <v>1202.66</v>
+        <v>1202.67</v>
       </c>
       <c r="F123" t="n">
         <v>46618</v>
@@ -18937,13 +18937,13 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>1197.64</v>
+        <v>1197.61</v>
       </c>
       <c r="D124" t="n">
-        <v>1192.5</v>
+        <v>1192.47</v>
       </c>
       <c r="E124" t="n">
-        <v>1202.79</v>
+        <v>1202.76</v>
       </c>
       <c r="F124" t="n">
         <v>25055</v>
@@ -19088,13 +19088,13 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>1196.8</v>
+        <v>1196.76</v>
       </c>
       <c r="D125" t="n">
-        <v>1192.54</v>
+        <v>1192.5</v>
       </c>
       <c r="E125" t="n">
-        <v>1201.06</v>
+        <v>1201.03</v>
       </c>
       <c r="F125" t="n">
         <v>73505</v>
@@ -19239,13 +19239,13 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>1194.6</v>
+        <v>1194.56</v>
       </c>
       <c r="D126" t="n">
-        <v>1188.49</v>
+        <v>1188.45</v>
       </c>
       <c r="E126" t="n">
-        <v>1200.72</v>
+        <v>1200.68</v>
       </c>
       <c r="F126" t="n">
         <v>32196</v>
@@ -19390,13 +19390,13 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>1191.09</v>
+        <v>1191.07</v>
       </c>
       <c r="D127" t="n">
-        <v>1183.92</v>
+        <v>1183.89</v>
       </c>
       <c r="E127" t="n">
-        <v>1198.26</v>
+        <v>1198.24</v>
       </c>
       <c r="F127" t="n">
         <v>9902</v>
@@ -19541,13 +19541,13 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>1190.53</v>
+        <v>1190.49</v>
       </c>
       <c r="D128" t="n">
-        <v>1183.4</v>
+        <v>1183.37</v>
       </c>
       <c r="E128" t="n">
-        <v>1197.65</v>
+        <v>1197.62</v>
       </c>
       <c r="F128" t="n">
         <v>17841</v>
@@ -19692,13 +19692,13 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>1184.31</v>
+        <v>1184.28</v>
       </c>
       <c r="D129" t="n">
-        <v>1174.85</v>
+        <v>1174.82</v>
       </c>
       <c r="E129" t="n">
-        <v>1193.77</v>
+        <v>1193.74</v>
       </c>
       <c r="F129" t="n">
         <v>8214</v>
@@ -19843,13 +19843,13 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>1184.01</v>
+        <v>1183.98</v>
       </c>
       <c r="D130" t="n">
-        <v>1172.49</v>
+        <v>1172.46</v>
       </c>
       <c r="E130" t="n">
-        <v>1195.53</v>
+        <v>1195.5</v>
       </c>
       <c r="F130" t="n">
         <v>4933</v>
@@ -19994,13 +19994,13 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>1183.49</v>
+        <v>1183.46</v>
       </c>
       <c r="D131" t="n">
-        <v>1176.66</v>
+        <v>1176.63</v>
       </c>
       <c r="E131" t="n">
-        <v>1190.32</v>
+        <v>1190.29</v>
       </c>
       <c r="F131" t="n">
         <v>15483</v>
@@ -20145,13 +20145,13 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>1181.93</v>
+        <v>1181.9</v>
       </c>
       <c r="D132" t="n">
-        <v>1173.92</v>
+        <v>1173.89</v>
       </c>
       <c r="E132" t="n">
-        <v>1189.93</v>
+        <v>1189.9</v>
       </c>
       <c r="F132" t="n">
         <v>12636</v>
@@ -20216,13 +20216,13 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>1181.86</v>
+        <v>1181.82</v>
       </c>
       <c r="D133" t="n">
-        <v>1172.17</v>
+        <v>1172.14</v>
       </c>
       <c r="E133" t="n">
-        <v>1191.54</v>
+        <v>1191.51</v>
       </c>
       <c r="F133" t="n">
         <v>7967</v>
@@ -20287,13 +20287,13 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>1181.58</v>
+        <v>1181.56</v>
       </c>
       <c r="D134" t="n">
-        <v>1172.9</v>
+        <v>1172.87</v>
       </c>
       <c r="E134" t="n">
-        <v>1190.27</v>
+        <v>1190.24</v>
       </c>
       <c r="F134" t="n">
         <v>6643</v>
@@ -20438,13 +20438,13 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>1179.93</v>
+        <v>1179.92</v>
       </c>
       <c r="D135" t="n">
-        <v>1173.86</v>
+        <v>1173.85</v>
       </c>
       <c r="E135" t="n">
-        <v>1186</v>
+        <v>1185.99</v>
       </c>
       <c r="F135" t="n">
         <v>23893</v>
@@ -20589,13 +20589,13 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>1179.11</v>
+        <v>1179.08</v>
       </c>
       <c r="D136" t="n">
-        <v>1173.2</v>
+        <v>1173.17</v>
       </c>
       <c r="E136" t="n">
-        <v>1185.02</v>
+        <v>1184.99</v>
       </c>
       <c r="F136" t="n">
         <v>32836</v>
@@ -20660,13 +20660,13 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>1179.02</v>
+        <v>1178.99</v>
       </c>
       <c r="D137" t="n">
-        <v>1167.82</v>
+        <v>1167.8</v>
       </c>
       <c r="E137" t="n">
-        <v>1190.21</v>
+        <v>1190.19</v>
       </c>
       <c r="F137" t="n">
         <v>3191</v>
@@ -20811,13 +20811,13 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>1177.69</v>
+        <v>1177.66</v>
       </c>
       <c r="D138" t="n">
-        <v>1167.86</v>
+        <v>1167.83</v>
       </c>
       <c r="E138" t="n">
-        <v>1187.52</v>
+        <v>1187.48</v>
       </c>
       <c r="F138" t="n">
         <v>6534</v>
@@ -20962,13 +20962,13 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>1174.77</v>
+        <v>1174.74</v>
       </c>
       <c r="D139" t="n">
-        <v>1164.34</v>
+        <v>1164.31</v>
       </c>
       <c r="E139" t="n">
-        <v>1185.2</v>
+        <v>1185.17</v>
       </c>
       <c r="F139" t="n">
         <v>5006</v>
@@ -21113,13 +21113,13 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>1172.44</v>
+        <v>1172.41</v>
       </c>
       <c r="D140" t="n">
-        <v>1166.23</v>
+        <v>1166.2</v>
       </c>
       <c r="E140" t="n">
-        <v>1178.65</v>
+        <v>1178.62</v>
       </c>
       <c r="F140" t="n">
         <v>22479</v>
@@ -21264,13 +21264,13 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>1171.25</v>
+        <v>1171.24</v>
       </c>
       <c r="D141" t="n">
-        <v>1163.83</v>
+        <v>1163.82</v>
       </c>
       <c r="E141" t="n">
-        <v>1178.66</v>
+        <v>1178.65</v>
       </c>
       <c r="F141" t="n">
         <v>16057</v>
@@ -21415,13 +21415,13 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>1170.86</v>
+        <v>1170.83</v>
       </c>
       <c r="D142" t="n">
-        <v>1164.95</v>
+        <v>1164.91</v>
       </c>
       <c r="E142" t="n">
-        <v>1176.77</v>
+        <v>1176.74</v>
       </c>
       <c r="F142" t="n">
         <v>17763</v>
@@ -21566,13 +21566,13 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>1170.46</v>
+        <v>1170.44</v>
       </c>
       <c r="D143" t="n">
-        <v>1164.96</v>
+        <v>1164.94</v>
       </c>
       <c r="E143" t="n">
-        <v>1175.96</v>
+        <v>1175.94</v>
       </c>
       <c r="F143" t="n">
         <v>38491</v>
@@ -21717,13 +21717,13 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>1167.18</v>
+        <v>1167.16</v>
       </c>
       <c r="D144" t="n">
-        <v>1159.11</v>
+        <v>1159.08</v>
       </c>
       <c r="E144" t="n">
-        <v>1175.26</v>
+        <v>1175.23</v>
       </c>
       <c r="F144" t="n">
         <v>10224</v>
@@ -21868,13 +21868,13 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>1166.37</v>
+        <v>1166.35</v>
       </c>
       <c r="D145" t="n">
-        <v>1158.68</v>
+        <v>1158.65</v>
       </c>
       <c r="E145" t="n">
-        <v>1174.07</v>
+        <v>1174.04</v>
       </c>
       <c r="F145" t="n">
         <v>7936</v>
@@ -22019,13 +22019,13 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>1164.35</v>
+        <v>1164.33</v>
       </c>
       <c r="D146" t="n">
-        <v>1152.4</v>
+        <v>1152.38</v>
       </c>
       <c r="E146" t="n">
-        <v>1176.3</v>
+        <v>1176.28</v>
       </c>
       <c r="F146" t="n">
         <v>3776</v>
@@ -22170,13 +22170,13 @@
         </is>
       </c>
       <c r="C147" t="n">
-        <v>1156.85</v>
+        <v>1156.81</v>
       </c>
       <c r="D147" t="n">
-        <v>1145.34</v>
+        <v>1145.31</v>
       </c>
       <c r="E147" t="n">
-        <v>1168.36</v>
+        <v>1168.32</v>
       </c>
       <c r="F147" t="n">
         <v>3233</v>
@@ -22321,13 +22321,13 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>1155.6</v>
+        <v>1155.57</v>
       </c>
       <c r="D148" t="n">
-        <v>1147.21</v>
+        <v>1147.18</v>
       </c>
       <c r="E148" t="n">
-        <v>1163.99</v>
+        <v>1163.97</v>
       </c>
       <c r="F148" t="n">
         <v>6837</v>
@@ -22472,13 +22472,13 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>1155</v>
+        <v>1154.95</v>
       </c>
       <c r="D149" t="n">
-        <v>1142.37</v>
+        <v>1142.32</v>
       </c>
       <c r="E149" t="n">
-        <v>1167.63</v>
+        <v>1167.58</v>
       </c>
       <c r="F149" t="n">
         <v>3584</v>
@@ -22623,13 +22623,13 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>1152.01</v>
+        <v>1151.97</v>
       </c>
       <c r="D150" t="n">
-        <v>1138.79</v>
+        <v>1138.75</v>
       </c>
       <c r="E150" t="n">
-        <v>1165.23</v>
+        <v>1165.19</v>
       </c>
       <c r="F150" t="n">
         <v>4155</v>
@@ -22774,13 +22774,13 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>1151.62</v>
+        <v>1151.59</v>
       </c>
       <c r="D151" t="n">
-        <v>1136.21</v>
+        <v>1136.18</v>
       </c>
       <c r="E151" t="n">
-        <v>1167.03</v>
+        <v>1167</v>
       </c>
       <c r="F151" t="n">
         <v>1679</v>
@@ -22925,13 +22925,13 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>1149.75</v>
+        <v>1149.72</v>
       </c>
       <c r="D152" t="n">
-        <v>1137.44</v>
+        <v>1137.4</v>
       </c>
       <c r="E152" t="n">
-        <v>1162.06</v>
+        <v>1162.03</v>
       </c>
       <c r="F152" t="n">
         <v>2571</v>
@@ -23076,13 +23076,13 @@
         </is>
       </c>
       <c r="C153" t="n">
-        <v>1149.29</v>
+        <v>1149.25</v>
       </c>
       <c r="D153" t="n">
-        <v>1142.63</v>
+        <v>1142.6</v>
       </c>
       <c r="E153" t="n">
-        <v>1155.94</v>
+        <v>1155.91</v>
       </c>
       <c r="F153" t="n">
         <v>19402</v>
@@ -23227,13 +23227,13 @@
         </is>
       </c>
       <c r="C154" t="n">
-        <v>1148.78</v>
+        <v>1148.75</v>
       </c>
       <c r="D154" t="n">
-        <v>1139.51</v>
+        <v>1139.48</v>
       </c>
       <c r="E154" t="n">
-        <v>1158.05</v>
+        <v>1158.02</v>
       </c>
       <c r="F154" t="n">
         <v>7046</v>
@@ -23378,13 +23378,13 @@
         </is>
       </c>
       <c r="C155" t="n">
-        <v>1146.61</v>
+        <v>1146.58</v>
       </c>
       <c r="D155" t="n">
-        <v>1129.47</v>
+        <v>1129.43</v>
       </c>
       <c r="E155" t="n">
-        <v>1163.76</v>
+        <v>1163.72</v>
       </c>
       <c r="F155" t="n">
         <v>1295</v>
@@ -23529,13 +23529,13 @@
         </is>
       </c>
       <c r="C156" t="n">
-        <v>1143.55</v>
+        <v>1143.52</v>
       </c>
       <c r="D156" t="n">
-        <v>1133.65</v>
+        <v>1133.62</v>
       </c>
       <c r="E156" t="n">
-        <v>1153.45</v>
+        <v>1153.42</v>
       </c>
       <c r="F156" t="n">
         <v>4735</v>
@@ -23680,13 +23680,13 @@
         </is>
       </c>
       <c r="C157" t="n">
-        <v>1142.69</v>
+        <v>1142.66</v>
       </c>
       <c r="D157" t="n">
-        <v>1136.26</v>
+        <v>1136.23</v>
       </c>
       <c r="E157" t="n">
-        <v>1149.13</v>
+        <v>1149.09</v>
       </c>
       <c r="F157" t="n">
         <v>12296</v>
@@ -23831,13 +23831,13 @@
         </is>
       </c>
       <c r="C158" t="n">
-        <v>1141.12</v>
+        <v>1141.1</v>
       </c>
       <c r="D158" t="n">
-        <v>1134.39</v>
+        <v>1134.38</v>
       </c>
       <c r="E158" t="n">
-        <v>1147.85</v>
+        <v>1147.83</v>
       </c>
       <c r="F158" t="n">
         <v>19171</v>
@@ -23982,13 +23982,13 @@
         </is>
       </c>
       <c r="C159" t="n">
-        <v>1140.52</v>
+        <v>1140.48</v>
       </c>
       <c r="D159" t="n">
-        <v>1133.8</v>
+        <v>1133.76</v>
       </c>
       <c r="E159" t="n">
-        <v>1147.23</v>
+        <v>1147.2</v>
       </c>
       <c r="F159" t="n">
         <v>19366</v>
@@ -24133,13 +24133,13 @@
         </is>
       </c>
       <c r="C160" t="n">
-        <v>1138.17</v>
+        <v>1138.13</v>
       </c>
       <c r="D160" t="n">
-        <v>1127.2</v>
+        <v>1127.16</v>
       </c>
       <c r="E160" t="n">
-        <v>1149.14</v>
+        <v>1149.1</v>
       </c>
       <c r="F160" t="n">
         <v>4964</v>
@@ -24284,13 +24284,13 @@
         </is>
       </c>
       <c r="C161" t="n">
-        <v>1136.21</v>
+        <v>1136.18</v>
       </c>
       <c r="D161" t="n">
-        <v>1127.3</v>
+        <v>1127.27</v>
       </c>
       <c r="E161" t="n">
-        <v>1145.12</v>
+        <v>1145.09</v>
       </c>
       <c r="F161" t="n">
         <v>7363</v>
@@ -24435,13 +24435,13 @@
         </is>
       </c>
       <c r="C162" t="n">
-        <v>1135.71</v>
+        <v>1135.7</v>
       </c>
       <c r="D162" t="n">
-        <v>1126.2</v>
+        <v>1126.19</v>
       </c>
       <c r="E162" t="n">
-        <v>1145.22</v>
+        <v>1145.21</v>
       </c>
       <c r="F162" t="n">
         <v>8925</v>
@@ -24586,13 +24586,13 @@
         </is>
       </c>
       <c r="C163" t="n">
-        <v>1130.72</v>
+        <v>1130.68</v>
       </c>
       <c r="D163" t="n">
-        <v>1121.87</v>
+        <v>1121.83</v>
       </c>
       <c r="E163" t="n">
-        <v>1139.57</v>
+        <v>1139.53</v>
       </c>
       <c r="F163" t="n">
         <v>11116</v>
@@ -24737,13 +24737,13 @@
         </is>
       </c>
       <c r="C164" t="n">
-        <v>1128.82</v>
+        <v>1128.79</v>
       </c>
       <c r="D164" t="n">
-        <v>1121.39</v>
+        <v>1121.36</v>
       </c>
       <c r="E164" t="n">
-        <v>1136.24</v>
+        <v>1136.21</v>
       </c>
       <c r="F164" t="n">
         <v>20691</v>
@@ -24888,13 +24888,13 @@
         </is>
       </c>
       <c r="C165" t="n">
-        <v>1128.03</v>
+        <v>1128</v>
       </c>
       <c r="D165" t="n">
-        <v>1121.63</v>
+        <v>1121.61</v>
       </c>
       <c r="E165" t="n">
-        <v>1134.42</v>
+        <v>1134.39</v>
       </c>
       <c r="F165" t="n">
         <v>20115</v>
@@ -25039,13 +25039,13 @@
         </is>
       </c>
       <c r="C166" t="n">
-        <v>1126.94</v>
+        <v>1126.9</v>
       </c>
       <c r="D166" t="n">
-        <v>1114.77</v>
+        <v>1114.73</v>
       </c>
       <c r="E166" t="n">
-        <v>1139.11</v>
+        <v>1139.06</v>
       </c>
       <c r="F166" t="n">
         <v>2921</v>
@@ -25190,13 +25190,13 @@
         </is>
       </c>
       <c r="C167" t="n">
-        <v>1126.54</v>
+        <v>1126.5</v>
       </c>
       <c r="D167" t="n">
-        <v>1110.85</v>
+        <v>1110.81</v>
       </c>
       <c r="E167" t="n">
-        <v>1142.22</v>
+        <v>1142.19</v>
       </c>
       <c r="F167" t="n">
         <v>1785</v>
@@ -25341,13 +25341,13 @@
         </is>
       </c>
       <c r="C168" t="n">
-        <v>1120.56</v>
+        <v>1120.52</v>
       </c>
       <c r="D168" t="n">
-        <v>1109.56</v>
+        <v>1109.52</v>
       </c>
       <c r="E168" t="n">
-        <v>1131.56</v>
+        <v>1131.53</v>
       </c>
       <c r="F168" t="n">
         <v>5184</v>
@@ -25492,13 +25492,13 @@
         </is>
       </c>
       <c r="C169" t="n">
-        <v>1118.67</v>
+        <v>1118.64</v>
       </c>
       <c r="D169" t="n">
-        <v>1100.44</v>
+        <v>1100.42</v>
       </c>
       <c r="E169" t="n">
-        <v>1136.9</v>
+        <v>1136.87</v>
       </c>
       <c r="F169" t="n">
         <v>1143</v>
@@ -25643,13 +25643,13 @@
         </is>
       </c>
       <c r="C170" t="n">
-        <v>1114.23</v>
+        <v>1114.19</v>
       </c>
       <c r="D170" t="n">
-        <v>1105.04</v>
+        <v>1105.01</v>
       </c>
       <c r="E170" t="n">
-        <v>1123.42</v>
+        <v>1123.38</v>
       </c>
       <c r="F170" t="n">
         <v>6923</v>
@@ -25794,13 +25794,13 @@
         </is>
       </c>
       <c r="C171" t="n">
-        <v>1113.95</v>
+        <v>1113.92</v>
       </c>
       <c r="D171" t="n">
-        <v>1099.53</v>
+        <v>1099.5</v>
       </c>
       <c r="E171" t="n">
-        <v>1128.38</v>
+        <v>1128.34</v>
       </c>
       <c r="F171" t="n">
         <v>2201</v>
@@ -25948,10 +25948,10 @@
         <v>1113.84</v>
       </c>
       <c r="D172" t="n">
-        <v>1106.11</v>
+        <v>1106.1</v>
       </c>
       <c r="E172" t="n">
-        <v>1121.58</v>
+        <v>1121.57</v>
       </c>
       <c r="F172" t="n">
         <v>10853</v>
@@ -26096,13 +26096,13 @@
         </is>
       </c>
       <c r="C173" t="n">
-        <v>1110.95</v>
+        <v>1110.92</v>
       </c>
       <c r="D173" t="n">
-        <v>1103.08</v>
+        <v>1103.05</v>
       </c>
       <c r="E173" t="n">
-        <v>1118.83</v>
+        <v>1118.8</v>
       </c>
       <c r="F173" t="n">
         <v>8045</v>
@@ -26247,13 +26247,13 @@
         </is>
       </c>
       <c r="C174" t="n">
-        <v>1109.24</v>
+        <v>1109.2</v>
       </c>
       <c r="D174" t="n">
-        <v>1099.93</v>
+        <v>1099.89</v>
       </c>
       <c r="E174" t="n">
-        <v>1118.54</v>
+        <v>1118.5</v>
       </c>
       <c r="F174" t="n">
         <v>8977</v>
@@ -26398,13 +26398,13 @@
         </is>
       </c>
       <c r="C175" t="n">
-        <v>1107.79</v>
+        <v>1107.78</v>
       </c>
       <c r="D175" t="n">
-        <v>1100.73</v>
+        <v>1100.72</v>
       </c>
       <c r="E175" t="n">
-        <v>1114.85</v>
+        <v>1114.83</v>
       </c>
       <c r="F175" t="n">
         <v>14148</v>
@@ -26549,13 +26549,13 @@
         </is>
       </c>
       <c r="C176" t="n">
-        <v>1091.31</v>
+        <v>1091.3</v>
       </c>
       <c r="D176" t="n">
-        <v>1079.79</v>
+        <v>1079.78</v>
       </c>
       <c r="E176" t="n">
-        <v>1102.84</v>
+        <v>1102.82</v>
       </c>
       <c r="F176" t="n">
         <v>4779</v>
@@ -26700,13 +26700,13 @@
         </is>
       </c>
       <c r="C177" t="n">
-        <v>1089.72</v>
+        <v>1089.68</v>
       </c>
       <c r="D177" t="n">
-        <v>1080.36</v>
+        <v>1080.32</v>
       </c>
       <c r="E177" t="n">
-        <v>1099.07</v>
+        <v>1099.03</v>
       </c>
       <c r="F177" t="n">
         <v>7598</v>
@@ -26851,13 +26851,13 @@
         </is>
       </c>
       <c r="C178" t="n">
-        <v>1074.26</v>
+        <v>1074.23</v>
       </c>
       <c r="D178" t="n">
-        <v>1063.06</v>
+        <v>1063.03</v>
       </c>
       <c r="E178" t="n">
-        <v>1085.45</v>
+        <v>1085.42</v>
       </c>
       <c r="F178" t="n">
         <v>6329</v>
@@ -27002,13 +27002,13 @@
         </is>
       </c>
       <c r="C179" t="n">
-        <v>1070.01</v>
+        <v>1069.98</v>
       </c>
       <c r="D179" t="n">
-        <v>1060.05</v>
+        <v>1060.01</v>
       </c>
       <c r="E179" t="n">
-        <v>1079.97</v>
+        <v>1079.94</v>
       </c>
       <c r="F179" t="n">
         <v>6964</v>
@@ -27153,13 +27153,13 @@
         </is>
       </c>
       <c r="C180" t="n">
-        <v>1066.9</v>
+        <v>1066.86</v>
       </c>
       <c r="D180" t="n">
-        <v>1055.36</v>
+        <v>1055.33</v>
       </c>
       <c r="E180" t="n">
-        <v>1078.44</v>
+        <v>1078.4</v>
       </c>
       <c r="F180" t="n">
         <v>5745</v>
@@ -27304,13 +27304,13 @@
         </is>
       </c>
       <c r="C181" t="n">
-        <v>1065.49</v>
+        <v>1065.45</v>
       </c>
       <c r="D181" t="n">
-        <v>1050.18</v>
+        <v>1050.15</v>
       </c>
       <c r="E181" t="n">
-        <v>1080.79</v>
+        <v>1080.76</v>
       </c>
       <c r="F181" t="n">
         <v>1743</v>
@@ -27455,13 +27455,13 @@
         </is>
       </c>
       <c r="C182" t="n">
-        <v>1061.36</v>
+        <v>1061.33</v>
       </c>
       <c r="D182" t="n">
-        <v>1049.32</v>
+        <v>1049.29</v>
       </c>
       <c r="E182" t="n">
-        <v>1073.41</v>
+        <v>1073.37</v>
       </c>
       <c r="F182" t="n">
         <v>3925</v>
@@ -27606,13 +27606,13 @@
         </is>
       </c>
       <c r="C183" t="n">
-        <v>1055.63</v>
+        <v>1055.59</v>
       </c>
       <c r="D183" t="n">
-        <v>1043.94</v>
+        <v>1043.9</v>
       </c>
       <c r="E183" t="n">
-        <v>1067.33</v>
+        <v>1067.28</v>
       </c>
       <c r="F183" t="n">
         <v>4658</v>
@@ -27757,13 +27757,13 @@
         </is>
       </c>
       <c r="C184" t="n">
-        <v>1040.85</v>
+        <v>1040.82</v>
       </c>
       <c r="D184" t="n">
-        <v>1029.38</v>
+        <v>1029.35</v>
       </c>
       <c r="E184" t="n">
-        <v>1052.31</v>
+        <v>1052.28</v>
       </c>
       <c r="F184" t="n">
         <v>4845</v>
@@ -27908,13 +27908,13 @@
         </is>
       </c>
       <c r="C185" t="n">
-        <v>1023.77</v>
+        <v>1023.73</v>
       </c>
       <c r="D185" t="n">
-        <v>1010.12</v>
+        <v>1010.09</v>
       </c>
       <c r="E185" t="n">
-        <v>1037.41</v>
+        <v>1037.37</v>
       </c>
       <c r="F185" t="n">
         <v>2657</v>
@@ -28059,13 +28059,13 @@
         </is>
       </c>
       <c r="C186" t="n">
-        <v>1021.64</v>
+        <v>1021.6</v>
       </c>
       <c r="D186" t="n">
-        <v>1010.7</v>
+        <v>1010.66</v>
       </c>
       <c r="E186" t="n">
-        <v>1032.58</v>
+        <v>1032.55</v>
       </c>
       <c r="F186" t="n">
         <v>6311</v>
@@ -28210,13 +28210,13 @@
         </is>
       </c>
       <c r="C187" t="n">
-        <v>995.155</v>
+        <v>995.12</v>
       </c>
       <c r="D187" t="n">
-        <v>982.515</v>
+        <v>982.48</v>
       </c>
       <c r="E187" t="n">
-        <v>1007.8</v>
+        <v>1007.76</v>
       </c>
       <c r="F187" t="n">
         <v>4914</v>
@@ -28361,13 +28361,13 @@
         </is>
       </c>
       <c r="C188" t="n">
-        <v>990.83</v>
+        <v>990.8049999999999</v>
       </c>
       <c r="D188" t="n">
-        <v>978.376</v>
+        <v>978.353</v>
       </c>
       <c r="E188" t="n">
-        <v>1003.28</v>
+        <v>1003.26</v>
       </c>
       <c r="F188" t="n">
         <v>4203</v>
@@ -28512,13 +28512,13 @@
         </is>
       </c>
       <c r="C189" t="n">
-        <v>979.566</v>
+        <v>979.528</v>
       </c>
       <c r="D189" t="n">
-        <v>965.932</v>
+        <v>965.895</v>
       </c>
       <c r="E189" t="n">
-        <v>993.201</v>
+        <v>993.1609999999999</v>
       </c>
       <c r="F189" t="n">
         <v>3412</v>
@@ -28663,13 +28663,13 @@
         </is>
       </c>
       <c r="C190" t="n">
-        <v>971.601</v>
+        <v>971.576</v>
       </c>
       <c r="D190" t="n">
-        <v>955.659</v>
+        <v>955.636</v>
       </c>
       <c r="E190" t="n">
-        <v>987.542</v>
+        <v>987.515</v>
       </c>
       <c r="F190" t="n">
         <v>2391</v>
@@ -28814,13 +28814,13 @@
         </is>
       </c>
       <c r="C191" t="n">
-        <v>952.16</v>
+        <v>952.127</v>
       </c>
       <c r="D191" t="n">
-        <v>939.321</v>
+        <v>939.289</v>
       </c>
       <c r="E191" t="n">
-        <v>964.999</v>
+        <v>964.965</v>
       </c>
       <c r="F191" t="n">
         <v>3287</v>
@@ -29039,7 +29039,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -29074,7 +29074,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -29109,7 +29109,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -29144,7 +29144,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -29179,7 +29179,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -29218,7 +29218,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -29253,7 +29253,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -29288,7 +29288,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -29323,7 +29323,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -29358,7 +29358,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -29393,7 +29393,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -29463,7 +29463,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -29498,7 +29498,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -29533,7 +29533,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -29630,14 +29630,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>qwen3.5-397b-a17b</t>
+          <t>kimi-k2.5-thinking</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>397</v>
+        <v>1000</v>
       </c>
       <c r="C3" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -29646,21 +29646,21 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>artificial_analysis</t>
+          <t>override</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>kimi-k2.5-thinking</t>
+          <t>qwen3.5-397b-a17b</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1000</v>
+        <v>397</v>
       </c>
       <c r="C4" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -29669,7 +29669,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>artificial_analysis</t>
         </is>
       </c>
     </row>
@@ -29883,14 +29883,14 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>qwen3.5-122b-a10b</t>
+          <t>deepseek-r1-0528</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>125</v>
+        <v>685</v>
       </c>
       <c r="C14" t="n">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -29906,7 +29906,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>deepseek-r1-0528</t>
+          <t>deepseek-v3.1</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -29929,14 +29929,14 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>deepseek-v3.1</t>
+          <t>qwen3.5-122b-a10b</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>685</v>
+        <v>125</v>
       </c>
       <c r="C16" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -30113,18 +30113,18 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>glm-4.5</t>
+          <t>qwen3.5-27b</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>355</v>
+        <v>27.8</v>
       </c>
       <c r="C24" t="n">
-        <v>32</v>
+        <v>27.8</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>moe</t>
+          <t>dense</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -30136,18 +30136,18 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>qwen3.5-27b</t>
+          <t>glm-4.5</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>27.8</v>
+        <v>355</v>
       </c>
       <c r="C25" t="n">
-        <v>27.8</v>
+        <v>32</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>dense</t>
+          <t>moe</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -30159,14 +30159,14 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>qwen3-235b-a22b-no-thinking</t>
+          <t>minimax-m2.5</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="C26" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -30175,21 +30175,21 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>artificial_analysis</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>qwen3-next-80b-a3b-instruct</t>
+          <t>qwen3-235b-a22b-no-thinking</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>80</v>
+        <v>235</v>
       </c>
       <c r="C27" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -30198,21 +30198,21 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>artificial_analysis</t>
+          <t>name_parsing</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>minimax-m2.5</t>
+          <t>qwen3-next-80b-a3b-instruct</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>230</v>
+        <v>80</v>
       </c>
       <c r="C28" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -30297,14 +30297,14 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>qwen3-vl-235b-a22b-thinking</t>
+          <t>qwen3.5-35b-a3b</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>235</v>
+        <v>36</v>
       </c>
       <c r="C32" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -30313,21 +30313,21 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>artificial_analysis</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>qwen3.5-35b-a3b</t>
+          <t>qwen3-vl-235b-a22b-thinking</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>36</v>
+        <v>235</v>
       </c>
       <c r="C33" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -30336,7 +30336,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>artificial_analysis</t>
+          <t>name_parsing</t>
         </is>
       </c>
     </row>
@@ -31408,14 +31408,14 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>athene-70b-0725</t>
+          <t>olmo-3-32b-think</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>70</v>
+        <v>32.2</v>
       </c>
       <c r="C81" t="n">
-        <v>70</v>
+        <v>32.2</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -31424,21 +31424,21 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>artificial_analysis</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>olmo-3-32b-think</t>
+          <t>athene-70b-0725</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>32.2</v>
+        <v>70</v>
       </c>
       <c r="C82" t="n">
-        <v>32.2</v>
+        <v>70</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -31447,7 +31447,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>artificial_analysis</t>
+          <t>name_parsing</t>
         </is>
       </c>
     </row>

--- a/arena_enrichment/output/arena_leaderboard_enriched.xlsx
+++ b/arena_enrichment/output/arena_leaderboard_enriched.xlsx
@@ -675,16 +675,16 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>1453.95</v>
+        <v>1453.49</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1447.45</v>
+        <v>1447.25</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1460.45</v>
+        <v>1459.74</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>9031</v>
+        <v>10020</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
@@ -826,16 +826,16 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>1451.99</v>
+        <v>1452.54</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1446.38</v>
+        <v>1447.11</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1457.61</v>
+        <v>1457.96</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>13903</v>
+        <v>15234</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
@@ -977,16 +977,16 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>1449.89</v>
+        <v>1451.5</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1443.15</v>
+        <v>1445.12</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1456.64</v>
+        <v>1457.89</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>8090</v>
+        <v>9337</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
@@ -1128,16 +1128,16 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>1441.47</v>
+        <v>1441.41</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1435.29</v>
+        <v>1435.23</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1447.66</v>
+        <v>1447.59</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>11896</v>
+        <v>11891</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
@@ -1279,16 +1279,16 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1438.1</v>
+        <v>1439.99</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1432.03</v>
+        <v>1434.23</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1444.16</v>
+        <v>1445.75</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>10086</v>
+        <v>11375</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
@@ -1430,16 +1430,16 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>1429.62</v>
+        <v>1430.06</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>1425.81</v>
+        <v>1426.29</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1433.42</v>
+        <v>1433.83</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>38973</v>
+        <v>39914</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
@@ -1581,16 +1581,16 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>1425.94</v>
+        <v>1426.03</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>1421.94</v>
+        <v>1422.04</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1429.93</v>
+        <v>1430.02</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>35019</v>
+        <v>35013</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
@@ -1732,13 +1732,13 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>1424.22</v>
+        <v>1424.28</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1417.62</v>
+        <v>1417.69</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1430.81</v>
+        <v>1430.88</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>8922</v>
@@ -1883,16 +1883,16 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>1423.96</v>
+        <v>1424</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>1417.47</v>
+        <v>1417.52</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1430.45</v>
+        <v>1430.49</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>11652</v>
+        <v>11649</v>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
@@ -2030,36 +2030,36 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>deepseek-v3.2</t>
+          <t>qwen3-235b-a22b-instruct-2507</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>1423.23</v>
+        <v>1422.82</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>1419.02</v>
+        <v>1419.88</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1427.44</v>
+        <v>1425.75</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>33766</v>
+        <v>75677</v>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>DeepSeek</t>
+          <t>Alibaba</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Apache 2.0</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>685</v>
+        <v>235</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
@@ -2072,22 +2072,22 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>1370</v>
+        <v>470</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>1712.5</v>
+        <v>587.5</v>
       </c>
       <c r="O11" s="2" t="n">
-        <v>685</v>
+        <v>235</v>
       </c>
       <c r="P11" s="2" t="n">
-        <v>856.2</v>
+        <v>293.8</v>
       </c>
       <c r="Q11" s="2" t="n">
-        <v>342.5</v>
+        <v>117.5</v>
       </c>
       <c r="R11" s="2" t="n">
-        <v>428.1</v>
+        <v>146.9</v>
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
@@ -2144,9 +2144,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AD11" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AD11" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AE11" s="3" t="inlineStr">
@@ -2159,9 +2159,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AG11" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AG11" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AH11" s="2" t="inlineStr">
@@ -2181,36 +2181,36 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>qwen3-235b-a22b-instruct-2507</t>
+          <t>deepseek-v3.2</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1422.96</v>
+        <v>1422.28</v>
       </c>
       <c r="D12" t="n">
-        <v>1420</v>
+        <v>1418.15</v>
       </c>
       <c r="E12" t="n">
-        <v>1425.92</v>
+        <v>1426.41</v>
       </c>
       <c r="F12" t="n">
-        <v>74402</v>
+        <v>35098</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alibaba</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>235</v>
+        <v>685</v>
       </c>
       <c r="J12" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -2223,22 +2223,22 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>470</v>
+        <v>1370</v>
       </c>
       <c r="N12" t="n">
-        <v>587.5</v>
+        <v>1712.5</v>
       </c>
       <c r="O12" t="n">
-        <v>235</v>
+        <v>685</v>
       </c>
       <c r="P12" t="n">
-        <v>293.8</v>
+        <v>856.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>117.5</v>
+        <v>342.5</v>
       </c>
       <c r="R12" t="n">
-        <v>146.9</v>
+        <v>428.1</v>
       </c>
       <c r="S12" s="5" t="inlineStr">
         <is>
@@ -2295,9 +2295,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AD12" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AD12" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AE12" s="5" t="inlineStr">
@@ -2310,9 +2310,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AG12" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AG12" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
@@ -2339,13 +2339,13 @@
         <v>1420.63</v>
       </c>
       <c r="D13" t="n">
-        <v>1416.32</v>
+        <v>1416.4</v>
       </c>
       <c r="E13" t="n">
-        <v>1424.94</v>
+        <v>1424.86</v>
       </c>
       <c r="F13" t="n">
-        <v>28519</v>
+        <v>29743</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -2487,16 +2487,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1420.18</v>
+        <v>1420.23</v>
       </c>
       <c r="D14" t="n">
-        <v>1414.57</v>
+        <v>1414.62</v>
       </c>
       <c r="E14" t="n">
-        <v>1425.79</v>
+        <v>1425.84</v>
       </c>
       <c r="F14" t="n">
-        <v>19106</v>
+        <v>19107</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -2634,36 +2634,36 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>qwen3.5-122b-a10b</t>
+          <t>deepseek-v3.1</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1418.95</v>
+        <v>1418.69</v>
       </c>
       <c r="D15" t="n">
-        <v>1410.21</v>
+        <v>1412.69</v>
       </c>
       <c r="E15" t="n">
-        <v>1427.7</v>
+        <v>1424.69</v>
       </c>
       <c r="F15" t="n">
-        <v>4515</v>
+        <v>15170</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alibaba</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>125</v>
+        <v>685</v>
       </c>
       <c r="J15" t="n">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -2676,22 +2676,22 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>250</v>
+        <v>1370</v>
       </c>
       <c r="N15" t="n">
-        <v>312.5</v>
+        <v>1712.5</v>
       </c>
       <c r="O15" t="n">
-        <v>125</v>
+        <v>685</v>
       </c>
       <c r="P15" t="n">
-        <v>156.2</v>
+        <v>856.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>62.5</v>
+        <v>342.5</v>
       </c>
       <c r="R15" t="n">
-        <v>78.09999999999999</v>
+        <v>428.1</v>
       </c>
       <c r="S15" s="5" t="inlineStr">
         <is>
@@ -2703,9 +2703,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="U15" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="U15" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="V15" s="5" t="inlineStr">
@@ -2718,9 +2718,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="X15" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="X15" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="Y15" s="5" t="inlineStr">
@@ -2733,9 +2733,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AA15" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AA15" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AB15" s="5" t="inlineStr">
@@ -2743,14 +2743,14 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AC15" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AD15" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AC15" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD15" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AE15" s="5" t="inlineStr">
@@ -2758,14 +2758,14 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AF15" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AG15" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AF15" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AG15" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
@@ -2775,7 +2775,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>B200 SXM</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
     </row>
@@ -2785,36 +2785,36 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>deepseek-v3.1</t>
+          <t>kimi-k2-0905-preview</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1418.7</v>
+        <v>1418.48</v>
       </c>
       <c r="D16" t="n">
-        <v>1412.7</v>
+        <v>1411.99</v>
       </c>
       <c r="E16" t="n">
-        <v>1424.7</v>
+        <v>1424.97</v>
       </c>
       <c r="F16" t="n">
-        <v>15170</v>
+        <v>11875</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>DeepSeek</t>
+          <t>Moonshot</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Modified MIT</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>685</v>
+        <v>1000</v>
       </c>
       <c r="J16" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -2823,26 +2823,26 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>artificial_analysis</t>
+          <t>override</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>1370</v>
+        <v>2000</v>
       </c>
       <c r="N16" t="n">
-        <v>1712.5</v>
+        <v>2500</v>
       </c>
       <c r="O16" t="n">
-        <v>685</v>
+        <v>1000</v>
       </c>
       <c r="P16" t="n">
-        <v>856.2</v>
+        <v>1250</v>
       </c>
       <c r="Q16" t="n">
-        <v>342.5</v>
+        <v>500</v>
       </c>
       <c r="R16" t="n">
-        <v>428.1</v>
+        <v>625</v>
       </c>
       <c r="S16" s="5" t="inlineStr">
         <is>
@@ -2936,36 +2936,36 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>kimi-k2-0905-preview</t>
+          <t>qwen3.5-122b-a10b</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1418.38</v>
+        <v>1417.83</v>
       </c>
       <c r="D17" t="n">
-        <v>1411.89</v>
+        <v>1410.11</v>
       </c>
       <c r="E17" t="n">
-        <v>1424.87</v>
+        <v>1425.56</v>
       </c>
       <c r="F17" t="n">
-        <v>11874</v>
+        <v>5844</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Moonshot</t>
+          <t>Alibaba</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Modified MIT</t>
+          <t>Apache 2.0</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1000</v>
+        <v>125</v>
       </c>
       <c r="J17" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -2974,26 +2974,26 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>artificial_analysis</t>
         </is>
       </c>
       <c r="M17" t="n">
-        <v>2000</v>
+        <v>250</v>
       </c>
       <c r="N17" t="n">
-        <v>2500</v>
+        <v>312.5</v>
       </c>
       <c r="O17" t="n">
-        <v>1000</v>
+        <v>125</v>
       </c>
       <c r="P17" t="n">
-        <v>1250</v>
+        <v>156.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>500</v>
+        <v>62.5</v>
       </c>
       <c r="R17" t="n">
-        <v>625</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="S17" s="5" t="inlineStr">
         <is>
@@ -3005,9 +3005,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="U17" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="U17" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="V17" s="5" t="inlineStr">
@@ -3020,9 +3020,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="X17" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="X17" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Y17" s="5" t="inlineStr">
@@ -3035,9 +3035,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AA17" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AA17" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AB17" s="5" t="inlineStr">
@@ -3045,14 +3045,14 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AC17" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AD17" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AC17" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AD17" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AE17" s="5" t="inlineStr">
@@ -3060,14 +3060,14 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AF17" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AG17" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AF17" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AG17" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>B200 SXM</t>
         </is>
       </c>
     </row>
@@ -3087,36 +3087,36 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>deepseek-v3.1-thinking</t>
+          <t>mistral-large-3</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1417.21</v>
+        <v>1417.26</v>
       </c>
       <c r="D18" t="n">
-        <v>1410.62</v>
+        <v>1413.15</v>
       </c>
       <c r="E18" t="n">
-        <v>1423.79</v>
+        <v>1421.37</v>
       </c>
       <c r="F18" t="n">
-        <v>11913</v>
+        <v>31701</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>DeepSeek</t>
+          <t>Mistral</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Apache 2.0</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>685</v>
+        <v>675</v>
       </c>
       <c r="J18" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -3129,22 +3129,22 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>1370</v>
+        <v>1350</v>
       </c>
       <c r="N18" t="n">
-        <v>1712.5</v>
+        <v>1687.5</v>
       </c>
       <c r="O18" t="n">
-        <v>685</v>
+        <v>675</v>
       </c>
       <c r="P18" t="n">
-        <v>856.2</v>
+        <v>843.8</v>
       </c>
       <c r="Q18" t="n">
-        <v>342.5</v>
+        <v>337.5</v>
       </c>
       <c r="R18" t="n">
-        <v>428.1</v>
+        <v>421.9</v>
       </c>
       <c r="S18" s="5" t="inlineStr">
         <is>
@@ -3238,36 +3238,36 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>kimi-k2-0711-preview</t>
+          <t>deepseek-v3.1-thinking</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1417.15</v>
+        <v>1417.23</v>
       </c>
       <c r="D19" t="n">
-        <v>1412.33</v>
+        <v>1410.65</v>
       </c>
       <c r="E19" t="n">
-        <v>1421.97</v>
+        <v>1423.82</v>
       </c>
       <c r="F19" t="n">
-        <v>28377</v>
+        <v>11912</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Moonshot</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Modified MIT</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1000</v>
+        <v>685</v>
       </c>
       <c r="J19" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -3276,26 +3276,26 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>artificial_analysis</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>2000</v>
+        <v>1370</v>
       </c>
       <c r="N19" t="n">
-        <v>2500</v>
+        <v>1712.5</v>
       </c>
       <c r="O19" t="n">
-        <v>1000</v>
+        <v>685</v>
       </c>
       <c r="P19" t="n">
-        <v>1250</v>
+        <v>856.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>500</v>
+        <v>342.5</v>
       </c>
       <c r="R19" t="n">
-        <v>625</v>
+        <v>428.1</v>
       </c>
       <c r="S19" s="5" t="inlineStr">
         <is>
@@ -3389,36 +3389,36 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>deepseek-v3.1-terminus</t>
+          <t>kimi-k2-0711-preview</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1416.54</v>
+        <v>1417.07</v>
       </c>
       <c r="D20" t="n">
-        <v>1406.96</v>
+        <v>1412.25</v>
       </c>
       <c r="E20" t="n">
-        <v>1426.12</v>
+        <v>1421.88</v>
       </c>
       <c r="F20" t="n">
-        <v>3732</v>
+        <v>28373</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>DeepSeek</t>
+          <t>Moonshot</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Modified MIT</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>685</v>
+        <v>1000</v>
       </c>
       <c r="J20" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -3427,26 +3427,26 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>artificial_analysis</t>
+          <t>override</t>
         </is>
       </c>
       <c r="M20" t="n">
-        <v>1370</v>
+        <v>2000</v>
       </c>
       <c r="N20" t="n">
-        <v>1712.5</v>
+        <v>2500</v>
       </c>
       <c r="O20" t="n">
-        <v>685</v>
+        <v>1000</v>
       </c>
       <c r="P20" t="n">
-        <v>856.2</v>
+        <v>1250</v>
       </c>
       <c r="Q20" t="n">
-        <v>342.5</v>
+        <v>500</v>
       </c>
       <c r="R20" t="n">
-        <v>428.1</v>
+        <v>625</v>
       </c>
       <c r="S20" s="5" t="inlineStr">
         <is>
@@ -3540,36 +3540,36 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>mistral-large-3</t>
+          <t>deepseek-v3.1-terminus</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1416.34</v>
+        <v>1416.6</v>
       </c>
       <c r="D21" t="n">
-        <v>1412.15</v>
+        <v>1407.02</v>
       </c>
       <c r="E21" t="n">
-        <v>1420.52</v>
+        <v>1426.18</v>
       </c>
       <c r="F21" t="n">
-        <v>30359</v>
+        <v>3732</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Mistral</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>675</v>
+        <v>685</v>
       </c>
       <c r="J21" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -3582,22 +3582,22 @@
         </is>
       </c>
       <c r="M21" t="n">
-        <v>1350</v>
+        <v>1370</v>
       </c>
       <c r="N21" t="n">
-        <v>1687.5</v>
+        <v>1712.5</v>
       </c>
       <c r="O21" t="n">
-        <v>675</v>
+        <v>685</v>
       </c>
       <c r="P21" t="n">
-        <v>843.8</v>
+        <v>856.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>337.5</v>
+        <v>342.5</v>
       </c>
       <c r="R21" t="n">
-        <v>421.9</v>
+        <v>428.1</v>
       </c>
       <c r="S21" s="5" t="inlineStr">
         <is>
@@ -3695,16 +3695,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1415.94</v>
+        <v>1416</v>
       </c>
       <c r="D22" t="n">
-        <v>1409.45</v>
+        <v>1409.51</v>
       </c>
       <c r="E22" t="n">
-        <v>1422.43</v>
+        <v>1422.49</v>
       </c>
       <c r="F22" t="n">
-        <v>11555</v>
+        <v>11553</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -3846,16 +3846,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1415.39</v>
+        <v>1415.47</v>
       </c>
       <c r="D23" t="n">
-        <v>1405.48</v>
+        <v>1405.56</v>
       </c>
       <c r="E23" t="n">
-        <v>1425.3</v>
+        <v>1425.38</v>
       </c>
       <c r="F23" t="n">
-        <v>3508</v>
+        <v>3507</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -3997,16 +3997,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1410.51</v>
+        <v>1410.56</v>
       </c>
       <c r="D24" t="n">
-        <v>1405.64</v>
+        <v>1405.68</v>
       </c>
       <c r="E24" t="n">
-        <v>1415.39</v>
+        <v>1415.44</v>
       </c>
       <c r="F24" t="n">
-        <v>24545</v>
+        <v>24543</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -4148,16 +4148,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1409.64</v>
+        <v>1408.03</v>
       </c>
       <c r="D25" t="n">
-        <v>1401.12</v>
+        <v>1400.43</v>
       </c>
       <c r="E25" t="n">
-        <v>1418.17</v>
+        <v>1415.64</v>
       </c>
       <c r="F25" t="n">
-        <v>4671</v>
+        <v>5989</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -4299,16 +4299,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1403.5</v>
+        <v>1405.49</v>
       </c>
       <c r="D26" t="n">
-        <v>1397.03</v>
+        <v>1399.35</v>
       </c>
       <c r="E26" t="n">
-        <v>1409.97</v>
+        <v>1411.64</v>
       </c>
       <c r="F26" t="n">
-        <v>9308</v>
+        <v>10646</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -4450,16 +4450,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1402.65</v>
+        <v>1402.7</v>
       </c>
       <c r="D27" t="n">
-        <v>1398.18</v>
+        <v>1398.23</v>
       </c>
       <c r="E27" t="n">
-        <v>1407.13</v>
+        <v>1407.18</v>
       </c>
       <c r="F27" t="n">
-        <v>39190</v>
+        <v>39188</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -4601,13 +4601,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1402.36</v>
+        <v>1402.49</v>
       </c>
       <c r="D28" t="n">
-        <v>1397.53</v>
+        <v>1397.67</v>
       </c>
       <c r="E28" t="n">
-        <v>1407.18</v>
+        <v>1407.31</v>
       </c>
       <c r="F28" t="n">
         <v>22600</v>
@@ -4752,16 +4752,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1400.96</v>
+        <v>1401.08</v>
       </c>
       <c r="D29" t="n">
-        <v>1394.58</v>
+        <v>1394.71</v>
       </c>
       <c r="E29" t="n">
-        <v>1407.34</v>
+        <v>1407.45</v>
       </c>
       <c r="F29" t="n">
-        <v>11435</v>
+        <v>11436</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -4903,16 +4903,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1399.54</v>
+        <v>1399.58</v>
       </c>
       <c r="D30" t="n">
-        <v>1393.05</v>
+        <v>1393.1</v>
       </c>
       <c r="E30" t="n">
-        <v>1406.02</v>
+        <v>1406.07</v>
       </c>
       <c r="F30" t="n">
-        <v>9171</v>
+        <v>9170</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -5054,13 +5054,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1398.17</v>
+        <v>1398.2</v>
       </c>
       <c r="D31" t="n">
-        <v>1393.32</v>
+        <v>1393.35</v>
       </c>
       <c r="E31" t="n">
-        <v>1403.02</v>
+        <v>1403.06</v>
       </c>
       <c r="F31" t="n">
         <v>18524</v>
@@ -5205,16 +5205,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1397.63</v>
+        <v>1397.78</v>
       </c>
       <c r="D32" t="n">
-        <v>1389.03</v>
+        <v>1390.24</v>
       </c>
       <c r="E32" t="n">
-        <v>1406.22</v>
+        <v>1405.32</v>
       </c>
       <c r="F32" t="n">
-        <v>4726</v>
+        <v>6209</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -5356,16 +5356,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1396.2</v>
+        <v>1396.31</v>
       </c>
       <c r="D33" t="n">
-        <v>1389.38</v>
+        <v>1389.49</v>
       </c>
       <c r="E33" t="n">
-        <v>1403.01</v>
+        <v>1403.12</v>
       </c>
       <c r="F33" t="n">
-        <v>7892</v>
+        <v>7890</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -5507,16 +5507,16 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1394.86</v>
+        <v>1394.89</v>
       </c>
       <c r="D34" t="n">
-        <v>1391.01</v>
+        <v>1391.04</v>
       </c>
       <c r="E34" t="n">
-        <v>1398.71</v>
+        <v>1398.74</v>
       </c>
       <c r="F34" t="n">
-        <v>46351</v>
+        <v>46347</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -5658,16 +5658,16 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1392.89</v>
+        <v>1392.6</v>
       </c>
       <c r="D35" t="n">
-        <v>1388.3</v>
+        <v>1388.1</v>
       </c>
       <c r="E35" t="n">
-        <v>1397.48</v>
+        <v>1397.09</v>
       </c>
       <c r="F35" t="n">
-        <v>22766</v>
+        <v>24140</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -5805,36 +5805,36 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>step-3.5-flash</t>
+          <t>mimo-v2-flash (thinking)</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1389.23</v>
+        <v>1387.58</v>
       </c>
       <c r="D36" t="n">
-        <v>1383.3</v>
+        <v>1381.25</v>
       </c>
       <c r="E36" t="n">
-        <v>1395.15</v>
+        <v>1393.91</v>
       </c>
       <c r="F36" t="n">
-        <v>11573</v>
+        <v>10857</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>StepFun</t>
+          <t>Xiaomi</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>196</v>
+        <v>309</v>
       </c>
       <c r="J36" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -5847,22 +5847,22 @@
         </is>
       </c>
       <c r="M36" t="n">
-        <v>392</v>
+        <v>618</v>
       </c>
       <c r="N36" t="n">
-        <v>490</v>
+        <v>772.5</v>
       </c>
       <c r="O36" t="n">
-        <v>196</v>
+        <v>309</v>
       </c>
       <c r="P36" t="n">
-        <v>245</v>
+        <v>386.2</v>
       </c>
       <c r="Q36" t="n">
-        <v>98</v>
+        <v>154.5</v>
       </c>
       <c r="R36" t="n">
-        <v>122.5</v>
+        <v>193.1</v>
       </c>
       <c r="S36" s="5" t="inlineStr">
         <is>
@@ -5904,9 +5904,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AA36" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AA36" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AB36" s="5" t="inlineStr">
@@ -5919,9 +5919,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AD36" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AD36" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AE36" s="5" t="inlineStr">
@@ -5929,9 +5929,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AF36" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AF36" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AG36" s="6" t="inlineStr">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>B300 SXM</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
     </row>
@@ -5956,24 +5956,24 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>qwen3-coder-480b-a35b-instruct</t>
+          <t>step-3.5-flash</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1387.29</v>
+        <v>1387.44</v>
       </c>
       <c r="D37" t="n">
-        <v>1382.38</v>
+        <v>1381.75</v>
       </c>
       <c r="E37" t="n">
-        <v>1392.19</v>
+        <v>1393.12</v>
       </c>
       <c r="F37" t="n">
-        <v>26338</v>
+        <v>12872</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alibaba</t>
+          <t>StepFun</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -5982,10 +5982,10 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>480</v>
+        <v>196</v>
       </c>
       <c r="J37" t="n">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -5998,22 +5998,22 @@
         </is>
       </c>
       <c r="M37" t="n">
-        <v>960</v>
+        <v>392</v>
       </c>
       <c r="N37" t="n">
-        <v>1200</v>
+        <v>490</v>
       </c>
       <c r="O37" t="n">
-        <v>480</v>
+        <v>196</v>
       </c>
       <c r="P37" t="n">
-        <v>600</v>
+        <v>245</v>
       </c>
       <c r="Q37" t="n">
-        <v>240</v>
+        <v>98</v>
       </c>
       <c r="R37" t="n">
-        <v>300</v>
+        <v>122.5</v>
       </c>
       <c r="S37" s="5" t="inlineStr">
         <is>
@@ -6055,9 +6055,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AA37" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AA37" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AB37" s="5" t="inlineStr">
@@ -6070,9 +6070,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AD37" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AD37" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AE37" s="5" t="inlineStr">
@@ -6080,14 +6080,14 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AF37" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AG37" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AF37" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AG37" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AH37" t="inlineStr">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>B300 SXM</t>
         </is>
       </c>
     </row>
@@ -6107,36 +6107,36 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>mimo-v2-flash (thinking)</t>
+          <t>qwen3-coder-480b-a35b-instruct</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1387.15</v>
+        <v>1387.23</v>
       </c>
       <c r="D38" t="n">
-        <v>1380.81</v>
+        <v>1382.33</v>
       </c>
       <c r="E38" t="n">
-        <v>1393.49</v>
+        <v>1392.13</v>
       </c>
       <c r="F38" t="n">
-        <v>10848</v>
+        <v>26337</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Xiaomi</t>
+          <t>Alibaba</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Apache 2.0</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>309</v>
+        <v>480</v>
       </c>
       <c r="J38" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -6149,22 +6149,22 @@
         </is>
       </c>
       <c r="M38" t="n">
-        <v>618</v>
+        <v>960</v>
       </c>
       <c r="N38" t="n">
-        <v>772.5</v>
+        <v>1200</v>
       </c>
       <c r="O38" t="n">
-        <v>309</v>
+        <v>480</v>
       </c>
       <c r="P38" t="n">
-        <v>386.2</v>
+        <v>600</v>
       </c>
       <c r="Q38" t="n">
-        <v>154.5</v>
+        <v>240</v>
       </c>
       <c r="R38" t="n">
-        <v>193.1</v>
+        <v>300</v>
       </c>
       <c r="S38" s="5" t="inlineStr">
         <is>
@@ -6236,9 +6236,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AG38" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AG38" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AH38" t="inlineStr">
@@ -6262,16 +6262,16 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1386.14</v>
+        <v>1386.15</v>
       </c>
       <c r="D39" t="n">
-        <v>1380.82</v>
+        <v>1380.84</v>
       </c>
       <c r="E39" t="n">
         <v>1391.45</v>
       </c>
       <c r="F39" t="n">
-        <v>17019</v>
+        <v>17024</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -6413,13 +6413,13 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1384.04</v>
+        <v>1384.2</v>
       </c>
       <c r="D40" t="n">
-        <v>1379.17</v>
+        <v>1379.33</v>
       </c>
       <c r="E40" t="n">
-        <v>1388.92</v>
+        <v>1389.07</v>
       </c>
       <c r="F40" t="n">
         <v>23938</v>
@@ -6564,13 +6564,13 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1377.94</v>
+        <v>1378.38</v>
       </c>
       <c r="D41" t="n">
-        <v>1366.64</v>
+        <v>1367.07</v>
       </c>
       <c r="E41" t="n">
-        <v>1389.25</v>
+        <v>1389.68</v>
       </c>
       <c r="F41" t="n">
         <v>2773</v>
@@ -6711,24 +6711,24 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>qwen3-235b-a22b</t>
+          <t>trinity-large</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1375.14</v>
+        <v>1376.84</v>
       </c>
       <c r="D42" t="n">
-        <v>1370.47</v>
+        <v>1369.44</v>
       </c>
       <c r="E42" t="n">
-        <v>1379.81</v>
+        <v>1384.24</v>
       </c>
       <c r="F42" t="n">
-        <v>26961</v>
+        <v>6974</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alibaba</t>
+          <t>Arcee AI</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -6737,52 +6737,52 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>235</v>
+        <v>70</v>
       </c>
       <c r="J42" t="n">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>moe</t>
+          <t>dense</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>artificial_analysis</t>
+          <t>override</t>
         </is>
       </c>
       <c r="M42" t="n">
-        <v>470</v>
+        <v>140</v>
       </c>
       <c r="N42" t="n">
-        <v>587.5</v>
+        <v>175</v>
       </c>
       <c r="O42" t="n">
-        <v>235</v>
+        <v>70</v>
       </c>
       <c r="P42" t="n">
-        <v>293.8</v>
+        <v>87.5</v>
       </c>
       <c r="Q42" t="n">
-        <v>117.5</v>
+        <v>35</v>
       </c>
       <c r="R42" t="n">
-        <v>146.9</v>
+        <v>43.8</v>
       </c>
       <c r="S42" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="T42" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U42" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="T42" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U42" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="V42" s="5" t="inlineStr">
@@ -6795,9 +6795,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="X42" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="X42" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Y42" s="5" t="inlineStr">
@@ -6805,24 +6805,24 @@
           <t>No</t>
         </is>
       </c>
-      <c r="Z42" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AA42" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AB42" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AC42" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="Z42" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AA42" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB42" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AC42" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AD42" s="6" t="inlineStr">
@@ -6830,14 +6830,14 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="AE42" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AF42" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AE42" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AF42" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AG42" s="6" t="inlineStr">
@@ -6847,12 +6847,12 @@
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>B200 SXM</t>
         </is>
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>RTX PRO 6000</t>
         </is>
       </c>
     </row>
@@ -6862,24 +6862,24 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>trinity-large</t>
+          <t>qwen3-235b-a22b</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1374.74</v>
+        <v>1375.24</v>
       </c>
       <c r="D43" t="n">
-        <v>1366.42</v>
+        <v>1370.57</v>
       </c>
       <c r="E43" t="n">
-        <v>1383.05</v>
+        <v>1379.91</v>
       </c>
       <c r="F43" t="n">
-        <v>5482</v>
+        <v>26961</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Arcee AI</t>
+          <t>Alibaba</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -6888,52 +6888,52 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>70</v>
+        <v>235</v>
       </c>
       <c r="J43" t="n">
-        <v>70</v>
+        <v>22</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>dense</t>
+          <t>moe</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>artificial_analysis</t>
         </is>
       </c>
       <c r="M43" t="n">
-        <v>140</v>
+        <v>470</v>
       </c>
       <c r="N43" t="n">
-        <v>175</v>
+        <v>587.5</v>
       </c>
       <c r="O43" t="n">
-        <v>70</v>
+        <v>235</v>
       </c>
       <c r="P43" t="n">
-        <v>87.5</v>
+        <v>293.8</v>
       </c>
       <c r="Q43" t="n">
-        <v>35</v>
+        <v>117.5</v>
       </c>
       <c r="R43" t="n">
-        <v>43.8</v>
+        <v>146.9</v>
       </c>
       <c r="S43" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="T43" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="U43" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="T43" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U43" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="V43" s="5" t="inlineStr">
@@ -6946,9 +6946,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="X43" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="X43" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="Y43" s="5" t="inlineStr">
@@ -6956,24 +6956,24 @@
           <t>No</t>
         </is>
       </c>
-      <c r="Z43" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AA43" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB43" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AC43" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="Z43" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA43" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AB43" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AC43" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AD43" s="6" t="inlineStr">
@@ -6981,14 +6981,14 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="AE43" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AF43" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AE43" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF43" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AG43" s="6" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="AH43" t="inlineStr">
         <is>
-          <t>B200 SXM</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>RTX PRO 6000</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
     </row>
@@ -7017,16 +7017,16 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1372.46</v>
+        <v>1372.56</v>
       </c>
       <c r="D44" t="n">
-        <v>1368.19</v>
+        <v>1368.29</v>
       </c>
       <c r="E44" t="n">
-        <v>1376.73</v>
+        <v>1376.83</v>
       </c>
       <c r="F44" t="n">
-        <v>31058</v>
+        <v>31057</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -7168,16 +7168,16 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1369.04</v>
+        <v>1369.01</v>
       </c>
       <c r="D45" t="n">
-        <v>1363.19</v>
+        <v>1363.17</v>
       </c>
       <c r="E45" t="n">
-        <v>1374.88</v>
+        <v>1374.86</v>
       </c>
       <c r="F45" t="n">
-        <v>13704</v>
+        <v>13702</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -7319,16 +7319,16 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1368.23</v>
+        <v>1368.32</v>
       </c>
       <c r="D46" t="n">
-        <v>1362.35</v>
+        <v>1362.46</v>
       </c>
       <c r="E46" t="n">
-        <v>1374.1</v>
+        <v>1374.19</v>
       </c>
       <c r="F46" t="n">
-        <v>11744</v>
+        <v>11748</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -7470,16 +7470,16 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1367.02</v>
+        <v>1367.05</v>
       </c>
       <c r="D47" t="n">
-        <v>1362.76</v>
+        <v>1362.79</v>
       </c>
       <c r="E47" t="n">
-        <v>1371.28</v>
+        <v>1371.31</v>
       </c>
       <c r="F47" t="n">
-        <v>36285</v>
+        <v>36287</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -7621,16 +7621,16 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1365.59</v>
+        <v>1365.66</v>
       </c>
       <c r="D48" t="n">
-        <v>1361.94</v>
+        <v>1362</v>
       </c>
       <c r="E48" t="n">
-        <v>1369.25</v>
+        <v>1369.31</v>
       </c>
       <c r="F48" t="n">
-        <v>48382</v>
+        <v>48375</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -7772,16 +7772,16 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1364.47</v>
+        <v>1364.44</v>
       </c>
       <c r="D49" t="n">
-        <v>1354.68</v>
+        <v>1354.7</v>
       </c>
       <c r="E49" t="n">
-        <v>1374.27</v>
+        <v>1374.18</v>
       </c>
       <c r="F49" t="n">
-        <v>3556</v>
+        <v>3581</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -7923,13 +7923,13 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1358.95</v>
+        <v>1358.99</v>
       </c>
       <c r="D50" t="n">
-        <v>1354.24</v>
+        <v>1354.28</v>
       </c>
       <c r="E50" t="n">
-        <v>1363.66</v>
+        <v>1363.7</v>
       </c>
       <c r="F50" t="n">
         <v>21770</v>
@@ -8074,13 +8074,13 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1356.9</v>
+        <v>1356.95</v>
       </c>
       <c r="D51" t="n">
-        <v>1351.74</v>
+        <v>1351.78</v>
       </c>
       <c r="E51" t="n">
-        <v>1362.07</v>
+        <v>1362.12</v>
       </c>
       <c r="F51" t="n">
         <v>18178</v>
@@ -8225,16 +8225,16 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1356.48</v>
+        <v>1356.65</v>
       </c>
       <c r="D52" t="n">
-        <v>1348.07</v>
+        <v>1348.25</v>
       </c>
       <c r="E52" t="n">
-        <v>1364.89</v>
+        <v>1365.06</v>
       </c>
       <c r="F52" t="n">
-        <v>5274</v>
+        <v>5273</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -8376,16 +8376,16 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1354.86</v>
+        <v>1354.89</v>
       </c>
       <c r="D53" t="n">
-        <v>1350.49</v>
+        <v>1350.52</v>
       </c>
       <c r="E53" t="n">
-        <v>1359.23</v>
+        <v>1359.26</v>
       </c>
       <c r="F53" t="n">
-        <v>30658</v>
+        <v>30655</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -8527,13 +8527,13 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1353.63</v>
+        <v>1353.7</v>
       </c>
       <c r="D54" t="n">
-        <v>1350.19</v>
+        <v>1350.26</v>
       </c>
       <c r="E54" t="n">
-        <v>1357.07</v>
+        <v>1357.14</v>
       </c>
       <c r="F54" t="n">
         <v>56995</v>
@@ -8678,13 +8678,13 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1353.45</v>
+        <v>1353.5</v>
       </c>
       <c r="D55" t="n">
-        <v>1345.09</v>
+        <v>1345.13</v>
       </c>
       <c r="E55" t="n">
-        <v>1361.82</v>
+        <v>1361.86</v>
       </c>
       <c r="F55" t="n">
         <v>4938</v>
@@ -8829,13 +8829,13 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1347.99</v>
+        <v>1348.06</v>
       </c>
       <c r="D56" t="n">
-        <v>1340.59</v>
+        <v>1340.67</v>
       </c>
       <c r="E56" t="n">
-        <v>1355.39</v>
+        <v>1355.46</v>
       </c>
       <c r="F56" t="n">
         <v>6566</v>
@@ -8900,13 +8900,13 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1347.81</v>
+        <v>1347.9</v>
       </c>
       <c r="D57" t="n">
-        <v>1340.52</v>
+        <v>1340.62</v>
       </c>
       <c r="E57" t="n">
-        <v>1355.09</v>
+        <v>1355.19</v>
       </c>
       <c r="F57" t="n">
         <v>6962</v>
@@ -9051,16 +9051,16 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1347.62</v>
+        <v>1347.68</v>
       </c>
       <c r="D58" t="n">
-        <v>1339.78</v>
+        <v>1339.84</v>
       </c>
       <c r="E58" t="n">
-        <v>1355.46</v>
+        <v>1355.52</v>
       </c>
       <c r="F58" t="n">
-        <v>6661</v>
+        <v>6659</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -9202,13 +9202,13 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1347.52</v>
+        <v>1347.57</v>
       </c>
       <c r="D59" t="n">
-        <v>1338.05</v>
+        <v>1338.1</v>
       </c>
       <c r="E59" t="n">
-        <v>1356.99</v>
+        <v>1357.04</v>
       </c>
       <c r="F59" t="n">
         <v>3926</v>
@@ -9353,13 +9353,13 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1347.5</v>
+        <v>1347.52</v>
       </c>
       <c r="D60" t="n">
-        <v>1335.8</v>
+        <v>1335.82</v>
       </c>
       <c r="E60" t="n">
-        <v>1359.21</v>
+        <v>1359.22</v>
       </c>
       <c r="F60" t="n">
         <v>2549</v>
@@ -9504,13 +9504,13 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1342.15</v>
+        <v>1342.18</v>
       </c>
       <c r="D61" t="n">
-        <v>1332.64</v>
+        <v>1332.67</v>
       </c>
       <c r="E61" t="n">
-        <v>1351.67</v>
+        <v>1351.7</v>
       </c>
       <c r="F61" t="n">
         <v>3829</v>
@@ -9655,16 +9655,16 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1342</v>
+        <v>1342.17</v>
       </c>
       <c r="D62" t="n">
-        <v>1332.08</v>
+        <v>1332.25</v>
       </c>
       <c r="E62" t="n">
-        <v>1351.91</v>
+        <v>1352.08</v>
       </c>
       <c r="F62" t="n">
-        <v>3400</v>
+        <v>3399</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -9806,16 +9806,16 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1336.26</v>
+        <v>1336.31</v>
       </c>
       <c r="D63" t="n">
-        <v>1331.86</v>
+        <v>1331.92</v>
       </c>
       <c r="E63" t="n">
-        <v>1340.66</v>
+        <v>1340.71</v>
       </c>
       <c r="F63" t="n">
-        <v>25934</v>
+        <v>25930</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -9957,13 +9957,13 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1335.47</v>
+        <v>1335.44</v>
       </c>
       <c r="D64" t="n">
-        <v>1331.8</v>
+        <v>1331.78</v>
       </c>
       <c r="E64" t="n">
-        <v>1339.13</v>
+        <v>1339.11</v>
       </c>
       <c r="F64" t="n">
         <v>41375</v>
@@ -10108,13 +10108,13 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1333.66</v>
+        <v>1333.64</v>
       </c>
       <c r="D65" t="n">
-        <v>1330.1</v>
+        <v>1330.09</v>
       </c>
       <c r="E65" t="n">
-        <v>1337.21</v>
+        <v>1337.2</v>
       </c>
       <c r="F65" t="n">
         <v>59656</v>
@@ -10259,16 +10259,16 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1331.39</v>
+        <v>1331.44</v>
       </c>
       <c r="D66" t="n">
-        <v>1325.23</v>
+        <v>1325.28</v>
       </c>
       <c r="E66" t="n">
-        <v>1337.55</v>
+        <v>1337.59</v>
       </c>
       <c r="F66" t="n">
-        <v>12206</v>
+        <v>12208</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -10410,16 +10410,16 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1328.92</v>
+        <v>1329.22</v>
       </c>
       <c r="D67" t="n">
-        <v>1307.7</v>
+        <v>1308.02</v>
       </c>
       <c r="E67" t="n">
-        <v>1350.13</v>
+        <v>1350.43</v>
       </c>
       <c r="F67" t="n">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -10561,16 +10561,16 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1328.65</v>
+        <v>1328.66</v>
       </c>
       <c r="D68" t="n">
-        <v>1323.95</v>
+        <v>1323.97</v>
       </c>
       <c r="E68" t="n">
-        <v>1333.34</v>
+        <v>1333.35</v>
       </c>
       <c r="F68" t="n">
-        <v>27213</v>
+        <v>27214</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -10712,16 +10712,16 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1328.03</v>
+        <v>1328.01</v>
       </c>
       <c r="D69" t="n">
-        <v>1323.81</v>
+        <v>1323.8</v>
       </c>
       <c r="E69" t="n">
-        <v>1332.25</v>
+        <v>1332.23</v>
       </c>
       <c r="F69" t="n">
-        <v>40876</v>
+        <v>40879</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -10863,13 +10863,13 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1327.96</v>
+        <v>1328.01</v>
       </c>
       <c r="D70" t="n">
-        <v>1315.78</v>
+        <v>1315.83</v>
       </c>
       <c r="E70" t="n">
-        <v>1340.13</v>
+        <v>1340.18</v>
       </c>
       <c r="F70" t="n">
         <v>2218</v>
@@ -11014,13 +11014,13 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1323.83</v>
+        <v>1323.88</v>
       </c>
       <c r="D71" t="n">
-        <v>1315.57</v>
+        <v>1315.61</v>
       </c>
       <c r="E71" t="n">
-        <v>1332.1</v>
+        <v>1332.14</v>
       </c>
       <c r="F71" t="n">
         <v>6795</v>
@@ -11165,16 +11165,16 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1322.73</v>
+        <v>1322.71</v>
       </c>
       <c r="D72" t="n">
-        <v>1318.05</v>
+        <v>1318.03</v>
       </c>
       <c r="E72" t="n">
-        <v>1327.41</v>
+        <v>1327.39</v>
       </c>
       <c r="F72" t="n">
-        <v>30938</v>
+        <v>30933</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -11316,13 +11316,13 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1320.97</v>
+        <v>1320.99</v>
       </c>
       <c r="D73" t="n">
-        <v>1313.73</v>
+        <v>1313.75</v>
       </c>
       <c r="E73" t="n">
-        <v>1328.21</v>
+        <v>1328.23</v>
       </c>
       <c r="F73" t="n">
         <v>7104</v>
@@ -11467,16 +11467,16 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1319.57</v>
+        <v>1319.59</v>
       </c>
       <c r="D74" t="n">
-        <v>1314.46</v>
+        <v>1314.49</v>
       </c>
       <c r="E74" t="n">
-        <v>1324.68</v>
+        <v>1324.7</v>
       </c>
       <c r="F74" t="n">
-        <v>23137</v>
+        <v>23138</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -11618,16 +11618,16 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>1319.31</v>
+        <v>1319.33</v>
       </c>
       <c r="D75" t="n">
-        <v>1315.9</v>
+        <v>1315.91</v>
       </c>
       <c r="E75" t="n">
-        <v>1322.73</v>
+        <v>1322.75</v>
       </c>
       <c r="F75" t="n">
-        <v>55372</v>
+        <v>55370</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -11769,13 +11769,13 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>1318.48</v>
+        <v>1318.68</v>
       </c>
       <c r="D76" t="n">
-        <v>1312.85</v>
+        <v>1313.06</v>
       </c>
       <c r="E76" t="n">
-        <v>1324.11</v>
+        <v>1324.31</v>
       </c>
       <c r="F76" t="n">
         <v>15376</v>
@@ -11920,13 +11920,13 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1318.37</v>
+        <v>1318.39</v>
       </c>
       <c r="D77" t="n">
-        <v>1312.69</v>
+        <v>1312.71</v>
       </c>
       <c r="E77" t="n">
-        <v>1324.05</v>
+        <v>1324.07</v>
       </c>
       <c r="F77" t="n">
         <v>16478</v>
@@ -11991,16 +11991,16 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1317.9</v>
+        <v>1317.93</v>
       </c>
       <c r="D78" t="n">
-        <v>1311.54</v>
+        <v>1311.57</v>
       </c>
       <c r="E78" t="n">
-        <v>1324.25</v>
+        <v>1324.28</v>
       </c>
       <c r="F78" t="n">
-        <v>10748</v>
+        <v>10750</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -12142,13 +12142,13 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>1314.85</v>
+        <v>1314.9</v>
       </c>
       <c r="D79" t="n">
-        <v>1310.34</v>
+        <v>1310.38</v>
       </c>
       <c r="E79" t="n">
-        <v>1319.37</v>
+        <v>1319.42</v>
       </c>
       <c r="F79" t="n">
         <v>24739</v>
@@ -12299,7 +12299,7 @@
         <v>1310.46</v>
       </c>
       <c r="E80" t="n">
-        <v>1318.23</v>
+        <v>1318.24</v>
       </c>
       <c r="F80" t="n">
         <v>45459</v>
@@ -12444,13 +12444,13 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1307.44</v>
+        <v>1307.47</v>
       </c>
       <c r="D81" t="n">
-        <v>1302.77</v>
+        <v>1302.79</v>
       </c>
       <c r="E81" t="n">
-        <v>1312.12</v>
+        <v>1312.15</v>
       </c>
       <c r="F81" t="n">
         <v>24572</v>
@@ -12595,16 +12595,16 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>1306.69</v>
+        <v>1306.86</v>
       </c>
       <c r="D82" t="n">
-        <v>1298.42</v>
+        <v>1298.59</v>
       </c>
       <c r="E82" t="n">
-        <v>1314.96</v>
+        <v>1315.13</v>
       </c>
       <c r="F82" t="n">
-        <v>5859</v>
+        <v>5858</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -12746,13 +12746,13 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>1306.38</v>
+        <v>1306.4</v>
       </c>
       <c r="D83" t="n">
-        <v>1300.73</v>
+        <v>1300.74</v>
       </c>
       <c r="E83" t="n">
-        <v>1312.04</v>
+        <v>1312.05</v>
       </c>
       <c r="F83" t="n">
         <v>19621</v>
@@ -12897,13 +12897,13 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>1305.6</v>
+        <v>1305.61</v>
       </c>
       <c r="D84" t="n">
-        <v>1301.2</v>
+        <v>1301.21</v>
       </c>
       <c r="E84" t="n">
-        <v>1309.99</v>
+        <v>1310</v>
       </c>
       <c r="F84" t="n">
         <v>28073</v>
@@ -13048,16 +13048,16 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>1304.11</v>
+        <v>1304.16</v>
       </c>
       <c r="D85" t="n">
-        <v>1299.63</v>
+        <v>1299.67</v>
       </c>
       <c r="E85" t="n">
-        <v>1308.6</v>
+        <v>1308.65</v>
       </c>
       <c r="F85" t="n">
-        <v>33824</v>
+        <v>33821</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -13199,13 +13199,13 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>1303.57</v>
+        <v>1303.59</v>
       </c>
       <c r="D86" t="n">
-        <v>1294.24</v>
+        <v>1294.27</v>
       </c>
       <c r="E86" t="n">
-        <v>1312.89</v>
+        <v>1312.91</v>
       </c>
       <c r="F86" t="n">
         <v>4171</v>
@@ -13350,13 +13350,13 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>1303.15</v>
+        <v>1303.18</v>
       </c>
       <c r="D87" t="n">
-        <v>1299.12</v>
+        <v>1299.15</v>
       </c>
       <c r="E87" t="n">
-        <v>1307.18</v>
+        <v>1307.21</v>
       </c>
       <c r="F87" t="n">
         <v>39406</v>
@@ -13501,13 +13501,13 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>1299.15</v>
+        <v>1299.21</v>
       </c>
       <c r="D88" t="n">
-        <v>1291.4</v>
+        <v>1291.45</v>
       </c>
       <c r="E88" t="n">
-        <v>1306.91</v>
+        <v>1306.96</v>
       </c>
       <c r="F88" t="n">
         <v>7140</v>
@@ -13652,13 +13652,13 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>1293.79</v>
+        <v>1293.81</v>
       </c>
       <c r="D89" t="n">
-        <v>1290.09</v>
+        <v>1290.11</v>
       </c>
       <c r="E89" t="n">
-        <v>1297.48</v>
+        <v>1297.5</v>
       </c>
       <c r="F89" t="n">
         <v>55240</v>
@@ -13957,10 +13957,10 @@
         <v>1288.44</v>
       </c>
       <c r="D91" t="n">
-        <v>1285.11</v>
+        <v>1285.1</v>
       </c>
       <c r="E91" t="n">
-        <v>1291.78</v>
+        <v>1291.77</v>
       </c>
       <c r="F91" t="n">
         <v>75754</v>
@@ -14101,36 +14101,36 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>ibm-granite-h-small</t>
+          <t>llama-3.1-tulu-3-70b</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>1286.97</v>
+        <v>1286.93</v>
       </c>
       <c r="D92" t="n">
-        <v>1278.51</v>
+        <v>1276.45</v>
       </c>
       <c r="E92" t="n">
-        <v>1295.42</v>
+        <v>1297.4</v>
       </c>
       <c r="F92" t="n">
-        <v>5589</v>
+        <v>2846</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>Ai2</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
+          <t>Llama 3.1</t>
         </is>
       </c>
       <c r="I92" t="n">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="J92" t="n">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
@@ -14139,30 +14139,30 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>name_parsing</t>
         </is>
       </c>
       <c r="M92" t="n">
-        <v>16</v>
+        <v>140</v>
       </c>
       <c r="N92" t="n">
-        <v>20</v>
+        <v>175</v>
       </c>
       <c r="O92" t="n">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="P92" t="n">
-        <v>10</v>
+        <v>87.5</v>
       </c>
       <c r="Q92" t="n">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="R92" t="n">
-        <v>5</v>
-      </c>
-      <c r="S92" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+        <v>43.8</v>
+      </c>
+      <c r="S92" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="T92" s="6" t="inlineStr">
@@ -14175,14 +14175,14 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="V92" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W92" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="V92" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W92" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="X92" s="6" t="inlineStr">
@@ -14190,9 +14190,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="Y92" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="Y92" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="Z92" s="6" t="inlineStr">
@@ -14237,12 +14237,12 @@
       </c>
       <c r="AH92" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>B200 SXM</t>
         </is>
       </c>
       <c r="AI92" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>RTX PRO 6000</t>
         </is>
       </c>
     </row>
@@ -14252,36 +14252,36 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>llama-3.1-tulu-3-70b</t>
+          <t>ibm-granite-h-small</t>
         </is>
       </c>
       <c r="C93" t="n">
         <v>1286.91</v>
       </c>
       <c r="D93" t="n">
-        <v>1276.43</v>
+        <v>1278.46</v>
       </c>
       <c r="E93" t="n">
-        <v>1297.38</v>
+        <v>1295.36</v>
       </c>
       <c r="F93" t="n">
-        <v>2846</v>
+        <v>5586</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Ai2</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Llama 3.1</t>
+          <t>Apache 2.0</t>
         </is>
       </c>
       <c r="I93" t="n">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="J93" t="n">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
@@ -14290,30 +14290,30 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>override</t>
         </is>
       </c>
       <c r="M93" t="n">
-        <v>140</v>
+        <v>16</v>
       </c>
       <c r="N93" t="n">
-        <v>175</v>
+        <v>20</v>
       </c>
       <c r="O93" t="n">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="P93" t="n">
-        <v>87.5</v>
+        <v>10</v>
       </c>
       <c r="Q93" t="n">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="R93" t="n">
-        <v>43.8</v>
-      </c>
-      <c r="S93" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+        <v>5</v>
+      </c>
+      <c r="S93" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="T93" s="6" t="inlineStr">
@@ -14326,14 +14326,14 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="V93" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W93" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="V93" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W93" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="X93" s="6" t="inlineStr">
@@ -14341,9 +14341,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="Y93" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="Y93" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Z93" s="6" t="inlineStr">
@@ -14388,12 +14388,12 @@
       </c>
       <c r="AH93" t="inlineStr">
         <is>
-          <t>B200 SXM</t>
+          <t>H100 SXM</t>
         </is>
       </c>
       <c r="AI93" t="inlineStr">
         <is>
-          <t>RTX PRO 6000</t>
+          <t>H100 SXM</t>
         </is>
       </c>
     </row>
@@ -14407,13 +14407,13 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1286.52</v>
+        <v>1286.5</v>
       </c>
       <c r="D94" t="n">
-        <v>1276.55</v>
+        <v>1276.53</v>
       </c>
       <c r="E94" t="n">
-        <v>1296.5</v>
+        <v>1296.47</v>
       </c>
       <c r="F94" t="n">
         <v>3749</v>
@@ -14558,16 +14558,16 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1285.29</v>
+        <v>1285.55</v>
       </c>
       <c r="D95" t="n">
-        <v>1278.01</v>
+        <v>1278.27</v>
       </c>
       <c r="E95" t="n">
-        <v>1292.58</v>
+        <v>1292.83</v>
       </c>
       <c r="F95" t="n">
-        <v>8408</v>
+        <v>8406</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
@@ -14715,7 +14715,7 @@
         <v>1272.86</v>
       </c>
       <c r="E96" t="n">
-        <v>1286.56</v>
+        <v>1286.57</v>
       </c>
       <c r="F96" t="n">
         <v>10072</v>
@@ -14860,13 +14860,13 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1277.58</v>
+        <v>1277.56</v>
       </c>
       <c r="D97" t="n">
-        <v>1272.26</v>
+        <v>1272.24</v>
       </c>
       <c r="E97" t="n">
-        <v>1282.9</v>
+        <v>1282.89</v>
       </c>
       <c r="F97" t="n">
         <v>19659</v>
@@ -15014,10 +15014,10 @@
         <v>1276.74</v>
       </c>
       <c r="D98" t="n">
-        <v>1270.18</v>
+        <v>1270.17</v>
       </c>
       <c r="E98" t="n">
-        <v>1283.31</v>
+        <v>1283.3</v>
       </c>
       <c r="F98" t="n">
         <v>9866</v>
@@ -15162,13 +15162,13 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>1276.3</v>
+        <v>1276.28</v>
       </c>
       <c r="D99" t="n">
-        <v>1272.74</v>
+        <v>1272.72</v>
       </c>
       <c r="E99" t="n">
-        <v>1279.86</v>
+        <v>1279.85</v>
       </c>
       <c r="F99" t="n">
         <v>156876</v>
@@ -15319,7 +15319,7 @@
         <v>1268.5</v>
       </c>
       <c r="E100" t="n">
-        <v>1280.25</v>
+        <v>1280.26</v>
       </c>
       <c r="F100" t="n">
         <v>14681</v>
@@ -15464,13 +15464,13 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1270.89</v>
+        <v>1270.91</v>
       </c>
       <c r="D101" t="n">
-        <v>1262.78</v>
+        <v>1262.79</v>
       </c>
       <c r="E101" t="n">
-        <v>1279.01</v>
+        <v>1279.03</v>
       </c>
       <c r="F101" t="n">
         <v>5432</v>
@@ -15615,10 +15615,10 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>1267.3</v>
+        <v>1267.31</v>
       </c>
       <c r="D102" t="n">
-        <v>1262.45</v>
+        <v>1262.46</v>
       </c>
       <c r="E102" t="n">
         <v>1272.16</v>
@@ -15766,13 +15766,13 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>1265.9</v>
+        <v>1265.89</v>
       </c>
       <c r="D103" t="n">
-        <v>1262.13</v>
+        <v>1262.12</v>
       </c>
       <c r="E103" t="n">
-        <v>1269.68</v>
+        <v>1269.67</v>
       </c>
       <c r="F103" t="n">
         <v>54611</v>
@@ -15917,13 +15917,13 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>1264.5</v>
+        <v>1264.47</v>
       </c>
       <c r="D104" t="n">
-        <v>1258.22</v>
+        <v>1258.19</v>
       </c>
       <c r="E104" t="n">
-        <v>1270.77</v>
+        <v>1270.74</v>
       </c>
       <c r="F104" t="n">
         <v>15147</v>
@@ -16068,13 +16068,13 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>1262.12</v>
+        <v>1262.09</v>
       </c>
       <c r="D105" t="n">
-        <v>1257.8</v>
+        <v>1257.78</v>
       </c>
       <c r="E105" t="n">
-        <v>1266.43</v>
+        <v>1266.41</v>
       </c>
       <c r="F105" t="n">
         <v>77554</v>
@@ -16219,13 +16219,13 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>1262.04</v>
+        <v>1262.02</v>
       </c>
       <c r="D106" t="n">
-        <v>1257.11</v>
+        <v>1257.09</v>
       </c>
       <c r="E106" t="n">
-        <v>1266.97</v>
+        <v>1266.95</v>
       </c>
       <c r="F106" t="n">
         <v>37325</v>
@@ -16370,13 +16370,13 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>1256.41</v>
+        <v>1256.42</v>
       </c>
       <c r="D107" t="n">
         <v>1251.86</v>
       </c>
       <c r="E107" t="n">
-        <v>1260.97</v>
+        <v>1260.98</v>
       </c>
       <c r="F107" t="n">
         <v>24126</v>
@@ -16672,13 +16672,13 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>1250.38</v>
+        <v>1250.35</v>
       </c>
       <c r="D109" t="n">
-        <v>1243.79</v>
+        <v>1243.76</v>
       </c>
       <c r="E109" t="n">
-        <v>1256.96</v>
+        <v>1256.94</v>
       </c>
       <c r="F109" t="n">
         <v>10140</v>
@@ -16974,13 +16974,13 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>1237.51</v>
+        <v>1237.52</v>
       </c>
       <c r="D111" t="n">
-        <v>1228.42</v>
+        <v>1228.43</v>
       </c>
       <c r="E111" t="n">
-        <v>1246.61</v>
+        <v>1246.62</v>
       </c>
       <c r="F111" t="n">
         <v>4781</v>
@@ -17125,13 +17125,13 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>1234.26</v>
+        <v>1234.24</v>
       </c>
       <c r="D112" t="n">
-        <v>1228.71</v>
+        <v>1228.68</v>
       </c>
       <c r="E112" t="n">
-        <v>1239.81</v>
+        <v>1239.79</v>
       </c>
       <c r="F112" t="n">
         <v>26195</v>
@@ -17276,13 +17276,13 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>1233.36</v>
+        <v>1233.32</v>
       </c>
       <c r="D113" t="n">
-        <v>1228.08</v>
+        <v>1228.05</v>
       </c>
       <c r="E113" t="n">
-        <v>1238.63</v>
+        <v>1238.6</v>
       </c>
       <c r="F113" t="n">
         <v>39302</v>
@@ -17427,13 +17427,13 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>1229.63</v>
+        <v>1229.59</v>
       </c>
       <c r="D114" t="n">
-        <v>1225.09</v>
+        <v>1225.05</v>
       </c>
       <c r="E114" t="n">
-        <v>1234.17</v>
+        <v>1234.14</v>
       </c>
       <c r="F114" t="n">
         <v>51416</v>
@@ -17578,13 +17578,13 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>1227.12</v>
+        <v>1227.09</v>
       </c>
       <c r="D115" t="n">
-        <v>1222.35</v>
+        <v>1222.31</v>
       </c>
       <c r="E115" t="n">
-        <v>1231.9</v>
+        <v>1231.87</v>
       </c>
       <c r="F115" t="n">
         <v>54036</v>
@@ -17729,13 +17729,13 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>1223.4</v>
+        <v>1223.39</v>
       </c>
       <c r="D116" t="n">
-        <v>1219.69</v>
+        <v>1219.67</v>
       </c>
       <c r="E116" t="n">
-        <v>1227.12</v>
+        <v>1227.11</v>
       </c>
       <c r="F116" t="n">
         <v>104642</v>
@@ -17880,13 +17880,13 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>1223.23</v>
+        <v>1223.25</v>
       </c>
       <c r="D117" t="n">
-        <v>1216.28</v>
+        <v>1216.29</v>
       </c>
       <c r="E117" t="n">
-        <v>1230.19</v>
+        <v>1230.2</v>
       </c>
       <c r="F117" t="n">
         <v>9818</v>
@@ -18031,13 +18031,13 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>1221.4</v>
+        <v>1221.43</v>
       </c>
       <c r="D118" t="n">
-        <v>1210.71</v>
+        <v>1210.74</v>
       </c>
       <c r="E118" t="n">
-        <v>1232.09</v>
+        <v>1232.12</v>
       </c>
       <c r="F118" t="n">
         <v>2896</v>
@@ -18333,13 +18333,13 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>1212.91</v>
+        <v>1212.87</v>
       </c>
       <c r="D120" t="n">
-        <v>1202.09</v>
+        <v>1202.06</v>
       </c>
       <c r="E120" t="n">
-        <v>1223.72</v>
+        <v>1223.68</v>
       </c>
       <c r="F120" t="n">
         <v>4652</v>
@@ -18484,13 +18484,13 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>1211.91</v>
+        <v>1211.95</v>
       </c>
       <c r="D121" t="n">
-        <v>1207.8</v>
+        <v>1207.83</v>
       </c>
       <c r="E121" t="n">
-        <v>1216.01</v>
+        <v>1216.06</v>
       </c>
       <c r="F121" t="n">
         <v>49605</v>
@@ -18635,13 +18635,13 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>1208.66</v>
+        <v>1208.63</v>
       </c>
       <c r="D122" t="n">
-        <v>1197.54</v>
+        <v>1197.51</v>
       </c>
       <c r="E122" t="n">
-        <v>1219.77</v>
+        <v>1219.74</v>
       </c>
       <c r="F122" t="n">
         <v>3090</v>
@@ -18786,13 +18786,13 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>1204.03</v>
+        <v>1203.99</v>
       </c>
       <c r="D123" t="n">
-        <v>1197.91</v>
+        <v>1197.87</v>
       </c>
       <c r="E123" t="n">
-        <v>1210.15</v>
+        <v>1210.11</v>
       </c>
       <c r="F123" t="n">
         <v>21741</v>
@@ -18937,13 +18937,13 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>1199.3</v>
+        <v>1199.31</v>
       </c>
       <c r="D124" t="n">
-        <v>1195.24</v>
+        <v>1195.25</v>
       </c>
       <c r="E124" t="n">
-        <v>1203.35</v>
+        <v>1203.37</v>
       </c>
       <c r="F124" t="n">
         <v>46616</v>
@@ -19088,13 +19088,13 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>1198.15</v>
+        <v>1198.12</v>
       </c>
       <c r="D125" t="n">
-        <v>1193</v>
+        <v>1192.97</v>
       </c>
       <c r="E125" t="n">
-        <v>1203.3</v>
+        <v>1203.27</v>
       </c>
       <c r="F125" t="n">
         <v>25055</v>
@@ -19239,13 +19239,13 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>1197.32</v>
+        <v>1197.29</v>
       </c>
       <c r="D126" t="n">
-        <v>1193.06</v>
+        <v>1193.02</v>
       </c>
       <c r="E126" t="n">
-        <v>1201.59</v>
+        <v>1201.55</v>
       </c>
       <c r="F126" t="n">
         <v>73503</v>
@@ -19390,13 +19390,13 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>1195.22</v>
+        <v>1195.17</v>
       </c>
       <c r="D127" t="n">
-        <v>1189.11</v>
+        <v>1189.06</v>
       </c>
       <c r="E127" t="n">
-        <v>1201.33</v>
+        <v>1201.29</v>
       </c>
       <c r="F127" t="n">
         <v>32191</v>
@@ -19541,13 +19541,13 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>1191.6</v>
+        <v>1191.62</v>
       </c>
       <c r="D128" t="n">
-        <v>1184.43</v>
+        <v>1184.44</v>
       </c>
       <c r="E128" t="n">
-        <v>1198.78</v>
+        <v>1198.79</v>
       </c>
       <c r="F128" t="n">
         <v>9901</v>
@@ -19692,13 +19692,13 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>1191.11</v>
+        <v>1191.08</v>
       </c>
       <c r="D129" t="n">
-        <v>1183.98</v>
+        <v>1183.95</v>
       </c>
       <c r="E129" t="n">
-        <v>1198.23</v>
+        <v>1198.2</v>
       </c>
       <c r="F129" t="n">
         <v>17839</v>
@@ -19843,13 +19843,13 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>1184.82</v>
+        <v>1184.79</v>
       </c>
       <c r="D130" t="n">
-        <v>1175.36</v>
+        <v>1175.33</v>
       </c>
       <c r="E130" t="n">
-        <v>1194.28</v>
+        <v>1194.25</v>
       </c>
       <c r="F130" t="n">
         <v>8214</v>
@@ -19994,13 +19994,13 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>1184.54</v>
+        <v>1184.49</v>
       </c>
       <c r="D131" t="n">
-        <v>1173.03</v>
+        <v>1172.98</v>
       </c>
       <c r="E131" t="n">
-        <v>1196.06</v>
+        <v>1196.01</v>
       </c>
       <c r="F131" t="n">
         <v>4932</v>
@@ -20145,13 +20145,13 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>1184.01</v>
+        <v>1183.99</v>
       </c>
       <c r="D132" t="n">
-        <v>1177.18</v>
+        <v>1177.16</v>
       </c>
       <c r="E132" t="n">
-        <v>1190.83</v>
+        <v>1190.82</v>
       </c>
       <c r="F132" t="n">
         <v>15483</v>
@@ -20296,13 +20296,13 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>1182.41</v>
+        <v>1182.36</v>
       </c>
       <c r="D133" t="n">
-        <v>1174.4</v>
+        <v>1174.36</v>
       </c>
       <c r="E133" t="n">
-        <v>1190.41</v>
+        <v>1190.37</v>
       </c>
       <c r="F133" t="n">
         <v>12637</v>
@@ -20367,13 +20367,13 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>1182.33</v>
+        <v>1182.27</v>
       </c>
       <c r="D134" t="n">
-        <v>1172.65</v>
+        <v>1172.59</v>
       </c>
       <c r="E134" t="n">
-        <v>1192.01</v>
+        <v>1191.95</v>
       </c>
       <c r="F134" t="n">
         <v>7968</v>
@@ -20438,13 +20438,13 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>1182.2</v>
+        <v>1182.14</v>
       </c>
       <c r="D135" t="n">
-        <v>1173.51</v>
+        <v>1173.45</v>
       </c>
       <c r="E135" t="n">
-        <v>1190.88</v>
+        <v>1190.82</v>
       </c>
       <c r="F135" t="n">
         <v>6638</v>
@@ -20589,13 +20589,13 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>1180.52</v>
+        <v>1180.47</v>
       </c>
       <c r="D136" t="n">
-        <v>1174.45</v>
+        <v>1174.4</v>
       </c>
       <c r="E136" t="n">
-        <v>1186.59</v>
+        <v>1186.55</v>
       </c>
       <c r="F136" t="n">
         <v>23893</v>
@@ -20740,13 +20740,13 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>1179.63</v>
+        <v>1179.58</v>
       </c>
       <c r="D137" t="n">
-        <v>1173.72</v>
+        <v>1173.67</v>
       </c>
       <c r="E137" t="n">
-        <v>1185.54</v>
+        <v>1185.49</v>
       </c>
       <c r="F137" t="n">
         <v>32832</v>
@@ -20811,13 +20811,13 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>1179.18</v>
+        <v>1179.16</v>
       </c>
       <c r="D138" t="n">
-        <v>1167.97</v>
+        <v>1167.95</v>
       </c>
       <c r="E138" t="n">
-        <v>1190.39</v>
+        <v>1190.37</v>
       </c>
       <c r="F138" t="n">
         <v>3188</v>
@@ -20962,13 +20962,13 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>1178.2</v>
+        <v>1178.17</v>
       </c>
       <c r="D139" t="n">
-        <v>1168.37</v>
+        <v>1168.35</v>
       </c>
       <c r="E139" t="n">
-        <v>1188.03</v>
+        <v>1188</v>
       </c>
       <c r="F139" t="n">
         <v>6535</v>
@@ -21113,13 +21113,13 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>1175.31</v>
+        <v>1175.25</v>
       </c>
       <c r="D140" t="n">
-        <v>1164.88</v>
+        <v>1164.82</v>
       </c>
       <c r="E140" t="n">
-        <v>1185.74</v>
+        <v>1185.68</v>
       </c>
       <c r="F140" t="n">
         <v>5006</v>
@@ -21264,13 +21264,13 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>1172.92</v>
+        <v>1172.89</v>
       </c>
       <c r="D141" t="n">
-        <v>1166.71</v>
+        <v>1166.67</v>
       </c>
       <c r="E141" t="n">
-        <v>1179.14</v>
+        <v>1179.1</v>
       </c>
       <c r="F141" t="n">
         <v>22479</v>
@@ -21415,13 +21415,13 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>1171.84</v>
+        <v>1171.83</v>
       </c>
       <c r="D142" t="n">
         <v>1164.42</v>
       </c>
       <c r="E142" t="n">
-        <v>1179.26</v>
+        <v>1179.25</v>
       </c>
       <c r="F142" t="n">
         <v>16056</v>
@@ -21566,13 +21566,13 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>1171.27</v>
+        <v>1171.24</v>
       </c>
       <c r="D143" t="n">
-        <v>1165.36</v>
+        <v>1165.33</v>
       </c>
       <c r="E143" t="n">
-        <v>1177.18</v>
+        <v>1177.16</v>
       </c>
       <c r="F143" t="n">
         <v>17766</v>
@@ -21717,13 +21717,13 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>1170.95</v>
+        <v>1170.93</v>
       </c>
       <c r="D144" t="n">
-        <v>1165.44</v>
+        <v>1165.42</v>
       </c>
       <c r="E144" t="n">
-        <v>1176.45</v>
+        <v>1176.43</v>
       </c>
       <c r="F144" t="n">
         <v>38492</v>
@@ -21868,13 +21868,13 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>1167.69</v>
+        <v>1167.67</v>
       </c>
       <c r="D145" t="n">
-        <v>1159.62</v>
+        <v>1159.59</v>
       </c>
       <c r="E145" t="n">
-        <v>1175.77</v>
+        <v>1175.74</v>
       </c>
       <c r="F145" t="n">
         <v>10224</v>
@@ -22019,13 +22019,13 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>1166.89</v>
+        <v>1166.88</v>
       </c>
       <c r="D146" t="n">
-        <v>1159.2</v>
+        <v>1159.18</v>
       </c>
       <c r="E146" t="n">
-        <v>1174.58</v>
+        <v>1174.57</v>
       </c>
       <c r="F146" t="n">
         <v>7936</v>
@@ -22170,13 +22170,13 @@
         </is>
       </c>
       <c r="C147" t="n">
-        <v>1164.89</v>
+        <v>1164.87</v>
       </c>
       <c r="D147" t="n">
-        <v>1152.94</v>
+        <v>1152.93</v>
       </c>
       <c r="E147" t="n">
-        <v>1176.83</v>
+        <v>1176.81</v>
       </c>
       <c r="F147" t="n">
         <v>3777</v>
@@ -22321,13 +22321,13 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>1157.2</v>
+        <v>1157.26</v>
       </c>
       <c r="D148" t="n">
-        <v>1145.69</v>
+        <v>1145.75</v>
       </c>
       <c r="E148" t="n">
-        <v>1168.7</v>
+        <v>1168.77</v>
       </c>
       <c r="F148" t="n">
         <v>3231</v>
@@ -22472,13 +22472,13 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>1156.2</v>
+        <v>1156.16</v>
       </c>
       <c r="D149" t="n">
-        <v>1147.81</v>
+        <v>1147.76</v>
       </c>
       <c r="E149" t="n">
-        <v>1164.59</v>
+        <v>1164.55</v>
       </c>
       <c r="F149" t="n">
         <v>6837</v>
@@ -22623,13 +22623,13 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>1155.52</v>
+        <v>1155.49</v>
       </c>
       <c r="D150" t="n">
-        <v>1142.89</v>
+        <v>1142.87</v>
       </c>
       <c r="E150" t="n">
-        <v>1168.15</v>
+        <v>1168.12</v>
       </c>
       <c r="F150" t="n">
         <v>3585</v>
@@ -22774,13 +22774,13 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>1152.51</v>
+        <v>1152.47</v>
       </c>
       <c r="D151" t="n">
-        <v>1139.3</v>
+        <v>1139.26</v>
       </c>
       <c r="E151" t="n">
-        <v>1165.73</v>
+        <v>1165.69</v>
       </c>
       <c r="F151" t="n">
         <v>4155</v>
@@ -22925,13 +22925,13 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>1152.14</v>
+        <v>1152.1</v>
       </c>
       <c r="D152" t="n">
-        <v>1136.73</v>
+        <v>1136.69</v>
       </c>
       <c r="E152" t="n">
-        <v>1167.55</v>
+        <v>1167.5</v>
       </c>
       <c r="F152" t="n">
         <v>1679</v>
@@ -23076,13 +23076,13 @@
         </is>
       </c>
       <c r="C153" t="n">
-        <v>1150.22</v>
+        <v>1150.17</v>
       </c>
       <c r="D153" t="n">
-        <v>1137.91</v>
+        <v>1137.86</v>
       </c>
       <c r="E153" t="n">
-        <v>1162.53</v>
+        <v>1162.47</v>
       </c>
       <c r="F153" t="n">
         <v>2572</v>
@@ -23227,13 +23227,13 @@
         </is>
       </c>
       <c r="C154" t="n">
-        <v>1149.76</v>
+        <v>1149.73</v>
       </c>
       <c r="D154" t="n">
-        <v>1143.11</v>
+        <v>1143.08</v>
       </c>
       <c r="E154" t="n">
-        <v>1156.42</v>
+        <v>1156.39</v>
       </c>
       <c r="F154" t="n">
         <v>19402</v>
@@ -23378,13 +23378,13 @@
         </is>
       </c>
       <c r="C155" t="n">
-        <v>1149.34</v>
+        <v>1149.29</v>
       </c>
       <c r="D155" t="n">
-        <v>1140.07</v>
+        <v>1140.03</v>
       </c>
       <c r="E155" t="n">
-        <v>1158.6</v>
+        <v>1158.56</v>
       </c>
       <c r="F155" t="n">
         <v>7044</v>
@@ -23529,13 +23529,13 @@
         </is>
       </c>
       <c r="C156" t="n">
-        <v>1147.15</v>
+        <v>1147.08</v>
       </c>
       <c r="D156" t="n">
-        <v>1130.01</v>
+        <v>1129.95</v>
       </c>
       <c r="E156" t="n">
-        <v>1164.29</v>
+        <v>1164.22</v>
       </c>
       <c r="F156" t="n">
         <v>1295</v>
@@ -23680,13 +23680,13 @@
         </is>
       </c>
       <c r="C157" t="n">
-        <v>1143.95</v>
+        <v>1143.92</v>
       </c>
       <c r="D157" t="n">
-        <v>1134.05</v>
+        <v>1134.02</v>
       </c>
       <c r="E157" t="n">
-        <v>1153.84</v>
+        <v>1153.82</v>
       </c>
       <c r="F157" t="n">
         <v>4737</v>
@@ -23831,13 +23831,13 @@
         </is>
       </c>
       <c r="C158" t="n">
-        <v>1143.25</v>
+        <v>1143.22</v>
       </c>
       <c r="D158" t="n">
-        <v>1136.82</v>
+        <v>1136.79</v>
       </c>
       <c r="E158" t="n">
-        <v>1149.68</v>
+        <v>1149.65</v>
       </c>
       <c r="F158" t="n">
         <v>12297</v>
@@ -23982,13 +23982,13 @@
         </is>
       </c>
       <c r="C159" t="n">
-        <v>1141.64</v>
+        <v>1141.62</v>
       </c>
       <c r="D159" t="n">
-        <v>1134.91</v>
+        <v>1134.89</v>
       </c>
       <c r="E159" t="n">
-        <v>1148.37</v>
+        <v>1148.35</v>
       </c>
       <c r="F159" t="n">
         <v>19174</v>
@@ -24133,13 +24133,13 @@
         </is>
       </c>
       <c r="C160" t="n">
-        <v>1141.04</v>
+        <v>1140.98</v>
       </c>
       <c r="D160" t="n">
-        <v>1134.32</v>
+        <v>1134.27</v>
       </c>
       <c r="E160" t="n">
-        <v>1147.76</v>
+        <v>1147.7</v>
       </c>
       <c r="F160" t="n">
         <v>19367</v>
@@ -24284,13 +24284,13 @@
         </is>
       </c>
       <c r="C161" t="n">
-        <v>1138.7</v>
+        <v>1138.64</v>
       </c>
       <c r="D161" t="n">
-        <v>1127.73</v>
+        <v>1127.67</v>
       </c>
       <c r="E161" t="n">
-        <v>1149.67</v>
+        <v>1149.61</v>
       </c>
       <c r="F161" t="n">
         <v>4964</v>
@@ -24435,13 +24435,13 @@
         </is>
       </c>
       <c r="C162" t="n">
-        <v>1136.7</v>
+        <v>1136.66</v>
       </c>
       <c r="D162" t="n">
-        <v>1127.79</v>
+        <v>1127.75</v>
       </c>
       <c r="E162" t="n">
-        <v>1145.6</v>
+        <v>1145.56</v>
       </c>
       <c r="F162" t="n">
         <v>7366</v>
@@ -24586,13 +24586,13 @@
         </is>
       </c>
       <c r="C163" t="n">
-        <v>1136.28</v>
+        <v>1136.24</v>
       </c>
       <c r="D163" t="n">
-        <v>1126.77</v>
+        <v>1126.73</v>
       </c>
       <c r="E163" t="n">
-        <v>1145.79</v>
+        <v>1145.75</v>
       </c>
       <c r="F163" t="n">
         <v>8925</v>
@@ -24737,13 +24737,13 @@
         </is>
       </c>
       <c r="C164" t="n">
-        <v>1131.19</v>
+        <v>1131.16</v>
       </c>
       <c r="D164" t="n">
-        <v>1122.34</v>
+        <v>1122.31</v>
       </c>
       <c r="E164" t="n">
-        <v>1140.04</v>
+        <v>1140.01</v>
       </c>
       <c r="F164" t="n">
         <v>11118</v>
@@ -24888,13 +24888,13 @@
         </is>
       </c>
       <c r="C165" t="n">
-        <v>1129.35</v>
+        <v>1129.3</v>
       </c>
       <c r="D165" t="n">
-        <v>1121.92</v>
+        <v>1121.88</v>
       </c>
       <c r="E165" t="n">
-        <v>1136.78</v>
+        <v>1136.73</v>
       </c>
       <c r="F165" t="n">
         <v>20685</v>
@@ -25039,13 +25039,13 @@
         </is>
       </c>
       <c r="C166" t="n">
-        <v>1128.57</v>
+        <v>1128.56</v>
       </c>
       <c r="D166" t="n">
-        <v>1122.18</v>
+        <v>1122.16</v>
       </c>
       <c r="E166" t="n">
-        <v>1134.97</v>
+        <v>1134.95</v>
       </c>
       <c r="F166" t="n">
         <v>20118</v>
@@ -25190,13 +25190,13 @@
         </is>
       </c>
       <c r="C167" t="n">
-        <v>1127.45</v>
+        <v>1127.4</v>
       </c>
       <c r="D167" t="n">
-        <v>1115.28</v>
+        <v>1115.24</v>
       </c>
       <c r="E167" t="n">
-        <v>1139.61</v>
+        <v>1139.56</v>
       </c>
       <c r="F167" t="n">
         <v>2921</v>
@@ -25341,13 +25341,13 @@
         </is>
       </c>
       <c r="C168" t="n">
-        <v>1127.04</v>
+        <v>1127.01</v>
       </c>
       <c r="D168" t="n">
-        <v>1111.36</v>
+        <v>1111.33</v>
       </c>
       <c r="E168" t="n">
-        <v>1142.73</v>
+        <v>1142.68</v>
       </c>
       <c r="F168" t="n">
         <v>1785</v>
@@ -25492,13 +25492,13 @@
         </is>
       </c>
       <c r="C169" t="n">
-        <v>1121.1</v>
+        <v>1121.05</v>
       </c>
       <c r="D169" t="n">
-        <v>1110.1</v>
+        <v>1110.05</v>
       </c>
       <c r="E169" t="n">
-        <v>1132.11</v>
+        <v>1132.05</v>
       </c>
       <c r="F169" t="n">
         <v>5182</v>
@@ -25643,13 +25643,13 @@
         </is>
       </c>
       <c r="C170" t="n">
-        <v>1119.19</v>
+        <v>1119.16</v>
       </c>
       <c r="D170" t="n">
-        <v>1100.97</v>
+        <v>1100.95</v>
       </c>
       <c r="E170" t="n">
-        <v>1137.41</v>
+        <v>1137.38</v>
       </c>
       <c r="F170" t="n">
         <v>1143</v>
@@ -25794,13 +25794,13 @@
         </is>
       </c>
       <c r="C171" t="n">
-        <v>1114.75</v>
+        <v>1114.7</v>
       </c>
       <c r="D171" t="n">
-        <v>1105.56</v>
+        <v>1105.51</v>
       </c>
       <c r="E171" t="n">
-        <v>1123.94</v>
+        <v>1123.88</v>
       </c>
       <c r="F171" t="n">
         <v>6923</v>
@@ -25945,13 +25945,13 @@
         </is>
       </c>
       <c r="C172" t="n">
-        <v>1114.48</v>
+        <v>1114.44</v>
       </c>
       <c r="D172" t="n">
-        <v>1100.06</v>
+        <v>1100.02</v>
       </c>
       <c r="E172" t="n">
-        <v>1128.9</v>
+        <v>1128.86</v>
       </c>
       <c r="F172" t="n">
         <v>2199</v>
@@ -26096,13 +26096,13 @@
         </is>
       </c>
       <c r="C173" t="n">
-        <v>1114.42</v>
+        <v>1114.37</v>
       </c>
       <c r="D173" t="n">
-        <v>1106.68</v>
+        <v>1106.63</v>
       </c>
       <c r="E173" t="n">
-        <v>1122.15</v>
+        <v>1122.1</v>
       </c>
       <c r="F173" t="n">
         <v>10854</v>
@@ -26247,13 +26247,13 @@
         </is>
       </c>
       <c r="C174" t="n">
-        <v>1111.46</v>
+        <v>1111.45</v>
       </c>
       <c r="D174" t="n">
-        <v>1103.59</v>
+        <v>1103.58</v>
       </c>
       <c r="E174" t="n">
-        <v>1119.34</v>
+        <v>1119.32</v>
       </c>
       <c r="F174" t="n">
         <v>8045</v>
@@ -26398,13 +26398,13 @@
         </is>
       </c>
       <c r="C175" t="n">
-        <v>1109.73</v>
+        <v>1109.67</v>
       </c>
       <c r="D175" t="n">
-        <v>1100.43</v>
+        <v>1100.37</v>
       </c>
       <c r="E175" t="n">
-        <v>1119.03</v>
+        <v>1118.97</v>
       </c>
       <c r="F175" t="n">
         <v>8977</v>
@@ -26549,13 +26549,13 @@
         </is>
       </c>
       <c r="C176" t="n">
-        <v>1108.3</v>
+        <v>1108.27</v>
       </c>
       <c r="D176" t="n">
-        <v>1101.24</v>
+        <v>1101.22</v>
       </c>
       <c r="E176" t="n">
-        <v>1115.35</v>
+        <v>1115.33</v>
       </c>
       <c r="F176" t="n">
         <v>14148</v>
@@ -26700,13 +26700,13 @@
         </is>
       </c>
       <c r="C177" t="n">
-        <v>1091.89</v>
+        <v>1091.84</v>
       </c>
       <c r="D177" t="n">
-        <v>1080.37</v>
+        <v>1080.32</v>
       </c>
       <c r="E177" t="n">
-        <v>1103.41</v>
+        <v>1103.36</v>
       </c>
       <c r="F177" t="n">
         <v>4780</v>
@@ -26851,13 +26851,13 @@
         </is>
       </c>
       <c r="C178" t="n">
-        <v>1090.29</v>
+        <v>1090.23</v>
       </c>
       <c r="D178" t="n">
-        <v>1080.94</v>
+        <v>1080.88</v>
       </c>
       <c r="E178" t="n">
-        <v>1099.65</v>
+        <v>1099.58</v>
       </c>
       <c r="F178" t="n">
         <v>7597</v>
@@ -27005,10 +27005,10 @@
         <v>1074.74</v>
       </c>
       <c r="D179" t="n">
-        <v>1063.55</v>
+        <v>1063.54</v>
       </c>
       <c r="E179" t="n">
-        <v>1085.94</v>
+        <v>1085.93</v>
       </c>
       <c r="F179" t="n">
         <v>6328</v>
@@ -27153,13 +27153,13 @@
         </is>
       </c>
       <c r="C180" t="n">
-        <v>1070.52</v>
+        <v>1070.47</v>
       </c>
       <c r="D180" t="n">
-        <v>1060.56</v>
+        <v>1060.51</v>
       </c>
       <c r="E180" t="n">
-        <v>1080.48</v>
+        <v>1080.42</v>
       </c>
       <c r="F180" t="n">
         <v>6965</v>
@@ -27304,13 +27304,13 @@
         </is>
       </c>
       <c r="C181" t="n">
-        <v>1067.49</v>
+        <v>1067.37</v>
       </c>
       <c r="D181" t="n">
-        <v>1055.95</v>
+        <v>1055.84</v>
       </c>
       <c r="E181" t="n">
-        <v>1079.02</v>
+        <v>1078.9</v>
       </c>
       <c r="F181" t="n">
         <v>5745</v>
@@ -27455,13 +27455,13 @@
         </is>
       </c>
       <c r="C182" t="n">
-        <v>1066.04</v>
+        <v>1065.96</v>
       </c>
       <c r="D182" t="n">
-        <v>1050.74</v>
+        <v>1050.66</v>
       </c>
       <c r="E182" t="n">
-        <v>1081.34</v>
+        <v>1081.25</v>
       </c>
       <c r="F182" t="n">
         <v>1743</v>
@@ -27606,13 +27606,13 @@
         </is>
       </c>
       <c r="C183" t="n">
-        <v>1061.89</v>
+        <v>1061.81</v>
       </c>
       <c r="D183" t="n">
-        <v>1049.85</v>
+        <v>1049.77</v>
       </c>
       <c r="E183" t="n">
-        <v>1073.93</v>
+        <v>1073.85</v>
       </c>
       <c r="F183" t="n">
         <v>3924</v>
@@ -27757,13 +27757,13 @@
         </is>
       </c>
       <c r="C184" t="n">
-        <v>1056.15</v>
+        <v>1056.1</v>
       </c>
       <c r="D184" t="n">
-        <v>1044.46</v>
+        <v>1044.41</v>
       </c>
       <c r="E184" t="n">
-        <v>1067.84</v>
+        <v>1067.79</v>
       </c>
       <c r="F184" t="n">
         <v>4658</v>
@@ -27908,13 +27908,13 @@
         </is>
       </c>
       <c r="C185" t="n">
-        <v>1041.39</v>
+        <v>1041.32</v>
       </c>
       <c r="D185" t="n">
-        <v>1029.93</v>
+        <v>1029.87</v>
       </c>
       <c r="E185" t="n">
-        <v>1052.85</v>
+        <v>1052.78</v>
       </c>
       <c r="F185" t="n">
         <v>4845</v>
@@ -28059,13 +28059,13 @@
         </is>
       </c>
       <c r="C186" t="n">
-        <v>1024.25</v>
+        <v>1024.2</v>
       </c>
       <c r="D186" t="n">
-        <v>1010.61</v>
+        <v>1010.56</v>
       </c>
       <c r="E186" t="n">
-        <v>1037.9</v>
+        <v>1037.84</v>
       </c>
       <c r="F186" t="n">
         <v>2658</v>
@@ -28210,13 +28210,13 @@
         </is>
       </c>
       <c r="C187" t="n">
-        <v>1022.13</v>
+        <v>1022.05</v>
       </c>
       <c r="D187" t="n">
-        <v>1011.19</v>
+        <v>1011.11</v>
       </c>
       <c r="E187" t="n">
-        <v>1033.07</v>
+        <v>1032.99</v>
       </c>
       <c r="F187" t="n">
         <v>6310</v>
@@ -28361,13 +28361,13 @@
         </is>
       </c>
       <c r="C188" t="n">
-        <v>995.668</v>
+        <v>995.624</v>
       </c>
       <c r="D188" t="n">
-        <v>983.032</v>
+        <v>982.992</v>
       </c>
       <c r="E188" t="n">
-        <v>1008.3</v>
+        <v>1008.26</v>
       </c>
       <c r="F188" t="n">
         <v>4914</v>
@@ -28512,13 +28512,13 @@
         </is>
       </c>
       <c r="C189" t="n">
-        <v>991.381</v>
+        <v>991.314</v>
       </c>
       <c r="D189" t="n">
-        <v>978.932</v>
+        <v>978.869</v>
       </c>
       <c r="E189" t="n">
-        <v>1003.83</v>
+        <v>1003.76</v>
       </c>
       <c r="F189" t="n">
         <v>4203</v>
@@ -28663,13 +28663,13 @@
         </is>
       </c>
       <c r="C190" t="n">
-        <v>980.138</v>
+        <v>980.034</v>
       </c>
       <c r="D190" t="n">
-        <v>966.51</v>
+        <v>966.412</v>
       </c>
       <c r="E190" t="n">
-        <v>993.7670000000001</v>
+        <v>993.657</v>
       </c>
       <c r="F190" t="n">
         <v>3412</v>
@@ -28814,13 +28814,13 @@
         </is>
       </c>
       <c r="C191" t="n">
-        <v>972.199</v>
+        <v>972.085</v>
       </c>
       <c r="D191" t="n">
-        <v>956.266</v>
+        <v>956.16</v>
       </c>
       <c r="E191" t="n">
-        <v>988.1319999999999</v>
+        <v>988.01</v>
       </c>
       <c r="F191" t="n">
         <v>2391</v>
@@ -28965,13 +28965,13 @@
         </is>
       </c>
       <c r="C192" t="n">
-        <v>952.686</v>
+        <v>952.633</v>
       </c>
       <c r="D192" t="n">
-        <v>939.853</v>
+        <v>939.806</v>
       </c>
       <c r="E192" t="n">
-        <v>965.519</v>
+        <v>965.46</v>
       </c>
       <c r="F192" t="n">
         <v>3287</v>
@@ -29260,7 +29260,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -29369,7 +29369,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -29474,7 +29474,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -29544,7 +29544,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -29579,7 +29579,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -29649,7 +29649,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -29965,14 +29965,14 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>deepseek-v3.2</t>
+          <t>qwen3-235b-a22b-instruct-2507</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>685</v>
+        <v>235</v>
       </c>
       <c r="C11" t="n">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -29988,14 +29988,14 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>qwen3-235b-a22b-instruct-2507</t>
+          <t>deepseek-v3.2</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>235</v>
+        <v>685</v>
       </c>
       <c r="C12" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -30057,14 +30057,14 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>qwen3.5-122b-a10b</t>
+          <t>deepseek-v3.1</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>125</v>
+        <v>685</v>
       </c>
       <c r="C15" t="n">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -30080,14 +30080,14 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>deepseek-v3.1</t>
+          <t>kimi-k2-0905-preview</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>685</v>
+        <v>1000</v>
       </c>
       <c r="C16" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -30096,21 +30096,21 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>artificial_analysis</t>
+          <t>override</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>kimi-k2-0905-preview</t>
+          <t>qwen3.5-122b-a10b</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1000</v>
+        <v>125</v>
       </c>
       <c r="C17" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -30119,21 +30119,21 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>artificial_analysis</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>deepseek-v3.1-thinking</t>
+          <t>mistral-large-3</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>685</v>
+        <v>675</v>
       </c>
       <c r="C18" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -30149,14 +30149,14 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>kimi-k2-0711-preview</t>
+          <t>deepseek-v3.1-thinking</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1000</v>
+        <v>685</v>
       </c>
       <c r="C19" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -30165,21 +30165,21 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>artificial_analysis</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>deepseek-v3.1-terminus</t>
+          <t>kimi-k2-0711-preview</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>685</v>
+        <v>1000</v>
       </c>
       <c r="C20" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -30188,21 +30188,21 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>artificial_analysis</t>
+          <t>override</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>mistral-large-3</t>
+          <t>deepseek-v3.1-terminus</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>675</v>
+        <v>685</v>
       </c>
       <c r="C21" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -30540,14 +30540,14 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>step-3.5-flash</t>
+          <t>mimo-v2-flash (thinking)</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>196</v>
+        <v>309</v>
       </c>
       <c r="C36" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -30563,14 +30563,14 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>qwen3-coder-480b-a35b-instruct</t>
+          <t>step-3.5-flash</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>480</v>
+        <v>196</v>
       </c>
       <c r="C37" t="n">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -30586,14 +30586,14 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>mimo-v2-flash (thinking)</t>
+          <t>qwen3-coder-480b-a35b-instruct</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>309</v>
+        <v>480</v>
       </c>
       <c r="C38" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -30678,46 +30678,46 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>qwen3-235b-a22b</t>
+          <t>trinity-large</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>235</v>
+        <v>70</v>
       </c>
       <c r="C42" t="n">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>moe</t>
+          <t>dense</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>artificial_analysis</t>
+          <t>override</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>trinity-large</t>
+          <t>qwen3-235b-a22b</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>70</v>
+        <v>235</v>
       </c>
       <c r="C43" t="n">
-        <v>70</v>
+        <v>22</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>dense</t>
+          <t>moe</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>artificial_analysis</t>
         </is>
       </c>
     </row>
@@ -31812,14 +31812,14 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>ibm-granite-h-small</t>
+          <t>llama-3.1-tulu-3-70b</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="C92" t="n">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -31828,21 +31828,21 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>name_parsing</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>llama-3.1-tulu-3-70b</t>
+          <t>ibm-granite-h-small</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="C93" t="n">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -31851,7 +31851,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>override</t>
         </is>
       </c>
     </row>

--- a/arena_enrichment/output/arena_leaderboard_enriched.xlsx
+++ b/arena_enrichment/output/arena_leaderboard_enriched.xlsx
@@ -675,16 +675,16 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>1453.49</v>
+        <v>1456.58</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1447.25</v>
+        <v>1450.55</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1459.74</v>
+        <v>1462.6</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>10020</v>
+        <v>10991</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
@@ -826,16 +826,16 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>1452.54</v>
+        <v>1453.11</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1447.11</v>
+        <v>1447.83</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1457.96</v>
+        <v>1458.39</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>15234</v>
+        <v>16231</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
@@ -977,16 +977,16 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>1451.5</v>
+        <v>1451.6</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1445.12</v>
+        <v>1445.43</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1457.89</v>
+        <v>1457.76</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>9337</v>
+        <v>10225</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
@@ -1128,16 +1128,16 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>1441.41</v>
+        <v>1442.31</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1435.23</v>
+        <v>1436.22</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1447.59</v>
+        <v>1448.39</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>11891</v>
+        <v>12421</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
@@ -1279,16 +1279,16 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1439.99</v>
+        <v>1432.45</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1434.23</v>
+        <v>1425.9</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1445.75</v>
+        <v>1439.01</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>11375</v>
+        <v>8472</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
@@ -1430,16 +1430,16 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>1430.06</v>
+        <v>1429.8</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>1426.29</v>
+        <v>1426.11</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1433.83</v>
+        <v>1433.49</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>39914</v>
+        <v>41979</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
@@ -1581,16 +1581,16 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>1426.03</v>
+        <v>1425.97</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>1422.04</v>
+        <v>1422.03</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1430.02</v>
+        <v>1429.9</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>35013</v>
+        <v>36415</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
@@ -1732,16 +1732,16 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>1424.28</v>
+        <v>1424.82</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1417.69</v>
+        <v>1418.3</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1430.88</v>
+        <v>1431.34</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>8922</v>
+        <v>9201</v>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
@@ -1879,20 +1879,20 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>deepseek-v3.2-exp</t>
+          <t>deepseek-v3.2</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>1424</v>
+        <v>1424.04</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>1417.52</v>
+        <v>1419.98</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1430.49</v>
+        <v>1428.09</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>11649</v>
+        <v>36698</v>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
@@ -2030,36 +2030,36 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>qwen3-235b-a22b-instruct-2507</t>
+          <t>deepseek-v3.2-exp</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>1422.82</v>
+        <v>1423.54</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>1419.88</v>
+        <v>1417.15</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1425.75</v>
+        <v>1429.94</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>75677</v>
+        <v>12186</v>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Alibaba</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>235</v>
+        <v>685</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
@@ -2072,22 +2072,22 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>470</v>
+        <v>1370</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>587.5</v>
+        <v>1712.5</v>
       </c>
       <c r="O11" s="2" t="n">
-        <v>235</v>
+        <v>685</v>
       </c>
       <c r="P11" s="2" t="n">
-        <v>293.8</v>
+        <v>856.2</v>
       </c>
       <c r="Q11" s="2" t="n">
-        <v>117.5</v>
+        <v>342.5</v>
       </c>
       <c r="R11" s="2" t="n">
-        <v>146.9</v>
+        <v>428.1</v>
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
@@ -2144,9 +2144,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AD11" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AD11" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AE11" s="3" t="inlineStr">
@@ -2159,9 +2159,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AG11" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AG11" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AH11" s="2" t="inlineStr">
@@ -2181,36 +2181,36 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>deepseek-v3.2</t>
+          <t>qwen3-235b-a22b-instruct-2507</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1422.28</v>
+        <v>1422.03</v>
       </c>
       <c r="D12" t="n">
-        <v>1418.15</v>
+        <v>1419.14</v>
       </c>
       <c r="E12" t="n">
-        <v>1426.41</v>
+        <v>1424.92</v>
       </c>
       <c r="F12" t="n">
-        <v>35098</v>
+        <v>77979</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>DeepSeek</t>
+          <t>Alibaba</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Apache 2.0</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>685</v>
+        <v>235</v>
       </c>
       <c r="J12" t="n">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -2223,22 +2223,22 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>1370</v>
+        <v>470</v>
       </c>
       <c r="N12" t="n">
-        <v>1712.5</v>
+        <v>587.5</v>
       </c>
       <c r="O12" t="n">
-        <v>685</v>
+        <v>235</v>
       </c>
       <c r="P12" t="n">
-        <v>856.2</v>
+        <v>293.8</v>
       </c>
       <c r="Q12" t="n">
-        <v>342.5</v>
+        <v>117.5</v>
       </c>
       <c r="R12" t="n">
-        <v>428.1</v>
+        <v>146.9</v>
       </c>
       <c r="S12" s="5" t="inlineStr">
         <is>
@@ -2295,9 +2295,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AD12" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AD12" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AE12" s="5" t="inlineStr">
@@ -2310,9 +2310,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AG12" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AG12" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
@@ -2336,16 +2336,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1420.63</v>
+        <v>1421.63</v>
       </c>
       <c r="D13" t="n">
-        <v>1416.4</v>
+        <v>1417.47</v>
       </c>
       <c r="E13" t="n">
-        <v>1424.86</v>
+        <v>1425.79</v>
       </c>
       <c r="F13" t="n">
-        <v>29743</v>
+        <v>31230</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -2487,16 +2487,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1420.23</v>
+        <v>1420.87</v>
       </c>
       <c r="D14" t="n">
-        <v>1414.62</v>
+        <v>1415.25</v>
       </c>
       <c r="E14" t="n">
-        <v>1425.84</v>
+        <v>1426.49</v>
       </c>
       <c r="F14" t="n">
-        <v>19107</v>
+        <v>18855</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -2634,36 +2634,36 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>deepseek-v3.1</t>
+          <t>qwen3.5-122b-a10b</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1418.69</v>
+        <v>1417.96</v>
       </c>
       <c r="D15" t="n">
-        <v>1412.69</v>
+        <v>1410.68</v>
       </c>
       <c r="E15" t="n">
-        <v>1424.69</v>
+        <v>1425.25</v>
       </c>
       <c r="F15" t="n">
-        <v>15170</v>
+        <v>6630</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>DeepSeek</t>
+          <t>Alibaba</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Apache 2.0</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>685</v>
+        <v>125</v>
       </c>
       <c r="J15" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -2676,22 +2676,22 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>1370</v>
+        <v>250</v>
       </c>
       <c r="N15" t="n">
-        <v>1712.5</v>
+        <v>312.5</v>
       </c>
       <c r="O15" t="n">
-        <v>685</v>
+        <v>125</v>
       </c>
       <c r="P15" t="n">
-        <v>856.2</v>
+        <v>156.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>342.5</v>
+        <v>62.5</v>
       </c>
       <c r="R15" t="n">
-        <v>428.1</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="S15" s="5" t="inlineStr">
         <is>
@@ -2703,9 +2703,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="U15" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="U15" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="V15" s="5" t="inlineStr">
@@ -2718,9 +2718,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="X15" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="X15" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Y15" s="5" t="inlineStr">
@@ -2733,9 +2733,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AA15" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AA15" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AB15" s="5" t="inlineStr">
@@ -2743,14 +2743,14 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AC15" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AD15" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AC15" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AD15" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AE15" s="5" t="inlineStr">
@@ -2758,14 +2758,14 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AF15" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AG15" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AF15" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AG15" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
@@ -2775,7 +2775,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>B200 SXM</t>
         </is>
       </c>
     </row>
@@ -2785,36 +2785,36 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>kimi-k2-0905-preview</t>
+          <t>deepseek-v3.1</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1418.48</v>
+        <v>1417.96</v>
       </c>
       <c r="D16" t="n">
-        <v>1411.99</v>
+        <v>1411.97</v>
       </c>
       <c r="E16" t="n">
-        <v>1424.97</v>
+        <v>1423.95</v>
       </c>
       <c r="F16" t="n">
-        <v>11875</v>
+        <v>15170</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Moonshot</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Modified MIT</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1000</v>
+        <v>685</v>
       </c>
       <c r="J16" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -2823,26 +2823,26 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>artificial_analysis</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>2000</v>
+        <v>1370</v>
       </c>
       <c r="N16" t="n">
-        <v>2500</v>
+        <v>1712.5</v>
       </c>
       <c r="O16" t="n">
-        <v>1000</v>
+        <v>685</v>
       </c>
       <c r="P16" t="n">
-        <v>1250</v>
+        <v>856.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>500</v>
+        <v>342.5</v>
       </c>
       <c r="R16" t="n">
-        <v>625</v>
+        <v>428.1</v>
       </c>
       <c r="S16" s="5" t="inlineStr">
         <is>
@@ -2936,36 +2936,36 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>qwen3.5-122b-a10b</t>
+          <t>kimi-k2-0905-preview</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1417.83</v>
+        <v>1417.4</v>
       </c>
       <c r="D17" t="n">
-        <v>1410.11</v>
+        <v>1410.93</v>
       </c>
       <c r="E17" t="n">
-        <v>1425.56</v>
+        <v>1423.87</v>
       </c>
       <c r="F17" t="n">
-        <v>5844</v>
+        <v>11954</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alibaba</t>
+          <t>Moonshot</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
+          <t>Modified MIT</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>125</v>
+        <v>1000</v>
       </c>
       <c r="J17" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -2974,26 +2974,26 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>artificial_analysis</t>
+          <t>override</t>
         </is>
       </c>
       <c r="M17" t="n">
-        <v>250</v>
+        <v>2000</v>
       </c>
       <c r="N17" t="n">
-        <v>312.5</v>
+        <v>2500</v>
       </c>
       <c r="O17" t="n">
-        <v>125</v>
+        <v>1000</v>
       </c>
       <c r="P17" t="n">
-        <v>156.2</v>
+        <v>1250</v>
       </c>
       <c r="Q17" t="n">
-        <v>62.5</v>
+        <v>500</v>
       </c>
       <c r="R17" t="n">
-        <v>78.09999999999999</v>
+        <v>625</v>
       </c>
       <c r="S17" s="5" t="inlineStr">
         <is>
@@ -3005,9 +3005,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="U17" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="U17" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="V17" s="5" t="inlineStr">
@@ -3020,9 +3020,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="X17" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="X17" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="Y17" s="5" t="inlineStr">
@@ -3035,9 +3035,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AA17" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AA17" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AB17" s="5" t="inlineStr">
@@ -3045,14 +3045,14 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AC17" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AD17" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AC17" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD17" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AE17" s="5" t="inlineStr">
@@ -3060,14 +3060,14 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AF17" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AG17" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AF17" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AG17" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>B200 SXM</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
     </row>
@@ -3087,36 +3087,36 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>mistral-large-3</t>
+          <t>kimi-k2-0711-preview</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1417.26</v>
+        <v>1416.95</v>
       </c>
       <c r="D18" t="n">
-        <v>1413.15</v>
+        <v>1412.12</v>
       </c>
       <c r="E18" t="n">
-        <v>1421.37</v>
+        <v>1421.78</v>
       </c>
       <c r="F18" t="n">
-        <v>31701</v>
+        <v>28137</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Mistral</t>
+          <t>Moonshot</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
+          <t>Modified MIT</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>675</v>
+        <v>1000</v>
       </c>
       <c r="J18" t="n">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -3125,26 +3125,26 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>artificial_analysis</t>
+          <t>override</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>1350</v>
+        <v>2000</v>
       </c>
       <c r="N18" t="n">
-        <v>1687.5</v>
+        <v>2500</v>
       </c>
       <c r="O18" t="n">
-        <v>675</v>
+        <v>1000</v>
       </c>
       <c r="P18" t="n">
-        <v>843.8</v>
+        <v>1250</v>
       </c>
       <c r="Q18" t="n">
-        <v>337.5</v>
+        <v>500</v>
       </c>
       <c r="R18" t="n">
-        <v>421.9</v>
+        <v>625</v>
       </c>
       <c r="S18" s="5" t="inlineStr">
         <is>
@@ -3242,16 +3242,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1417.23</v>
+        <v>1416.82</v>
       </c>
       <c r="D19" t="n">
-        <v>1410.65</v>
+        <v>1410.24</v>
       </c>
       <c r="E19" t="n">
-        <v>1423.82</v>
+        <v>1423.4</v>
       </c>
       <c r="F19" t="n">
-        <v>11912</v>
+        <v>11903</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -3389,36 +3389,36 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>kimi-k2-0711-preview</t>
+          <t>mistral-large-3</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1417.07</v>
+        <v>1416.54</v>
       </c>
       <c r="D20" t="n">
-        <v>1412.25</v>
+        <v>1412.52</v>
       </c>
       <c r="E20" t="n">
-        <v>1421.88</v>
+        <v>1420.56</v>
       </c>
       <c r="F20" t="n">
-        <v>28373</v>
+        <v>33352</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Moonshot</t>
+          <t>Mistral</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Modified MIT</t>
+          <t>Apache 2.0</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1000</v>
+        <v>675</v>
       </c>
       <c r="J20" t="n">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -3427,26 +3427,26 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>artificial_analysis</t>
         </is>
       </c>
       <c r="M20" t="n">
-        <v>2000</v>
+        <v>1350</v>
       </c>
       <c r="N20" t="n">
-        <v>2500</v>
+        <v>1687.5</v>
       </c>
       <c r="O20" t="n">
-        <v>1000</v>
+        <v>675</v>
       </c>
       <c r="P20" t="n">
-        <v>1250</v>
+        <v>843.8</v>
       </c>
       <c r="Q20" t="n">
-        <v>500</v>
+        <v>337.5</v>
       </c>
       <c r="R20" t="n">
-        <v>625</v>
+        <v>421.9</v>
       </c>
       <c r="S20" s="5" t="inlineStr">
         <is>
@@ -3540,20 +3540,20 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>deepseek-v3.1-terminus</t>
+          <t>deepseek-v3.1-terminus-thinking</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1416.6</v>
+        <v>1416.26</v>
       </c>
       <c r="D21" t="n">
-        <v>1407.02</v>
+        <v>1406.34</v>
       </c>
       <c r="E21" t="n">
         <v>1426.18</v>
       </c>
       <c r="F21" t="n">
-        <v>3732</v>
+        <v>3508</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -3691,36 +3691,36 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>qwen3-vl-235b-a22b-instruct</t>
+          <t>deepseek-v3.1-terminus</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1416</v>
+        <v>1415.44</v>
       </c>
       <c r="D22" t="n">
-        <v>1409.51</v>
+        <v>1405.86</v>
       </c>
       <c r="E22" t="n">
-        <v>1422.49</v>
+        <v>1425.01</v>
       </c>
       <c r="F22" t="n">
-        <v>11553</v>
+        <v>3744</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alibaba</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>235</v>
+        <v>685</v>
       </c>
       <c r="J22" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -3733,22 +3733,22 @@
         </is>
       </c>
       <c r="M22" t="n">
-        <v>470</v>
+        <v>1370</v>
       </c>
       <c r="N22" t="n">
-        <v>587.5</v>
+        <v>1712.5</v>
       </c>
       <c r="O22" t="n">
-        <v>235</v>
+        <v>685</v>
       </c>
       <c r="P22" t="n">
-        <v>293.8</v>
+        <v>856.2</v>
       </c>
       <c r="Q22" t="n">
-        <v>117.5</v>
+        <v>342.5</v>
       </c>
       <c r="R22" t="n">
-        <v>146.9</v>
+        <v>428.1</v>
       </c>
       <c r="S22" s="5" t="inlineStr">
         <is>
@@ -3805,9 +3805,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AD22" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AD22" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AE22" s="5" t="inlineStr">
@@ -3820,9 +3820,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AG22" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AG22" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
@@ -3842,36 +3842,36 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>deepseek-v3.1-terminus-thinking</t>
+          <t>qwen3-vl-235b-a22b-instruct</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1415.47</v>
+        <v>1415.31</v>
       </c>
       <c r="D23" t="n">
-        <v>1405.56</v>
+        <v>1408.87</v>
       </c>
       <c r="E23" t="n">
-        <v>1425.38</v>
+        <v>1421.76</v>
       </c>
       <c r="F23" t="n">
-        <v>3507</v>
+        <v>11714</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>DeepSeek</t>
+          <t>Alibaba</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Apache 2.0</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>685</v>
+        <v>235</v>
       </c>
       <c r="J23" t="n">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -3884,22 +3884,22 @@
         </is>
       </c>
       <c r="M23" t="n">
-        <v>1370</v>
+        <v>470</v>
       </c>
       <c r="N23" t="n">
-        <v>1712.5</v>
+        <v>587.5</v>
       </c>
       <c r="O23" t="n">
-        <v>685</v>
+        <v>235</v>
       </c>
       <c r="P23" t="n">
-        <v>856.2</v>
+        <v>293.8</v>
       </c>
       <c r="Q23" t="n">
-        <v>342.5</v>
+        <v>117.5</v>
       </c>
       <c r="R23" t="n">
-        <v>428.1</v>
+        <v>146.9</v>
       </c>
       <c r="S23" s="5" t="inlineStr">
         <is>
@@ -3956,9 +3956,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AD23" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AD23" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AE23" s="5" t="inlineStr">
@@ -3971,9 +3971,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AG23" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AG23" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
@@ -3997,16 +3997,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1410.56</v>
+        <v>1410.72</v>
       </c>
       <c r="D24" t="n">
-        <v>1405.68</v>
+        <v>1405.86</v>
       </c>
       <c r="E24" t="n">
-        <v>1415.44</v>
+        <v>1415.57</v>
       </c>
       <c r="F24" t="n">
-        <v>24543</v>
+        <v>24669</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -4148,16 +4148,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1408.03</v>
+        <v>1406.56</v>
       </c>
       <c r="D25" t="n">
-        <v>1400.43</v>
+        <v>1399.32</v>
       </c>
       <c r="E25" t="n">
-        <v>1415.64</v>
+        <v>1413.79</v>
       </c>
       <c r="F25" t="n">
-        <v>5989</v>
+        <v>6731</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -4299,16 +4299,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1405.49</v>
+        <v>1405.13</v>
       </c>
       <c r="D26" t="n">
-        <v>1399.35</v>
+        <v>1399.21</v>
       </c>
       <c r="E26" t="n">
-        <v>1411.64</v>
+        <v>1411.04</v>
       </c>
       <c r="F26" t="n">
-        <v>10646</v>
+        <v>11697</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -4450,16 +4450,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1402.7</v>
+        <v>1402.46</v>
       </c>
       <c r="D27" t="n">
-        <v>1398.23</v>
+        <v>1397.98</v>
       </c>
       <c r="E27" t="n">
-        <v>1407.18</v>
+        <v>1406.94</v>
       </c>
       <c r="F27" t="n">
-        <v>39188</v>
+        <v>38861</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -4601,16 +4601,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1402.49</v>
+        <v>1401.27</v>
       </c>
       <c r="D28" t="n">
-        <v>1397.67</v>
+        <v>1396.52</v>
       </c>
       <c r="E28" t="n">
-        <v>1407.31</v>
+        <v>1406.03</v>
       </c>
       <c r="F28" t="n">
-        <v>22600</v>
+        <v>23252</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -4752,16 +4752,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1401.08</v>
+        <v>1400.52</v>
       </c>
       <c r="D29" t="n">
-        <v>1394.71</v>
+        <v>1394.17</v>
       </c>
       <c r="E29" t="n">
-        <v>1407.45</v>
+        <v>1406.88</v>
       </c>
       <c r="F29" t="n">
-        <v>11436</v>
+        <v>11535</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -4903,16 +4903,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1399.58</v>
+        <v>1399.05</v>
       </c>
       <c r="D30" t="n">
-        <v>1393.1</v>
+        <v>1392.55</v>
       </c>
       <c r="E30" t="n">
-        <v>1406.07</v>
+        <v>1405.55</v>
       </c>
       <c r="F30" t="n">
-        <v>9170</v>
+        <v>9137</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -5050,36 +5050,36 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>deepseek-r1</t>
+          <t>qwen3.5-35b-a3b</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1398.2</v>
+        <v>1398.94</v>
       </c>
       <c r="D31" t="n">
-        <v>1393.35</v>
+        <v>1391.78</v>
       </c>
       <c r="E31" t="n">
-        <v>1403.06</v>
+        <v>1406.1</v>
       </c>
       <c r="F31" t="n">
-        <v>18524</v>
+        <v>6983</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>DeepSeek</t>
+          <t>Alibaba</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Apache 2.0</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>685</v>
+        <v>36</v>
       </c>
       <c r="J31" t="n">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -5092,36 +5092,36 @@
         </is>
       </c>
       <c r="M31" t="n">
-        <v>1370</v>
+        <v>72</v>
       </c>
       <c r="N31" t="n">
-        <v>1712.5</v>
+        <v>90</v>
       </c>
       <c r="O31" t="n">
-        <v>685</v>
+        <v>36</v>
       </c>
       <c r="P31" t="n">
-        <v>856.2</v>
+        <v>45</v>
       </c>
       <c r="Q31" t="n">
-        <v>342.5</v>
+        <v>18</v>
       </c>
       <c r="R31" t="n">
-        <v>428.1</v>
-      </c>
-      <c r="S31" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T31" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U31" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+        <v>22.5</v>
+      </c>
+      <c r="S31" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T31" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U31" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="V31" s="5" t="inlineStr">
@@ -5129,69 +5129,69 @@
           <t>No</t>
         </is>
       </c>
-      <c r="W31" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X31" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Y31" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z31" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AA31" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AB31" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AC31" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AD31" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AE31" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AF31" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AG31" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="W31" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X31" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y31" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z31" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AA31" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB31" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AC31" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AD31" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE31" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AF31" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AG31" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>RTX PRO 6000</t>
         </is>
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>H100 SXM</t>
         </is>
       </c>
     </row>
@@ -5201,36 +5201,36 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>qwen3.5-35b-a3b</t>
+          <t>deepseek-r1</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1397.78</v>
+        <v>1397.55</v>
       </c>
       <c r="D32" t="n">
-        <v>1390.24</v>
+        <v>1392.69</v>
       </c>
       <c r="E32" t="n">
-        <v>1405.32</v>
+        <v>1402.4</v>
       </c>
       <c r="F32" t="n">
-        <v>6209</v>
+        <v>18524</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alibaba</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>36</v>
+        <v>685</v>
       </c>
       <c r="J32" t="n">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -5243,36 +5243,36 @@
         </is>
       </c>
       <c r="M32" t="n">
-        <v>72</v>
+        <v>1370</v>
       </c>
       <c r="N32" t="n">
-        <v>90</v>
+        <v>1712.5</v>
       </c>
       <c r="O32" t="n">
-        <v>36</v>
+        <v>685</v>
       </c>
       <c r="P32" t="n">
-        <v>45</v>
+        <v>856.2</v>
       </c>
       <c r="Q32" t="n">
-        <v>18</v>
+        <v>342.5</v>
       </c>
       <c r="R32" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="S32" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="T32" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="U32" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+        <v>428.1</v>
+      </c>
+      <c r="S32" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T32" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U32" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="V32" s="5" t="inlineStr">
@@ -5280,69 +5280,69 @@
           <t>No</t>
         </is>
       </c>
-      <c r="W32" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X32" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Y32" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z32" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AA32" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB32" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AC32" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AD32" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AE32" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AF32" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AG32" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="W32" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X32" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y32" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z32" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA32" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AB32" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AC32" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD32" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE32" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF32" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AG32" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>RTX PRO 6000</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
     </row>
@@ -5356,16 +5356,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1396.31</v>
+        <v>1395.52</v>
       </c>
       <c r="D33" t="n">
-        <v>1389.49</v>
+        <v>1388.77</v>
       </c>
       <c r="E33" t="n">
-        <v>1403.12</v>
+        <v>1402.27</v>
       </c>
       <c r="F33" t="n">
-        <v>7890</v>
+        <v>8081</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -5507,16 +5507,16 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1394.89</v>
+        <v>1394.33</v>
       </c>
       <c r="D34" t="n">
-        <v>1391.04</v>
+        <v>1390.48</v>
       </c>
       <c r="E34" t="n">
-        <v>1398.74</v>
+        <v>1398.17</v>
       </c>
       <c r="F34" t="n">
-        <v>46347</v>
+        <v>46197</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -5658,16 +5658,16 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1392.6</v>
+        <v>1391.94</v>
       </c>
       <c r="D35" t="n">
-        <v>1388.1</v>
+        <v>1387.54</v>
       </c>
       <c r="E35" t="n">
-        <v>1397.09</v>
+        <v>1396.35</v>
       </c>
       <c r="F35" t="n">
-        <v>24140</v>
+        <v>25505</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -5809,16 +5809,16 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1387.58</v>
+        <v>1387.77</v>
       </c>
       <c r="D36" t="n">
-        <v>1381.25</v>
+        <v>1381.52</v>
       </c>
       <c r="E36" t="n">
-        <v>1393.91</v>
+        <v>1394.02</v>
       </c>
       <c r="F36" t="n">
-        <v>10857</v>
+        <v>11256</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -5960,16 +5960,16 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1387.44</v>
+        <v>1387.19</v>
       </c>
       <c r="D37" t="n">
-        <v>1381.75</v>
+        <v>1381.68</v>
       </c>
       <c r="E37" t="n">
-        <v>1393.12</v>
+        <v>1392.7</v>
       </c>
       <c r="F37" t="n">
-        <v>12872</v>
+        <v>13845</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -6111,16 +6111,16 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1387.23</v>
+        <v>1386.89</v>
       </c>
       <c r="D38" t="n">
-        <v>1382.33</v>
+        <v>1381.98</v>
       </c>
       <c r="E38" t="n">
-        <v>1392.13</v>
+        <v>1391.8</v>
       </c>
       <c r="F38" t="n">
-        <v>26337</v>
+        <v>26234</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -6262,16 +6262,16 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1386.15</v>
+        <v>1385.85</v>
       </c>
       <c r="D39" t="n">
-        <v>1380.84</v>
+        <v>1380.62</v>
       </c>
       <c r="E39" t="n">
-        <v>1391.45</v>
+        <v>1391.09</v>
       </c>
       <c r="F39" t="n">
-        <v>17024</v>
+        <v>17581</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -6413,16 +6413,16 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1384.2</v>
+        <v>1382.93</v>
       </c>
       <c r="D40" t="n">
-        <v>1379.33</v>
+        <v>1378.09</v>
       </c>
       <c r="E40" t="n">
-        <v>1389.07</v>
+        <v>1387.78</v>
       </c>
       <c r="F40" t="n">
-        <v>23938</v>
+        <v>24134</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -6564,16 +6564,16 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1378.38</v>
+        <v>1377.9</v>
       </c>
       <c r="D41" t="n">
-        <v>1367.07</v>
+        <v>1366.7</v>
       </c>
       <c r="E41" t="n">
-        <v>1389.68</v>
+        <v>1389.1</v>
       </c>
       <c r="F41" t="n">
-        <v>2773</v>
+        <v>2861</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -6715,16 +6715,16 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1376.84</v>
+        <v>1375.51</v>
       </c>
       <c r="D42" t="n">
-        <v>1369.44</v>
+        <v>1368.46</v>
       </c>
       <c r="E42" t="n">
-        <v>1384.24</v>
+        <v>1382.56</v>
       </c>
       <c r="F42" t="n">
-        <v>6974</v>
+        <v>7749</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -6866,16 +6866,16 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1375.24</v>
+        <v>1374.53</v>
       </c>
       <c r="D43" t="n">
-        <v>1370.57</v>
+        <v>1369.86</v>
       </c>
       <c r="E43" t="n">
-        <v>1379.91</v>
+        <v>1379.2</v>
       </c>
       <c r="F43" t="n">
-        <v>26961</v>
+        <v>26703</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -7017,16 +7017,16 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1372.56</v>
+        <v>1372.36</v>
       </c>
       <c r="D44" t="n">
-        <v>1368.29</v>
+        <v>1368.13</v>
       </c>
       <c r="E44" t="n">
-        <v>1376.83</v>
+        <v>1376.59</v>
       </c>
       <c r="F44" t="n">
-        <v>31057</v>
+        <v>31597</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -7168,16 +7168,16 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1369.01</v>
+        <v>1368.76</v>
       </c>
       <c r="D45" t="n">
-        <v>1363.17</v>
+        <v>1362.96</v>
       </c>
       <c r="E45" t="n">
-        <v>1374.86</v>
+        <v>1374.57</v>
       </c>
       <c r="F45" t="n">
-        <v>13702</v>
+        <v>13940</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -7319,16 +7319,16 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1368.32</v>
+        <v>1368.33</v>
       </c>
       <c r="D46" t="n">
-        <v>1362.46</v>
+        <v>1362.54</v>
       </c>
       <c r="E46" t="n">
-        <v>1374.19</v>
+        <v>1374.12</v>
       </c>
       <c r="F46" t="n">
-        <v>11748</v>
+        <v>12110</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -7466,40 +7466,40 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>minimax-m1</t>
+          <t>gemma-3-27b-it</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1367.05</v>
+        <v>1365.29</v>
       </c>
       <c r="D47" t="n">
-        <v>1362.79</v>
+        <v>1361.64</v>
       </c>
       <c r="E47" t="n">
-        <v>1371.31</v>
+        <v>1368.94</v>
       </c>
       <c r="F47" t="n">
-        <v>36287</v>
+        <v>48251</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>MiniMax</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
+          <t>Gemma</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>456</v>
+        <v>27.4</v>
       </c>
       <c r="J47" t="n">
-        <v>45.9</v>
+        <v>27.4</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>moe</t>
+          <t>dense</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -7508,91 +7508,91 @@
         </is>
       </c>
       <c r="M47" t="n">
-        <v>912</v>
+        <v>54.8</v>
       </c>
       <c r="N47" t="n">
-        <v>1140</v>
+        <v>68.5</v>
       </c>
       <c r="O47" t="n">
-        <v>456</v>
+        <v>27.4</v>
       </c>
       <c r="P47" t="n">
-        <v>570</v>
+        <v>34.2</v>
       </c>
       <c r="Q47" t="n">
-        <v>228</v>
+        <v>13.7</v>
       </c>
       <c r="R47" t="n">
-        <v>285</v>
-      </c>
-      <c r="S47" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T47" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U47" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="V47" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W47" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X47" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Y47" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z47" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AA47" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AB47" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AC47" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AD47" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AE47" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AF47" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+        <v>17.1</v>
+      </c>
+      <c r="S47" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T47" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U47" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V47" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W47" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X47" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y47" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z47" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AA47" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB47" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AC47" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AD47" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE47" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AF47" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AG47" s="6" t="inlineStr">
@@ -7602,12 +7602,12 @@
       </c>
       <c r="AH47" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>H100 SXM</t>
         </is>
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>H100 SXM</t>
         </is>
       </c>
     </row>
@@ -7617,40 +7617,40 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>gemma-3-27b-it</t>
+          <t>minimax-m1</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1365.66</v>
+        <v>1364.92</v>
       </c>
       <c r="D48" t="n">
-        <v>1362</v>
+        <v>1360.68</v>
       </c>
       <c r="E48" t="n">
-        <v>1369.31</v>
+        <v>1369.16</v>
       </c>
       <c r="F48" t="n">
-        <v>48375</v>
+        <v>36105</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>MiniMax</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Gemma</t>
+          <t>Apache 2.0</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>27.4</v>
+        <v>456</v>
       </c>
       <c r="J48" t="n">
-        <v>27.4</v>
+        <v>45.9</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>dense</t>
+          <t>moe</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -7659,91 +7659,91 @@
         </is>
       </c>
       <c r="M48" t="n">
-        <v>54.8</v>
+        <v>912</v>
       </c>
       <c r="N48" t="n">
-        <v>68.5</v>
+        <v>1140</v>
       </c>
       <c r="O48" t="n">
-        <v>27.4</v>
+        <v>456</v>
       </c>
       <c r="P48" t="n">
-        <v>34.2</v>
+        <v>570</v>
       </c>
       <c r="Q48" t="n">
-        <v>13.7</v>
+        <v>228</v>
       </c>
       <c r="R48" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="S48" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="T48" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="U48" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="V48" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W48" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X48" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Y48" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z48" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AA48" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB48" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AC48" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AD48" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AE48" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AF48" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+        <v>285</v>
+      </c>
+      <c r="S48" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T48" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U48" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V48" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W48" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X48" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y48" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z48" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA48" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AB48" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AC48" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD48" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE48" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF48" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AG48" s="6" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="AH48" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
     </row>
@@ -7772,16 +7772,16 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1364.44</v>
+        <v>1364.66</v>
       </c>
       <c r="D49" t="n">
-        <v>1354.7</v>
+        <v>1355.08</v>
       </c>
       <c r="E49" t="n">
-        <v>1374.18</v>
+        <v>1374.24</v>
       </c>
       <c r="F49" t="n">
-        <v>3581</v>
+        <v>3711</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -7923,13 +7923,13 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1358.99</v>
+        <v>1358.24</v>
       </c>
       <c r="D50" t="n">
-        <v>1354.28</v>
+        <v>1353.53</v>
       </c>
       <c r="E50" t="n">
-        <v>1363.7</v>
+        <v>1362.95</v>
       </c>
       <c r="F50" t="n">
         <v>21770</v>
@@ -8074,16 +8074,16 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1356.95</v>
+        <v>1357.02</v>
       </c>
       <c r="D51" t="n">
-        <v>1351.78</v>
+        <v>1351.85</v>
       </c>
       <c r="E51" t="n">
-        <v>1362.12</v>
+        <v>1362.19</v>
       </c>
       <c r="F51" t="n">
-        <v>18178</v>
+        <v>18036</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -8225,16 +8225,16 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1356.65</v>
+        <v>1356.08</v>
       </c>
       <c r="D52" t="n">
-        <v>1348.25</v>
+        <v>1347.78</v>
       </c>
       <c r="E52" t="n">
-        <v>1365.06</v>
+        <v>1364.37</v>
       </c>
       <c r="F52" t="n">
-        <v>5273</v>
+        <v>5464</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -8376,16 +8376,16 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1354.89</v>
+        <v>1353.71</v>
       </c>
       <c r="D53" t="n">
-        <v>1350.52</v>
+        <v>1349.39</v>
       </c>
       <c r="E53" t="n">
-        <v>1359.26</v>
+        <v>1358.04</v>
       </c>
       <c r="F53" t="n">
-        <v>30655</v>
+        <v>31132</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -8527,16 +8527,16 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1353.7</v>
+        <v>1353.43</v>
       </c>
       <c r="D54" t="n">
-        <v>1350.26</v>
+        <v>1350</v>
       </c>
       <c r="E54" t="n">
-        <v>1357.14</v>
+        <v>1356.85</v>
       </c>
       <c r="F54" t="n">
-        <v>56995</v>
+        <v>57152</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -8678,16 +8678,16 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1353.5</v>
+        <v>1352.89</v>
       </c>
       <c r="D55" t="n">
-        <v>1345.13</v>
+        <v>1344.56</v>
       </c>
       <c r="E55" t="n">
-        <v>1361.86</v>
+        <v>1361.22</v>
       </c>
       <c r="F55" t="n">
-        <v>4938</v>
+        <v>4994</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -8829,16 +8829,16 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1348.06</v>
+        <v>1347.69</v>
       </c>
       <c r="D56" t="n">
-        <v>1340.67</v>
+        <v>1340.32</v>
       </c>
       <c r="E56" t="n">
-        <v>1355.46</v>
+        <v>1355.06</v>
       </c>
       <c r="F56" t="n">
-        <v>6566</v>
+        <v>6604</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -8896,36 +8896,36 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ling-flash-2.0</t>
+          <t>minimax-m2</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1347.9</v>
+        <v>1347.14</v>
       </c>
       <c r="D57" t="n">
-        <v>1340.62</v>
+        <v>1339.44</v>
       </c>
       <c r="E57" t="n">
-        <v>1355.19</v>
+        <v>1354.85</v>
       </c>
       <c r="F57" t="n">
-        <v>6962</v>
+        <v>6965</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Ant Group</t>
+          <t>MiniMax</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Apache 2.0</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>103</v>
+        <v>230</v>
       </c>
       <c r="J57" t="n">
-        <v>6.1</v>
+        <v>10</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
@@ -8938,22 +8938,22 @@
         </is>
       </c>
       <c r="M57" t="n">
-        <v>206</v>
+        <v>460</v>
       </c>
       <c r="N57" t="n">
-        <v>257.5</v>
+        <v>575</v>
       </c>
       <c r="O57" t="n">
-        <v>103</v>
+        <v>230</v>
       </c>
       <c r="P57" t="n">
-        <v>128.8</v>
+        <v>287.5</v>
       </c>
       <c r="Q57" t="n">
-        <v>51.5</v>
+        <v>115</v>
       </c>
       <c r="R57" t="n">
-        <v>64.40000000000001</v>
+        <v>143.8</v>
       </c>
       <c r="S57" s="5" t="inlineStr">
         <is>
@@ -8965,9 +8965,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="U57" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="U57" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="V57" s="5" t="inlineStr">
@@ -8980,9 +8980,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="X57" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="X57" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="Y57" s="5" t="inlineStr">
@@ -8990,14 +8990,14 @@
           <t>No</t>
         </is>
       </c>
-      <c r="Z57" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AA57" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="Z57" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA57" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AB57" s="5" t="inlineStr">
@@ -9005,9 +9005,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AC57" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AC57" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AD57" s="6" t="inlineStr">
@@ -9015,9 +9015,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="AE57" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AE57" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AF57" s="6" t="inlineStr">
@@ -9032,12 +9032,12 @@
       </c>
       <c r="AH57" t="inlineStr">
         <is>
+          <t>MULTI-GPU</t>
+        </is>
+      </c>
+      <c r="AI57" t="inlineStr">
+        <is>
           <t>B300 SXM</t>
-        </is>
-      </c>
-      <c r="AI57" t="inlineStr">
-        <is>
-          <t>H200 SXM</t>
         </is>
       </c>
     </row>
@@ -9047,24 +9047,24 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>minimax-m2</t>
+          <t>qwen3-32b</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1347.68</v>
+        <v>1346.98</v>
       </c>
       <c r="D58" t="n">
-        <v>1339.84</v>
+        <v>1337.51</v>
       </c>
       <c r="E58" t="n">
-        <v>1355.52</v>
+        <v>1356.44</v>
       </c>
       <c r="F58" t="n">
-        <v>6659</v>
+        <v>3926</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>MiniMax</t>
+          <t>Alibaba</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -9073,14 +9073,14 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>230</v>
+        <v>32.8</v>
       </c>
       <c r="J58" t="n">
-        <v>10</v>
+        <v>32.8</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>moe</t>
+          <t>dense</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -9089,36 +9089,36 @@
         </is>
       </c>
       <c r="M58" t="n">
-        <v>460</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="N58" t="n">
-        <v>575</v>
+        <v>82</v>
       </c>
       <c r="O58" t="n">
-        <v>230</v>
+        <v>32.8</v>
       </c>
       <c r="P58" t="n">
-        <v>287.5</v>
+        <v>41</v>
       </c>
       <c r="Q58" t="n">
-        <v>115</v>
+        <v>16.4</v>
       </c>
       <c r="R58" t="n">
-        <v>143.8</v>
-      </c>
-      <c r="S58" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T58" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U58" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+        <v>20.5</v>
+      </c>
+      <c r="S58" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T58" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U58" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="V58" s="5" t="inlineStr">
@@ -9126,39 +9126,39 @@
           <t>No</t>
         </is>
       </c>
-      <c r="W58" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X58" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Y58" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z58" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AA58" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AB58" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AC58" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="W58" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X58" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y58" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z58" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AA58" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB58" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AC58" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AD58" s="6" t="inlineStr">
@@ -9166,9 +9166,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="AE58" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AE58" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AF58" s="6" t="inlineStr">
@@ -9183,12 +9183,12 @@
       </c>
       <c r="AH58" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>RTX PRO 6000</t>
         </is>
       </c>
       <c r="AI58" t="inlineStr">
         <is>
-          <t>B300 SXM</t>
+          <t>H100 SXM</t>
         </is>
       </c>
     </row>
@@ -9198,36 +9198,36 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>qwen3-32b</t>
+          <t>llama-3.1-nemotron-ultra-253b-v1</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1347.57</v>
+        <v>1346.88</v>
       </c>
       <c r="D59" t="n">
-        <v>1338.1</v>
+        <v>1335.18</v>
       </c>
       <c r="E59" t="n">
-        <v>1357.04</v>
+        <v>1358.59</v>
       </c>
       <c r="F59" t="n">
-        <v>3926</v>
+        <v>2549</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alibaba</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
+          <t>Nvidia Open Model</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>32.8</v>
+        <v>253</v>
       </c>
       <c r="J59" t="n">
-        <v>32.8</v>
+        <v>253</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
@@ -9240,36 +9240,36 @@
         </is>
       </c>
       <c r="M59" t="n">
-        <v>65.59999999999999</v>
+        <v>506</v>
       </c>
       <c r="N59" t="n">
-        <v>82</v>
+        <v>632.5</v>
       </c>
       <c r="O59" t="n">
-        <v>32.8</v>
+        <v>253</v>
       </c>
       <c r="P59" t="n">
-        <v>41</v>
+        <v>316.2</v>
       </c>
       <c r="Q59" t="n">
-        <v>16.4</v>
+        <v>126.5</v>
       </c>
       <c r="R59" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="S59" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="T59" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="U59" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+        <v>158.1</v>
+      </c>
+      <c r="S59" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T59" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U59" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="V59" s="5" t="inlineStr">
@@ -9277,39 +9277,39 @@
           <t>No</t>
         </is>
       </c>
-      <c r="W59" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X59" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Y59" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z59" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AA59" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB59" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AC59" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="W59" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X59" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y59" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z59" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA59" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AB59" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AC59" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AD59" s="6" t="inlineStr">
@@ -9317,14 +9317,14 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="AE59" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AF59" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AE59" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF59" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AG59" s="6" t="inlineStr">
@@ -9334,12 +9334,12 @@
       </c>
       <c r="AH59" t="inlineStr">
         <is>
-          <t>RTX PRO 6000</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
     </row>
@@ -9349,40 +9349,40 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>llama-3.1-nemotron-ultra-253b-v1</t>
+          <t>ling-flash-2.0</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1347.52</v>
+        <v>1346.03</v>
       </c>
       <c r="D60" t="n">
-        <v>1335.82</v>
+        <v>1338.83</v>
       </c>
       <c r="E60" t="n">
-        <v>1359.22</v>
+        <v>1353.24</v>
       </c>
       <c r="F60" t="n">
-        <v>2549</v>
+        <v>7142</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Ant Group</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Nvidia Open Model</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="I60" t="n">
-        <v>253</v>
+        <v>103</v>
       </c>
       <c r="J60" t="n">
-        <v>253</v>
+        <v>6.1</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>dense</t>
+          <t>moe</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -9391,22 +9391,22 @@
         </is>
       </c>
       <c r="M60" t="n">
-        <v>506</v>
+        <v>206</v>
       </c>
       <c r="N60" t="n">
-        <v>632.5</v>
+        <v>257.5</v>
       </c>
       <c r="O60" t="n">
-        <v>253</v>
+        <v>103</v>
       </c>
       <c r="P60" t="n">
-        <v>316.2</v>
+        <v>128.8</v>
       </c>
       <c r="Q60" t="n">
-        <v>126.5</v>
+        <v>51.5</v>
       </c>
       <c r="R60" t="n">
-        <v>158.1</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="S60" s="5" t="inlineStr">
         <is>
@@ -9418,9 +9418,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="U60" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="U60" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="V60" s="5" t="inlineStr">
@@ -9433,9 +9433,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="X60" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="X60" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Y60" s="5" t="inlineStr">
@@ -9443,14 +9443,14 @@
           <t>No</t>
         </is>
       </c>
-      <c r="Z60" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AA60" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="Z60" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AA60" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AB60" s="5" t="inlineStr">
@@ -9458,9 +9458,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AC60" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AC60" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AD60" s="6" t="inlineStr">
@@ -9468,14 +9468,14 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="AE60" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AF60" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AE60" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AF60" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AG60" s="6" t="inlineStr">
@@ -9485,12 +9485,12 @@
       </c>
       <c r="AH60" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>B300 SXM</t>
         </is>
       </c>
       <c r="AI60" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>H200 SXM</t>
         </is>
       </c>
     </row>
@@ -9500,36 +9500,36 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>gemma-3-12b-it</t>
+          <t>nvidia-llama-3.3-nemotron-super-49b-v1.5</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1342.18</v>
+        <v>1342.62</v>
       </c>
       <c r="D61" t="n">
-        <v>1332.67</v>
+        <v>1332.7</v>
       </c>
       <c r="E61" t="n">
-        <v>1351.7</v>
+        <v>1352.53</v>
       </c>
       <c r="F61" t="n">
-        <v>3829</v>
+        <v>3393</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Gemma</t>
+          <t>Nvidia Open</t>
         </is>
       </c>
       <c r="I61" t="n">
-        <v>12.2</v>
+        <v>49</v>
       </c>
       <c r="J61" t="n">
-        <v>12.2</v>
+        <v>49</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
@@ -9542,26 +9542,26 @@
         </is>
       </c>
       <c r="M61" t="n">
-        <v>24.4</v>
+        <v>98</v>
       </c>
       <c r="N61" t="n">
-        <v>30.5</v>
+        <v>122.5</v>
       </c>
       <c r="O61" t="n">
-        <v>12.2</v>
+        <v>49</v>
       </c>
       <c r="P61" t="n">
-        <v>15.2</v>
+        <v>61.2</v>
       </c>
       <c r="Q61" t="n">
-        <v>6.1</v>
+        <v>24.5</v>
       </c>
       <c r="R61" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="S61" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+        <v>30.6</v>
+      </c>
+      <c r="S61" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="T61" s="6" t="inlineStr">
@@ -9574,9 +9574,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="V61" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="V61" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="W61" s="6" t="inlineStr">
@@ -9636,7 +9636,7 @@
       </c>
       <c r="AH61" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>H200 SXM</t>
         </is>
       </c>
       <c r="AI61" t="inlineStr">
@@ -9651,36 +9651,36 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>nvidia-llama-3.3-nemotron-super-49b-v1.5</t>
+          <t>gemma-3-12b-it</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1342.17</v>
+        <v>1341.49</v>
       </c>
       <c r="D62" t="n">
-        <v>1332.25</v>
+        <v>1331.98</v>
       </c>
       <c r="E62" t="n">
-        <v>1352.08</v>
+        <v>1351.01</v>
       </c>
       <c r="F62" t="n">
-        <v>3399</v>
+        <v>3829</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Nvidia Open</t>
+          <t>Gemma</t>
         </is>
       </c>
       <c r="I62" t="n">
-        <v>49</v>
+        <v>12.2</v>
       </c>
       <c r="J62" t="n">
-        <v>49</v>
+        <v>12.2</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
@@ -9693,26 +9693,26 @@
         </is>
       </c>
       <c r="M62" t="n">
-        <v>98</v>
+        <v>24.4</v>
       </c>
       <c r="N62" t="n">
-        <v>122.5</v>
+        <v>30.5</v>
       </c>
       <c r="O62" t="n">
-        <v>49</v>
+        <v>12.2</v>
       </c>
       <c r="P62" t="n">
-        <v>61.2</v>
+        <v>15.2</v>
       </c>
       <c r="Q62" t="n">
-        <v>24.5</v>
+        <v>6.1</v>
       </c>
       <c r="R62" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="S62" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+        <v>7.6</v>
+      </c>
+      <c r="S62" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="T62" s="6" t="inlineStr">
@@ -9725,9 +9725,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="V62" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="V62" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W62" s="6" t="inlineStr">
@@ -9787,7 +9787,7 @@
       </c>
       <c r="AH62" t="inlineStr">
         <is>
-          <t>H200 SXM</t>
+          <t>H100 SXM</t>
         </is>
       </c>
       <c r="AI62" t="inlineStr">
@@ -9806,16 +9806,16 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1336.31</v>
+        <v>1335.54</v>
       </c>
       <c r="D63" t="n">
-        <v>1331.92</v>
+        <v>1331.13</v>
       </c>
       <c r="E63" t="n">
-        <v>1340.71</v>
+        <v>1339.94</v>
       </c>
       <c r="F63" t="n">
-        <v>25930</v>
+        <v>25776</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -9957,13 +9957,13 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1335.44</v>
+        <v>1334.53</v>
       </c>
       <c r="D64" t="n">
-        <v>1331.78</v>
+        <v>1330.86</v>
       </c>
       <c r="E64" t="n">
-        <v>1339.11</v>
+        <v>1338.2</v>
       </c>
       <c r="F64" t="n">
         <v>41375</v>
@@ -10108,13 +10108,13 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1333.64</v>
+        <v>1332.71</v>
       </c>
       <c r="D65" t="n">
-        <v>1330.09</v>
+        <v>1329.15</v>
       </c>
       <c r="E65" t="n">
-        <v>1337.2</v>
+        <v>1336.27</v>
       </c>
       <c r="F65" t="n">
         <v>59656</v>
@@ -10259,16 +10259,16 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1331.44</v>
+        <v>1331.57</v>
       </c>
       <c r="D66" t="n">
-        <v>1325.28</v>
+        <v>1325.5</v>
       </c>
       <c r="E66" t="n">
-        <v>1337.59</v>
+        <v>1337.65</v>
       </c>
       <c r="F66" t="n">
-        <v>12208</v>
+        <v>12572</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -10406,24 +10406,24 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>molmo-2-8b</t>
+          <t>qwen3-30b-a3b</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1329.22</v>
+        <v>1327.73</v>
       </c>
       <c r="D67" t="n">
-        <v>1308.02</v>
+        <v>1323.02</v>
       </c>
       <c r="E67" t="n">
-        <v>1350.43</v>
+        <v>1332.43</v>
       </c>
       <c r="F67" t="n">
-        <v>816</v>
+        <v>26937</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Ai2</t>
+          <t>Alibaba</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -10432,14 +10432,14 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>8.699999999999999</v>
+        <v>30.5</v>
       </c>
       <c r="J67" t="n">
-        <v>8.699999999999999</v>
+        <v>3.3</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>dense</t>
+          <t>moe</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -10448,22 +10448,22 @@
         </is>
       </c>
       <c r="M67" t="n">
-        <v>17.4</v>
+        <v>61</v>
       </c>
       <c r="N67" t="n">
-        <v>21.8</v>
+        <v>76.2</v>
       </c>
       <c r="O67" t="n">
-        <v>8.699999999999999</v>
+        <v>30.5</v>
       </c>
       <c r="P67" t="n">
-        <v>10.9</v>
+        <v>38.1</v>
       </c>
       <c r="Q67" t="n">
-        <v>4.3</v>
+        <v>15.2</v>
       </c>
       <c r="R67" t="n">
-        <v>5.4</v>
+        <v>19.1</v>
       </c>
       <c r="S67" s="6" t="inlineStr">
         <is>
@@ -10557,68 +10557,68 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>qwen3-30b-a3b</t>
+          <t>llama-3.3-nemotron-49b-super-v1</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1328.66</v>
+        <v>1327.39</v>
       </c>
       <c r="D68" t="n">
-        <v>1323.97</v>
+        <v>1315.22</v>
       </c>
       <c r="E68" t="n">
-        <v>1333.35</v>
+        <v>1339.56</v>
       </c>
       <c r="F68" t="n">
-        <v>27214</v>
+        <v>2218</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alibaba</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="I68" t="n">
-        <v>30.5</v>
+        <v>49</v>
       </c>
       <c r="J68" t="n">
-        <v>3.3</v>
+        <v>49</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>moe</t>
+          <t>dense</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>artificial_analysis</t>
+          <t>name_parsing</t>
         </is>
       </c>
       <c r="M68" t="n">
-        <v>61</v>
+        <v>98</v>
       </c>
       <c r="N68" t="n">
-        <v>76.2</v>
+        <v>122.5</v>
       </c>
       <c r="O68" t="n">
-        <v>30.5</v>
+        <v>49</v>
       </c>
       <c r="P68" t="n">
-        <v>38.1</v>
+        <v>61.2</v>
       </c>
       <c r="Q68" t="n">
-        <v>15.2</v>
+        <v>24.5</v>
       </c>
       <c r="R68" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="S68" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+        <v>30.6</v>
+      </c>
+      <c r="S68" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="T68" s="6" t="inlineStr">
@@ -10631,9 +10631,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="V68" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="V68" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="W68" s="6" t="inlineStr">
@@ -10693,7 +10693,7 @@
       </c>
       <c r="AH68" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>H200 SXM</t>
         </is>
       </c>
       <c r="AI68" t="inlineStr">
@@ -10712,16 +10712,16 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1328.01</v>
+        <v>1326.79</v>
       </c>
       <c r="D69" t="n">
-        <v>1323.8</v>
+        <v>1322.57</v>
       </c>
       <c r="E69" t="n">
-        <v>1332.23</v>
+        <v>1331.02</v>
       </c>
       <c r="F69" t="n">
-        <v>40879</v>
+        <v>40577</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -10859,36 +10859,36 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>llama-3.3-nemotron-49b-super-v1</t>
+          <t>molmo-2-8b</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1328.01</v>
+        <v>1325.31</v>
       </c>
       <c r="D70" t="n">
-        <v>1315.83</v>
+        <v>1304.22</v>
       </c>
       <c r="E70" t="n">
-        <v>1340.18</v>
+        <v>1346.39</v>
       </c>
       <c r="F70" t="n">
-        <v>2218</v>
+        <v>841</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Ai2</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Apache 2.0</t>
         </is>
       </c>
       <c r="I70" t="n">
-        <v>49</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J70" t="n">
-        <v>49</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
@@ -10897,30 +10897,30 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>artificial_analysis</t>
         </is>
       </c>
       <c r="M70" t="n">
-        <v>98</v>
+        <v>17.4</v>
       </c>
       <c r="N70" t="n">
-        <v>122.5</v>
+        <v>21.8</v>
       </c>
       <c r="O70" t="n">
-        <v>49</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="P70" t="n">
-        <v>61.2</v>
+        <v>10.9</v>
       </c>
       <c r="Q70" t="n">
-        <v>24.5</v>
+        <v>4.3</v>
       </c>
       <c r="R70" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="S70" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+        <v>5.4</v>
+      </c>
+      <c r="S70" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="T70" s="6" t="inlineStr">
@@ -10933,9 +10933,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="V70" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="V70" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W70" s="6" t="inlineStr">
@@ -10995,7 +10995,7 @@
       </c>
       <c r="AH70" t="inlineStr">
         <is>
-          <t>H200 SXM</t>
+          <t>H100 SXM</t>
         </is>
       </c>
       <c r="AI70" t="inlineStr">
@@ -11014,13 +11014,13 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1323.88</v>
+        <v>1323.13</v>
       </c>
       <c r="D71" t="n">
-        <v>1315.61</v>
+        <v>1314.87</v>
       </c>
       <c r="E71" t="n">
-        <v>1332.14</v>
+        <v>1331.39</v>
       </c>
       <c r="F71" t="n">
         <v>6795</v>
@@ -11165,16 +11165,16 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1322.71</v>
+        <v>1322.17</v>
       </c>
       <c r="D72" t="n">
-        <v>1318.03</v>
+        <v>1317.49</v>
       </c>
       <c r="E72" t="n">
-        <v>1327.39</v>
+        <v>1326.86</v>
       </c>
       <c r="F72" t="n">
-        <v>30933</v>
+        <v>30775</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -11316,16 +11316,16 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1320.99</v>
+        <v>1320.76</v>
       </c>
       <c r="D73" t="n">
-        <v>1313.75</v>
+        <v>1313.6</v>
       </c>
       <c r="E73" t="n">
-        <v>1328.23</v>
+        <v>1327.93</v>
       </c>
       <c r="F73" t="n">
-        <v>7104</v>
+        <v>7275</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -11467,16 +11467,16 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1319.59</v>
+        <v>1318.41</v>
       </c>
       <c r="D74" t="n">
-        <v>1314.49</v>
+        <v>1313.3</v>
       </c>
       <c r="E74" t="n">
-        <v>1324.7</v>
+        <v>1323.53</v>
       </c>
       <c r="F74" t="n">
-        <v>23138</v>
+        <v>22950</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -11618,16 +11618,16 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>1319.33</v>
+        <v>1318.25</v>
       </c>
       <c r="D75" t="n">
-        <v>1315.91</v>
+        <v>1314.83</v>
       </c>
       <c r="E75" t="n">
-        <v>1322.75</v>
+        <v>1321.67</v>
       </c>
       <c r="F75" t="n">
-        <v>55370</v>
+        <v>55173</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -11769,16 +11769,16 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>1318.68</v>
+        <v>1317.74</v>
       </c>
       <c r="D76" t="n">
-        <v>1313.06</v>
+        <v>1312.18</v>
       </c>
       <c r="E76" t="n">
-        <v>1324.31</v>
+        <v>1323.3</v>
       </c>
       <c r="F76" t="n">
-        <v>15376</v>
+        <v>15869</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -11916,68 +11916,148 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>qwen-max-0919</t>
+          <t>gpt-oss-20b</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1318.39</v>
+        <v>1317.6</v>
       </c>
       <c r="D77" t="n">
-        <v>1312.71</v>
+        <v>1311.26</v>
       </c>
       <c r="E77" t="n">
-        <v>1324.07</v>
+        <v>1323.94</v>
       </c>
       <c r="F77" t="n">
-        <v>16478</v>
+        <v>10758</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alibaba</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Qwen</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
+          <t>Apache 2.0</t>
+        </is>
+      </c>
+      <c r="I77" t="n">
+        <v>21</v>
+      </c>
+      <c r="J77" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="M77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
-      <c r="O77" t="inlineStr"/>
-      <c r="P77" t="inlineStr"/>
-      <c r="Q77" t="inlineStr"/>
-      <c r="R77" t="inlineStr"/>
-      <c r="S77" t="inlineStr"/>
-      <c r="T77" t="inlineStr"/>
-      <c r="U77" t="inlineStr"/>
-      <c r="V77" t="inlineStr"/>
-      <c r="W77" t="inlineStr"/>
-      <c r="X77" t="inlineStr"/>
-      <c r="Y77" t="inlineStr"/>
-      <c r="Z77" t="inlineStr"/>
-      <c r="AA77" t="inlineStr"/>
-      <c r="AB77" t="inlineStr"/>
-      <c r="AC77" t="inlineStr"/>
-      <c r="AD77" t="inlineStr"/>
-      <c r="AE77" t="inlineStr"/>
-      <c r="AF77" t="inlineStr"/>
-      <c r="AG77" t="inlineStr"/>
+          <t>override</t>
+        </is>
+      </c>
+      <c r="M77" t="n">
+        <v>42</v>
+      </c>
+      <c r="N77" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="O77" t="n">
+        <v>21</v>
+      </c>
+      <c r="P77" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="R77" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="S77" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T77" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U77" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V77" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W77" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X77" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y77" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z77" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AA77" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB77" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AC77" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AD77" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE77" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AF77" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AG77" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AH77" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>H100 SXM</t>
         </is>
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>H100 SXM</t>
         </is>
       </c>
     </row>
@@ -11987,148 +12067,68 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>gpt-oss-20b</t>
+          <t>qwen-max-0919</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1317.93</v>
+        <v>1317.6</v>
       </c>
       <c r="D78" t="n">
-        <v>1311.57</v>
+        <v>1311.92</v>
       </c>
       <c r="E78" t="n">
-        <v>1324.28</v>
+        <v>1323.28</v>
       </c>
       <c r="F78" t="n">
-        <v>10750</v>
+        <v>16478</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Alibaba</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
-        </is>
-      </c>
-      <c r="I78" t="n">
-        <v>21</v>
-      </c>
-      <c r="J78" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+          <t>Qwen</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr">
         <is>
-          <t>override</t>
-        </is>
-      </c>
-      <c r="M78" t="n">
-        <v>42</v>
-      </c>
-      <c r="N78" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="O78" t="n">
-        <v>21</v>
-      </c>
-      <c r="P78" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="Q78" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="R78" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="S78" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="T78" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="U78" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="V78" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W78" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X78" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Y78" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z78" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AA78" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB78" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AC78" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AD78" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AE78" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AF78" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AG78" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
+      <c r="O78" t="inlineStr"/>
+      <c r="P78" t="inlineStr"/>
+      <c r="Q78" t="inlineStr"/>
+      <c r="R78" t="inlineStr"/>
+      <c r="S78" t="inlineStr"/>
+      <c r="T78" t="inlineStr"/>
+      <c r="U78" t="inlineStr"/>
+      <c r="V78" t="inlineStr"/>
+      <c r="W78" t="inlineStr"/>
+      <c r="X78" t="inlineStr"/>
+      <c r="Y78" t="inlineStr"/>
+      <c r="Z78" t="inlineStr"/>
+      <c r="AA78" t="inlineStr"/>
+      <c r="AB78" t="inlineStr"/>
+      <c r="AC78" t="inlineStr"/>
+      <c r="AD78" t="inlineStr"/>
+      <c r="AE78" t="inlineStr"/>
+      <c r="AF78" t="inlineStr"/>
+      <c r="AG78" t="inlineStr"/>
       <c r="AH78" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -12142,13 +12142,13 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>1314.9</v>
+        <v>1314.13</v>
       </c>
       <c r="D79" t="n">
-        <v>1310.38</v>
+        <v>1309.61</v>
       </c>
       <c r="E79" t="n">
-        <v>1319.42</v>
+        <v>1318.65</v>
       </c>
       <c r="F79" t="n">
         <v>24739</v>
@@ -12293,13 +12293,13 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1314.35</v>
+        <v>1313.53</v>
       </c>
       <c r="D80" t="n">
-        <v>1310.46</v>
+        <v>1309.63</v>
       </c>
       <c r="E80" t="n">
-        <v>1318.24</v>
+        <v>1317.42</v>
       </c>
       <c r="F80" t="n">
         <v>45459</v>
@@ -12444,13 +12444,13 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1307.47</v>
+        <v>1306.71</v>
       </c>
       <c r="D81" t="n">
-        <v>1302.79</v>
+        <v>1302.04</v>
       </c>
       <c r="E81" t="n">
-        <v>1312.15</v>
+        <v>1311.39</v>
       </c>
       <c r="F81" t="n">
         <v>24572</v>
@@ -12595,16 +12595,16 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>1306.86</v>
+        <v>1305.71</v>
       </c>
       <c r="D82" t="n">
-        <v>1298.59</v>
+        <v>1297.58</v>
       </c>
       <c r="E82" t="n">
-        <v>1315.13</v>
+        <v>1313.85</v>
       </c>
       <c r="F82" t="n">
-        <v>5858</v>
+        <v>6089</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -12746,13 +12746,13 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>1306.4</v>
+        <v>1305.65</v>
       </c>
       <c r="D83" t="n">
-        <v>1300.74</v>
+        <v>1299.99</v>
       </c>
       <c r="E83" t="n">
-        <v>1312.05</v>
+        <v>1311.31</v>
       </c>
       <c r="F83" t="n">
         <v>19621</v>
@@ -12897,13 +12897,13 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>1305.61</v>
+        <v>1304.82</v>
       </c>
       <c r="D84" t="n">
-        <v>1301.21</v>
+        <v>1300.42</v>
       </c>
       <c r="E84" t="n">
-        <v>1310</v>
+        <v>1309.22</v>
       </c>
       <c r="F84" t="n">
         <v>28073</v>
@@ -13048,16 +13048,16 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>1304.16</v>
+        <v>1302.89</v>
       </c>
       <c r="D85" t="n">
-        <v>1299.67</v>
+        <v>1298.41</v>
       </c>
       <c r="E85" t="n">
-        <v>1308.65</v>
+        <v>1307.37</v>
       </c>
       <c r="F85" t="n">
-        <v>33821</v>
+        <v>33775</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -13199,13 +13199,13 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>1303.59</v>
+        <v>1302.89</v>
       </c>
       <c r="D86" t="n">
-        <v>1294.27</v>
+        <v>1293.57</v>
       </c>
       <c r="E86" t="n">
-        <v>1312.91</v>
+        <v>1312.21</v>
       </c>
       <c r="F86" t="n">
         <v>4171</v>
@@ -13350,13 +13350,13 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>1303.18</v>
+        <v>1302.42</v>
       </c>
       <c r="D87" t="n">
-        <v>1299.15</v>
+        <v>1298.38</v>
       </c>
       <c r="E87" t="n">
-        <v>1307.21</v>
+        <v>1306.45</v>
       </c>
       <c r="F87" t="n">
         <v>39406</v>
@@ -13501,13 +13501,13 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>1299.21</v>
+        <v>1298.5</v>
       </c>
       <c r="D88" t="n">
-        <v>1291.45</v>
+        <v>1290.75</v>
       </c>
       <c r="E88" t="n">
-        <v>1306.96</v>
+        <v>1306.26</v>
       </c>
       <c r="F88" t="n">
         <v>7140</v>
@@ -13652,13 +13652,13 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>1293.81</v>
+        <v>1292.98</v>
       </c>
       <c r="D89" t="n">
-        <v>1290.11</v>
+        <v>1289.28</v>
       </c>
       <c r="E89" t="n">
-        <v>1297.5</v>
+        <v>1296.68</v>
       </c>
       <c r="F89" t="n">
         <v>55240</v>
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>1289.12</v>
+        <v>1288.36</v>
       </c>
       <c r="D90" t="n">
-        <v>1281.82</v>
+        <v>1281.06</v>
       </c>
       <c r="E90" t="n">
-        <v>1296.42</v>
+        <v>1295.66</v>
       </c>
       <c r="F90" t="n">
         <v>8662</v>
@@ -13954,13 +13954,13 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>1288.44</v>
+        <v>1287.74</v>
       </c>
       <c r="D91" t="n">
-        <v>1285.1</v>
+        <v>1284.4</v>
       </c>
       <c r="E91" t="n">
-        <v>1291.77</v>
+        <v>1291.08</v>
       </c>
       <c r="F91" t="n">
         <v>75754</v>
@@ -14101,36 +14101,36 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>llama-3.1-tulu-3-70b</t>
+          <t>ibm-granite-h-small</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>1286.93</v>
+        <v>1286.73</v>
       </c>
       <c r="D92" t="n">
-        <v>1276.45</v>
+        <v>1278.42</v>
       </c>
       <c r="E92" t="n">
-        <v>1297.4</v>
+        <v>1295.04</v>
       </c>
       <c r="F92" t="n">
-        <v>2846</v>
+        <v>5800</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Ai2</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Llama 3.1</t>
+          <t>Apache 2.0</t>
         </is>
       </c>
       <c r="I92" t="n">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="J92" t="n">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
@@ -14139,30 +14139,30 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>override</t>
         </is>
       </c>
       <c r="M92" t="n">
-        <v>140</v>
+        <v>16</v>
       </c>
       <c r="N92" t="n">
-        <v>175</v>
+        <v>20</v>
       </c>
       <c r="O92" t="n">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="P92" t="n">
-        <v>87.5</v>
+        <v>10</v>
       </c>
       <c r="Q92" t="n">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="R92" t="n">
-        <v>43.8</v>
-      </c>
-      <c r="S92" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+        <v>5</v>
+      </c>
+      <c r="S92" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="T92" s="6" t="inlineStr">
@@ -14175,14 +14175,14 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="V92" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W92" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="V92" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W92" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="X92" s="6" t="inlineStr">
@@ -14190,9 +14190,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="Y92" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="Y92" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Z92" s="6" t="inlineStr">
@@ -14237,12 +14237,12 @@
       </c>
       <c r="AH92" t="inlineStr">
         <is>
-          <t>B200 SXM</t>
+          <t>H100 SXM</t>
         </is>
       </c>
       <c r="AI92" t="inlineStr">
         <is>
-          <t>RTX PRO 6000</t>
+          <t>H100 SXM</t>
         </is>
       </c>
     </row>
@@ -14252,24 +14252,24 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>ibm-granite-h-small</t>
+          <t>olmo-3.1-32b-think</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>1286.91</v>
+        <v>1286.4</v>
       </c>
       <c r="D93" t="n">
-        <v>1278.46</v>
+        <v>1279.21</v>
       </c>
       <c r="E93" t="n">
-        <v>1295.36</v>
+        <v>1293.6</v>
       </c>
       <c r="F93" t="n">
-        <v>5586</v>
+        <v>8680</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>Ai2</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -14278,10 +14278,10 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>8</v>
+        <v>32.2</v>
       </c>
       <c r="J93" t="n">
-        <v>8</v>
+        <v>32.2</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
@@ -14290,26 +14290,26 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>artificial_analysis</t>
         </is>
       </c>
       <c r="M93" t="n">
-        <v>16</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="N93" t="n">
-        <v>20</v>
+        <v>80.5</v>
       </c>
       <c r="O93" t="n">
-        <v>8</v>
+        <v>32.2</v>
       </c>
       <c r="P93" t="n">
-        <v>10</v>
+        <v>40.2</v>
       </c>
       <c r="Q93" t="n">
-        <v>4</v>
+        <v>16.1</v>
       </c>
       <c r="R93" t="n">
-        <v>5</v>
+        <v>20.1</v>
       </c>
       <c r="S93" s="6" t="inlineStr">
         <is>
@@ -14326,9 +14326,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="V93" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="V93" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="W93" s="6" t="inlineStr">
@@ -14388,7 +14388,7 @@
       </c>
       <c r="AH93" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>RTX PRO 6000</t>
         </is>
       </c>
       <c r="AI93" t="inlineStr">
@@ -14403,24 +14403,24 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>llama-3.1-nemotron-51b-instruct</t>
+          <t>llama-3.1-tulu-3-70b</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1286.5</v>
+        <v>1286.02</v>
       </c>
       <c r="D94" t="n">
-        <v>1276.53</v>
+        <v>1275.54</v>
       </c>
       <c r="E94" t="n">
-        <v>1296.47</v>
+        <v>1296.49</v>
       </c>
       <c r="F94" t="n">
-        <v>3749</v>
+        <v>2846</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Ai2</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -14429,10 +14429,10 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="J94" t="n">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
@@ -14445,22 +14445,22 @@
         </is>
       </c>
       <c r="M94" t="n">
-        <v>102</v>
+        <v>140</v>
       </c>
       <c r="N94" t="n">
-        <v>127.5</v>
+        <v>175</v>
       </c>
       <c r="O94" t="n">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="P94" t="n">
-        <v>63.8</v>
+        <v>87.5</v>
       </c>
       <c r="Q94" t="n">
-        <v>25.5</v>
+        <v>35</v>
       </c>
       <c r="R94" t="n">
-        <v>31.9</v>
+        <v>43.8</v>
       </c>
       <c r="S94" s="5" t="inlineStr">
         <is>
@@ -14482,9 +14482,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="W94" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="W94" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="X94" s="6" t="inlineStr">
@@ -14492,9 +14492,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="Y94" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="Y94" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="Z94" s="6" t="inlineStr">
@@ -14539,12 +14539,12 @@
       </c>
       <c r="AH94" t="inlineStr">
         <is>
-          <t>H200 SXM</t>
+          <t>B200 SXM</t>
         </is>
       </c>
       <c r="AI94" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>RTX PRO 6000</t>
         </is>
       </c>
     </row>
@@ -14554,36 +14554,36 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>olmo-3.1-32b-think</t>
+          <t>llama-3.1-nemotron-51b-instruct</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1285.55</v>
+        <v>1285.58</v>
       </c>
       <c r="D95" t="n">
-        <v>1278.27</v>
+        <v>1275.61</v>
       </c>
       <c r="E95" t="n">
-        <v>1292.83</v>
+        <v>1295.56</v>
       </c>
       <c r="F95" t="n">
-        <v>8406</v>
+        <v>3749</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Ai2</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
+          <t>Llama 3.1</t>
         </is>
       </c>
       <c r="I95" t="n">
-        <v>32.2</v>
+        <v>51</v>
       </c>
       <c r="J95" t="n">
-        <v>32.2</v>
+        <v>51</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
@@ -14592,30 +14592,30 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>artificial_analysis</t>
+          <t>name_parsing</t>
         </is>
       </c>
       <c r="M95" t="n">
-        <v>64.40000000000001</v>
+        <v>102</v>
       </c>
       <c r="N95" t="n">
-        <v>80.5</v>
+        <v>127.5</v>
       </c>
       <c r="O95" t="n">
-        <v>32.2</v>
+        <v>51</v>
       </c>
       <c r="P95" t="n">
-        <v>40.2</v>
+        <v>63.8</v>
       </c>
       <c r="Q95" t="n">
-        <v>16.1</v>
+        <v>25.5</v>
       </c>
       <c r="R95" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="S95" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+        <v>31.9</v>
+      </c>
+      <c r="S95" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="T95" s="6" t="inlineStr">
@@ -14690,7 +14690,7 @@
       </c>
       <c r="AH95" t="inlineStr">
         <is>
-          <t>RTX PRO 6000</t>
+          <t>H200 SXM</t>
         </is>
       </c>
       <c r="AI95" t="inlineStr">
@@ -14709,13 +14709,13 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>1279.71</v>
+        <v>1279</v>
       </c>
       <c r="D96" t="n">
-        <v>1272.86</v>
+        <v>1272.14</v>
       </c>
       <c r="E96" t="n">
-        <v>1286.57</v>
+        <v>1285.85</v>
       </c>
       <c r="F96" t="n">
         <v>10072</v>
@@ -14860,13 +14860,13 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1277.56</v>
+        <v>1276.56</v>
       </c>
       <c r="D97" t="n">
-        <v>1272.24</v>
+        <v>1271.24</v>
       </c>
       <c r="E97" t="n">
-        <v>1282.89</v>
+        <v>1281.89</v>
       </c>
       <c r="F97" t="n">
         <v>19659</v>
@@ -15011,13 +15011,13 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>1276.74</v>
+        <v>1275.78</v>
       </c>
       <c r="D98" t="n">
-        <v>1270.17</v>
+        <v>1269.22</v>
       </c>
       <c r="E98" t="n">
-        <v>1283.3</v>
+        <v>1282.35</v>
       </c>
       <c r="F98" t="n">
         <v>9866</v>
@@ -15162,13 +15162,13 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>1276.28</v>
+        <v>1275.42</v>
       </c>
       <c r="D99" t="n">
-        <v>1272.72</v>
+        <v>1271.85</v>
       </c>
       <c r="E99" t="n">
-        <v>1279.85</v>
+        <v>1278.99</v>
       </c>
       <c r="F99" t="n">
         <v>156876</v>
@@ -15313,13 +15313,13 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>1274.38</v>
+        <v>1273.61</v>
       </c>
       <c r="D100" t="n">
-        <v>1268.5</v>
+        <v>1267.73</v>
       </c>
       <c r="E100" t="n">
-        <v>1280.26</v>
+        <v>1279.49</v>
       </c>
       <c r="F100" t="n">
         <v>14681</v>
@@ -15464,13 +15464,13 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1270.91</v>
+        <v>1270.08</v>
       </c>
       <c r="D101" t="n">
-        <v>1262.79</v>
+        <v>1261.96</v>
       </c>
       <c r="E101" t="n">
-        <v>1279.03</v>
+        <v>1278.2</v>
       </c>
       <c r="F101" t="n">
         <v>5432</v>
@@ -15615,13 +15615,13 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>1267.31</v>
+        <v>1266.48</v>
       </c>
       <c r="D102" t="n">
-        <v>1262.46</v>
+        <v>1261.62</v>
       </c>
       <c r="E102" t="n">
-        <v>1272.16</v>
+        <v>1271.34</v>
       </c>
       <c r="F102" t="n">
         <v>27124</v>
@@ -15766,13 +15766,13 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>1265.89</v>
+        <v>1265.21</v>
       </c>
       <c r="D103" t="n">
-        <v>1262.12</v>
+        <v>1261.43</v>
       </c>
       <c r="E103" t="n">
-        <v>1269.67</v>
+        <v>1268.99</v>
       </c>
       <c r="F103" t="n">
         <v>54611</v>
@@ -15917,13 +15917,13 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>1264.47</v>
+        <v>1263.65</v>
       </c>
       <c r="D104" t="n">
-        <v>1258.19</v>
+        <v>1257.37</v>
       </c>
       <c r="E104" t="n">
-        <v>1270.74</v>
+        <v>1269.93</v>
       </c>
       <c r="F104" t="n">
         <v>15147</v>
@@ -16068,13 +16068,13 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>1262.09</v>
+        <v>1261.09</v>
       </c>
       <c r="D105" t="n">
-        <v>1257.78</v>
+        <v>1256.77</v>
       </c>
       <c r="E105" t="n">
-        <v>1266.41</v>
+        <v>1265.4</v>
       </c>
       <c r="F105" t="n">
         <v>77554</v>
@@ -16219,13 +16219,13 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>1262.02</v>
+        <v>1261.05</v>
       </c>
       <c r="D106" t="n">
-        <v>1257.09</v>
+        <v>1256.12</v>
       </c>
       <c r="E106" t="n">
-        <v>1266.95</v>
+        <v>1265.99</v>
       </c>
       <c r="F106" t="n">
         <v>37325</v>
@@ -16370,13 +16370,13 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>1256.42</v>
+        <v>1255.63</v>
       </c>
       <c r="D107" t="n">
-        <v>1251.86</v>
+        <v>1251.06</v>
       </c>
       <c r="E107" t="n">
-        <v>1260.98</v>
+        <v>1260.19</v>
       </c>
       <c r="F107" t="n">
         <v>24126</v>
@@ -16521,13 +16521,13 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>1252.3</v>
+        <v>1251.43</v>
       </c>
       <c r="D108" t="n">
-        <v>1241.51</v>
+        <v>1240.64</v>
       </c>
       <c r="E108" t="n">
-        <v>1263.1</v>
+        <v>1262.23</v>
       </c>
       <c r="F108" t="n">
         <v>3334</v>
@@ -16672,13 +16672,13 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>1250.35</v>
+        <v>1249.39</v>
       </c>
       <c r="D109" t="n">
-        <v>1243.76</v>
+        <v>1242.8</v>
       </c>
       <c r="E109" t="n">
-        <v>1256.94</v>
+        <v>1255.99</v>
       </c>
       <c r="F109" t="n">
         <v>10140</v>
@@ -16823,13 +16823,13 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>1239.3</v>
+        <v>1238.55</v>
       </c>
       <c r="D110" t="n">
-        <v>1232.08</v>
+        <v>1231.33</v>
       </c>
       <c r="E110" t="n">
-        <v>1246.52</v>
+        <v>1245.77</v>
       </c>
       <c r="F110" t="n">
         <v>8858</v>
@@ -16974,13 +16974,13 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>1237.52</v>
+        <v>1236.73</v>
       </c>
       <c r="D111" t="n">
-        <v>1228.43</v>
+        <v>1227.64</v>
       </c>
       <c r="E111" t="n">
-        <v>1246.62</v>
+        <v>1245.83</v>
       </c>
       <c r="F111" t="n">
         <v>4781</v>
@@ -17125,13 +17125,13 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>1234.24</v>
+        <v>1233.3</v>
       </c>
       <c r="D112" t="n">
-        <v>1228.68</v>
+        <v>1227.75</v>
       </c>
       <c r="E112" t="n">
-        <v>1239.79</v>
+        <v>1238.85</v>
       </c>
       <c r="F112" t="n">
         <v>26195</v>
@@ -17276,13 +17276,13 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>1233.32</v>
+        <v>1232.37</v>
       </c>
       <c r="D113" t="n">
-        <v>1228.05</v>
+        <v>1227.09</v>
       </c>
       <c r="E113" t="n">
-        <v>1238.6</v>
+        <v>1237.64</v>
       </c>
       <c r="F113" t="n">
         <v>39302</v>
@@ -17427,13 +17427,13 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>1229.59</v>
+        <v>1228.59</v>
       </c>
       <c r="D114" t="n">
-        <v>1225.05</v>
+        <v>1224.04</v>
       </c>
       <c r="E114" t="n">
-        <v>1234.14</v>
+        <v>1233.14</v>
       </c>
       <c r="F114" t="n">
         <v>51416</v>
@@ -17578,13 +17578,13 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>1227.09</v>
+        <v>1226.07</v>
       </c>
       <c r="D115" t="n">
-        <v>1222.31</v>
+        <v>1221.29</v>
       </c>
       <c r="E115" t="n">
-        <v>1231.87</v>
+        <v>1230.85</v>
       </c>
       <c r="F115" t="n">
         <v>54036</v>
@@ -17729,13 +17729,13 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>1223.39</v>
+        <v>1222.5</v>
       </c>
       <c r="D116" t="n">
-        <v>1219.67</v>
+        <v>1218.77</v>
       </c>
       <c r="E116" t="n">
-        <v>1227.11</v>
+        <v>1226.22</v>
       </c>
       <c r="F116" t="n">
         <v>104642</v>
@@ -17880,13 +17880,13 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>1223.25</v>
+        <v>1222.43</v>
       </c>
       <c r="D117" t="n">
-        <v>1216.29</v>
+        <v>1215.47</v>
       </c>
       <c r="E117" t="n">
-        <v>1230.2</v>
+        <v>1229.38</v>
       </c>
       <c r="F117" t="n">
         <v>9818</v>
@@ -18031,13 +18031,13 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>1221.43</v>
+        <v>1220.54</v>
       </c>
       <c r="D118" t="n">
-        <v>1210.74</v>
+        <v>1209.86</v>
       </c>
       <c r="E118" t="n">
-        <v>1232.12</v>
+        <v>1231.23</v>
       </c>
       <c r="F118" t="n">
         <v>2896</v>
@@ -18182,13 +18182,13 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>1213.65</v>
+        <v>1212.68</v>
       </c>
       <c r="D119" t="n">
-        <v>1208.62</v>
+        <v>1207.65</v>
       </c>
       <c r="E119" t="n">
-        <v>1218.68</v>
+        <v>1217.72</v>
       </c>
       <c r="F119" t="n">
         <v>24146</v>
@@ -18333,13 +18333,13 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>1212.87</v>
+        <v>1211.88</v>
       </c>
       <c r="D120" t="n">
-        <v>1202.06</v>
+        <v>1201.07</v>
       </c>
       <c r="E120" t="n">
-        <v>1223.68</v>
+        <v>1222.69</v>
       </c>
       <c r="F120" t="n">
         <v>4652</v>
@@ -18484,13 +18484,13 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>1211.95</v>
+        <v>1211.15</v>
       </c>
       <c r="D121" t="n">
-        <v>1207.83</v>
+        <v>1207.04</v>
       </c>
       <c r="E121" t="n">
-        <v>1216.06</v>
+        <v>1215.27</v>
       </c>
       <c r="F121" t="n">
         <v>49605</v>
@@ -18635,13 +18635,13 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>1208.63</v>
+        <v>1207.65</v>
       </c>
       <c r="D122" t="n">
-        <v>1197.51</v>
+        <v>1196.53</v>
       </c>
       <c r="E122" t="n">
-        <v>1219.74</v>
+        <v>1218.76</v>
       </c>
       <c r="F122" t="n">
         <v>3090</v>
@@ -18786,13 +18786,13 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>1203.99</v>
+        <v>1203</v>
       </c>
       <c r="D123" t="n">
-        <v>1197.87</v>
+        <v>1196.88</v>
       </c>
       <c r="E123" t="n">
-        <v>1210.11</v>
+        <v>1209.12</v>
       </c>
       <c r="F123" t="n">
         <v>21741</v>
@@ -18937,13 +18937,13 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>1199.31</v>
+        <v>1198.66</v>
       </c>
       <c r="D124" t="n">
-        <v>1195.25</v>
+        <v>1194.6</v>
       </c>
       <c r="E124" t="n">
-        <v>1203.37</v>
+        <v>1202.72</v>
       </c>
       <c r="F124" t="n">
         <v>46616</v>
@@ -19088,13 +19088,13 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>1198.12</v>
+        <v>1197.12</v>
       </c>
       <c r="D125" t="n">
-        <v>1192.97</v>
+        <v>1191.97</v>
       </c>
       <c r="E125" t="n">
-        <v>1203.27</v>
+        <v>1202.27</v>
       </c>
       <c r="F125" t="n">
         <v>25055</v>
@@ -19239,13 +19239,13 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>1197.29</v>
+        <v>1196.27</v>
       </c>
       <c r="D126" t="n">
-        <v>1193.02</v>
+        <v>1192.01</v>
       </c>
       <c r="E126" t="n">
-        <v>1201.55</v>
+        <v>1200.54</v>
       </c>
       <c r="F126" t="n">
         <v>73503</v>
@@ -19390,13 +19390,13 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>1195.17</v>
+        <v>1194.2</v>
       </c>
       <c r="D127" t="n">
-        <v>1189.06</v>
+        <v>1188.08</v>
       </c>
       <c r="E127" t="n">
-        <v>1201.29</v>
+        <v>1200.31</v>
       </c>
       <c r="F127" t="n">
         <v>32191</v>
@@ -19541,13 +19541,13 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>1191.62</v>
+        <v>1190.68</v>
       </c>
       <c r="D128" t="n">
-        <v>1184.44</v>
+        <v>1183.51</v>
       </c>
       <c r="E128" t="n">
-        <v>1198.79</v>
+        <v>1197.86</v>
       </c>
       <c r="F128" t="n">
         <v>9901</v>
@@ -19692,13 +19692,13 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>1191.08</v>
+        <v>1190.1</v>
       </c>
       <c r="D129" t="n">
-        <v>1183.95</v>
+        <v>1182.98</v>
       </c>
       <c r="E129" t="n">
-        <v>1198.2</v>
+        <v>1197.23</v>
       </c>
       <c r="F129" t="n">
         <v>17839</v>
@@ -19843,13 +19843,13 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>1184.79</v>
+        <v>1183.79</v>
       </c>
       <c r="D130" t="n">
-        <v>1175.33</v>
+        <v>1174.33</v>
       </c>
       <c r="E130" t="n">
-        <v>1194.25</v>
+        <v>1193.25</v>
       </c>
       <c r="F130" t="n">
         <v>8214</v>
@@ -19994,13 +19994,13 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>1184.49</v>
+        <v>1183.51</v>
       </c>
       <c r="D131" t="n">
-        <v>1172.98</v>
+        <v>1172</v>
       </c>
       <c r="E131" t="n">
-        <v>1196.01</v>
+        <v>1195.03</v>
       </c>
       <c r="F131" t="n">
         <v>4932</v>
@@ -20145,13 +20145,13 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>1183.99</v>
+        <v>1183.03</v>
       </c>
       <c r="D132" t="n">
-        <v>1177.16</v>
+        <v>1176.2</v>
       </c>
       <c r="E132" t="n">
-        <v>1190.82</v>
+        <v>1189.86</v>
       </c>
       <c r="F132" t="n">
         <v>15483</v>
@@ -20296,13 +20296,13 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>1182.36</v>
+        <v>1181.38</v>
       </c>
       <c r="D133" t="n">
-        <v>1174.36</v>
+        <v>1173.38</v>
       </c>
       <c r="E133" t="n">
-        <v>1190.37</v>
+        <v>1189.39</v>
       </c>
       <c r="F133" t="n">
         <v>12637</v>
@@ -20367,13 +20367,13 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>1182.27</v>
+        <v>1181.32</v>
       </c>
       <c r="D134" t="n">
-        <v>1172.59</v>
+        <v>1171.64</v>
       </c>
       <c r="E134" t="n">
-        <v>1191.95</v>
+        <v>1191</v>
       </c>
       <c r="F134" t="n">
         <v>7968</v>
@@ -20438,13 +20438,13 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>1182.14</v>
+        <v>1181.23</v>
       </c>
       <c r="D135" t="n">
-        <v>1173.45</v>
+        <v>1172.54</v>
       </c>
       <c r="E135" t="n">
-        <v>1190.82</v>
+        <v>1189.92</v>
       </c>
       <c r="F135" t="n">
         <v>6638</v>
@@ -20589,13 +20589,13 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>1180.47</v>
+        <v>1179.81</v>
       </c>
       <c r="D136" t="n">
-        <v>1174.4</v>
+        <v>1173.74</v>
       </c>
       <c r="E136" t="n">
-        <v>1186.55</v>
+        <v>1185.89</v>
       </c>
       <c r="F136" t="n">
         <v>23893</v>
@@ -20740,13 +20740,13 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>1179.58</v>
+        <v>1178.61</v>
       </c>
       <c r="D137" t="n">
-        <v>1173.67</v>
+        <v>1172.69</v>
       </c>
       <c r="E137" t="n">
-        <v>1185.49</v>
+        <v>1184.52</v>
       </c>
       <c r="F137" t="n">
         <v>32832</v>
@@ -20811,13 +20811,13 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>1179.16</v>
+        <v>1178.19</v>
       </c>
       <c r="D138" t="n">
-        <v>1167.95</v>
+        <v>1166.98</v>
       </c>
       <c r="E138" t="n">
-        <v>1190.37</v>
+        <v>1189.4</v>
       </c>
       <c r="F138" t="n">
         <v>3188</v>
@@ -20962,13 +20962,13 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>1178.17</v>
+        <v>1177.14</v>
       </c>
       <c r="D139" t="n">
-        <v>1168.35</v>
+        <v>1167.31</v>
       </c>
       <c r="E139" t="n">
-        <v>1188</v>
+        <v>1186.96</v>
       </c>
       <c r="F139" t="n">
         <v>6535</v>
@@ -21113,13 +21113,13 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>1175.25</v>
+        <v>1174.3</v>
       </c>
       <c r="D140" t="n">
-        <v>1164.82</v>
+        <v>1163.87</v>
       </c>
       <c r="E140" t="n">
-        <v>1185.68</v>
+        <v>1184.73</v>
       </c>
       <c r="F140" t="n">
         <v>5006</v>
@@ -21264,13 +21264,13 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>1172.89</v>
+        <v>1171.89</v>
       </c>
       <c r="D141" t="n">
-        <v>1166.67</v>
+        <v>1165.67</v>
       </c>
       <c r="E141" t="n">
-        <v>1179.1</v>
+        <v>1178.1</v>
       </c>
       <c r="F141" t="n">
         <v>22479</v>
@@ -21415,13 +21415,13 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>1171.83</v>
+        <v>1170.79</v>
       </c>
       <c r="D142" t="n">
-        <v>1164.42</v>
+        <v>1163.38</v>
       </c>
       <c r="E142" t="n">
-        <v>1179.25</v>
+        <v>1178.21</v>
       </c>
       <c r="F142" t="n">
         <v>16056</v>
@@ -21566,13 +21566,13 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>1171.24</v>
+        <v>1170.26</v>
       </c>
       <c r="D143" t="n">
-        <v>1165.33</v>
+        <v>1164.35</v>
       </c>
       <c r="E143" t="n">
-        <v>1177.16</v>
+        <v>1176.18</v>
       </c>
       <c r="F143" t="n">
         <v>17766</v>
@@ -21717,13 +21717,13 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>1170.93</v>
+        <v>1169.92</v>
       </c>
       <c r="D144" t="n">
-        <v>1165.42</v>
+        <v>1164.42</v>
       </c>
       <c r="E144" t="n">
-        <v>1176.43</v>
+        <v>1175.43</v>
       </c>
       <c r="F144" t="n">
         <v>38492</v>
@@ -21868,13 +21868,13 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>1167.67</v>
+        <v>1166.65</v>
       </c>
       <c r="D145" t="n">
-        <v>1159.59</v>
+        <v>1158.58</v>
       </c>
       <c r="E145" t="n">
-        <v>1175.74</v>
+        <v>1174.73</v>
       </c>
       <c r="F145" t="n">
         <v>10224</v>
@@ -22019,13 +22019,13 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>1166.88</v>
+        <v>1165.96</v>
       </c>
       <c r="D146" t="n">
-        <v>1159.18</v>
+        <v>1158.26</v>
       </c>
       <c r="E146" t="n">
-        <v>1174.57</v>
+        <v>1173.65</v>
       </c>
       <c r="F146" t="n">
         <v>7936</v>
@@ -22170,13 +22170,13 @@
         </is>
       </c>
       <c r="C147" t="n">
-        <v>1164.87</v>
+        <v>1163.86</v>
       </c>
       <c r="D147" t="n">
-        <v>1152.93</v>
+        <v>1151.92</v>
       </c>
       <c r="E147" t="n">
-        <v>1176.81</v>
+        <v>1175.8</v>
       </c>
       <c r="F147" t="n">
         <v>3777</v>
@@ -22321,13 +22321,13 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>1157.26</v>
+        <v>1156.15</v>
       </c>
       <c r="D148" t="n">
-        <v>1145.75</v>
+        <v>1144.64</v>
       </c>
       <c r="E148" t="n">
-        <v>1168.77</v>
+        <v>1167.65</v>
       </c>
       <c r="F148" t="n">
         <v>3231</v>
@@ -22472,13 +22472,13 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>1156.16</v>
+        <v>1155.21</v>
       </c>
       <c r="D149" t="n">
-        <v>1147.76</v>
+        <v>1146.81</v>
       </c>
       <c r="E149" t="n">
-        <v>1164.55</v>
+        <v>1163.6</v>
       </c>
       <c r="F149" t="n">
         <v>6837</v>
@@ -22623,13 +22623,13 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>1155.49</v>
+        <v>1154.42</v>
       </c>
       <c r="D150" t="n">
-        <v>1142.87</v>
+        <v>1141.8</v>
       </c>
       <c r="E150" t="n">
-        <v>1168.12</v>
+        <v>1167.05</v>
       </c>
       <c r="F150" t="n">
         <v>3585</v>
@@ -22774,13 +22774,13 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>1152.47</v>
+        <v>1151.46</v>
       </c>
       <c r="D151" t="n">
-        <v>1139.26</v>
+        <v>1138.25</v>
       </c>
       <c r="E151" t="n">
-        <v>1165.69</v>
+        <v>1164.68</v>
       </c>
       <c r="F151" t="n">
         <v>4155</v>
@@ -22925,13 +22925,13 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>1152.1</v>
+        <v>1151.11</v>
       </c>
       <c r="D152" t="n">
-        <v>1136.69</v>
+        <v>1135.71</v>
       </c>
       <c r="E152" t="n">
-        <v>1167.5</v>
+        <v>1166.51</v>
       </c>
       <c r="F152" t="n">
         <v>1679</v>
@@ -23076,13 +23076,13 @@
         </is>
       </c>
       <c r="C153" t="n">
-        <v>1150.17</v>
+        <v>1149.2</v>
       </c>
       <c r="D153" t="n">
-        <v>1137.86</v>
+        <v>1136.9</v>
       </c>
       <c r="E153" t="n">
-        <v>1162.47</v>
+        <v>1161.51</v>
       </c>
       <c r="F153" t="n">
         <v>2572</v>
@@ -23227,13 +23227,13 @@
         </is>
       </c>
       <c r="C154" t="n">
-        <v>1149.73</v>
+        <v>1148.71</v>
       </c>
       <c r="D154" t="n">
-        <v>1143.08</v>
+        <v>1142.06</v>
       </c>
       <c r="E154" t="n">
-        <v>1156.39</v>
+        <v>1155.37</v>
       </c>
       <c r="F154" t="n">
         <v>19402</v>
@@ -23378,13 +23378,13 @@
         </is>
       </c>
       <c r="C155" t="n">
-        <v>1149.29</v>
+        <v>1148.31</v>
       </c>
       <c r="D155" t="n">
-        <v>1140.03</v>
+        <v>1139.04</v>
       </c>
       <c r="E155" t="n">
-        <v>1158.56</v>
+        <v>1157.58</v>
       </c>
       <c r="F155" t="n">
         <v>7044</v>
@@ -23529,13 +23529,13 @@
         </is>
       </c>
       <c r="C156" t="n">
-        <v>1147.08</v>
+        <v>1146.15</v>
       </c>
       <c r="D156" t="n">
-        <v>1129.95</v>
+        <v>1129.01</v>
       </c>
       <c r="E156" t="n">
-        <v>1164.22</v>
+        <v>1163.28</v>
       </c>
       <c r="F156" t="n">
         <v>1295</v>
@@ -23680,13 +23680,13 @@
         </is>
       </c>
       <c r="C157" t="n">
-        <v>1143.92</v>
+        <v>1142.95</v>
       </c>
       <c r="D157" t="n">
-        <v>1134.02</v>
+        <v>1133.05</v>
       </c>
       <c r="E157" t="n">
-        <v>1153.82</v>
+        <v>1152.84</v>
       </c>
       <c r="F157" t="n">
         <v>4737</v>
@@ -23831,13 +23831,13 @@
         </is>
       </c>
       <c r="C158" t="n">
-        <v>1143.22</v>
+        <v>1142.24</v>
       </c>
       <c r="D158" t="n">
-        <v>1136.79</v>
+        <v>1135.81</v>
       </c>
       <c r="E158" t="n">
-        <v>1149.65</v>
+        <v>1148.68</v>
       </c>
       <c r="F158" t="n">
         <v>12297</v>
@@ -23982,13 +23982,13 @@
         </is>
       </c>
       <c r="C159" t="n">
-        <v>1141.62</v>
+        <v>1140.63</v>
       </c>
       <c r="D159" t="n">
-        <v>1134.89</v>
+        <v>1133.9</v>
       </c>
       <c r="E159" t="n">
-        <v>1148.35</v>
+        <v>1147.36</v>
       </c>
       <c r="F159" t="n">
         <v>19174</v>
@@ -24133,13 +24133,13 @@
         </is>
       </c>
       <c r="C160" t="n">
-        <v>1140.98</v>
+        <v>1140.02</v>
       </c>
       <c r="D160" t="n">
-        <v>1134.27</v>
+        <v>1133.3</v>
       </c>
       <c r="E160" t="n">
-        <v>1147.7</v>
+        <v>1146.73</v>
       </c>
       <c r="F160" t="n">
         <v>19367</v>
@@ -24284,13 +24284,13 @@
         </is>
       </c>
       <c r="C161" t="n">
-        <v>1138.64</v>
+        <v>1137.68</v>
       </c>
       <c r="D161" t="n">
-        <v>1127.67</v>
+        <v>1126.71</v>
       </c>
       <c r="E161" t="n">
-        <v>1149.61</v>
+        <v>1148.65</v>
       </c>
       <c r="F161" t="n">
         <v>4964</v>
@@ -24435,13 +24435,13 @@
         </is>
       </c>
       <c r="C162" t="n">
-        <v>1136.66</v>
+        <v>1135.67</v>
       </c>
       <c r="D162" t="n">
-        <v>1127.75</v>
+        <v>1126.76</v>
       </c>
       <c r="E162" t="n">
-        <v>1145.56</v>
+        <v>1144.58</v>
       </c>
       <c r="F162" t="n">
         <v>7366</v>
@@ -24586,13 +24586,13 @@
         </is>
       </c>
       <c r="C163" t="n">
-        <v>1136.24</v>
+        <v>1135.51</v>
       </c>
       <c r="D163" t="n">
-        <v>1126.73</v>
+        <v>1126</v>
       </c>
       <c r="E163" t="n">
-        <v>1145.75</v>
+        <v>1145.02</v>
       </c>
       <c r="F163" t="n">
         <v>8925</v>
@@ -24737,13 +24737,13 @@
         </is>
       </c>
       <c r="C164" t="n">
-        <v>1131.16</v>
+        <v>1130.13</v>
       </c>
       <c r="D164" t="n">
-        <v>1122.31</v>
+        <v>1121.28</v>
       </c>
       <c r="E164" t="n">
-        <v>1140.01</v>
+        <v>1138.98</v>
       </c>
       <c r="F164" t="n">
         <v>11118</v>
@@ -24888,13 +24888,13 @@
         </is>
       </c>
       <c r="C165" t="n">
-        <v>1129.3</v>
+        <v>1128.35</v>
       </c>
       <c r="D165" t="n">
-        <v>1121.88</v>
+        <v>1120.92</v>
       </c>
       <c r="E165" t="n">
-        <v>1136.73</v>
+        <v>1135.77</v>
       </c>
       <c r="F165" t="n">
         <v>20685</v>
@@ -25039,13 +25039,13 @@
         </is>
       </c>
       <c r="C166" t="n">
-        <v>1128.56</v>
+        <v>1127.55</v>
       </c>
       <c r="D166" t="n">
-        <v>1122.16</v>
+        <v>1121.15</v>
       </c>
       <c r="E166" t="n">
-        <v>1134.95</v>
+        <v>1133.94</v>
       </c>
       <c r="F166" t="n">
         <v>20118</v>
@@ -25190,13 +25190,13 @@
         </is>
       </c>
       <c r="C167" t="n">
-        <v>1127.4</v>
+        <v>1126.4</v>
       </c>
       <c r="D167" t="n">
-        <v>1115.24</v>
+        <v>1114.24</v>
       </c>
       <c r="E167" t="n">
-        <v>1139.56</v>
+        <v>1138.56</v>
       </c>
       <c r="F167" t="n">
         <v>2921</v>
@@ -25341,13 +25341,13 @@
         </is>
       </c>
       <c r="C168" t="n">
-        <v>1127.01</v>
+        <v>1125.99</v>
       </c>
       <c r="D168" t="n">
-        <v>1111.33</v>
+        <v>1110.32</v>
       </c>
       <c r="E168" t="n">
-        <v>1142.68</v>
+        <v>1141.67</v>
       </c>
       <c r="F168" t="n">
         <v>1785</v>
@@ -25492,13 +25492,13 @@
         </is>
       </c>
       <c r="C169" t="n">
-        <v>1121.05</v>
+        <v>1120.08</v>
       </c>
       <c r="D169" t="n">
-        <v>1110.05</v>
+        <v>1109.08</v>
       </c>
       <c r="E169" t="n">
-        <v>1132.05</v>
+        <v>1131.09</v>
       </c>
       <c r="F169" t="n">
         <v>5182</v>
@@ -25643,13 +25643,13 @@
         </is>
       </c>
       <c r="C170" t="n">
-        <v>1119.16</v>
+        <v>1118.22</v>
       </c>
       <c r="D170" t="n">
-        <v>1100.95</v>
+        <v>1100</v>
       </c>
       <c r="E170" t="n">
-        <v>1137.38</v>
+        <v>1136.44</v>
       </c>
       <c r="F170" t="n">
         <v>1143</v>
@@ -25794,13 +25794,13 @@
         </is>
       </c>
       <c r="C171" t="n">
-        <v>1114.7</v>
+        <v>1113.73</v>
       </c>
       <c r="D171" t="n">
-        <v>1105.51</v>
+        <v>1104.55</v>
       </c>
       <c r="E171" t="n">
-        <v>1123.88</v>
+        <v>1122.92</v>
       </c>
       <c r="F171" t="n">
         <v>6923</v>
@@ -25941,36 +25941,36 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>smollm2-1.7b-instruct</t>
+          <t>gemma-1.1-2b-it</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>1114.44</v>
+        <v>1113.7</v>
       </c>
       <c r="D172" t="n">
-        <v>1100.02</v>
+        <v>1105.96</v>
       </c>
       <c r="E172" t="n">
-        <v>1128.86</v>
+        <v>1121.43</v>
       </c>
       <c r="F172" t="n">
-        <v>2199</v>
+        <v>10854</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>HuggingFace</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
+          <t>Gemma license</t>
         </is>
       </c>
       <c r="I172" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="J172" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="K172" t="inlineStr">
         <is>
@@ -25983,22 +25983,22 @@
         </is>
       </c>
       <c r="M172" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="N172" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="O172" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="P172" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="Q172" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="R172" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="S172" s="6" t="inlineStr">
         <is>
@@ -26092,36 +26092,36 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>gemma-1.1-2b-it</t>
+          <t>smollm2-1.7b-instruct</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>1114.37</v>
+        <v>1113.48</v>
       </c>
       <c r="D173" t="n">
-        <v>1106.63</v>
+        <v>1099.06</v>
       </c>
       <c r="E173" t="n">
-        <v>1122.1</v>
+        <v>1127.9</v>
       </c>
       <c r="F173" t="n">
-        <v>10854</v>
+        <v>2199</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>HuggingFace</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Gemma license</t>
+          <t>Apache 2.0</t>
         </is>
       </c>
       <c r="I173" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="J173" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="K173" t="inlineStr">
         <is>
@@ -26134,22 +26134,22 @@
         </is>
       </c>
       <c r="M173" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="N173" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="O173" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="P173" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="Q173" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="R173" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="S173" s="6" t="inlineStr">
         <is>
@@ -26247,13 +26247,13 @@
         </is>
       </c>
       <c r="C174" t="n">
-        <v>1111.45</v>
+        <v>1110.5</v>
       </c>
       <c r="D174" t="n">
-        <v>1103.58</v>
+        <v>1102.63</v>
       </c>
       <c r="E174" t="n">
-        <v>1119.32</v>
+        <v>1118.38</v>
       </c>
       <c r="F174" t="n">
         <v>8045</v>
@@ -26398,13 +26398,13 @@
         </is>
       </c>
       <c r="C175" t="n">
-        <v>1109.67</v>
+        <v>1108.71</v>
       </c>
       <c r="D175" t="n">
-        <v>1100.37</v>
+        <v>1099.41</v>
       </c>
       <c r="E175" t="n">
-        <v>1118.97</v>
+        <v>1118.01</v>
       </c>
       <c r="F175" t="n">
         <v>8977</v>
@@ -26549,13 +26549,13 @@
         </is>
       </c>
       <c r="C176" t="n">
-        <v>1108.27</v>
+        <v>1107.26</v>
       </c>
       <c r="D176" t="n">
-        <v>1101.22</v>
+        <v>1100.2</v>
       </c>
       <c r="E176" t="n">
-        <v>1115.33</v>
+        <v>1114.32</v>
       </c>
       <c r="F176" t="n">
         <v>14148</v>
@@ -26700,13 +26700,13 @@
         </is>
       </c>
       <c r="C177" t="n">
-        <v>1091.84</v>
+        <v>1091.11</v>
       </c>
       <c r="D177" t="n">
-        <v>1080.32</v>
+        <v>1079.59</v>
       </c>
       <c r="E177" t="n">
-        <v>1103.36</v>
+        <v>1102.63</v>
       </c>
       <c r="F177" t="n">
         <v>4780</v>
@@ -26851,13 +26851,13 @@
         </is>
       </c>
       <c r="C178" t="n">
-        <v>1090.23</v>
+        <v>1089.28</v>
       </c>
       <c r="D178" t="n">
-        <v>1080.88</v>
+        <v>1079.92</v>
       </c>
       <c r="E178" t="n">
-        <v>1099.58</v>
+        <v>1098.63</v>
       </c>
       <c r="F178" t="n">
         <v>7597</v>
@@ -27002,13 +27002,13 @@
         </is>
       </c>
       <c r="C179" t="n">
-        <v>1074.74</v>
+        <v>1073.66</v>
       </c>
       <c r="D179" t="n">
-        <v>1063.54</v>
+        <v>1062.47</v>
       </c>
       <c r="E179" t="n">
-        <v>1085.93</v>
+        <v>1084.86</v>
       </c>
       <c r="F179" t="n">
         <v>6328</v>
@@ -27153,13 +27153,13 @@
         </is>
       </c>
       <c r="C180" t="n">
-        <v>1070.47</v>
+        <v>1069.5</v>
       </c>
       <c r="D180" t="n">
-        <v>1060.51</v>
+        <v>1059.54</v>
       </c>
       <c r="E180" t="n">
-        <v>1080.42</v>
+        <v>1079.45</v>
       </c>
       <c r="F180" t="n">
         <v>6965</v>
@@ -27304,13 +27304,13 @@
         </is>
       </c>
       <c r="C181" t="n">
-        <v>1067.37</v>
+        <v>1066.57</v>
       </c>
       <c r="D181" t="n">
-        <v>1055.84</v>
+        <v>1055.04</v>
       </c>
       <c r="E181" t="n">
-        <v>1078.9</v>
+        <v>1078.09</v>
       </c>
       <c r="F181" t="n">
         <v>5745</v>
@@ -27455,13 +27455,13 @@
         </is>
       </c>
       <c r="C182" t="n">
-        <v>1065.96</v>
+        <v>1065.07</v>
       </c>
       <c r="D182" t="n">
-        <v>1050.66</v>
+        <v>1049.78</v>
       </c>
       <c r="E182" t="n">
-        <v>1081.25</v>
+        <v>1080.37</v>
       </c>
       <c r="F182" t="n">
         <v>1743</v>
@@ -27606,13 +27606,13 @@
         </is>
       </c>
       <c r="C183" t="n">
-        <v>1061.81</v>
+        <v>1060.92</v>
       </c>
       <c r="D183" t="n">
-        <v>1049.77</v>
+        <v>1048.88</v>
       </c>
       <c r="E183" t="n">
-        <v>1073.85</v>
+        <v>1072.96</v>
       </c>
       <c r="F183" t="n">
         <v>3924</v>
@@ -27757,13 +27757,13 @@
         </is>
       </c>
       <c r="C184" t="n">
-        <v>1056.1</v>
+        <v>1055.12</v>
       </c>
       <c r="D184" t="n">
-        <v>1044.41</v>
+        <v>1043.43</v>
       </c>
       <c r="E184" t="n">
-        <v>1067.79</v>
+        <v>1066.81</v>
       </c>
       <c r="F184" t="n">
         <v>4658</v>
@@ -27908,13 +27908,13 @@
         </is>
       </c>
       <c r="C185" t="n">
-        <v>1041.32</v>
+        <v>1040.39</v>
       </c>
       <c r="D185" t="n">
-        <v>1029.87</v>
+        <v>1028.94</v>
       </c>
       <c r="E185" t="n">
-        <v>1052.78</v>
+        <v>1051.85</v>
       </c>
       <c r="F185" t="n">
         <v>4845</v>
@@ -28059,13 +28059,13 @@
         </is>
       </c>
       <c r="C186" t="n">
-        <v>1024.2</v>
+        <v>1023.23</v>
       </c>
       <c r="D186" t="n">
-        <v>1010.56</v>
+        <v>1009.59</v>
       </c>
       <c r="E186" t="n">
-        <v>1037.84</v>
+        <v>1036.87</v>
       </c>
       <c r="F186" t="n">
         <v>2658</v>
@@ -28210,13 +28210,13 @@
         </is>
       </c>
       <c r="C187" t="n">
-        <v>1022.05</v>
+        <v>1021.15</v>
       </c>
       <c r="D187" t="n">
-        <v>1011.11</v>
+        <v>1010.21</v>
       </c>
       <c r="E187" t="n">
-        <v>1032.99</v>
+        <v>1032.08</v>
       </c>
       <c r="F187" t="n">
         <v>6310</v>
@@ -28361,13 +28361,13 @@
         </is>
       </c>
       <c r="C188" t="n">
-        <v>995.624</v>
+        <v>994.631</v>
       </c>
       <c r="D188" t="n">
-        <v>982.992</v>
+        <v>982</v>
       </c>
       <c r="E188" t="n">
-        <v>1008.26</v>
+        <v>1007.26</v>
       </c>
       <c r="F188" t="n">
         <v>4914</v>
@@ -28512,13 +28512,13 @@
         </is>
       </c>
       <c r="C189" t="n">
-        <v>991.314</v>
+        <v>990.405</v>
       </c>
       <c r="D189" t="n">
-        <v>978.869</v>
+        <v>977.962</v>
       </c>
       <c r="E189" t="n">
-        <v>1003.76</v>
+        <v>1002.85</v>
       </c>
       <c r="F189" t="n">
         <v>4203</v>
@@ -28663,13 +28663,13 @@
         </is>
       </c>
       <c r="C190" t="n">
-        <v>980.034</v>
+        <v>979.199</v>
       </c>
       <c r="D190" t="n">
-        <v>966.412</v>
+        <v>965.578</v>
       </c>
       <c r="E190" t="n">
-        <v>993.657</v>
+        <v>992.8200000000001</v>
       </c>
       <c r="F190" t="n">
         <v>3412</v>
@@ -28814,13 +28814,13 @@
         </is>
       </c>
       <c r="C191" t="n">
-        <v>972.085</v>
+        <v>971.3049999999999</v>
       </c>
       <c r="D191" t="n">
-        <v>956.16</v>
+        <v>955.383</v>
       </c>
       <c r="E191" t="n">
-        <v>988.01</v>
+        <v>987.227</v>
       </c>
       <c r="F191" t="n">
         <v>2391</v>
@@ -28965,13 +28965,13 @@
         </is>
       </c>
       <c r="C192" t="n">
-        <v>952.633</v>
+        <v>951.67</v>
       </c>
       <c r="D192" t="n">
-        <v>939.806</v>
+        <v>938.8440000000001</v>
       </c>
       <c r="E192" t="n">
-        <v>965.46</v>
+        <v>964.495</v>
       </c>
       <c r="F192" t="n">
         <v>3287</v>
@@ -29260,7 +29260,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -29369,7 +29369,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -29474,7 +29474,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -29544,7 +29544,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -29579,7 +29579,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -29649,7 +29649,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -29942,7 +29942,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>deepseek-v3.2-exp</t>
+          <t>deepseek-v3.2</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -29965,14 +29965,14 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>qwen3-235b-a22b-instruct-2507</t>
+          <t>deepseek-v3.2-exp</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>235</v>
+        <v>685</v>
       </c>
       <c r="C11" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -29988,14 +29988,14 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>deepseek-v3.2</t>
+          <t>qwen3-235b-a22b-instruct-2507</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>685</v>
+        <v>235</v>
       </c>
       <c r="C12" t="n">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -30057,14 +30057,14 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>deepseek-v3.1</t>
+          <t>qwen3.5-122b-a10b</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>685</v>
+        <v>125</v>
       </c>
       <c r="C15" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -30080,14 +30080,14 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>kimi-k2-0905-preview</t>
+          <t>deepseek-v3.1</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1000</v>
+        <v>685</v>
       </c>
       <c r="C16" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -30096,21 +30096,21 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>artificial_analysis</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>qwen3.5-122b-a10b</t>
+          <t>kimi-k2-0905-preview</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>125</v>
+        <v>1000</v>
       </c>
       <c r="C17" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -30119,21 +30119,21 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>artificial_analysis</t>
+          <t>override</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>mistral-large-3</t>
+          <t>kimi-k2-0711-preview</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>675</v>
+        <v>1000</v>
       </c>
       <c r="C18" t="n">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -30142,7 +30142,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>artificial_analysis</t>
+          <t>override</t>
         </is>
       </c>
     </row>
@@ -30172,14 +30172,14 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>kimi-k2-0711-preview</t>
+          <t>mistral-large-3</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1000</v>
+        <v>675</v>
       </c>
       <c r="C20" t="n">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -30188,14 +30188,14 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>artificial_analysis</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>deepseek-v3.1-terminus</t>
+          <t>deepseek-v3.1-terminus-thinking</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -30218,14 +30218,14 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>qwen3-vl-235b-a22b-instruct</t>
+          <t>deepseek-v3.1-terminus</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>235</v>
+        <v>685</v>
       </c>
       <c r="C22" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -30241,14 +30241,14 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>deepseek-v3.1-terminus-thinking</t>
+          <t>qwen3-vl-235b-a22b-instruct</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>685</v>
+        <v>235</v>
       </c>
       <c r="C23" t="n">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -30425,14 +30425,14 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>deepseek-r1</t>
+          <t>qwen3.5-35b-a3b</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>685</v>
+        <v>36</v>
       </c>
       <c r="C31" t="n">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -30448,14 +30448,14 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>qwen3.5-35b-a3b</t>
+          <t>deepseek-r1</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>36</v>
+        <v>685</v>
       </c>
       <c r="C32" t="n">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -30793,18 +30793,18 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>minimax-m1</t>
+          <t>gemma-3-27b-it</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>456</v>
+        <v>27.4</v>
       </c>
       <c r="C47" t="n">
-        <v>45.9</v>
+        <v>27.4</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>moe</t>
+          <t>dense</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -30816,18 +30816,18 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>gemma-3-27b-it</t>
+          <t>minimax-m1</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>27.4</v>
+        <v>456</v>
       </c>
       <c r="C48" t="n">
-        <v>27.4</v>
+        <v>45.9</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>dense</t>
+          <t>moe</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -31015,14 +31015,14 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>ling-flash-2.0</t>
+          <t>minimax-m2</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>103</v>
+        <v>230</v>
       </c>
       <c r="C57" t="n">
-        <v>6.1</v>
+        <v>10</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -31038,18 +31038,18 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>minimax-m2</t>
+          <t>qwen3-32b</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>230</v>
+        <v>32.8</v>
       </c>
       <c r="C58" t="n">
-        <v>10</v>
+        <v>32.8</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>moe</t>
+          <t>dense</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -31061,14 +31061,14 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>qwen3-32b</t>
+          <t>llama-3.1-nemotron-ultra-253b-v1</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>32.8</v>
+        <v>253</v>
       </c>
       <c r="C59" t="n">
-        <v>32.8</v>
+        <v>253</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -31084,18 +31084,18 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>llama-3.1-nemotron-ultra-253b-v1</t>
+          <t>ling-flash-2.0</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>253</v>
+        <v>103</v>
       </c>
       <c r="C60" t="n">
-        <v>253</v>
+        <v>6.1</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>dense</t>
+          <t>moe</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -31107,14 +31107,14 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>gemma-3-12b-it</t>
+          <t>nvidia-llama-3.3-nemotron-super-49b-v1.5</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>12.2</v>
+        <v>49</v>
       </c>
       <c r="C61" t="n">
-        <v>12.2</v>
+        <v>49</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -31130,14 +31130,14 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>nvidia-llama-3.3-nemotron-super-49b-v1.5</t>
+          <t>gemma-3-12b-it</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>49</v>
+        <v>12.2</v>
       </c>
       <c r="C62" t="n">
-        <v>49</v>
+        <v>12.2</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -31245,18 +31245,18 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>molmo-2-8b</t>
+          <t>qwen3-30b-a3b</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>8.699999999999999</v>
+        <v>30.5</v>
       </c>
       <c r="C67" t="n">
-        <v>8.699999999999999</v>
+        <v>3.3</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>dense</t>
+          <t>moe</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -31268,23 +31268,23 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>qwen3-30b-a3b</t>
+          <t>llama-3.3-nemotron-49b-super-v1</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>30.5</v>
+        <v>49</v>
       </c>
       <c r="C68" t="n">
-        <v>3.3</v>
+        <v>49</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>moe</t>
+          <t>dense</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>artificial_analysis</t>
+          <t>name_parsing</t>
         </is>
       </c>
     </row>
@@ -31314,14 +31314,14 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>llama-3.3-nemotron-49b-super-v1</t>
+          <t>molmo-2-8b</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>49</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="C70" t="n">
-        <v>49</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -31330,7 +31330,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>artificial_analysis</t>
         </is>
       </c>
     </row>
@@ -31475,38 +31475,38 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>qwen-max-0919</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr"/>
-      <c r="C77" t="inlineStr"/>
-      <c r="D77" t="inlineStr"/>
+          <t>gpt-oss-20b</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>21</v>
+      </c>
+      <c r="C77" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>override</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>gpt-oss-20b</t>
-        </is>
-      </c>
-      <c r="B78" t="n">
-        <v>21</v>
-      </c>
-      <c r="C78" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+          <t>qwen-max-0919</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr"/>
+      <c r="C78" t="inlineStr"/>
+      <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -31812,14 +31812,14 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>llama-3.1-tulu-3-70b</t>
+          <t>ibm-granite-h-small</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="C92" t="n">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -31828,21 +31828,21 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>override</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>ibm-granite-h-small</t>
+          <t>olmo-3.1-32b-think</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>8</v>
+        <v>32.2</v>
       </c>
       <c r="C93" t="n">
-        <v>8</v>
+        <v>32.2</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -31851,21 +31851,21 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>artificial_analysis</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>llama-3.1-nemotron-51b-instruct</t>
+          <t>llama-3.1-tulu-3-70b</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="C94" t="n">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -31881,14 +31881,14 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>olmo-3.1-32b-think</t>
+          <t>llama-3.1-nemotron-51b-instruct</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>32.2</v>
+        <v>51</v>
       </c>
       <c r="C95" t="n">
-        <v>32.2</v>
+        <v>51</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -31897,7 +31897,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>artificial_analysis</t>
+          <t>name_parsing</t>
         </is>
       </c>
     </row>
@@ -33628,14 +33628,14 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>smollm2-1.7b-instruct</t>
+          <t>gemma-1.1-2b-it</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="C172" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -33651,14 +33651,14 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>gemma-1.1-2b-it</t>
+          <t>smollm2-1.7b-instruct</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="C173" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>

--- a/arena_enrichment/output/arena_leaderboard_enriched.xlsx
+++ b/arena_enrichment/output/arena_leaderboard_enriched.xlsx
@@ -675,16 +675,16 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>1456.58</v>
+        <v>1456.41</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1450.55</v>
+        <v>1450.39</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1462.6</v>
+        <v>1462.44</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>10991</v>
+        <v>11023</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
@@ -826,16 +826,16 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>1453.11</v>
+        <v>1452.81</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1447.83</v>
+        <v>1447.54</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1458.39</v>
+        <v>1458.08</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>16231</v>
+        <v>16269</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
@@ -977,16 +977,16 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>1451.6</v>
+        <v>1451.77</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1445.43</v>
+        <v>1445.62</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1457.76</v>
+        <v>1457.93</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>10225</v>
+        <v>10272</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
@@ -1128,13 +1128,13 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>1442.31</v>
+        <v>1442.28</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1436.22</v>
+        <v>1436.2</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1448.39</v>
+        <v>1448.36</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>12421</v>
@@ -1282,13 +1282,13 @@
         <v>1432.45</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1425.9</v>
+        <v>1425.89</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1439.01</v>
+        <v>1439</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>8472</v>
+        <v>8473</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
@@ -1430,16 +1430,16 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>1429.8</v>
+        <v>1429.83</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>1426.11</v>
+        <v>1426.14</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1433.49</v>
+        <v>1433.53</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>41979</v>
+        <v>42016</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
@@ -1581,13 +1581,13 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>1425.97</v>
+        <v>1425.98</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>1422.03</v>
+        <v>1422.04</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1429.9</v>
+        <v>1429.91</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>36415</v>
@@ -1735,7 +1735,7 @@
         <v>1424.82</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1418.3</v>
+        <v>1418.31</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>1431.34</v>
@@ -1883,16 +1883,16 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>1424.04</v>
+        <v>1424.05</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>1419.98</v>
+        <v>1420</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1428.09</v>
+        <v>1428.1</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>36698</v>
+        <v>36746</v>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
@@ -2034,13 +2034,13 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>1423.54</v>
+        <v>1423.55</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>1417.15</v>
+        <v>1417.16</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1429.94</v>
+        <v>1429.95</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>12186</v>
@@ -2185,16 +2185,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1422.03</v>
+        <v>1422.02</v>
       </c>
       <c r="D12" t="n">
         <v>1419.14</v>
       </c>
       <c r="E12" t="n">
-        <v>1424.92</v>
+        <v>1424.91</v>
       </c>
       <c r="F12" t="n">
-        <v>77979</v>
+        <v>78018</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -2336,16 +2336,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1421.63</v>
+        <v>1421.61</v>
       </c>
       <c r="D13" t="n">
-        <v>1417.47</v>
+        <v>1417.46</v>
       </c>
       <c r="E13" t="n">
-        <v>1425.79</v>
+        <v>1425.77</v>
       </c>
       <c r="F13" t="n">
-        <v>31230</v>
+        <v>31259</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -2487,13 +2487,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1420.87</v>
+        <v>1420.88</v>
       </c>
       <c r="D14" t="n">
-        <v>1415.25</v>
+        <v>1415.26</v>
       </c>
       <c r="E14" t="n">
-        <v>1426.49</v>
+        <v>1426.5</v>
       </c>
       <c r="F14" t="n">
         <v>18855</v>
@@ -2634,36 +2634,36 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>qwen3.5-122b-a10b</t>
+          <t>deepseek-v3.1</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1417.96</v>
       </c>
       <c r="D15" t="n">
-        <v>1410.68</v>
+        <v>1411.97</v>
       </c>
       <c r="E15" t="n">
-        <v>1425.25</v>
+        <v>1423.95</v>
       </c>
       <c r="F15" t="n">
-        <v>6630</v>
+        <v>15170</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alibaba</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>125</v>
+        <v>685</v>
       </c>
       <c r="J15" t="n">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -2676,22 +2676,22 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>250</v>
+        <v>1370</v>
       </c>
       <c r="N15" t="n">
-        <v>312.5</v>
+        <v>1712.5</v>
       </c>
       <c r="O15" t="n">
-        <v>125</v>
+        <v>685</v>
       </c>
       <c r="P15" t="n">
-        <v>156.2</v>
+        <v>856.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>62.5</v>
+        <v>342.5</v>
       </c>
       <c r="R15" t="n">
-        <v>78.09999999999999</v>
+        <v>428.1</v>
       </c>
       <c r="S15" s="5" t="inlineStr">
         <is>
@@ -2703,9 +2703,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="U15" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="U15" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="V15" s="5" t="inlineStr">
@@ -2718,9 +2718,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="X15" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="X15" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="Y15" s="5" t="inlineStr">
@@ -2733,9 +2733,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AA15" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AA15" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AB15" s="5" t="inlineStr">
@@ -2743,14 +2743,14 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AC15" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AD15" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AC15" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD15" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AE15" s="5" t="inlineStr">
@@ -2758,14 +2758,14 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AF15" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AG15" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AF15" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AG15" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
@@ -2775,7 +2775,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>B200 SXM</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
     </row>
@@ -2785,36 +2785,36 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>deepseek-v3.1</t>
+          <t>qwen3.5-122b-a10b</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1417.96</v>
+        <v>1417.58</v>
       </c>
       <c r="D16" t="n">
-        <v>1411.97</v>
+        <v>1410.32</v>
       </c>
       <c r="E16" t="n">
-        <v>1423.95</v>
+        <v>1424.83</v>
       </c>
       <c r="F16" t="n">
-        <v>15170</v>
+        <v>6688</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>DeepSeek</t>
+          <t>Alibaba</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Apache 2.0</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>685</v>
+        <v>125</v>
       </c>
       <c r="J16" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -2827,22 +2827,22 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>1370</v>
+        <v>250</v>
       </c>
       <c r="N16" t="n">
-        <v>1712.5</v>
+        <v>312.5</v>
       </c>
       <c r="O16" t="n">
-        <v>685</v>
+        <v>125</v>
       </c>
       <c r="P16" t="n">
-        <v>856.2</v>
+        <v>156.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>342.5</v>
+        <v>62.5</v>
       </c>
       <c r="R16" t="n">
-        <v>428.1</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="S16" s="5" t="inlineStr">
         <is>
@@ -2854,9 +2854,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="U16" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="U16" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="V16" s="5" t="inlineStr">
@@ -2869,9 +2869,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="X16" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="X16" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Y16" s="5" t="inlineStr">
@@ -2884,9 +2884,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AA16" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AA16" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AB16" s="5" t="inlineStr">
@@ -2894,14 +2894,14 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AC16" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AD16" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AC16" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AD16" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AE16" s="5" t="inlineStr">
@@ -2909,14 +2909,14 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AF16" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AG16" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AF16" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AG16" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
@@ -2926,7 +2926,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>B200 SXM</t>
         </is>
       </c>
     </row>
@@ -2940,13 +2940,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1417.4</v>
+        <v>1417.39</v>
       </c>
       <c r="D17" t="n">
-        <v>1410.93</v>
+        <v>1410.92</v>
       </c>
       <c r="E17" t="n">
-        <v>1423.87</v>
+        <v>1423.86</v>
       </c>
       <c r="F17" t="n">
         <v>11954</v>
@@ -3091,13 +3091,13 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1416.95</v>
+        <v>1416.93</v>
       </c>
       <c r="D18" t="n">
-        <v>1412.12</v>
+        <v>1412.1</v>
       </c>
       <c r="E18" t="n">
-        <v>1421.78</v>
+        <v>1421.76</v>
       </c>
       <c r="F18" t="n">
         <v>28137</v>
@@ -3393,16 +3393,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1416.54</v>
+        <v>1416.4</v>
       </c>
       <c r="D20" t="n">
-        <v>1412.52</v>
+        <v>1412.38</v>
       </c>
       <c r="E20" t="n">
-        <v>1420.56</v>
+        <v>1420.42</v>
       </c>
       <c r="F20" t="n">
-        <v>33352</v>
+        <v>33411</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -3544,10 +3544,10 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1416.26</v>
+        <v>1416.27</v>
       </c>
       <c r="D21" t="n">
-        <v>1406.34</v>
+        <v>1406.35</v>
       </c>
       <c r="E21" t="n">
         <v>1426.18</v>
@@ -3846,7 +3846,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1415.31</v>
+        <v>1415.32</v>
       </c>
       <c r="D23" t="n">
         <v>1408.87</v>
@@ -3997,13 +3997,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1410.72</v>
+        <v>1410.73</v>
       </c>
       <c r="D24" t="n">
-        <v>1405.86</v>
+        <v>1405.88</v>
       </c>
       <c r="E24" t="n">
-        <v>1415.57</v>
+        <v>1415.59</v>
       </c>
       <c r="F24" t="n">
         <v>24669</v>
@@ -4148,16 +4148,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1406.56</v>
+        <v>1406.36</v>
       </c>
       <c r="D25" t="n">
-        <v>1399.32</v>
+        <v>1399.16</v>
       </c>
       <c r="E25" t="n">
-        <v>1413.79</v>
+        <v>1413.57</v>
       </c>
       <c r="F25" t="n">
-        <v>6731</v>
+        <v>6777</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -4299,16 +4299,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1405.13</v>
+        <v>1405.23</v>
       </c>
       <c r="D26" t="n">
-        <v>1399.21</v>
+        <v>1399.33</v>
       </c>
       <c r="E26" t="n">
-        <v>1411.04</v>
+        <v>1411.14</v>
       </c>
       <c r="F26" t="n">
-        <v>11697</v>
+        <v>11752</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -4450,10 +4450,10 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1402.46</v>
+        <v>1402.47</v>
       </c>
       <c r="D27" t="n">
-        <v>1397.98</v>
+        <v>1397.99</v>
       </c>
       <c r="E27" t="n">
         <v>1406.94</v>
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1401.27</v>
+        <v>1401.28</v>
       </c>
       <c r="D28" t="n">
         <v>1396.52</v>
@@ -4752,13 +4752,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1400.52</v>
+        <v>1400.54</v>
       </c>
       <c r="D29" t="n">
-        <v>1394.17</v>
+        <v>1394.18</v>
       </c>
       <c r="E29" t="n">
-        <v>1406.88</v>
+        <v>1406.9</v>
       </c>
       <c r="F29" t="n">
         <v>11535</v>
@@ -4903,13 +4903,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1399.05</v>
+        <v>1399.06</v>
       </c>
       <c r="D30" t="n">
-        <v>1392.55</v>
+        <v>1392.57</v>
       </c>
       <c r="E30" t="n">
-        <v>1405.55</v>
+        <v>1405.56</v>
       </c>
       <c r="F30" t="n">
         <v>9137</v>
@@ -5054,16 +5054,16 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1398.94</v>
+        <v>1399.04</v>
       </c>
       <c r="D31" t="n">
-        <v>1391.78</v>
+        <v>1391.91</v>
       </c>
       <c r="E31" t="n">
-        <v>1406.1</v>
+        <v>1406.17</v>
       </c>
       <c r="F31" t="n">
-        <v>6983</v>
+        <v>7042</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -5208,7 +5208,7 @@
         <v>1397.55</v>
       </c>
       <c r="D32" t="n">
-        <v>1392.69</v>
+        <v>1392.7</v>
       </c>
       <c r="E32" t="n">
         <v>1402.4</v>
@@ -5356,13 +5356,13 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1395.52</v>
+        <v>1395.53</v>
       </c>
       <c r="D33" t="n">
-        <v>1388.77</v>
+        <v>1388.78</v>
       </c>
       <c r="E33" t="n">
-        <v>1402.27</v>
+        <v>1402.28</v>
       </c>
       <c r="F33" t="n">
         <v>8081</v>
@@ -5510,10 +5510,10 @@
         <v>1394.33</v>
       </c>
       <c r="D34" t="n">
-        <v>1390.48</v>
+        <v>1390.49</v>
       </c>
       <c r="E34" t="n">
-        <v>1398.17</v>
+        <v>1398.18</v>
       </c>
       <c r="F34" t="n">
         <v>46197</v>
@@ -5658,16 +5658,16 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1391.94</v>
+        <v>1391.92</v>
       </c>
       <c r="D35" t="n">
-        <v>1387.54</v>
+        <v>1387.53</v>
       </c>
       <c r="E35" t="n">
-        <v>1396.35</v>
+        <v>1396.32</v>
       </c>
       <c r="F35" t="n">
-        <v>25505</v>
+        <v>25545</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -5809,13 +5809,13 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1387.77</v>
+        <v>1387.75</v>
       </c>
       <c r="D36" t="n">
-        <v>1381.52</v>
+        <v>1381.5</v>
       </c>
       <c r="E36" t="n">
-        <v>1394.02</v>
+        <v>1394</v>
       </c>
       <c r="F36" t="n">
         <v>11256</v>
@@ -5960,16 +5960,16 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1387.19</v>
+        <v>1387.55</v>
       </c>
       <c r="D37" t="n">
-        <v>1381.68</v>
+        <v>1382.05</v>
       </c>
       <c r="E37" t="n">
-        <v>1392.7</v>
+        <v>1393.05</v>
       </c>
       <c r="F37" t="n">
-        <v>13845</v>
+        <v>13890</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -6114,7 +6114,7 @@
         <v>1386.89</v>
       </c>
       <c r="D38" t="n">
-        <v>1381.98</v>
+        <v>1381.97</v>
       </c>
       <c r="E38" t="n">
         <v>1391.8</v>
@@ -6262,16 +6262,16 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1385.85</v>
+        <v>1385.82</v>
       </c>
       <c r="D39" t="n">
-        <v>1380.62</v>
+        <v>1380.59</v>
       </c>
       <c r="E39" t="n">
-        <v>1391.09</v>
+        <v>1391.06</v>
       </c>
       <c r="F39" t="n">
-        <v>17581</v>
+        <v>17582</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -6413,13 +6413,13 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1382.93</v>
+        <v>1382.94</v>
       </c>
       <c r="D40" t="n">
         <v>1378.09</v>
       </c>
       <c r="E40" t="n">
-        <v>1387.78</v>
+        <v>1387.79</v>
       </c>
       <c r="F40" t="n">
         <v>24134</v>
@@ -6570,7 +6570,7 @@
         <v>1366.7</v>
       </c>
       <c r="E41" t="n">
-        <v>1389.1</v>
+        <v>1389.09</v>
       </c>
       <c r="F41" t="n">
         <v>2861</v>
@@ -6711,24 +6711,24 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>trinity-large</t>
+          <t>qwen3-235b-a22b</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1375.51</v>
+        <v>1374.53</v>
       </c>
       <c r="D42" t="n">
-        <v>1368.46</v>
+        <v>1369.86</v>
       </c>
       <c r="E42" t="n">
-        <v>1382.56</v>
+        <v>1379.21</v>
       </c>
       <c r="F42" t="n">
-        <v>7749</v>
+        <v>26703</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Arcee AI</t>
+          <t>Alibaba</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -6737,52 +6737,52 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>70</v>
+        <v>235</v>
       </c>
       <c r="J42" t="n">
-        <v>70</v>
+        <v>22</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>dense</t>
+          <t>moe</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>artificial_analysis</t>
         </is>
       </c>
       <c r="M42" t="n">
-        <v>140</v>
+        <v>470</v>
       </c>
       <c r="N42" t="n">
-        <v>175</v>
+        <v>587.5</v>
       </c>
       <c r="O42" t="n">
-        <v>70</v>
+        <v>235</v>
       </c>
       <c r="P42" t="n">
-        <v>87.5</v>
+        <v>293.8</v>
       </c>
       <c r="Q42" t="n">
-        <v>35</v>
+        <v>117.5</v>
       </c>
       <c r="R42" t="n">
-        <v>43.8</v>
+        <v>146.9</v>
       </c>
       <c r="S42" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="T42" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="U42" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="T42" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U42" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="V42" s="5" t="inlineStr">
@@ -6795,9 +6795,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="X42" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="X42" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="Y42" s="5" t="inlineStr">
@@ -6805,24 +6805,24 @@
           <t>No</t>
         </is>
       </c>
-      <c r="Z42" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AA42" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB42" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AC42" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="Z42" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA42" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AB42" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AC42" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AD42" s="6" t="inlineStr">
@@ -6830,14 +6830,14 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="AE42" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AF42" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AE42" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF42" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AG42" s="6" t="inlineStr">
@@ -6847,12 +6847,12 @@
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>B200 SXM</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>RTX PRO 6000</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
     </row>
@@ -6862,24 +6862,24 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>qwen3-235b-a22b</t>
+          <t>trinity-large</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1374.53</v>
+        <v>1374.37</v>
       </c>
       <c r="D43" t="n">
-        <v>1369.86</v>
+        <v>1367.33</v>
       </c>
       <c r="E43" t="n">
-        <v>1379.2</v>
+        <v>1381.41</v>
       </c>
       <c r="F43" t="n">
-        <v>26703</v>
+        <v>7793</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alibaba</t>
+          <t>Arcee AI</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -6888,52 +6888,52 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>235</v>
+        <v>70</v>
       </c>
       <c r="J43" t="n">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>moe</t>
+          <t>dense</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>artificial_analysis</t>
+          <t>override</t>
         </is>
       </c>
       <c r="M43" t="n">
-        <v>470</v>
+        <v>140</v>
       </c>
       <c r="N43" t="n">
-        <v>587.5</v>
+        <v>175</v>
       </c>
       <c r="O43" t="n">
-        <v>235</v>
+        <v>70</v>
       </c>
       <c r="P43" t="n">
-        <v>293.8</v>
+        <v>87.5</v>
       </c>
       <c r="Q43" t="n">
-        <v>117.5</v>
+        <v>35</v>
       </c>
       <c r="R43" t="n">
-        <v>146.9</v>
+        <v>43.8</v>
       </c>
       <c r="S43" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="T43" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U43" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="T43" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U43" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="V43" s="5" t="inlineStr">
@@ -6946,9 +6946,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="X43" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="X43" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Y43" s="5" t="inlineStr">
@@ -6956,24 +6956,24 @@
           <t>No</t>
         </is>
       </c>
-      <c r="Z43" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AA43" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AB43" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AC43" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="Z43" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AA43" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB43" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AC43" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AD43" s="6" t="inlineStr">
@@ -6981,14 +6981,14 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="AE43" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AF43" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AE43" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AF43" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AG43" s="6" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="AH43" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>B200 SXM</t>
         </is>
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>RTX PRO 6000</t>
         </is>
       </c>
     </row>
@@ -7017,13 +7017,13 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1372.36</v>
+        <v>1372.38</v>
       </c>
       <c r="D44" t="n">
-        <v>1368.13</v>
+        <v>1368.15</v>
       </c>
       <c r="E44" t="n">
-        <v>1376.59</v>
+        <v>1376.6</v>
       </c>
       <c r="F44" t="n">
         <v>31597</v>
@@ -7168,7 +7168,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1368.76</v>
+        <v>1368.77</v>
       </c>
       <c r="D45" t="n">
         <v>1362.96</v>
@@ -7319,16 +7319,16 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1368.33</v>
+        <v>1368.3</v>
       </c>
       <c r="D46" t="n">
-        <v>1362.54</v>
+        <v>1362.51</v>
       </c>
       <c r="E46" t="n">
-        <v>1374.12</v>
+        <v>1374.08</v>
       </c>
       <c r="F46" t="n">
-        <v>12110</v>
+        <v>12109</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -7621,16 +7621,16 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1364.92</v>
+        <v>1364.91</v>
       </c>
       <c r="D48" t="n">
-        <v>1360.68</v>
+        <v>1360.67</v>
       </c>
       <c r="E48" t="n">
-        <v>1369.16</v>
+        <v>1369.15</v>
       </c>
       <c r="F48" t="n">
-        <v>36105</v>
+        <v>36104</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -7772,13 +7772,13 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1364.66</v>
+        <v>1364.6</v>
       </c>
       <c r="D49" t="n">
-        <v>1355.08</v>
+        <v>1355.02</v>
       </c>
       <c r="E49" t="n">
-        <v>1374.24</v>
+        <v>1374.18</v>
       </c>
       <c r="F49" t="n">
         <v>3711</v>
@@ -7926,7 +7926,7 @@
         <v>1358.24</v>
       </c>
       <c r="D50" t="n">
-        <v>1353.53</v>
+        <v>1353.52</v>
       </c>
       <c r="E50" t="n">
         <v>1362.95</v>
@@ -8074,13 +8074,13 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1357.02</v>
+        <v>1357.03</v>
       </c>
       <c r="D51" t="n">
-        <v>1351.85</v>
+        <v>1351.86</v>
       </c>
       <c r="E51" t="n">
-        <v>1362.19</v>
+        <v>1362.2</v>
       </c>
       <c r="F51" t="n">
         <v>18036</v>
@@ -8225,13 +8225,13 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1356.08</v>
+        <v>1356.09</v>
       </c>
       <c r="D52" t="n">
-        <v>1347.78</v>
+        <v>1347.79</v>
       </c>
       <c r="E52" t="n">
-        <v>1364.37</v>
+        <v>1364.38</v>
       </c>
       <c r="F52" t="n">
         <v>5464</v>
@@ -8829,13 +8829,13 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1347.69</v>
+        <v>1347.7</v>
       </c>
       <c r="D56" t="n">
-        <v>1340.32</v>
+        <v>1340.33</v>
       </c>
       <c r="E56" t="n">
-        <v>1355.06</v>
+        <v>1355.08</v>
       </c>
       <c r="F56" t="n">
         <v>6604</v>
@@ -8906,7 +8906,7 @@
         <v>1339.44</v>
       </c>
       <c r="E57" t="n">
-        <v>1354.85</v>
+        <v>1354.84</v>
       </c>
       <c r="F57" t="n">
         <v>6965</v>
@@ -9054,10 +9054,10 @@
         <v>1346.98</v>
       </c>
       <c r="D58" t="n">
-        <v>1337.51</v>
+        <v>1337.52</v>
       </c>
       <c r="E58" t="n">
-        <v>1356.44</v>
+        <v>1356.45</v>
       </c>
       <c r="F58" t="n">
         <v>3926</v>
@@ -9208,7 +9208,7 @@
         <v>1335.18</v>
       </c>
       <c r="E59" t="n">
-        <v>1358.59</v>
+        <v>1358.58</v>
       </c>
       <c r="F59" t="n">
         <v>2549</v>
@@ -9353,13 +9353,13 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1346.03</v>
+        <v>1346.05</v>
       </c>
       <c r="D60" t="n">
-        <v>1338.83</v>
+        <v>1338.84</v>
       </c>
       <c r="E60" t="n">
-        <v>1353.24</v>
+        <v>1353.26</v>
       </c>
       <c r="F60" t="n">
         <v>7142</v>
@@ -9504,13 +9504,13 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1342.62</v>
+        <v>1342.63</v>
       </c>
       <c r="D61" t="n">
-        <v>1332.7</v>
+        <v>1332.71</v>
       </c>
       <c r="E61" t="n">
-        <v>1352.53</v>
+        <v>1352.54</v>
       </c>
       <c r="F61" t="n">
         <v>3393</v>
@@ -9806,13 +9806,13 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1335.54</v>
+        <v>1335.55</v>
       </c>
       <c r="D63" t="n">
-        <v>1331.13</v>
+        <v>1331.14</v>
       </c>
       <c r="E63" t="n">
-        <v>1339.94</v>
+        <v>1339.96</v>
       </c>
       <c r="F63" t="n">
         <v>25776</v>
@@ -9957,13 +9957,13 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1334.53</v>
+        <v>1334.5</v>
       </c>
       <c r="D64" t="n">
-        <v>1330.86</v>
+        <v>1330.83</v>
       </c>
       <c r="E64" t="n">
-        <v>1338.2</v>
+        <v>1338.17</v>
       </c>
       <c r="F64" t="n">
         <v>41375</v>
@@ -10108,13 +10108,13 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1332.71</v>
+        <v>1332.69</v>
       </c>
       <c r="D65" t="n">
-        <v>1329.15</v>
+        <v>1329.13</v>
       </c>
       <c r="E65" t="n">
-        <v>1336.27</v>
+        <v>1336.25</v>
       </c>
       <c r="F65" t="n">
         <v>59656</v>
@@ -10259,13 +10259,13 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1331.57</v>
+        <v>1331.54</v>
       </c>
       <c r="D66" t="n">
-        <v>1325.5</v>
+        <v>1325.47</v>
       </c>
       <c r="E66" t="n">
-        <v>1337.65</v>
+        <v>1337.62</v>
       </c>
       <c r="F66" t="n">
         <v>12572</v>
@@ -10413,7 +10413,7 @@
         <v>1327.73</v>
       </c>
       <c r="D67" t="n">
-        <v>1323.02</v>
+        <v>1323.03</v>
       </c>
       <c r="E67" t="n">
         <v>1332.43</v>
@@ -10561,13 +10561,13 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1327.39</v>
+        <v>1327.4</v>
       </c>
       <c r="D68" t="n">
-        <v>1315.22</v>
+        <v>1315.23</v>
       </c>
       <c r="E68" t="n">
-        <v>1339.56</v>
+        <v>1339.57</v>
       </c>
       <c r="F68" t="n">
         <v>2218</v>
@@ -10712,13 +10712,13 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1326.79</v>
+        <v>1326.77</v>
       </c>
       <c r="D69" t="n">
-        <v>1322.57</v>
+        <v>1322.55</v>
       </c>
       <c r="E69" t="n">
-        <v>1331.02</v>
+        <v>1331</v>
       </c>
       <c r="F69" t="n">
         <v>40577</v>
@@ -10863,13 +10863,13 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1325.31</v>
+        <v>1325.26</v>
       </c>
       <c r="D70" t="n">
-        <v>1304.22</v>
+        <v>1304.17</v>
       </c>
       <c r="E70" t="n">
-        <v>1346.39</v>
+        <v>1346.34</v>
       </c>
       <c r="F70" t="n">
         <v>841</v>
@@ -11014,10 +11014,10 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1323.13</v>
+        <v>1323.12</v>
       </c>
       <c r="D71" t="n">
-        <v>1314.87</v>
+        <v>1314.86</v>
       </c>
       <c r="E71" t="n">
         <v>1331.39</v>
@@ -11165,13 +11165,13 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1322.17</v>
+        <v>1322.16</v>
       </c>
       <c r="D72" t="n">
-        <v>1317.49</v>
+        <v>1317.48</v>
       </c>
       <c r="E72" t="n">
-        <v>1326.86</v>
+        <v>1326.84</v>
       </c>
       <c r="F72" t="n">
         <v>30775</v>
@@ -11316,13 +11316,13 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1320.76</v>
+        <v>1320.77</v>
       </c>
       <c r="D73" t="n">
-        <v>1313.6</v>
+        <v>1313.61</v>
       </c>
       <c r="E73" t="n">
-        <v>1327.93</v>
+        <v>1327.94</v>
       </c>
       <c r="F73" t="n">
         <v>7275</v>
@@ -11470,7 +11470,7 @@
         <v>1318.41</v>
       </c>
       <c r="D74" t="n">
-        <v>1313.3</v>
+        <v>1313.29</v>
       </c>
       <c r="E74" t="n">
         <v>1323.53</v>
@@ -11618,16 +11618,16 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>1318.25</v>
+        <v>1318.23</v>
       </c>
       <c r="D75" t="n">
-        <v>1314.83</v>
+        <v>1314.81</v>
       </c>
       <c r="E75" t="n">
-        <v>1321.67</v>
+        <v>1321.66</v>
       </c>
       <c r="F75" t="n">
-        <v>55173</v>
+        <v>55172</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -11769,13 +11769,13 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>1317.74</v>
+        <v>1317.73</v>
       </c>
       <c r="D76" t="n">
-        <v>1312.18</v>
+        <v>1312.17</v>
       </c>
       <c r="E76" t="n">
-        <v>1323.3</v>
+        <v>1323.29</v>
       </c>
       <c r="F76" t="n">
         <v>15869</v>
@@ -11920,13 +11920,13 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1317.6</v>
+        <v>1317.59</v>
       </c>
       <c r="D77" t="n">
-        <v>1311.26</v>
+        <v>1311.25</v>
       </c>
       <c r="E77" t="n">
-        <v>1323.94</v>
+        <v>1323.93</v>
       </c>
       <c r="F77" t="n">
         <v>10758</v>
@@ -12071,13 +12071,13 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1317.6</v>
+        <v>1317.59</v>
       </c>
       <c r="D78" t="n">
-        <v>1311.92</v>
+        <v>1311.91</v>
       </c>
       <c r="E78" t="n">
-        <v>1323.28</v>
+        <v>1323.27</v>
       </c>
       <c r="F78" t="n">
         <v>16478</v>
@@ -12293,13 +12293,13 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1313.53</v>
+        <v>1313.51</v>
       </c>
       <c r="D80" t="n">
-        <v>1309.63</v>
+        <v>1309.62</v>
       </c>
       <c r="E80" t="n">
-        <v>1317.42</v>
+        <v>1317.41</v>
       </c>
       <c r="F80" t="n">
         <v>45459</v>
@@ -12447,7 +12447,7 @@
         <v>1306.71</v>
       </c>
       <c r="D81" t="n">
-        <v>1302.04</v>
+        <v>1302.03</v>
       </c>
       <c r="E81" t="n">
         <v>1311.39</v>
@@ -12595,13 +12595,13 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>1305.71</v>
+        <v>1305.73</v>
       </c>
       <c r="D82" t="n">
-        <v>1297.58</v>
+        <v>1297.59</v>
       </c>
       <c r="E82" t="n">
-        <v>1313.85</v>
+        <v>1313.86</v>
       </c>
       <c r="F82" t="n">
         <v>6089</v>
@@ -12746,13 +12746,13 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>1305.65</v>
+        <v>1305.64</v>
       </c>
       <c r="D83" t="n">
-        <v>1299.99</v>
+        <v>1299.98</v>
       </c>
       <c r="E83" t="n">
-        <v>1311.31</v>
+        <v>1311.3</v>
       </c>
       <c r="F83" t="n">
         <v>19621</v>
@@ -12897,13 +12897,13 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>1304.82</v>
+        <v>1304.81</v>
       </c>
       <c r="D84" t="n">
-        <v>1300.42</v>
+        <v>1300.41</v>
       </c>
       <c r="E84" t="n">
-        <v>1309.22</v>
+        <v>1309.21</v>
       </c>
       <c r="F84" t="n">
         <v>28073</v>
@@ -13044,36 +13044,36 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>mistral-small-3.1-24b-instruct-2503</t>
+          <t>gemma-3-4b-it</t>
         </is>
       </c>
       <c r="C85" t="n">
         <v>1302.89</v>
       </c>
       <c r="D85" t="n">
-        <v>1298.41</v>
+        <v>1293.57</v>
       </c>
       <c r="E85" t="n">
-        <v>1307.37</v>
+        <v>1312.21</v>
       </c>
       <c r="F85" t="n">
-        <v>33775</v>
+        <v>4171</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Mistral</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
+          <t>Gemma</t>
         </is>
       </c>
       <c r="I85" t="n">
-        <v>24</v>
+        <v>4.3</v>
       </c>
       <c r="J85" t="n">
-        <v>24</v>
+        <v>4.3</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
@@ -13086,22 +13086,22 @@
         </is>
       </c>
       <c r="M85" t="n">
-        <v>48</v>
+        <v>8.6</v>
       </c>
       <c r="N85" t="n">
-        <v>60</v>
+        <v>10.8</v>
       </c>
       <c r="O85" t="n">
-        <v>24</v>
+        <v>4.3</v>
       </c>
       <c r="P85" t="n">
-        <v>30</v>
+        <v>5.4</v>
       </c>
       <c r="Q85" t="n">
-        <v>12</v>
+        <v>2.1</v>
       </c>
       <c r="R85" t="n">
-        <v>15</v>
+        <v>2.7</v>
       </c>
       <c r="S85" s="6" t="inlineStr">
         <is>
@@ -13195,36 +13195,36 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>gemma-3-4b-it</t>
+          <t>mistral-small-3.1-24b-instruct-2503</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>1302.89</v>
+        <v>1302.88</v>
       </c>
       <c r="D86" t="n">
-        <v>1293.57</v>
+        <v>1298.4</v>
       </c>
       <c r="E86" t="n">
-        <v>1312.21</v>
+        <v>1307.36</v>
       </c>
       <c r="F86" t="n">
-        <v>4171</v>
+        <v>33775</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Mistral</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Gemma</t>
+          <t>Apache 2.0</t>
         </is>
       </c>
       <c r="I86" t="n">
-        <v>4.3</v>
+        <v>24</v>
       </c>
       <c r="J86" t="n">
-        <v>4.3</v>
+        <v>24</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
@@ -13237,22 +13237,22 @@
         </is>
       </c>
       <c r="M86" t="n">
-        <v>8.6</v>
+        <v>48</v>
       </c>
       <c r="N86" t="n">
-        <v>10.8</v>
+        <v>60</v>
       </c>
       <c r="O86" t="n">
-        <v>4.3</v>
+        <v>24</v>
       </c>
       <c r="P86" t="n">
-        <v>5.4</v>
+        <v>30</v>
       </c>
       <c r="Q86" t="n">
-        <v>2.1</v>
+        <v>12</v>
       </c>
       <c r="R86" t="n">
-        <v>2.7</v>
+        <v>15</v>
       </c>
       <c r="S86" s="6" t="inlineStr">
         <is>
@@ -13350,7 +13350,7 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>1302.42</v>
+        <v>1302.41</v>
       </c>
       <c r="D87" t="n">
         <v>1298.38</v>
@@ -13501,7 +13501,7 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>1298.5</v>
+        <v>1298.51</v>
       </c>
       <c r="D88" t="n">
         <v>1290.75</v>
@@ -13652,13 +13652,13 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>1292.98</v>
+        <v>1292.97</v>
       </c>
       <c r="D89" t="n">
-        <v>1289.28</v>
+        <v>1289.27</v>
       </c>
       <c r="E89" t="n">
-        <v>1296.68</v>
+        <v>1296.66</v>
       </c>
       <c r="F89" t="n">
         <v>55240</v>
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>1288.36</v>
+        <v>1288.34</v>
       </c>
       <c r="D90" t="n">
-        <v>1281.06</v>
+        <v>1281.04</v>
       </c>
       <c r="E90" t="n">
-        <v>1295.66</v>
+        <v>1295.64</v>
       </c>
       <c r="F90" t="n">
         <v>8662</v>
@@ -14105,13 +14105,13 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>1286.73</v>
+        <v>1286.71</v>
       </c>
       <c r="D92" t="n">
-        <v>1278.42</v>
+        <v>1278.4</v>
       </c>
       <c r="E92" t="n">
-        <v>1295.04</v>
+        <v>1295.02</v>
       </c>
       <c r="F92" t="n">
         <v>5800</v>
@@ -14259,10 +14259,10 @@
         <v>1286.4</v>
       </c>
       <c r="D93" t="n">
-        <v>1279.21</v>
+        <v>1279.2</v>
       </c>
       <c r="E93" t="n">
-        <v>1293.6</v>
+        <v>1293.59</v>
       </c>
       <c r="F93" t="n">
         <v>8680</v>
@@ -14407,13 +14407,13 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1286.02</v>
+        <v>1286</v>
       </c>
       <c r="D94" t="n">
-        <v>1275.54</v>
+        <v>1275.53</v>
       </c>
       <c r="E94" t="n">
-        <v>1296.49</v>
+        <v>1296.48</v>
       </c>
       <c r="F94" t="n">
         <v>2846</v>
@@ -14558,13 +14558,13 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1285.58</v>
+        <v>1285.55</v>
       </c>
       <c r="D95" t="n">
-        <v>1275.61</v>
+        <v>1275.58</v>
       </c>
       <c r="E95" t="n">
-        <v>1295.56</v>
+        <v>1295.53</v>
       </c>
       <c r="F95" t="n">
         <v>3749</v>
@@ -14709,13 +14709,13 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>1279</v>
+        <v>1278.99</v>
       </c>
       <c r="D96" t="n">
-        <v>1272.14</v>
+        <v>1272.13</v>
       </c>
       <c r="E96" t="n">
-        <v>1285.85</v>
+        <v>1285.84</v>
       </c>
       <c r="F96" t="n">
         <v>10072</v>
@@ -14860,13 +14860,13 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1276.56</v>
+        <v>1276.53</v>
       </c>
       <c r="D97" t="n">
-        <v>1271.24</v>
+        <v>1271.21</v>
       </c>
       <c r="E97" t="n">
-        <v>1281.89</v>
+        <v>1281.86</v>
       </c>
       <c r="F97" t="n">
         <v>19659</v>
@@ -15011,13 +15011,13 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>1275.78</v>
+        <v>1275.76</v>
       </c>
       <c r="D98" t="n">
-        <v>1269.22</v>
+        <v>1269.19</v>
       </c>
       <c r="E98" t="n">
-        <v>1282.35</v>
+        <v>1282.32</v>
       </c>
       <c r="F98" t="n">
         <v>9866</v>
@@ -15162,13 +15162,13 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>1275.42</v>
+        <v>1275.4</v>
       </c>
       <c r="D99" t="n">
-        <v>1271.85</v>
+        <v>1271.83</v>
       </c>
       <c r="E99" t="n">
-        <v>1278.99</v>
+        <v>1278.97</v>
       </c>
       <c r="F99" t="n">
         <v>156876</v>
@@ -15313,13 +15313,13 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>1273.61</v>
+        <v>1273.6</v>
       </c>
       <c r="D100" t="n">
-        <v>1267.73</v>
+        <v>1267.72</v>
       </c>
       <c r="E100" t="n">
-        <v>1279.49</v>
+        <v>1279.48</v>
       </c>
       <c r="F100" t="n">
         <v>14681</v>
@@ -15464,13 +15464,13 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1270.08</v>
+        <v>1270.07</v>
       </c>
       <c r="D101" t="n">
-        <v>1261.96</v>
+        <v>1261.95</v>
       </c>
       <c r="E101" t="n">
-        <v>1278.2</v>
+        <v>1278.18</v>
       </c>
       <c r="F101" t="n">
         <v>5432</v>
@@ -15615,13 +15615,13 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>1266.48</v>
+        <v>1266.46</v>
       </c>
       <c r="D102" t="n">
-        <v>1261.62</v>
+        <v>1261.61</v>
       </c>
       <c r="E102" t="n">
-        <v>1271.34</v>
+        <v>1271.32</v>
       </c>
       <c r="F102" t="n">
         <v>27124</v>
@@ -15766,13 +15766,13 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>1265.21</v>
+        <v>1265.2</v>
       </c>
       <c r="D103" t="n">
-        <v>1261.43</v>
+        <v>1261.42</v>
       </c>
       <c r="E103" t="n">
-        <v>1268.99</v>
+        <v>1268.98</v>
       </c>
       <c r="F103" t="n">
         <v>54611</v>
@@ -15917,13 +15917,13 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>1263.65</v>
+        <v>1263.63</v>
       </c>
       <c r="D104" t="n">
-        <v>1257.37</v>
+        <v>1257.35</v>
       </c>
       <c r="E104" t="n">
-        <v>1269.93</v>
+        <v>1269.91</v>
       </c>
       <c r="F104" t="n">
         <v>15147</v>
@@ -16068,13 +16068,13 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>1261.09</v>
+        <v>1261.05</v>
       </c>
       <c r="D105" t="n">
-        <v>1256.77</v>
+        <v>1256.74</v>
       </c>
       <c r="E105" t="n">
-        <v>1265.4</v>
+        <v>1265.37</v>
       </c>
       <c r="F105" t="n">
         <v>77554</v>
@@ -16219,13 +16219,13 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>1261.05</v>
+        <v>1261.02</v>
       </c>
       <c r="D106" t="n">
-        <v>1256.12</v>
+        <v>1256.09</v>
       </c>
       <c r="E106" t="n">
-        <v>1265.99</v>
+        <v>1265.95</v>
       </c>
       <c r="F106" t="n">
         <v>37325</v>
@@ -16370,13 +16370,13 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>1255.63</v>
+        <v>1255.61</v>
       </c>
       <c r="D107" t="n">
-        <v>1251.06</v>
+        <v>1251.05</v>
       </c>
       <c r="E107" t="n">
-        <v>1260.19</v>
+        <v>1260.18</v>
       </c>
       <c r="F107" t="n">
         <v>24126</v>
@@ -16521,13 +16521,13 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>1251.43</v>
+        <v>1251.41</v>
       </c>
       <c r="D108" t="n">
-        <v>1240.64</v>
+        <v>1240.62</v>
       </c>
       <c r="E108" t="n">
-        <v>1262.23</v>
+        <v>1262.21</v>
       </c>
       <c r="F108" t="n">
         <v>3334</v>
@@ -16672,13 +16672,13 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>1249.39</v>
+        <v>1249.36</v>
       </c>
       <c r="D109" t="n">
-        <v>1242.8</v>
+        <v>1242.77</v>
       </c>
       <c r="E109" t="n">
-        <v>1255.99</v>
+        <v>1255.96</v>
       </c>
       <c r="F109" t="n">
         <v>10140</v>
@@ -16823,13 +16823,13 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>1238.55</v>
+        <v>1238.54</v>
       </c>
       <c r="D110" t="n">
-        <v>1231.33</v>
+        <v>1231.32</v>
       </c>
       <c r="E110" t="n">
-        <v>1245.77</v>
+        <v>1245.76</v>
       </c>
       <c r="F110" t="n">
         <v>8858</v>
@@ -16974,13 +16974,13 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>1236.73</v>
+        <v>1236.72</v>
       </c>
       <c r="D111" t="n">
-        <v>1227.64</v>
+        <v>1227.63</v>
       </c>
       <c r="E111" t="n">
-        <v>1245.83</v>
+        <v>1245.82</v>
       </c>
       <c r="F111" t="n">
         <v>4781</v>
@@ -17125,13 +17125,13 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>1233.3</v>
+        <v>1233.27</v>
       </c>
       <c r="D112" t="n">
-        <v>1227.75</v>
+        <v>1227.72</v>
       </c>
       <c r="E112" t="n">
-        <v>1238.85</v>
+        <v>1238.82</v>
       </c>
       <c r="F112" t="n">
         <v>26195</v>
@@ -17276,13 +17276,13 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>1232.37</v>
+        <v>1232.33</v>
       </c>
       <c r="D113" t="n">
-        <v>1227.09</v>
+        <v>1227.06</v>
       </c>
       <c r="E113" t="n">
-        <v>1237.64</v>
+        <v>1237.61</v>
       </c>
       <c r="F113" t="n">
         <v>39302</v>
@@ -17427,13 +17427,13 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>1228.59</v>
+        <v>1228.56</v>
       </c>
       <c r="D114" t="n">
-        <v>1224.04</v>
+        <v>1224.01</v>
       </c>
       <c r="E114" t="n">
-        <v>1233.14</v>
+        <v>1233.1</v>
       </c>
       <c r="F114" t="n">
         <v>51416</v>
@@ -17578,13 +17578,13 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>1226.07</v>
+        <v>1226.04</v>
       </c>
       <c r="D115" t="n">
-        <v>1221.29</v>
+        <v>1221.26</v>
       </c>
       <c r="E115" t="n">
-        <v>1230.85</v>
+        <v>1230.82</v>
       </c>
       <c r="F115" t="n">
         <v>54036</v>
@@ -17729,13 +17729,13 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>1222.5</v>
+        <v>1222.47</v>
       </c>
       <c r="D116" t="n">
-        <v>1218.77</v>
+        <v>1218.75</v>
       </c>
       <c r="E116" t="n">
-        <v>1226.22</v>
+        <v>1226.19</v>
       </c>
       <c r="F116" t="n">
         <v>104642</v>
@@ -17880,13 +17880,13 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>1222.43</v>
+        <v>1222.42</v>
       </c>
       <c r="D117" t="n">
-        <v>1215.47</v>
+        <v>1215.46</v>
       </c>
       <c r="E117" t="n">
-        <v>1229.38</v>
+        <v>1229.37</v>
       </c>
       <c r="F117" t="n">
         <v>9818</v>
@@ -18031,13 +18031,13 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>1220.54</v>
+        <v>1220.53</v>
       </c>
       <c r="D118" t="n">
-        <v>1209.86</v>
+        <v>1209.84</v>
       </c>
       <c r="E118" t="n">
-        <v>1231.23</v>
+        <v>1231.22</v>
       </c>
       <c r="F118" t="n">
         <v>2896</v>
@@ -18182,13 +18182,13 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>1212.68</v>
+        <v>1212.66</v>
       </c>
       <c r="D119" t="n">
-        <v>1207.65</v>
+        <v>1207.63</v>
       </c>
       <c r="E119" t="n">
-        <v>1217.72</v>
+        <v>1217.69</v>
       </c>
       <c r="F119" t="n">
         <v>24146</v>
@@ -18333,13 +18333,13 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>1211.88</v>
+        <v>1211.85</v>
       </c>
       <c r="D120" t="n">
-        <v>1201.07</v>
+        <v>1201.04</v>
       </c>
       <c r="E120" t="n">
-        <v>1222.69</v>
+        <v>1222.66</v>
       </c>
       <c r="F120" t="n">
         <v>4652</v>
@@ -18484,13 +18484,13 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>1211.15</v>
+        <v>1211.14</v>
       </c>
       <c r="D121" t="n">
-        <v>1207.04</v>
+        <v>1207.03</v>
       </c>
       <c r="E121" t="n">
-        <v>1215.27</v>
+        <v>1215.26</v>
       </c>
       <c r="F121" t="n">
         <v>49605</v>
@@ -18635,13 +18635,13 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>1207.65</v>
+        <v>1207.62</v>
       </c>
       <c r="D122" t="n">
-        <v>1196.53</v>
+        <v>1196.5</v>
       </c>
       <c r="E122" t="n">
-        <v>1218.76</v>
+        <v>1218.73</v>
       </c>
       <c r="F122" t="n">
         <v>3090</v>
@@ -18786,13 +18786,13 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>1203</v>
+        <v>1202.96</v>
       </c>
       <c r="D123" t="n">
-        <v>1196.88</v>
+        <v>1196.84</v>
       </c>
       <c r="E123" t="n">
-        <v>1209.12</v>
+        <v>1209.08</v>
       </c>
       <c r="F123" t="n">
         <v>21741</v>
@@ -19088,13 +19088,13 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>1197.12</v>
+        <v>1197.09</v>
       </c>
       <c r="D125" t="n">
-        <v>1191.97</v>
+        <v>1191.94</v>
       </c>
       <c r="E125" t="n">
-        <v>1202.27</v>
+        <v>1202.24</v>
       </c>
       <c r="F125" t="n">
         <v>25055</v>
@@ -19239,13 +19239,13 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>1196.27</v>
+        <v>1196.24</v>
       </c>
       <c r="D126" t="n">
-        <v>1192.01</v>
+        <v>1191.97</v>
       </c>
       <c r="E126" t="n">
-        <v>1200.54</v>
+        <v>1200.51</v>
       </c>
       <c r="F126" t="n">
         <v>73503</v>
@@ -19390,13 +19390,13 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>1194.2</v>
+        <v>1194.16</v>
       </c>
       <c r="D127" t="n">
-        <v>1188.08</v>
+        <v>1188.04</v>
       </c>
       <c r="E127" t="n">
-        <v>1200.31</v>
+        <v>1200.27</v>
       </c>
       <c r="F127" t="n">
         <v>32191</v>
@@ -19541,13 +19541,13 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>1190.68</v>
+        <v>1190.66</v>
       </c>
       <c r="D128" t="n">
-        <v>1183.51</v>
+        <v>1183.49</v>
       </c>
       <c r="E128" t="n">
-        <v>1197.86</v>
+        <v>1197.84</v>
       </c>
       <c r="F128" t="n">
         <v>9901</v>
@@ -19692,13 +19692,13 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>1190.1</v>
+        <v>1190.07</v>
       </c>
       <c r="D129" t="n">
-        <v>1182.98</v>
+        <v>1182.95</v>
       </c>
       <c r="E129" t="n">
-        <v>1197.23</v>
+        <v>1197.2</v>
       </c>
       <c r="F129" t="n">
         <v>17839</v>
@@ -19843,13 +19843,13 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>1183.79</v>
+        <v>1183.75</v>
       </c>
       <c r="D130" t="n">
-        <v>1174.33</v>
+        <v>1174.29</v>
       </c>
       <c r="E130" t="n">
-        <v>1193.25</v>
+        <v>1193.21</v>
       </c>
       <c r="F130" t="n">
         <v>8214</v>
@@ -19994,13 +19994,13 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>1183.51</v>
+        <v>1183.48</v>
       </c>
       <c r="D131" t="n">
-        <v>1172</v>
+        <v>1171.96</v>
       </c>
       <c r="E131" t="n">
-        <v>1195.03</v>
+        <v>1194.99</v>
       </c>
       <c r="F131" t="n">
         <v>4932</v>
@@ -20145,13 +20145,13 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>1183.03</v>
+        <v>1183</v>
       </c>
       <c r="D132" t="n">
-        <v>1176.2</v>
+        <v>1176.17</v>
       </c>
       <c r="E132" t="n">
-        <v>1189.86</v>
+        <v>1189.83</v>
       </c>
       <c r="F132" t="n">
         <v>15483</v>
@@ -20296,13 +20296,13 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>1181.38</v>
+        <v>1181.35</v>
       </c>
       <c r="D133" t="n">
-        <v>1173.38</v>
+        <v>1173.34</v>
       </c>
       <c r="E133" t="n">
-        <v>1189.39</v>
+        <v>1189.35</v>
       </c>
       <c r="F133" t="n">
         <v>12637</v>
@@ -20367,13 +20367,13 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>1181.32</v>
+        <v>1181.28</v>
       </c>
       <c r="D134" t="n">
-        <v>1171.64</v>
+        <v>1171.6</v>
       </c>
       <c r="E134" t="n">
-        <v>1191</v>
+        <v>1190.97</v>
       </c>
       <c r="F134" t="n">
         <v>7968</v>
@@ -20438,13 +20438,13 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>1181.23</v>
+        <v>1181.19</v>
       </c>
       <c r="D135" t="n">
-        <v>1172.54</v>
+        <v>1172.51</v>
       </c>
       <c r="E135" t="n">
-        <v>1189.92</v>
+        <v>1189.88</v>
       </c>
       <c r="F135" t="n">
         <v>6638</v>
@@ -20589,13 +20589,13 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>1179.81</v>
+        <v>1179.8</v>
       </c>
       <c r="D136" t="n">
-        <v>1173.74</v>
+        <v>1173.73</v>
       </c>
       <c r="E136" t="n">
-        <v>1185.89</v>
+        <v>1185.87</v>
       </c>
       <c r="F136" t="n">
         <v>23893</v>
@@ -20740,13 +20740,13 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>1178.61</v>
+        <v>1178.57</v>
       </c>
       <c r="D137" t="n">
-        <v>1172.69</v>
+        <v>1172.65</v>
       </c>
       <c r="E137" t="n">
-        <v>1184.52</v>
+        <v>1184.48</v>
       </c>
       <c r="F137" t="n">
         <v>32832</v>
@@ -20811,13 +20811,13 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>1178.19</v>
+        <v>1178.17</v>
       </c>
       <c r="D138" t="n">
-        <v>1166.98</v>
+        <v>1166.96</v>
       </c>
       <c r="E138" t="n">
-        <v>1189.4</v>
+        <v>1189.38</v>
       </c>
       <c r="F138" t="n">
         <v>3188</v>
@@ -20962,13 +20962,13 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>1177.14</v>
+        <v>1177.1</v>
       </c>
       <c r="D139" t="n">
-        <v>1167.31</v>
+        <v>1167.27</v>
       </c>
       <c r="E139" t="n">
-        <v>1186.96</v>
+        <v>1186.93</v>
       </c>
       <c r="F139" t="n">
         <v>6535</v>
@@ -21113,13 +21113,13 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>1174.3</v>
+        <v>1174.26</v>
       </c>
       <c r="D140" t="n">
-        <v>1163.87</v>
+        <v>1163.83</v>
       </c>
       <c r="E140" t="n">
-        <v>1184.73</v>
+        <v>1184.69</v>
       </c>
       <c r="F140" t="n">
         <v>5006</v>
@@ -21264,13 +21264,13 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>1171.89</v>
+        <v>1171.85</v>
       </c>
       <c r="D141" t="n">
-        <v>1165.67</v>
+        <v>1165.64</v>
       </c>
       <c r="E141" t="n">
-        <v>1178.1</v>
+        <v>1178.07</v>
       </c>
       <c r="F141" t="n">
         <v>22479</v>
@@ -21415,13 +21415,13 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>1170.79</v>
+        <v>1170.76</v>
       </c>
       <c r="D142" t="n">
-        <v>1163.38</v>
+        <v>1163.35</v>
       </c>
       <c r="E142" t="n">
-        <v>1178.21</v>
+        <v>1178.18</v>
       </c>
       <c r="F142" t="n">
         <v>16056</v>
@@ -21566,13 +21566,13 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>1170.26</v>
+        <v>1170.23</v>
       </c>
       <c r="D143" t="n">
-        <v>1164.35</v>
+        <v>1164.31</v>
       </c>
       <c r="E143" t="n">
-        <v>1176.18</v>
+        <v>1176.14</v>
       </c>
       <c r="F143" t="n">
         <v>17766</v>
@@ -21717,13 +21717,13 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>1169.92</v>
+        <v>1169.89</v>
       </c>
       <c r="D144" t="n">
-        <v>1164.42</v>
+        <v>1164.39</v>
       </c>
       <c r="E144" t="n">
-        <v>1175.43</v>
+        <v>1175.4</v>
       </c>
       <c r="F144" t="n">
         <v>38492</v>
@@ -21868,13 +21868,13 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>1166.65</v>
+        <v>1166.62</v>
       </c>
       <c r="D145" t="n">
-        <v>1158.58</v>
+        <v>1158.55</v>
       </c>
       <c r="E145" t="n">
-        <v>1174.73</v>
+        <v>1174.69</v>
       </c>
       <c r="F145" t="n">
         <v>10224</v>
@@ -22019,13 +22019,13 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>1165.96</v>
+        <v>1165.93</v>
       </c>
       <c r="D146" t="n">
-        <v>1158.26</v>
+        <v>1158.24</v>
       </c>
       <c r="E146" t="n">
-        <v>1173.65</v>
+        <v>1173.63</v>
       </c>
       <c r="F146" t="n">
         <v>7936</v>
@@ -22170,13 +22170,13 @@
         </is>
       </c>
       <c r="C147" t="n">
-        <v>1163.86</v>
+        <v>1163.83</v>
       </c>
       <c r="D147" t="n">
-        <v>1151.92</v>
+        <v>1151.89</v>
       </c>
       <c r="E147" t="n">
-        <v>1175.8</v>
+        <v>1175.77</v>
       </c>
       <c r="F147" t="n">
         <v>3777</v>
@@ -22321,13 +22321,13 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>1156.15</v>
+        <v>1156.13</v>
       </c>
       <c r="D148" t="n">
-        <v>1144.64</v>
+        <v>1144.62</v>
       </c>
       <c r="E148" t="n">
-        <v>1167.65</v>
+        <v>1167.63</v>
       </c>
       <c r="F148" t="n">
         <v>3231</v>
@@ -22472,13 +22472,13 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>1155.21</v>
+        <v>1155.17</v>
       </c>
       <c r="D149" t="n">
-        <v>1146.81</v>
+        <v>1146.78</v>
       </c>
       <c r="E149" t="n">
-        <v>1163.6</v>
+        <v>1163.57</v>
       </c>
       <c r="F149" t="n">
         <v>6837</v>
@@ -22623,13 +22623,13 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>1154.42</v>
+        <v>1154.38</v>
       </c>
       <c r="D150" t="n">
-        <v>1141.8</v>
+        <v>1141.76</v>
       </c>
       <c r="E150" t="n">
-        <v>1167.05</v>
+        <v>1167.01</v>
       </c>
       <c r="F150" t="n">
         <v>3585</v>
@@ -22774,13 +22774,13 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>1151.46</v>
+        <v>1151.42</v>
       </c>
       <c r="D151" t="n">
-        <v>1138.25</v>
+        <v>1138.21</v>
       </c>
       <c r="E151" t="n">
-        <v>1164.68</v>
+        <v>1164.64</v>
       </c>
       <c r="F151" t="n">
         <v>4155</v>
@@ -22925,13 +22925,13 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>1151.11</v>
+        <v>1151.07</v>
       </c>
       <c r="D152" t="n">
-        <v>1135.71</v>
+        <v>1135.67</v>
       </c>
       <c r="E152" t="n">
-        <v>1166.51</v>
+        <v>1166.48</v>
       </c>
       <c r="F152" t="n">
         <v>1679</v>
@@ -23076,13 +23076,13 @@
         </is>
       </c>
       <c r="C153" t="n">
-        <v>1149.2</v>
+        <v>1149.17</v>
       </c>
       <c r="D153" t="n">
-        <v>1136.9</v>
+        <v>1136.86</v>
       </c>
       <c r="E153" t="n">
-        <v>1161.51</v>
+        <v>1161.47</v>
       </c>
       <c r="F153" t="n">
         <v>2572</v>
@@ -23227,13 +23227,13 @@
         </is>
       </c>
       <c r="C154" t="n">
-        <v>1148.71</v>
+        <v>1148.68</v>
       </c>
       <c r="D154" t="n">
-        <v>1142.06</v>
+        <v>1142.02</v>
       </c>
       <c r="E154" t="n">
-        <v>1155.37</v>
+        <v>1155.33</v>
       </c>
       <c r="F154" t="n">
         <v>19402</v>
@@ -23378,13 +23378,13 @@
         </is>
       </c>
       <c r="C155" t="n">
-        <v>1148.31</v>
+        <v>1148.27</v>
       </c>
       <c r="D155" t="n">
-        <v>1139.04</v>
+        <v>1139.01</v>
       </c>
       <c r="E155" t="n">
-        <v>1157.58</v>
+        <v>1157.54</v>
       </c>
       <c r="F155" t="n">
         <v>7044</v>
@@ -23529,13 +23529,13 @@
         </is>
       </c>
       <c r="C156" t="n">
-        <v>1146.15</v>
+        <v>1146.11</v>
       </c>
       <c r="D156" t="n">
-        <v>1129.01</v>
+        <v>1128.98</v>
       </c>
       <c r="E156" t="n">
-        <v>1163.28</v>
+        <v>1163.24</v>
       </c>
       <c r="F156" t="n">
         <v>1295</v>
@@ -23680,13 +23680,13 @@
         </is>
       </c>
       <c r="C157" t="n">
-        <v>1142.95</v>
+        <v>1142.92</v>
       </c>
       <c r="D157" t="n">
-        <v>1133.05</v>
+        <v>1133.02</v>
       </c>
       <c r="E157" t="n">
-        <v>1152.84</v>
+        <v>1152.81</v>
       </c>
       <c r="F157" t="n">
         <v>4737</v>
@@ -23831,13 +23831,13 @@
         </is>
       </c>
       <c r="C158" t="n">
-        <v>1142.24</v>
+        <v>1142.21</v>
       </c>
       <c r="D158" t="n">
-        <v>1135.81</v>
+        <v>1135.78</v>
       </c>
       <c r="E158" t="n">
-        <v>1148.68</v>
+        <v>1148.65</v>
       </c>
       <c r="F158" t="n">
         <v>12297</v>
@@ -23982,13 +23982,13 @@
         </is>
       </c>
       <c r="C159" t="n">
-        <v>1140.63</v>
+        <v>1140.6</v>
       </c>
       <c r="D159" t="n">
-        <v>1133.9</v>
+        <v>1133.87</v>
       </c>
       <c r="E159" t="n">
-        <v>1147.36</v>
+        <v>1147.33</v>
       </c>
       <c r="F159" t="n">
         <v>19174</v>
@@ -24133,13 +24133,13 @@
         </is>
       </c>
       <c r="C160" t="n">
-        <v>1140.02</v>
+        <v>1139.98</v>
       </c>
       <c r="D160" t="n">
-        <v>1133.3</v>
+        <v>1133.26</v>
       </c>
       <c r="E160" t="n">
-        <v>1146.73</v>
+        <v>1146.69</v>
       </c>
       <c r="F160" t="n">
         <v>19367</v>
@@ -24284,13 +24284,13 @@
         </is>
       </c>
       <c r="C161" t="n">
-        <v>1137.68</v>
+        <v>1137.64</v>
       </c>
       <c r="D161" t="n">
-        <v>1126.71</v>
+        <v>1126.67</v>
       </c>
       <c r="E161" t="n">
-        <v>1148.65</v>
+        <v>1148.61</v>
       </c>
       <c r="F161" t="n">
         <v>4964</v>
@@ -24435,13 +24435,13 @@
         </is>
       </c>
       <c r="C162" t="n">
-        <v>1135.67</v>
+        <v>1135.64</v>
       </c>
       <c r="D162" t="n">
-        <v>1126.76</v>
+        <v>1126.73</v>
       </c>
       <c r="E162" t="n">
-        <v>1144.58</v>
+        <v>1144.54</v>
       </c>
       <c r="F162" t="n">
         <v>7366</v>
@@ -24586,13 +24586,13 @@
         </is>
       </c>
       <c r="C163" t="n">
-        <v>1135.51</v>
+        <v>1135.49</v>
       </c>
       <c r="D163" t="n">
-        <v>1126</v>
+        <v>1125.98</v>
       </c>
       <c r="E163" t="n">
-        <v>1145.02</v>
+        <v>1145</v>
       </c>
       <c r="F163" t="n">
         <v>8925</v>
@@ -24737,13 +24737,13 @@
         </is>
       </c>
       <c r="C164" t="n">
-        <v>1130.13</v>
+        <v>1130.09</v>
       </c>
       <c r="D164" t="n">
-        <v>1121.28</v>
+        <v>1121.24</v>
       </c>
       <c r="E164" t="n">
-        <v>1138.98</v>
+        <v>1138.95</v>
       </c>
       <c r="F164" t="n">
         <v>11118</v>
@@ -24888,13 +24888,13 @@
         </is>
       </c>
       <c r="C165" t="n">
-        <v>1128.35</v>
+        <v>1128.31</v>
       </c>
       <c r="D165" t="n">
-        <v>1120.92</v>
+        <v>1120.88</v>
       </c>
       <c r="E165" t="n">
-        <v>1135.77</v>
+        <v>1135.74</v>
       </c>
       <c r="F165" t="n">
         <v>20685</v>
@@ -25039,13 +25039,13 @@
         </is>
       </c>
       <c r="C166" t="n">
-        <v>1127.55</v>
+        <v>1127.51</v>
       </c>
       <c r="D166" t="n">
-        <v>1121.15</v>
+        <v>1121.12</v>
       </c>
       <c r="E166" t="n">
-        <v>1133.94</v>
+        <v>1133.91</v>
       </c>
       <c r="F166" t="n">
         <v>20118</v>
@@ -25190,13 +25190,13 @@
         </is>
       </c>
       <c r="C167" t="n">
-        <v>1126.4</v>
+        <v>1126.37</v>
       </c>
       <c r="D167" t="n">
-        <v>1114.24</v>
+        <v>1114.21</v>
       </c>
       <c r="E167" t="n">
-        <v>1138.56</v>
+        <v>1138.53</v>
       </c>
       <c r="F167" t="n">
         <v>2921</v>
@@ -25341,13 +25341,13 @@
         </is>
       </c>
       <c r="C168" t="n">
-        <v>1125.99</v>
+        <v>1125.96</v>
       </c>
       <c r="D168" t="n">
-        <v>1110.32</v>
+        <v>1110.28</v>
       </c>
       <c r="E168" t="n">
-        <v>1141.67</v>
+        <v>1141.64</v>
       </c>
       <c r="F168" t="n">
         <v>1785</v>
@@ -25492,13 +25492,13 @@
         </is>
       </c>
       <c r="C169" t="n">
-        <v>1120.08</v>
+        <v>1120.04</v>
       </c>
       <c r="D169" t="n">
-        <v>1109.08</v>
+        <v>1109.04</v>
       </c>
       <c r="E169" t="n">
-        <v>1131.09</v>
+        <v>1131.05</v>
       </c>
       <c r="F169" t="n">
         <v>5182</v>
@@ -25643,13 +25643,13 @@
         </is>
       </c>
       <c r="C170" t="n">
-        <v>1118.22</v>
+        <v>1118.19</v>
       </c>
       <c r="D170" t="n">
-        <v>1100</v>
+        <v>1099.97</v>
       </c>
       <c r="E170" t="n">
-        <v>1136.44</v>
+        <v>1136.41</v>
       </c>
       <c r="F170" t="n">
         <v>1143</v>
@@ -25794,13 +25794,13 @@
         </is>
       </c>
       <c r="C171" t="n">
-        <v>1113.73</v>
+        <v>1113.7</v>
       </c>
       <c r="D171" t="n">
-        <v>1104.55</v>
+        <v>1104.51</v>
       </c>
       <c r="E171" t="n">
-        <v>1122.92</v>
+        <v>1122.88</v>
       </c>
       <c r="F171" t="n">
         <v>6923</v>
@@ -25945,13 +25945,13 @@
         </is>
       </c>
       <c r="C172" t="n">
-        <v>1113.7</v>
+        <v>1113.68</v>
       </c>
       <c r="D172" t="n">
-        <v>1105.96</v>
+        <v>1105.94</v>
       </c>
       <c r="E172" t="n">
-        <v>1121.43</v>
+        <v>1121.42</v>
       </c>
       <c r="F172" t="n">
         <v>10854</v>
@@ -26096,13 +26096,13 @@
         </is>
       </c>
       <c r="C173" t="n">
-        <v>1113.48</v>
+        <v>1113.45</v>
       </c>
       <c r="D173" t="n">
-        <v>1099.06</v>
+        <v>1099.03</v>
       </c>
       <c r="E173" t="n">
-        <v>1127.9</v>
+        <v>1127.87</v>
       </c>
       <c r="F173" t="n">
         <v>2199</v>
@@ -26247,13 +26247,13 @@
         </is>
       </c>
       <c r="C174" t="n">
-        <v>1110.5</v>
+        <v>1110.48</v>
       </c>
       <c r="D174" t="n">
-        <v>1102.63</v>
+        <v>1102.6</v>
       </c>
       <c r="E174" t="n">
-        <v>1118.38</v>
+        <v>1118.35</v>
       </c>
       <c r="F174" t="n">
         <v>8045</v>
@@ -26398,13 +26398,13 @@
         </is>
       </c>
       <c r="C175" t="n">
-        <v>1108.71</v>
+        <v>1108.67</v>
       </c>
       <c r="D175" t="n">
-        <v>1099.41</v>
+        <v>1099.37</v>
       </c>
       <c r="E175" t="n">
-        <v>1118.01</v>
+        <v>1117.97</v>
       </c>
       <c r="F175" t="n">
         <v>8977</v>
@@ -26549,13 +26549,13 @@
         </is>
       </c>
       <c r="C176" t="n">
-        <v>1107.26</v>
+        <v>1107.23</v>
       </c>
       <c r="D176" t="n">
-        <v>1100.2</v>
+        <v>1100.17</v>
       </c>
       <c r="E176" t="n">
-        <v>1114.32</v>
+        <v>1114.29</v>
       </c>
       <c r="F176" t="n">
         <v>14148</v>
@@ -26700,13 +26700,13 @@
         </is>
       </c>
       <c r="C177" t="n">
-        <v>1091.11</v>
+        <v>1091.09</v>
       </c>
       <c r="D177" t="n">
-        <v>1079.59</v>
+        <v>1079.57</v>
       </c>
       <c r="E177" t="n">
-        <v>1102.63</v>
+        <v>1102.61</v>
       </c>
       <c r="F177" t="n">
         <v>4780</v>
@@ -26851,13 +26851,13 @@
         </is>
       </c>
       <c r="C178" t="n">
-        <v>1089.28</v>
+        <v>1089.24</v>
       </c>
       <c r="D178" t="n">
-        <v>1079.92</v>
+        <v>1079.88</v>
       </c>
       <c r="E178" t="n">
-        <v>1098.63</v>
+        <v>1098.59</v>
       </c>
       <c r="F178" t="n">
         <v>7597</v>
@@ -27002,13 +27002,13 @@
         </is>
       </c>
       <c r="C179" t="n">
-        <v>1073.66</v>
+        <v>1073.63</v>
       </c>
       <c r="D179" t="n">
-        <v>1062.47</v>
+        <v>1062.44</v>
       </c>
       <c r="E179" t="n">
-        <v>1084.86</v>
+        <v>1084.82</v>
       </c>
       <c r="F179" t="n">
         <v>6328</v>
@@ -27153,13 +27153,13 @@
         </is>
       </c>
       <c r="C180" t="n">
-        <v>1069.5</v>
+        <v>1069.46</v>
       </c>
       <c r="D180" t="n">
-        <v>1059.54</v>
+        <v>1059.5</v>
       </c>
       <c r="E180" t="n">
-        <v>1079.45</v>
+        <v>1079.41</v>
       </c>
       <c r="F180" t="n">
         <v>6965</v>
@@ -27304,13 +27304,13 @@
         </is>
       </c>
       <c r="C181" t="n">
-        <v>1066.57</v>
+        <v>1066.53</v>
       </c>
       <c r="D181" t="n">
-        <v>1055.04</v>
+        <v>1055</v>
       </c>
       <c r="E181" t="n">
-        <v>1078.09</v>
+        <v>1078.05</v>
       </c>
       <c r="F181" t="n">
         <v>5745</v>
@@ -27455,13 +27455,13 @@
         </is>
       </c>
       <c r="C182" t="n">
-        <v>1065.07</v>
+        <v>1065.04</v>
       </c>
       <c r="D182" t="n">
-        <v>1049.78</v>
+        <v>1049.74</v>
       </c>
       <c r="E182" t="n">
-        <v>1080.37</v>
+        <v>1080.33</v>
       </c>
       <c r="F182" t="n">
         <v>1743</v>
@@ -27606,13 +27606,13 @@
         </is>
       </c>
       <c r="C183" t="n">
-        <v>1060.92</v>
+        <v>1060.88</v>
       </c>
       <c r="D183" t="n">
-        <v>1048.88</v>
+        <v>1048.85</v>
       </c>
       <c r="E183" t="n">
-        <v>1072.96</v>
+        <v>1072.92</v>
       </c>
       <c r="F183" t="n">
         <v>3924</v>
@@ -27757,13 +27757,13 @@
         </is>
       </c>
       <c r="C184" t="n">
-        <v>1055.12</v>
+        <v>1055.08</v>
       </c>
       <c r="D184" t="n">
-        <v>1043.43</v>
+        <v>1043.39</v>
       </c>
       <c r="E184" t="n">
-        <v>1066.81</v>
+        <v>1066.77</v>
       </c>
       <c r="F184" t="n">
         <v>4658</v>
@@ -27908,13 +27908,13 @@
         </is>
       </c>
       <c r="C185" t="n">
-        <v>1040.39</v>
+        <v>1040.35</v>
       </c>
       <c r="D185" t="n">
-        <v>1028.94</v>
+        <v>1028.9</v>
       </c>
       <c r="E185" t="n">
-        <v>1051.85</v>
+        <v>1051.81</v>
       </c>
       <c r="F185" t="n">
         <v>4845</v>
@@ -28059,13 +28059,13 @@
         </is>
       </c>
       <c r="C186" t="n">
-        <v>1023.23</v>
+        <v>1023.19</v>
       </c>
       <c r="D186" t="n">
-        <v>1009.59</v>
+        <v>1009.55</v>
       </c>
       <c r="E186" t="n">
-        <v>1036.87</v>
+        <v>1036.83</v>
       </c>
       <c r="F186" t="n">
         <v>2658</v>
@@ -28210,13 +28210,13 @@
         </is>
       </c>
       <c r="C187" t="n">
-        <v>1021.15</v>
+        <v>1021.11</v>
       </c>
       <c r="D187" t="n">
-        <v>1010.21</v>
+        <v>1010.17</v>
       </c>
       <c r="E187" t="n">
-        <v>1032.08</v>
+        <v>1032.04</v>
       </c>
       <c r="F187" t="n">
         <v>6310</v>
@@ -28361,13 +28361,13 @@
         </is>
       </c>
       <c r="C188" t="n">
-        <v>994.631</v>
+        <v>994.5940000000001</v>
       </c>
       <c r="D188" t="n">
-        <v>982</v>
+        <v>981.963</v>
       </c>
       <c r="E188" t="n">
-        <v>1007.26</v>
+        <v>1007.23</v>
       </c>
       <c r="F188" t="n">
         <v>4914</v>
@@ -28512,13 +28512,13 @@
         </is>
       </c>
       <c r="C189" t="n">
-        <v>990.405</v>
+        <v>990.37</v>
       </c>
       <c r="D189" t="n">
-        <v>977.962</v>
+        <v>977.927</v>
       </c>
       <c r="E189" t="n">
-        <v>1002.85</v>
+        <v>1002.81</v>
       </c>
       <c r="F189" t="n">
         <v>4203</v>
@@ -28663,13 +28663,13 @@
         </is>
       </c>
       <c r="C190" t="n">
-        <v>979.199</v>
+        <v>979.158</v>
       </c>
       <c r="D190" t="n">
-        <v>965.578</v>
+        <v>965.537</v>
       </c>
       <c r="E190" t="n">
-        <v>992.8200000000001</v>
+        <v>992.779</v>
       </c>
       <c r="F190" t="n">
         <v>3412</v>
@@ -28814,13 +28814,13 @@
         </is>
       </c>
       <c r="C191" t="n">
-        <v>971.3049999999999</v>
+        <v>971.268</v>
       </c>
       <c r="D191" t="n">
-        <v>955.383</v>
+        <v>955.346</v>
       </c>
       <c r="E191" t="n">
-        <v>987.227</v>
+        <v>987.1900000000001</v>
       </c>
       <c r="F191" t="n">
         <v>2391</v>
@@ -28965,13 +28965,13 @@
         </is>
       </c>
       <c r="C192" t="n">
-        <v>951.67</v>
+        <v>951.633</v>
       </c>
       <c r="D192" t="n">
-        <v>938.8440000000001</v>
+        <v>938.808</v>
       </c>
       <c r="E192" t="n">
-        <v>964.495</v>
+        <v>964.4589999999999</v>
       </c>
       <c r="F192" t="n">
         <v>3287</v>
@@ -29260,7 +29260,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -29369,7 +29369,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -29474,7 +29474,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -29544,7 +29544,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -29649,7 +29649,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -30057,14 +30057,14 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>qwen3.5-122b-a10b</t>
+          <t>deepseek-v3.1</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>125</v>
+        <v>685</v>
       </c>
       <c r="C15" t="n">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -30080,14 +30080,14 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>deepseek-v3.1</t>
+          <t>qwen3.5-122b-a10b</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>685</v>
+        <v>125</v>
       </c>
       <c r="C16" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -30678,46 +30678,46 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>trinity-large</t>
+          <t>qwen3-235b-a22b</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>70</v>
+        <v>235</v>
       </c>
       <c r="C42" t="n">
-        <v>70</v>
+        <v>22</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>dense</t>
+          <t>moe</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>artificial_analysis</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>qwen3-235b-a22b</t>
+          <t>trinity-large</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>235</v>
+        <v>70</v>
       </c>
       <c r="C43" t="n">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>moe</t>
+          <t>dense</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>artificial_analysis</t>
+          <t>override</t>
         </is>
       </c>
     </row>
@@ -31651,14 +31651,14 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>mistral-small-3.1-24b-instruct-2503</t>
+          <t>gemma-3-4b-it</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>24</v>
+        <v>4.3</v>
       </c>
       <c r="C85" t="n">
-        <v>24</v>
+        <v>4.3</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -31674,14 +31674,14 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>gemma-3-4b-it</t>
+          <t>mistral-small-3.1-24b-instruct-2503</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>4.3</v>
+        <v>24</v>
       </c>
       <c r="C86" t="n">
-        <v>4.3</v>
+        <v>24</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>

--- a/arena_enrichment/output/arena_leaderboard_enriched.xlsx
+++ b/arena_enrichment/output/arena_leaderboard_enriched.xlsx
@@ -675,16 +675,16 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>1456.41</v>
+        <v>1455.3</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1450.39</v>
+        <v>1449.31</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1462.44</v>
+        <v>1461.29</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>11023</v>
+        <v>11093</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
@@ -826,16 +826,16 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>1452.81</v>
+        <v>1452.68</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1447.54</v>
+        <v>1447.42</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1458.08</v>
+        <v>1457.94</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>16269</v>
+        <v>16262</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
@@ -977,16 +977,16 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>1451.77</v>
+        <v>1451.63</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1445.62</v>
+        <v>1445.51</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1457.93</v>
+        <v>1457.74</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>10272</v>
+        <v>10431</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
@@ -1128,16 +1128,16 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>1442.28</v>
+        <v>1442.63</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1436.2</v>
+        <v>1436.52</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1448.36</v>
+        <v>1448.75</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>12421</v>
+        <v>12242</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
@@ -1279,16 +1279,16 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1432.45</v>
+        <v>1433.19</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1425.89</v>
+        <v>1426.57</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1439</v>
+        <v>1439.82</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>8473</v>
+        <v>8257</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
@@ -1430,16 +1430,16 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>1429.83</v>
+        <v>1429.69</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>1426.14</v>
+        <v>1425.99</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1433.53</v>
+        <v>1433.39</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>42016</v>
+        <v>41738</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
@@ -1581,16 +1581,16 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>1425.98</v>
+        <v>1425.85</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>1422.04</v>
+        <v>1421.9</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1429.91</v>
+        <v>1429.79</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>36415</v>
+        <v>36102</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
@@ -1732,16 +1732,16 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>1424.82</v>
+        <v>1424.73</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1418.31</v>
+        <v>1418.22</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1431.34</v>
+        <v>1431.25</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>9201</v>
+        <v>9188</v>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
@@ -1883,16 +1883,16 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>1424.05</v>
+        <v>1424.52</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>1420</v>
+        <v>1420.46</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1428.1</v>
+        <v>1428.57</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>36746</v>
+        <v>36511</v>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
@@ -2034,16 +2034,16 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>1423.55</v>
+        <v>1423.24</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>1417.16</v>
+        <v>1416.84</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1429.95</v>
+        <v>1429.64</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>12186</v>
+        <v>12088</v>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
@@ -2185,16 +2185,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1422.02</v>
+        <v>1422.08</v>
       </c>
       <c r="D12" t="n">
-        <v>1419.14</v>
+        <v>1419.2</v>
       </c>
       <c r="E12" t="n">
-        <v>1424.91</v>
+        <v>1424.97</v>
       </c>
       <c r="F12" t="n">
-        <v>78018</v>
+        <v>77683</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -2336,16 +2336,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1421.61</v>
+        <v>1421.6</v>
       </c>
       <c r="D13" t="n">
-        <v>1417.46</v>
+        <v>1417.44</v>
       </c>
       <c r="E13" t="n">
-        <v>1425.77</v>
+        <v>1425.76</v>
       </c>
       <c r="F13" t="n">
-        <v>31259</v>
+        <v>31048</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -2487,16 +2487,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1420.88</v>
+        <v>1421.02</v>
       </c>
       <c r="D14" t="n">
-        <v>1415.26</v>
+        <v>1415.4</v>
       </c>
       <c r="E14" t="n">
-        <v>1426.5</v>
+        <v>1426.64</v>
       </c>
       <c r="F14" t="n">
-        <v>18855</v>
+        <v>18831</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -2638,16 +2638,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1417.96</v>
+        <v>1418.02</v>
       </c>
       <c r="D15" t="n">
-        <v>1411.97</v>
+        <v>1412.03</v>
       </c>
       <c r="E15" t="n">
-        <v>1423.95</v>
+        <v>1424.01</v>
       </c>
       <c r="F15" t="n">
-        <v>15170</v>
+        <v>15150</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -2785,36 +2785,36 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>qwen3.5-122b-a10b</t>
+          <t>kimi-k2-0905-preview</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1417.58</v>
+        <v>1417.75</v>
       </c>
       <c r="D16" t="n">
-        <v>1410.32</v>
+        <v>1411.28</v>
       </c>
       <c r="E16" t="n">
-        <v>1424.83</v>
+        <v>1424.23</v>
       </c>
       <c r="F16" t="n">
-        <v>6688</v>
+        <v>11924</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alibaba</t>
+          <t>Moonshot</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
+          <t>Modified MIT</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>125</v>
+        <v>1000</v>
       </c>
       <c r="J16" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -2823,26 +2823,26 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>artificial_analysis</t>
+          <t>override</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>250</v>
+        <v>2000</v>
       </c>
       <c r="N16" t="n">
-        <v>312.5</v>
+        <v>2500</v>
       </c>
       <c r="O16" t="n">
-        <v>125</v>
+        <v>1000</v>
       </c>
       <c r="P16" t="n">
-        <v>156.2</v>
+        <v>1250</v>
       </c>
       <c r="Q16" t="n">
-        <v>62.5</v>
+        <v>500</v>
       </c>
       <c r="R16" t="n">
-        <v>78.09999999999999</v>
+        <v>625</v>
       </c>
       <c r="S16" s="5" t="inlineStr">
         <is>
@@ -2854,9 +2854,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="U16" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="U16" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="V16" s="5" t="inlineStr">
@@ -2869,9 +2869,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="X16" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="X16" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="Y16" s="5" t="inlineStr">
@@ -2884,9 +2884,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AA16" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AA16" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AB16" s="5" t="inlineStr">
@@ -2894,14 +2894,14 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AC16" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AD16" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AC16" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD16" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AE16" s="5" t="inlineStr">
@@ -2909,14 +2909,14 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AF16" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AG16" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AF16" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AG16" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
@@ -2926,7 +2926,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>B200 SXM</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
     </row>
@@ -2936,36 +2936,36 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>kimi-k2-0905-preview</t>
+          <t>qwen3.5-122b-a10b</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1417.39</v>
+        <v>1417.32</v>
       </c>
       <c r="D17" t="n">
-        <v>1410.92</v>
+        <v>1410.19</v>
       </c>
       <c r="E17" t="n">
-        <v>1423.86</v>
+        <v>1424.45</v>
       </c>
       <c r="F17" t="n">
-        <v>11954</v>
+        <v>6946</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Moonshot</t>
+          <t>Alibaba</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Modified MIT</t>
+          <t>Apache 2.0</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1000</v>
+        <v>125</v>
       </c>
       <c r="J17" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -2974,26 +2974,26 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>artificial_analysis</t>
         </is>
       </c>
       <c r="M17" t="n">
-        <v>2000</v>
+        <v>250</v>
       </c>
       <c r="N17" t="n">
-        <v>2500</v>
+        <v>312.5</v>
       </c>
       <c r="O17" t="n">
-        <v>1000</v>
+        <v>125</v>
       </c>
       <c r="P17" t="n">
-        <v>1250</v>
+        <v>156.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>500</v>
+        <v>62.5</v>
       </c>
       <c r="R17" t="n">
-        <v>625</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="S17" s="5" t="inlineStr">
         <is>
@@ -3005,9 +3005,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="U17" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="U17" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="V17" s="5" t="inlineStr">
@@ -3020,9 +3020,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="X17" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="X17" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Y17" s="5" t="inlineStr">
@@ -3035,9 +3035,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AA17" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AA17" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AB17" s="5" t="inlineStr">
@@ -3045,14 +3045,14 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AC17" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AD17" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AC17" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AD17" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AE17" s="5" t="inlineStr">
@@ -3060,14 +3060,14 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AF17" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AG17" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AF17" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AG17" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>B200 SXM</t>
         </is>
       </c>
     </row>
@@ -3091,16 +3091,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1416.93</v>
+        <v>1417.05</v>
       </c>
       <c r="D18" t="n">
-        <v>1412.1</v>
+        <v>1412.22</v>
       </c>
       <c r="E18" t="n">
-        <v>1421.76</v>
+        <v>1421.89</v>
       </c>
       <c r="F18" t="n">
-        <v>28137</v>
+        <v>28082</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -3242,16 +3242,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1416.82</v>
+        <v>1416.93</v>
       </c>
       <c r="D19" t="n">
-        <v>1410.24</v>
+        <v>1410.35</v>
       </c>
       <c r="E19" t="n">
-        <v>1423.4</v>
+        <v>1423.51</v>
       </c>
       <c r="F19" t="n">
-        <v>11903</v>
+        <v>11885</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -3389,36 +3389,36 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>mistral-large-3</t>
+          <t>deepseek-v3.1-terminus-thinking</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1416.4</v>
+        <v>1416.41</v>
       </c>
       <c r="D20" t="n">
-        <v>1412.38</v>
+        <v>1406.47</v>
       </c>
       <c r="E20" t="n">
-        <v>1420.42</v>
+        <v>1426.34</v>
       </c>
       <c r="F20" t="n">
-        <v>33411</v>
+        <v>3497</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Mistral</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>675</v>
+        <v>685</v>
       </c>
       <c r="J20" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -3431,22 +3431,22 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>1350</v>
+        <v>1370</v>
       </c>
       <c r="N20" t="n">
-        <v>1687.5</v>
+        <v>1712.5</v>
       </c>
       <c r="O20" t="n">
-        <v>675</v>
+        <v>685</v>
       </c>
       <c r="P20" t="n">
-        <v>843.8</v>
+        <v>856.2</v>
       </c>
       <c r="Q20" t="n">
-        <v>337.5</v>
+        <v>342.5</v>
       </c>
       <c r="R20" t="n">
-        <v>421.9</v>
+        <v>428.1</v>
       </c>
       <c r="S20" s="5" t="inlineStr">
         <is>
@@ -3540,36 +3540,36 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>deepseek-v3.1-terminus-thinking</t>
+          <t>mistral-large-3</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1416.27</v>
+        <v>1416.39</v>
       </c>
       <c r="D21" t="n">
-        <v>1406.35</v>
+        <v>1412.35</v>
       </c>
       <c r="E21" t="n">
-        <v>1426.18</v>
+        <v>1420.42</v>
       </c>
       <c r="F21" t="n">
-        <v>3508</v>
+        <v>33200</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>DeepSeek</t>
+          <t>Mistral</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Apache 2.0</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>685</v>
+        <v>675</v>
       </c>
       <c r="J21" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -3582,22 +3582,22 @@
         </is>
       </c>
       <c r="M21" t="n">
-        <v>1370</v>
+        <v>1350</v>
       </c>
       <c r="N21" t="n">
-        <v>1712.5</v>
+        <v>1687.5</v>
       </c>
       <c r="O21" t="n">
-        <v>685</v>
+        <v>675</v>
       </c>
       <c r="P21" t="n">
-        <v>856.2</v>
+        <v>843.8</v>
       </c>
       <c r="Q21" t="n">
-        <v>342.5</v>
+        <v>337.5</v>
       </c>
       <c r="R21" t="n">
-        <v>428.1</v>
+        <v>421.9</v>
       </c>
       <c r="S21" s="5" t="inlineStr">
         <is>
@@ -3695,16 +3695,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1415.44</v>
+        <v>1415.62</v>
       </c>
       <c r="D22" t="n">
-        <v>1405.86</v>
+        <v>1406.04</v>
       </c>
       <c r="E22" t="n">
-        <v>1425.01</v>
+        <v>1425.2</v>
       </c>
       <c r="F22" t="n">
-        <v>3744</v>
+        <v>3736</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -3846,16 +3846,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1415.32</v>
+        <v>1415.46</v>
       </c>
       <c r="D23" t="n">
-        <v>1408.87</v>
+        <v>1409</v>
       </c>
       <c r="E23" t="n">
-        <v>1421.76</v>
+        <v>1421.91</v>
       </c>
       <c r="F23" t="n">
-        <v>11714</v>
+        <v>11645</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -3997,16 +3997,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1410.73</v>
+        <v>1410.68</v>
       </c>
       <c r="D24" t="n">
-        <v>1405.88</v>
+        <v>1405.83</v>
       </c>
       <c r="E24" t="n">
-        <v>1415.59</v>
+        <v>1415.54</v>
       </c>
       <c r="F24" t="n">
-        <v>24669</v>
+        <v>24640</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -4148,16 +4148,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1406.36</v>
+        <v>1406.31</v>
       </c>
       <c r="D25" t="n">
-        <v>1399.16</v>
+        <v>1399.21</v>
       </c>
       <c r="E25" t="n">
-        <v>1413.57</v>
+        <v>1413.42</v>
       </c>
       <c r="F25" t="n">
-        <v>6777</v>
+        <v>6957</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -4299,16 +4299,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1405.23</v>
+        <v>1405.31</v>
       </c>
       <c r="D26" t="n">
-        <v>1399.33</v>
+        <v>1399.46</v>
       </c>
       <c r="E26" t="n">
-        <v>1411.14</v>
+        <v>1411.17</v>
       </c>
       <c r="F26" t="n">
-        <v>11752</v>
+        <v>11909</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -4450,16 +4450,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1402.47</v>
+        <v>1402.71</v>
       </c>
       <c r="D27" t="n">
-        <v>1397.99</v>
+        <v>1398.23</v>
       </c>
       <c r="E27" t="n">
-        <v>1406.94</v>
+        <v>1407.19</v>
       </c>
       <c r="F27" t="n">
-        <v>38861</v>
+        <v>38797</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -4601,16 +4601,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1401.28</v>
+        <v>1401.49</v>
       </c>
       <c r="D28" t="n">
-        <v>1396.52</v>
+        <v>1396.73</v>
       </c>
       <c r="E28" t="n">
-        <v>1406.03</v>
+        <v>1406.25</v>
       </c>
       <c r="F28" t="n">
-        <v>23252</v>
+        <v>23187</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -4748,36 +4748,36 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>longcat-flash-chat</t>
+          <t>qwen3.5-35b-a3b</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1400.54</v>
+        <v>1401</v>
       </c>
       <c r="D29" t="n">
-        <v>1394.18</v>
+        <v>1393.98</v>
       </c>
       <c r="E29" t="n">
-        <v>1406.9</v>
+        <v>1408.01</v>
       </c>
       <c r="F29" t="n">
-        <v>11535</v>
+        <v>7278</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Meituan</t>
+          <t>Alibaba</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Apache 2.0</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>560</v>
+        <v>36</v>
       </c>
       <c r="J29" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -4786,40 +4786,40 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>artificial_analysis</t>
         </is>
       </c>
       <c r="M29" t="n">
-        <v>1120</v>
+        <v>72</v>
       </c>
       <c r="N29" t="n">
-        <v>1400</v>
+        <v>90</v>
       </c>
       <c r="O29" t="n">
-        <v>560</v>
+        <v>36</v>
       </c>
       <c r="P29" t="n">
-        <v>700</v>
+        <v>45</v>
       </c>
       <c r="Q29" t="n">
-        <v>280</v>
+        <v>18</v>
       </c>
       <c r="R29" t="n">
-        <v>350</v>
-      </c>
-      <c r="S29" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T29" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U29" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+        <v>22.5</v>
+      </c>
+      <c r="S29" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T29" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U29" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="V29" s="5" t="inlineStr">
@@ -4827,69 +4827,69 @@
           <t>No</t>
         </is>
       </c>
-      <c r="W29" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X29" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Y29" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z29" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AA29" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AB29" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AC29" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AD29" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AE29" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AF29" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AG29" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="W29" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X29" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y29" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z29" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AA29" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB29" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AC29" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AD29" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE29" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AF29" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AG29" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>RTX PRO 6000</t>
         </is>
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>H100 SXM</t>
         </is>
       </c>
     </row>
@@ -4899,36 +4899,36 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>qwen3-235b-a22b-thinking-2507</t>
+          <t>longcat-flash-chat</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1399.06</v>
+        <v>1400.43</v>
       </c>
       <c r="D30" t="n">
-        <v>1392.57</v>
+        <v>1394.07</v>
       </c>
       <c r="E30" t="n">
-        <v>1405.56</v>
+        <v>1406.79</v>
       </c>
       <c r="F30" t="n">
-        <v>9137</v>
+        <v>11517</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alibaba</t>
+          <t>Meituan</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>235</v>
+        <v>560</v>
       </c>
       <c r="J30" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -4937,26 +4937,26 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>override</t>
         </is>
       </c>
       <c r="M30" t="n">
-        <v>470</v>
+        <v>1120</v>
       </c>
       <c r="N30" t="n">
-        <v>587.5</v>
+        <v>1400</v>
       </c>
       <c r="O30" t="n">
-        <v>235</v>
+        <v>560</v>
       </c>
       <c r="P30" t="n">
-        <v>293.8</v>
+        <v>700</v>
       </c>
       <c r="Q30" t="n">
-        <v>117.5</v>
+        <v>280</v>
       </c>
       <c r="R30" t="n">
-        <v>146.9</v>
+        <v>350</v>
       </c>
       <c r="S30" s="5" t="inlineStr">
         <is>
@@ -5013,9 +5013,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AD30" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AD30" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AE30" s="5" t="inlineStr">
@@ -5028,9 +5028,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AG30" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AG30" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AH30" t="inlineStr">
@@ -5050,20 +5050,20 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>qwen3.5-35b-a3b</t>
+          <t>qwen3-235b-a22b-thinking-2507</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1399.04</v>
+        <v>1399.16</v>
       </c>
       <c r="D31" t="n">
-        <v>1391.91</v>
+        <v>1392.66</v>
       </c>
       <c r="E31" t="n">
-        <v>1406.17</v>
+        <v>1405.66</v>
       </c>
       <c r="F31" t="n">
-        <v>7042</v>
+        <v>9128</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -5076,10 +5076,10 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>36</v>
+        <v>235</v>
       </c>
       <c r="J31" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -5088,40 +5088,40 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>artificial_analysis</t>
+          <t>name_parsing</t>
         </is>
       </c>
       <c r="M31" t="n">
-        <v>72</v>
+        <v>470</v>
       </c>
       <c r="N31" t="n">
-        <v>90</v>
+        <v>587.5</v>
       </c>
       <c r="O31" t="n">
-        <v>36</v>
+        <v>235</v>
       </c>
       <c r="P31" t="n">
-        <v>45</v>
+        <v>293.8</v>
       </c>
       <c r="Q31" t="n">
-        <v>18</v>
+        <v>117.5</v>
       </c>
       <c r="R31" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="S31" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="T31" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="U31" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+        <v>146.9</v>
+      </c>
+      <c r="S31" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T31" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U31" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="V31" s="5" t="inlineStr">
@@ -5129,39 +5129,39 @@
           <t>No</t>
         </is>
       </c>
-      <c r="W31" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X31" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Y31" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z31" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AA31" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB31" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AC31" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="W31" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X31" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y31" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z31" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA31" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AB31" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AC31" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AD31" s="6" t="inlineStr">
@@ -5169,14 +5169,14 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="AE31" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AF31" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AE31" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF31" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AG31" s="6" t="inlineStr">
@@ -5186,12 +5186,12 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>RTX PRO 6000</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
     </row>
@@ -5205,13 +5205,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1397.55</v>
+        <v>1397.57</v>
       </c>
       <c r="D32" t="n">
-        <v>1392.7</v>
+        <v>1392.72</v>
       </c>
       <c r="E32" t="n">
-        <v>1402.4</v>
+        <v>1402.43</v>
       </c>
       <c r="F32" t="n">
         <v>18524</v>
@@ -5356,16 +5356,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1395.53</v>
+        <v>1395.82</v>
       </c>
       <c r="D33" t="n">
-        <v>1388.78</v>
+        <v>1389.06</v>
       </c>
       <c r="E33" t="n">
-        <v>1402.28</v>
+        <v>1402.58</v>
       </c>
       <c r="F33" t="n">
-        <v>8081</v>
+        <v>8052</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -5507,16 +5507,16 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1394.33</v>
+        <v>1394.34</v>
       </c>
       <c r="D34" t="n">
         <v>1390.49</v>
       </c>
       <c r="E34" t="n">
-        <v>1398.18</v>
+        <v>1398.19</v>
       </c>
       <c r="F34" t="n">
-        <v>46197</v>
+        <v>46144</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -5658,16 +5658,16 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1391.92</v>
+        <v>1391.89</v>
       </c>
       <c r="D35" t="n">
-        <v>1387.53</v>
+        <v>1387.49</v>
       </c>
       <c r="E35" t="n">
-        <v>1396.32</v>
+        <v>1396.3</v>
       </c>
       <c r="F35" t="n">
-        <v>25545</v>
+        <v>25427</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -5805,36 +5805,36 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>mimo-v2-flash (thinking)</t>
+          <t>step-3.5-flash</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1387.75</v>
+        <v>1388.71</v>
       </c>
       <c r="D36" t="n">
-        <v>1381.5</v>
+        <v>1383.19</v>
       </c>
       <c r="E36" t="n">
-        <v>1394</v>
+        <v>1394.23</v>
       </c>
       <c r="F36" t="n">
-        <v>11256</v>
+        <v>13885</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Xiaomi</t>
+          <t>StepFun</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Apache 2.0</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>309</v>
+        <v>196</v>
       </c>
       <c r="J36" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -5847,22 +5847,22 @@
         </is>
       </c>
       <c r="M36" t="n">
-        <v>618</v>
+        <v>392</v>
       </c>
       <c r="N36" t="n">
-        <v>772.5</v>
+        <v>490</v>
       </c>
       <c r="O36" t="n">
-        <v>309</v>
+        <v>196</v>
       </c>
       <c r="P36" t="n">
-        <v>386.2</v>
+        <v>245</v>
       </c>
       <c r="Q36" t="n">
-        <v>154.5</v>
+        <v>98</v>
       </c>
       <c r="R36" t="n">
-        <v>193.1</v>
+        <v>122.5</v>
       </c>
       <c r="S36" s="5" t="inlineStr">
         <is>
@@ -5904,9 +5904,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AA36" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AA36" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AB36" s="5" t="inlineStr">
@@ -5919,9 +5919,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AD36" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AD36" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AE36" s="5" t="inlineStr">
@@ -5929,9 +5929,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AF36" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AF36" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AG36" s="6" t="inlineStr">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>B300 SXM</t>
         </is>
       </c>
     </row>
@@ -5956,36 +5956,36 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>step-3.5-flash</t>
+          <t>mimo-v2-flash (thinking)</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1387.55</v>
+        <v>1387.3</v>
       </c>
       <c r="D37" t="n">
-        <v>1382.05</v>
+        <v>1381.01</v>
       </c>
       <c r="E37" t="n">
-        <v>1393.05</v>
+        <v>1393.59</v>
       </c>
       <c r="F37" t="n">
-        <v>13890</v>
+        <v>11053</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>StepFun</t>
+          <t>Xiaomi</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>196</v>
+        <v>309</v>
       </c>
       <c r="J37" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -5998,22 +5998,22 @@
         </is>
       </c>
       <c r="M37" t="n">
-        <v>392</v>
+        <v>618</v>
       </c>
       <c r="N37" t="n">
-        <v>490</v>
+        <v>772.5</v>
       </c>
       <c r="O37" t="n">
-        <v>196</v>
+        <v>309</v>
       </c>
       <c r="P37" t="n">
-        <v>245</v>
+        <v>386.2</v>
       </c>
       <c r="Q37" t="n">
-        <v>98</v>
+        <v>154.5</v>
       </c>
       <c r="R37" t="n">
-        <v>122.5</v>
+        <v>193.1</v>
       </c>
       <c r="S37" s="5" t="inlineStr">
         <is>
@@ -6055,9 +6055,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AA37" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AA37" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AB37" s="5" t="inlineStr">
@@ -6070,9 +6070,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AD37" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AD37" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AE37" s="5" t="inlineStr">
@@ -6080,9 +6080,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AF37" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AF37" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AG37" s="6" t="inlineStr">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>B300 SXM</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
     </row>
@@ -6111,16 +6111,16 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1386.89</v>
+        <v>1387.09</v>
       </c>
       <c r="D38" t="n">
-        <v>1381.97</v>
+        <v>1382.17</v>
       </c>
       <c r="E38" t="n">
-        <v>1391.8</v>
+        <v>1392</v>
       </c>
       <c r="F38" t="n">
-        <v>26234</v>
+        <v>26162</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -6262,16 +6262,16 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1385.82</v>
+        <v>1385.97</v>
       </c>
       <c r="D39" t="n">
-        <v>1380.59</v>
+        <v>1380.7</v>
       </c>
       <c r="E39" t="n">
-        <v>1391.06</v>
+        <v>1391.24</v>
       </c>
       <c r="F39" t="n">
-        <v>17582</v>
+        <v>17271</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -6419,10 +6419,10 @@
         <v>1378.09</v>
       </c>
       <c r="E40" t="n">
-        <v>1387.79</v>
+        <v>1387.8</v>
       </c>
       <c r="F40" t="n">
-        <v>24134</v>
+        <v>24086</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -6564,16 +6564,16 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1377.9</v>
+        <v>1378</v>
       </c>
       <c r="D41" t="n">
-        <v>1366.7</v>
+        <v>1366.75</v>
       </c>
       <c r="E41" t="n">
-        <v>1389.09</v>
+        <v>1389.26</v>
       </c>
       <c r="F41" t="n">
-        <v>2861</v>
+        <v>2836</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -6711,24 +6711,24 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>qwen3-235b-a22b</t>
+          <t>trinity-large</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1374.53</v>
+        <v>1375.54</v>
       </c>
       <c r="D42" t="n">
-        <v>1369.86</v>
+        <v>1368.63</v>
       </c>
       <c r="E42" t="n">
-        <v>1379.21</v>
+        <v>1382.45</v>
       </c>
       <c r="F42" t="n">
-        <v>26703</v>
+        <v>8033</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alibaba</t>
+          <t>Arcee AI</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -6737,52 +6737,52 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>235</v>
+        <v>70</v>
       </c>
       <c r="J42" t="n">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>moe</t>
+          <t>dense</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>artificial_analysis</t>
+          <t>override</t>
         </is>
       </c>
       <c r="M42" t="n">
-        <v>470</v>
+        <v>140</v>
       </c>
       <c r="N42" t="n">
-        <v>587.5</v>
+        <v>175</v>
       </c>
       <c r="O42" t="n">
-        <v>235</v>
+        <v>70</v>
       </c>
       <c r="P42" t="n">
-        <v>293.8</v>
+        <v>87.5</v>
       </c>
       <c r="Q42" t="n">
-        <v>117.5</v>
+        <v>35</v>
       </c>
       <c r="R42" t="n">
-        <v>146.9</v>
+        <v>43.8</v>
       </c>
       <c r="S42" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="T42" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U42" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="T42" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U42" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="V42" s="5" t="inlineStr">
@@ -6795,9 +6795,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="X42" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="X42" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Y42" s="5" t="inlineStr">
@@ -6805,24 +6805,24 @@
           <t>No</t>
         </is>
       </c>
-      <c r="Z42" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AA42" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AB42" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AC42" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="Z42" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AA42" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB42" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AC42" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AD42" s="6" t="inlineStr">
@@ -6830,14 +6830,14 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="AE42" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AF42" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AE42" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AF42" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AG42" s="6" t="inlineStr">
@@ -6847,12 +6847,12 @@
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>B200 SXM</t>
         </is>
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>RTX PRO 6000</t>
         </is>
       </c>
     </row>
@@ -6862,24 +6862,24 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>trinity-large</t>
+          <t>qwen3-235b-a22b</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1374.37</v>
+        <v>1374.5</v>
       </c>
       <c r="D43" t="n">
-        <v>1367.33</v>
+        <v>1369.83</v>
       </c>
       <c r="E43" t="n">
-        <v>1381.41</v>
+        <v>1379.18</v>
       </c>
       <c r="F43" t="n">
-        <v>7793</v>
+        <v>26679</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Arcee AI</t>
+          <t>Alibaba</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -6888,52 +6888,52 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>70</v>
+        <v>235</v>
       </c>
       <c r="J43" t="n">
-        <v>70</v>
+        <v>22</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>dense</t>
+          <t>moe</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>artificial_analysis</t>
         </is>
       </c>
       <c r="M43" t="n">
-        <v>140</v>
+        <v>470</v>
       </c>
       <c r="N43" t="n">
-        <v>175</v>
+        <v>587.5</v>
       </c>
       <c r="O43" t="n">
-        <v>70</v>
+        <v>235</v>
       </c>
       <c r="P43" t="n">
-        <v>87.5</v>
+        <v>293.8</v>
       </c>
       <c r="Q43" t="n">
-        <v>35</v>
+        <v>117.5</v>
       </c>
       <c r="R43" t="n">
-        <v>43.8</v>
+        <v>146.9</v>
       </c>
       <c r="S43" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="T43" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="U43" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="T43" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U43" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="V43" s="5" t="inlineStr">
@@ -6946,9 +6946,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="X43" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="X43" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="Y43" s="5" t="inlineStr">
@@ -6956,24 +6956,24 @@
           <t>No</t>
         </is>
       </c>
-      <c r="Z43" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AA43" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB43" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AC43" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="Z43" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA43" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AB43" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AC43" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AD43" s="6" t="inlineStr">
@@ -6981,14 +6981,14 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="AE43" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AF43" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AE43" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF43" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AG43" s="6" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="AH43" t="inlineStr">
         <is>
-          <t>B200 SXM</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>RTX PRO 6000</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
     </row>
@@ -7017,16 +7017,16 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1372.38</v>
+        <v>1372.36</v>
       </c>
       <c r="D44" t="n">
-        <v>1368.15</v>
+        <v>1368.13</v>
       </c>
       <c r="E44" t="n">
         <v>1376.6</v>
       </c>
       <c r="F44" t="n">
-        <v>31597</v>
+        <v>31546</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -7168,16 +7168,16 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1368.77</v>
+        <v>1368.85</v>
       </c>
       <c r="D45" t="n">
-        <v>1362.96</v>
+        <v>1363.04</v>
       </c>
       <c r="E45" t="n">
-        <v>1374.57</v>
+        <v>1374.66</v>
       </c>
       <c r="F45" t="n">
-        <v>13940</v>
+        <v>13906</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -7319,16 +7319,16 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1368.3</v>
+        <v>1368.47</v>
       </c>
       <c r="D46" t="n">
-        <v>1362.51</v>
+        <v>1362.64</v>
       </c>
       <c r="E46" t="n">
-        <v>1374.08</v>
+        <v>1374.31</v>
       </c>
       <c r="F46" t="n">
-        <v>12109</v>
+        <v>11857</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -7470,16 +7470,16 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1365.29</v>
+        <v>1365.3</v>
       </c>
       <c r="D47" t="n">
-        <v>1361.64</v>
+        <v>1361.65</v>
       </c>
       <c r="E47" t="n">
-        <v>1368.94</v>
+        <v>1368.95</v>
       </c>
       <c r="F47" t="n">
-        <v>48251</v>
+        <v>48195</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -7617,36 +7617,36 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>minimax-m1</t>
+          <t>nvidia-nemotron-3-super-120b-a12b</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1364.91</v>
+        <v>1364.56</v>
       </c>
       <c r="D48" t="n">
-        <v>1360.67</v>
+        <v>1354.88</v>
       </c>
       <c r="E48" t="n">
-        <v>1369.15</v>
+        <v>1374.23</v>
       </c>
       <c r="F48" t="n">
-        <v>36104</v>
+        <v>3641</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>MiniMax</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
+          <t>NVIDIA Open Model</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>456</v>
+        <v>120.6</v>
       </c>
       <c r="J48" t="n">
-        <v>45.9</v>
+        <v>12.7</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -7659,22 +7659,22 @@
         </is>
       </c>
       <c r="M48" t="n">
-        <v>912</v>
+        <v>241.2</v>
       </c>
       <c r="N48" t="n">
-        <v>1140</v>
+        <v>301.5</v>
       </c>
       <c r="O48" t="n">
-        <v>456</v>
+        <v>120.6</v>
       </c>
       <c r="P48" t="n">
-        <v>570</v>
+        <v>150.8</v>
       </c>
       <c r="Q48" t="n">
-        <v>228</v>
+        <v>60.3</v>
       </c>
       <c r="R48" t="n">
-        <v>285</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="S48" s="5" t="inlineStr">
         <is>
@@ -7686,9 +7686,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="U48" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="U48" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="V48" s="5" t="inlineStr">
@@ -7701,9 +7701,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="X48" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="X48" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Y48" s="5" t="inlineStr">
@@ -7716,9 +7716,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AA48" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AA48" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AB48" s="5" t="inlineStr">
@@ -7726,14 +7726,14 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AC48" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AD48" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AC48" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AD48" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AE48" s="5" t="inlineStr">
@@ -7741,9 +7741,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AF48" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AF48" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AG48" s="6" t="inlineStr">
@@ -7758,7 +7758,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>B200 SXM</t>
         </is>
       </c>
     </row>
@@ -7768,36 +7768,36 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>nvidia-nemotron-3-super-120b-a12b</t>
+          <t>minimax-m1</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1364.6</v>
+        <v>1364.38</v>
       </c>
       <c r="D49" t="n">
-        <v>1355.02</v>
+        <v>1360.14</v>
       </c>
       <c r="E49" t="n">
-        <v>1374.18</v>
+        <v>1368.63</v>
       </c>
       <c r="F49" t="n">
-        <v>3711</v>
+        <v>35951</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>MiniMax</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>NVIDIA Open Model</t>
+          <t>Apache 2.0</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>120.6</v>
+        <v>456</v>
       </c>
       <c r="J49" t="n">
-        <v>12.7</v>
+        <v>45.9</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -7810,22 +7810,22 @@
         </is>
       </c>
       <c r="M49" t="n">
-        <v>241.2</v>
+        <v>912</v>
       </c>
       <c r="N49" t="n">
-        <v>301.5</v>
+        <v>1140</v>
       </c>
       <c r="O49" t="n">
-        <v>120.6</v>
+        <v>456</v>
       </c>
       <c r="P49" t="n">
-        <v>150.8</v>
+        <v>570</v>
       </c>
       <c r="Q49" t="n">
-        <v>60.3</v>
+        <v>228</v>
       </c>
       <c r="R49" t="n">
-        <v>75.40000000000001</v>
+        <v>285</v>
       </c>
       <c r="S49" s="5" t="inlineStr">
         <is>
@@ -7837,9 +7837,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="U49" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="U49" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="V49" s="5" t="inlineStr">
@@ -7852,9 +7852,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="X49" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="X49" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="Y49" s="5" t="inlineStr">
@@ -7867,9 +7867,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AA49" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AA49" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AB49" s="5" t="inlineStr">
@@ -7877,14 +7877,14 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AC49" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AD49" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AC49" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD49" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AE49" s="5" t="inlineStr">
@@ -7892,9 +7892,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AF49" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AF49" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AG49" s="6" t="inlineStr">
@@ -7909,7 +7909,7 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>B200 SXM</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
     </row>
@@ -7923,13 +7923,13 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1358.24</v>
+        <v>1358.28</v>
       </c>
       <c r="D50" t="n">
-        <v>1353.52</v>
+        <v>1353.57</v>
       </c>
       <c r="E50" t="n">
-        <v>1362.95</v>
+        <v>1362.99</v>
       </c>
       <c r="F50" t="n">
         <v>21770</v>
@@ -8074,16 +8074,16 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1357.03</v>
+        <v>1357.11</v>
       </c>
       <c r="D51" t="n">
-        <v>1351.86</v>
+        <v>1351.94</v>
       </c>
       <c r="E51" t="n">
-        <v>1362.2</v>
+        <v>1362.29</v>
       </c>
       <c r="F51" t="n">
-        <v>18036</v>
+        <v>18015</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -8225,16 +8225,16 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1356.09</v>
+        <v>1356.52</v>
       </c>
       <c r="D52" t="n">
-        <v>1347.79</v>
+        <v>1348.18</v>
       </c>
       <c r="E52" t="n">
-        <v>1364.38</v>
+        <v>1364.86</v>
       </c>
       <c r="F52" t="n">
-        <v>5464</v>
+        <v>5387</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -8376,16 +8376,16 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1353.71</v>
+        <v>1353.82</v>
       </c>
       <c r="D53" t="n">
-        <v>1349.39</v>
+        <v>1349.49</v>
       </c>
       <c r="E53" t="n">
-        <v>1358.04</v>
+        <v>1358.15</v>
       </c>
       <c r="F53" t="n">
-        <v>31132</v>
+        <v>31077</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -8527,16 +8527,16 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1353.43</v>
+        <v>1353.53</v>
       </c>
       <c r="D54" t="n">
-        <v>1350</v>
+        <v>1350.1</v>
       </c>
       <c r="E54" t="n">
-        <v>1356.85</v>
+        <v>1356.95</v>
       </c>
       <c r="F54" t="n">
-        <v>57152</v>
+        <v>57068</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -8678,16 +8678,16 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1352.89</v>
+        <v>1352.97</v>
       </c>
       <c r="D55" t="n">
-        <v>1344.56</v>
+        <v>1344.64</v>
       </c>
       <c r="E55" t="n">
-        <v>1361.22</v>
+        <v>1361.3</v>
       </c>
       <c r="F55" t="n">
-        <v>4994</v>
+        <v>4989</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -8829,16 +8829,16 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1347.7</v>
+        <v>1347.78</v>
       </c>
       <c r="D56" t="n">
-        <v>1340.33</v>
+        <v>1340.41</v>
       </c>
       <c r="E56" t="n">
-        <v>1355.08</v>
+        <v>1355.16</v>
       </c>
       <c r="F56" t="n">
-        <v>6604</v>
+        <v>6600</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -8900,16 +8900,16 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1347.14</v>
+        <v>1347.22</v>
       </c>
       <c r="D57" t="n">
-        <v>1339.44</v>
+        <v>1339.51</v>
       </c>
       <c r="E57" t="n">
-        <v>1354.84</v>
+        <v>1354.93</v>
       </c>
       <c r="F57" t="n">
-        <v>6965</v>
+        <v>6950</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -9051,13 +9051,13 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1346.98</v>
+        <v>1347</v>
       </c>
       <c r="D58" t="n">
-        <v>1337.52</v>
+        <v>1337.53</v>
       </c>
       <c r="E58" t="n">
-        <v>1356.45</v>
+        <v>1356.47</v>
       </c>
       <c r="F58" t="n">
         <v>3926</v>
@@ -9202,13 +9202,13 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1346.88</v>
+        <v>1346.91</v>
       </c>
       <c r="D59" t="n">
-        <v>1335.18</v>
+        <v>1335.21</v>
       </c>
       <c r="E59" t="n">
-        <v>1358.58</v>
+        <v>1358.61</v>
       </c>
       <c r="F59" t="n">
         <v>2549</v>
@@ -9353,16 +9353,16 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1346.05</v>
+        <v>1346.03</v>
       </c>
       <c r="D60" t="n">
-        <v>1338.84</v>
+        <v>1338.82</v>
       </c>
       <c r="E60" t="n">
-        <v>1353.26</v>
+        <v>1353.25</v>
       </c>
       <c r="F60" t="n">
-        <v>7142</v>
+        <v>7125</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -9504,16 +9504,16 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1342.63</v>
+        <v>1342.72</v>
       </c>
       <c r="D61" t="n">
-        <v>1332.71</v>
+        <v>1332.8</v>
       </c>
       <c r="E61" t="n">
-        <v>1352.54</v>
+        <v>1352.63</v>
       </c>
       <c r="F61" t="n">
-        <v>3393</v>
+        <v>3392</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -9655,13 +9655,13 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1341.49</v>
+        <v>1341.52</v>
       </c>
       <c r="D62" t="n">
-        <v>1331.98</v>
+        <v>1332</v>
       </c>
       <c r="E62" t="n">
-        <v>1351.01</v>
+        <v>1351.03</v>
       </c>
       <c r="F62" t="n">
         <v>3829</v>
@@ -9806,16 +9806,16 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1335.55</v>
+        <v>1335.63</v>
       </c>
       <c r="D63" t="n">
-        <v>1331.14</v>
+        <v>1331.23</v>
       </c>
       <c r="E63" t="n">
-        <v>1339.96</v>
+        <v>1340.04</v>
       </c>
       <c r="F63" t="n">
-        <v>25776</v>
+        <v>25749</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -9957,13 +9957,13 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1334.5</v>
+        <v>1334.6</v>
       </c>
       <c r="D64" t="n">
-        <v>1330.83</v>
+        <v>1330.93</v>
       </c>
       <c r="E64" t="n">
-        <v>1338.17</v>
+        <v>1338.27</v>
       </c>
       <c r="F64" t="n">
         <v>41375</v>
@@ -10108,13 +10108,13 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1332.69</v>
+        <v>1332.78</v>
       </c>
       <c r="D65" t="n">
-        <v>1329.13</v>
+        <v>1329.22</v>
       </c>
       <c r="E65" t="n">
-        <v>1336.25</v>
+        <v>1336.35</v>
       </c>
       <c r="F65" t="n">
         <v>59656</v>
@@ -10259,16 +10259,16 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1331.54</v>
+        <v>1330.82</v>
       </c>
       <c r="D66" t="n">
-        <v>1325.47</v>
+        <v>1324.71</v>
       </c>
       <c r="E66" t="n">
-        <v>1337.62</v>
+        <v>1336.94</v>
       </c>
       <c r="F66" t="n">
-        <v>12572</v>
+        <v>12326</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -10410,16 +10410,16 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1327.73</v>
+        <v>1327.69</v>
       </c>
       <c r="D67" t="n">
-        <v>1323.03</v>
+        <v>1322.98</v>
       </c>
       <c r="E67" t="n">
-        <v>1332.43</v>
+        <v>1332.39</v>
       </c>
       <c r="F67" t="n">
-        <v>26937</v>
+        <v>26908</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -10561,13 +10561,13 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1327.4</v>
+        <v>1327.41</v>
       </c>
       <c r="D68" t="n">
-        <v>1315.23</v>
+        <v>1315.24</v>
       </c>
       <c r="E68" t="n">
-        <v>1339.57</v>
+        <v>1339.58</v>
       </c>
       <c r="F68" t="n">
         <v>2218</v>
@@ -10712,16 +10712,16 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1326.77</v>
+        <v>1326.83</v>
       </c>
       <c r="D69" t="n">
-        <v>1322.55</v>
+        <v>1322.6</v>
       </c>
       <c r="E69" t="n">
-        <v>1331</v>
+        <v>1331.06</v>
       </c>
       <c r="F69" t="n">
-        <v>40577</v>
+        <v>40529</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -10863,16 +10863,16 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1325.26</v>
+        <v>1326.21</v>
       </c>
       <c r="D70" t="n">
-        <v>1304.17</v>
+        <v>1304.74</v>
       </c>
       <c r="E70" t="n">
-        <v>1346.34</v>
+        <v>1347.69</v>
       </c>
       <c r="F70" t="n">
-        <v>841</v>
+        <v>811</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -11014,13 +11014,13 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1323.12</v>
+        <v>1323.18</v>
       </c>
       <c r="D71" t="n">
-        <v>1314.86</v>
+        <v>1314.91</v>
       </c>
       <c r="E71" t="n">
-        <v>1331.39</v>
+        <v>1331.44</v>
       </c>
       <c r="F71" t="n">
         <v>6795</v>
@@ -11165,16 +11165,16 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1322.16</v>
+        <v>1322.31</v>
       </c>
       <c r="D72" t="n">
-        <v>1317.48</v>
+        <v>1317.62</v>
       </c>
       <c r="E72" t="n">
-        <v>1326.84</v>
+        <v>1326.99</v>
       </c>
       <c r="F72" t="n">
-        <v>30775</v>
+        <v>30740</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -11316,16 +11316,16 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1320.77</v>
+        <v>1321</v>
       </c>
       <c r="D73" t="n">
-        <v>1313.61</v>
+        <v>1313.83</v>
       </c>
       <c r="E73" t="n">
-        <v>1327.94</v>
+        <v>1328.18</v>
       </c>
       <c r="F73" t="n">
-        <v>7275</v>
+        <v>7252</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -11467,16 +11467,16 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1318.41</v>
+        <v>1318.46</v>
       </c>
       <c r="D74" t="n">
-        <v>1313.29</v>
+        <v>1313.34</v>
       </c>
       <c r="E74" t="n">
-        <v>1323.53</v>
+        <v>1323.57</v>
       </c>
       <c r="F74" t="n">
-        <v>22950</v>
+        <v>22915</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -11618,16 +11618,16 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>1318.23</v>
+        <v>1318.26</v>
       </c>
       <c r="D75" t="n">
-        <v>1314.81</v>
+        <v>1314.83</v>
       </c>
       <c r="E75" t="n">
-        <v>1321.66</v>
+        <v>1321.68</v>
       </c>
       <c r="F75" t="n">
-        <v>55172</v>
+        <v>55149</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -11765,33 +11765,33 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>nvidia-nemotron-3-nano-30b-a3b-bf16</t>
+          <t>gpt-oss-20b</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>1317.73</v>
+        <v>1317.87</v>
       </c>
       <c r="D76" t="n">
-        <v>1312.17</v>
+        <v>1311.53</v>
       </c>
       <c r="E76" t="n">
-        <v>1323.29</v>
+        <v>1324.21</v>
       </c>
       <c r="F76" t="n">
-        <v>15869</v>
+        <v>10750</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>NVIDIA Open Model</t>
+          <t>Apache 2.0</t>
         </is>
       </c>
       <c r="I76" t="n">
-        <v>31.6</v>
+        <v>21</v>
       </c>
       <c r="J76" t="n">
         <v>3.6</v>
@@ -11803,26 +11803,26 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>artificial_analysis</t>
+          <t>override</t>
         </is>
       </c>
       <c r="M76" t="n">
-        <v>63.2</v>
+        <v>42</v>
       </c>
       <c r="N76" t="n">
-        <v>79</v>
+        <v>52.5</v>
       </c>
       <c r="O76" t="n">
-        <v>31.6</v>
+        <v>21</v>
       </c>
       <c r="P76" t="n">
-        <v>39.5</v>
+        <v>26.2</v>
       </c>
       <c r="Q76" t="n">
-        <v>15.8</v>
+        <v>10.5</v>
       </c>
       <c r="R76" t="n">
-        <v>19.8</v>
+        <v>13.1</v>
       </c>
       <c r="S76" s="6" t="inlineStr">
         <is>
@@ -11916,33 +11916,33 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>gpt-oss-20b</t>
+          <t>nvidia-nemotron-3-nano-30b-a3b-bf16</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1317.59</v>
+        <v>1317.8</v>
       </c>
       <c r="D77" t="n">
-        <v>1311.25</v>
+        <v>1312.21</v>
       </c>
       <c r="E77" t="n">
-        <v>1323.93</v>
+        <v>1323.39</v>
       </c>
       <c r="F77" t="n">
-        <v>10758</v>
+        <v>15650</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
+          <t>NVIDIA Open Model</t>
         </is>
       </c>
       <c r="I77" t="n">
-        <v>21</v>
+        <v>31.6</v>
       </c>
       <c r="J77" t="n">
         <v>3.6</v>
@@ -11954,26 +11954,26 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>artificial_analysis</t>
         </is>
       </c>
       <c r="M77" t="n">
-        <v>42</v>
+        <v>63.2</v>
       </c>
       <c r="N77" t="n">
-        <v>52.5</v>
+        <v>79</v>
       </c>
       <c r="O77" t="n">
-        <v>21</v>
+        <v>31.6</v>
       </c>
       <c r="P77" t="n">
-        <v>26.2</v>
+        <v>39.5</v>
       </c>
       <c r="Q77" t="n">
-        <v>10.5</v>
+        <v>15.8</v>
       </c>
       <c r="R77" t="n">
-        <v>13.1</v>
+        <v>19.8</v>
       </c>
       <c r="S77" s="6" t="inlineStr">
         <is>
@@ -12071,13 +12071,13 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1317.59</v>
+        <v>1317.65</v>
       </c>
       <c r="D78" t="n">
-        <v>1311.91</v>
+        <v>1311.97</v>
       </c>
       <c r="E78" t="n">
-        <v>1323.27</v>
+        <v>1323.33</v>
       </c>
       <c r="F78" t="n">
         <v>16478</v>
@@ -12142,13 +12142,13 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>1314.13</v>
+        <v>1314.18</v>
       </c>
       <c r="D79" t="n">
-        <v>1309.61</v>
+        <v>1309.66</v>
       </c>
       <c r="E79" t="n">
-        <v>1318.65</v>
+        <v>1318.7</v>
       </c>
       <c r="F79" t="n">
         <v>24739</v>
@@ -12293,13 +12293,13 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1313.51</v>
+        <v>1313.58</v>
       </c>
       <c r="D80" t="n">
-        <v>1309.62</v>
+        <v>1309.68</v>
       </c>
       <c r="E80" t="n">
-        <v>1317.41</v>
+        <v>1317.48</v>
       </c>
       <c r="F80" t="n">
         <v>45459</v>
@@ -12444,13 +12444,13 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1306.71</v>
+        <v>1306.76</v>
       </c>
       <c r="D81" t="n">
-        <v>1302.03</v>
+        <v>1302.08</v>
       </c>
       <c r="E81" t="n">
-        <v>1311.39</v>
+        <v>1311.44</v>
       </c>
       <c r="F81" t="n">
         <v>24572</v>
@@ -12595,16 +12595,16 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>1305.73</v>
+        <v>1306.09</v>
       </c>
       <c r="D82" t="n">
-        <v>1297.59</v>
+        <v>1297.92</v>
       </c>
       <c r="E82" t="n">
-        <v>1313.86</v>
+        <v>1314.25</v>
       </c>
       <c r="F82" t="n">
-        <v>6089</v>
+        <v>6023</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -12746,13 +12746,13 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>1305.64</v>
+        <v>1305.67</v>
       </c>
       <c r="D83" t="n">
-        <v>1299.98</v>
+        <v>1300.01</v>
       </c>
       <c r="E83" t="n">
-        <v>1311.3</v>
+        <v>1311.33</v>
       </c>
       <c r="F83" t="n">
         <v>19621</v>
@@ -12897,13 +12897,13 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>1304.81</v>
+        <v>1304.87</v>
       </c>
       <c r="D84" t="n">
-        <v>1300.41</v>
+        <v>1300.47</v>
       </c>
       <c r="E84" t="n">
-        <v>1309.21</v>
+        <v>1309.27</v>
       </c>
       <c r="F84" t="n">
         <v>28073</v>
@@ -13048,13 +13048,13 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>1302.89</v>
+        <v>1302.91</v>
       </c>
       <c r="D85" t="n">
-        <v>1293.57</v>
+        <v>1293.59</v>
       </c>
       <c r="E85" t="n">
-        <v>1312.21</v>
+        <v>1312.23</v>
       </c>
       <c r="F85" t="n">
         <v>4171</v>
@@ -13199,16 +13199,16 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>1302.88</v>
+        <v>1302.9</v>
       </c>
       <c r="D86" t="n">
-        <v>1298.4</v>
+        <v>1298.42</v>
       </c>
       <c r="E86" t="n">
-        <v>1307.36</v>
+        <v>1307.38</v>
       </c>
       <c r="F86" t="n">
-        <v>33775</v>
+        <v>33731</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -13350,13 +13350,13 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>1302.41</v>
+        <v>1302.47</v>
       </c>
       <c r="D87" t="n">
-        <v>1298.38</v>
+        <v>1298.43</v>
       </c>
       <c r="E87" t="n">
-        <v>1306.45</v>
+        <v>1306.5</v>
       </c>
       <c r="F87" t="n">
         <v>39406</v>
@@ -13501,13 +13501,13 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>1298.51</v>
+        <v>1298.52</v>
       </c>
       <c r="D88" t="n">
-        <v>1290.75</v>
+        <v>1290.77</v>
       </c>
       <c r="E88" t="n">
-        <v>1306.26</v>
+        <v>1306.28</v>
       </c>
       <c r="F88" t="n">
         <v>7140</v>
@@ -13652,13 +13652,13 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>1292.97</v>
+        <v>1293.02</v>
       </c>
       <c r="D89" t="n">
-        <v>1289.27</v>
+        <v>1289.32</v>
       </c>
       <c r="E89" t="n">
-        <v>1296.66</v>
+        <v>1296.72</v>
       </c>
       <c r="F89" t="n">
         <v>55240</v>
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>1288.34</v>
+        <v>1288.4</v>
       </c>
       <c r="D90" t="n">
-        <v>1281.04</v>
+        <v>1281.1</v>
       </c>
       <c r="E90" t="n">
-        <v>1295.64</v>
+        <v>1295.7</v>
       </c>
       <c r="F90" t="n">
         <v>8662</v>
@@ -13954,13 +13954,13 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>1287.74</v>
+        <v>1287.76</v>
       </c>
       <c r="D91" t="n">
-        <v>1284.4</v>
+        <v>1284.42</v>
       </c>
       <c r="E91" t="n">
-        <v>1291.08</v>
+        <v>1291.1</v>
       </c>
       <c r="F91" t="n">
         <v>75754</v>
@@ -14105,16 +14105,16 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>1286.71</v>
+        <v>1287.41</v>
       </c>
       <c r="D92" t="n">
-        <v>1278.4</v>
+        <v>1279.09</v>
       </c>
       <c r="E92" t="n">
-        <v>1295.02</v>
+        <v>1295.72</v>
       </c>
       <c r="F92" t="n">
-        <v>5800</v>
+        <v>5783</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -14252,20 +14252,20 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>olmo-3.1-32b-think</t>
+          <t>llama-3.1-tulu-3-70b</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>1286.4</v>
+        <v>1286.08</v>
       </c>
       <c r="D93" t="n">
-        <v>1279.2</v>
+        <v>1275.61</v>
       </c>
       <c r="E93" t="n">
-        <v>1293.59</v>
+        <v>1296.56</v>
       </c>
       <c r="F93" t="n">
-        <v>8680</v>
+        <v>2846</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -14274,14 +14274,14 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
+          <t>Llama 3.1</t>
         </is>
       </c>
       <c r="I93" t="n">
-        <v>32.2</v>
+        <v>70</v>
       </c>
       <c r="J93" t="n">
-        <v>32.2</v>
+        <v>70</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
@@ -14290,30 +14290,30 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>artificial_analysis</t>
+          <t>name_parsing</t>
         </is>
       </c>
       <c r="M93" t="n">
-        <v>64.40000000000001</v>
+        <v>140</v>
       </c>
       <c r="N93" t="n">
-        <v>80.5</v>
+        <v>175</v>
       </c>
       <c r="O93" t="n">
-        <v>32.2</v>
+        <v>70</v>
       </c>
       <c r="P93" t="n">
-        <v>40.2</v>
+        <v>87.5</v>
       </c>
       <c r="Q93" t="n">
-        <v>16.1</v>
+        <v>35</v>
       </c>
       <c r="R93" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="S93" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+        <v>43.8</v>
+      </c>
+      <c r="S93" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="T93" s="6" t="inlineStr">
@@ -14331,9 +14331,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="W93" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="W93" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="X93" s="6" t="inlineStr">
@@ -14341,9 +14341,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="Y93" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="Y93" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="Z93" s="6" t="inlineStr">
@@ -14388,12 +14388,12 @@
       </c>
       <c r="AH93" t="inlineStr">
         <is>
+          <t>B200 SXM</t>
+        </is>
+      </c>
+      <c r="AI93" t="inlineStr">
+        <is>
           <t>RTX PRO 6000</t>
-        </is>
-      </c>
-      <c r="AI93" t="inlineStr">
-        <is>
-          <t>H100 SXM</t>
         </is>
       </c>
     </row>
@@ -14403,20 +14403,20 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>llama-3.1-tulu-3-70b</t>
+          <t>olmo-3.1-32b-think</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1286</v>
+        <v>1285.88</v>
       </c>
       <c r="D94" t="n">
-        <v>1275.53</v>
+        <v>1278.65</v>
       </c>
       <c r="E94" t="n">
-        <v>1296.48</v>
+        <v>1293.1</v>
       </c>
       <c r="F94" t="n">
-        <v>2846</v>
+        <v>8575</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -14425,14 +14425,14 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Llama 3.1</t>
+          <t>Apache 2.0</t>
         </is>
       </c>
       <c r="I94" t="n">
-        <v>70</v>
+        <v>32.2</v>
       </c>
       <c r="J94" t="n">
-        <v>70</v>
+        <v>32.2</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
@@ -14441,30 +14441,30 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>artificial_analysis</t>
         </is>
       </c>
       <c r="M94" t="n">
-        <v>140</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="N94" t="n">
-        <v>175</v>
+        <v>80.5</v>
       </c>
       <c r="O94" t="n">
-        <v>70</v>
+        <v>32.2</v>
       </c>
       <c r="P94" t="n">
-        <v>87.5</v>
+        <v>40.2</v>
       </c>
       <c r="Q94" t="n">
-        <v>35</v>
+        <v>16.1</v>
       </c>
       <c r="R94" t="n">
-        <v>43.8</v>
-      </c>
-      <c r="S94" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+        <v>20.1</v>
+      </c>
+      <c r="S94" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="T94" s="6" t="inlineStr">
@@ -14482,9 +14482,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="W94" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="W94" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="X94" s="6" t="inlineStr">
@@ -14492,9 +14492,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="Y94" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="Y94" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Z94" s="6" t="inlineStr">
@@ -14539,12 +14539,12 @@
       </c>
       <c r="AH94" t="inlineStr">
         <is>
-          <t>B200 SXM</t>
+          <t>RTX PRO 6000</t>
         </is>
       </c>
       <c r="AI94" t="inlineStr">
         <is>
-          <t>RTX PRO 6000</t>
+          <t>H100 SXM</t>
         </is>
       </c>
     </row>
@@ -14558,13 +14558,13 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1285.55</v>
+        <v>1285.65</v>
       </c>
       <c r="D95" t="n">
-        <v>1275.58</v>
+        <v>1275.67</v>
       </c>
       <c r="E95" t="n">
-        <v>1295.53</v>
+        <v>1295.62</v>
       </c>
       <c r="F95" t="n">
         <v>3749</v>
@@ -14709,13 +14709,13 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>1278.99</v>
+        <v>1279.01</v>
       </c>
       <c r="D96" t="n">
-        <v>1272.13</v>
+        <v>1272.16</v>
       </c>
       <c r="E96" t="n">
-        <v>1285.84</v>
+        <v>1285.87</v>
       </c>
       <c r="F96" t="n">
         <v>10072</v>
@@ -14860,13 +14860,13 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1276.53</v>
+        <v>1276.65</v>
       </c>
       <c r="D97" t="n">
-        <v>1271.21</v>
+        <v>1271.33</v>
       </c>
       <c r="E97" t="n">
-        <v>1281.86</v>
+        <v>1281.97</v>
       </c>
       <c r="F97" t="n">
         <v>19659</v>
@@ -15011,13 +15011,13 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>1275.76</v>
+        <v>1275.86</v>
       </c>
       <c r="D98" t="n">
-        <v>1269.19</v>
+        <v>1269.3</v>
       </c>
       <c r="E98" t="n">
-        <v>1282.32</v>
+        <v>1282.43</v>
       </c>
       <c r="F98" t="n">
         <v>9866</v>
@@ -15162,13 +15162,13 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>1275.4</v>
+        <v>1275.47</v>
       </c>
       <c r="D99" t="n">
-        <v>1271.83</v>
+        <v>1271.9</v>
       </c>
       <c r="E99" t="n">
-        <v>1278.97</v>
+        <v>1279.04</v>
       </c>
       <c r="F99" t="n">
         <v>156876</v>
@@ -15313,13 +15313,13 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>1273.6</v>
+        <v>1273.66</v>
       </c>
       <c r="D100" t="n">
-        <v>1267.72</v>
+        <v>1267.78</v>
       </c>
       <c r="E100" t="n">
-        <v>1279.48</v>
+        <v>1279.54</v>
       </c>
       <c r="F100" t="n">
         <v>14681</v>
@@ -15464,13 +15464,13 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1270.07</v>
+        <v>1270.13</v>
       </c>
       <c r="D101" t="n">
-        <v>1261.95</v>
+        <v>1262.02</v>
       </c>
       <c r="E101" t="n">
-        <v>1278.18</v>
+        <v>1278.25</v>
       </c>
       <c r="F101" t="n">
         <v>5432</v>
@@ -15615,13 +15615,13 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>1266.46</v>
+        <v>1266.53</v>
       </c>
       <c r="D102" t="n">
-        <v>1261.61</v>
+        <v>1261.67</v>
       </c>
       <c r="E102" t="n">
-        <v>1271.32</v>
+        <v>1271.38</v>
       </c>
       <c r="F102" t="n">
         <v>27124</v>
@@ -15766,13 +15766,13 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>1265.2</v>
+        <v>1265.22</v>
       </c>
       <c r="D103" t="n">
-        <v>1261.42</v>
+        <v>1261.44</v>
       </c>
       <c r="E103" t="n">
-        <v>1268.98</v>
+        <v>1269.01</v>
       </c>
       <c r="F103" t="n">
         <v>54611</v>
@@ -15917,13 +15917,13 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>1263.63</v>
+        <v>1263.7</v>
       </c>
       <c r="D104" t="n">
-        <v>1257.35</v>
+        <v>1257.42</v>
       </c>
       <c r="E104" t="n">
-        <v>1269.91</v>
+        <v>1269.98</v>
       </c>
       <c r="F104" t="n">
         <v>15147</v>
@@ -16068,13 +16068,13 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>1261.05</v>
+        <v>1261.18</v>
       </c>
       <c r="D105" t="n">
-        <v>1256.74</v>
+        <v>1256.86</v>
       </c>
       <c r="E105" t="n">
-        <v>1265.37</v>
+        <v>1265.49</v>
       </c>
       <c r="F105" t="n">
         <v>77554</v>
@@ -16219,13 +16219,13 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>1261.02</v>
+        <v>1261.13</v>
       </c>
       <c r="D106" t="n">
-        <v>1256.09</v>
+        <v>1256.2</v>
       </c>
       <c r="E106" t="n">
-        <v>1265.95</v>
+        <v>1266.06</v>
       </c>
       <c r="F106" t="n">
         <v>37325</v>
@@ -16370,13 +16370,13 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>1255.61</v>
+        <v>1255.68</v>
       </c>
       <c r="D107" t="n">
-        <v>1251.05</v>
+        <v>1251.11</v>
       </c>
       <c r="E107" t="n">
-        <v>1260.18</v>
+        <v>1260.24</v>
       </c>
       <c r="F107" t="n">
         <v>24126</v>
@@ -16521,13 +16521,13 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>1251.41</v>
+        <v>1251.5</v>
       </c>
       <c r="D108" t="n">
-        <v>1240.62</v>
+        <v>1240.71</v>
       </c>
       <c r="E108" t="n">
-        <v>1262.21</v>
+        <v>1262.29</v>
       </c>
       <c r="F108" t="n">
         <v>3334</v>
@@ -16672,13 +16672,13 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>1249.36</v>
+        <v>1249.47</v>
       </c>
       <c r="D109" t="n">
-        <v>1242.77</v>
+        <v>1242.88</v>
       </c>
       <c r="E109" t="n">
-        <v>1255.96</v>
+        <v>1256.06</v>
       </c>
       <c r="F109" t="n">
         <v>10140</v>
@@ -16823,13 +16823,13 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>1238.54</v>
+        <v>1238.58</v>
       </c>
       <c r="D110" t="n">
-        <v>1231.32</v>
+        <v>1231.37</v>
       </c>
       <c r="E110" t="n">
-        <v>1245.76</v>
+        <v>1245.8</v>
       </c>
       <c r="F110" t="n">
         <v>8858</v>
@@ -16974,13 +16974,13 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>1236.72</v>
+        <v>1236.78</v>
       </c>
       <c r="D111" t="n">
-        <v>1227.63</v>
+        <v>1227.69</v>
       </c>
       <c r="E111" t="n">
-        <v>1245.82</v>
+        <v>1245.88</v>
       </c>
       <c r="F111" t="n">
         <v>4781</v>
@@ -17125,13 +17125,13 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>1233.27</v>
+        <v>1233.37</v>
       </c>
       <c r="D112" t="n">
-        <v>1227.72</v>
+        <v>1227.82</v>
       </c>
       <c r="E112" t="n">
-        <v>1238.82</v>
+        <v>1238.92</v>
       </c>
       <c r="F112" t="n">
         <v>26195</v>
@@ -17276,13 +17276,13 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>1232.33</v>
+        <v>1232.45</v>
       </c>
       <c r="D113" t="n">
-        <v>1227.06</v>
+        <v>1227.17</v>
       </c>
       <c r="E113" t="n">
-        <v>1237.61</v>
+        <v>1237.72</v>
       </c>
       <c r="F113" t="n">
         <v>39302</v>
@@ -17427,13 +17427,13 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>1228.56</v>
+        <v>1228.68</v>
       </c>
       <c r="D114" t="n">
-        <v>1224.01</v>
+        <v>1224.13</v>
       </c>
       <c r="E114" t="n">
-        <v>1233.1</v>
+        <v>1233.23</v>
       </c>
       <c r="F114" t="n">
         <v>51416</v>
@@ -17578,13 +17578,13 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>1226.04</v>
+        <v>1226.17</v>
       </c>
       <c r="D115" t="n">
-        <v>1221.26</v>
+        <v>1221.39</v>
       </c>
       <c r="E115" t="n">
-        <v>1230.82</v>
+        <v>1230.95</v>
       </c>
       <c r="F115" t="n">
         <v>54036</v>
@@ -17729,13 +17729,13 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>1222.47</v>
+        <v>1222.56</v>
       </c>
       <c r="D116" t="n">
-        <v>1218.75</v>
+        <v>1218.84</v>
       </c>
       <c r="E116" t="n">
-        <v>1226.19</v>
+        <v>1226.28</v>
       </c>
       <c r="F116" t="n">
         <v>104642</v>
@@ -17880,13 +17880,13 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>1222.42</v>
+        <v>1222.47</v>
       </c>
       <c r="D117" t="n">
-        <v>1215.46</v>
+        <v>1215.51</v>
       </c>
       <c r="E117" t="n">
-        <v>1229.37</v>
+        <v>1229.43</v>
       </c>
       <c r="F117" t="n">
         <v>9818</v>
@@ -18031,13 +18031,13 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>1220.53</v>
+        <v>1220.6</v>
       </c>
       <c r="D118" t="n">
-        <v>1209.84</v>
+        <v>1209.91</v>
       </c>
       <c r="E118" t="n">
-        <v>1231.22</v>
+        <v>1231.29</v>
       </c>
       <c r="F118" t="n">
         <v>2896</v>
@@ -18182,13 +18182,13 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>1212.66</v>
+        <v>1212.77</v>
       </c>
       <c r="D119" t="n">
-        <v>1207.63</v>
+        <v>1207.73</v>
       </c>
       <c r="E119" t="n">
-        <v>1217.69</v>
+        <v>1217.8</v>
       </c>
       <c r="F119" t="n">
         <v>24146</v>
@@ -18333,13 +18333,13 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>1211.85</v>
+        <v>1211.97</v>
       </c>
       <c r="D120" t="n">
-        <v>1201.04</v>
+        <v>1201.16</v>
       </c>
       <c r="E120" t="n">
-        <v>1222.66</v>
+        <v>1222.78</v>
       </c>
       <c r="F120" t="n">
         <v>4652</v>
@@ -18484,13 +18484,13 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>1211.14</v>
+        <v>1211.19</v>
       </c>
       <c r="D121" t="n">
-        <v>1207.03</v>
+        <v>1207.08</v>
       </c>
       <c r="E121" t="n">
-        <v>1215.26</v>
+        <v>1215.31</v>
       </c>
       <c r="F121" t="n">
         <v>49605</v>
@@ -18635,13 +18635,13 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>1207.62</v>
+        <v>1207.73</v>
       </c>
       <c r="D122" t="n">
-        <v>1196.5</v>
+        <v>1196.61</v>
       </c>
       <c r="E122" t="n">
-        <v>1218.73</v>
+        <v>1218.84</v>
       </c>
       <c r="F122" t="n">
         <v>3090</v>
@@ -18786,13 +18786,13 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>1202.96</v>
+        <v>1203.09</v>
       </c>
       <c r="D123" t="n">
-        <v>1196.84</v>
+        <v>1196.97</v>
       </c>
       <c r="E123" t="n">
-        <v>1209.08</v>
+        <v>1209.21</v>
       </c>
       <c r="F123" t="n">
         <v>21741</v>
@@ -19088,13 +19088,13 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>1197.09</v>
+        <v>1197.21</v>
       </c>
       <c r="D125" t="n">
-        <v>1191.94</v>
+        <v>1192.06</v>
       </c>
       <c r="E125" t="n">
-        <v>1202.24</v>
+        <v>1202.36</v>
       </c>
       <c r="F125" t="n">
         <v>25055</v>
@@ -19239,13 +19239,13 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>1196.24</v>
+        <v>1196.37</v>
       </c>
       <c r="D126" t="n">
-        <v>1191.97</v>
+        <v>1192.1</v>
       </c>
       <c r="E126" t="n">
-        <v>1200.51</v>
+        <v>1200.63</v>
       </c>
       <c r="F126" t="n">
         <v>73503</v>
@@ -19390,13 +19390,13 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>1194.16</v>
+        <v>1194.28</v>
       </c>
       <c r="D127" t="n">
-        <v>1188.04</v>
+        <v>1188.16</v>
       </c>
       <c r="E127" t="n">
-        <v>1200.27</v>
+        <v>1200.39</v>
       </c>
       <c r="F127" t="n">
         <v>32191</v>
@@ -19541,13 +19541,13 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>1190.66</v>
+        <v>1190.75</v>
       </c>
       <c r="D128" t="n">
-        <v>1183.49</v>
+        <v>1183.58</v>
       </c>
       <c r="E128" t="n">
-        <v>1197.84</v>
+        <v>1197.93</v>
       </c>
       <c r="F128" t="n">
         <v>9901</v>
@@ -19692,13 +19692,13 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>1190.07</v>
+        <v>1190.19</v>
       </c>
       <c r="D129" t="n">
-        <v>1182.95</v>
+        <v>1183.06</v>
       </c>
       <c r="E129" t="n">
-        <v>1197.2</v>
+        <v>1197.31</v>
       </c>
       <c r="F129" t="n">
         <v>17839</v>
@@ -19843,13 +19843,13 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>1183.75</v>
+        <v>1183.88</v>
       </c>
       <c r="D130" t="n">
-        <v>1174.29</v>
+        <v>1174.42</v>
       </c>
       <c r="E130" t="n">
-        <v>1193.21</v>
+        <v>1193.34</v>
       </c>
       <c r="F130" t="n">
         <v>8214</v>
@@ -19994,13 +19994,13 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>1183.48</v>
+        <v>1183.6</v>
       </c>
       <c r="D131" t="n">
-        <v>1171.96</v>
+        <v>1172.08</v>
       </c>
       <c r="E131" t="n">
-        <v>1194.99</v>
+        <v>1195.12</v>
       </c>
       <c r="F131" t="n">
         <v>4932</v>
@@ -20145,13 +20145,13 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>1183</v>
+        <v>1183.11</v>
       </c>
       <c r="D132" t="n">
-        <v>1176.17</v>
+        <v>1176.28</v>
       </c>
       <c r="E132" t="n">
-        <v>1189.83</v>
+        <v>1189.94</v>
       </c>
       <c r="F132" t="n">
         <v>15483</v>
@@ -20296,13 +20296,13 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>1181.35</v>
+        <v>1181.47</v>
       </c>
       <c r="D133" t="n">
-        <v>1173.34</v>
+        <v>1173.46</v>
       </c>
       <c r="E133" t="n">
-        <v>1189.35</v>
+        <v>1189.47</v>
       </c>
       <c r="F133" t="n">
         <v>12637</v>
@@ -20367,13 +20367,13 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>1181.28</v>
+        <v>1181.4</v>
       </c>
       <c r="D134" t="n">
-        <v>1171.6</v>
+        <v>1171.72</v>
       </c>
       <c r="E134" t="n">
-        <v>1190.97</v>
+        <v>1191.08</v>
       </c>
       <c r="F134" t="n">
         <v>7968</v>
@@ -20438,13 +20438,13 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>1181.19</v>
+        <v>1181.3</v>
       </c>
       <c r="D135" t="n">
-        <v>1172.51</v>
+        <v>1172.61</v>
       </c>
       <c r="E135" t="n">
-        <v>1189.88</v>
+        <v>1189.98</v>
       </c>
       <c r="F135" t="n">
         <v>6638</v>
@@ -20589,13 +20589,13 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>1179.8</v>
+        <v>1179.83</v>
       </c>
       <c r="D136" t="n">
-        <v>1173.73</v>
+        <v>1173.75</v>
       </c>
       <c r="E136" t="n">
-        <v>1185.87</v>
+        <v>1185.9</v>
       </c>
       <c r="F136" t="n">
         <v>23893</v>
@@ -20740,13 +20740,13 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>1178.57</v>
+        <v>1178.69</v>
       </c>
       <c r="D137" t="n">
-        <v>1172.65</v>
+        <v>1172.77</v>
       </c>
       <c r="E137" t="n">
-        <v>1184.48</v>
+        <v>1184.6</v>
       </c>
       <c r="F137" t="n">
         <v>32832</v>
@@ -20811,13 +20811,13 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>1178.17</v>
+        <v>1178.27</v>
       </c>
       <c r="D138" t="n">
-        <v>1166.96</v>
+        <v>1167.06</v>
       </c>
       <c r="E138" t="n">
-        <v>1189.38</v>
+        <v>1189.48</v>
       </c>
       <c r="F138" t="n">
         <v>3188</v>
@@ -20962,13 +20962,13 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>1177.1</v>
+        <v>1177.23</v>
       </c>
       <c r="D139" t="n">
-        <v>1167.27</v>
+        <v>1167.41</v>
       </c>
       <c r="E139" t="n">
-        <v>1186.93</v>
+        <v>1187.06</v>
       </c>
       <c r="F139" t="n">
         <v>6535</v>
@@ -21113,13 +21113,13 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>1174.26</v>
+        <v>1174.38</v>
       </c>
       <c r="D140" t="n">
-        <v>1163.83</v>
+        <v>1163.95</v>
       </c>
       <c r="E140" t="n">
-        <v>1184.69</v>
+        <v>1184.81</v>
       </c>
       <c r="F140" t="n">
         <v>5006</v>
@@ -21264,13 +21264,13 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>1171.85</v>
+        <v>1171.98</v>
       </c>
       <c r="D141" t="n">
-        <v>1165.64</v>
+        <v>1165.77</v>
       </c>
       <c r="E141" t="n">
-        <v>1178.07</v>
+        <v>1178.19</v>
       </c>
       <c r="F141" t="n">
         <v>22479</v>
@@ -21415,13 +21415,13 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>1170.76</v>
+        <v>1170.9</v>
       </c>
       <c r="D142" t="n">
-        <v>1163.35</v>
+        <v>1163.48</v>
       </c>
       <c r="E142" t="n">
-        <v>1178.18</v>
+        <v>1178.31</v>
       </c>
       <c r="F142" t="n">
         <v>16056</v>
@@ -21566,13 +21566,13 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>1170.23</v>
+        <v>1170.35</v>
       </c>
       <c r="D143" t="n">
-        <v>1164.31</v>
+        <v>1164.43</v>
       </c>
       <c r="E143" t="n">
-        <v>1176.14</v>
+        <v>1176.26</v>
       </c>
       <c r="F143" t="n">
         <v>17766</v>
@@ -21717,13 +21717,13 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>1169.89</v>
+        <v>1170.02</v>
       </c>
       <c r="D144" t="n">
-        <v>1164.39</v>
+        <v>1164.51</v>
       </c>
       <c r="E144" t="n">
-        <v>1175.4</v>
+        <v>1175.52</v>
       </c>
       <c r="F144" t="n">
         <v>38492</v>
@@ -21868,13 +21868,13 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>1166.62</v>
+        <v>1166.75</v>
       </c>
       <c r="D145" t="n">
-        <v>1158.55</v>
+        <v>1158.67</v>
       </c>
       <c r="E145" t="n">
-        <v>1174.69</v>
+        <v>1174.82</v>
       </c>
       <c r="F145" t="n">
         <v>10224</v>
@@ -22019,13 +22019,13 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>1165.93</v>
+        <v>1166.02</v>
       </c>
       <c r="D146" t="n">
-        <v>1158.24</v>
+        <v>1158.33</v>
       </c>
       <c r="E146" t="n">
-        <v>1173.63</v>
+        <v>1173.72</v>
       </c>
       <c r="F146" t="n">
         <v>7936</v>
@@ -22170,13 +22170,13 @@
         </is>
       </c>
       <c r="C147" t="n">
-        <v>1163.83</v>
+        <v>1163.95</v>
       </c>
       <c r="D147" t="n">
-        <v>1151.89</v>
+        <v>1152.01</v>
       </c>
       <c r="E147" t="n">
-        <v>1175.77</v>
+        <v>1175.89</v>
       </c>
       <c r="F147" t="n">
         <v>3777</v>
@@ -22321,13 +22321,13 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>1156.13</v>
+        <v>1156.25</v>
       </c>
       <c r="D148" t="n">
-        <v>1144.62</v>
+        <v>1144.75</v>
       </c>
       <c r="E148" t="n">
-        <v>1167.63</v>
+        <v>1167.76</v>
       </c>
       <c r="F148" t="n">
         <v>3231</v>
@@ -22472,13 +22472,13 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>1155.17</v>
+        <v>1155.28</v>
       </c>
       <c r="D149" t="n">
-        <v>1146.78</v>
+        <v>1146.89</v>
       </c>
       <c r="E149" t="n">
-        <v>1163.57</v>
+        <v>1163.68</v>
       </c>
       <c r="F149" t="n">
         <v>6837</v>
@@ -22623,13 +22623,13 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>1154.38</v>
+        <v>1154.52</v>
       </c>
       <c r="D150" t="n">
-        <v>1141.76</v>
+        <v>1141.9</v>
       </c>
       <c r="E150" t="n">
-        <v>1167.01</v>
+        <v>1167.15</v>
       </c>
       <c r="F150" t="n">
         <v>3585</v>
@@ -22774,13 +22774,13 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>1151.42</v>
+        <v>1151.55</v>
       </c>
       <c r="D151" t="n">
-        <v>1138.21</v>
+        <v>1138.34</v>
       </c>
       <c r="E151" t="n">
-        <v>1164.64</v>
+        <v>1164.77</v>
       </c>
       <c r="F151" t="n">
         <v>4155</v>
@@ -22925,13 +22925,13 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>1151.07</v>
+        <v>1151.2</v>
       </c>
       <c r="D152" t="n">
-        <v>1135.67</v>
+        <v>1135.8</v>
       </c>
       <c r="E152" t="n">
-        <v>1166.48</v>
+        <v>1166.6</v>
       </c>
       <c r="F152" t="n">
         <v>1679</v>
@@ -23076,13 +23076,13 @@
         </is>
       </c>
       <c r="C153" t="n">
-        <v>1149.17</v>
+        <v>1149.28</v>
       </c>
       <c r="D153" t="n">
-        <v>1136.86</v>
+        <v>1136.98</v>
       </c>
       <c r="E153" t="n">
-        <v>1161.47</v>
+        <v>1161.59</v>
       </c>
       <c r="F153" t="n">
         <v>2572</v>
@@ -23227,13 +23227,13 @@
         </is>
       </c>
       <c r="C154" t="n">
-        <v>1148.68</v>
+        <v>1148.81</v>
       </c>
       <c r="D154" t="n">
-        <v>1142.02</v>
+        <v>1142.15</v>
       </c>
       <c r="E154" t="n">
-        <v>1155.33</v>
+        <v>1155.46</v>
       </c>
       <c r="F154" t="n">
         <v>19402</v>
@@ -23378,13 +23378,13 @@
         </is>
       </c>
       <c r="C155" t="n">
-        <v>1148.27</v>
+        <v>1148.4</v>
       </c>
       <c r="D155" t="n">
-        <v>1139.01</v>
+        <v>1139.13</v>
       </c>
       <c r="E155" t="n">
-        <v>1157.54</v>
+        <v>1157.66</v>
       </c>
       <c r="F155" t="n">
         <v>7044</v>
@@ -23529,13 +23529,13 @@
         </is>
       </c>
       <c r="C156" t="n">
-        <v>1146.11</v>
+        <v>1146.22</v>
       </c>
       <c r="D156" t="n">
-        <v>1128.98</v>
+        <v>1129.09</v>
       </c>
       <c r="E156" t="n">
-        <v>1163.24</v>
+        <v>1163.36</v>
       </c>
       <c r="F156" t="n">
         <v>1295</v>
@@ -23680,13 +23680,13 @@
         </is>
       </c>
       <c r="C157" t="n">
-        <v>1142.92</v>
+        <v>1143.03</v>
       </c>
       <c r="D157" t="n">
-        <v>1133.02</v>
+        <v>1133.13</v>
       </c>
       <c r="E157" t="n">
-        <v>1152.81</v>
+        <v>1152.93</v>
       </c>
       <c r="F157" t="n">
         <v>4737</v>
@@ -23831,13 +23831,13 @@
         </is>
       </c>
       <c r="C158" t="n">
-        <v>1142.21</v>
+        <v>1142.33</v>
       </c>
       <c r="D158" t="n">
-        <v>1135.78</v>
+        <v>1135.89</v>
       </c>
       <c r="E158" t="n">
-        <v>1148.65</v>
+        <v>1148.76</v>
       </c>
       <c r="F158" t="n">
         <v>12297</v>
@@ -23982,13 +23982,13 @@
         </is>
       </c>
       <c r="C159" t="n">
-        <v>1140.6</v>
+        <v>1140.72</v>
       </c>
       <c r="D159" t="n">
-        <v>1133.87</v>
+        <v>1133.99</v>
       </c>
       <c r="E159" t="n">
-        <v>1147.33</v>
+        <v>1147.45</v>
       </c>
       <c r="F159" t="n">
         <v>19174</v>
@@ -24133,13 +24133,13 @@
         </is>
       </c>
       <c r="C160" t="n">
-        <v>1139.98</v>
+        <v>1140.1</v>
       </c>
       <c r="D160" t="n">
-        <v>1133.26</v>
+        <v>1133.38</v>
       </c>
       <c r="E160" t="n">
-        <v>1146.69</v>
+        <v>1146.81</v>
       </c>
       <c r="F160" t="n">
         <v>19367</v>
@@ -24284,13 +24284,13 @@
         </is>
       </c>
       <c r="C161" t="n">
-        <v>1137.64</v>
+        <v>1137.76</v>
       </c>
       <c r="D161" t="n">
-        <v>1126.67</v>
+        <v>1126.79</v>
       </c>
       <c r="E161" t="n">
-        <v>1148.61</v>
+        <v>1148.73</v>
       </c>
       <c r="F161" t="n">
         <v>4964</v>
@@ -24435,13 +24435,13 @@
         </is>
       </c>
       <c r="C162" t="n">
-        <v>1135.64</v>
+        <v>1135.76</v>
       </c>
       <c r="D162" t="n">
-        <v>1126.73</v>
+        <v>1126.85</v>
       </c>
       <c r="E162" t="n">
-        <v>1144.54</v>
+        <v>1144.67</v>
       </c>
       <c r="F162" t="n">
         <v>7366</v>
@@ -24586,13 +24586,13 @@
         </is>
       </c>
       <c r="C163" t="n">
-        <v>1135.49</v>
+        <v>1135.54</v>
       </c>
       <c r="D163" t="n">
-        <v>1125.98</v>
+        <v>1126.03</v>
       </c>
       <c r="E163" t="n">
-        <v>1145</v>
+        <v>1145.05</v>
       </c>
       <c r="F163" t="n">
         <v>8925</v>
@@ -24737,13 +24737,13 @@
         </is>
       </c>
       <c r="C164" t="n">
-        <v>1130.09</v>
+        <v>1130.23</v>
       </c>
       <c r="D164" t="n">
-        <v>1121.24</v>
+        <v>1121.38</v>
       </c>
       <c r="E164" t="n">
-        <v>1138.95</v>
+        <v>1139.08</v>
       </c>
       <c r="F164" t="n">
         <v>11118</v>
@@ -24888,13 +24888,13 @@
         </is>
       </c>
       <c r="C165" t="n">
-        <v>1128.31</v>
+        <v>1128.43</v>
       </c>
       <c r="D165" t="n">
-        <v>1120.88</v>
+        <v>1121</v>
       </c>
       <c r="E165" t="n">
-        <v>1135.74</v>
+        <v>1135.85</v>
       </c>
       <c r="F165" t="n">
         <v>20685</v>
@@ -25039,13 +25039,13 @@
         </is>
       </c>
       <c r="C166" t="n">
-        <v>1127.51</v>
+        <v>1127.64</v>
       </c>
       <c r="D166" t="n">
-        <v>1121.12</v>
+        <v>1121.24</v>
       </c>
       <c r="E166" t="n">
-        <v>1133.91</v>
+        <v>1134.03</v>
       </c>
       <c r="F166" t="n">
         <v>20118</v>
@@ -25190,13 +25190,13 @@
         </is>
       </c>
       <c r="C167" t="n">
-        <v>1126.37</v>
+        <v>1126.49</v>
       </c>
       <c r="D167" t="n">
-        <v>1114.21</v>
+        <v>1114.33</v>
       </c>
       <c r="E167" t="n">
-        <v>1138.53</v>
+        <v>1138.65</v>
       </c>
       <c r="F167" t="n">
         <v>2921</v>
@@ -25341,13 +25341,13 @@
         </is>
       </c>
       <c r="C168" t="n">
-        <v>1125.96</v>
+        <v>1126.09</v>
       </c>
       <c r="D168" t="n">
-        <v>1110.28</v>
+        <v>1110.41</v>
       </c>
       <c r="E168" t="n">
-        <v>1141.64</v>
+        <v>1141.76</v>
       </c>
       <c r="F168" t="n">
         <v>1785</v>
@@ -25492,13 +25492,13 @@
         </is>
       </c>
       <c r="C169" t="n">
-        <v>1120.04</v>
+        <v>1120.16</v>
       </c>
       <c r="D169" t="n">
-        <v>1109.04</v>
+        <v>1109.16</v>
       </c>
       <c r="E169" t="n">
-        <v>1131.05</v>
+        <v>1131.17</v>
       </c>
       <c r="F169" t="n">
         <v>5182</v>
@@ -25643,13 +25643,13 @@
         </is>
       </c>
       <c r="C170" t="n">
-        <v>1118.19</v>
+        <v>1118.29</v>
       </c>
       <c r="D170" t="n">
-        <v>1099.97</v>
+        <v>1100.08</v>
       </c>
       <c r="E170" t="n">
-        <v>1136.41</v>
+        <v>1136.51</v>
       </c>
       <c r="F170" t="n">
         <v>1143</v>
@@ -25794,13 +25794,13 @@
         </is>
       </c>
       <c r="C171" t="n">
-        <v>1113.7</v>
+        <v>1113.81</v>
       </c>
       <c r="D171" t="n">
-        <v>1104.51</v>
+        <v>1104.63</v>
       </c>
       <c r="E171" t="n">
-        <v>1122.88</v>
+        <v>1123</v>
       </c>
       <c r="F171" t="n">
         <v>6923</v>
@@ -25945,13 +25945,13 @@
         </is>
       </c>
       <c r="C172" t="n">
-        <v>1113.68</v>
+        <v>1113.71</v>
       </c>
       <c r="D172" t="n">
-        <v>1105.94</v>
+        <v>1105.97</v>
       </c>
       <c r="E172" t="n">
-        <v>1121.42</v>
+        <v>1121.45</v>
       </c>
       <c r="F172" t="n">
         <v>10854</v>
@@ -26096,13 +26096,13 @@
         </is>
       </c>
       <c r="C173" t="n">
-        <v>1113.45</v>
+        <v>1113.56</v>
       </c>
       <c r="D173" t="n">
-        <v>1099.03</v>
+        <v>1099.14</v>
       </c>
       <c r="E173" t="n">
-        <v>1127.87</v>
+        <v>1127.98</v>
       </c>
       <c r="F173" t="n">
         <v>2199</v>
@@ -26247,13 +26247,13 @@
         </is>
       </c>
       <c r="C174" t="n">
-        <v>1110.48</v>
+        <v>1110.58</v>
       </c>
       <c r="D174" t="n">
-        <v>1102.6</v>
+        <v>1102.7</v>
       </c>
       <c r="E174" t="n">
-        <v>1118.35</v>
+        <v>1118.45</v>
       </c>
       <c r="F174" t="n">
         <v>8045</v>
@@ -26398,13 +26398,13 @@
         </is>
       </c>
       <c r="C175" t="n">
-        <v>1108.67</v>
+        <v>1108.79</v>
       </c>
       <c r="D175" t="n">
-        <v>1099.37</v>
+        <v>1099.49</v>
       </c>
       <c r="E175" t="n">
-        <v>1117.97</v>
+        <v>1118.09</v>
       </c>
       <c r="F175" t="n">
         <v>8977</v>
@@ -26549,13 +26549,13 @@
         </is>
       </c>
       <c r="C176" t="n">
-        <v>1107.23</v>
+        <v>1107.36</v>
       </c>
       <c r="D176" t="n">
-        <v>1100.17</v>
+        <v>1100.3</v>
       </c>
       <c r="E176" t="n">
-        <v>1114.29</v>
+        <v>1114.42</v>
       </c>
       <c r="F176" t="n">
         <v>14148</v>
@@ -26700,13 +26700,13 @@
         </is>
       </c>
       <c r="C177" t="n">
-        <v>1091.09</v>
+        <v>1091.14</v>
       </c>
       <c r="D177" t="n">
-        <v>1079.57</v>
+        <v>1079.62</v>
       </c>
       <c r="E177" t="n">
-        <v>1102.61</v>
+        <v>1102.65</v>
       </c>
       <c r="F177" t="n">
         <v>4780</v>
@@ -26851,13 +26851,13 @@
         </is>
       </c>
       <c r="C178" t="n">
-        <v>1089.24</v>
+        <v>1089.35</v>
       </c>
       <c r="D178" t="n">
-        <v>1079.88</v>
+        <v>1080</v>
       </c>
       <c r="E178" t="n">
-        <v>1098.59</v>
+        <v>1098.71</v>
       </c>
       <c r="F178" t="n">
         <v>7597</v>
@@ -27002,13 +27002,13 @@
         </is>
       </c>
       <c r="C179" t="n">
-        <v>1073.63</v>
+        <v>1073.77</v>
       </c>
       <c r="D179" t="n">
-        <v>1062.44</v>
+        <v>1062.58</v>
       </c>
       <c r="E179" t="n">
-        <v>1084.82</v>
+        <v>1084.96</v>
       </c>
       <c r="F179" t="n">
         <v>6328</v>
@@ -27153,13 +27153,13 @@
         </is>
       </c>
       <c r="C180" t="n">
-        <v>1069.46</v>
+        <v>1069.58</v>
       </c>
       <c r="D180" t="n">
-        <v>1059.5</v>
+        <v>1059.63</v>
       </c>
       <c r="E180" t="n">
-        <v>1079.41</v>
+        <v>1079.53</v>
       </c>
       <c r="F180" t="n">
         <v>6965</v>
@@ -27304,13 +27304,13 @@
         </is>
       </c>
       <c r="C181" t="n">
-        <v>1066.53</v>
+        <v>1066.61</v>
       </c>
       <c r="D181" t="n">
-        <v>1055</v>
+        <v>1055.09</v>
       </c>
       <c r="E181" t="n">
-        <v>1078.05</v>
+        <v>1078.14</v>
       </c>
       <c r="F181" t="n">
         <v>5745</v>
@@ -27455,13 +27455,13 @@
         </is>
       </c>
       <c r="C182" t="n">
-        <v>1065.04</v>
+        <v>1065.14</v>
       </c>
       <c r="D182" t="n">
-        <v>1049.74</v>
+        <v>1049.85</v>
       </c>
       <c r="E182" t="n">
-        <v>1080.33</v>
+        <v>1080.43</v>
       </c>
       <c r="F182" t="n">
         <v>1743</v>
@@ -27606,13 +27606,13 @@
         </is>
       </c>
       <c r="C183" t="n">
-        <v>1060.88</v>
+        <v>1060.99</v>
       </c>
       <c r="D183" t="n">
-        <v>1048.85</v>
+        <v>1048.95</v>
       </c>
       <c r="E183" t="n">
-        <v>1072.92</v>
+        <v>1073.02</v>
       </c>
       <c r="F183" t="n">
         <v>3924</v>
@@ -27757,13 +27757,13 @@
         </is>
       </c>
       <c r="C184" t="n">
-        <v>1055.08</v>
+        <v>1055.2</v>
       </c>
       <c r="D184" t="n">
-        <v>1043.39</v>
+        <v>1043.51</v>
       </c>
       <c r="E184" t="n">
-        <v>1066.77</v>
+        <v>1066.89</v>
       </c>
       <c r="F184" t="n">
         <v>4658</v>
@@ -27908,13 +27908,13 @@
         </is>
       </c>
       <c r="C185" t="n">
-        <v>1040.35</v>
+        <v>1040.47</v>
       </c>
       <c r="D185" t="n">
-        <v>1028.9</v>
+        <v>1029.01</v>
       </c>
       <c r="E185" t="n">
-        <v>1051.81</v>
+        <v>1051.92</v>
       </c>
       <c r="F185" t="n">
         <v>4845</v>
@@ -28059,13 +28059,13 @@
         </is>
       </c>
       <c r="C186" t="n">
-        <v>1023.19</v>
+        <v>1023.31</v>
       </c>
       <c r="D186" t="n">
-        <v>1009.55</v>
+        <v>1009.67</v>
       </c>
       <c r="E186" t="n">
-        <v>1036.83</v>
+        <v>1036.95</v>
       </c>
       <c r="F186" t="n">
         <v>2658</v>
@@ -28210,13 +28210,13 @@
         </is>
       </c>
       <c r="C187" t="n">
-        <v>1021.11</v>
+        <v>1021.21</v>
       </c>
       <c r="D187" t="n">
-        <v>1010.17</v>
+        <v>1010.28</v>
       </c>
       <c r="E187" t="n">
-        <v>1032.04</v>
+        <v>1032.15</v>
       </c>
       <c r="F187" t="n">
         <v>6310</v>
@@ -28361,13 +28361,13 @@
         </is>
       </c>
       <c r="C188" t="n">
-        <v>994.5940000000001</v>
+        <v>994.7190000000001</v>
       </c>
       <c r="D188" t="n">
-        <v>981.963</v>
+        <v>982.0890000000001</v>
       </c>
       <c r="E188" t="n">
-        <v>1007.23</v>
+        <v>1007.35</v>
       </c>
       <c r="F188" t="n">
         <v>4914</v>
@@ -28512,13 +28512,13 @@
         </is>
       </c>
       <c r="C189" t="n">
-        <v>990.37</v>
+        <v>990.477</v>
       </c>
       <c r="D189" t="n">
-        <v>977.927</v>
+        <v>978.0359999999999</v>
       </c>
       <c r="E189" t="n">
-        <v>1002.81</v>
+        <v>1002.92</v>
       </c>
       <c r="F189" t="n">
         <v>4203</v>
@@ -28663,13 +28663,13 @@
         </is>
       </c>
       <c r="C190" t="n">
-        <v>979.158</v>
+        <v>979.252</v>
       </c>
       <c r="D190" t="n">
-        <v>965.537</v>
+        <v>965.633</v>
       </c>
       <c r="E190" t="n">
-        <v>992.779</v>
+        <v>992.87</v>
       </c>
       <c r="F190" t="n">
         <v>3412</v>
@@ -28814,13 +28814,13 @@
         </is>
       </c>
       <c r="C191" t="n">
-        <v>971.268</v>
+        <v>971.349</v>
       </c>
       <c r="D191" t="n">
-        <v>955.346</v>
+        <v>955.4299999999999</v>
       </c>
       <c r="E191" t="n">
-        <v>987.1900000000001</v>
+        <v>987.269</v>
       </c>
       <c r="F191" t="n">
         <v>2391</v>
@@ -28965,13 +28965,13 @@
         </is>
       </c>
       <c r="C192" t="n">
-        <v>951.633</v>
+        <v>951.751</v>
       </c>
       <c r="D192" t="n">
-        <v>938.808</v>
+        <v>938.928</v>
       </c>
       <c r="E192" t="n">
-        <v>964.4589999999999</v>
+        <v>964.574</v>
       </c>
       <c r="F192" t="n">
         <v>3287</v>
@@ -29260,7 +29260,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -29369,7 +29369,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -29474,7 +29474,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -29544,7 +29544,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -29649,7 +29649,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -30080,14 +30080,14 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>qwen3.5-122b-a10b</t>
+          <t>kimi-k2-0905-preview</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>125</v>
+        <v>1000</v>
       </c>
       <c r="C16" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -30096,21 +30096,21 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>artificial_analysis</t>
+          <t>override</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>kimi-k2-0905-preview</t>
+          <t>qwen3.5-122b-a10b</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1000</v>
+        <v>125</v>
       </c>
       <c r="C17" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -30119,7 +30119,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>artificial_analysis</t>
         </is>
       </c>
     </row>
@@ -30172,14 +30172,14 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>mistral-large-3</t>
+          <t>deepseek-v3.1-terminus-thinking</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>675</v>
+        <v>685</v>
       </c>
       <c r="C20" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -30195,14 +30195,14 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>deepseek-v3.1-terminus-thinking</t>
+          <t>mistral-large-3</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>685</v>
+        <v>675</v>
       </c>
       <c r="C21" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -30379,14 +30379,14 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>longcat-flash-chat</t>
+          <t>qwen3.5-35b-a3b</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>560</v>
+        <v>36</v>
       </c>
       <c r="C29" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -30395,21 +30395,21 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>artificial_analysis</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>qwen3-235b-a22b-thinking-2507</t>
+          <t>longcat-flash-chat</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>235</v>
+        <v>560</v>
       </c>
       <c r="C30" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -30418,21 +30418,21 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>override</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>qwen3.5-35b-a3b</t>
+          <t>qwen3-235b-a22b-thinking-2507</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>36</v>
+        <v>235</v>
       </c>
       <c r="C31" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -30441,7 +30441,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>artificial_analysis</t>
+          <t>name_parsing</t>
         </is>
       </c>
     </row>
@@ -30540,14 +30540,14 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>mimo-v2-flash (thinking)</t>
+          <t>step-3.5-flash</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>309</v>
+        <v>196</v>
       </c>
       <c r="C36" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -30563,14 +30563,14 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>step-3.5-flash</t>
+          <t>mimo-v2-flash (thinking)</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>196</v>
+        <v>309</v>
       </c>
       <c r="C37" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -30678,46 +30678,46 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>qwen3-235b-a22b</t>
+          <t>trinity-large</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>235</v>
+        <v>70</v>
       </c>
       <c r="C42" t="n">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>moe</t>
+          <t>dense</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>artificial_analysis</t>
+          <t>override</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>trinity-large</t>
+          <t>qwen3-235b-a22b</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>70</v>
+        <v>235</v>
       </c>
       <c r="C43" t="n">
-        <v>70</v>
+        <v>22</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>dense</t>
+          <t>moe</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>artificial_analysis</t>
         </is>
       </c>
     </row>
@@ -30816,14 +30816,14 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>minimax-m1</t>
+          <t>nvidia-nemotron-3-super-120b-a12b</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>456</v>
+        <v>120.6</v>
       </c>
       <c r="C48" t="n">
-        <v>45.9</v>
+        <v>12.7</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -30839,14 +30839,14 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>nvidia-nemotron-3-super-120b-a12b</t>
+          <t>minimax-m1</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>120.6</v>
+        <v>456</v>
       </c>
       <c r="C49" t="n">
-        <v>12.7</v>
+        <v>45.9</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -31452,11 +31452,11 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>nvidia-nemotron-3-nano-30b-a3b-bf16</t>
+          <t>gpt-oss-20b</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>31.6</v>
+        <v>21</v>
       </c>
       <c r="C76" t="n">
         <v>3.6</v>
@@ -31468,18 +31468,18 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>artificial_analysis</t>
+          <t>override</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>gpt-oss-20b</t>
+          <t>nvidia-nemotron-3-nano-30b-a3b-bf16</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>21</v>
+        <v>31.6</v>
       </c>
       <c r="C77" t="n">
         <v>3.6</v>
@@ -31491,7 +31491,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>artificial_analysis</t>
         </is>
       </c>
     </row>
@@ -31835,14 +31835,14 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>olmo-3.1-32b-think</t>
+          <t>llama-3.1-tulu-3-70b</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>32.2</v>
+        <v>70</v>
       </c>
       <c r="C93" t="n">
-        <v>32.2</v>
+        <v>70</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -31851,21 +31851,21 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>artificial_analysis</t>
+          <t>name_parsing</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>llama-3.1-tulu-3-70b</t>
+          <t>olmo-3.1-32b-think</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>70</v>
+        <v>32.2</v>
       </c>
       <c r="C94" t="n">
-        <v>70</v>
+        <v>32.2</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -31874,7 +31874,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>artificial_analysis</t>
         </is>
       </c>
     </row>

--- a/arena_enrichment/output/arena_leaderboard_enriched.xlsx
+++ b/arena_enrichment/output/arena_leaderboard_enriched.xlsx
@@ -675,16 +675,16 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>1455.3</v>
+        <v>1455.62</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1449.31</v>
+        <v>1449.64</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1461.29</v>
+        <v>1461.6</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>11093</v>
+        <v>11101</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
@@ -826,16 +826,16 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>1452.68</v>
+        <v>1453.54</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1447.42</v>
+        <v>1448.43</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1457.94</v>
+        <v>1458.66</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>16262</v>
+        <v>17271</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
@@ -977,16 +977,16 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>1451.63</v>
+        <v>1450.4</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1445.51</v>
+        <v>1444.52</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1457.74</v>
+        <v>1456.29</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>10431</v>
+        <v>11497</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
@@ -1128,16 +1128,16 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>1442.63</v>
+        <v>1442.9</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1436.52</v>
+        <v>1436.77</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1448.75</v>
+        <v>1449.03</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>12242</v>
+        <v>12201</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
@@ -1279,16 +1279,16 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1433.19</v>
+        <v>1433.18</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1426.57</v>
+        <v>1426.54</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1439.82</v>
+        <v>1439.81</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>8257</v>
+        <v>8232</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
@@ -1430,16 +1430,16 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>1429.69</v>
+        <v>1429.59</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>1425.99</v>
+        <v>1425.94</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1433.39</v>
+        <v>1433.25</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>41738</v>
+        <v>42603</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
@@ -1581,16 +1581,16 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>1425.85</v>
+        <v>1425.86</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>1421.9</v>
+        <v>1421.92</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1429.79</v>
+        <v>1429.81</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>36102</v>
+        <v>35981</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
@@ -1732,16 +1732,16 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>1424.73</v>
+        <v>1424.86</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1418.22</v>
+        <v>1418.33</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1431.25</v>
+        <v>1431.39</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>9188</v>
+        <v>9148</v>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
@@ -1883,16 +1883,16 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>1424.52</v>
+        <v>1423.93</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>1420.46</v>
+        <v>1419.94</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1428.57</v>
+        <v>1427.92</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>36511</v>
+        <v>37482</v>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
@@ -2034,16 +2034,16 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>1423.24</v>
+        <v>1422.85</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>1416.84</v>
+        <v>1416.45</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1429.64</v>
+        <v>1429.26</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>12088</v>
+        <v>12031</v>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
@@ -2185,16 +2185,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1422.08</v>
+        <v>1422.16</v>
       </c>
       <c r="D12" t="n">
-        <v>1419.2</v>
+        <v>1419.29</v>
       </c>
       <c r="E12" t="n">
-        <v>1424.97</v>
+        <v>1425.03</v>
       </c>
       <c r="F12" t="n">
-        <v>77683</v>
+        <v>78407</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -2336,16 +2336,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1421.6</v>
+        <v>1421.84</v>
       </c>
       <c r="D13" t="n">
-        <v>1417.44</v>
+        <v>1417.75</v>
       </c>
       <c r="E13" t="n">
-        <v>1425.76</v>
+        <v>1425.94</v>
       </c>
       <c r="F13" t="n">
-        <v>31048</v>
+        <v>32014</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -2487,16 +2487,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1421.02</v>
+        <v>1421.68</v>
       </c>
       <c r="D14" t="n">
-        <v>1415.4</v>
+        <v>1416.03</v>
       </c>
       <c r="E14" t="n">
-        <v>1426.64</v>
+        <v>1427.33</v>
       </c>
       <c r="F14" t="n">
-        <v>18831</v>
+        <v>18593</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -2638,16 +2638,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1418.02</v>
+        <v>1417.89</v>
       </c>
       <c r="D15" t="n">
-        <v>1412.03</v>
+        <v>1411.88</v>
       </c>
       <c r="E15" t="n">
-        <v>1424.01</v>
+        <v>1423.89</v>
       </c>
       <c r="F15" t="n">
-        <v>15150</v>
+        <v>15080</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -2785,36 +2785,36 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>kimi-k2-0905-preview</t>
+          <t>qwen3.5-122b-a10b</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1417.75</v>
+        <v>1417.82</v>
       </c>
       <c r="D16" t="n">
-        <v>1411.28</v>
+        <v>1411.16</v>
       </c>
       <c r="E16" t="n">
-        <v>1424.23</v>
+        <v>1424.47</v>
       </c>
       <c r="F16" t="n">
-        <v>11924</v>
+        <v>8124</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Moonshot</t>
+          <t>Alibaba</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Modified MIT</t>
+          <t>Apache 2.0</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1000</v>
+        <v>125</v>
       </c>
       <c r="J16" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -2823,26 +2823,26 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>artificial_analysis</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>2000</v>
+        <v>250</v>
       </c>
       <c r="N16" t="n">
-        <v>2500</v>
+        <v>312.5</v>
       </c>
       <c r="O16" t="n">
-        <v>1000</v>
+        <v>125</v>
       </c>
       <c r="P16" t="n">
-        <v>1250</v>
+        <v>156.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>500</v>
+        <v>62.5</v>
       </c>
       <c r="R16" t="n">
-        <v>625</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="S16" s="5" t="inlineStr">
         <is>
@@ -2854,9 +2854,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="U16" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="U16" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="V16" s="5" t="inlineStr">
@@ -2869,9 +2869,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="X16" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="X16" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Y16" s="5" t="inlineStr">
@@ -2884,9 +2884,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AA16" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AA16" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AB16" s="5" t="inlineStr">
@@ -2894,14 +2894,14 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AC16" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AD16" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AC16" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AD16" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AE16" s="5" t="inlineStr">
@@ -2909,14 +2909,14 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AF16" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AG16" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AF16" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AG16" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
@@ -2926,7 +2926,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>B200 SXM</t>
         </is>
       </c>
     </row>
@@ -2936,36 +2936,36 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>qwen3.5-122b-a10b</t>
+          <t>kimi-k2-0905-preview</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1417.32</v>
+        <v>1417.67</v>
       </c>
       <c r="D17" t="n">
-        <v>1410.19</v>
+        <v>1411.19</v>
       </c>
       <c r="E17" t="n">
-        <v>1424.45</v>
+        <v>1424.15</v>
       </c>
       <c r="F17" t="n">
-        <v>6946</v>
+        <v>11873</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alibaba</t>
+          <t>Moonshot</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
+          <t>Modified MIT</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>125</v>
+        <v>1000</v>
       </c>
       <c r="J17" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -2974,26 +2974,26 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>artificial_analysis</t>
+          <t>override</t>
         </is>
       </c>
       <c r="M17" t="n">
-        <v>250</v>
+        <v>2000</v>
       </c>
       <c r="N17" t="n">
-        <v>312.5</v>
+        <v>2500</v>
       </c>
       <c r="O17" t="n">
-        <v>125</v>
+        <v>1000</v>
       </c>
       <c r="P17" t="n">
-        <v>156.2</v>
+        <v>1250</v>
       </c>
       <c r="Q17" t="n">
-        <v>62.5</v>
+        <v>500</v>
       </c>
       <c r="R17" t="n">
-        <v>78.09999999999999</v>
+        <v>625</v>
       </c>
       <c r="S17" s="5" t="inlineStr">
         <is>
@@ -3005,9 +3005,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="U17" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="U17" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="V17" s="5" t="inlineStr">
@@ -3020,9 +3020,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="X17" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="X17" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="Y17" s="5" t="inlineStr">
@@ -3035,9 +3035,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AA17" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AA17" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AB17" s="5" t="inlineStr">
@@ -3045,14 +3045,14 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AC17" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AD17" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AC17" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD17" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AE17" s="5" t="inlineStr">
@@ -3060,14 +3060,14 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AF17" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AG17" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AF17" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AG17" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>B200 SXM</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
     </row>
@@ -3091,16 +3091,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1417.05</v>
+        <v>1417.15</v>
       </c>
       <c r="D18" t="n">
-        <v>1412.22</v>
+        <v>1412.31</v>
       </c>
       <c r="E18" t="n">
-        <v>1421.89</v>
+        <v>1422</v>
       </c>
       <c r="F18" t="n">
-        <v>28082</v>
+        <v>27871</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -3242,16 +3242,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1416.93</v>
+        <v>1416.76</v>
       </c>
       <c r="D19" t="n">
-        <v>1410.35</v>
+        <v>1410.17</v>
       </c>
       <c r="E19" t="n">
-        <v>1423.51</v>
+        <v>1423.36</v>
       </c>
       <c r="F19" t="n">
-        <v>11885</v>
+        <v>11822</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -3393,16 +3393,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1416.41</v>
+        <v>1416.07</v>
       </c>
       <c r="D20" t="n">
-        <v>1406.47</v>
+        <v>1406.12</v>
       </c>
       <c r="E20" t="n">
-        <v>1426.34</v>
+        <v>1426.01</v>
       </c>
       <c r="F20" t="n">
-        <v>3497</v>
+        <v>3492</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -3540,24 +3540,24 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>mistral-large-3</t>
+          <t>qwen3-vl-235b-a22b-instruct</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1416.39</v>
+        <v>1415.72</v>
       </c>
       <c r="D21" t="n">
-        <v>1412.35</v>
+        <v>1409.26</v>
       </c>
       <c r="E21" t="n">
-        <v>1420.42</v>
+        <v>1422.18</v>
       </c>
       <c r="F21" t="n">
-        <v>33200</v>
+        <v>11614</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Mistral</t>
+          <t>Alibaba</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -3566,10 +3566,10 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>675</v>
+        <v>235</v>
       </c>
       <c r="J21" t="n">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -3582,22 +3582,22 @@
         </is>
       </c>
       <c r="M21" t="n">
-        <v>1350</v>
+        <v>470</v>
       </c>
       <c r="N21" t="n">
-        <v>1687.5</v>
+        <v>587.5</v>
       </c>
       <c r="O21" t="n">
-        <v>675</v>
+        <v>235</v>
       </c>
       <c r="P21" t="n">
-        <v>843.8</v>
+        <v>293.8</v>
       </c>
       <c r="Q21" t="n">
-        <v>337.5</v>
+        <v>117.5</v>
       </c>
       <c r="R21" t="n">
-        <v>421.9</v>
+        <v>146.9</v>
       </c>
       <c r="S21" s="5" t="inlineStr">
         <is>
@@ -3654,9 +3654,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AD21" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AD21" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AE21" s="5" t="inlineStr">
@@ -3669,9 +3669,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AG21" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AG21" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
@@ -3691,36 +3691,36 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>deepseek-v3.1-terminus</t>
+          <t>mistral-large-3</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1415.62</v>
+        <v>1415.67</v>
       </c>
       <c r="D22" t="n">
-        <v>1406.04</v>
+        <v>1411.69</v>
       </c>
       <c r="E22" t="n">
-        <v>1425.2</v>
+        <v>1419.64</v>
       </c>
       <c r="F22" t="n">
-        <v>3736</v>
+        <v>34238</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>DeepSeek</t>
+          <t>Mistral</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Apache 2.0</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>685</v>
+        <v>675</v>
       </c>
       <c r="J22" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -3733,22 +3733,22 @@
         </is>
       </c>
       <c r="M22" t="n">
-        <v>1370</v>
+        <v>1350</v>
       </c>
       <c r="N22" t="n">
-        <v>1712.5</v>
+        <v>1687.5</v>
       </c>
       <c r="O22" t="n">
-        <v>685</v>
+        <v>675</v>
       </c>
       <c r="P22" t="n">
-        <v>856.2</v>
+        <v>843.8</v>
       </c>
       <c r="Q22" t="n">
-        <v>342.5</v>
+        <v>337.5</v>
       </c>
       <c r="R22" t="n">
-        <v>428.1</v>
+        <v>421.9</v>
       </c>
       <c r="S22" s="5" t="inlineStr">
         <is>
@@ -3842,36 +3842,36 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>qwen3-vl-235b-a22b-instruct</t>
+          <t>deepseek-v3.1-terminus</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1415.46</v>
+        <v>1415.65</v>
       </c>
       <c r="D23" t="n">
-        <v>1409</v>
+        <v>1406.05</v>
       </c>
       <c r="E23" t="n">
-        <v>1421.91</v>
+        <v>1425.25</v>
       </c>
       <c r="F23" t="n">
-        <v>11645</v>
+        <v>3724</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alibaba</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>235</v>
+        <v>685</v>
       </c>
       <c r="J23" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -3884,22 +3884,22 @@
         </is>
       </c>
       <c r="M23" t="n">
-        <v>470</v>
+        <v>1370</v>
       </c>
       <c r="N23" t="n">
-        <v>587.5</v>
+        <v>1712.5</v>
       </c>
       <c r="O23" t="n">
-        <v>235</v>
+        <v>685</v>
       </c>
       <c r="P23" t="n">
-        <v>293.8</v>
+        <v>856.2</v>
       </c>
       <c r="Q23" t="n">
-        <v>117.5</v>
+        <v>342.5</v>
       </c>
       <c r="R23" t="n">
-        <v>146.9</v>
+        <v>428.1</v>
       </c>
       <c r="S23" s="5" t="inlineStr">
         <is>
@@ -3956,9 +3956,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AD23" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AD23" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AE23" s="5" t="inlineStr">
@@ -3971,9 +3971,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AG23" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AG23" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
@@ -3997,16 +3997,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1410.68</v>
+        <v>1410.99</v>
       </c>
       <c r="D24" t="n">
-        <v>1405.83</v>
+        <v>1406.12</v>
       </c>
       <c r="E24" t="n">
-        <v>1415.54</v>
+        <v>1415.85</v>
       </c>
       <c r="F24" t="n">
-        <v>24640</v>
+        <v>24516</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -4144,40 +4144,40 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>qwen3.5-27b</t>
+          <t>minimax-m2.5</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1406.31</v>
+        <v>1405.61</v>
       </c>
       <c r="D25" t="n">
-        <v>1399.21</v>
+        <v>1399.97</v>
       </c>
       <c r="E25" t="n">
-        <v>1413.42</v>
+        <v>1411.24</v>
       </c>
       <c r="F25" t="n">
-        <v>6957</v>
+        <v>13000</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alibaba</t>
+          <t>MiniMax</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
+          <t>Modified MIT</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>27.8</v>
+        <v>230</v>
       </c>
       <c r="J25" t="n">
-        <v>27.8</v>
+        <v>10</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>dense</t>
+          <t>moe</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -4186,76 +4186,76 @@
         </is>
       </c>
       <c r="M25" t="n">
-        <v>55.6</v>
+        <v>460</v>
       </c>
       <c r="N25" t="n">
-        <v>69.5</v>
+        <v>575</v>
       </c>
       <c r="O25" t="n">
-        <v>27.8</v>
+        <v>230</v>
       </c>
       <c r="P25" t="n">
-        <v>34.8</v>
+        <v>287.5</v>
       </c>
       <c r="Q25" t="n">
-        <v>13.9</v>
+        <v>115</v>
       </c>
       <c r="R25" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="S25" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="T25" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="U25" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="V25" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W25" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X25" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Y25" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z25" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AA25" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB25" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AC25" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+        <v>143.8</v>
+      </c>
+      <c r="S25" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T25" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U25" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V25" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W25" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X25" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y25" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z25" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA25" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AB25" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AC25" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AD25" s="6" t="inlineStr">
@@ -4263,9 +4263,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="AE25" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AE25" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AF25" s="6" t="inlineStr">
@@ -4280,12 +4280,12 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>B300 SXM</t>
         </is>
       </c>
     </row>
@@ -4295,40 +4295,40 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>minimax-m2.5</t>
+          <t>qwen3.5-27b</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1405.31</v>
+        <v>1405.26</v>
       </c>
       <c r="D26" t="n">
-        <v>1399.46</v>
+        <v>1398.59</v>
       </c>
       <c r="E26" t="n">
-        <v>1411.17</v>
+        <v>1411.92</v>
       </c>
       <c r="F26" t="n">
-        <v>11909</v>
+        <v>8055</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>MiniMax</t>
+          <t>Alibaba</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Modified MIT</t>
+          <t>Apache 2.0</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>230</v>
+        <v>27.8</v>
       </c>
       <c r="J26" t="n">
-        <v>10</v>
+        <v>27.8</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>moe</t>
+          <t>dense</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -4337,76 +4337,76 @@
         </is>
       </c>
       <c r="M26" t="n">
-        <v>460</v>
+        <v>55.6</v>
       </c>
       <c r="N26" t="n">
-        <v>575</v>
+        <v>69.5</v>
       </c>
       <c r="O26" t="n">
-        <v>230</v>
+        <v>27.8</v>
       </c>
       <c r="P26" t="n">
-        <v>287.5</v>
+        <v>34.8</v>
       </c>
       <c r="Q26" t="n">
-        <v>115</v>
+        <v>13.9</v>
       </c>
       <c r="R26" t="n">
-        <v>143.8</v>
-      </c>
-      <c r="S26" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T26" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U26" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="V26" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W26" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X26" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Y26" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z26" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AA26" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AB26" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AC26" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+        <v>17.4</v>
+      </c>
+      <c r="S26" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T26" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U26" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V26" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W26" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X26" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y26" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z26" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AA26" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB26" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AC26" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AD26" s="6" t="inlineStr">
@@ -4414,9 +4414,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="AE26" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AE26" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AF26" s="6" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>H100 SXM</t>
         </is>
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>B300 SXM</t>
+          <t>H100 SXM</t>
         </is>
       </c>
     </row>
@@ -4450,16 +4450,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1402.71</v>
+        <v>1402.66</v>
       </c>
       <c r="D27" t="n">
-        <v>1398.23</v>
+        <v>1398.17</v>
       </c>
       <c r="E27" t="n">
-        <v>1407.19</v>
+        <v>1407.15</v>
       </c>
       <c r="F27" t="n">
-        <v>38797</v>
+        <v>38481</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -4597,20 +4597,20 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>qwen3-next-80b-a3b-instruct</t>
+          <t>qwen3.5-35b-a3b</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1401.49</v>
+        <v>1402.2</v>
       </c>
       <c r="D28" t="n">
-        <v>1396.73</v>
+        <v>1395.62</v>
       </c>
       <c r="E28" t="n">
-        <v>1406.25</v>
+        <v>1408.79</v>
       </c>
       <c r="F28" t="n">
-        <v>23187</v>
+        <v>8393</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -4623,7 +4623,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>80</v>
+        <v>36</v>
       </c>
       <c r="J28" t="n">
         <v>3</v>
@@ -4639,31 +4639,31 @@
         </is>
       </c>
       <c r="M28" t="n">
-        <v>160</v>
+        <v>72</v>
       </c>
       <c r="N28" t="n">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="O28" t="n">
-        <v>80</v>
+        <v>36</v>
       </c>
       <c r="P28" t="n">
-        <v>100</v>
+        <v>45</v>
       </c>
       <c r="Q28" t="n">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="R28" t="n">
-        <v>50</v>
-      </c>
-      <c r="S28" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T28" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+        <v>22.5</v>
+      </c>
+      <c r="S28" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T28" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="U28" s="6" t="inlineStr">
@@ -4676,9 +4676,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="W28" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="W28" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="X28" s="6" t="inlineStr">
@@ -4686,9 +4686,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="Y28" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="Y28" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Z28" s="6" t="inlineStr">
@@ -4701,9 +4701,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB28" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AB28" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AC28" s="6" t="inlineStr">
@@ -4733,12 +4733,12 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>B300 SXM</t>
+          <t>RTX PRO 6000</t>
         </is>
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>H200 SXM</t>
+          <t>H100 SXM</t>
         </is>
       </c>
     </row>
@@ -4748,20 +4748,20 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>qwen3.5-35b-a3b</t>
+          <t>qwen3-next-80b-a3b-instruct</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1401</v>
+        <v>1401.6</v>
       </c>
       <c r="D29" t="n">
-        <v>1393.98</v>
+        <v>1396.83</v>
       </c>
       <c r="E29" t="n">
-        <v>1408.01</v>
+        <v>1406.37</v>
       </c>
       <c r="F29" t="n">
-        <v>7278</v>
+        <v>23100</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -4774,7 +4774,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="J29" t="n">
         <v>3</v>
@@ -4790,31 +4790,31 @@
         </is>
       </c>
       <c r="M29" t="n">
-        <v>72</v>
+        <v>160</v>
       </c>
       <c r="N29" t="n">
-        <v>90</v>
+        <v>200</v>
       </c>
       <c r="O29" t="n">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="P29" t="n">
-        <v>45</v>
+        <v>100</v>
       </c>
       <c r="Q29" t="n">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="R29" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="S29" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="T29" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+        <v>50</v>
+      </c>
+      <c r="S29" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T29" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="U29" s="6" t="inlineStr">
@@ -4827,9 +4827,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="W29" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="W29" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="X29" s="6" t="inlineStr">
@@ -4837,9 +4837,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="Y29" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="Y29" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="Z29" s="6" t="inlineStr">
@@ -4852,9 +4852,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB29" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AB29" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AC29" s="6" t="inlineStr">
@@ -4884,12 +4884,12 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>RTX PRO 6000</t>
+          <t>B300 SXM</t>
         </is>
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>H200 SXM</t>
         </is>
       </c>
     </row>
@@ -4903,16 +4903,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1400.43</v>
+        <v>1400.74</v>
       </c>
       <c r="D30" t="n">
-        <v>1394.07</v>
+        <v>1394.37</v>
       </c>
       <c r="E30" t="n">
-        <v>1406.79</v>
+        <v>1407.1</v>
       </c>
       <c r="F30" t="n">
-        <v>11517</v>
+        <v>11478</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -5054,16 +5054,16 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1399.16</v>
+        <v>1399.63</v>
       </c>
       <c r="D31" t="n">
-        <v>1392.66</v>
+        <v>1393.11</v>
       </c>
       <c r="E31" t="n">
-        <v>1405.66</v>
+        <v>1406.15</v>
       </c>
       <c r="F31" t="n">
-        <v>9128</v>
+        <v>9060</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -5205,13 +5205,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1397.57</v>
+        <v>1397.55</v>
       </c>
       <c r="D32" t="n">
-        <v>1392.72</v>
+        <v>1392.7</v>
       </c>
       <c r="E32" t="n">
-        <v>1402.43</v>
+        <v>1402.41</v>
       </c>
       <c r="F32" t="n">
         <v>18524</v>
@@ -5356,16 +5356,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1395.82</v>
+        <v>1395.56</v>
       </c>
       <c r="D33" t="n">
-        <v>1389.06</v>
+        <v>1388.79</v>
       </c>
       <c r="E33" t="n">
-        <v>1402.58</v>
+        <v>1402.33</v>
       </c>
       <c r="F33" t="n">
-        <v>8052</v>
+        <v>8027</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -5507,16 +5507,16 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1394.34</v>
+        <v>1394.55</v>
       </c>
       <c r="D34" t="n">
-        <v>1390.49</v>
+        <v>1390.7</v>
       </c>
       <c r="E34" t="n">
-        <v>1398.19</v>
+        <v>1398.41</v>
       </c>
       <c r="F34" t="n">
-        <v>46144</v>
+        <v>45807</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -5658,16 +5658,16 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1391.89</v>
+        <v>1391.9</v>
       </c>
       <c r="D35" t="n">
-        <v>1387.49</v>
+        <v>1387.55</v>
       </c>
       <c r="E35" t="n">
-        <v>1396.3</v>
+        <v>1396.24</v>
       </c>
       <c r="F35" t="n">
-        <v>25427</v>
+        <v>26410</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -5809,16 +5809,16 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1388.71</v>
+        <v>1390.82</v>
       </c>
       <c r="D36" t="n">
-        <v>1383.19</v>
+        <v>1385.47</v>
       </c>
       <c r="E36" t="n">
-        <v>1394.23</v>
+        <v>1396.18</v>
       </c>
       <c r="F36" t="n">
-        <v>13885</v>
+        <v>14862</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -5956,36 +5956,36 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>mimo-v2-flash (thinking)</t>
+          <t>qwen3-coder-480b-a35b-instruct</t>
         </is>
       </c>
       <c r="C37" t="n">
         <v>1387.3</v>
       </c>
       <c r="D37" t="n">
-        <v>1381.01</v>
+        <v>1382.36</v>
       </c>
       <c r="E37" t="n">
-        <v>1393.59</v>
+        <v>1392.23</v>
       </c>
       <c r="F37" t="n">
-        <v>11053</v>
+        <v>25977</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Xiaomi</t>
+          <t>Alibaba</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Apache 2.0</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>309</v>
+        <v>480</v>
       </c>
       <c r="J37" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -5998,22 +5998,22 @@
         </is>
       </c>
       <c r="M37" t="n">
-        <v>618</v>
+        <v>960</v>
       </c>
       <c r="N37" t="n">
-        <v>772.5</v>
+        <v>1200</v>
       </c>
       <c r="O37" t="n">
-        <v>309</v>
+        <v>480</v>
       </c>
       <c r="P37" t="n">
-        <v>386.2</v>
+        <v>600</v>
       </c>
       <c r="Q37" t="n">
-        <v>154.5</v>
+        <v>240</v>
       </c>
       <c r="R37" t="n">
-        <v>193.1</v>
+        <v>300</v>
       </c>
       <c r="S37" s="5" t="inlineStr">
         <is>
@@ -6085,9 +6085,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AG37" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AG37" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AH37" t="inlineStr">
@@ -6107,36 +6107,36 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>qwen3-coder-480b-a35b-instruct</t>
+          <t>mimo-v2-flash (thinking)</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1387.09</v>
+        <v>1387.29</v>
       </c>
       <c r="D38" t="n">
-        <v>1382.17</v>
+        <v>1381</v>
       </c>
       <c r="E38" t="n">
-        <v>1392</v>
+        <v>1393.58</v>
       </c>
       <c r="F38" t="n">
-        <v>26162</v>
+        <v>11012</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alibaba</t>
+          <t>Xiaomi</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>480</v>
+        <v>309</v>
       </c>
       <c r="J38" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -6149,22 +6149,22 @@
         </is>
       </c>
       <c r="M38" t="n">
-        <v>960</v>
+        <v>618</v>
       </c>
       <c r="N38" t="n">
-        <v>1200</v>
+        <v>772.5</v>
       </c>
       <c r="O38" t="n">
-        <v>480</v>
+        <v>309</v>
       </c>
       <c r="P38" t="n">
-        <v>600</v>
+        <v>386.2</v>
       </c>
       <c r="Q38" t="n">
-        <v>240</v>
+        <v>154.5</v>
       </c>
       <c r="R38" t="n">
-        <v>300</v>
+        <v>193.1</v>
       </c>
       <c r="S38" s="5" t="inlineStr">
         <is>
@@ -6236,9 +6236,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AG38" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AG38" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AH38" t="inlineStr">
@@ -6262,16 +6262,16 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1385.97</v>
+        <v>1386.24</v>
       </c>
       <c r="D39" t="n">
-        <v>1380.7</v>
+        <v>1380.97</v>
       </c>
       <c r="E39" t="n">
-        <v>1391.24</v>
+        <v>1391.51</v>
       </c>
       <c r="F39" t="n">
-        <v>17271</v>
+        <v>17228</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -6413,16 +6413,16 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1382.94</v>
+        <v>1383.12</v>
       </c>
       <c r="D40" t="n">
-        <v>1378.09</v>
+        <v>1378.25</v>
       </c>
       <c r="E40" t="n">
-        <v>1387.8</v>
+        <v>1387.98</v>
       </c>
       <c r="F40" t="n">
-        <v>24086</v>
+        <v>23958</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -6564,16 +6564,16 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1378</v>
+        <v>1377.98</v>
       </c>
       <c r="D41" t="n">
-        <v>1366.75</v>
+        <v>1366.7</v>
       </c>
       <c r="E41" t="n">
-        <v>1389.26</v>
+        <v>1389.25</v>
       </c>
       <c r="F41" t="n">
-        <v>2836</v>
+        <v>2823</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -6715,16 +6715,16 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1375.54</v>
+        <v>1376.01</v>
       </c>
       <c r="D42" t="n">
-        <v>1368.63</v>
+        <v>1369.51</v>
       </c>
       <c r="E42" t="n">
-        <v>1382.45</v>
+        <v>1382.51</v>
       </c>
       <c r="F42" t="n">
-        <v>8033</v>
+        <v>9281</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -6866,16 +6866,16 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1374.5</v>
+        <v>1374.31</v>
       </c>
       <c r="D43" t="n">
-        <v>1369.83</v>
+        <v>1369.63</v>
       </c>
       <c r="E43" t="n">
-        <v>1379.18</v>
+        <v>1379</v>
       </c>
       <c r="F43" t="n">
-        <v>26679</v>
+        <v>26433</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -7017,16 +7017,16 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1372.36</v>
+        <v>1372.63</v>
       </c>
       <c r="D44" t="n">
-        <v>1368.13</v>
+        <v>1368.39</v>
       </c>
       <c r="E44" t="n">
-        <v>1376.6</v>
+        <v>1376.87</v>
       </c>
       <c r="F44" t="n">
-        <v>31546</v>
+        <v>31391</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -7168,16 +7168,16 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1368.85</v>
+        <v>1369.01</v>
       </c>
       <c r="D45" t="n">
-        <v>1363.04</v>
+        <v>1363.19</v>
       </c>
       <c r="E45" t="n">
-        <v>1374.66</v>
+        <v>1374.82</v>
       </c>
       <c r="F45" t="n">
-        <v>13906</v>
+        <v>13843</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -7319,16 +7319,16 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1368.47</v>
+        <v>1368.7</v>
       </c>
       <c r="D46" t="n">
-        <v>1362.64</v>
+        <v>1362.86</v>
       </c>
       <c r="E46" t="n">
-        <v>1374.31</v>
+        <v>1374.54</v>
       </c>
       <c r="F46" t="n">
-        <v>11857</v>
+        <v>11829</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -7470,16 +7470,16 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1365.3</v>
+        <v>1365.08</v>
       </c>
       <c r="D47" t="n">
-        <v>1361.65</v>
+        <v>1361.43</v>
       </c>
       <c r="E47" t="n">
-        <v>1368.95</v>
+        <v>1368.73</v>
       </c>
       <c r="F47" t="n">
-        <v>48195</v>
+        <v>47859</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -7621,16 +7621,16 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1364.56</v>
+        <v>1364.59</v>
       </c>
       <c r="D48" t="n">
-        <v>1354.88</v>
+        <v>1354.9</v>
       </c>
       <c r="E48" t="n">
-        <v>1374.23</v>
+        <v>1374.28</v>
       </c>
       <c r="F48" t="n">
-        <v>3641</v>
+        <v>3626</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -7772,16 +7772,16 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1364.38</v>
+        <v>1363.14</v>
       </c>
       <c r="D49" t="n">
-        <v>1360.14</v>
+        <v>1358.89</v>
       </c>
       <c r="E49" t="n">
-        <v>1368.63</v>
+        <v>1367.4</v>
       </c>
       <c r="F49" t="n">
-        <v>35951</v>
+        <v>35529</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -7923,13 +7923,13 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1358.28</v>
+        <v>1358.25</v>
       </c>
       <c r="D50" t="n">
-        <v>1353.57</v>
+        <v>1353.54</v>
       </c>
       <c r="E50" t="n">
-        <v>1362.99</v>
+        <v>1362.97</v>
       </c>
       <c r="F50" t="n">
         <v>21770</v>
@@ -8074,16 +8074,16 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1357.11</v>
+        <v>1356.85</v>
       </c>
       <c r="D51" t="n">
-        <v>1351.94</v>
+        <v>1351.67</v>
       </c>
       <c r="E51" t="n">
-        <v>1362.29</v>
+        <v>1362.04</v>
       </c>
       <c r="F51" t="n">
-        <v>18015</v>
+        <v>17852</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -8225,16 +8225,16 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1356.52</v>
+        <v>1356.44</v>
       </c>
       <c r="D52" t="n">
-        <v>1348.18</v>
+        <v>1348.08</v>
       </c>
       <c r="E52" t="n">
-        <v>1364.86</v>
+        <v>1364.8</v>
       </c>
       <c r="F52" t="n">
-        <v>5387</v>
+        <v>5365</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -8376,16 +8376,16 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1353.82</v>
+        <v>1353.78</v>
       </c>
       <c r="D53" t="n">
-        <v>1349.49</v>
+        <v>1349.44</v>
       </c>
       <c r="E53" t="n">
-        <v>1358.15</v>
+        <v>1358.12</v>
       </c>
       <c r="F53" t="n">
-        <v>31077</v>
+        <v>30921</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -8527,16 +8527,16 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1353.53</v>
+        <v>1353.46</v>
       </c>
       <c r="D54" t="n">
-        <v>1350.1</v>
+        <v>1350.02</v>
       </c>
       <c r="E54" t="n">
-        <v>1356.95</v>
+        <v>1356.89</v>
       </c>
       <c r="F54" t="n">
-        <v>57068</v>
+        <v>56679</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -8678,16 +8678,16 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1352.97</v>
+        <v>1353.28</v>
       </c>
       <c r="D55" t="n">
-        <v>1344.64</v>
+        <v>1344.95</v>
       </c>
       <c r="E55" t="n">
-        <v>1361.3</v>
+        <v>1361.61</v>
       </c>
       <c r="F55" t="n">
-        <v>4989</v>
+        <v>4979</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -8829,16 +8829,16 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1347.78</v>
+        <v>1347.48</v>
       </c>
       <c r="D56" t="n">
-        <v>1340.41</v>
+        <v>1340.09</v>
       </c>
       <c r="E56" t="n">
-        <v>1355.16</v>
+        <v>1354.86</v>
       </c>
       <c r="F56" t="n">
-        <v>6600</v>
+        <v>6581</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -8896,24 +8896,24 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>minimax-m2</t>
+          <t>qwen3-32b</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1347.22</v>
+        <v>1347.01</v>
       </c>
       <c r="D57" t="n">
-        <v>1339.51</v>
+        <v>1337.54</v>
       </c>
       <c r="E57" t="n">
-        <v>1354.93</v>
+        <v>1356.48</v>
       </c>
       <c r="F57" t="n">
-        <v>6950</v>
+        <v>3926</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>MiniMax</t>
+          <t>Alibaba</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -8922,14 +8922,14 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>230</v>
+        <v>32.8</v>
       </c>
       <c r="J57" t="n">
-        <v>10</v>
+        <v>32.8</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>moe</t>
+          <t>dense</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -8938,36 +8938,36 @@
         </is>
       </c>
       <c r="M57" t="n">
-        <v>460</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="N57" t="n">
-        <v>575</v>
+        <v>82</v>
       </c>
       <c r="O57" t="n">
-        <v>230</v>
+        <v>32.8</v>
       </c>
       <c r="P57" t="n">
-        <v>287.5</v>
+        <v>41</v>
       </c>
       <c r="Q57" t="n">
-        <v>115</v>
+        <v>16.4</v>
       </c>
       <c r="R57" t="n">
-        <v>143.8</v>
-      </c>
-      <c r="S57" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T57" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U57" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+        <v>20.5</v>
+      </c>
+      <c r="S57" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T57" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U57" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="V57" s="5" t="inlineStr">
@@ -8975,39 +8975,39 @@
           <t>No</t>
         </is>
       </c>
-      <c r="W57" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X57" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Y57" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z57" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AA57" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AB57" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AC57" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="W57" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X57" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y57" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z57" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AA57" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB57" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AC57" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AD57" s="6" t="inlineStr">
@@ -9015,9 +9015,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="AE57" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AE57" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AF57" s="6" t="inlineStr">
@@ -9032,12 +9032,12 @@
       </c>
       <c r="AH57" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>RTX PRO 6000</t>
         </is>
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>B300 SXM</t>
+          <t>H100 SXM</t>
         </is>
       </c>
     </row>
@@ -9047,36 +9047,36 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>qwen3-32b</t>
+          <t>llama-3.1-nemotron-ultra-253b-v1</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1347</v>
+        <v>1346.9</v>
       </c>
       <c r="D58" t="n">
-        <v>1337.53</v>
+        <v>1335.2</v>
       </c>
       <c r="E58" t="n">
-        <v>1356.47</v>
+        <v>1358.6</v>
       </c>
       <c r="F58" t="n">
-        <v>3926</v>
+        <v>2549</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alibaba</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
+          <t>Nvidia Open Model</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>32.8</v>
+        <v>253</v>
       </c>
       <c r="J58" t="n">
-        <v>32.8</v>
+        <v>253</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
@@ -9089,36 +9089,36 @@
         </is>
       </c>
       <c r="M58" t="n">
-        <v>65.59999999999999</v>
+        <v>506</v>
       </c>
       <c r="N58" t="n">
-        <v>82</v>
+        <v>632.5</v>
       </c>
       <c r="O58" t="n">
-        <v>32.8</v>
+        <v>253</v>
       </c>
       <c r="P58" t="n">
-        <v>41</v>
+        <v>316.2</v>
       </c>
       <c r="Q58" t="n">
-        <v>16.4</v>
+        <v>126.5</v>
       </c>
       <c r="R58" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="S58" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="T58" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="U58" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+        <v>158.1</v>
+      </c>
+      <c r="S58" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T58" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U58" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="V58" s="5" t="inlineStr">
@@ -9126,39 +9126,39 @@
           <t>No</t>
         </is>
       </c>
-      <c r="W58" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X58" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Y58" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z58" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AA58" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB58" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AC58" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="W58" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X58" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y58" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z58" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA58" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AB58" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AC58" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AD58" s="6" t="inlineStr">
@@ -9166,14 +9166,14 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="AE58" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AF58" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AE58" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF58" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AG58" s="6" t="inlineStr">
@@ -9183,12 +9183,12 @@
       </c>
       <c r="AH58" t="inlineStr">
         <is>
-          <t>RTX PRO 6000</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
       <c r="AI58" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
     </row>
@@ -9198,40 +9198,40 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>llama-3.1-nemotron-ultra-253b-v1</t>
+          <t>minimax-m2</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1346.91</v>
+        <v>1346.61</v>
       </c>
       <c r="D59" t="n">
-        <v>1335.21</v>
+        <v>1338.89</v>
       </c>
       <c r="E59" t="n">
-        <v>1358.61</v>
+        <v>1354.33</v>
       </c>
       <c r="F59" t="n">
-        <v>2549</v>
+        <v>6919</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>MiniMax</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Nvidia Open Model</t>
+          <t>Apache 2.0</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>253</v>
+        <v>230</v>
       </c>
       <c r="J59" t="n">
-        <v>253</v>
+        <v>10</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>dense</t>
+          <t>moe</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -9240,22 +9240,22 @@
         </is>
       </c>
       <c r="M59" t="n">
-        <v>506</v>
+        <v>460</v>
       </c>
       <c r="N59" t="n">
-        <v>632.5</v>
+        <v>575</v>
       </c>
       <c r="O59" t="n">
-        <v>253</v>
+        <v>230</v>
       </c>
       <c r="P59" t="n">
-        <v>316.2</v>
+        <v>287.5</v>
       </c>
       <c r="Q59" t="n">
-        <v>126.5</v>
+        <v>115</v>
       </c>
       <c r="R59" t="n">
-        <v>158.1</v>
+        <v>143.8</v>
       </c>
       <c r="S59" s="5" t="inlineStr">
         <is>
@@ -9322,9 +9322,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AF59" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AF59" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AG59" s="6" t="inlineStr">
@@ -9339,7 +9339,7 @@
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>B300 SXM</t>
         </is>
       </c>
     </row>
@@ -9353,16 +9353,16 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1346.03</v>
+        <v>1346.2</v>
       </c>
       <c r="D60" t="n">
-        <v>1338.82</v>
+        <v>1338.97</v>
       </c>
       <c r="E60" t="n">
-        <v>1353.25</v>
+        <v>1353.43</v>
       </c>
       <c r="F60" t="n">
-        <v>7125</v>
+        <v>7087</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -9504,16 +9504,16 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1342.72</v>
+        <v>1342.64</v>
       </c>
       <c r="D61" t="n">
-        <v>1332.8</v>
+        <v>1332.69</v>
       </c>
       <c r="E61" t="n">
-        <v>1352.63</v>
+        <v>1352.59</v>
       </c>
       <c r="F61" t="n">
-        <v>3392</v>
+        <v>3369</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -9655,13 +9655,13 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1341.52</v>
+        <v>1341.43</v>
       </c>
       <c r="D62" t="n">
-        <v>1332</v>
+        <v>1331.92</v>
       </c>
       <c r="E62" t="n">
-        <v>1351.03</v>
+        <v>1350.95</v>
       </c>
       <c r="F62" t="n">
         <v>3829</v>
@@ -9806,16 +9806,16 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1335.63</v>
+        <v>1335.53</v>
       </c>
       <c r="D63" t="n">
-        <v>1331.23</v>
+        <v>1331.12</v>
       </c>
       <c r="E63" t="n">
-        <v>1340.04</v>
+        <v>1339.95</v>
       </c>
       <c r="F63" t="n">
-        <v>25749</v>
+        <v>25531</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -9957,13 +9957,13 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1334.6</v>
+        <v>1334.53</v>
       </c>
       <c r="D64" t="n">
-        <v>1330.93</v>
+        <v>1330.86</v>
       </c>
       <c r="E64" t="n">
-        <v>1338.27</v>
+        <v>1338.21</v>
       </c>
       <c r="F64" t="n">
         <v>41375</v>
@@ -10108,13 +10108,13 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1332.78</v>
+        <v>1332.73</v>
       </c>
       <c r="D65" t="n">
-        <v>1329.22</v>
+        <v>1329.17</v>
       </c>
       <c r="E65" t="n">
-        <v>1336.35</v>
+        <v>1336.29</v>
       </c>
       <c r="F65" t="n">
         <v>59656</v>
@@ -10259,16 +10259,16 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1330.82</v>
+        <v>1330.76</v>
       </c>
       <c r="D66" t="n">
-        <v>1324.71</v>
+        <v>1324.64</v>
       </c>
       <c r="E66" t="n">
-        <v>1336.94</v>
+        <v>1336.88</v>
       </c>
       <c r="F66" t="n">
-        <v>12326</v>
+        <v>12281</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -10410,16 +10410,16 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1327.69</v>
+        <v>1327.52</v>
       </c>
       <c r="D67" t="n">
-        <v>1322.98</v>
+        <v>1322.81</v>
       </c>
       <c r="E67" t="n">
-        <v>1332.39</v>
+        <v>1332.23</v>
       </c>
       <c r="F67" t="n">
-        <v>26908</v>
+        <v>26650</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -10561,13 +10561,13 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1327.41</v>
+        <v>1327.37</v>
       </c>
       <c r="D68" t="n">
-        <v>1315.24</v>
+        <v>1315.2</v>
       </c>
       <c r="E68" t="n">
-        <v>1339.58</v>
+        <v>1339.54</v>
       </c>
       <c r="F68" t="n">
         <v>2218</v>
@@ -10712,16 +10712,16 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1326.83</v>
+        <v>1326.87</v>
       </c>
       <c r="D69" t="n">
-        <v>1322.6</v>
+        <v>1322.63</v>
       </c>
       <c r="E69" t="n">
-        <v>1331.06</v>
+        <v>1331.11</v>
       </c>
       <c r="F69" t="n">
-        <v>40529</v>
+        <v>40218</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -10863,16 +10863,16 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1326.21</v>
+        <v>1326.42</v>
       </c>
       <c r="D70" t="n">
-        <v>1304.74</v>
+        <v>1304.95</v>
       </c>
       <c r="E70" t="n">
-        <v>1347.69</v>
+        <v>1347.89</v>
       </c>
       <c r="F70" t="n">
-        <v>811</v>
+        <v>806</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -11017,10 +11017,10 @@
         <v>1323.18</v>
       </c>
       <c r="D71" t="n">
-        <v>1314.91</v>
+        <v>1314.92</v>
       </c>
       <c r="E71" t="n">
-        <v>1331.44</v>
+        <v>1331.45</v>
       </c>
       <c r="F71" t="n">
         <v>6795</v>
@@ -11165,16 +11165,16 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1322.31</v>
+        <v>1322.09</v>
       </c>
       <c r="D72" t="n">
-        <v>1317.62</v>
+        <v>1317.39</v>
       </c>
       <c r="E72" t="n">
-        <v>1326.99</v>
+        <v>1326.78</v>
       </c>
       <c r="F72" t="n">
-        <v>30740</v>
+        <v>30517</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -11316,16 +11316,16 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1321</v>
+        <v>1320.82</v>
       </c>
       <c r="D73" t="n">
-        <v>1313.83</v>
+        <v>1313.64</v>
       </c>
       <c r="E73" t="n">
-        <v>1328.18</v>
+        <v>1328.01</v>
       </c>
       <c r="F73" t="n">
-        <v>7252</v>
+        <v>7222</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -11463,68 +11463,68 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>gemma-3n-e4b-it</t>
+          <t>llama-3.3-70b-instruct</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1318.46</v>
+        <v>1318.24</v>
       </c>
       <c r="D74" t="n">
-        <v>1313.34</v>
+        <v>1314.81</v>
       </c>
       <c r="E74" t="n">
-        <v>1323.57</v>
+        <v>1321.68</v>
       </c>
       <c r="F74" t="n">
-        <v>22915</v>
+        <v>54891</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Gemma</t>
+          <t>Llama-3.3</t>
         </is>
       </c>
       <c r="I74" t="n">
-        <v>8.4</v>
+        <v>70</v>
       </c>
       <c r="J74" t="n">
-        <v>4</v>
+        <v>70</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>moe</t>
+          <t>dense</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>artificial_analysis</t>
+          <t>name_parsing</t>
         </is>
       </c>
       <c r="M74" t="n">
-        <v>16.8</v>
+        <v>140</v>
       </c>
       <c r="N74" t="n">
-        <v>21</v>
+        <v>175</v>
       </c>
       <c r="O74" t="n">
-        <v>8.4</v>
+        <v>70</v>
       </c>
       <c r="P74" t="n">
-        <v>10.5</v>
+        <v>87.5</v>
       </c>
       <c r="Q74" t="n">
-        <v>4.2</v>
+        <v>35</v>
       </c>
       <c r="R74" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="S74" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+        <v>43.8</v>
+      </c>
+      <c r="S74" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="T74" s="6" t="inlineStr">
@@ -11537,14 +11537,14 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="V74" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W74" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="V74" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W74" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="X74" s="6" t="inlineStr">
@@ -11552,9 +11552,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="Y74" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="Y74" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="Z74" s="6" t="inlineStr">
@@ -11599,12 +11599,12 @@
       </c>
       <c r="AH74" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>B200 SXM</t>
         </is>
       </c>
       <c r="AI74" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>RTX PRO 6000</t>
         </is>
       </c>
     </row>
@@ -11614,68 +11614,68 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>llama-3.3-70b-instruct</t>
+          <t>gpt-oss-20b</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>1318.26</v>
+        <v>1318.2</v>
       </c>
       <c r="D75" t="n">
-        <v>1314.83</v>
+        <v>1311.85</v>
       </c>
       <c r="E75" t="n">
-        <v>1321.68</v>
+        <v>1324.54</v>
       </c>
       <c r="F75" t="n">
-        <v>55149</v>
+        <v>10706</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Llama-3.3</t>
+          <t>Apache 2.0</t>
         </is>
       </c>
       <c r="I75" t="n">
-        <v>70</v>
+        <v>21</v>
       </c>
       <c r="J75" t="n">
-        <v>70</v>
+        <v>3.6</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>dense</t>
+          <t>moe</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>override</t>
         </is>
       </c>
       <c r="M75" t="n">
-        <v>140</v>
+        <v>42</v>
       </c>
       <c r="N75" t="n">
-        <v>175</v>
+        <v>52.5</v>
       </c>
       <c r="O75" t="n">
-        <v>70</v>
+        <v>21</v>
       </c>
       <c r="P75" t="n">
-        <v>87.5</v>
+        <v>26.2</v>
       </c>
       <c r="Q75" t="n">
-        <v>35</v>
+        <v>10.5</v>
       </c>
       <c r="R75" t="n">
-        <v>43.8</v>
-      </c>
-      <c r="S75" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+        <v>13.1</v>
+      </c>
+      <c r="S75" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="T75" s="6" t="inlineStr">
@@ -11688,14 +11688,14 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="V75" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W75" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="V75" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W75" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="X75" s="6" t="inlineStr">
@@ -11703,9 +11703,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="Y75" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="Y75" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Z75" s="6" t="inlineStr">
@@ -11750,12 +11750,12 @@
       </c>
       <c r="AH75" t="inlineStr">
         <is>
-          <t>B200 SXM</t>
+          <t>H100 SXM</t>
         </is>
       </c>
       <c r="AI75" t="inlineStr">
         <is>
-          <t>RTX PRO 6000</t>
+          <t>H100 SXM</t>
         </is>
       </c>
     </row>
@@ -11765,64 +11765,64 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>gpt-oss-20b</t>
+          <t>gemma-3n-e4b-it</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>1317.87</v>
+        <v>1318.08</v>
       </c>
       <c r="D76" t="n">
-        <v>1311.53</v>
+        <v>1312.95</v>
       </c>
       <c r="E76" t="n">
-        <v>1324.21</v>
+        <v>1323.22</v>
       </c>
       <c r="F76" t="n">
-        <v>10750</v>
+        <v>22730</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
+          <t>Gemma</t>
         </is>
       </c>
       <c r="I76" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="J76" t="n">
+        <v>4</v>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>artificial_analysis</t>
+        </is>
+      </c>
+      <c r="M76" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="N76" t="n">
         <v>21</v>
       </c>
-      <c r="J76" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>override</t>
-        </is>
-      </c>
-      <c r="M76" t="n">
-        <v>42</v>
-      </c>
-      <c r="N76" t="n">
-        <v>52.5</v>
-      </c>
       <c r="O76" t="n">
-        <v>21</v>
+        <v>8.4</v>
       </c>
       <c r="P76" t="n">
-        <v>26.2</v>
+        <v>10.5</v>
       </c>
       <c r="Q76" t="n">
-        <v>10.5</v>
+        <v>4.2</v>
       </c>
       <c r="R76" t="n">
-        <v>13.1</v>
+        <v>5.2</v>
       </c>
       <c r="S76" s="6" t="inlineStr">
         <is>
@@ -11920,16 +11920,16 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1317.8</v>
+        <v>1317.76</v>
       </c>
       <c r="D77" t="n">
-        <v>1312.21</v>
+        <v>1312.17</v>
       </c>
       <c r="E77" t="n">
-        <v>1323.39</v>
+        <v>1323.35</v>
       </c>
       <c r="F77" t="n">
-        <v>15650</v>
+        <v>15606</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -12071,13 +12071,13 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1317.65</v>
+        <v>1317.63</v>
       </c>
       <c r="D78" t="n">
-        <v>1311.97</v>
+        <v>1311.95</v>
       </c>
       <c r="E78" t="n">
-        <v>1323.33</v>
+        <v>1323.32</v>
       </c>
       <c r="F78" t="n">
         <v>16478</v>
@@ -12142,13 +12142,13 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>1314.18</v>
+        <v>1314.17</v>
       </c>
       <c r="D79" t="n">
-        <v>1309.66</v>
+        <v>1309.64</v>
       </c>
       <c r="E79" t="n">
-        <v>1318.7</v>
+        <v>1318.69</v>
       </c>
       <c r="F79" t="n">
         <v>24739</v>
@@ -12293,13 +12293,13 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1313.58</v>
+        <v>1313.56</v>
       </c>
       <c r="D80" t="n">
-        <v>1309.68</v>
+        <v>1309.66</v>
       </c>
       <c r="E80" t="n">
-        <v>1317.48</v>
+        <v>1317.46</v>
       </c>
       <c r="F80" t="n">
         <v>45459</v>
@@ -12591,36 +12591,36 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>olmo-3-32b-think</t>
+          <t>athene-70b-0725</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>1306.09</v>
+        <v>1305.62</v>
       </c>
       <c r="D82" t="n">
-        <v>1297.92</v>
+        <v>1299.96</v>
       </c>
       <c r="E82" t="n">
-        <v>1314.25</v>
+        <v>1311.28</v>
       </c>
       <c r="F82" t="n">
-        <v>6023</v>
+        <v>19621</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Ai2</t>
+          <t>NexusFlow</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
+          <t>CC-BY-NC-4.0</t>
         </is>
       </c>
       <c r="I82" t="n">
-        <v>32.2</v>
+        <v>70</v>
       </c>
       <c r="J82" t="n">
-        <v>32.2</v>
+        <v>70</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
@@ -12629,30 +12629,30 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>artificial_analysis</t>
+          <t>name_parsing</t>
         </is>
       </c>
       <c r="M82" t="n">
-        <v>64.40000000000001</v>
+        <v>140</v>
       </c>
       <c r="N82" t="n">
-        <v>80.5</v>
+        <v>175</v>
       </c>
       <c r="O82" t="n">
-        <v>32.2</v>
+        <v>70</v>
       </c>
       <c r="P82" t="n">
-        <v>40.2</v>
+        <v>87.5</v>
       </c>
       <c r="Q82" t="n">
-        <v>16.1</v>
+        <v>35</v>
       </c>
       <c r="R82" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="S82" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+        <v>43.8</v>
+      </c>
+      <c r="S82" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="T82" s="6" t="inlineStr">
@@ -12670,9 +12670,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="W82" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="W82" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="X82" s="6" t="inlineStr">
@@ -12680,9 +12680,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="Y82" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="Y82" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="Z82" s="6" t="inlineStr">
@@ -12727,12 +12727,12 @@
       </c>
       <c r="AH82" t="inlineStr">
         <is>
+          <t>B200 SXM</t>
+        </is>
+      </c>
+      <c r="AI82" t="inlineStr">
+        <is>
           <t>RTX PRO 6000</t>
-        </is>
-      </c>
-      <c r="AI82" t="inlineStr">
-        <is>
-          <t>H100 SXM</t>
         </is>
       </c>
     </row>
@@ -12742,36 +12742,36 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>athene-70b-0725</t>
+          <t>olmo-3-32b-think</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>1305.67</v>
+        <v>1305.41</v>
       </c>
       <c r="D83" t="n">
-        <v>1300.01</v>
+        <v>1297.24</v>
       </c>
       <c r="E83" t="n">
-        <v>1311.33</v>
+        <v>1313.59</v>
       </c>
       <c r="F83" t="n">
-        <v>19621</v>
+        <v>5999</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>NexusFlow</t>
+          <t>Ai2</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>CC-BY-NC-4.0</t>
+          <t>Apache 2.0</t>
         </is>
       </c>
       <c r="I83" t="n">
-        <v>70</v>
+        <v>32.2</v>
       </c>
       <c r="J83" t="n">
-        <v>70</v>
+        <v>32.2</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
@@ -12780,30 +12780,30 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>artificial_analysis</t>
         </is>
       </c>
       <c r="M83" t="n">
-        <v>140</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="N83" t="n">
-        <v>175</v>
+        <v>80.5</v>
       </c>
       <c r="O83" t="n">
-        <v>70</v>
+        <v>32.2</v>
       </c>
       <c r="P83" t="n">
-        <v>87.5</v>
+        <v>40.2</v>
       </c>
       <c r="Q83" t="n">
-        <v>35</v>
+        <v>16.1</v>
       </c>
       <c r="R83" t="n">
-        <v>43.8</v>
-      </c>
-      <c r="S83" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+        <v>20.1</v>
+      </c>
+      <c r="S83" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="T83" s="6" t="inlineStr">
@@ -12821,9 +12821,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="W83" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="W83" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="X83" s="6" t="inlineStr">
@@ -12831,9 +12831,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="Y83" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="Y83" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Z83" s="6" t="inlineStr">
@@ -12878,12 +12878,12 @@
       </c>
       <c r="AH83" t="inlineStr">
         <is>
-          <t>B200 SXM</t>
+          <t>RTX PRO 6000</t>
         </is>
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>RTX PRO 6000</t>
+          <t>H100 SXM</t>
         </is>
       </c>
     </row>
@@ -12897,13 +12897,13 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>1304.87</v>
+        <v>1304.84</v>
       </c>
       <c r="D84" t="n">
-        <v>1300.47</v>
+        <v>1300.44</v>
       </c>
       <c r="E84" t="n">
-        <v>1309.27</v>
+        <v>1309.24</v>
       </c>
       <c r="F84" t="n">
         <v>28073</v>
@@ -13048,13 +13048,13 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>1302.91</v>
+        <v>1302.83</v>
       </c>
       <c r="D85" t="n">
-        <v>1293.59</v>
+        <v>1293.51</v>
       </c>
       <c r="E85" t="n">
-        <v>1312.23</v>
+        <v>1312.15</v>
       </c>
       <c r="F85" t="n">
         <v>4171</v>
@@ -13199,16 +13199,16 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>1302.9</v>
+        <v>1302.78</v>
       </c>
       <c r="D86" t="n">
-        <v>1298.42</v>
+        <v>1298.29</v>
       </c>
       <c r="E86" t="n">
-        <v>1307.38</v>
+        <v>1307.27</v>
       </c>
       <c r="F86" t="n">
-        <v>33731</v>
+        <v>33485</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -13350,10 +13350,10 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>1302.47</v>
+        <v>1302.46</v>
       </c>
       <c r="D87" t="n">
-        <v>1298.43</v>
+        <v>1298.42</v>
       </c>
       <c r="E87" t="n">
         <v>1306.5</v>
@@ -13501,13 +13501,13 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>1298.52</v>
+        <v>1298.48</v>
       </c>
       <c r="D88" t="n">
-        <v>1290.77</v>
+        <v>1290.72</v>
       </c>
       <c r="E88" t="n">
-        <v>1306.28</v>
+        <v>1306.23</v>
       </c>
       <c r="F88" t="n">
         <v>7140</v>
@@ -13652,13 +13652,13 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>1293.02</v>
+        <v>1292.97</v>
       </c>
       <c r="D89" t="n">
-        <v>1289.32</v>
+        <v>1289.26</v>
       </c>
       <c r="E89" t="n">
-        <v>1296.72</v>
+        <v>1296.67</v>
       </c>
       <c r="F89" t="n">
         <v>55240</v>
@@ -13954,13 +13954,13 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>1287.76</v>
+        <v>1287.74</v>
       </c>
       <c r="D91" t="n">
-        <v>1284.42</v>
+        <v>1284.4</v>
       </c>
       <c r="E91" t="n">
-        <v>1291.1</v>
+        <v>1291.09</v>
       </c>
       <c r="F91" t="n">
         <v>75754</v>
@@ -14105,16 +14105,16 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>1287.41</v>
+        <v>1286.98</v>
       </c>
       <c r="D92" t="n">
-        <v>1279.09</v>
+        <v>1278.64</v>
       </c>
       <c r="E92" t="n">
-        <v>1295.72</v>
+        <v>1295.32</v>
       </c>
       <c r="F92" t="n">
-        <v>5783</v>
+        <v>5748</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -14256,13 +14256,13 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>1286.08</v>
+        <v>1286.02</v>
       </c>
       <c r="D93" t="n">
-        <v>1275.61</v>
+        <v>1275.54</v>
       </c>
       <c r="E93" t="n">
-        <v>1296.56</v>
+        <v>1296.49</v>
       </c>
       <c r="F93" t="n">
         <v>2846</v>
@@ -14403,36 +14403,36 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>olmo-3.1-32b-think</t>
+          <t>llama-3.1-nemotron-51b-instruct</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1285.88</v>
+        <v>1285.6</v>
       </c>
       <c r="D94" t="n">
-        <v>1278.65</v>
+        <v>1275.63</v>
       </c>
       <c r="E94" t="n">
-        <v>1293.1</v>
+        <v>1295.58</v>
       </c>
       <c r="F94" t="n">
-        <v>8575</v>
+        <v>3749</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Ai2</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
+          <t>Llama 3.1</t>
         </is>
       </c>
       <c r="I94" t="n">
-        <v>32.2</v>
+        <v>51</v>
       </c>
       <c r="J94" t="n">
-        <v>32.2</v>
+        <v>51</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
@@ -14441,30 +14441,30 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>artificial_analysis</t>
+          <t>name_parsing</t>
         </is>
       </c>
       <c r="M94" t="n">
-        <v>64.40000000000001</v>
+        <v>102</v>
       </c>
       <c r="N94" t="n">
-        <v>80.5</v>
+        <v>127.5</v>
       </c>
       <c r="O94" t="n">
-        <v>32.2</v>
+        <v>51</v>
       </c>
       <c r="P94" t="n">
-        <v>40.2</v>
+        <v>63.8</v>
       </c>
       <c r="Q94" t="n">
-        <v>16.1</v>
+        <v>25.5</v>
       </c>
       <c r="R94" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="S94" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+        <v>31.9</v>
+      </c>
+      <c r="S94" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="T94" s="6" t="inlineStr">
@@ -14539,7 +14539,7 @@
       </c>
       <c r="AH94" t="inlineStr">
         <is>
-          <t>RTX PRO 6000</t>
+          <t>H200 SXM</t>
         </is>
       </c>
       <c r="AI94" t="inlineStr">
@@ -14554,36 +14554,36 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>llama-3.1-nemotron-51b-instruct</t>
+          <t>olmo-3.1-32b-think</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1285.65</v>
+        <v>1285.52</v>
       </c>
       <c r="D95" t="n">
-        <v>1275.67</v>
+        <v>1278.29</v>
       </c>
       <c r="E95" t="n">
-        <v>1295.62</v>
+        <v>1292.75</v>
       </c>
       <c r="F95" t="n">
-        <v>3749</v>
+        <v>8544</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Ai2</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Llama 3.1</t>
+          <t>Apache 2.0</t>
         </is>
       </c>
       <c r="I95" t="n">
-        <v>51</v>
+        <v>32.2</v>
       </c>
       <c r="J95" t="n">
-        <v>51</v>
+        <v>32.2</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
@@ -14592,30 +14592,30 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>artificial_analysis</t>
         </is>
       </c>
       <c r="M95" t="n">
-        <v>102</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="N95" t="n">
-        <v>127.5</v>
+        <v>80.5</v>
       </c>
       <c r="O95" t="n">
-        <v>51</v>
+        <v>32.2</v>
       </c>
       <c r="P95" t="n">
-        <v>63.8</v>
+        <v>40.2</v>
       </c>
       <c r="Q95" t="n">
-        <v>25.5</v>
+        <v>16.1</v>
       </c>
       <c r="R95" t="n">
-        <v>31.9</v>
-      </c>
-      <c r="S95" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+        <v>20.1</v>
+      </c>
+      <c r="S95" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="T95" s="6" t="inlineStr">
@@ -14690,7 +14690,7 @@
       </c>
       <c r="AH95" t="inlineStr">
         <is>
-          <t>H200 SXM</t>
+          <t>RTX PRO 6000</t>
         </is>
       </c>
       <c r="AI95" t="inlineStr">
@@ -14709,13 +14709,13 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>1279.01</v>
+        <v>1278.99</v>
       </c>
       <c r="D96" t="n">
-        <v>1272.16</v>
+        <v>1272.13</v>
       </c>
       <c r="E96" t="n">
-        <v>1285.87</v>
+        <v>1285.85</v>
       </c>
       <c r="F96" t="n">
         <v>10072</v>
@@ -14860,13 +14860,13 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1276.65</v>
+        <v>1276.58</v>
       </c>
       <c r="D97" t="n">
-        <v>1271.33</v>
+        <v>1271.25</v>
       </c>
       <c r="E97" t="n">
-        <v>1281.97</v>
+        <v>1281.9</v>
       </c>
       <c r="F97" t="n">
         <v>19659</v>
@@ -15011,13 +15011,13 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>1275.86</v>
+        <v>1275.8</v>
       </c>
       <c r="D98" t="n">
-        <v>1269.3</v>
+        <v>1269.23</v>
       </c>
       <c r="E98" t="n">
-        <v>1282.43</v>
+        <v>1282.36</v>
       </c>
       <c r="F98" t="n">
         <v>9866</v>
@@ -15162,13 +15162,13 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>1275.47</v>
+        <v>1275.42</v>
       </c>
       <c r="D99" t="n">
-        <v>1271.9</v>
+        <v>1271.85</v>
       </c>
       <c r="E99" t="n">
-        <v>1279.04</v>
+        <v>1278.99</v>
       </c>
       <c r="F99" t="n">
         <v>156876</v>
@@ -15313,13 +15313,13 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>1273.66</v>
+        <v>1273.63</v>
       </c>
       <c r="D100" t="n">
-        <v>1267.78</v>
+        <v>1267.75</v>
       </c>
       <c r="E100" t="n">
-        <v>1279.54</v>
+        <v>1279.52</v>
       </c>
       <c r="F100" t="n">
         <v>14681</v>
@@ -15464,13 +15464,13 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1270.13</v>
+        <v>1270.12</v>
       </c>
       <c r="D101" t="n">
-        <v>1262.02</v>
+        <v>1262</v>
       </c>
       <c r="E101" t="n">
-        <v>1278.25</v>
+        <v>1278.24</v>
       </c>
       <c r="F101" t="n">
         <v>5432</v>
@@ -15615,13 +15615,13 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>1266.53</v>
+        <v>1266.48</v>
       </c>
       <c r="D102" t="n">
-        <v>1261.67</v>
+        <v>1261.62</v>
       </c>
       <c r="E102" t="n">
-        <v>1271.38</v>
+        <v>1271.34</v>
       </c>
       <c r="F102" t="n">
         <v>27124</v>
@@ -15766,13 +15766,13 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>1265.22</v>
+        <v>1265.21</v>
       </c>
       <c r="D103" t="n">
-        <v>1261.44</v>
+        <v>1261.42</v>
       </c>
       <c r="E103" t="n">
-        <v>1269.01</v>
+        <v>1268.99</v>
       </c>
       <c r="F103" t="n">
         <v>54611</v>
@@ -15923,7 +15923,7 @@
         <v>1257.42</v>
       </c>
       <c r="E104" t="n">
-        <v>1269.98</v>
+        <v>1269.97</v>
       </c>
       <c r="F104" t="n">
         <v>15147</v>
@@ -16068,13 +16068,13 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>1261.18</v>
+        <v>1261.12</v>
       </c>
       <c r="D105" t="n">
-        <v>1256.86</v>
+        <v>1256.8</v>
       </c>
       <c r="E105" t="n">
-        <v>1265.49</v>
+        <v>1265.43</v>
       </c>
       <c r="F105" t="n">
         <v>77554</v>
@@ -16219,13 +16219,13 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>1261.13</v>
+        <v>1261.08</v>
       </c>
       <c r="D106" t="n">
-        <v>1256.2</v>
+        <v>1256.14</v>
       </c>
       <c r="E106" t="n">
-        <v>1266.06</v>
+        <v>1266.01</v>
       </c>
       <c r="F106" t="n">
         <v>37325</v>
@@ -16370,13 +16370,13 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>1255.68</v>
+        <v>1255.63</v>
       </c>
       <c r="D107" t="n">
-        <v>1251.11</v>
+        <v>1251.06</v>
       </c>
       <c r="E107" t="n">
-        <v>1260.24</v>
+        <v>1260.19</v>
       </c>
       <c r="F107" t="n">
         <v>24126</v>
@@ -16521,13 +16521,13 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>1251.5</v>
+        <v>1251.41</v>
       </c>
       <c r="D108" t="n">
-        <v>1240.71</v>
+        <v>1240.62</v>
       </c>
       <c r="E108" t="n">
-        <v>1262.29</v>
+        <v>1262.2</v>
       </c>
       <c r="F108" t="n">
         <v>3334</v>
@@ -16672,13 +16672,13 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>1249.47</v>
+        <v>1249.43</v>
       </c>
       <c r="D109" t="n">
-        <v>1242.88</v>
+        <v>1242.84</v>
       </c>
       <c r="E109" t="n">
-        <v>1256.06</v>
+        <v>1256.02</v>
       </c>
       <c r="F109" t="n">
         <v>10140</v>
@@ -16823,13 +16823,13 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>1238.58</v>
+        <v>1238.57</v>
       </c>
       <c r="D110" t="n">
-        <v>1231.37</v>
+        <v>1231.35</v>
       </c>
       <c r="E110" t="n">
-        <v>1245.8</v>
+        <v>1245.79</v>
       </c>
       <c r="F110" t="n">
         <v>8858</v>
@@ -16977,10 +16977,10 @@
         <v>1236.78</v>
       </c>
       <c r="D111" t="n">
-        <v>1227.69</v>
+        <v>1227.68</v>
       </c>
       <c r="E111" t="n">
-        <v>1245.88</v>
+        <v>1245.87</v>
       </c>
       <c r="F111" t="n">
         <v>4781</v>
@@ -17125,13 +17125,13 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>1233.37</v>
+        <v>1233.32</v>
       </c>
       <c r="D112" t="n">
-        <v>1227.82</v>
+        <v>1227.77</v>
       </c>
       <c r="E112" t="n">
-        <v>1238.92</v>
+        <v>1238.88</v>
       </c>
       <c r="F112" t="n">
         <v>26195</v>
@@ -17276,13 +17276,13 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>1232.45</v>
+        <v>1232.4</v>
       </c>
       <c r="D113" t="n">
-        <v>1227.17</v>
+        <v>1227.12</v>
       </c>
       <c r="E113" t="n">
-        <v>1237.72</v>
+        <v>1237.68</v>
       </c>
       <c r="F113" t="n">
         <v>39302</v>
@@ -17427,13 +17427,13 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>1228.68</v>
+        <v>1228.63</v>
       </c>
       <c r="D114" t="n">
-        <v>1224.13</v>
+        <v>1224.08</v>
       </c>
       <c r="E114" t="n">
-        <v>1233.23</v>
+        <v>1233.18</v>
       </c>
       <c r="F114" t="n">
         <v>51416</v>
@@ -17578,13 +17578,13 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>1226.17</v>
+        <v>1226.11</v>
       </c>
       <c r="D115" t="n">
-        <v>1221.39</v>
+        <v>1221.33</v>
       </c>
       <c r="E115" t="n">
-        <v>1230.95</v>
+        <v>1230.89</v>
       </c>
       <c r="F115" t="n">
         <v>54036</v>
@@ -17729,13 +17729,13 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>1222.56</v>
+        <v>1222.5</v>
       </c>
       <c r="D116" t="n">
-        <v>1218.84</v>
+        <v>1218.78</v>
       </c>
       <c r="E116" t="n">
-        <v>1226.28</v>
+        <v>1226.23</v>
       </c>
       <c r="F116" t="n">
         <v>104642</v>
@@ -17880,13 +17880,13 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>1222.47</v>
+        <v>1222.42</v>
       </c>
       <c r="D117" t="n">
-        <v>1215.51</v>
+        <v>1215.46</v>
       </c>
       <c r="E117" t="n">
-        <v>1229.43</v>
+        <v>1229.37</v>
       </c>
       <c r="F117" t="n">
         <v>9818</v>
@@ -18031,13 +18031,13 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>1220.6</v>
+        <v>1220.54</v>
       </c>
       <c r="D118" t="n">
-        <v>1209.91</v>
+        <v>1209.85</v>
       </c>
       <c r="E118" t="n">
-        <v>1231.29</v>
+        <v>1231.23</v>
       </c>
       <c r="F118" t="n">
         <v>2896</v>
@@ -18182,13 +18182,13 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>1212.77</v>
+        <v>1212.69</v>
       </c>
       <c r="D119" t="n">
-        <v>1207.73</v>
+        <v>1207.66</v>
       </c>
       <c r="E119" t="n">
-        <v>1217.8</v>
+        <v>1217.73</v>
       </c>
       <c r="F119" t="n">
         <v>24146</v>
@@ -18333,13 +18333,13 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>1211.97</v>
+        <v>1211.92</v>
       </c>
       <c r="D120" t="n">
-        <v>1201.16</v>
+        <v>1201.11</v>
       </c>
       <c r="E120" t="n">
-        <v>1222.78</v>
+        <v>1222.73</v>
       </c>
       <c r="F120" t="n">
         <v>4652</v>
@@ -18484,13 +18484,13 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>1211.19</v>
+        <v>1211.15</v>
       </c>
       <c r="D121" t="n">
-        <v>1207.08</v>
+        <v>1207.03</v>
       </c>
       <c r="E121" t="n">
-        <v>1215.31</v>
+        <v>1215.27</v>
       </c>
       <c r="F121" t="n">
         <v>49605</v>
@@ -18635,13 +18635,13 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>1207.73</v>
+        <v>1207.67</v>
       </c>
       <c r="D122" t="n">
-        <v>1196.61</v>
+        <v>1196.56</v>
       </c>
       <c r="E122" t="n">
-        <v>1218.84</v>
+        <v>1218.79</v>
       </c>
       <c r="F122" t="n">
         <v>3090</v>
@@ -18786,13 +18786,13 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>1203.09</v>
+        <v>1203.04</v>
       </c>
       <c r="D123" t="n">
-        <v>1196.97</v>
+        <v>1196.91</v>
       </c>
       <c r="E123" t="n">
-        <v>1209.21</v>
+        <v>1209.16</v>
       </c>
       <c r="F123" t="n">
         <v>21741</v>
@@ -18937,13 +18937,13 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>1198.66</v>
+        <v>1198.63</v>
       </c>
       <c r="D124" t="n">
-        <v>1194.6</v>
+        <v>1194.56</v>
       </c>
       <c r="E124" t="n">
-        <v>1202.72</v>
+        <v>1202.69</v>
       </c>
       <c r="F124" t="n">
         <v>46616</v>
@@ -19088,13 +19088,13 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>1197.21</v>
+        <v>1197.15</v>
       </c>
       <c r="D125" t="n">
-        <v>1192.06</v>
+        <v>1192</v>
       </c>
       <c r="E125" t="n">
-        <v>1202.36</v>
+        <v>1202.31</v>
       </c>
       <c r="F125" t="n">
         <v>25055</v>
@@ -19239,13 +19239,13 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>1196.37</v>
+        <v>1196.31</v>
       </c>
       <c r="D126" t="n">
-        <v>1192.1</v>
+        <v>1192.04</v>
       </c>
       <c r="E126" t="n">
-        <v>1200.63</v>
+        <v>1200.58</v>
       </c>
       <c r="F126" t="n">
         <v>73503</v>
@@ -19390,13 +19390,13 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>1194.28</v>
+        <v>1194.24</v>
       </c>
       <c r="D127" t="n">
-        <v>1188.16</v>
+        <v>1188.13</v>
       </c>
       <c r="E127" t="n">
-        <v>1200.39</v>
+        <v>1200.36</v>
       </c>
       <c r="F127" t="n">
         <v>32191</v>
@@ -19541,13 +19541,13 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>1190.75</v>
+        <v>1190.67</v>
       </c>
       <c r="D128" t="n">
-        <v>1183.58</v>
+        <v>1183.49</v>
       </c>
       <c r="E128" t="n">
-        <v>1197.93</v>
+        <v>1197.84</v>
       </c>
       <c r="F128" t="n">
         <v>9901</v>
@@ -19692,13 +19692,13 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>1190.19</v>
+        <v>1190.13</v>
       </c>
       <c r="D129" t="n">
-        <v>1183.06</v>
+        <v>1183</v>
       </c>
       <c r="E129" t="n">
-        <v>1197.31</v>
+        <v>1197.26</v>
       </c>
       <c r="F129" t="n">
         <v>17839</v>
@@ -19843,13 +19843,13 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>1183.88</v>
+        <v>1183.82</v>
       </c>
       <c r="D130" t="n">
-        <v>1174.42</v>
+        <v>1174.36</v>
       </c>
       <c r="E130" t="n">
-        <v>1193.34</v>
+        <v>1193.28</v>
       </c>
       <c r="F130" t="n">
         <v>8214</v>
@@ -19994,13 +19994,13 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>1183.6</v>
+        <v>1183.57</v>
       </c>
       <c r="D131" t="n">
-        <v>1172.08</v>
+        <v>1172.05</v>
       </c>
       <c r="E131" t="n">
-        <v>1195.12</v>
+        <v>1195.09</v>
       </c>
       <c r="F131" t="n">
         <v>4932</v>
@@ -20145,13 +20145,13 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>1183.11</v>
+        <v>1183.04</v>
       </c>
       <c r="D132" t="n">
-        <v>1176.28</v>
+        <v>1176.21</v>
       </c>
       <c r="E132" t="n">
-        <v>1189.94</v>
+        <v>1189.87</v>
       </c>
       <c r="F132" t="n">
         <v>15483</v>
@@ -20296,13 +20296,13 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>1181.47</v>
+        <v>1181.43</v>
       </c>
       <c r="D133" t="n">
-        <v>1173.46</v>
+        <v>1173.43</v>
       </c>
       <c r="E133" t="n">
-        <v>1189.47</v>
+        <v>1189.44</v>
       </c>
       <c r="F133" t="n">
         <v>12637</v>
@@ -20367,13 +20367,13 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>1181.4</v>
+        <v>1181.38</v>
       </c>
       <c r="D134" t="n">
-        <v>1171.72</v>
+        <v>1171.7</v>
       </c>
       <c r="E134" t="n">
-        <v>1191.08</v>
+        <v>1191.07</v>
       </c>
       <c r="F134" t="n">
         <v>7968</v>
@@ -20438,10 +20438,10 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>1181.3</v>
+        <v>1181.29</v>
       </c>
       <c r="D135" t="n">
-        <v>1172.61</v>
+        <v>1172.6</v>
       </c>
       <c r="E135" t="n">
         <v>1189.98</v>
@@ -20589,13 +20589,13 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>1179.83</v>
+        <v>1179.85</v>
       </c>
       <c r="D136" t="n">
-        <v>1173.75</v>
+        <v>1173.78</v>
       </c>
       <c r="E136" t="n">
-        <v>1185.9</v>
+        <v>1185.93</v>
       </c>
       <c r="F136" t="n">
         <v>23893</v>
@@ -20740,13 +20740,13 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>1178.69</v>
+        <v>1178.66</v>
       </c>
       <c r="D137" t="n">
-        <v>1172.77</v>
+        <v>1172.74</v>
       </c>
       <c r="E137" t="n">
-        <v>1184.6</v>
+        <v>1184.57</v>
       </c>
       <c r="F137" t="n">
         <v>32832</v>
@@ -20811,13 +20811,13 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>1178.27</v>
+        <v>1178.21</v>
       </c>
       <c r="D138" t="n">
-        <v>1167.06</v>
+        <v>1167</v>
       </c>
       <c r="E138" t="n">
-        <v>1189.48</v>
+        <v>1189.42</v>
       </c>
       <c r="F138" t="n">
         <v>3188</v>
@@ -20962,13 +20962,13 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>1177.23</v>
+        <v>1177.16</v>
       </c>
       <c r="D139" t="n">
-        <v>1167.41</v>
+        <v>1167.34</v>
       </c>
       <c r="E139" t="n">
-        <v>1187.06</v>
+        <v>1186.99</v>
       </c>
       <c r="F139" t="n">
         <v>6535</v>
@@ -21113,13 +21113,13 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>1174.38</v>
+        <v>1174.35</v>
       </c>
       <c r="D140" t="n">
-        <v>1163.95</v>
+        <v>1163.93</v>
       </c>
       <c r="E140" t="n">
-        <v>1184.81</v>
+        <v>1184.78</v>
       </c>
       <c r="F140" t="n">
         <v>5006</v>
@@ -21264,13 +21264,13 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>1171.98</v>
+        <v>1171.93</v>
       </c>
       <c r="D141" t="n">
-        <v>1165.77</v>
+        <v>1165.71</v>
       </c>
       <c r="E141" t="n">
-        <v>1178.19</v>
+        <v>1178.14</v>
       </c>
       <c r="F141" t="n">
         <v>22479</v>
@@ -21415,13 +21415,13 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>1170.9</v>
+        <v>1170.79</v>
       </c>
       <c r="D142" t="n">
-        <v>1163.48</v>
+        <v>1163.38</v>
       </c>
       <c r="E142" t="n">
-        <v>1178.31</v>
+        <v>1178.21</v>
       </c>
       <c r="F142" t="n">
         <v>16056</v>
@@ -21566,13 +21566,13 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>1170.35</v>
+        <v>1170.29</v>
       </c>
       <c r="D143" t="n">
-        <v>1164.43</v>
+        <v>1164.37</v>
       </c>
       <c r="E143" t="n">
-        <v>1176.26</v>
+        <v>1176.2</v>
       </c>
       <c r="F143" t="n">
         <v>17766</v>
@@ -21717,13 +21717,13 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>1170.02</v>
+        <v>1169.94</v>
       </c>
       <c r="D144" t="n">
-        <v>1164.51</v>
+        <v>1164.44</v>
       </c>
       <c r="E144" t="n">
-        <v>1175.52</v>
+        <v>1175.45</v>
       </c>
       <c r="F144" t="n">
         <v>38492</v>
@@ -21868,13 +21868,13 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>1166.75</v>
+        <v>1166.68</v>
       </c>
       <c r="D145" t="n">
-        <v>1158.67</v>
+        <v>1158.61</v>
       </c>
       <c r="E145" t="n">
-        <v>1174.82</v>
+        <v>1174.76</v>
       </c>
       <c r="F145" t="n">
         <v>10224</v>
@@ -22019,13 +22019,13 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>1166.02</v>
+        <v>1165.97</v>
       </c>
       <c r="D146" t="n">
-        <v>1158.33</v>
+        <v>1158.27</v>
       </c>
       <c r="E146" t="n">
-        <v>1173.72</v>
+        <v>1173.67</v>
       </c>
       <c r="F146" t="n">
         <v>7936</v>
@@ -22170,13 +22170,13 @@
         </is>
       </c>
       <c r="C147" t="n">
-        <v>1163.95</v>
+        <v>1163.88</v>
       </c>
       <c r="D147" t="n">
-        <v>1152.01</v>
+        <v>1151.93</v>
       </c>
       <c r="E147" t="n">
-        <v>1175.89</v>
+        <v>1175.82</v>
       </c>
       <c r="F147" t="n">
         <v>3777</v>
@@ -22321,13 +22321,13 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>1156.25</v>
+        <v>1156.1</v>
       </c>
       <c r="D148" t="n">
-        <v>1144.75</v>
+        <v>1144.59</v>
       </c>
       <c r="E148" t="n">
-        <v>1167.76</v>
+        <v>1167.6</v>
       </c>
       <c r="F148" t="n">
         <v>3231</v>
@@ -22472,13 +22472,13 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>1155.28</v>
+        <v>1155.26</v>
       </c>
       <c r="D149" t="n">
-        <v>1146.89</v>
+        <v>1146.86</v>
       </c>
       <c r="E149" t="n">
-        <v>1163.68</v>
+        <v>1163.65</v>
       </c>
       <c r="F149" t="n">
         <v>6837</v>
@@ -22623,13 +22623,13 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>1154.52</v>
+        <v>1154.45</v>
       </c>
       <c r="D150" t="n">
-        <v>1141.9</v>
+        <v>1141.83</v>
       </c>
       <c r="E150" t="n">
-        <v>1167.15</v>
+        <v>1167.08</v>
       </c>
       <c r="F150" t="n">
         <v>3585</v>
@@ -22774,13 +22774,13 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>1151.55</v>
+        <v>1151.5</v>
       </c>
       <c r="D151" t="n">
-        <v>1138.34</v>
+        <v>1138.29</v>
       </c>
       <c r="E151" t="n">
-        <v>1164.77</v>
+        <v>1164.72</v>
       </c>
       <c r="F151" t="n">
         <v>4155</v>
@@ -22925,13 +22925,13 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>1151.2</v>
+        <v>1151.15</v>
       </c>
       <c r="D152" t="n">
-        <v>1135.8</v>
+        <v>1135.75</v>
       </c>
       <c r="E152" t="n">
-        <v>1166.6</v>
+        <v>1166.55</v>
       </c>
       <c r="F152" t="n">
         <v>1679</v>
@@ -23076,13 +23076,13 @@
         </is>
       </c>
       <c r="C153" t="n">
-        <v>1149.28</v>
+        <v>1149.26</v>
       </c>
       <c r="D153" t="n">
-        <v>1136.98</v>
+        <v>1136.95</v>
       </c>
       <c r="E153" t="n">
-        <v>1161.59</v>
+        <v>1161.56</v>
       </c>
       <c r="F153" t="n">
         <v>2572</v>
@@ -23227,13 +23227,13 @@
         </is>
       </c>
       <c r="C154" t="n">
-        <v>1148.81</v>
+        <v>1148.74</v>
       </c>
       <c r="D154" t="n">
-        <v>1142.15</v>
+        <v>1142.08</v>
       </c>
       <c r="E154" t="n">
-        <v>1155.46</v>
+        <v>1155.4</v>
       </c>
       <c r="F154" t="n">
         <v>19402</v>
@@ -23378,13 +23378,13 @@
         </is>
       </c>
       <c r="C155" t="n">
-        <v>1148.4</v>
+        <v>1148.35</v>
       </c>
       <c r="D155" t="n">
-        <v>1139.13</v>
+        <v>1139.09</v>
       </c>
       <c r="E155" t="n">
-        <v>1157.66</v>
+        <v>1157.62</v>
       </c>
       <c r="F155" t="n">
         <v>7044</v>
@@ -23535,7 +23535,7 @@
         <v>1129.09</v>
       </c>
       <c r="E156" t="n">
-        <v>1163.36</v>
+        <v>1163.35</v>
       </c>
       <c r="F156" t="n">
         <v>1295</v>
@@ -23680,13 +23680,13 @@
         </is>
       </c>
       <c r="C157" t="n">
-        <v>1143.03</v>
+        <v>1142.97</v>
       </c>
       <c r="D157" t="n">
-        <v>1133.13</v>
+        <v>1133.07</v>
       </c>
       <c r="E157" t="n">
-        <v>1152.93</v>
+        <v>1152.87</v>
       </c>
       <c r="F157" t="n">
         <v>4737</v>
@@ -23831,13 +23831,13 @@
         </is>
       </c>
       <c r="C158" t="n">
-        <v>1142.33</v>
+        <v>1142.27</v>
       </c>
       <c r="D158" t="n">
-        <v>1135.89</v>
+        <v>1135.84</v>
       </c>
       <c r="E158" t="n">
-        <v>1148.76</v>
+        <v>1148.71</v>
       </c>
       <c r="F158" t="n">
         <v>12297</v>
@@ -23982,13 +23982,13 @@
         </is>
       </c>
       <c r="C159" t="n">
-        <v>1140.72</v>
+        <v>1140.65</v>
       </c>
       <c r="D159" t="n">
-        <v>1133.99</v>
+        <v>1133.92</v>
       </c>
       <c r="E159" t="n">
-        <v>1147.45</v>
+        <v>1147.38</v>
       </c>
       <c r="F159" t="n">
         <v>19174</v>
@@ -24133,13 +24133,13 @@
         </is>
       </c>
       <c r="C160" t="n">
-        <v>1140.1</v>
+        <v>1140.07</v>
       </c>
       <c r="D160" t="n">
-        <v>1133.38</v>
+        <v>1133.36</v>
       </c>
       <c r="E160" t="n">
-        <v>1146.81</v>
+        <v>1146.79</v>
       </c>
       <c r="F160" t="n">
         <v>19367</v>
@@ -24284,13 +24284,13 @@
         </is>
       </c>
       <c r="C161" t="n">
-        <v>1137.76</v>
+        <v>1137.74</v>
       </c>
       <c r="D161" t="n">
-        <v>1126.79</v>
+        <v>1126.77</v>
       </c>
       <c r="E161" t="n">
-        <v>1148.73</v>
+        <v>1148.71</v>
       </c>
       <c r="F161" t="n">
         <v>4964</v>
@@ -24435,13 +24435,13 @@
         </is>
       </c>
       <c r="C162" t="n">
-        <v>1135.76</v>
+        <v>1135.71</v>
       </c>
       <c r="D162" t="n">
-        <v>1126.85</v>
+        <v>1126.8</v>
       </c>
       <c r="E162" t="n">
-        <v>1144.67</v>
+        <v>1144.62</v>
       </c>
       <c r="F162" t="n">
         <v>7366</v>
@@ -24586,10 +24586,10 @@
         </is>
       </c>
       <c r="C163" t="n">
-        <v>1135.54</v>
+        <v>1135.55</v>
       </c>
       <c r="D163" t="n">
-        <v>1126.03</v>
+        <v>1126.04</v>
       </c>
       <c r="E163" t="n">
         <v>1145.05</v>
@@ -24737,13 +24737,13 @@
         </is>
       </c>
       <c r="C164" t="n">
-        <v>1130.23</v>
+        <v>1130.16</v>
       </c>
       <c r="D164" t="n">
-        <v>1121.38</v>
+        <v>1121.31</v>
       </c>
       <c r="E164" t="n">
-        <v>1139.08</v>
+        <v>1139.01</v>
       </c>
       <c r="F164" t="n">
         <v>11118</v>
@@ -24888,13 +24888,13 @@
         </is>
       </c>
       <c r="C165" t="n">
-        <v>1128.43</v>
+        <v>1128.4</v>
       </c>
       <c r="D165" t="n">
-        <v>1121</v>
+        <v>1120.97</v>
       </c>
       <c r="E165" t="n">
-        <v>1135.85</v>
+        <v>1135.82</v>
       </c>
       <c r="F165" t="n">
         <v>20685</v>
@@ -25039,13 +25039,13 @@
         </is>
       </c>
       <c r="C166" t="n">
-        <v>1127.64</v>
+        <v>1127.57</v>
       </c>
       <c r="D166" t="n">
-        <v>1121.24</v>
+        <v>1121.17</v>
       </c>
       <c r="E166" t="n">
-        <v>1134.03</v>
+        <v>1133.97</v>
       </c>
       <c r="F166" t="n">
         <v>20118</v>
@@ -25190,13 +25190,13 @@
         </is>
       </c>
       <c r="C167" t="n">
-        <v>1126.49</v>
+        <v>1126.45</v>
       </c>
       <c r="D167" t="n">
-        <v>1114.33</v>
+        <v>1114.29</v>
       </c>
       <c r="E167" t="n">
-        <v>1138.65</v>
+        <v>1138.61</v>
       </c>
       <c r="F167" t="n">
         <v>2921</v>
@@ -25341,13 +25341,13 @@
         </is>
       </c>
       <c r="C168" t="n">
-        <v>1126.09</v>
+        <v>1126.04</v>
       </c>
       <c r="D168" t="n">
-        <v>1110.41</v>
+        <v>1110.36</v>
       </c>
       <c r="E168" t="n">
-        <v>1141.76</v>
+        <v>1141.71</v>
       </c>
       <c r="F168" t="n">
         <v>1785</v>
@@ -25492,13 +25492,13 @@
         </is>
       </c>
       <c r="C169" t="n">
-        <v>1120.16</v>
+        <v>1120.14</v>
       </c>
       <c r="D169" t="n">
-        <v>1109.16</v>
+        <v>1109.13</v>
       </c>
       <c r="E169" t="n">
-        <v>1131.17</v>
+        <v>1131.14</v>
       </c>
       <c r="F169" t="n">
         <v>5182</v>
@@ -25643,13 +25643,13 @@
         </is>
       </c>
       <c r="C170" t="n">
-        <v>1118.29</v>
+        <v>1118.24</v>
       </c>
       <c r="D170" t="n">
-        <v>1100.08</v>
+        <v>1100.03</v>
       </c>
       <c r="E170" t="n">
-        <v>1136.51</v>
+        <v>1136.45</v>
       </c>
       <c r="F170" t="n">
         <v>1143</v>
@@ -25794,13 +25794,13 @@
         </is>
       </c>
       <c r="C171" t="n">
-        <v>1113.81</v>
+        <v>1113.79</v>
       </c>
       <c r="D171" t="n">
-        <v>1104.63</v>
+        <v>1104.61</v>
       </c>
       <c r="E171" t="n">
-        <v>1123</v>
+        <v>1122.97</v>
       </c>
       <c r="F171" t="n">
         <v>6923</v>
@@ -25945,13 +25945,13 @@
         </is>
       </c>
       <c r="C172" t="n">
-        <v>1113.71</v>
+        <v>1113.73</v>
       </c>
       <c r="D172" t="n">
-        <v>1105.97</v>
+        <v>1106</v>
       </c>
       <c r="E172" t="n">
-        <v>1121.45</v>
+        <v>1121.47</v>
       </c>
       <c r="F172" t="n">
         <v>10854</v>
@@ -26096,13 +26096,13 @@
         </is>
       </c>
       <c r="C173" t="n">
-        <v>1113.56</v>
+        <v>1113.53</v>
       </c>
       <c r="D173" t="n">
-        <v>1099.14</v>
+        <v>1099.11</v>
       </c>
       <c r="E173" t="n">
-        <v>1127.98</v>
+        <v>1127.94</v>
       </c>
       <c r="F173" t="n">
         <v>2199</v>
@@ -26247,13 +26247,13 @@
         </is>
       </c>
       <c r="C174" t="n">
-        <v>1110.58</v>
+        <v>1110.52</v>
       </c>
       <c r="D174" t="n">
-        <v>1102.7</v>
+        <v>1102.64</v>
       </c>
       <c r="E174" t="n">
-        <v>1118.45</v>
+        <v>1118.4</v>
       </c>
       <c r="F174" t="n">
         <v>8045</v>
@@ -26398,13 +26398,13 @@
         </is>
       </c>
       <c r="C175" t="n">
-        <v>1108.79</v>
+        <v>1108.77</v>
       </c>
       <c r="D175" t="n">
-        <v>1099.49</v>
+        <v>1099.47</v>
       </c>
       <c r="E175" t="n">
-        <v>1118.09</v>
+        <v>1118.07</v>
       </c>
       <c r="F175" t="n">
         <v>8977</v>
@@ -26549,13 +26549,13 @@
         </is>
       </c>
       <c r="C176" t="n">
-        <v>1107.36</v>
+        <v>1107.28</v>
       </c>
       <c r="D176" t="n">
-        <v>1100.3</v>
+        <v>1100.22</v>
       </c>
       <c r="E176" t="n">
-        <v>1114.42</v>
+        <v>1114.34</v>
       </c>
       <c r="F176" t="n">
         <v>14148</v>
@@ -26700,13 +26700,13 @@
         </is>
       </c>
       <c r="C177" t="n">
-        <v>1091.14</v>
+        <v>1091.15</v>
       </c>
       <c r="D177" t="n">
-        <v>1079.62</v>
+        <v>1079.64</v>
       </c>
       <c r="E177" t="n">
-        <v>1102.65</v>
+        <v>1102.67</v>
       </c>
       <c r="F177" t="n">
         <v>4780</v>
@@ -26854,10 +26854,10 @@
         <v>1089.35</v>
       </c>
       <c r="D178" t="n">
-        <v>1080</v>
+        <v>1079.99</v>
       </c>
       <c r="E178" t="n">
-        <v>1098.71</v>
+        <v>1098.7</v>
       </c>
       <c r="F178" t="n">
         <v>7597</v>
@@ -27002,13 +27002,13 @@
         </is>
       </c>
       <c r="C179" t="n">
-        <v>1073.77</v>
+        <v>1073.67</v>
       </c>
       <c r="D179" t="n">
-        <v>1062.58</v>
+        <v>1062.48</v>
       </c>
       <c r="E179" t="n">
-        <v>1084.96</v>
+        <v>1084.86</v>
       </c>
       <c r="F179" t="n">
         <v>6328</v>
@@ -27153,13 +27153,13 @@
         </is>
       </c>
       <c r="C180" t="n">
-        <v>1069.58</v>
+        <v>1069.55</v>
       </c>
       <c r="D180" t="n">
-        <v>1059.63</v>
+        <v>1059.6</v>
       </c>
       <c r="E180" t="n">
-        <v>1079.53</v>
+        <v>1079.5</v>
       </c>
       <c r="F180" t="n">
         <v>6965</v>
@@ -27304,13 +27304,13 @@
         </is>
       </c>
       <c r="C181" t="n">
-        <v>1066.61</v>
+        <v>1066.69</v>
       </c>
       <c r="D181" t="n">
-        <v>1055.09</v>
+        <v>1055.16</v>
       </c>
       <c r="E181" t="n">
-        <v>1078.14</v>
+        <v>1078.21</v>
       </c>
       <c r="F181" t="n">
         <v>5745</v>
@@ -27455,13 +27455,13 @@
         </is>
       </c>
       <c r="C182" t="n">
-        <v>1065.14</v>
+        <v>1065.16</v>
       </c>
       <c r="D182" t="n">
-        <v>1049.85</v>
+        <v>1049.87</v>
       </c>
       <c r="E182" t="n">
-        <v>1080.43</v>
+        <v>1080.45</v>
       </c>
       <c r="F182" t="n">
         <v>1743</v>
@@ -27606,13 +27606,13 @@
         </is>
       </c>
       <c r="C183" t="n">
-        <v>1060.99</v>
+        <v>1061</v>
       </c>
       <c r="D183" t="n">
-        <v>1048.95</v>
+        <v>1048.97</v>
       </c>
       <c r="E183" t="n">
-        <v>1073.02</v>
+        <v>1073.04</v>
       </c>
       <c r="F183" t="n">
         <v>3924</v>
@@ -27757,13 +27757,13 @@
         </is>
       </c>
       <c r="C184" t="n">
-        <v>1055.2</v>
+        <v>1055.18</v>
       </c>
       <c r="D184" t="n">
-        <v>1043.51</v>
+        <v>1043.49</v>
       </c>
       <c r="E184" t="n">
-        <v>1066.89</v>
+        <v>1066.87</v>
       </c>
       <c r="F184" t="n">
         <v>4658</v>
@@ -27908,13 +27908,13 @@
         </is>
       </c>
       <c r="C185" t="n">
-        <v>1040.47</v>
+        <v>1040.46</v>
       </c>
       <c r="D185" t="n">
-        <v>1029.01</v>
+        <v>1029</v>
       </c>
       <c r="E185" t="n">
-        <v>1051.92</v>
+        <v>1051.91</v>
       </c>
       <c r="F185" t="n">
         <v>4845</v>
@@ -28059,13 +28059,13 @@
         </is>
       </c>
       <c r="C186" t="n">
-        <v>1023.31</v>
+        <v>1023.29</v>
       </c>
       <c r="D186" t="n">
-        <v>1009.67</v>
+        <v>1009.65</v>
       </c>
       <c r="E186" t="n">
-        <v>1036.95</v>
+        <v>1036.93</v>
       </c>
       <c r="F186" t="n">
         <v>2658</v>
@@ -28210,13 +28210,13 @@
         </is>
       </c>
       <c r="C187" t="n">
-        <v>1021.21</v>
+        <v>1021.23</v>
       </c>
       <c r="D187" t="n">
-        <v>1010.28</v>
+        <v>1010.3</v>
       </c>
       <c r="E187" t="n">
-        <v>1032.15</v>
+        <v>1032.16</v>
       </c>
       <c r="F187" t="n">
         <v>6310</v>
@@ -28361,13 +28361,13 @@
         </is>
       </c>
       <c r="C188" t="n">
-        <v>994.7190000000001</v>
+        <v>994.677</v>
       </c>
       <c r="D188" t="n">
-        <v>982.0890000000001</v>
+        <v>982.049</v>
       </c>
       <c r="E188" t="n">
-        <v>1007.35</v>
+        <v>1007.31</v>
       </c>
       <c r="F188" t="n">
         <v>4914</v>
@@ -28512,13 +28512,13 @@
         </is>
       </c>
       <c r="C189" t="n">
-        <v>990.477</v>
+        <v>990.473</v>
       </c>
       <c r="D189" t="n">
-        <v>978.0359999999999</v>
+        <v>978.033</v>
       </c>
       <c r="E189" t="n">
-        <v>1002.92</v>
+        <v>1002.91</v>
       </c>
       <c r="F189" t="n">
         <v>4203</v>
@@ -28663,13 +28663,13 @@
         </is>
       </c>
       <c r="C190" t="n">
-        <v>979.252</v>
+        <v>979.307</v>
       </c>
       <c r="D190" t="n">
-        <v>965.633</v>
+        <v>965.691</v>
       </c>
       <c r="E190" t="n">
-        <v>992.87</v>
+        <v>992.924</v>
       </c>
       <c r="F190" t="n">
         <v>3412</v>
@@ -28814,13 +28814,13 @@
         </is>
       </c>
       <c r="C191" t="n">
-        <v>971.349</v>
+        <v>971.422</v>
       </c>
       <c r="D191" t="n">
-        <v>955.4299999999999</v>
+        <v>955.5069999999999</v>
       </c>
       <c r="E191" t="n">
-        <v>987.269</v>
+        <v>987.338</v>
       </c>
       <c r="F191" t="n">
         <v>2391</v>
@@ -28965,13 +28965,13 @@
         </is>
       </c>
       <c r="C192" t="n">
-        <v>951.751</v>
+        <v>951.724</v>
       </c>
       <c r="D192" t="n">
-        <v>938.928</v>
+        <v>938.904</v>
       </c>
       <c r="E192" t="n">
-        <v>964.574</v>
+        <v>964.545</v>
       </c>
       <c r="F192" t="n">
         <v>3287</v>
@@ -29190,7 +29190,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -29225,7 +29225,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -29260,7 +29260,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -29295,7 +29295,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -29330,7 +29330,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -29369,7 +29369,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -29404,7 +29404,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -29439,7 +29439,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -29474,7 +29474,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -29509,7 +29509,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -29544,7 +29544,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -29614,7 +29614,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -29649,7 +29649,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -30080,14 +30080,14 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>kimi-k2-0905-preview</t>
+          <t>qwen3.5-122b-a10b</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1000</v>
+        <v>125</v>
       </c>
       <c r="C16" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -30096,21 +30096,21 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>artificial_analysis</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>qwen3.5-122b-a10b</t>
+          <t>kimi-k2-0905-preview</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>125</v>
+        <v>1000</v>
       </c>
       <c r="C17" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -30119,7 +30119,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>artificial_analysis</t>
+          <t>override</t>
         </is>
       </c>
     </row>
@@ -30195,14 +30195,14 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>mistral-large-3</t>
+          <t>qwen3-vl-235b-a22b-instruct</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>675</v>
+        <v>235</v>
       </c>
       <c r="C21" t="n">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -30218,14 +30218,14 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>deepseek-v3.1-terminus</t>
+          <t>mistral-large-3</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>685</v>
+        <v>675</v>
       </c>
       <c r="C22" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -30241,14 +30241,14 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>qwen3-vl-235b-a22b-instruct</t>
+          <t>deepseek-v3.1-terminus</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>235</v>
+        <v>685</v>
       </c>
       <c r="C23" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -30287,18 +30287,18 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>qwen3.5-27b</t>
+          <t>minimax-m2.5</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>27.8</v>
+        <v>230</v>
       </c>
       <c r="C25" t="n">
-        <v>27.8</v>
+        <v>10</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>dense</t>
+          <t>moe</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -30310,18 +30310,18 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>minimax-m2.5</t>
+          <t>qwen3.5-27b</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>230</v>
+        <v>27.8</v>
       </c>
       <c r="C26" t="n">
-        <v>10</v>
+        <v>27.8</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>moe</t>
+          <t>dense</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -30356,11 +30356,11 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>qwen3-next-80b-a3b-instruct</t>
+          <t>qwen3.5-35b-a3b</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>80</v>
+        <v>36</v>
       </c>
       <c r="C28" t="n">
         <v>3</v>
@@ -30379,11 +30379,11 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>qwen3.5-35b-a3b</t>
+          <t>qwen3-next-80b-a3b-instruct</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="C29" t="n">
         <v>3</v>
@@ -30563,14 +30563,14 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>mimo-v2-flash (thinking)</t>
+          <t>qwen3-coder-480b-a35b-instruct</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>309</v>
+        <v>480</v>
       </c>
       <c r="C37" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -30586,14 +30586,14 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>qwen3-coder-480b-a35b-instruct</t>
+          <t>mimo-v2-flash (thinking)</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>480</v>
+        <v>309</v>
       </c>
       <c r="C38" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -31015,18 +31015,18 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>minimax-m2</t>
+          <t>qwen3-32b</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>230</v>
+        <v>32.8</v>
       </c>
       <c r="C57" t="n">
-        <v>10</v>
+        <v>32.8</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>moe</t>
+          <t>dense</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -31038,14 +31038,14 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>qwen3-32b</t>
+          <t>llama-3.1-nemotron-ultra-253b-v1</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>32.8</v>
+        <v>253</v>
       </c>
       <c r="C58" t="n">
-        <v>32.8</v>
+        <v>253</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -31061,18 +31061,18 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>llama-3.1-nemotron-ultra-253b-v1</t>
+          <t>minimax-m2</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>253</v>
+        <v>230</v>
       </c>
       <c r="C59" t="n">
-        <v>253</v>
+        <v>10</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>dense</t>
+          <t>moe</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -31406,60 +31406,60 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>gemma-3n-e4b-it</t>
+          <t>llama-3.3-70b-instruct</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>8.4</v>
+        <v>70</v>
       </c>
       <c r="C74" t="n">
-        <v>4</v>
+        <v>70</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>moe</t>
+          <t>dense</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>artificial_analysis</t>
+          <t>name_parsing</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>llama-3.3-70b-instruct</t>
+          <t>gpt-oss-20b</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>70</v>
+        <v>21</v>
       </c>
       <c r="C75" t="n">
-        <v>70</v>
+        <v>3.6</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>dense</t>
+          <t>moe</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>override</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>gpt-oss-20b</t>
+          <t>gemma-3n-e4b-it</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>21</v>
+        <v>8.4</v>
       </c>
       <c r="C76" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -31468,7 +31468,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>artificial_analysis</t>
         </is>
       </c>
     </row>
@@ -31582,14 +31582,14 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>olmo-3-32b-think</t>
+          <t>athene-70b-0725</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>32.2</v>
+        <v>70</v>
       </c>
       <c r="C82" t="n">
-        <v>32.2</v>
+        <v>70</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -31598,21 +31598,21 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>artificial_analysis</t>
+          <t>name_parsing</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>athene-70b-0725</t>
+          <t>olmo-3-32b-think</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>70</v>
+        <v>32.2</v>
       </c>
       <c r="C83" t="n">
-        <v>70</v>
+        <v>32.2</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -31621,7 +31621,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>artificial_analysis</t>
         </is>
       </c>
     </row>
@@ -31858,14 +31858,14 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>olmo-3.1-32b-think</t>
+          <t>llama-3.1-nemotron-51b-instruct</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>32.2</v>
+        <v>51</v>
       </c>
       <c r="C94" t="n">
-        <v>32.2</v>
+        <v>51</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -31874,21 +31874,21 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>artificial_analysis</t>
+          <t>name_parsing</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>llama-3.1-nemotron-51b-instruct</t>
+          <t>olmo-3.1-32b-think</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>51</v>
+        <v>32.2</v>
       </c>
       <c r="C95" t="n">
-        <v>51</v>
+        <v>32.2</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -31897,7 +31897,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>artificial_analysis</t>
         </is>
       </c>
     </row>

--- a/arena_enrichment/output/arena_leaderboard_enriched.xlsx
+++ b/arena_enrichment/output/arena_leaderboard_enriched.xlsx
@@ -675,16 +675,16 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>1467.44</v>
+        <v>1470.67</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1458.06</v>
+        <v>1462.54</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1476.82</v>
+        <v>1478.79</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>3743</v>
+        <v>5096</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
@@ -746,16 +746,16 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>1455.57</v>
+        <v>1454.59</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1450.02</v>
+        <v>1449.11</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1461.11</v>
+        <v>1460.08</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>13401</v>
+        <v>13834</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
@@ -897,16 +897,16 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>1452.49</v>
+        <v>1452.25</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1447.47</v>
+        <v>1447.22</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1457.51</v>
+        <v>1457.28</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>17843</v>
+        <v>17758</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
@@ -1048,16 +1048,16 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>1451.16</v>
+        <v>1450.88</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1443.56</v>
+        <v>1443.29</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1458.76</v>
+        <v>1458.46</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>6002</v>
+        <v>6013</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
@@ -1199,16 +1199,16 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1447.74</v>
+        <v>1447.63</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1442.42</v>
+        <v>1442.39</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1453.06</v>
+        <v>1452.87</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>14584</v>
+        <v>15184</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
@@ -1350,13 +1350,13 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>1442.71</v>
+        <v>1442.61</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>1436.58</v>
+        <v>1436.48</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1448.83</v>
+        <v>1448.73</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>12179</v>
@@ -1421,16 +1421,16 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>1437.89</v>
+        <v>1437.75</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>1430.27</v>
+        <v>1430.14</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1445.5</v>
+        <v>1445.35</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>5939</v>
+        <v>5950</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
@@ -1572,16 +1572,16 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>1432.95</v>
+        <v>1432.6</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1426.34</v>
+        <v>1426</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1439.56</v>
+        <v>1439.21</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>8247</v>
+        <v>8248</v>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
@@ -1723,16 +1723,16 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>1430</v>
+        <v>1429.95</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>1426.46</v>
+        <v>1426.43</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1433.53</v>
+        <v>1433.47</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>45444</v>
+        <v>46041</v>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
@@ -1874,13 +1874,13 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>1425.84</v>
+        <v>1425.81</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>1421.9</v>
+        <v>1421.87</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1429.78</v>
+        <v>1429.75</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>35926</v>
@@ -1945,16 +1945,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1424.81</v>
+        <v>1424.71</v>
       </c>
       <c r="D12" t="n">
-        <v>1418.28</v>
+        <v>1418.18</v>
       </c>
       <c r="E12" t="n">
-        <v>1431.35</v>
+        <v>1431.25</v>
       </c>
       <c r="F12" t="n">
-        <v>9141</v>
+        <v>9144</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -2016,16 +2016,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1424.42</v>
+        <v>1424.15</v>
       </c>
       <c r="D13" t="n">
-        <v>1420.59</v>
+        <v>1420.35</v>
       </c>
       <c r="E13" t="n">
-        <v>1428.24</v>
+        <v>1427.95</v>
       </c>
       <c r="F13" t="n">
-        <v>40436</v>
+        <v>41005</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -2083,68 +2083,148 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>deepseek-v3.2-exp</t>
+          <t>qwen3-235b-a22b-instruct-2507</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1422.83</v>
+        <v>1423.01</v>
       </c>
       <c r="D14" t="n">
-        <v>1416.43</v>
+        <v>1420.21</v>
       </c>
       <c r="E14" t="n">
-        <v>1429.23</v>
+        <v>1425.81</v>
       </c>
       <c r="F14" t="n">
-        <v>12022</v>
+        <v>81805</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>DeepSeek</t>
+          <t>Alibaba</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+          <t>Apache 2.0</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>235</v>
+      </c>
+      <c r="J14" t="n">
+        <v>22</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr"/>
-      <c r="AA14" t="inlineStr"/>
-      <c r="AB14" t="inlineStr"/>
-      <c r="AC14" t="inlineStr"/>
-      <c r="AD14" t="inlineStr"/>
-      <c r="AE14" t="inlineStr"/>
-      <c r="AF14" t="inlineStr"/>
-      <c r="AG14" t="inlineStr"/>
+          <t>name_parsing</t>
+        </is>
+      </c>
+      <c r="M14" t="n">
+        <v>470</v>
+      </c>
+      <c r="N14" t="n">
+        <v>587.5</v>
+      </c>
+      <c r="O14" t="n">
+        <v>235</v>
+      </c>
+      <c r="P14" t="n">
+        <v>293.8</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>117.5</v>
+      </c>
+      <c r="R14" t="n">
+        <v>146.9</v>
+      </c>
+      <c r="S14" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T14" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U14" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V14" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W14" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X14" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y14" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z14" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA14" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AB14" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AC14" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD14" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE14" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF14" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AG14" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
     </row>
@@ -2154,148 +2234,68 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>qwen3-235b-a22b-instruct-2507</t>
+          <t>deepseek-v3.2-exp</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1422.64</v>
+        <v>1422.74</v>
       </c>
       <c r="D15" t="n">
-        <v>1419.83</v>
+        <v>1416.34</v>
       </c>
       <c r="E15" t="n">
-        <v>1425.44</v>
+        <v>1429.14</v>
       </c>
       <c r="F15" t="n">
-        <v>81260</v>
+        <v>12019</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alibaba</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>235</v>
-      </c>
-      <c r="J15" t="n">
-        <v>22</v>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>name_parsing</t>
-        </is>
-      </c>
-      <c r="M15" t="n">
-        <v>470</v>
-      </c>
-      <c r="N15" t="n">
-        <v>587.5</v>
-      </c>
-      <c r="O15" t="n">
-        <v>235</v>
-      </c>
-      <c r="P15" t="n">
-        <v>293.8</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>117.5</v>
-      </c>
-      <c r="R15" t="n">
-        <v>146.9</v>
-      </c>
-      <c r="S15" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T15" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U15" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="V15" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W15" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X15" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Y15" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z15" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AA15" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AB15" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AC15" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AD15" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AE15" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AF15" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AG15" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="inlineStr"/>
+      <c r="AE15" t="inlineStr"/>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="inlineStr"/>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -2309,16 +2309,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1422.34</v>
+        <v>1422.54</v>
       </c>
       <c r="D16" t="n">
-        <v>1418.42</v>
+        <v>1418.65</v>
       </c>
       <c r="E16" t="n">
-        <v>1426.26</v>
+        <v>1426.43</v>
       </c>
       <c r="F16" t="n">
-        <v>34901</v>
+        <v>35432</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -2380,13 +2380,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1421.72</v>
+        <v>1421.62</v>
       </c>
       <c r="D17" t="n">
-        <v>1416.08</v>
+        <v>1415.97</v>
       </c>
       <c r="E17" t="n">
-        <v>1427.37</v>
+        <v>1427.26</v>
       </c>
       <c r="F17" t="n">
         <v>18599</v>
@@ -2447,68 +2447,148 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>deepseek-v3.1</t>
+          <t>kimi-k2-0905-preview</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1417.88</v>
+        <v>1417.87</v>
       </c>
       <c r="D18" t="n">
-        <v>1411.88</v>
+        <v>1411.39</v>
       </c>
       <c r="E18" t="n">
-        <v>1423.88</v>
+        <v>1424.35</v>
       </c>
       <c r="F18" t="n">
-        <v>15083</v>
+        <v>11867</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>DeepSeek</t>
+          <t>Moonshot</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+          <t>Modified MIT</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J18" t="n">
+        <v>32</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
-      <c r="W18" t="inlineStr"/>
-      <c r="X18" t="inlineStr"/>
-      <c r="Y18" t="inlineStr"/>
-      <c r="Z18" t="inlineStr"/>
-      <c r="AA18" t="inlineStr"/>
-      <c r="AB18" t="inlineStr"/>
-      <c r="AC18" t="inlineStr"/>
-      <c r="AD18" t="inlineStr"/>
-      <c r="AE18" t="inlineStr"/>
-      <c r="AF18" t="inlineStr"/>
-      <c r="AG18" t="inlineStr"/>
+          <t>override</t>
+        </is>
+      </c>
+      <c r="M18" t="n">
+        <v>2000</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2500</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1250</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>500</v>
+      </c>
+      <c r="R18" t="n">
+        <v>625</v>
+      </c>
+      <c r="S18" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T18" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U18" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V18" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W18" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X18" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y18" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z18" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA18" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AB18" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AC18" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD18" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE18" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF18" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AG18" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
     </row>
@@ -2518,36 +2598,36 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>kimi-k2-0905-preview</t>
+          <t>qwen3.5-122b-a10b</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1417.68</v>
+        <v>1417.84</v>
       </c>
       <c r="D19" t="n">
-        <v>1411.19</v>
+        <v>1412.16</v>
       </c>
       <c r="E19" t="n">
-        <v>1424.16</v>
+        <v>1423.53</v>
       </c>
       <c r="F19" t="n">
-        <v>11864</v>
+        <v>11895</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Moonshot</t>
+          <t>Alibaba</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Modified MIT</t>
+          <t>Apache 2.0</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1000</v>
+        <v>122</v>
       </c>
       <c r="J19" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -2556,26 +2636,26 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>name_parsing</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>2000</v>
+        <v>244</v>
       </c>
       <c r="N19" t="n">
-        <v>2500</v>
+        <v>305</v>
       </c>
       <c r="O19" t="n">
-        <v>1000</v>
+        <v>122</v>
       </c>
       <c r="P19" t="n">
-        <v>1250</v>
+        <v>152.5</v>
       </c>
       <c r="Q19" t="n">
-        <v>500</v>
+        <v>61</v>
       </c>
       <c r="R19" t="n">
-        <v>625</v>
+        <v>76.2</v>
       </c>
       <c r="S19" s="5" t="inlineStr">
         <is>
@@ -2587,9 +2667,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="U19" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="U19" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="V19" s="5" t="inlineStr">
@@ -2602,9 +2682,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="X19" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="X19" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Y19" s="5" t="inlineStr">
@@ -2617,9 +2697,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AA19" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AA19" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AB19" s="5" t="inlineStr">
@@ -2627,14 +2707,14 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AC19" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AD19" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AC19" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AD19" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AE19" s="5" t="inlineStr">
@@ -2642,14 +2722,14 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AF19" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AG19" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AF19" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AG19" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
@@ -2659,7 +2739,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>B200 SXM</t>
         </is>
       </c>
     </row>
@@ -2669,20 +2749,20 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>deepseek-v3.1-thinking</t>
+          <t>deepseek-v3.1</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1416.93</v>
+        <v>1417.84</v>
       </c>
       <c r="D20" t="n">
-        <v>1410.34</v>
+        <v>1411.83</v>
       </c>
       <c r="E20" t="n">
-        <v>1423.52</v>
+        <v>1423.84</v>
       </c>
       <c r="F20" t="n">
-        <v>11820</v>
+        <v>15079</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -2740,36 +2820,36 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>qwen3.5-122b-a10b</t>
+          <t>kimi-k2-0711-preview</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1416.84</v>
+        <v>1416.86</v>
       </c>
       <c r="D21" t="n">
-        <v>1411.04</v>
+        <v>1412.02</v>
       </c>
       <c r="E21" t="n">
-        <v>1422.64</v>
+        <v>1421.7</v>
       </c>
       <c r="F21" t="n">
-        <v>11276</v>
+        <v>27875</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alibaba</t>
+          <t>Moonshot</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
+          <t>Modified MIT</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>122</v>
+        <v>1000</v>
       </c>
       <c r="J21" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -2778,26 +2858,26 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>override</t>
         </is>
       </c>
       <c r="M21" t="n">
-        <v>244</v>
+        <v>2000</v>
       </c>
       <c r="N21" t="n">
-        <v>305</v>
+        <v>2500</v>
       </c>
       <c r="O21" t="n">
-        <v>122</v>
+        <v>1000</v>
       </c>
       <c r="P21" t="n">
-        <v>152.5</v>
+        <v>1250</v>
       </c>
       <c r="Q21" t="n">
-        <v>61</v>
+        <v>500</v>
       </c>
       <c r="R21" t="n">
-        <v>76.2</v>
+        <v>625</v>
       </c>
       <c r="S21" s="5" t="inlineStr">
         <is>
@@ -2809,9 +2889,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="U21" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="U21" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="V21" s="5" t="inlineStr">
@@ -2824,9 +2904,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="X21" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="X21" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="Y21" s="5" t="inlineStr">
@@ -2839,9 +2919,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AA21" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AA21" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AB21" s="5" t="inlineStr">
@@ -2849,14 +2929,14 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AC21" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AD21" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AC21" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD21" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AE21" s="5" t="inlineStr">
@@ -2864,14 +2944,14 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AF21" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AG21" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AF21" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AG21" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
@@ -2881,7 +2961,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>B200 SXM</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
     </row>
@@ -2891,148 +2971,68 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>kimi-k2-0711-preview</t>
+          <t>deepseek-v3.1-thinking</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1416.76</v>
+        <v>1416.85</v>
       </c>
       <c r="D22" t="n">
-        <v>1411.92</v>
+        <v>1410.26</v>
       </c>
       <c r="E22" t="n">
-        <v>1421.6</v>
+        <v>1423.44</v>
       </c>
       <c r="F22" t="n">
-        <v>27874</v>
+        <v>11820</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Moonshot</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Modified MIT</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J22" t="n">
-        <v>32</v>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
-          <t>override</t>
-        </is>
-      </c>
-      <c r="M22" t="n">
-        <v>2000</v>
-      </c>
-      <c r="N22" t="n">
-        <v>2500</v>
-      </c>
-      <c r="O22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="P22" t="n">
-        <v>1250</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>500</v>
-      </c>
-      <c r="R22" t="n">
-        <v>625</v>
-      </c>
-      <c r="S22" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T22" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U22" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="V22" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W22" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X22" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Y22" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z22" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AA22" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AB22" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AC22" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AD22" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AE22" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AF22" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AG22" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr"/>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr"/>
+      <c r="AB22" t="inlineStr"/>
+      <c r="AC22" t="inlineStr"/>
+      <c r="AD22" t="inlineStr"/>
+      <c r="AE22" t="inlineStr"/>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="inlineStr"/>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -3046,16 +3046,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1416.29</v>
+        <v>1416.76</v>
       </c>
       <c r="D23" t="n">
-        <v>1406.35</v>
+        <v>1406.81</v>
       </c>
       <c r="E23" t="n">
-        <v>1426.23</v>
+        <v>1426.71</v>
       </c>
       <c r="F23" t="n">
-        <v>3491</v>
+        <v>3488</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -3113,148 +3113,68 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>qwen3-vl-235b-a22b-instruct</t>
+          <t>deepseek-v3.1-terminus</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1415.79</v>
+        <v>1415.99</v>
       </c>
       <c r="D24" t="n">
-        <v>1409.33</v>
+        <v>1406.39</v>
       </c>
       <c r="E24" t="n">
-        <v>1422.25</v>
+        <v>1425.59</v>
       </c>
       <c r="F24" t="n">
-        <v>11612</v>
+        <v>3723</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alibaba</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
-        <v>235</v>
-      </c>
-      <c r="J24" t="n">
-        <v>22</v>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
-          <t>name_parsing</t>
-        </is>
-      </c>
-      <c r="M24" t="n">
-        <v>470</v>
-      </c>
-      <c r="N24" t="n">
-        <v>587.5</v>
-      </c>
-      <c r="O24" t="n">
-        <v>235</v>
-      </c>
-      <c r="P24" t="n">
-        <v>293.8</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>117.5</v>
-      </c>
-      <c r="R24" t="n">
-        <v>146.9</v>
-      </c>
-      <c r="S24" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T24" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U24" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="V24" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W24" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X24" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Y24" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z24" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AA24" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AB24" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AC24" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AD24" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AE24" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AF24" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AG24" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr"/>
+      <c r="AB24" t="inlineStr"/>
+      <c r="AC24" t="inlineStr"/>
+      <c r="AD24" t="inlineStr"/>
+      <c r="AE24" t="inlineStr"/>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="inlineStr"/>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -3264,68 +3184,148 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>deepseek-v3.1-terminus</t>
+          <t>qwen3-vl-235b-a22b-instruct</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1415.69</v>
+        <v>1415.6</v>
       </c>
       <c r="D25" t="n">
-        <v>1406.09</v>
+        <v>1409.14</v>
       </c>
       <c r="E25" t="n">
-        <v>1425.29</v>
+        <v>1422.06</v>
       </c>
       <c r="F25" t="n">
-        <v>3724</v>
+        <v>11606</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>DeepSeek</t>
+          <t>Alibaba</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
+          <t>Apache 2.0</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>235</v>
+      </c>
+      <c r="J25" t="n">
+        <v>22</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="inlineStr"/>
-      <c r="T25" t="inlineStr"/>
-      <c r="U25" t="inlineStr"/>
-      <c r="V25" t="inlineStr"/>
-      <c r="W25" t="inlineStr"/>
-      <c r="X25" t="inlineStr"/>
-      <c r="Y25" t="inlineStr"/>
-      <c r="Z25" t="inlineStr"/>
-      <c r="AA25" t="inlineStr"/>
-      <c r="AB25" t="inlineStr"/>
-      <c r="AC25" t="inlineStr"/>
-      <c r="AD25" t="inlineStr"/>
-      <c r="AE25" t="inlineStr"/>
-      <c r="AF25" t="inlineStr"/>
-      <c r="AG25" t="inlineStr"/>
+          <t>name_parsing</t>
+        </is>
+      </c>
+      <c r="M25" t="n">
+        <v>470</v>
+      </c>
+      <c r="N25" t="n">
+        <v>587.5</v>
+      </c>
+      <c r="O25" t="n">
+        <v>235</v>
+      </c>
+      <c r="P25" t="n">
+        <v>293.8</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>117.5</v>
+      </c>
+      <c r="R25" t="n">
+        <v>146.9</v>
+      </c>
+      <c r="S25" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T25" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U25" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V25" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W25" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X25" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y25" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z25" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA25" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AB25" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AC25" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD25" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE25" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF25" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AG25" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
     </row>
@@ -3339,16 +3339,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1415.02</v>
+        <v>1414.65</v>
       </c>
       <c r="D26" t="n">
-        <v>1411.22</v>
+        <v>1410.86</v>
       </c>
       <c r="E26" t="n">
-        <v>1418.83</v>
+        <v>1418.43</v>
       </c>
       <c r="F26" t="n">
-        <v>37459</v>
+        <v>38100</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -3490,13 +3490,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1410.91</v>
+        <v>1410.86</v>
       </c>
       <c r="D27" t="n">
-        <v>1406.05</v>
+        <v>1406</v>
       </c>
       <c r="E27" t="n">
-        <v>1415.77</v>
+        <v>1415.73</v>
       </c>
       <c r="F27" t="n">
         <v>24510</v>
@@ -3641,16 +3641,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1404.43</v>
+        <v>1403.46</v>
       </c>
       <c r="D28" t="n">
-        <v>1399.27</v>
+        <v>1398.38</v>
       </c>
       <c r="E28" t="n">
-        <v>1409.58</v>
+        <v>1408.54</v>
       </c>
       <c r="F28" t="n">
-        <v>16347</v>
+        <v>16978</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -3712,16 +3712,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1403.94</v>
+        <v>1403.21</v>
       </c>
       <c r="D29" t="n">
-        <v>1398.07</v>
+        <v>1397.45</v>
       </c>
       <c r="E29" t="n">
-        <v>1409.82</v>
+        <v>1408.96</v>
       </c>
       <c r="F29" t="n">
-        <v>11073</v>
+        <v>11646</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -3863,16 +3863,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1402.65</v>
+        <v>1402.62</v>
       </c>
       <c r="D30" t="n">
-        <v>1398.16</v>
+        <v>1398.13</v>
       </c>
       <c r="E30" t="n">
-        <v>1407.13</v>
+        <v>1407.11</v>
       </c>
       <c r="F30" t="n">
-        <v>38482</v>
+        <v>38481</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -4014,16 +4014,16 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1401.59</v>
+        <v>1401.56</v>
       </c>
       <c r="D31" t="n">
-        <v>1396.82</v>
+        <v>1396.79</v>
       </c>
       <c r="E31" t="n">
-        <v>1406.36</v>
+        <v>1406.32</v>
       </c>
       <c r="F31" t="n">
-        <v>23076</v>
+        <v>23083</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -4165,16 +4165,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1401.06</v>
+        <v>1400.97</v>
       </c>
       <c r="D32" t="n">
-        <v>1394.7</v>
+        <v>1394.61</v>
       </c>
       <c r="E32" t="n">
-        <v>1407.42</v>
+        <v>1407.33</v>
       </c>
       <c r="F32" t="n">
-        <v>11481</v>
+        <v>11477</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -4316,16 +4316,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1399.79</v>
+        <v>1399.64</v>
       </c>
       <c r="D33" t="n">
-        <v>1393.28</v>
+        <v>1393.13</v>
       </c>
       <c r="E33" t="n">
-        <v>1406.3</v>
+        <v>1406.16</v>
       </c>
       <c r="F33" t="n">
-        <v>9063</v>
+        <v>9062</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1397.49</v>
+        <v>1397.51</v>
       </c>
       <c r="D34" t="n">
-        <v>1392.63</v>
+        <v>1392.65</v>
       </c>
       <c r="E34" t="n">
-        <v>1402.34</v>
+        <v>1402.37</v>
       </c>
       <c r="F34" t="n">
         <v>18524</v>
@@ -4618,16 +4618,16 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1396.83</v>
+        <v>1395.67</v>
       </c>
       <c r="D35" t="n">
-        <v>1391.06</v>
+        <v>1390.01</v>
       </c>
       <c r="E35" t="n">
-        <v>1402.6</v>
+        <v>1401.34</v>
       </c>
       <c r="F35" t="n">
-        <v>11495</v>
+        <v>12090</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -4769,13 +4769,13 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1395.48</v>
+        <v>1395.3</v>
       </c>
       <c r="D36" t="n">
-        <v>1388.71</v>
+        <v>1388.53</v>
       </c>
       <c r="E36" t="n">
-        <v>1402.25</v>
+        <v>1402.07</v>
       </c>
       <c r="F36" t="n">
         <v>8019</v>
@@ -4920,16 +4920,16 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1394.57</v>
+        <v>1394.58</v>
       </c>
       <c r="D37" t="n">
-        <v>1390.71</v>
+        <v>1390.73</v>
       </c>
       <c r="E37" t="n">
-        <v>1398.42</v>
+        <v>1398.44</v>
       </c>
       <c r="F37" t="n">
-        <v>45803</v>
+        <v>45805</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -5071,16 +5071,16 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1392.09</v>
+        <v>1392.03</v>
       </c>
       <c r="D38" t="n">
-        <v>1387.96</v>
+        <v>1387.93</v>
       </c>
       <c r="E38" t="n">
-        <v>1396.23</v>
+        <v>1396.14</v>
       </c>
       <c r="F38" t="n">
-        <v>29395</v>
+        <v>30013</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -5142,16 +5142,16 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1391.39</v>
+        <v>1390.99</v>
       </c>
       <c r="D39" t="n">
-        <v>1386.43</v>
+        <v>1386.08</v>
       </c>
       <c r="E39" t="n">
-        <v>1396.34</v>
+        <v>1395.89</v>
       </c>
       <c r="F39" t="n">
-        <v>17808</v>
+        <v>18351</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -5213,16 +5213,16 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1387.45</v>
+        <v>1387.36</v>
       </c>
       <c r="D40" t="n">
-        <v>1382.52</v>
+        <v>1382.43</v>
       </c>
       <c r="E40" t="n">
-        <v>1392.38</v>
+        <v>1392.29</v>
       </c>
       <c r="F40" t="n">
-        <v>25972</v>
+        <v>25964</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -5364,16 +5364,16 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1387.36</v>
+        <v>1387.17</v>
       </c>
       <c r="D41" t="n">
-        <v>1381.09</v>
+        <v>1380.9</v>
       </c>
       <c r="E41" t="n">
-        <v>1393.63</v>
+        <v>1393.44</v>
       </c>
       <c r="F41" t="n">
-        <v>11025</v>
+        <v>11024</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -5435,16 +5435,16 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1385.74</v>
+        <v>1385.57</v>
       </c>
       <c r="D42" t="n">
-        <v>1380.48</v>
+        <v>1380.32</v>
       </c>
       <c r="E42" t="n">
-        <v>1391</v>
+        <v>1390.83</v>
       </c>
       <c r="F42" t="n">
-        <v>17234</v>
+        <v>17237</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -5506,16 +5506,16 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1383.1</v>
+        <v>1383.03</v>
       </c>
       <c r="D43" t="n">
-        <v>1378.24</v>
+        <v>1378.17</v>
       </c>
       <c r="E43" t="n">
-        <v>1387.96</v>
+        <v>1387.89</v>
       </c>
       <c r="F43" t="n">
-        <v>23953</v>
+        <v>23946</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -5657,16 +5657,16 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1377.89</v>
+        <v>1377.73</v>
       </c>
       <c r="D44" t="n">
-        <v>1366.6</v>
+        <v>1366.45</v>
       </c>
       <c r="E44" t="n">
-        <v>1389.17</v>
+        <v>1389</v>
       </c>
       <c r="F44" t="n">
-        <v>2816</v>
+        <v>2818</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -5728,16 +5728,16 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1375.11</v>
+        <v>1374.63</v>
       </c>
       <c r="D45" t="n">
-        <v>1369.39</v>
+        <v>1369</v>
       </c>
       <c r="E45" t="n">
-        <v>1380.83</v>
+        <v>1380.26</v>
       </c>
       <c r="F45" t="n">
-        <v>12625</v>
+        <v>13146</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -5879,16 +5879,16 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1374.41</v>
+        <v>1374.35</v>
       </c>
       <c r="D46" t="n">
-        <v>1369.73</v>
+        <v>1369.67</v>
       </c>
       <c r="E46" t="n">
-        <v>1379.09</v>
+        <v>1379.03</v>
       </c>
       <c r="F46" t="n">
-        <v>26430</v>
+        <v>26429</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -6030,13 +6030,13 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1372.79</v>
+        <v>1372.81</v>
       </c>
       <c r="D47" t="n">
-        <v>1368.56</v>
+        <v>1368.58</v>
       </c>
       <c r="E47" t="n">
-        <v>1377.03</v>
+        <v>1377.05</v>
       </c>
       <c r="F47" t="n">
         <v>31382</v>
@@ -6101,16 +6101,16 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1368.98</v>
+        <v>1368.89</v>
       </c>
       <c r="D48" t="n">
-        <v>1363.17</v>
+        <v>1363.08</v>
       </c>
       <c r="E48" t="n">
-        <v>1374.8</v>
+        <v>1374.71</v>
       </c>
       <c r="F48" t="n">
-        <v>13842</v>
+        <v>13834</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -6252,16 +6252,16 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1368.71</v>
+        <v>1368.52</v>
       </c>
       <c r="D49" t="n">
-        <v>1362.89</v>
+        <v>1362.7</v>
       </c>
       <c r="E49" t="n">
-        <v>1374.53</v>
+        <v>1374.34</v>
       </c>
       <c r="F49" t="n">
-        <v>11834</v>
+        <v>11833</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -6326,13 +6326,13 @@
         <v>1365.09</v>
       </c>
       <c r="D50" t="n">
-        <v>1361.43</v>
+        <v>1361.44</v>
       </c>
       <c r="E50" t="n">
-        <v>1368.74</v>
+        <v>1368.75</v>
       </c>
       <c r="F50" t="n">
-        <v>47853</v>
+        <v>47852</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -6470,148 +6470,68 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>nvidia-nemotron-3-super-120b-a12b</t>
+          <t>minimax-m1</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1363.98</v>
+        <v>1363.32</v>
       </c>
       <c r="D51" t="n">
-        <v>1354.3</v>
+        <v>1359.07</v>
       </c>
       <c r="E51" t="n">
-        <v>1373.66</v>
+        <v>1367.58</v>
       </c>
       <c r="F51" t="n">
-        <v>3622</v>
+        <v>35522</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>MiniMax</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>NVIDIA Open Model</t>
-        </is>
-      </c>
-      <c r="I51" t="n">
-        <v>120</v>
-      </c>
-      <c r="J51" t="n">
-        <v>12</v>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+          <t>Apache 2.0</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr">
         <is>
-          <t>name_parsing</t>
-        </is>
-      </c>
-      <c r="M51" t="n">
-        <v>240</v>
-      </c>
-      <c r="N51" t="n">
-        <v>300</v>
-      </c>
-      <c r="O51" t="n">
-        <v>120</v>
-      </c>
-      <c r="P51" t="n">
-        <v>150</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>60</v>
-      </c>
-      <c r="R51" t="n">
-        <v>75</v>
-      </c>
-      <c r="S51" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T51" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U51" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="V51" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W51" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X51" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Y51" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z51" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AA51" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB51" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AC51" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AD51" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AE51" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AF51" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AG51" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr"/>
+      <c r="S51" t="inlineStr"/>
+      <c r="T51" t="inlineStr"/>
+      <c r="U51" t="inlineStr"/>
+      <c r="V51" t="inlineStr"/>
+      <c r="W51" t="inlineStr"/>
+      <c r="X51" t="inlineStr"/>
+      <c r="Y51" t="inlineStr"/>
+      <c r="Z51" t="inlineStr"/>
+      <c r="AA51" t="inlineStr"/>
+      <c r="AB51" t="inlineStr"/>
+      <c r="AC51" t="inlineStr"/>
+      <c r="AD51" t="inlineStr"/>
+      <c r="AE51" t="inlineStr"/>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="inlineStr"/>
       <c r="AH51" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>B200 SXM</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -6621,68 +6541,148 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>minimax-m1</t>
+          <t>nvidia-nemotron-3-super-120b-a12b</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1363.25</v>
+        <v>1361.41</v>
       </c>
       <c r="D52" t="n">
-        <v>1359</v>
+        <v>1354.12</v>
       </c>
       <c r="E52" t="n">
-        <v>1367.5</v>
+        <v>1368.7</v>
       </c>
       <c r="F52" t="n">
-        <v>35531</v>
+        <v>7460</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>MiniMax</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
+          <t>NVIDIA Open Model</t>
+        </is>
+      </c>
+      <c r="I52" t="n">
+        <v>120</v>
+      </c>
+      <c r="J52" t="n">
+        <v>12</v>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr"/>
-      <c r="P52" t="inlineStr"/>
-      <c r="Q52" t="inlineStr"/>
-      <c r="R52" t="inlineStr"/>
-      <c r="S52" t="inlineStr"/>
-      <c r="T52" t="inlineStr"/>
-      <c r="U52" t="inlineStr"/>
-      <c r="V52" t="inlineStr"/>
-      <c r="W52" t="inlineStr"/>
-      <c r="X52" t="inlineStr"/>
-      <c r="Y52" t="inlineStr"/>
-      <c r="Z52" t="inlineStr"/>
-      <c r="AA52" t="inlineStr"/>
-      <c r="AB52" t="inlineStr"/>
-      <c r="AC52" t="inlineStr"/>
-      <c r="AD52" t="inlineStr"/>
-      <c r="AE52" t="inlineStr"/>
-      <c r="AF52" t="inlineStr"/>
-      <c r="AG52" t="inlineStr"/>
+          <t>name_parsing</t>
+        </is>
+      </c>
+      <c r="M52" t="n">
+        <v>240</v>
+      </c>
+      <c r="N52" t="n">
+        <v>300</v>
+      </c>
+      <c r="O52" t="n">
+        <v>120</v>
+      </c>
+      <c r="P52" t="n">
+        <v>150</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>60</v>
+      </c>
+      <c r="R52" t="n">
+        <v>75</v>
+      </c>
+      <c r="S52" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T52" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U52" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V52" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W52" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X52" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y52" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z52" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA52" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB52" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AC52" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AD52" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE52" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF52" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AG52" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AH52" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>B200 SXM</t>
         </is>
       </c>
     </row>
@@ -6702,7 +6702,7 @@
         <v>1353.44</v>
       </c>
       <c r="E53" t="n">
-        <v>1362.87</v>
+        <v>1362.88</v>
       </c>
       <c r="F53" t="n">
         <v>21770</v>
@@ -6847,16 +6847,16 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1356.96</v>
+        <v>1357</v>
       </c>
       <c r="D54" t="n">
-        <v>1351.77</v>
+        <v>1351.82</v>
       </c>
       <c r="E54" t="n">
-        <v>1362.14</v>
+        <v>1362.19</v>
       </c>
       <c r="F54" t="n">
-        <v>17847</v>
+        <v>17845</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -6918,16 +6918,16 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1356.16</v>
+        <v>1356.29</v>
       </c>
       <c r="D55" t="n">
-        <v>1347.81</v>
+        <v>1347.93</v>
       </c>
       <c r="E55" t="n">
-        <v>1364.52</v>
+        <v>1364.64</v>
       </c>
       <c r="F55" t="n">
-        <v>5358</v>
+        <v>5357</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -7069,16 +7069,16 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1353.82</v>
+        <v>1353.7</v>
       </c>
       <c r="D56" t="n">
-        <v>1349.48</v>
+        <v>1349.36</v>
       </c>
       <c r="E56" t="n">
-        <v>1358.15</v>
+        <v>1358.03</v>
       </c>
       <c r="F56" t="n">
-        <v>30896</v>
+        <v>30903</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -7220,13 +7220,13 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1353.42</v>
+        <v>1353.36</v>
       </c>
       <c r="D57" t="n">
-        <v>1349.99</v>
+        <v>1349.93</v>
       </c>
       <c r="E57" t="n">
-        <v>1356.85</v>
+        <v>1356.8</v>
       </c>
       <c r="F57" t="n">
         <v>56669</v>
@@ -7291,16 +7291,16 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1353.29</v>
+        <v>1353.31</v>
       </c>
       <c r="D58" t="n">
-        <v>1344.96</v>
+        <v>1344.98</v>
       </c>
       <c r="E58" t="n">
-        <v>1361.62</v>
+        <v>1361.64</v>
       </c>
       <c r="F58" t="n">
-        <v>4981</v>
+        <v>4980</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -7362,16 +7362,16 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1347.52</v>
+        <v>1347.64</v>
       </c>
       <c r="D59" t="n">
-        <v>1340.14</v>
+        <v>1340.26</v>
       </c>
       <c r="E59" t="n">
-        <v>1354.9</v>
+        <v>1355.02</v>
       </c>
       <c r="F59" t="n">
-        <v>6582</v>
+        <v>6587</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -7433,13 +7433,13 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1347.02</v>
+        <v>1347</v>
       </c>
       <c r="D60" t="n">
-        <v>1337.56</v>
+        <v>1337.54</v>
       </c>
       <c r="E60" t="n">
-        <v>1356.48</v>
+        <v>1356.46</v>
       </c>
       <c r="F60" t="n">
         <v>3926</v>
@@ -7584,13 +7584,13 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1346.81</v>
+        <v>1346.84</v>
       </c>
       <c r="D61" t="n">
-        <v>1335.11</v>
+        <v>1335.14</v>
       </c>
       <c r="E61" t="n">
-        <v>1358.5</v>
+        <v>1358.53</v>
       </c>
       <c r="F61" t="n">
         <v>2549</v>
@@ -7735,16 +7735,16 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1346.58</v>
+        <v>1346.54</v>
       </c>
       <c r="D62" t="n">
-        <v>1338.86</v>
+        <v>1338.82</v>
       </c>
       <c r="E62" t="n">
-        <v>1354.3</v>
+        <v>1354.26</v>
       </c>
       <c r="F62" t="n">
-        <v>6918</v>
+        <v>6916</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -7886,16 +7886,16 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1346.3</v>
+        <v>1346.22</v>
       </c>
       <c r="D63" t="n">
-        <v>1339.07</v>
+        <v>1338.99</v>
       </c>
       <c r="E63" t="n">
-        <v>1353.53</v>
+        <v>1353.45</v>
       </c>
       <c r="F63" t="n">
-        <v>7080</v>
+        <v>7079</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -7957,13 +7957,13 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1342.75</v>
+        <v>1342.73</v>
       </c>
       <c r="D64" t="n">
-        <v>1332.8</v>
+        <v>1332.78</v>
       </c>
       <c r="E64" t="n">
-        <v>1352.7</v>
+        <v>1352.68</v>
       </c>
       <c r="F64" t="n">
         <v>3367</v>
@@ -8108,13 +8108,13 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1341.41</v>
+        <v>1341.42</v>
       </c>
       <c r="D65" t="n">
-        <v>1331.9</v>
+        <v>1331.91</v>
       </c>
       <c r="E65" t="n">
-        <v>1350.92</v>
+        <v>1350.93</v>
       </c>
       <c r="F65" t="n">
         <v>3829</v>
@@ -8259,16 +8259,16 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1335.65</v>
+        <v>1335.63</v>
       </c>
       <c r="D66" t="n">
-        <v>1331.23</v>
+        <v>1331.21</v>
       </c>
       <c r="E66" t="n">
-        <v>1340.07</v>
+        <v>1340.05</v>
       </c>
       <c r="F66" t="n">
-        <v>25524</v>
+        <v>25518</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -8410,13 +8410,13 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1334.22</v>
+        <v>1334.26</v>
       </c>
       <c r="D67" t="n">
-        <v>1330.54</v>
+        <v>1330.58</v>
       </c>
       <c r="E67" t="n">
-        <v>1337.9</v>
+        <v>1337.94</v>
       </c>
       <c r="F67" t="n">
         <v>41375</v>
@@ -8561,13 +8561,13 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1332.42</v>
+        <v>1332.47</v>
       </c>
       <c r="D68" t="n">
-        <v>1328.85</v>
+        <v>1328.9</v>
       </c>
       <c r="E68" t="n">
-        <v>1335.99</v>
+        <v>1336.03</v>
       </c>
       <c r="F68" t="n">
         <v>59656</v>
@@ -8712,16 +8712,16 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1330.93</v>
+        <v>1330.82</v>
       </c>
       <c r="D69" t="n">
-        <v>1324.83</v>
+        <v>1324.72</v>
       </c>
       <c r="E69" t="n">
-        <v>1337.03</v>
+        <v>1336.92</v>
       </c>
       <c r="F69" t="n">
-        <v>12298</v>
+        <v>12293</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -8863,13 +8863,13 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1327.38</v>
+        <v>1327.39</v>
       </c>
       <c r="D70" t="n">
-        <v>1315.21</v>
+        <v>1315.22</v>
       </c>
       <c r="E70" t="n">
-        <v>1339.54</v>
+        <v>1339.56</v>
       </c>
       <c r="F70" t="n">
         <v>2218</v>
@@ -9010,24 +9010,24 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>qwen3-30b-a3b</t>
+          <t>molmo-2-8b</t>
         </is>
       </c>
       <c r="C71" t="n">
         <v>1327.33</v>
       </c>
       <c r="D71" t="n">
-        <v>1322.62</v>
+        <v>1305.94</v>
       </c>
       <c r="E71" t="n">
-        <v>1332.04</v>
+        <v>1348.72</v>
       </c>
       <c r="F71" t="n">
-        <v>26655</v>
+        <v>805</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alibaba</t>
+          <t>Ai2</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -9036,14 +9036,14 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="J71" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>moe</t>
+          <t>dense</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -9052,22 +9052,22 @@
         </is>
       </c>
       <c r="M71" t="n">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="N71" t="n">
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="O71" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="P71" t="n">
-        <v>37.5</v>
+        <v>10</v>
       </c>
       <c r="Q71" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="R71" t="n">
-        <v>18.8</v>
+        <v>5</v>
       </c>
       <c r="S71" s="6" t="inlineStr">
         <is>
@@ -9161,36 +9161,36 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>llama-4-maverick-17b-128e-instruct</t>
+          <t>qwen3-30b-a3b</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1326.63</v>
+        <v>1327.29</v>
       </c>
       <c r="D72" t="n">
-        <v>1322.39</v>
+        <v>1322.58</v>
       </c>
       <c r="E72" t="n">
-        <v>1330.86</v>
+        <v>1332</v>
       </c>
       <c r="F72" t="n">
-        <v>40218</v>
+        <v>26647</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>Alibaba</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Llama 4</t>
+          <t>Apache 2.0</t>
         </is>
       </c>
       <c r="I72" t="n">
-        <v>400</v>
+        <v>30</v>
       </c>
       <c r="J72" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
@@ -9199,95 +9199,95 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>name_parsing</t>
         </is>
       </c>
       <c r="M72" t="n">
-        <v>800</v>
+        <v>60</v>
       </c>
       <c r="N72" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="O72" t="n">
-        <v>400</v>
+        <v>30</v>
       </c>
       <c r="P72" t="n">
-        <v>500</v>
+        <v>37.5</v>
       </c>
       <c r="Q72" t="n">
-        <v>200</v>
+        <v>15</v>
       </c>
       <c r="R72" t="n">
-        <v>250</v>
-      </c>
-      <c r="S72" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T72" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U72" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="V72" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W72" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X72" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Y72" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z72" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AA72" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AB72" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AC72" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AD72" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AE72" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AF72" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+        <v>18.8</v>
+      </c>
+      <c r="S72" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T72" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U72" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V72" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W72" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X72" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y72" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z72" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AA72" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB72" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AC72" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AD72" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE72" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AF72" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AG72" s="6" t="inlineStr">
@@ -9297,12 +9297,12 @@
       </c>
       <c r="AH72" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>H100 SXM</t>
         </is>
       </c>
       <c r="AI72" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>H100 SXM</t>
         </is>
       </c>
     </row>
@@ -9312,133 +9312,133 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>molmo-2-8b</t>
+          <t>llama-4-maverick-17b-128e-instruct</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1326.32</v>
+        <v>1326.67</v>
       </c>
       <c r="D73" t="n">
-        <v>1304.91</v>
+        <v>1322.44</v>
       </c>
       <c r="E73" t="n">
-        <v>1347.73</v>
+        <v>1330.91</v>
       </c>
       <c r="F73" t="n">
-        <v>806</v>
+        <v>40220</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Ai2</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
+          <t>Llama 4</t>
         </is>
       </c>
       <c r="I73" t="n">
-        <v>8</v>
+        <v>400</v>
       </c>
       <c r="J73" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>dense</t>
+          <t>moe</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>override</t>
         </is>
       </c>
       <c r="M73" t="n">
-        <v>16</v>
+        <v>800</v>
       </c>
       <c r="N73" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="O73" t="n">
-        <v>8</v>
+        <v>400</v>
       </c>
       <c r="P73" t="n">
-        <v>10</v>
+        <v>500</v>
       </c>
       <c r="Q73" t="n">
-        <v>4</v>
+        <v>200</v>
       </c>
       <c r="R73" t="n">
-        <v>5</v>
-      </c>
-      <c r="S73" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="T73" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="U73" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="V73" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W73" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X73" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Y73" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z73" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AA73" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB73" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AC73" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AD73" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AE73" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AF73" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+        <v>250</v>
+      </c>
+      <c r="S73" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T73" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U73" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V73" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W73" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X73" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y73" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z73" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA73" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AB73" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AC73" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD73" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE73" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF73" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AG73" s="6" t="inlineStr">
@@ -9448,12 +9448,12 @@
       </c>
       <c r="AH73" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
       <c r="AI73" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
     </row>
@@ -9467,13 +9467,13 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1323.08</v>
+        <v>1323.09</v>
       </c>
       <c r="D74" t="n">
-        <v>1314.82</v>
+        <v>1314.83</v>
       </c>
       <c r="E74" t="n">
-        <v>1331.34</v>
+        <v>1331.35</v>
       </c>
       <c r="F74" t="n">
         <v>6795</v>
@@ -9538,16 +9538,16 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>1321.91</v>
+        <v>1321.93</v>
       </c>
       <c r="D75" t="n">
-        <v>1317.21</v>
+        <v>1317.24</v>
       </c>
       <c r="E75" t="n">
-        <v>1326.6</v>
+        <v>1326.62</v>
       </c>
       <c r="F75" t="n">
-        <v>30505</v>
+        <v>30500</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -9695,10 +9695,10 @@
         <v>1313.64</v>
       </c>
       <c r="E76" t="n">
-        <v>1328.01</v>
+        <v>1328.02</v>
       </c>
       <c r="F76" t="n">
-        <v>7219</v>
+        <v>7217</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -9760,16 +9760,16 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1317.98</v>
+        <v>1318.04</v>
       </c>
       <c r="D77" t="n">
-        <v>1312.85</v>
+        <v>1312.9</v>
       </c>
       <c r="E77" t="n">
-        <v>1323.11</v>
+        <v>1323.17</v>
       </c>
       <c r="F77" t="n">
-        <v>22730</v>
+        <v>22729</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -9911,16 +9911,16 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1317.98</v>
+        <v>1317.95</v>
       </c>
       <c r="D78" t="n">
-        <v>1314.55</v>
+        <v>1314.52</v>
       </c>
       <c r="E78" t="n">
-        <v>1321.41</v>
+        <v>1321.39</v>
       </c>
       <c r="F78" t="n">
-        <v>54890</v>
+        <v>54887</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -10058,36 +10058,36 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>nvidia-nemotron-3-nano-30b-a3b-bf16</t>
+          <t>gpt-oss-20b</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>1317.76</v>
+        <v>1317.68</v>
       </c>
       <c r="D79" t="n">
-        <v>1312.18</v>
+        <v>1311.33</v>
       </c>
       <c r="E79" t="n">
-        <v>1323.34</v>
+        <v>1324.03</v>
       </c>
       <c r="F79" t="n">
-        <v>15595</v>
+        <v>10702</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>NVIDIA Open Model</t>
+          <t>Apache 2.0</t>
         </is>
       </c>
       <c r="I79" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="J79" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
@@ -10096,26 +10096,26 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>override</t>
         </is>
       </c>
       <c r="M79" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="N79" t="n">
-        <v>75</v>
+        <v>52.5</v>
       </c>
       <c r="O79" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="P79" t="n">
-        <v>37.5</v>
+        <v>26.2</v>
       </c>
       <c r="Q79" t="n">
-        <v>15</v>
+        <v>10.5</v>
       </c>
       <c r="R79" t="n">
-        <v>18.8</v>
+        <v>13.1</v>
       </c>
       <c r="S79" s="6" t="inlineStr">
         <is>
@@ -10209,36 +10209,36 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>gpt-oss-20b</t>
+          <t>nvidia-nemotron-3-nano-30b-a3b-bf16</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1317.7</v>
+        <v>1317.51</v>
       </c>
       <c r="D80" t="n">
-        <v>1311.35</v>
+        <v>1311.93</v>
       </c>
       <c r="E80" t="n">
-        <v>1324.05</v>
+        <v>1323.09</v>
       </c>
       <c r="F80" t="n">
-        <v>10702</v>
+        <v>15591</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
+          <t>NVIDIA Open Model</t>
         </is>
       </c>
       <c r="I80" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="J80" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
@@ -10247,26 +10247,26 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>name_parsing</t>
         </is>
       </c>
       <c r="M80" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="N80" t="n">
-        <v>52.5</v>
+        <v>75</v>
       </c>
       <c r="O80" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="P80" t="n">
-        <v>26.2</v>
+        <v>37.5</v>
       </c>
       <c r="Q80" t="n">
-        <v>10.5</v>
+        <v>15</v>
       </c>
       <c r="R80" t="n">
-        <v>13.1</v>
+        <v>18.8</v>
       </c>
       <c r="S80" s="6" t="inlineStr">
         <is>
@@ -10364,13 +10364,13 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1317.47</v>
+        <v>1317.5</v>
       </c>
       <c r="D81" t="n">
-        <v>1311.79</v>
+        <v>1311.81</v>
       </c>
       <c r="E81" t="n">
-        <v>1323.16</v>
+        <v>1323.18</v>
       </c>
       <c r="F81" t="n">
         <v>16478</v>
@@ -10435,10 +10435,10 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>1314.08</v>
+        <v>1314.07</v>
       </c>
       <c r="D82" t="n">
-        <v>1309.55</v>
+        <v>1309.54</v>
       </c>
       <c r="E82" t="n">
         <v>1318.6</v>
@@ -10586,13 +10586,13 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>1313.33</v>
+        <v>1313.38</v>
       </c>
       <c r="D83" t="n">
-        <v>1309.43</v>
+        <v>1309.48</v>
       </c>
       <c r="E83" t="n">
-        <v>1317.23</v>
+        <v>1317.28</v>
       </c>
       <c r="F83" t="n">
         <v>45459</v>
@@ -10737,13 +10737,13 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>1306.62</v>
+        <v>1306.64</v>
       </c>
       <c r="D84" t="n">
-        <v>1301.93</v>
+        <v>1301.96</v>
       </c>
       <c r="E84" t="n">
-        <v>1311.3</v>
+        <v>1311.33</v>
       </c>
       <c r="F84" t="n">
         <v>24572</v>
@@ -10808,13 +10808,13 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>1305.47</v>
+        <v>1305.54</v>
       </c>
       <c r="D85" t="n">
-        <v>1299.81</v>
+        <v>1299.88</v>
       </c>
       <c r="E85" t="n">
-        <v>1311.13</v>
+        <v>1311.2</v>
       </c>
       <c r="F85" t="n">
         <v>19621</v>
@@ -10959,16 +10959,16 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>1305.35</v>
+        <v>1305.14</v>
       </c>
       <c r="D86" t="n">
-        <v>1297.17</v>
+        <v>1296.96</v>
       </c>
       <c r="E86" t="n">
-        <v>1313.52</v>
+        <v>1313.32</v>
       </c>
       <c r="F86" t="n">
-        <v>5989</v>
+        <v>5988</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -11110,13 +11110,13 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>1304.66</v>
+        <v>1304.69</v>
       </c>
       <c r="D87" t="n">
-        <v>1300.25</v>
+        <v>1300.28</v>
       </c>
       <c r="E87" t="n">
-        <v>1309.06</v>
+        <v>1309.09</v>
       </c>
       <c r="F87" t="n">
         <v>28073</v>
@@ -11181,13 +11181,13 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>1302.78</v>
+        <v>1302.8</v>
       </c>
       <c r="D88" t="n">
-        <v>1293.47</v>
+        <v>1293.48</v>
       </c>
       <c r="E88" t="n">
-        <v>1312.1</v>
+        <v>1312.12</v>
       </c>
       <c r="F88" t="n">
         <v>4171</v>
@@ -11332,16 +11332,16 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>1302.74</v>
+        <v>1302.79</v>
       </c>
       <c r="D89" t="n">
-        <v>1298.25</v>
+        <v>1298.3</v>
       </c>
       <c r="E89" t="n">
-        <v>1307.23</v>
+        <v>1307.28</v>
       </c>
       <c r="F89" t="n">
-        <v>33482</v>
+        <v>33479</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -11483,13 +11483,13 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>1302.33</v>
+        <v>1302.35</v>
       </c>
       <c r="D90" t="n">
-        <v>1298.29</v>
+        <v>1298.31</v>
       </c>
       <c r="E90" t="n">
-        <v>1306.37</v>
+        <v>1306.39</v>
       </c>
       <c r="F90" t="n">
         <v>39406</v>
@@ -11634,13 +11634,13 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>1298.46</v>
+        <v>1298.48</v>
       </c>
       <c r="D91" t="n">
-        <v>1290.7</v>
+        <v>1290.73</v>
       </c>
       <c r="E91" t="n">
-        <v>1306.22</v>
+        <v>1306.24</v>
       </c>
       <c r="F91" t="n">
         <v>7140</v>
@@ -11785,13 +11785,13 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>1292.8</v>
+        <v>1292.83</v>
       </c>
       <c r="D92" t="n">
-        <v>1289.09</v>
+        <v>1289.12</v>
       </c>
       <c r="E92" t="n">
-        <v>1296.5</v>
+        <v>1296.53</v>
       </c>
       <c r="F92" t="n">
         <v>55240</v>
@@ -11936,13 +11936,13 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>1288.19</v>
+        <v>1288.25</v>
       </c>
       <c r="D93" t="n">
-        <v>1280.88</v>
+        <v>1280.95</v>
       </c>
       <c r="E93" t="n">
-        <v>1295.49</v>
+        <v>1295.55</v>
       </c>
       <c r="F93" t="n">
         <v>8662</v>
@@ -12007,13 +12007,13 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1287.56</v>
+        <v>1287.67</v>
       </c>
       <c r="D94" t="n">
-        <v>1284.21</v>
+        <v>1284.32</v>
       </c>
       <c r="E94" t="n">
-        <v>1290.9</v>
+        <v>1291.02</v>
       </c>
       <c r="F94" t="n">
         <v>75754</v>
@@ -12158,16 +12158,16 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1286.67</v>
+        <v>1286.84</v>
       </c>
       <c r="D95" t="n">
-        <v>1278.33</v>
+        <v>1278.5</v>
       </c>
       <c r="E95" t="n">
-        <v>1295.01</v>
+        <v>1295.18</v>
       </c>
       <c r="F95" t="n">
-        <v>5744</v>
+        <v>5747</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
@@ -12309,7 +12309,7 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>1285.81</v>
+        <v>1285.82</v>
       </c>
       <c r="D96" t="n">
         <v>1275.34</v>
@@ -12460,16 +12460,16 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1285.56</v>
+        <v>1285.55</v>
       </c>
       <c r="D97" t="n">
-        <v>1278.34</v>
+        <v>1278.33</v>
       </c>
       <c r="E97" t="n">
         <v>1292.78</v>
       </c>
       <c r="F97" t="n">
-        <v>8545</v>
+        <v>8546</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
@@ -12611,13 +12611,13 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>1285.27</v>
+        <v>1285.33</v>
       </c>
       <c r="D98" t="n">
-        <v>1275.3</v>
+        <v>1275.36</v>
       </c>
       <c r="E98" t="n">
-        <v>1295.25</v>
+        <v>1295.31</v>
       </c>
       <c r="F98" t="n">
         <v>3749</v>
@@ -12762,13 +12762,13 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>1278.81</v>
+        <v>1278.91</v>
       </c>
       <c r="D99" t="n">
-        <v>1271.95</v>
+        <v>1272.05</v>
       </c>
       <c r="E99" t="n">
-        <v>1285.66</v>
+        <v>1285.77</v>
       </c>
       <c r="F99" t="n">
         <v>10072</v>
@@ -12913,13 +12913,13 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>1276.22</v>
+        <v>1276.25</v>
       </c>
       <c r="D100" t="n">
-        <v>1270.9</v>
+        <v>1270.92</v>
       </c>
       <c r="E100" t="n">
-        <v>1281.55</v>
+        <v>1281.58</v>
       </c>
       <c r="F100" t="n">
         <v>19659</v>
@@ -13064,13 +13064,13 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1275.49</v>
+        <v>1275.51</v>
       </c>
       <c r="D101" t="n">
-        <v>1268.92</v>
+        <v>1268.95</v>
       </c>
       <c r="E101" t="n">
-        <v>1282.06</v>
+        <v>1282.08</v>
       </c>
       <c r="F101" t="n">
         <v>9866</v>
@@ -13215,13 +13215,13 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>1275.13</v>
+        <v>1275.2</v>
       </c>
       <c r="D102" t="n">
-        <v>1271.56</v>
+        <v>1271.63</v>
       </c>
       <c r="E102" t="n">
-        <v>1278.71</v>
+        <v>1278.78</v>
       </c>
       <c r="F102" t="n">
         <v>156876</v>
@@ -13366,13 +13366,13 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>1273.45</v>
+        <v>1273.48</v>
       </c>
       <c r="D103" t="n">
-        <v>1267.57</v>
+        <v>1267.6</v>
       </c>
       <c r="E103" t="n">
-        <v>1279.34</v>
+        <v>1279.37</v>
       </c>
       <c r="F103" t="n">
         <v>14681</v>
@@ -13517,13 +13517,13 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>1269.92</v>
+        <v>1269.95</v>
       </c>
       <c r="D104" t="n">
-        <v>1261.8</v>
+        <v>1261.83</v>
       </c>
       <c r="E104" t="n">
-        <v>1278.04</v>
+        <v>1278.07</v>
       </c>
       <c r="F104" t="n">
         <v>5432</v>
@@ -13668,13 +13668,13 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>1266.27</v>
+        <v>1266.32</v>
       </c>
       <c r="D105" t="n">
-        <v>1261.41</v>
+        <v>1261.45</v>
       </c>
       <c r="E105" t="n">
-        <v>1271.13</v>
+        <v>1271.18</v>
       </c>
       <c r="F105" t="n">
         <v>27124</v>
@@ -13819,13 +13819,13 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>1265.02</v>
+        <v>1265.14</v>
       </c>
       <c r="D106" t="n">
-        <v>1261.24</v>
+        <v>1261.35</v>
       </c>
       <c r="E106" t="n">
-        <v>1268.81</v>
+        <v>1268.93</v>
       </c>
       <c r="F106" t="n">
         <v>54611</v>
@@ -13970,13 +13970,13 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>1263.36</v>
+        <v>1263.47</v>
       </c>
       <c r="D107" t="n">
-        <v>1257.08</v>
+        <v>1257.19</v>
       </c>
       <c r="E107" t="n">
-        <v>1269.64</v>
+        <v>1269.75</v>
       </c>
       <c r="F107" t="n">
         <v>15147</v>
@@ -14121,13 +14121,13 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>1260.73</v>
+        <v>1260.77</v>
       </c>
       <c r="D108" t="n">
-        <v>1256.41</v>
+        <v>1256.45</v>
       </c>
       <c r="E108" t="n">
-        <v>1265.05</v>
+        <v>1265.09</v>
       </c>
       <c r="F108" t="n">
         <v>77554</v>
@@ -14192,13 +14192,13 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>1260.71</v>
+        <v>1260.76</v>
       </c>
       <c r="D109" t="n">
-        <v>1255.78</v>
+        <v>1255.82</v>
       </c>
       <c r="E109" t="n">
-        <v>1265.65</v>
+        <v>1265.7</v>
       </c>
       <c r="F109" t="n">
         <v>37325</v>
@@ -14343,13 +14343,13 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>1255.44</v>
+        <v>1255.47</v>
       </c>
       <c r="D110" t="n">
-        <v>1250.88</v>
+        <v>1250.91</v>
       </c>
       <c r="E110" t="n">
-        <v>1260.01</v>
+        <v>1260.04</v>
       </c>
       <c r="F110" t="n">
         <v>24126</v>
@@ -14645,13 +14645,13 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>1249.06</v>
+        <v>1249.11</v>
       </c>
       <c r="D112" t="n">
-        <v>1242.47</v>
+        <v>1242.52</v>
       </c>
       <c r="E112" t="n">
-        <v>1255.65</v>
+        <v>1255.71</v>
       </c>
       <c r="F112" t="n">
         <v>10140</v>
@@ -14796,13 +14796,13 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>1238.37</v>
+        <v>1238.44</v>
       </c>
       <c r="D113" t="n">
-        <v>1231.15</v>
+        <v>1231.22</v>
       </c>
       <c r="E113" t="n">
-        <v>1245.59</v>
+        <v>1245.66</v>
       </c>
       <c r="F113" t="n">
         <v>8858</v>
@@ -14867,13 +14867,13 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>1236.58</v>
+        <v>1236.63</v>
       </c>
       <c r="D114" t="n">
-        <v>1227.49</v>
+        <v>1227.53</v>
       </c>
       <c r="E114" t="n">
-        <v>1245.67</v>
+        <v>1245.72</v>
       </c>
       <c r="F114" t="n">
         <v>4781</v>
@@ -15018,13 +15018,13 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>1232.97</v>
+        <v>1233.03</v>
       </c>
       <c r="D115" t="n">
-        <v>1227.42</v>
+        <v>1227.47</v>
       </c>
       <c r="E115" t="n">
-        <v>1238.53</v>
+        <v>1238.58</v>
       </c>
       <c r="F115" t="n">
         <v>26195</v>
@@ -15169,13 +15169,13 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>1232.01</v>
+        <v>1232.08</v>
       </c>
       <c r="D116" t="n">
-        <v>1226.73</v>
+        <v>1226.8</v>
       </c>
       <c r="E116" t="n">
-        <v>1237.29</v>
+        <v>1237.35</v>
       </c>
       <c r="F116" t="n">
         <v>39302</v>
@@ -15320,13 +15320,13 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>1228.21</v>
+        <v>1228.26</v>
       </c>
       <c r="D117" t="n">
-        <v>1223.66</v>
+        <v>1223.71</v>
       </c>
       <c r="E117" t="n">
-        <v>1232.76</v>
+        <v>1232.81</v>
       </c>
       <c r="F117" t="n">
         <v>51416</v>
@@ -15471,13 +15471,13 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>1225.69</v>
+        <v>1225.73</v>
       </c>
       <c r="D118" t="n">
-        <v>1220.91</v>
+        <v>1220.95</v>
       </c>
       <c r="E118" t="n">
-        <v>1230.47</v>
+        <v>1230.51</v>
       </c>
       <c r="F118" t="n">
         <v>54036</v>
@@ -15542,13 +15542,13 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>1222.24</v>
+        <v>1222.28</v>
       </c>
       <c r="D119" t="n">
-        <v>1215.28</v>
+        <v>1215.32</v>
       </c>
       <c r="E119" t="n">
-        <v>1229.2</v>
+        <v>1229.24</v>
       </c>
       <c r="F119" t="n">
         <v>9818</v>
@@ -15693,13 +15693,13 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>1222.2</v>
+        <v>1222.26</v>
       </c>
       <c r="D120" t="n">
-        <v>1218.47</v>
+        <v>1218.54</v>
       </c>
       <c r="E120" t="n">
-        <v>1225.92</v>
+        <v>1225.99</v>
       </c>
       <c r="F120" t="n">
         <v>104642</v>
@@ -15847,10 +15847,10 @@
         <v>1220.36</v>
       </c>
       <c r="D121" t="n">
-        <v>1209.68</v>
+        <v>1209.67</v>
       </c>
       <c r="E121" t="n">
-        <v>1231.05</v>
+        <v>1231.04</v>
       </c>
       <c r="F121" t="n">
         <v>2896</v>
@@ -16146,13 +16146,13 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>1211.51</v>
+        <v>1211.57</v>
       </c>
       <c r="D123" t="n">
-        <v>1200.7</v>
+        <v>1200.76</v>
       </c>
       <c r="E123" t="n">
-        <v>1222.32</v>
+        <v>1222.38</v>
       </c>
       <c r="F123" t="n">
         <v>4652</v>
@@ -16297,13 +16297,13 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>1211.04</v>
+        <v>1211.05</v>
       </c>
       <c r="D124" t="n">
-        <v>1206.92</v>
+        <v>1206.93</v>
       </c>
       <c r="E124" t="n">
-        <v>1215.16</v>
+        <v>1215.17</v>
       </c>
       <c r="F124" t="n">
         <v>49605</v>
@@ -16448,13 +16448,13 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>1207.31</v>
+        <v>1207.35</v>
       </c>
       <c r="D125" t="n">
-        <v>1196.2</v>
+        <v>1196.24</v>
       </c>
       <c r="E125" t="n">
-        <v>1218.42</v>
+        <v>1218.46</v>
       </c>
       <c r="F125" t="n">
         <v>3090</v>
@@ -16599,13 +16599,13 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>1202.63</v>
+        <v>1202.68</v>
       </c>
       <c r="D126" t="n">
-        <v>1196.51</v>
+        <v>1196.56</v>
       </c>
       <c r="E126" t="n">
-        <v>1208.75</v>
+        <v>1208.8</v>
       </c>
       <c r="F126" t="n">
         <v>21741</v>
@@ -16750,13 +16750,13 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>1198.53</v>
+        <v>1198.63</v>
       </c>
       <c r="D127" t="n">
-        <v>1194.47</v>
+        <v>1194.56</v>
       </c>
       <c r="E127" t="n">
-        <v>1202.6</v>
+        <v>1202.7</v>
       </c>
       <c r="F127" t="n">
         <v>46616</v>
@@ -16901,13 +16901,13 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>1196.77</v>
+        <v>1196.81</v>
       </c>
       <c r="D128" t="n">
-        <v>1191.62</v>
+        <v>1191.65</v>
       </c>
       <c r="E128" t="n">
-        <v>1201.92</v>
+        <v>1201.96</v>
       </c>
       <c r="F128" t="n">
         <v>25055</v>
@@ -17052,13 +17052,13 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>1195.89</v>
+        <v>1195.94</v>
       </c>
       <c r="D129" t="n">
-        <v>1191.62</v>
+        <v>1191.67</v>
       </c>
       <c r="E129" t="n">
-        <v>1200.16</v>
+        <v>1200.21</v>
       </c>
       <c r="F129" t="n">
         <v>73503</v>
@@ -17203,13 +17203,13 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>1193.8</v>
+        <v>1193.88</v>
       </c>
       <c r="D130" t="n">
-        <v>1187.69</v>
+        <v>1187.76</v>
       </c>
       <c r="E130" t="n">
-        <v>1199.92</v>
+        <v>1199.99</v>
       </c>
       <c r="F130" t="n">
         <v>32191</v>
@@ -17277,7 +17277,7 @@
         <v>1190.44</v>
       </c>
       <c r="D131" t="n">
-        <v>1183.26</v>
+        <v>1183.27</v>
       </c>
       <c r="E131" t="n">
         <v>1197.62</v>
@@ -17425,13 +17425,13 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>1189.75</v>
+        <v>1189.8</v>
       </c>
       <c r="D132" t="n">
-        <v>1182.62</v>
+        <v>1182.68</v>
       </c>
       <c r="E132" t="n">
-        <v>1196.88</v>
+        <v>1196.93</v>
       </c>
       <c r="F132" t="n">
         <v>17839</v>
@@ -17576,13 +17576,13 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>1183.42</v>
+        <v>1183.46</v>
       </c>
       <c r="D133" t="n">
-        <v>1173.96</v>
+        <v>1174.01</v>
       </c>
       <c r="E133" t="n">
-        <v>1192.87</v>
+        <v>1192.92</v>
       </c>
       <c r="F133" t="n">
         <v>8214</v>
@@ -17727,13 +17727,13 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>1183.11</v>
+        <v>1183.19</v>
       </c>
       <c r="D134" t="n">
-        <v>1171.6</v>
+        <v>1171.68</v>
       </c>
       <c r="E134" t="n">
-        <v>1194.63</v>
+        <v>1194.71</v>
       </c>
       <c r="F134" t="n">
         <v>4932</v>
@@ -17878,13 +17878,13 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>1182.71</v>
+        <v>1182.74</v>
       </c>
       <c r="D135" t="n">
-        <v>1175.88</v>
+        <v>1175.91</v>
       </c>
       <c r="E135" t="n">
-        <v>1189.54</v>
+        <v>1189.58</v>
       </c>
       <c r="F135" t="n">
         <v>15483</v>
@@ -18029,13 +18029,13 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>1181</v>
+        <v>1181.07</v>
       </c>
       <c r="D136" t="n">
-        <v>1172.99</v>
+        <v>1173.07</v>
       </c>
       <c r="E136" t="n">
-        <v>1189</v>
+        <v>1189.07</v>
       </c>
       <c r="F136" t="n">
         <v>12637</v>
@@ -18100,13 +18100,13 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>1180.92</v>
+        <v>1181.02</v>
       </c>
       <c r="D137" t="n">
-        <v>1171.24</v>
+        <v>1171.34</v>
       </c>
       <c r="E137" t="n">
-        <v>1190.6</v>
+        <v>1190.7</v>
       </c>
       <c r="F137" t="n">
         <v>7968</v>
@@ -18171,13 +18171,13 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>1180.86</v>
+        <v>1180.97</v>
       </c>
       <c r="D138" t="n">
-        <v>1172.17</v>
+        <v>1172.28</v>
       </c>
       <c r="E138" t="n">
-        <v>1189.54</v>
+        <v>1189.65</v>
       </c>
       <c r="F138" t="n">
         <v>6638</v>
@@ -18322,13 +18322,13 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>1179.57</v>
+        <v>1179.75</v>
       </c>
       <c r="D139" t="n">
-        <v>1173.49</v>
+        <v>1173.67</v>
       </c>
       <c r="E139" t="n">
-        <v>1185.64</v>
+        <v>1185.82</v>
       </c>
       <c r="F139" t="n">
         <v>23893</v>
@@ -18473,13 +18473,13 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>1178.21</v>
+        <v>1178.29</v>
       </c>
       <c r="D140" t="n">
-        <v>1172.3</v>
+        <v>1172.37</v>
       </c>
       <c r="E140" t="n">
-        <v>1184.13</v>
+        <v>1184.21</v>
       </c>
       <c r="F140" t="n">
         <v>32832</v>
@@ -18544,13 +18544,13 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>1177.88</v>
+        <v>1177.92</v>
       </c>
       <c r="D141" t="n">
-        <v>1166.68</v>
+        <v>1166.71</v>
       </c>
       <c r="E141" t="n">
-        <v>1189.09</v>
+        <v>1189.12</v>
       </c>
       <c r="F141" t="n">
         <v>3188</v>
@@ -18695,13 +18695,13 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>1176.77</v>
+        <v>1176.79</v>
       </c>
       <c r="D142" t="n">
-        <v>1166.94</v>
+        <v>1166.96</v>
       </c>
       <c r="E142" t="n">
-        <v>1186.59</v>
+        <v>1186.61</v>
       </c>
       <c r="F142" t="n">
         <v>6535</v>
@@ -18846,13 +18846,13 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>1173.9</v>
+        <v>1173.99</v>
       </c>
       <c r="D143" t="n">
-        <v>1163.48</v>
+        <v>1163.57</v>
       </c>
       <c r="E143" t="n">
-        <v>1184.33</v>
+        <v>1184.42</v>
       </c>
       <c r="F143" t="n">
         <v>5006</v>
@@ -18997,13 +18997,13 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>1171.52</v>
+        <v>1171.57</v>
       </c>
       <c r="D144" t="n">
-        <v>1165.3</v>
+        <v>1165.35</v>
       </c>
       <c r="E144" t="n">
-        <v>1177.73</v>
+        <v>1177.78</v>
       </c>
       <c r="F144" t="n">
         <v>22479</v>
@@ -19148,13 +19148,13 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>1170.48</v>
+        <v>1170.47</v>
       </c>
       <c r="D145" t="n">
-        <v>1163.06</v>
+        <v>1163.05</v>
       </c>
       <c r="E145" t="n">
-        <v>1177.89</v>
+        <v>1177.88</v>
       </c>
       <c r="F145" t="n">
         <v>16056</v>
@@ -19299,13 +19299,13 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>1169.91</v>
+        <v>1169.95</v>
       </c>
       <c r="D146" t="n">
-        <v>1163.99</v>
+        <v>1164.04</v>
       </c>
       <c r="E146" t="n">
-        <v>1175.83</v>
+        <v>1175.87</v>
       </c>
       <c r="F146" t="n">
         <v>17766</v>
@@ -19450,13 +19450,13 @@
         </is>
       </c>
       <c r="C147" t="n">
-        <v>1169.58</v>
+        <v>1169.61</v>
       </c>
       <c r="D147" t="n">
-        <v>1164.08</v>
+        <v>1164.1</v>
       </c>
       <c r="E147" t="n">
-        <v>1175.09</v>
+        <v>1175.12</v>
       </c>
       <c r="F147" t="n">
         <v>38492</v>
@@ -19601,13 +19601,13 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>1166.29</v>
+        <v>1166.33</v>
       </c>
       <c r="D148" t="n">
-        <v>1158.22</v>
+        <v>1158.25</v>
       </c>
       <c r="E148" t="n">
-        <v>1174.37</v>
+        <v>1174.4</v>
       </c>
       <c r="F148" t="n">
         <v>10224</v>
@@ -19752,13 +19752,13 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>1165.66</v>
+        <v>1165.71</v>
       </c>
       <c r="D149" t="n">
-        <v>1157.96</v>
+        <v>1158.01</v>
       </c>
       <c r="E149" t="n">
-        <v>1173.35</v>
+        <v>1173.4</v>
       </c>
       <c r="F149" t="n">
         <v>7936</v>
@@ -19903,13 +19903,13 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>1163.52</v>
+        <v>1163.54</v>
       </c>
       <c r="D150" t="n">
-        <v>1151.58</v>
+        <v>1151.6</v>
       </c>
       <c r="E150" t="n">
-        <v>1175.46</v>
+        <v>1175.48</v>
       </c>
       <c r="F150" t="n">
         <v>3777</v>
@@ -20054,13 +20054,13 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>1155.93</v>
+        <v>1155.81</v>
       </c>
       <c r="D151" t="n">
-        <v>1144.43</v>
+        <v>1144.31</v>
       </c>
       <c r="E151" t="n">
-        <v>1167.44</v>
+        <v>1167.31</v>
       </c>
       <c r="F151" t="n">
         <v>3231</v>
@@ -20205,13 +20205,13 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>1154.84</v>
+        <v>1154.92</v>
       </c>
       <c r="D152" t="n">
-        <v>1146.45</v>
+        <v>1146.53</v>
       </c>
       <c r="E152" t="n">
-        <v>1163.23</v>
+        <v>1163.32</v>
       </c>
       <c r="F152" t="n">
         <v>6837</v>
@@ -20356,13 +20356,13 @@
         </is>
       </c>
       <c r="C153" t="n">
-        <v>1154.03</v>
+        <v>1154.04</v>
       </c>
       <c r="D153" t="n">
-        <v>1141.41</v>
+        <v>1141.42</v>
       </c>
       <c r="E153" t="n">
-        <v>1166.65</v>
+        <v>1166.66</v>
       </c>
       <c r="F153" t="n">
         <v>3585</v>
@@ -20507,13 +20507,13 @@
         </is>
       </c>
       <c r="C154" t="n">
-        <v>1151.07</v>
+        <v>1151.12</v>
       </c>
       <c r="D154" t="n">
-        <v>1137.86</v>
+        <v>1137.91</v>
       </c>
       <c r="E154" t="n">
-        <v>1164.28</v>
+        <v>1164.33</v>
       </c>
       <c r="F154" t="n">
         <v>4155</v>
@@ -20658,13 +20658,13 @@
         </is>
       </c>
       <c r="C155" t="n">
-        <v>1150.73</v>
+        <v>1150.79</v>
       </c>
       <c r="D155" t="n">
-        <v>1135.34</v>
+        <v>1135.4</v>
       </c>
       <c r="E155" t="n">
-        <v>1166.12</v>
+        <v>1166.19</v>
       </c>
       <c r="F155" t="n">
         <v>1679</v>
@@ -20809,13 +20809,13 @@
         </is>
       </c>
       <c r="C156" t="n">
-        <v>1148.81</v>
+        <v>1148.89</v>
       </c>
       <c r="D156" t="n">
-        <v>1136.51</v>
+        <v>1136.6</v>
       </c>
       <c r="E156" t="n">
-        <v>1161.1</v>
+        <v>1161.19</v>
       </c>
       <c r="F156" t="n">
         <v>2572</v>
@@ -20960,13 +20960,13 @@
         </is>
       </c>
       <c r="C157" t="n">
-        <v>1148.34</v>
+        <v>1148.37</v>
       </c>
       <c r="D157" t="n">
-        <v>1141.69</v>
+        <v>1141.72</v>
       </c>
       <c r="E157" t="n">
-        <v>1155</v>
+        <v>1155.03</v>
       </c>
       <c r="F157" t="n">
         <v>19402</v>
@@ -21111,13 +21111,13 @@
         </is>
       </c>
       <c r="C158" t="n">
-        <v>1147.93</v>
+        <v>1147.99</v>
       </c>
       <c r="D158" t="n">
-        <v>1138.67</v>
+        <v>1138.73</v>
       </c>
       <c r="E158" t="n">
-        <v>1157.19</v>
+        <v>1157.25</v>
       </c>
       <c r="F158" t="n">
         <v>7044</v>
@@ -21262,13 +21262,13 @@
         </is>
       </c>
       <c r="C159" t="n">
-        <v>1145.74</v>
+        <v>1145.85</v>
       </c>
       <c r="D159" t="n">
-        <v>1128.61</v>
+        <v>1128.73</v>
       </c>
       <c r="E159" t="n">
-        <v>1162.86</v>
+        <v>1162.98</v>
       </c>
       <c r="F159" t="n">
         <v>1295</v>
@@ -21413,13 +21413,13 @@
         </is>
       </c>
       <c r="C160" t="n">
-        <v>1142.6</v>
+        <v>1142.65</v>
       </c>
       <c r="D160" t="n">
-        <v>1132.71</v>
+        <v>1132.75</v>
       </c>
       <c r="E160" t="n">
-        <v>1152.5</v>
+        <v>1152.55</v>
       </c>
       <c r="F160" t="n">
         <v>4737</v>
@@ -21564,13 +21564,13 @@
         </is>
       </c>
       <c r="C161" t="n">
-        <v>1141.89</v>
+        <v>1141.94</v>
       </c>
       <c r="D161" t="n">
-        <v>1135.46</v>
+        <v>1135.51</v>
       </c>
       <c r="E161" t="n">
-        <v>1148.33</v>
+        <v>1148.38</v>
       </c>
       <c r="F161" t="n">
         <v>12297</v>
@@ -21715,13 +21715,13 @@
         </is>
       </c>
       <c r="C162" t="n">
-        <v>1140.29</v>
+        <v>1140.32</v>
       </c>
       <c r="D162" t="n">
-        <v>1133.56</v>
+        <v>1133.59</v>
       </c>
       <c r="E162" t="n">
-        <v>1147.02</v>
+        <v>1147.05</v>
       </c>
       <c r="F162" t="n">
         <v>19174</v>
@@ -21866,13 +21866,13 @@
         </is>
       </c>
       <c r="C163" t="n">
-        <v>1139.61</v>
+        <v>1139.7</v>
       </c>
       <c r="D163" t="n">
-        <v>1132.9</v>
+        <v>1132.98</v>
       </c>
       <c r="E163" t="n">
-        <v>1146.33</v>
+        <v>1146.42</v>
       </c>
       <c r="F163" t="n">
         <v>19367</v>
@@ -22017,13 +22017,13 @@
         </is>
       </c>
       <c r="C164" t="n">
-        <v>1137.26</v>
+        <v>1137.36</v>
       </c>
       <c r="D164" t="n">
-        <v>1126.3</v>
+        <v>1126.4</v>
       </c>
       <c r="E164" t="n">
-        <v>1148.23</v>
+        <v>1148.33</v>
       </c>
       <c r="F164" t="n">
         <v>4964</v>
@@ -22164,36 +22164,36 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>codellama-34b-instruct</t>
+          <t>gemma-7b-it</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>1135.3</v>
+        <v>1135.39</v>
       </c>
       <c r="D165" t="n">
-        <v>1126.39</v>
+        <v>1125.88</v>
       </c>
       <c r="E165" t="n">
-        <v>1144.2</v>
+        <v>1144.9</v>
       </c>
       <c r="F165" t="n">
-        <v>7366</v>
+        <v>8925</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Llama 2 Community</t>
+          <t>Gemma license</t>
         </is>
       </c>
       <c r="I165" t="n">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="J165" t="n">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="K165" t="inlineStr">
         <is>
@@ -22206,22 +22206,22 @@
         </is>
       </c>
       <c r="M165" t="n">
-        <v>68</v>
+        <v>14</v>
       </c>
       <c r="N165" t="n">
-        <v>85</v>
+        <v>17.5</v>
       </c>
       <c r="O165" t="n">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="P165" t="n">
-        <v>42.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Q165" t="n">
-        <v>17</v>
+        <v>3.5</v>
       </c>
       <c r="R165" t="n">
-        <v>21.2</v>
+        <v>4.4</v>
       </c>
       <c r="S165" s="6" t="inlineStr">
         <is>
@@ -22238,9 +22238,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="V165" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="V165" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W165" s="6" t="inlineStr">
@@ -22300,7 +22300,7 @@
       </c>
       <c r="AH165" t="inlineStr">
         <is>
-          <t>RTX PRO 6000</t>
+          <t>H100 SXM</t>
         </is>
       </c>
       <c r="AI165" t="inlineStr">
@@ -22315,36 +22315,36 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>gemma-7b-it</t>
+          <t>codellama-34b-instruct</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>1135.24</v>
+        <v>1135.36</v>
       </c>
       <c r="D166" t="n">
-        <v>1125.74</v>
+        <v>1126.45</v>
       </c>
       <c r="E166" t="n">
-        <v>1144.75</v>
+        <v>1144.26</v>
       </c>
       <c r="F166" t="n">
-        <v>8925</v>
+        <v>7366</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Gemma license</t>
+          <t>Llama 2 Community</t>
         </is>
       </c>
       <c r="I166" t="n">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="J166" t="n">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="K166" t="inlineStr">
         <is>
@@ -22357,22 +22357,22 @@
         </is>
       </c>
       <c r="M166" t="n">
-        <v>14</v>
+        <v>68</v>
       </c>
       <c r="N166" t="n">
-        <v>17.5</v>
+        <v>85</v>
       </c>
       <c r="O166" t="n">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="P166" t="n">
-        <v>8.800000000000001</v>
+        <v>42.5</v>
       </c>
       <c r="Q166" t="n">
-        <v>3.5</v>
+        <v>17</v>
       </c>
       <c r="R166" t="n">
-        <v>4.4</v>
+        <v>21.2</v>
       </c>
       <c r="S166" s="6" t="inlineStr">
         <is>
@@ -22389,9 +22389,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="V166" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="V166" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="W166" s="6" t="inlineStr">
@@ -22451,7 +22451,7 @@
       </c>
       <c r="AH166" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>RTX PRO 6000</t>
         </is>
       </c>
       <c r="AI166" t="inlineStr">
@@ -22470,13 +22470,13 @@
         </is>
       </c>
       <c r="C167" t="n">
-        <v>1129.76</v>
+        <v>1129.79</v>
       </c>
       <c r="D167" t="n">
-        <v>1120.91</v>
+        <v>1120.94</v>
       </c>
       <c r="E167" t="n">
-        <v>1138.6</v>
+        <v>1138.63</v>
       </c>
       <c r="F167" t="n">
         <v>11118</v>
@@ -22621,13 +22621,13 @@
         </is>
       </c>
       <c r="C168" t="n">
-        <v>1127.96</v>
+        <v>1128.05</v>
       </c>
       <c r="D168" t="n">
-        <v>1120.54</v>
+        <v>1120.62</v>
       </c>
       <c r="E168" t="n">
-        <v>1135.39</v>
+        <v>1135.47</v>
       </c>
       <c r="F168" t="n">
         <v>20685</v>
@@ -22772,13 +22772,13 @@
         </is>
       </c>
       <c r="C169" t="n">
-        <v>1127.21</v>
+        <v>1127.23</v>
       </c>
       <c r="D169" t="n">
-        <v>1120.81</v>
+        <v>1120.83</v>
       </c>
       <c r="E169" t="n">
-        <v>1133.6</v>
+        <v>1133.62</v>
       </c>
       <c r="F169" t="n">
         <v>20118</v>
@@ -22923,13 +22923,13 @@
         </is>
       </c>
       <c r="C170" t="n">
-        <v>1126.01</v>
+        <v>1126.07</v>
       </c>
       <c r="D170" t="n">
-        <v>1113.86</v>
+        <v>1113.92</v>
       </c>
       <c r="E170" t="n">
-        <v>1138.16</v>
+        <v>1138.22</v>
       </c>
       <c r="F170" t="n">
         <v>2921</v>
@@ -23074,13 +23074,13 @@
         </is>
       </c>
       <c r="C171" t="n">
-        <v>1125.61</v>
+        <v>1125.66</v>
       </c>
       <c r="D171" t="n">
-        <v>1109.94</v>
+        <v>1109.99</v>
       </c>
       <c r="E171" t="n">
-        <v>1141.28</v>
+        <v>1141.33</v>
       </c>
       <c r="F171" t="n">
         <v>1785</v>
@@ -23225,13 +23225,13 @@
         </is>
       </c>
       <c r="C172" t="n">
-        <v>1119.68</v>
+        <v>1119.77</v>
       </c>
       <c r="D172" t="n">
-        <v>1108.68</v>
+        <v>1108.77</v>
       </c>
       <c r="E172" t="n">
-        <v>1130.68</v>
+        <v>1130.77</v>
       </c>
       <c r="F172" t="n">
         <v>5182</v>
@@ -23376,13 +23376,13 @@
         </is>
       </c>
       <c r="C173" t="n">
-        <v>1117.89</v>
+        <v>1117.94</v>
       </c>
       <c r="D173" t="n">
-        <v>1099.69</v>
+        <v>1099.74</v>
       </c>
       <c r="E173" t="n">
-        <v>1136.09</v>
+        <v>1136.15</v>
       </c>
       <c r="F173" t="n">
         <v>1143</v>
@@ -23527,13 +23527,13 @@
         </is>
       </c>
       <c r="C174" t="n">
-        <v>1113.43</v>
+        <v>1113.62</v>
       </c>
       <c r="D174" t="n">
-        <v>1105.69</v>
+        <v>1105.88</v>
       </c>
       <c r="E174" t="n">
-        <v>1121.16</v>
+        <v>1121.35</v>
       </c>
       <c r="F174" t="n">
         <v>10854</v>
@@ -23678,13 +23678,13 @@
         </is>
       </c>
       <c r="C175" t="n">
-        <v>1113.33</v>
+        <v>1113.42</v>
       </c>
       <c r="D175" t="n">
-        <v>1104.16</v>
+        <v>1104.24</v>
       </c>
       <c r="E175" t="n">
-        <v>1122.51</v>
+        <v>1122.6</v>
       </c>
       <c r="F175" t="n">
         <v>6923</v>
@@ -23829,13 +23829,13 @@
         </is>
       </c>
       <c r="C176" t="n">
-        <v>1113.12</v>
+        <v>1113.19</v>
       </c>
       <c r="D176" t="n">
-        <v>1098.71</v>
+        <v>1098.78</v>
       </c>
       <c r="E176" t="n">
-        <v>1127.53</v>
+        <v>1127.6</v>
       </c>
       <c r="F176" t="n">
         <v>2199</v>
@@ -23980,13 +23980,13 @@
         </is>
       </c>
       <c r="C177" t="n">
-        <v>1110.2</v>
+        <v>1110.23</v>
       </c>
       <c r="D177" t="n">
-        <v>1102.32</v>
+        <v>1102.36</v>
       </c>
       <c r="E177" t="n">
-        <v>1118.07</v>
+        <v>1118.11</v>
       </c>
       <c r="F177" t="n">
         <v>8045</v>
@@ -24131,13 +24131,13 @@
         </is>
       </c>
       <c r="C178" t="n">
-        <v>1108.3</v>
+        <v>1108.4</v>
       </c>
       <c r="D178" t="n">
-        <v>1099.01</v>
+        <v>1099.1</v>
       </c>
       <c r="E178" t="n">
-        <v>1117.6</v>
+        <v>1117.7</v>
       </c>
       <c r="F178" t="n">
         <v>8977</v>
@@ -24282,13 +24282,13 @@
         </is>
       </c>
       <c r="C179" t="n">
-        <v>1106.92</v>
+        <v>1106.94</v>
       </c>
       <c r="D179" t="n">
-        <v>1099.86</v>
+        <v>1099.88</v>
       </c>
       <c r="E179" t="n">
-        <v>1113.98</v>
+        <v>1114</v>
       </c>
       <c r="F179" t="n">
         <v>14148</v>
@@ -24433,13 +24433,13 @@
         </is>
       </c>
       <c r="C180" t="n">
-        <v>1090.82</v>
+        <v>1090.98</v>
       </c>
       <c r="D180" t="n">
-        <v>1079.31</v>
+        <v>1079.47</v>
       </c>
       <c r="E180" t="n">
-        <v>1102.33</v>
+        <v>1102.5</v>
       </c>
       <c r="F180" t="n">
         <v>4780</v>
@@ -24584,13 +24584,13 @@
         </is>
       </c>
       <c r="C181" t="n">
-        <v>1088.85</v>
+        <v>1088.96</v>
       </c>
       <c r="D181" t="n">
-        <v>1079.5</v>
+        <v>1079.61</v>
       </c>
       <c r="E181" t="n">
-        <v>1098.2</v>
+        <v>1098.31</v>
       </c>
       <c r="F181" t="n">
         <v>7597</v>
@@ -24735,13 +24735,13 @@
         </is>
       </c>
       <c r="C182" t="n">
-        <v>1073.32</v>
+        <v>1073.31</v>
       </c>
       <c r="D182" t="n">
-        <v>1062.14</v>
+        <v>1062.12</v>
       </c>
       <c r="E182" t="n">
-        <v>1084.51</v>
+        <v>1084.49</v>
       </c>
       <c r="F182" t="n">
         <v>6328</v>
@@ -24886,13 +24886,13 @@
         </is>
       </c>
       <c r="C183" t="n">
-        <v>1069.1</v>
+        <v>1069.18</v>
       </c>
       <c r="D183" t="n">
-        <v>1059.16</v>
+        <v>1059.24</v>
       </c>
       <c r="E183" t="n">
-        <v>1079.05</v>
+        <v>1079.13</v>
       </c>
       <c r="F183" t="n">
         <v>6965</v>
@@ -25037,13 +25037,13 @@
         </is>
       </c>
       <c r="C184" t="n">
-        <v>1066.11</v>
+        <v>1066.33</v>
       </c>
       <c r="D184" t="n">
-        <v>1054.59</v>
+        <v>1054.82</v>
       </c>
       <c r="E184" t="n">
-        <v>1077.62</v>
+        <v>1077.85</v>
       </c>
       <c r="F184" t="n">
         <v>5745</v>
@@ -25188,13 +25188,13 @@
         </is>
       </c>
       <c r="C185" t="n">
-        <v>1064.65</v>
+        <v>1064.8</v>
       </c>
       <c r="D185" t="n">
-        <v>1049.37</v>
+        <v>1049.52</v>
       </c>
       <c r="E185" t="n">
-        <v>1079.93</v>
+        <v>1080.08</v>
       </c>
       <c r="F185" t="n">
         <v>1743</v>
@@ -25339,13 +25339,13 @@
         </is>
       </c>
       <c r="C186" t="n">
-        <v>1060.5</v>
+        <v>1060.65</v>
       </c>
       <c r="D186" t="n">
-        <v>1048.47</v>
+        <v>1048.62</v>
       </c>
       <c r="E186" t="n">
-        <v>1072.52</v>
+        <v>1072.67</v>
       </c>
       <c r="F186" t="n">
         <v>3924</v>
@@ -25490,13 +25490,13 @@
         </is>
       </c>
       <c r="C187" t="n">
-        <v>1054.71</v>
+        <v>1054.8</v>
       </c>
       <c r="D187" t="n">
-        <v>1043.03</v>
+        <v>1043.11</v>
       </c>
       <c r="E187" t="n">
-        <v>1066.4</v>
+        <v>1066.48</v>
       </c>
       <c r="F187" t="n">
         <v>4658</v>
@@ -25641,13 +25641,13 @@
         </is>
       </c>
       <c r="C188" t="n">
-        <v>1039.99</v>
+        <v>1040.1</v>
       </c>
       <c r="D188" t="n">
-        <v>1028.54</v>
+        <v>1028.65</v>
       </c>
       <c r="E188" t="n">
-        <v>1051.43</v>
+        <v>1051.55</v>
       </c>
       <c r="F188" t="n">
         <v>4845</v>
@@ -25792,13 +25792,13 @@
         </is>
       </c>
       <c r="C189" t="n">
-        <v>1022.83</v>
+        <v>1022.91</v>
       </c>
       <c r="D189" t="n">
-        <v>1009.2</v>
+        <v>1009.28</v>
       </c>
       <c r="E189" t="n">
-        <v>1036.46</v>
+        <v>1036.54</v>
       </c>
       <c r="F189" t="n">
         <v>2658</v>
@@ -25943,13 +25943,13 @@
         </is>
       </c>
       <c r="C190" t="n">
-        <v>1020.72</v>
+        <v>1020.86</v>
       </c>
       <c r="D190" t="n">
-        <v>1009.8</v>
+        <v>1009.94</v>
       </c>
       <c r="E190" t="n">
-        <v>1031.64</v>
+        <v>1031.79</v>
       </c>
       <c r="F190" t="n">
         <v>6310</v>
@@ -26094,13 +26094,13 @@
         </is>
       </c>
       <c r="C191" t="n">
-        <v>994.24</v>
+        <v>994.3049999999999</v>
       </c>
       <c r="D191" t="n">
-        <v>981.621</v>
+        <v>981.684</v>
       </c>
       <c r="E191" t="n">
-        <v>1006.86</v>
+        <v>1006.92</v>
       </c>
       <c r="F191" t="n">
         <v>4914</v>
@@ -26245,13 +26245,13 @@
         </is>
       </c>
       <c r="C192" t="n">
-        <v>990.008</v>
+        <v>990.131</v>
       </c>
       <c r="D192" t="n">
-        <v>977.578</v>
+        <v>977.7</v>
       </c>
       <c r="E192" t="n">
-        <v>1002.44</v>
+        <v>1002.56</v>
       </c>
       <c r="F192" t="n">
         <v>4203</v>
@@ -26396,13 +26396,13 @@
         </is>
       </c>
       <c r="C193" t="n">
-        <v>978.747</v>
+        <v>978.949</v>
       </c>
       <c r="D193" t="n">
-        <v>965.144</v>
+        <v>965.3440000000001</v>
       </c>
       <c r="E193" t="n">
-        <v>992.351</v>
+        <v>992.554</v>
       </c>
       <c r="F193" t="n">
         <v>3412</v>
@@ -26547,13 +26547,13 @@
         </is>
       </c>
       <c r="C194" t="n">
-        <v>970.862</v>
+        <v>971.096</v>
       </c>
       <c r="D194" t="n">
-        <v>954.963</v>
+        <v>955.196</v>
       </c>
       <c r="E194" t="n">
-        <v>986.76</v>
+        <v>986.996</v>
       </c>
       <c r="F194" t="n">
         <v>2391</v>
@@ -26698,13 +26698,13 @@
         </is>
       </c>
       <c r="C195" t="n">
-        <v>951.274</v>
+        <v>951.361</v>
       </c>
       <c r="D195" t="n">
-        <v>938.466</v>
+        <v>938.552</v>
       </c>
       <c r="E195" t="n">
-        <v>964.082</v>
+        <v>964.17</v>
       </c>
       <c r="F195" t="n">
         <v>3287</v>
@@ -27727,38 +27727,38 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>deepseek-v3.2-exp</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
+          <t>qwen3-235b-a22b-instruct-2507</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>235</v>
+      </c>
+      <c r="C14" t="n">
+        <v>22</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>name_parsing</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>qwen3-235b-a22b-instruct-2507</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>235</v>
-      </c>
-      <c r="C15" t="n">
-        <v>22</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+          <t>deepseek-v3.2-exp</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -27795,29 +27795,37 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>deepseek-v3.1</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
+          <t>kimi-k2-0905-preview</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C18" t="n">
+        <v>32</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>override</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>kimi-k2-0905-preview</t>
+          <t>qwen3.5-122b-a10b</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1000</v>
+        <v>122</v>
       </c>
       <c r="C19" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -27826,14 +27834,14 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>name_parsing</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>deepseek-v3.1-thinking</t>
+          <t>deepseek-v3.1</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
@@ -27848,14 +27856,14 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>qwen3.5-122b-a10b</t>
+          <t>kimi-k2-0711-preview</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>122</v>
+        <v>1000</v>
       </c>
       <c r="C21" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -27864,30 +27872,22 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>override</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>kimi-k2-0711-preview</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="C22" t="n">
-        <v>32</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+          <t>deepseek-v3.1-thinking</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -27909,38 +27909,38 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>qwen3-vl-235b-a22b-instruct</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>235</v>
-      </c>
-      <c r="C24" t="n">
-        <v>22</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+          <t>deepseek-v3.1-terminus</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>deepseek-v3.1-terminus</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
+          <t>qwen3-vl-235b-a22b-instruct</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>235</v>
+      </c>
+      <c r="C25" t="n">
+        <v>22</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>name_parsing</t>
         </is>
       </c>
     </row>
@@ -28458,38 +28458,38 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>nvidia-nemotron-3-super-120b-a12b</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>120</v>
-      </c>
-      <c r="C51" t="n">
-        <v>12</v>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+          <t>minimax-m1</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr"/>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>minimax-m1</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr"/>
-      <c r="C52" t="inlineStr"/>
-      <c r="D52" t="inlineStr"/>
+          <t>nvidia-nemotron-3-super-120b-a12b</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>120</v>
+      </c>
+      <c r="C52" t="n">
+        <v>12</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>name_parsing</t>
         </is>
       </c>
     </row>
@@ -28870,18 +28870,18 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>qwen3-30b-a3b</t>
+          <t>molmo-2-8b</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="C71" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>moe</t>
+          <t>dense</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -28893,14 +28893,14 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>llama-4-maverick-17b-128e-instruct</t>
+          <t>qwen3-30b-a3b</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>400</v>
+        <v>30</v>
       </c>
       <c r="C72" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -28909,30 +28909,30 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>name_parsing</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>molmo-2-8b</t>
+          <t>llama-4-maverick-17b-128e-instruct</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>8</v>
+        <v>400</v>
       </c>
       <c r="C73" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>dense</t>
+          <t>moe</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>override</t>
         </is>
       </c>
     </row>
@@ -29038,14 +29038,14 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>nvidia-nemotron-3-nano-30b-a3b-bf16</t>
+          <t>gpt-oss-20b</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="C79" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -29054,21 +29054,21 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>override</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>gpt-oss-20b</t>
+          <t>nvidia-nemotron-3-nano-30b-a3b-bf16</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="C80" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -29077,7 +29077,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>name_parsing</t>
         </is>
       </c>
     </row>
@@ -30928,14 +30928,14 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>codellama-34b-instruct</t>
+          <t>gemma-7b-it</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="C165" t="n">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -30951,14 +30951,14 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>gemma-7b-it</t>
+          <t>codellama-34b-instruct</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="C166" t="n">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>

--- a/arena_enrichment/output/arena_leaderboard_enriched.xlsx
+++ b/arena_enrichment/output/arena_leaderboard_enriched.xlsx
@@ -675,16 +675,16 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>1470.67</v>
+        <v>1470.88</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1462.54</v>
+        <v>1462.92</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1478.79</v>
+        <v>1478.83</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>5096</v>
+        <v>5326</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
@@ -746,16 +746,16 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>1454.59</v>
+        <v>1455.5</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1449.11</v>
+        <v>1450.05</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1460.08</v>
+        <v>1460.94</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>13834</v>
+        <v>14093</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
@@ -897,16 +897,16 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>1452.25</v>
+        <v>1451.7</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1447.22</v>
+        <v>1446.67</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1457.28</v>
+        <v>1456.74</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>17758</v>
+        <v>17735</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
@@ -1048,16 +1048,16 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>1450.88</v>
+        <v>1450.51</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1443.29</v>
+        <v>1442.89</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1458.46</v>
+        <v>1458.12</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>6013</v>
+        <v>5957</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
@@ -1199,16 +1199,16 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1447.63</v>
+        <v>1446.75</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1442.39</v>
+        <v>1441.53</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1452.87</v>
+        <v>1451.96</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>15184</v>
+        <v>15408</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>1448.73</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>12179</v>
+        <v>12180</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
@@ -1421,16 +1421,16 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>1437.75</v>
+        <v>1438.47</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>1430.14</v>
+        <v>1430.85</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1445.35</v>
+        <v>1446.09</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>5950</v>
+        <v>5927</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
@@ -1572,16 +1572,16 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>1432.6</v>
+        <v>1432.5</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1426</v>
+        <v>1425.89</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1439.21</v>
+        <v>1439.11</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>8248</v>
+        <v>8241</v>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
@@ -1723,16 +1723,16 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>1429.95</v>
+        <v>1430.28</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>1426.43</v>
+        <v>1426.76</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1433.47</v>
+        <v>1433.8</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>46041</v>
+        <v>46203</v>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
@@ -1874,16 +1874,16 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>1425.81</v>
+        <v>1425.74</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>1421.87</v>
+        <v>1421.8</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1429.75</v>
+        <v>1429.68</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>35926</v>
+        <v>35917</v>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
@@ -1945,16 +1945,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1424.71</v>
+        <v>1424.73</v>
       </c>
       <c r="D12" t="n">
-        <v>1418.18</v>
+        <v>1418.2</v>
       </c>
       <c r="E12" t="n">
-        <v>1431.25</v>
+        <v>1431.26</v>
       </c>
       <c r="F12" t="n">
-        <v>9144</v>
+        <v>9146</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -2016,16 +2016,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1424.15</v>
+        <v>1423.8</v>
       </c>
       <c r="D13" t="n">
-        <v>1420.35</v>
+        <v>1420.01</v>
       </c>
       <c r="E13" t="n">
-        <v>1427.95</v>
+        <v>1427.6</v>
       </c>
       <c r="F13" t="n">
-        <v>41005</v>
+        <v>41182</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -2087,16 +2087,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1423.01</v>
+        <v>1422.95</v>
       </c>
       <c r="D14" t="n">
-        <v>1420.21</v>
+        <v>1420.15</v>
       </c>
       <c r="E14" t="n">
-        <v>1425.81</v>
+        <v>1425.75</v>
       </c>
       <c r="F14" t="n">
-        <v>81805</v>
+        <v>82043</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -2238,13 +2238,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1422.74</v>
+        <v>1422.77</v>
       </c>
       <c r="D15" t="n">
-        <v>1416.34</v>
+        <v>1416.37</v>
       </c>
       <c r="E15" t="n">
-        <v>1429.14</v>
+        <v>1429.18</v>
       </c>
       <c r="F15" t="n">
         <v>12019</v>
@@ -2309,16 +2309,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1422.54</v>
+        <v>1422.63</v>
       </c>
       <c r="D16" t="n">
-        <v>1418.65</v>
+        <v>1418.75</v>
       </c>
       <c r="E16" t="n">
-        <v>1426.43</v>
+        <v>1426.52</v>
       </c>
       <c r="F16" t="n">
-        <v>35432</v>
+        <v>35638</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -2383,13 +2383,13 @@
         <v>1421.62</v>
       </c>
       <c r="D17" t="n">
-        <v>1415.97</v>
+        <v>1415.98</v>
       </c>
       <c r="E17" t="n">
-        <v>1427.26</v>
+        <v>1427.27</v>
       </c>
       <c r="F17" t="n">
-        <v>18599</v>
+        <v>18595</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -2447,148 +2447,68 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>kimi-k2-0905-preview</t>
+          <t>deepseek-v3.1</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1417.87</v>
+        <v>1417.79</v>
       </c>
       <c r="D18" t="n">
-        <v>1411.39</v>
+        <v>1411.79</v>
       </c>
       <c r="E18" t="n">
-        <v>1424.35</v>
+        <v>1423.8</v>
       </c>
       <c r="F18" t="n">
-        <v>11867</v>
+        <v>15074</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Moonshot</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Modified MIT</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J18" t="n">
-        <v>32</v>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>override</t>
-        </is>
-      </c>
-      <c r="M18" t="n">
-        <v>2000</v>
-      </c>
-      <c r="N18" t="n">
-        <v>2500</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1250</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>500</v>
-      </c>
-      <c r="R18" t="n">
-        <v>625</v>
-      </c>
-      <c r="S18" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T18" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U18" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="V18" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W18" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X18" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Y18" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z18" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AA18" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AB18" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AC18" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AD18" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AE18" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AF18" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AG18" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr"/>
+      <c r="AC18" t="inlineStr"/>
+      <c r="AD18" t="inlineStr"/>
+      <c r="AE18" t="inlineStr"/>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="inlineStr"/>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -2598,36 +2518,36 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>qwen3.5-122b-a10b</t>
+          <t>kimi-k2-0905-preview</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1417.84</v>
+        <v>1417.73</v>
       </c>
       <c r="D19" t="n">
-        <v>1412.16</v>
+        <v>1411.25</v>
       </c>
       <c r="E19" t="n">
-        <v>1423.53</v>
+        <v>1424.21</v>
       </c>
       <c r="F19" t="n">
-        <v>11895</v>
+        <v>11870</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alibaba</t>
+          <t>Moonshot</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
+          <t>Modified MIT</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>122</v>
+        <v>1000</v>
       </c>
       <c r="J19" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -2636,26 +2556,26 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>override</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>244</v>
+        <v>2000</v>
       </c>
       <c r="N19" t="n">
-        <v>305</v>
+        <v>2500</v>
       </c>
       <c r="O19" t="n">
-        <v>122</v>
+        <v>1000</v>
       </c>
       <c r="P19" t="n">
-        <v>152.5</v>
+        <v>1250</v>
       </c>
       <c r="Q19" t="n">
-        <v>61</v>
+        <v>500</v>
       </c>
       <c r="R19" t="n">
-        <v>76.2</v>
+        <v>625</v>
       </c>
       <c r="S19" s="5" t="inlineStr">
         <is>
@@ -2667,9 +2587,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="U19" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="U19" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="V19" s="5" t="inlineStr">
@@ -2682,9 +2602,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="X19" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="X19" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="Y19" s="5" t="inlineStr">
@@ -2697,9 +2617,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AA19" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AA19" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AB19" s="5" t="inlineStr">
@@ -2707,14 +2627,14 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AC19" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AD19" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AC19" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD19" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AE19" s="5" t="inlineStr">
@@ -2722,14 +2642,14 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AF19" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AG19" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AF19" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AG19" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
@@ -2739,7 +2659,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>B200 SXM</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
     </row>
@@ -2749,68 +2669,148 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>deepseek-v3.1</t>
+          <t>qwen3.5-122b-a10b</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1417.84</v>
+        <v>1417.71</v>
       </c>
       <c r="D20" t="n">
-        <v>1411.83</v>
+        <v>1412.07</v>
       </c>
       <c r="E20" t="n">
-        <v>1423.84</v>
+        <v>1423.35</v>
       </c>
       <c r="F20" t="n">
-        <v>15079</v>
+        <v>12139</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>DeepSeek</t>
+          <t>Alibaba</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
+          <t>Apache 2.0</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>122</v>
+      </c>
+      <c r="J20" t="n">
+        <v>10</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr"/>
-      <c r="W20" t="inlineStr"/>
-      <c r="X20" t="inlineStr"/>
-      <c r="Y20" t="inlineStr"/>
-      <c r="Z20" t="inlineStr"/>
-      <c r="AA20" t="inlineStr"/>
-      <c r="AB20" t="inlineStr"/>
-      <c r="AC20" t="inlineStr"/>
-      <c r="AD20" t="inlineStr"/>
-      <c r="AE20" t="inlineStr"/>
-      <c r="AF20" t="inlineStr"/>
-      <c r="AG20" t="inlineStr"/>
+          <t>name_parsing</t>
+        </is>
+      </c>
+      <c r="M20" t="n">
+        <v>244</v>
+      </c>
+      <c r="N20" t="n">
+        <v>305</v>
+      </c>
+      <c r="O20" t="n">
+        <v>122</v>
+      </c>
+      <c r="P20" t="n">
+        <v>152.5</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>61</v>
+      </c>
+      <c r="R20" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="S20" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T20" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U20" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V20" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W20" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X20" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y20" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z20" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA20" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB20" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AC20" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AD20" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE20" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF20" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AG20" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>B200 SXM</t>
         </is>
       </c>
     </row>
@@ -2824,16 +2824,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1416.86</v>
+        <v>1416.92</v>
       </c>
       <c r="D21" t="n">
-        <v>1412.02</v>
+        <v>1412.08</v>
       </c>
       <c r="E21" t="n">
-        <v>1421.7</v>
+        <v>1421.76</v>
       </c>
       <c r="F21" t="n">
-        <v>27875</v>
+        <v>27869</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -2975,16 +2975,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1416.85</v>
+        <v>1416.79</v>
       </c>
       <c r="D22" t="n">
-        <v>1410.26</v>
+        <v>1410.2</v>
       </c>
       <c r="E22" t="n">
-        <v>1423.44</v>
+        <v>1423.38</v>
       </c>
       <c r="F22" t="n">
-        <v>11820</v>
+        <v>11824</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -3046,16 +3046,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1416.76</v>
+        <v>1416.46</v>
       </c>
       <c r="D23" t="n">
-        <v>1406.81</v>
+        <v>1406.51</v>
       </c>
       <c r="E23" t="n">
-        <v>1426.71</v>
+        <v>1426.41</v>
       </c>
       <c r="F23" t="n">
-        <v>3488</v>
+        <v>3491</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -3117,16 +3117,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1415.99</v>
+        <v>1415.87</v>
       </c>
       <c r="D24" t="n">
-        <v>1406.39</v>
+        <v>1406.27</v>
       </c>
       <c r="E24" t="n">
-        <v>1425.59</v>
+        <v>1425.47</v>
       </c>
       <c r="F24" t="n">
-        <v>3723</v>
+        <v>3724</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -3188,16 +3188,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1415.6</v>
+        <v>1415.62</v>
       </c>
       <c r="D25" t="n">
-        <v>1409.14</v>
+        <v>1409.16</v>
       </c>
       <c r="E25" t="n">
-        <v>1422.06</v>
+        <v>1422.07</v>
       </c>
       <c r="F25" t="n">
-        <v>11606</v>
+        <v>11610</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -3339,16 +3339,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1414.65</v>
+        <v>1414.52</v>
       </c>
       <c r="D26" t="n">
-        <v>1410.86</v>
+        <v>1410.74</v>
       </c>
       <c r="E26" t="n">
-        <v>1418.43</v>
+        <v>1418.29</v>
       </c>
       <c r="F26" t="n">
-        <v>38100</v>
+        <v>38277</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -3490,16 +3490,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1410.86</v>
+        <v>1410.84</v>
       </c>
       <c r="D27" t="n">
-        <v>1406</v>
+        <v>1405.98</v>
       </c>
       <c r="E27" t="n">
-        <v>1415.73</v>
+        <v>1415.7</v>
       </c>
       <c r="F27" t="n">
-        <v>24510</v>
+        <v>24514</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -3641,16 +3641,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1403.46</v>
+        <v>1403.38</v>
       </c>
       <c r="D28" t="n">
-        <v>1398.38</v>
+        <v>1398.31</v>
       </c>
       <c r="E28" t="n">
-        <v>1408.54</v>
+        <v>1408.44</v>
       </c>
       <c r="F28" t="n">
-        <v>16978</v>
+        <v>17217</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -3708,20 +3708,20 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>qwen3.5-27b</t>
+          <t>qwen3-235b-a22b-no-thinking</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1403.21</v>
+        <v>1402.62</v>
       </c>
       <c r="D29" t="n">
-        <v>1397.45</v>
+        <v>1398.13</v>
       </c>
       <c r="E29" t="n">
-        <v>1408.96</v>
+        <v>1407.1</v>
       </c>
       <c r="F29" t="n">
-        <v>11646</v>
+        <v>38476</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -3734,14 +3734,14 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>27</v>
+        <v>235</v>
       </c>
       <c r="J29" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>dense</t>
+          <t>moe</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -3750,76 +3750,76 @@
         </is>
       </c>
       <c r="M29" t="n">
-        <v>54</v>
+        <v>470</v>
       </c>
       <c r="N29" t="n">
-        <v>67.5</v>
+        <v>587.5</v>
       </c>
       <c r="O29" t="n">
-        <v>27</v>
+        <v>235</v>
       </c>
       <c r="P29" t="n">
-        <v>33.8</v>
+        <v>293.8</v>
       </c>
       <c r="Q29" t="n">
-        <v>13.5</v>
+        <v>117.5</v>
       </c>
       <c r="R29" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="S29" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="T29" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="U29" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="V29" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W29" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X29" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Y29" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z29" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AA29" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB29" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AC29" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+        <v>146.9</v>
+      </c>
+      <c r="S29" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T29" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U29" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V29" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W29" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X29" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y29" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z29" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA29" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AB29" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AC29" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AD29" s="6" t="inlineStr">
@@ -3827,14 +3827,14 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="AE29" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AF29" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AE29" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF29" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AG29" s="6" t="inlineStr">
@@ -3844,12 +3844,12 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
     </row>
@@ -3859,20 +3859,20 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>qwen3-235b-a22b-no-thinking</t>
+          <t>qwen3.5-27b</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1402.62</v>
+        <v>1402.09</v>
       </c>
       <c r="D30" t="n">
-        <v>1398.13</v>
+        <v>1396.37</v>
       </c>
       <c r="E30" t="n">
-        <v>1407.11</v>
+        <v>1407.81</v>
       </c>
       <c r="F30" t="n">
-        <v>38481</v>
+        <v>11893</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -3885,14 +3885,14 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>235</v>
+        <v>27</v>
       </c>
       <c r="J30" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>moe</t>
+          <t>dense</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -3901,76 +3901,76 @@
         </is>
       </c>
       <c r="M30" t="n">
-        <v>470</v>
+        <v>54</v>
       </c>
       <c r="N30" t="n">
-        <v>587.5</v>
+        <v>67.5</v>
       </c>
       <c r="O30" t="n">
-        <v>235</v>
+        <v>27</v>
       </c>
       <c r="P30" t="n">
-        <v>293.8</v>
+        <v>33.8</v>
       </c>
       <c r="Q30" t="n">
-        <v>117.5</v>
+        <v>13.5</v>
       </c>
       <c r="R30" t="n">
-        <v>146.9</v>
-      </c>
-      <c r="S30" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T30" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U30" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="V30" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W30" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X30" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Y30" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z30" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AA30" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AB30" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AC30" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+        <v>16.9</v>
+      </c>
+      <c r="S30" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T30" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U30" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V30" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W30" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X30" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y30" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z30" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AA30" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB30" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AC30" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AD30" s="6" t="inlineStr">
@@ -3978,14 +3978,14 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="AE30" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AF30" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AE30" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AF30" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AG30" s="6" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>H100 SXM</t>
         </is>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>H100 SXM</t>
         </is>
       </c>
     </row>
@@ -4014,16 +4014,16 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1401.56</v>
+        <v>1401.53</v>
       </c>
       <c r="D31" t="n">
-        <v>1396.79</v>
+        <v>1396.76</v>
       </c>
       <c r="E31" t="n">
-        <v>1406.32</v>
+        <v>1406.29</v>
       </c>
       <c r="F31" t="n">
-        <v>23083</v>
+        <v>23076</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -4165,16 +4165,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1400.97</v>
+        <v>1400.96</v>
       </c>
       <c r="D32" t="n">
-        <v>1394.61</v>
+        <v>1394.59</v>
       </c>
       <c r="E32" t="n">
-        <v>1407.33</v>
+        <v>1407.32</v>
       </c>
       <c r="F32" t="n">
-        <v>11477</v>
+        <v>11481</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -4316,16 +4316,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1399.64</v>
+        <v>1399.67</v>
       </c>
       <c r="D33" t="n">
-        <v>1393.13</v>
+        <v>1393.15</v>
       </c>
       <c r="E33" t="n">
-        <v>1406.16</v>
+        <v>1406.18</v>
       </c>
       <c r="F33" t="n">
-        <v>9062</v>
+        <v>9061</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1397.51</v>
+        <v>1397.5</v>
       </c>
       <c r="D34" t="n">
-        <v>1392.65</v>
+        <v>1392.64</v>
       </c>
       <c r="E34" t="n">
-        <v>1402.37</v>
+        <v>1402.36</v>
       </c>
       <c r="F34" t="n">
         <v>18524</v>
@@ -4618,16 +4618,16 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1395.67</v>
+        <v>1395.54</v>
       </c>
       <c r="D35" t="n">
-        <v>1390.01</v>
+        <v>1389.91</v>
       </c>
       <c r="E35" t="n">
-        <v>1401.34</v>
+        <v>1401.17</v>
       </c>
       <c r="F35" t="n">
-        <v>12090</v>
+        <v>12328</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -4769,16 +4769,16 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1395.3</v>
+        <v>1395.36</v>
       </c>
       <c r="D36" t="n">
-        <v>1388.53</v>
+        <v>1388.6</v>
       </c>
       <c r="E36" t="n">
-        <v>1402.07</v>
+        <v>1402.13</v>
       </c>
       <c r="F36" t="n">
-        <v>8019</v>
+        <v>8024</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -4920,16 +4920,16 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1394.58</v>
+        <v>1394.59</v>
       </c>
       <c r="D37" t="n">
-        <v>1390.73</v>
+        <v>1390.74</v>
       </c>
       <c r="E37" t="n">
         <v>1398.44</v>
       </c>
       <c r="F37" t="n">
-        <v>45805</v>
+        <v>45800</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -5071,16 +5071,16 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1392.03</v>
+        <v>1392.1</v>
       </c>
       <c r="D38" t="n">
-        <v>1387.93</v>
+        <v>1388.01</v>
       </c>
       <c r="E38" t="n">
-        <v>1396.14</v>
+        <v>1396.19</v>
       </c>
       <c r="F38" t="n">
-        <v>30013</v>
+        <v>30218</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -5142,16 +5142,16 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1390.99</v>
+        <v>1391.58</v>
       </c>
       <c r="D39" t="n">
-        <v>1386.08</v>
+        <v>1386.69</v>
       </c>
       <c r="E39" t="n">
-        <v>1395.89</v>
+        <v>1396.47</v>
       </c>
       <c r="F39" t="n">
-        <v>18351</v>
+        <v>18567</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -5222,7 +5222,7 @@
         <v>1392.29</v>
       </c>
       <c r="F40" t="n">
-        <v>25964</v>
+        <v>25962</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -5364,16 +5364,16 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1387.17</v>
+        <v>1387.08</v>
       </c>
       <c r="D41" t="n">
-        <v>1380.9</v>
+        <v>1380.81</v>
       </c>
       <c r="E41" t="n">
-        <v>1393.44</v>
+        <v>1393.36</v>
       </c>
       <c r="F41" t="n">
-        <v>11024</v>
+        <v>11018</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -5435,16 +5435,16 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1385.57</v>
+        <v>1385.59</v>
       </c>
       <c r="D42" t="n">
-        <v>1380.32</v>
+        <v>1380.33</v>
       </c>
       <c r="E42" t="n">
-        <v>1390.83</v>
+        <v>1390.85</v>
       </c>
       <c r="F42" t="n">
-        <v>17237</v>
+        <v>17231</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -5506,16 +5506,16 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1383.03</v>
+        <v>1383.04</v>
       </c>
       <c r="D43" t="n">
-        <v>1378.17</v>
+        <v>1378.18</v>
       </c>
       <c r="E43" t="n">
-        <v>1387.89</v>
+        <v>1387.9</v>
       </c>
       <c r="F43" t="n">
-        <v>23946</v>
+        <v>23941</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -5657,16 +5657,16 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1377.73</v>
+        <v>1377.71</v>
       </c>
       <c r="D44" t="n">
-        <v>1366.45</v>
+        <v>1366.43</v>
       </c>
       <c r="E44" t="n">
-        <v>1389</v>
+        <v>1388.99</v>
       </c>
       <c r="F44" t="n">
-        <v>2818</v>
+        <v>2816</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -5724,24 +5724,24 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>trinity-large</t>
+          <t>qwen3-235b-a22b</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1374.63</v>
+        <v>1374.43</v>
       </c>
       <c r="D45" t="n">
-        <v>1369</v>
+        <v>1369.75</v>
       </c>
       <c r="E45" t="n">
-        <v>1380.26</v>
+        <v>1379.11</v>
       </c>
       <c r="F45" t="n">
-        <v>13146</v>
+        <v>26425</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Arcee AI</t>
+          <t>Alibaba</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -5750,52 +5750,52 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>70</v>
+        <v>235</v>
       </c>
       <c r="J45" t="n">
-        <v>70</v>
+        <v>22</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>dense</t>
+          <t>moe</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>name_parsing</t>
         </is>
       </c>
       <c r="M45" t="n">
-        <v>140</v>
+        <v>470</v>
       </c>
       <c r="N45" t="n">
-        <v>175</v>
+        <v>587.5</v>
       </c>
       <c r="O45" t="n">
-        <v>70</v>
+        <v>235</v>
       </c>
       <c r="P45" t="n">
-        <v>87.5</v>
+        <v>293.8</v>
       </c>
       <c r="Q45" t="n">
-        <v>35</v>
+        <v>117.5</v>
       </c>
       <c r="R45" t="n">
-        <v>43.8</v>
+        <v>146.9</v>
       </c>
       <c r="S45" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="T45" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="U45" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="T45" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U45" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="V45" s="5" t="inlineStr">
@@ -5808,9 +5808,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="X45" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="X45" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="Y45" s="5" t="inlineStr">
@@ -5818,24 +5818,24 @@
           <t>No</t>
         </is>
       </c>
-      <c r="Z45" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AA45" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB45" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AC45" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="Z45" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA45" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AB45" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AC45" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AD45" s="6" t="inlineStr">
@@ -5843,14 +5843,14 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="AE45" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AF45" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AE45" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF45" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AG45" s="6" t="inlineStr">
@@ -5860,12 +5860,12 @@
       </c>
       <c r="AH45" t="inlineStr">
         <is>
-          <t>B200 SXM</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>RTX PRO 6000</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
     </row>
@@ -5875,24 +5875,24 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>qwen3-235b-a22b</t>
+          <t>trinity-large-preview</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1374.35</v>
+        <v>1374.31</v>
       </c>
       <c r="D46" t="n">
-        <v>1369.67</v>
+        <v>1368.7</v>
       </c>
       <c r="E46" t="n">
-        <v>1379.03</v>
+        <v>1379.92</v>
       </c>
       <c r="F46" t="n">
-        <v>26429</v>
+        <v>13315</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alibaba</t>
+          <t>Arcee AI</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -5901,52 +5901,52 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>235</v>
+        <v>70</v>
       </c>
       <c r="J46" t="n">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>moe</t>
+          <t>dense</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>override</t>
         </is>
       </c>
       <c r="M46" t="n">
-        <v>470</v>
+        <v>140</v>
       </c>
       <c r="N46" t="n">
-        <v>587.5</v>
+        <v>175</v>
       </c>
       <c r="O46" t="n">
-        <v>235</v>
+        <v>70</v>
       </c>
       <c r="P46" t="n">
-        <v>293.8</v>
+        <v>87.5</v>
       </c>
       <c r="Q46" t="n">
-        <v>117.5</v>
+        <v>35</v>
       </c>
       <c r="R46" t="n">
-        <v>146.9</v>
+        <v>43.8</v>
       </c>
       <c r="S46" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="T46" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U46" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="T46" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U46" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="V46" s="5" t="inlineStr">
@@ -5959,9 +5959,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="X46" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="X46" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Y46" s="5" t="inlineStr">
@@ -5969,24 +5969,24 @@
           <t>No</t>
         </is>
       </c>
-      <c r="Z46" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AA46" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AB46" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AC46" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="Z46" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AA46" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB46" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AC46" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AD46" s="6" t="inlineStr">
@@ -5994,14 +5994,14 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="AE46" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AF46" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AE46" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AF46" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AG46" s="6" t="inlineStr">
@@ -6011,12 +6011,12 @@
       </c>
       <c r="AH46" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>B200 SXM</t>
         </is>
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>RTX PRO 6000</t>
         </is>
       </c>
     </row>
@@ -6030,16 +6030,16 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1372.81</v>
+        <v>1372.76</v>
       </c>
       <c r="D47" t="n">
-        <v>1368.58</v>
+        <v>1368.52</v>
       </c>
       <c r="E47" t="n">
-        <v>1377.05</v>
+        <v>1376.99</v>
       </c>
       <c r="F47" t="n">
-        <v>31382</v>
+        <v>31387</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -6101,16 +6101,16 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1368.89</v>
+        <v>1369.03</v>
       </c>
       <c r="D48" t="n">
-        <v>1363.08</v>
+        <v>1363.22</v>
       </c>
       <c r="E48" t="n">
-        <v>1374.71</v>
+        <v>1374.85</v>
       </c>
       <c r="F48" t="n">
-        <v>13834</v>
+        <v>13837</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -6252,16 +6252,16 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1368.52</v>
+        <v>1368.16</v>
       </c>
       <c r="D49" t="n">
-        <v>1362.7</v>
+        <v>1362.34</v>
       </c>
       <c r="E49" t="n">
-        <v>1374.34</v>
+        <v>1373.98</v>
       </c>
       <c r="F49" t="n">
-        <v>11833</v>
+        <v>11829</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -6323,13 +6323,13 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1365.09</v>
+        <v>1365.11</v>
       </c>
       <c r="D50" t="n">
-        <v>1361.44</v>
+        <v>1361.46</v>
       </c>
       <c r="E50" t="n">
-        <v>1368.75</v>
+        <v>1368.77</v>
       </c>
       <c r="F50" t="n">
         <v>47852</v>
@@ -6474,16 +6474,16 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1363.32</v>
+        <v>1363.35</v>
       </c>
       <c r="D51" t="n">
-        <v>1359.07</v>
+        <v>1359.09</v>
       </c>
       <c r="E51" t="n">
-        <v>1367.58</v>
+        <v>1367.6</v>
       </c>
       <c r="F51" t="n">
-        <v>35522</v>
+        <v>35518</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -6545,16 +6545,16 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1361.41</v>
+        <v>1361.07</v>
       </c>
       <c r="D52" t="n">
-        <v>1354.12</v>
+        <v>1353.78</v>
       </c>
       <c r="E52" t="n">
-        <v>1368.7</v>
+        <v>1368.37</v>
       </c>
       <c r="F52" t="n">
-        <v>7460</v>
+        <v>7449</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -6696,13 +6696,13 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1358.16</v>
+        <v>1358.15</v>
       </c>
       <c r="D53" t="n">
-        <v>1353.44</v>
+        <v>1353.43</v>
       </c>
       <c r="E53" t="n">
-        <v>1362.88</v>
+        <v>1362.86</v>
       </c>
       <c r="F53" t="n">
         <v>21770</v>
@@ -6847,16 +6847,16 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1357</v>
+        <v>1356.93</v>
       </c>
       <c r="D54" t="n">
-        <v>1351.82</v>
+        <v>1351.75</v>
       </c>
       <c r="E54" t="n">
-        <v>1362.19</v>
+        <v>1362.12</v>
       </c>
       <c r="F54" t="n">
-        <v>17845</v>
+        <v>17843</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -6918,16 +6918,16 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1356.29</v>
+        <v>1356.3</v>
       </c>
       <c r="D55" t="n">
-        <v>1347.93</v>
+        <v>1347.94</v>
       </c>
       <c r="E55" t="n">
-        <v>1364.64</v>
+        <v>1364.65</v>
       </c>
       <c r="F55" t="n">
-        <v>5357</v>
+        <v>5356</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -7069,13 +7069,13 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1353.7</v>
+        <v>1353.77</v>
       </c>
       <c r="D56" t="n">
-        <v>1349.36</v>
+        <v>1349.44</v>
       </c>
       <c r="E56" t="n">
-        <v>1358.03</v>
+        <v>1358.11</v>
       </c>
       <c r="F56" t="n">
         <v>30903</v>
@@ -7220,16 +7220,16 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1353.36</v>
+        <v>1353.31</v>
       </c>
       <c r="D57" t="n">
-        <v>1349.93</v>
+        <v>1349.88</v>
       </c>
       <c r="E57" t="n">
-        <v>1356.8</v>
+        <v>1356.74</v>
       </c>
       <c r="F57" t="n">
-        <v>56669</v>
+        <v>56670</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -7291,13 +7291,13 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1353.31</v>
+        <v>1353.08</v>
       </c>
       <c r="D58" t="n">
-        <v>1344.98</v>
+        <v>1344.75</v>
       </c>
       <c r="E58" t="n">
-        <v>1361.64</v>
+        <v>1361.41</v>
       </c>
       <c r="F58" t="n">
         <v>4980</v>
@@ -7362,13 +7362,13 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1347.64</v>
+        <v>1347.59</v>
       </c>
       <c r="D59" t="n">
-        <v>1340.26</v>
+        <v>1340.21</v>
       </c>
       <c r="E59" t="n">
-        <v>1355.02</v>
+        <v>1354.97</v>
       </c>
       <c r="F59" t="n">
         <v>6587</v>
@@ -7439,7 +7439,7 @@
         <v>1337.54</v>
       </c>
       <c r="E60" t="n">
-        <v>1356.46</v>
+        <v>1356.47</v>
       </c>
       <c r="F60" t="n">
         <v>3926</v>
@@ -7584,10 +7584,10 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1346.84</v>
+        <v>1346.83</v>
       </c>
       <c r="D61" t="n">
-        <v>1335.14</v>
+        <v>1335.13</v>
       </c>
       <c r="E61" t="n">
         <v>1358.53</v>
@@ -7735,16 +7735,16 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1346.54</v>
+        <v>1346.39</v>
       </c>
       <c r="D62" t="n">
-        <v>1338.82</v>
+        <v>1338.67</v>
       </c>
       <c r="E62" t="n">
-        <v>1354.26</v>
+        <v>1354.11</v>
       </c>
       <c r="F62" t="n">
-        <v>6916</v>
+        <v>6919</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -7886,16 +7886,16 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1346.22</v>
+        <v>1346.2</v>
       </c>
       <c r="D63" t="n">
-        <v>1338.99</v>
+        <v>1338.97</v>
       </c>
       <c r="E63" t="n">
-        <v>1353.45</v>
+        <v>1353.43</v>
       </c>
       <c r="F63" t="n">
-        <v>7079</v>
+        <v>7081</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -7957,16 +7957,16 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1342.73</v>
+        <v>1342.82</v>
       </c>
       <c r="D64" t="n">
-        <v>1332.78</v>
+        <v>1332.87</v>
       </c>
       <c r="E64" t="n">
-        <v>1352.68</v>
+        <v>1352.77</v>
       </c>
       <c r="F64" t="n">
-        <v>3367</v>
+        <v>3366</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -8108,10 +8108,10 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1341.42</v>
+        <v>1341.41</v>
       </c>
       <c r="D65" t="n">
-        <v>1331.91</v>
+        <v>1331.9</v>
       </c>
       <c r="E65" t="n">
         <v>1350.93</v>
@@ -8259,16 +8259,16 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1335.63</v>
+        <v>1335.65</v>
       </c>
       <c r="D66" t="n">
-        <v>1331.21</v>
+        <v>1331.23</v>
       </c>
       <c r="E66" t="n">
-        <v>1340.05</v>
+        <v>1340.07</v>
       </c>
       <c r="F66" t="n">
-        <v>25518</v>
+        <v>25522</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -8410,13 +8410,13 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1334.26</v>
+        <v>1334.25</v>
       </c>
       <c r="D67" t="n">
-        <v>1330.58</v>
+        <v>1330.57</v>
       </c>
       <c r="E67" t="n">
-        <v>1337.94</v>
+        <v>1337.93</v>
       </c>
       <c r="F67" t="n">
         <v>41375</v>
@@ -8561,13 +8561,13 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1332.47</v>
+        <v>1332.45</v>
       </c>
       <c r="D68" t="n">
-        <v>1328.9</v>
+        <v>1328.89</v>
       </c>
       <c r="E68" t="n">
-        <v>1336.03</v>
+        <v>1336.02</v>
       </c>
       <c r="F68" t="n">
         <v>59656</v>
@@ -8712,16 +8712,16 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1330.82</v>
+        <v>1330.9</v>
       </c>
       <c r="D69" t="n">
-        <v>1324.72</v>
+        <v>1324.8</v>
       </c>
       <c r="E69" t="n">
-        <v>1336.92</v>
+        <v>1337</v>
       </c>
       <c r="F69" t="n">
-        <v>12293</v>
+        <v>12291</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -8863,13 +8863,13 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1327.39</v>
+        <v>1327.38</v>
       </c>
       <c r="D70" t="n">
-        <v>1315.22</v>
+        <v>1315.21</v>
       </c>
       <c r="E70" t="n">
-        <v>1339.56</v>
+        <v>1339.55</v>
       </c>
       <c r="F70" t="n">
         <v>2218</v>
@@ -9010,24 +9010,24 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>molmo-2-8b</t>
+          <t>qwen3-30b-a3b</t>
         </is>
       </c>
       <c r="C71" t="n">
         <v>1327.33</v>
       </c>
       <c r="D71" t="n">
-        <v>1305.94</v>
+        <v>1322.61</v>
       </c>
       <c r="E71" t="n">
-        <v>1348.72</v>
+        <v>1332.04</v>
       </c>
       <c r="F71" t="n">
-        <v>805</v>
+        <v>26648</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Ai2</t>
+          <t>Alibaba</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -9036,14 +9036,14 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="J71" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>dense</t>
+          <t>moe</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -9052,22 +9052,22 @@
         </is>
       </c>
       <c r="M71" t="n">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="N71" t="n">
-        <v>20</v>
+        <v>75</v>
       </c>
       <c r="O71" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="P71" t="n">
-        <v>10</v>
+        <v>37.5</v>
       </c>
       <c r="Q71" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="R71" t="n">
-        <v>5</v>
+        <v>18.8</v>
       </c>
       <c r="S71" s="6" t="inlineStr">
         <is>
@@ -9161,24 +9161,24 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>qwen3-30b-a3b</t>
+          <t>molmo-2-8b</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1327.29</v>
+        <v>1326.95</v>
       </c>
       <c r="D72" t="n">
-        <v>1322.58</v>
+        <v>1305.57</v>
       </c>
       <c r="E72" t="n">
-        <v>1332</v>
+        <v>1348.34</v>
       </c>
       <c r="F72" t="n">
-        <v>26647</v>
+        <v>806</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alibaba</t>
+          <t>Ai2</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -9187,14 +9187,14 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="J72" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>moe</t>
+          <t>dense</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -9203,22 +9203,22 @@
         </is>
       </c>
       <c r="M72" t="n">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="N72" t="n">
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="O72" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="P72" t="n">
-        <v>37.5</v>
+        <v>10</v>
       </c>
       <c r="Q72" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="R72" t="n">
-        <v>18.8</v>
+        <v>5</v>
       </c>
       <c r="S72" s="6" t="inlineStr">
         <is>
@@ -9319,13 +9319,13 @@
         <v>1326.67</v>
       </c>
       <c r="D73" t="n">
-        <v>1322.44</v>
+        <v>1322.43</v>
       </c>
       <c r="E73" t="n">
-        <v>1330.91</v>
+        <v>1330.9</v>
       </c>
       <c r="F73" t="n">
-        <v>40220</v>
+        <v>40222</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -9467,13 +9467,13 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1323.09</v>
+        <v>1323.07</v>
       </c>
       <c r="D74" t="n">
-        <v>1314.83</v>
+        <v>1314.81</v>
       </c>
       <c r="E74" t="n">
-        <v>1331.35</v>
+        <v>1331.34</v>
       </c>
       <c r="F74" t="n">
         <v>6795</v>
@@ -9538,16 +9538,16 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>1321.93</v>
+        <v>1322.03</v>
       </c>
       <c r="D75" t="n">
-        <v>1317.24</v>
+        <v>1317.34</v>
       </c>
       <c r="E75" t="n">
-        <v>1326.62</v>
+        <v>1326.73</v>
       </c>
       <c r="F75" t="n">
-        <v>30500</v>
+        <v>30494</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -9689,16 +9689,16 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>1320.83</v>
+        <v>1320.78</v>
       </c>
       <c r="D76" t="n">
-        <v>1313.64</v>
+        <v>1313.6</v>
       </c>
       <c r="E76" t="n">
-        <v>1328.02</v>
+        <v>1327.97</v>
       </c>
       <c r="F76" t="n">
-        <v>7217</v>
+        <v>7221</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -9760,16 +9760,16 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1318.04</v>
+        <v>1318.03</v>
       </c>
       <c r="D77" t="n">
-        <v>1312.9</v>
+        <v>1312.89</v>
       </c>
       <c r="E77" t="n">
-        <v>1323.17</v>
+        <v>1323.16</v>
       </c>
       <c r="F77" t="n">
-        <v>22729</v>
+        <v>22723</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -9911,16 +9911,16 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1317.95</v>
+        <v>1317.94</v>
       </c>
       <c r="D78" t="n">
-        <v>1314.52</v>
+        <v>1314.51</v>
       </c>
       <c r="E78" t="n">
-        <v>1321.39</v>
+        <v>1321.38</v>
       </c>
       <c r="F78" t="n">
-        <v>54887</v>
+        <v>54888</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -10062,16 +10062,16 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>1317.68</v>
+        <v>1317.71</v>
       </c>
       <c r="D79" t="n">
-        <v>1311.33</v>
+        <v>1311.36</v>
       </c>
       <c r="E79" t="n">
-        <v>1324.03</v>
+        <v>1324.06</v>
       </c>
       <c r="F79" t="n">
-        <v>10702</v>
+        <v>10701</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -10213,16 +10213,16 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1317.51</v>
+        <v>1317.49</v>
       </c>
       <c r="D80" t="n">
-        <v>1311.93</v>
+        <v>1311.91</v>
       </c>
       <c r="E80" t="n">
-        <v>1323.09</v>
+        <v>1323.07</v>
       </c>
       <c r="F80" t="n">
-        <v>15591</v>
+        <v>15589</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -10364,13 +10364,13 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1317.5</v>
+        <v>1317.48</v>
       </c>
       <c r="D81" t="n">
-        <v>1311.81</v>
+        <v>1311.8</v>
       </c>
       <c r="E81" t="n">
-        <v>1323.18</v>
+        <v>1323.17</v>
       </c>
       <c r="F81" t="n">
         <v>16478</v>
@@ -10435,13 +10435,13 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>1314.07</v>
+        <v>1314.06</v>
       </c>
       <c r="D82" t="n">
-        <v>1309.54</v>
+        <v>1309.53</v>
       </c>
       <c r="E82" t="n">
-        <v>1318.6</v>
+        <v>1318.58</v>
       </c>
       <c r="F82" t="n">
         <v>24739</v>
@@ -10586,13 +10586,13 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>1313.38</v>
+        <v>1313.36</v>
       </c>
       <c r="D83" t="n">
-        <v>1309.48</v>
+        <v>1309.46</v>
       </c>
       <c r="E83" t="n">
-        <v>1317.28</v>
+        <v>1317.27</v>
       </c>
       <c r="F83" t="n">
         <v>45459</v>
@@ -10737,13 +10737,13 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>1306.64</v>
+        <v>1306.63</v>
       </c>
       <c r="D84" t="n">
-        <v>1301.96</v>
+        <v>1301.94</v>
       </c>
       <c r="E84" t="n">
-        <v>1311.33</v>
+        <v>1311.31</v>
       </c>
       <c r="F84" t="n">
         <v>24572</v>
@@ -10808,13 +10808,13 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>1305.54</v>
+        <v>1305.52</v>
       </c>
       <c r="D85" t="n">
-        <v>1299.88</v>
+        <v>1299.85</v>
       </c>
       <c r="E85" t="n">
-        <v>1311.2</v>
+        <v>1311.18</v>
       </c>
       <c r="F85" t="n">
         <v>19621</v>
@@ -10959,16 +10959,16 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>1305.14</v>
+        <v>1305.35</v>
       </c>
       <c r="D86" t="n">
-        <v>1296.96</v>
+        <v>1297.17</v>
       </c>
       <c r="E86" t="n">
-        <v>1313.32</v>
+        <v>1313.52</v>
       </c>
       <c r="F86" t="n">
-        <v>5988</v>
+        <v>5987</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -11110,13 +11110,13 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>1304.69</v>
+        <v>1304.68</v>
       </c>
       <c r="D87" t="n">
-        <v>1300.28</v>
+        <v>1300.27</v>
       </c>
       <c r="E87" t="n">
-        <v>1309.09</v>
+        <v>1309.08</v>
       </c>
       <c r="F87" t="n">
         <v>28073</v>
@@ -11187,7 +11187,7 @@
         <v>1293.48</v>
       </c>
       <c r="E88" t="n">
-        <v>1312.12</v>
+        <v>1312.11</v>
       </c>
       <c r="F88" t="n">
         <v>4171</v>
@@ -11332,16 +11332,16 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>1302.79</v>
+        <v>1302.77</v>
       </c>
       <c r="D89" t="n">
-        <v>1298.3</v>
+        <v>1298.27</v>
       </c>
       <c r="E89" t="n">
-        <v>1307.28</v>
+        <v>1307.26</v>
       </c>
       <c r="F89" t="n">
-        <v>33479</v>
+        <v>33474</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -11483,13 +11483,13 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>1302.35</v>
+        <v>1302.33</v>
       </c>
       <c r="D90" t="n">
-        <v>1298.31</v>
+        <v>1298.29</v>
       </c>
       <c r="E90" t="n">
-        <v>1306.39</v>
+        <v>1306.38</v>
       </c>
       <c r="F90" t="n">
         <v>39406</v>
@@ -11634,13 +11634,13 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>1298.48</v>
+        <v>1298.46</v>
       </c>
       <c r="D91" t="n">
-        <v>1290.73</v>
+        <v>1290.71</v>
       </c>
       <c r="E91" t="n">
-        <v>1306.24</v>
+        <v>1306.22</v>
       </c>
       <c r="F91" t="n">
         <v>7140</v>
@@ -11785,13 +11785,13 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>1292.83</v>
+        <v>1292.81</v>
       </c>
       <c r="D92" t="n">
-        <v>1289.12</v>
+        <v>1289.1</v>
       </c>
       <c r="E92" t="n">
-        <v>1296.53</v>
+        <v>1296.52</v>
       </c>
       <c r="F92" t="n">
         <v>55240</v>
@@ -11936,13 +11936,13 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>1288.25</v>
+        <v>1288.23</v>
       </c>
       <c r="D93" t="n">
-        <v>1280.95</v>
+        <v>1280.93</v>
       </c>
       <c r="E93" t="n">
-        <v>1295.55</v>
+        <v>1295.53</v>
       </c>
       <c r="F93" t="n">
         <v>8662</v>
@@ -12007,13 +12007,13 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1287.67</v>
+        <v>1287.64</v>
       </c>
       <c r="D94" t="n">
-        <v>1284.32</v>
+        <v>1284.29</v>
       </c>
       <c r="E94" t="n">
-        <v>1291.02</v>
+        <v>1290.99</v>
       </c>
       <c r="F94" t="n">
         <v>75754</v>
@@ -12158,16 +12158,16 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1286.84</v>
+        <v>1287.03</v>
       </c>
       <c r="D95" t="n">
-        <v>1278.5</v>
+        <v>1278.69</v>
       </c>
       <c r="E95" t="n">
-        <v>1295.18</v>
+        <v>1295.37</v>
       </c>
       <c r="F95" t="n">
-        <v>5747</v>
+        <v>5743</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
@@ -12309,13 +12309,13 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>1285.82</v>
+        <v>1285.81</v>
       </c>
       <c r="D96" t="n">
-        <v>1275.34</v>
+        <v>1275.33</v>
       </c>
       <c r="E96" t="n">
-        <v>1296.29</v>
+        <v>1296.28</v>
       </c>
       <c r="F96" t="n">
         <v>2846</v>
@@ -12460,16 +12460,16 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1285.55</v>
+        <v>1285.44</v>
       </c>
       <c r="D97" t="n">
-        <v>1278.33</v>
+        <v>1278.22</v>
       </c>
       <c r="E97" t="n">
-        <v>1292.78</v>
+        <v>1292.67</v>
       </c>
       <c r="F97" t="n">
-        <v>8546</v>
+        <v>8544</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
@@ -12611,13 +12611,13 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>1285.33</v>
+        <v>1285.32</v>
       </c>
       <c r="D98" t="n">
-        <v>1275.36</v>
+        <v>1275.35</v>
       </c>
       <c r="E98" t="n">
-        <v>1295.31</v>
+        <v>1295.29</v>
       </c>
       <c r="F98" t="n">
         <v>3749</v>
@@ -12762,13 +12762,13 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>1278.91</v>
+        <v>1278.88</v>
       </c>
       <c r="D99" t="n">
-        <v>1272.05</v>
+        <v>1272.02</v>
       </c>
       <c r="E99" t="n">
-        <v>1285.77</v>
+        <v>1285.74</v>
       </c>
       <c r="F99" t="n">
         <v>10072</v>
@@ -12913,13 +12913,13 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>1276.25</v>
+        <v>1276.24</v>
       </c>
       <c r="D100" t="n">
         <v>1270.92</v>
       </c>
       <c r="E100" t="n">
-        <v>1281.58</v>
+        <v>1281.57</v>
       </c>
       <c r="F100" t="n">
         <v>19659</v>
@@ -13067,7 +13067,7 @@
         <v>1275.51</v>
       </c>
       <c r="D101" t="n">
-        <v>1268.95</v>
+        <v>1268.94</v>
       </c>
       <c r="E101" t="n">
         <v>1282.08</v>
@@ -13215,13 +13215,13 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>1275.2</v>
+        <v>1275.19</v>
       </c>
       <c r="D102" t="n">
-        <v>1271.63</v>
+        <v>1271.61</v>
       </c>
       <c r="E102" t="n">
-        <v>1278.78</v>
+        <v>1278.76</v>
       </c>
       <c r="F102" t="n">
         <v>156876</v>
@@ -13366,13 +13366,13 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>1273.48</v>
+        <v>1273.47</v>
       </c>
       <c r="D103" t="n">
-        <v>1267.6</v>
+        <v>1267.59</v>
       </c>
       <c r="E103" t="n">
-        <v>1279.37</v>
+        <v>1279.36</v>
       </c>
       <c r="F103" t="n">
         <v>14681</v>
@@ -13517,13 +13517,13 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>1269.95</v>
+        <v>1269.93</v>
       </c>
       <c r="D104" t="n">
-        <v>1261.83</v>
+        <v>1261.81</v>
       </c>
       <c r="E104" t="n">
-        <v>1278.07</v>
+        <v>1278.05</v>
       </c>
       <c r="F104" t="n">
         <v>5432</v>
@@ -13668,13 +13668,13 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>1266.32</v>
+        <v>1266.3</v>
       </c>
       <c r="D105" t="n">
-        <v>1261.45</v>
+        <v>1261.44</v>
       </c>
       <c r="E105" t="n">
-        <v>1271.18</v>
+        <v>1271.16</v>
       </c>
       <c r="F105" t="n">
         <v>27124</v>
@@ -13819,13 +13819,13 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>1265.14</v>
+        <v>1265.11</v>
       </c>
       <c r="D106" t="n">
-        <v>1261.35</v>
+        <v>1261.32</v>
       </c>
       <c r="E106" t="n">
-        <v>1268.93</v>
+        <v>1268.9</v>
       </c>
       <c r="F106" t="n">
         <v>54611</v>
@@ -13970,13 +13970,13 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>1263.47</v>
+        <v>1263.45</v>
       </c>
       <c r="D107" t="n">
-        <v>1257.19</v>
+        <v>1257.17</v>
       </c>
       <c r="E107" t="n">
-        <v>1269.75</v>
+        <v>1269.73</v>
       </c>
       <c r="F107" t="n">
         <v>15147</v>
@@ -14121,13 +14121,13 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>1260.77</v>
+        <v>1260.76</v>
       </c>
       <c r="D108" t="n">
-        <v>1256.45</v>
+        <v>1256.44</v>
       </c>
       <c r="E108" t="n">
-        <v>1265.09</v>
+        <v>1265.08</v>
       </c>
       <c r="F108" t="n">
         <v>77554</v>
@@ -14192,13 +14192,13 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>1260.76</v>
+        <v>1260.75</v>
       </c>
       <c r="D109" t="n">
-        <v>1255.82</v>
+        <v>1255.81</v>
       </c>
       <c r="E109" t="n">
-        <v>1265.7</v>
+        <v>1265.68</v>
       </c>
       <c r="F109" t="n">
         <v>37325</v>
@@ -14343,13 +14343,13 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>1255.47</v>
+        <v>1255.46</v>
       </c>
       <c r="D110" t="n">
-        <v>1250.91</v>
+        <v>1250.9</v>
       </c>
       <c r="E110" t="n">
-        <v>1260.04</v>
+        <v>1260.03</v>
       </c>
       <c r="F110" t="n">
         <v>24126</v>
@@ -14645,13 +14645,13 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>1249.11</v>
+        <v>1249.1</v>
       </c>
       <c r="D112" t="n">
-        <v>1242.52</v>
+        <v>1242.51</v>
       </c>
       <c r="E112" t="n">
-        <v>1255.71</v>
+        <v>1255.7</v>
       </c>
       <c r="F112" t="n">
         <v>10140</v>
@@ -14796,13 +14796,13 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>1238.44</v>
+        <v>1238.42</v>
       </c>
       <c r="D113" t="n">
-        <v>1231.22</v>
+        <v>1231.2</v>
       </c>
       <c r="E113" t="n">
-        <v>1245.66</v>
+        <v>1245.64</v>
       </c>
       <c r="F113" t="n">
         <v>8858</v>
@@ -14867,13 +14867,13 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>1236.63</v>
+        <v>1236.61</v>
       </c>
       <c r="D114" t="n">
-        <v>1227.53</v>
+        <v>1227.52</v>
       </c>
       <c r="E114" t="n">
-        <v>1245.72</v>
+        <v>1245.71</v>
       </c>
       <c r="F114" t="n">
         <v>4781</v>
@@ -15018,13 +15018,13 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>1233.03</v>
+        <v>1233.01</v>
       </c>
       <c r="D115" t="n">
-        <v>1227.47</v>
+        <v>1227.46</v>
       </c>
       <c r="E115" t="n">
-        <v>1238.58</v>
+        <v>1238.57</v>
       </c>
       <c r="F115" t="n">
         <v>26195</v>
@@ -15169,13 +15169,13 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>1232.08</v>
+        <v>1232.06</v>
       </c>
       <c r="D116" t="n">
-        <v>1226.8</v>
+        <v>1226.79</v>
       </c>
       <c r="E116" t="n">
-        <v>1237.35</v>
+        <v>1237.34</v>
       </c>
       <c r="F116" t="n">
         <v>39302</v>
@@ -15320,13 +15320,13 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>1228.26</v>
+        <v>1228.25</v>
       </c>
       <c r="D117" t="n">
-        <v>1223.71</v>
+        <v>1223.7</v>
       </c>
       <c r="E117" t="n">
-        <v>1232.81</v>
+        <v>1232.8</v>
       </c>
       <c r="F117" t="n">
         <v>51416</v>
@@ -15474,7 +15474,7 @@
         <v>1225.73</v>
       </c>
       <c r="D118" t="n">
-        <v>1220.95</v>
+        <v>1220.94</v>
       </c>
       <c r="E118" t="n">
         <v>1230.51</v>
@@ -15542,13 +15542,13 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>1222.28</v>
+        <v>1222.26</v>
       </c>
       <c r="D119" t="n">
-        <v>1215.32</v>
+        <v>1215.31</v>
       </c>
       <c r="E119" t="n">
-        <v>1229.24</v>
+        <v>1229.22</v>
       </c>
       <c r="F119" t="n">
         <v>9818</v>
@@ -15693,13 +15693,13 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>1222.26</v>
+        <v>1222.25</v>
       </c>
       <c r="D120" t="n">
-        <v>1218.54</v>
+        <v>1218.52</v>
       </c>
       <c r="E120" t="n">
-        <v>1225.99</v>
+        <v>1225.98</v>
       </c>
       <c r="F120" t="n">
         <v>104642</v>
@@ -15844,7 +15844,7 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>1220.36</v>
+        <v>1220.35</v>
       </c>
       <c r="D121" t="n">
         <v>1209.67</v>
@@ -15998,10 +15998,10 @@
         <v>1212.41</v>
       </c>
       <c r="D122" t="n">
-        <v>1207.38</v>
+        <v>1207.37</v>
       </c>
       <c r="E122" t="n">
-        <v>1217.45</v>
+        <v>1217.44</v>
       </c>
       <c r="F122" t="n">
         <v>24146</v>
@@ -16146,13 +16146,13 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>1211.57</v>
+        <v>1211.56</v>
       </c>
       <c r="D123" t="n">
-        <v>1200.76</v>
+        <v>1200.75</v>
       </c>
       <c r="E123" t="n">
-        <v>1222.38</v>
+        <v>1222.37</v>
       </c>
       <c r="F123" t="n">
         <v>4652</v>
@@ -16297,13 +16297,13 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>1211.05</v>
+        <v>1211.03</v>
       </c>
       <c r="D124" t="n">
-        <v>1206.93</v>
+        <v>1206.91</v>
       </c>
       <c r="E124" t="n">
-        <v>1215.17</v>
+        <v>1215.16</v>
       </c>
       <c r="F124" t="n">
         <v>49605</v>
@@ -16448,10 +16448,10 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>1207.35</v>
+        <v>1207.34</v>
       </c>
       <c r="D125" t="n">
-        <v>1196.24</v>
+        <v>1196.23</v>
       </c>
       <c r="E125" t="n">
         <v>1218.46</v>
@@ -16599,13 +16599,13 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>1202.68</v>
+        <v>1202.67</v>
       </c>
       <c r="D126" t="n">
-        <v>1196.56</v>
+        <v>1196.55</v>
       </c>
       <c r="E126" t="n">
-        <v>1208.8</v>
+        <v>1208.79</v>
       </c>
       <c r="F126" t="n">
         <v>21741</v>
@@ -16750,13 +16750,13 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>1198.63</v>
+        <v>1198.6</v>
       </c>
       <c r="D127" t="n">
-        <v>1194.56</v>
+        <v>1194.53</v>
       </c>
       <c r="E127" t="n">
-        <v>1202.7</v>
+        <v>1202.67</v>
       </c>
       <c r="F127" t="n">
         <v>46616</v>
@@ -16901,13 +16901,13 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>1196.81</v>
+        <v>1196.8</v>
       </c>
       <c r="D128" t="n">
         <v>1191.65</v>
       </c>
       <c r="E128" t="n">
-        <v>1201.96</v>
+        <v>1201.95</v>
       </c>
       <c r="F128" t="n">
         <v>25055</v>
@@ -17052,13 +17052,13 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>1195.94</v>
+        <v>1195.93</v>
       </c>
       <c r="D129" t="n">
-        <v>1191.67</v>
+        <v>1191.66</v>
       </c>
       <c r="E129" t="n">
-        <v>1200.21</v>
+        <v>1200.2</v>
       </c>
       <c r="F129" t="n">
         <v>73503</v>
@@ -17203,13 +17203,13 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>1193.88</v>
+        <v>1193.86</v>
       </c>
       <c r="D130" t="n">
-        <v>1187.76</v>
+        <v>1187.75</v>
       </c>
       <c r="E130" t="n">
-        <v>1199.99</v>
+        <v>1199.98</v>
       </c>
       <c r="F130" t="n">
         <v>32191</v>
@@ -17274,13 +17274,13 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>1190.44</v>
+        <v>1190.43</v>
       </c>
       <c r="D131" t="n">
-        <v>1183.27</v>
+        <v>1183.26</v>
       </c>
       <c r="E131" t="n">
-        <v>1197.62</v>
+        <v>1197.61</v>
       </c>
       <c r="F131" t="n">
         <v>9901</v>
@@ -17425,13 +17425,13 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>1189.8</v>
+        <v>1189.79</v>
       </c>
       <c r="D132" t="n">
-        <v>1182.68</v>
+        <v>1182.67</v>
       </c>
       <c r="E132" t="n">
-        <v>1196.93</v>
+        <v>1196.92</v>
       </c>
       <c r="F132" t="n">
         <v>17839</v>
@@ -17579,10 +17579,10 @@
         <v>1183.46</v>
       </c>
       <c r="D133" t="n">
-        <v>1174.01</v>
+        <v>1174</v>
       </c>
       <c r="E133" t="n">
-        <v>1192.92</v>
+        <v>1192.91</v>
       </c>
       <c r="F133" t="n">
         <v>8214</v>
@@ -17727,13 +17727,13 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>1183.19</v>
+        <v>1183.18</v>
       </c>
       <c r="D134" t="n">
-        <v>1171.68</v>
+        <v>1171.67</v>
       </c>
       <c r="E134" t="n">
-        <v>1194.71</v>
+        <v>1194.69</v>
       </c>
       <c r="F134" t="n">
         <v>4932</v>
@@ -17878,13 +17878,13 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>1182.74</v>
+        <v>1182.73</v>
       </c>
       <c r="D135" t="n">
-        <v>1175.91</v>
+        <v>1175.9</v>
       </c>
       <c r="E135" t="n">
-        <v>1189.58</v>
+        <v>1189.57</v>
       </c>
       <c r="F135" t="n">
         <v>15483</v>
@@ -18029,13 +18029,13 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>1181.07</v>
+        <v>1181.06</v>
       </c>
       <c r="D136" t="n">
-        <v>1173.07</v>
+        <v>1173.05</v>
       </c>
       <c r="E136" t="n">
-        <v>1189.07</v>
+        <v>1189.06</v>
       </c>
       <c r="F136" t="n">
         <v>12637</v>
@@ -18100,13 +18100,13 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>1181.02</v>
+        <v>1181.01</v>
       </c>
       <c r="D137" t="n">
-        <v>1171.34</v>
+        <v>1171.33</v>
       </c>
       <c r="E137" t="n">
-        <v>1190.7</v>
+        <v>1190.69</v>
       </c>
       <c r="F137" t="n">
         <v>7968</v>
@@ -18171,13 +18171,13 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>1180.97</v>
+        <v>1180.95</v>
       </c>
       <c r="D138" t="n">
-        <v>1172.28</v>
+        <v>1172.26</v>
       </c>
       <c r="E138" t="n">
-        <v>1189.65</v>
+        <v>1189.64</v>
       </c>
       <c r="F138" t="n">
         <v>6638</v>
@@ -18322,13 +18322,13 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>1179.75</v>
+        <v>1179.71</v>
       </c>
       <c r="D139" t="n">
-        <v>1173.67</v>
+        <v>1173.64</v>
       </c>
       <c r="E139" t="n">
-        <v>1185.82</v>
+        <v>1185.78</v>
       </c>
       <c r="F139" t="n">
         <v>23893</v>
@@ -18473,13 +18473,13 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>1178.29</v>
+        <v>1178.28</v>
       </c>
       <c r="D140" t="n">
-        <v>1172.37</v>
+        <v>1172.36</v>
       </c>
       <c r="E140" t="n">
-        <v>1184.21</v>
+        <v>1184.19</v>
       </c>
       <c r="F140" t="n">
         <v>32832</v>
@@ -18544,13 +18544,13 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>1177.92</v>
+        <v>1177.91</v>
       </c>
       <c r="D141" t="n">
-        <v>1166.71</v>
+        <v>1166.7</v>
       </c>
       <c r="E141" t="n">
-        <v>1189.12</v>
+        <v>1189.11</v>
       </c>
       <c r="F141" t="n">
         <v>3188</v>
@@ -18695,7 +18695,7 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>1176.79</v>
+        <v>1176.78</v>
       </c>
       <c r="D142" t="n">
         <v>1166.96</v>
@@ -18846,13 +18846,13 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>1173.99</v>
+        <v>1173.98</v>
       </c>
       <c r="D143" t="n">
-        <v>1163.57</v>
+        <v>1163.55</v>
       </c>
       <c r="E143" t="n">
-        <v>1184.42</v>
+        <v>1184.41</v>
       </c>
       <c r="F143" t="n">
         <v>5006</v>
@@ -18997,13 +18997,13 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>1171.57</v>
+        <v>1171.56</v>
       </c>
       <c r="D144" t="n">
         <v>1165.35</v>
       </c>
       <c r="E144" t="n">
-        <v>1177.78</v>
+        <v>1177.77</v>
       </c>
       <c r="F144" t="n">
         <v>22479</v>
@@ -19299,13 +19299,13 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>1169.95</v>
+        <v>1169.94</v>
       </c>
       <c r="D146" t="n">
-        <v>1164.04</v>
+        <v>1164.03</v>
       </c>
       <c r="E146" t="n">
-        <v>1175.87</v>
+        <v>1175.86</v>
       </c>
       <c r="F146" t="n">
         <v>17766</v>
@@ -19456,7 +19456,7 @@
         <v>1164.1</v>
       </c>
       <c r="E147" t="n">
-        <v>1175.12</v>
+        <v>1175.11</v>
       </c>
       <c r="F147" t="n">
         <v>38492</v>
@@ -19601,13 +19601,13 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>1166.33</v>
+        <v>1166.32</v>
       </c>
       <c r="D148" t="n">
         <v>1158.25</v>
       </c>
       <c r="E148" t="n">
-        <v>1174.4</v>
+        <v>1174.39</v>
       </c>
       <c r="F148" t="n">
         <v>10224</v>
@@ -19752,13 +19752,13 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>1165.71</v>
+        <v>1165.69</v>
       </c>
       <c r="D149" t="n">
-        <v>1158.01</v>
+        <v>1158</v>
       </c>
       <c r="E149" t="n">
-        <v>1173.4</v>
+        <v>1173.39</v>
       </c>
       <c r="F149" t="n">
         <v>7936</v>
@@ -19903,13 +19903,13 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>1163.54</v>
+        <v>1163.53</v>
       </c>
       <c r="D150" t="n">
         <v>1151.6</v>
       </c>
       <c r="E150" t="n">
-        <v>1175.48</v>
+        <v>1175.47</v>
       </c>
       <c r="F150" t="n">
         <v>3777</v>
@@ -20054,13 +20054,13 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>1155.81</v>
+        <v>1155.82</v>
       </c>
       <c r="D151" t="n">
-        <v>1144.31</v>
+        <v>1144.32</v>
       </c>
       <c r="E151" t="n">
-        <v>1167.31</v>
+        <v>1167.32</v>
       </c>
       <c r="F151" t="n">
         <v>3231</v>
@@ -20205,13 +20205,13 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>1154.92</v>
+        <v>1154.91</v>
       </c>
       <c r="D152" t="n">
-        <v>1146.53</v>
+        <v>1146.52</v>
       </c>
       <c r="E152" t="n">
-        <v>1163.32</v>
+        <v>1163.3</v>
       </c>
       <c r="F152" t="n">
         <v>6837</v>
@@ -20507,13 +20507,13 @@
         </is>
       </c>
       <c r="C154" t="n">
-        <v>1151.12</v>
+        <v>1151.11</v>
       </c>
       <c r="D154" t="n">
         <v>1137.91</v>
       </c>
       <c r="E154" t="n">
-        <v>1164.33</v>
+        <v>1164.32</v>
       </c>
       <c r="F154" t="n">
         <v>4155</v>
@@ -20658,13 +20658,13 @@
         </is>
       </c>
       <c r="C155" t="n">
-        <v>1150.79</v>
+        <v>1150.78</v>
       </c>
       <c r="D155" t="n">
-        <v>1135.4</v>
+        <v>1135.39</v>
       </c>
       <c r="E155" t="n">
-        <v>1166.19</v>
+        <v>1166.17</v>
       </c>
       <c r="F155" t="n">
         <v>1679</v>
@@ -20809,13 +20809,13 @@
         </is>
       </c>
       <c r="C156" t="n">
-        <v>1148.89</v>
+        <v>1148.88</v>
       </c>
       <c r="D156" t="n">
-        <v>1136.6</v>
+        <v>1136.58</v>
       </c>
       <c r="E156" t="n">
-        <v>1161.19</v>
+        <v>1161.18</v>
       </c>
       <c r="F156" t="n">
         <v>2572</v>
@@ -20963,10 +20963,10 @@
         <v>1148.37</v>
       </c>
       <c r="D157" t="n">
-        <v>1141.72</v>
+        <v>1141.71</v>
       </c>
       <c r="E157" t="n">
-        <v>1155.03</v>
+        <v>1155.02</v>
       </c>
       <c r="F157" t="n">
         <v>19402</v>
@@ -21111,13 +21111,13 @@
         </is>
       </c>
       <c r="C158" t="n">
-        <v>1147.99</v>
+        <v>1147.98</v>
       </c>
       <c r="D158" t="n">
-        <v>1138.73</v>
+        <v>1138.72</v>
       </c>
       <c r="E158" t="n">
-        <v>1157.25</v>
+        <v>1157.24</v>
       </c>
       <c r="F158" t="n">
         <v>7044</v>
@@ -21262,13 +21262,13 @@
         </is>
       </c>
       <c r="C159" t="n">
-        <v>1145.85</v>
+        <v>1145.83</v>
       </c>
       <c r="D159" t="n">
-        <v>1128.73</v>
+        <v>1128.71</v>
       </c>
       <c r="E159" t="n">
-        <v>1162.98</v>
+        <v>1162.96</v>
       </c>
       <c r="F159" t="n">
         <v>1295</v>
@@ -21413,13 +21413,13 @@
         </is>
       </c>
       <c r="C160" t="n">
-        <v>1142.65</v>
+        <v>1142.64</v>
       </c>
       <c r="D160" t="n">
-        <v>1132.75</v>
+        <v>1132.74</v>
       </c>
       <c r="E160" t="n">
-        <v>1152.55</v>
+        <v>1152.54</v>
       </c>
       <c r="F160" t="n">
         <v>4737</v>
@@ -21564,13 +21564,13 @@
         </is>
       </c>
       <c r="C161" t="n">
-        <v>1141.94</v>
+        <v>1141.93</v>
       </c>
       <c r="D161" t="n">
-        <v>1135.51</v>
+        <v>1135.5</v>
       </c>
       <c r="E161" t="n">
-        <v>1148.38</v>
+        <v>1148.37</v>
       </c>
       <c r="F161" t="n">
         <v>12297</v>
@@ -21866,13 +21866,13 @@
         </is>
       </c>
       <c r="C163" t="n">
-        <v>1139.7</v>
+        <v>1139.69</v>
       </c>
       <c r="D163" t="n">
-        <v>1132.98</v>
+        <v>1132.97</v>
       </c>
       <c r="E163" t="n">
-        <v>1146.42</v>
+        <v>1146.4</v>
       </c>
       <c r="F163" t="n">
         <v>19367</v>
@@ -22017,13 +22017,13 @@
         </is>
       </c>
       <c r="C164" t="n">
-        <v>1137.36</v>
+        <v>1137.35</v>
       </c>
       <c r="D164" t="n">
-        <v>1126.4</v>
+        <v>1126.38</v>
       </c>
       <c r="E164" t="n">
-        <v>1148.33</v>
+        <v>1148.31</v>
       </c>
       <c r="F164" t="n">
         <v>4964</v>
@@ -22168,13 +22168,13 @@
         </is>
       </c>
       <c r="C165" t="n">
-        <v>1135.39</v>
+        <v>1135.36</v>
       </c>
       <c r="D165" t="n">
-        <v>1125.88</v>
+        <v>1125.85</v>
       </c>
       <c r="E165" t="n">
-        <v>1144.9</v>
+        <v>1144.87</v>
       </c>
       <c r="F165" t="n">
         <v>8925</v>
@@ -22319,13 +22319,13 @@
         </is>
       </c>
       <c r="C166" t="n">
-        <v>1135.36</v>
+        <v>1135.35</v>
       </c>
       <c r="D166" t="n">
-        <v>1126.45</v>
+        <v>1126.44</v>
       </c>
       <c r="E166" t="n">
-        <v>1144.26</v>
+        <v>1144.25</v>
       </c>
       <c r="F166" t="n">
         <v>7366</v>
@@ -22470,10 +22470,10 @@
         </is>
       </c>
       <c r="C167" t="n">
-        <v>1129.79</v>
+        <v>1129.78</v>
       </c>
       <c r="D167" t="n">
-        <v>1120.94</v>
+        <v>1120.93</v>
       </c>
       <c r="E167" t="n">
         <v>1138.63</v>
@@ -22621,13 +22621,13 @@
         </is>
       </c>
       <c r="C168" t="n">
-        <v>1128.05</v>
+        <v>1128.03</v>
       </c>
       <c r="D168" t="n">
-        <v>1120.62</v>
+        <v>1120.61</v>
       </c>
       <c r="E168" t="n">
-        <v>1135.47</v>
+        <v>1135.46</v>
       </c>
       <c r="F168" t="n">
         <v>20685</v>
@@ -22772,10 +22772,10 @@
         </is>
       </c>
       <c r="C169" t="n">
-        <v>1127.23</v>
+        <v>1127.22</v>
       </c>
       <c r="D169" t="n">
-        <v>1120.83</v>
+        <v>1120.82</v>
       </c>
       <c r="E169" t="n">
         <v>1133.62</v>
@@ -22923,13 +22923,13 @@
         </is>
       </c>
       <c r="C170" t="n">
-        <v>1126.07</v>
+        <v>1126.06</v>
       </c>
       <c r="D170" t="n">
-        <v>1113.92</v>
+        <v>1113.91</v>
       </c>
       <c r="E170" t="n">
-        <v>1138.22</v>
+        <v>1138.21</v>
       </c>
       <c r="F170" t="n">
         <v>2921</v>
@@ -23074,13 +23074,13 @@
         </is>
       </c>
       <c r="C171" t="n">
-        <v>1125.66</v>
+        <v>1125.65</v>
       </c>
       <c r="D171" t="n">
-        <v>1109.99</v>
+        <v>1109.98</v>
       </c>
       <c r="E171" t="n">
-        <v>1141.33</v>
+        <v>1141.32</v>
       </c>
       <c r="F171" t="n">
         <v>1785</v>
@@ -23225,13 +23225,13 @@
         </is>
       </c>
       <c r="C172" t="n">
-        <v>1119.77</v>
+        <v>1119.75</v>
       </c>
       <c r="D172" t="n">
-        <v>1108.77</v>
+        <v>1108.75</v>
       </c>
       <c r="E172" t="n">
-        <v>1130.77</v>
+        <v>1130.76</v>
       </c>
       <c r="F172" t="n">
         <v>5182</v>
@@ -23376,13 +23376,13 @@
         </is>
       </c>
       <c r="C173" t="n">
-        <v>1117.94</v>
+        <v>1117.93</v>
       </c>
       <c r="D173" t="n">
-        <v>1099.74</v>
+        <v>1099.73</v>
       </c>
       <c r="E173" t="n">
-        <v>1136.15</v>
+        <v>1136.14</v>
       </c>
       <c r="F173" t="n">
         <v>1143</v>
@@ -23527,13 +23527,13 @@
         </is>
       </c>
       <c r="C174" t="n">
-        <v>1113.62</v>
+        <v>1113.58</v>
       </c>
       <c r="D174" t="n">
-        <v>1105.88</v>
+        <v>1105.84</v>
       </c>
       <c r="E174" t="n">
-        <v>1121.35</v>
+        <v>1121.32</v>
       </c>
       <c r="F174" t="n">
         <v>10854</v>
@@ -23678,13 +23678,13 @@
         </is>
       </c>
       <c r="C175" t="n">
-        <v>1113.42</v>
+        <v>1113.41</v>
       </c>
       <c r="D175" t="n">
-        <v>1104.24</v>
+        <v>1104.23</v>
       </c>
       <c r="E175" t="n">
-        <v>1122.6</v>
+        <v>1122.59</v>
       </c>
       <c r="F175" t="n">
         <v>6923</v>
@@ -23829,13 +23829,13 @@
         </is>
       </c>
       <c r="C176" t="n">
-        <v>1113.19</v>
+        <v>1113.18</v>
       </c>
       <c r="D176" t="n">
-        <v>1098.78</v>
+        <v>1098.77</v>
       </c>
       <c r="E176" t="n">
-        <v>1127.6</v>
+        <v>1127.59</v>
       </c>
       <c r="F176" t="n">
         <v>2199</v>
@@ -23980,13 +23980,13 @@
         </is>
       </c>
       <c r="C177" t="n">
-        <v>1110.23</v>
+        <v>1110.22</v>
       </c>
       <c r="D177" t="n">
-        <v>1102.36</v>
+        <v>1102.35</v>
       </c>
       <c r="E177" t="n">
-        <v>1118.11</v>
+        <v>1118.1</v>
       </c>
       <c r="F177" t="n">
         <v>8045</v>
@@ -24131,13 +24131,13 @@
         </is>
       </c>
       <c r="C178" t="n">
-        <v>1108.4</v>
+        <v>1108.38</v>
       </c>
       <c r="D178" t="n">
-        <v>1099.1</v>
+        <v>1099.09</v>
       </c>
       <c r="E178" t="n">
-        <v>1117.7</v>
+        <v>1117.68</v>
       </c>
       <c r="F178" t="n">
         <v>8977</v>
@@ -24433,13 +24433,13 @@
         </is>
       </c>
       <c r="C180" t="n">
-        <v>1090.98</v>
+        <v>1090.95</v>
       </c>
       <c r="D180" t="n">
-        <v>1079.47</v>
+        <v>1079.44</v>
       </c>
       <c r="E180" t="n">
-        <v>1102.5</v>
+        <v>1102.46</v>
       </c>
       <c r="F180" t="n">
         <v>4780</v>
@@ -24584,13 +24584,13 @@
         </is>
       </c>
       <c r="C181" t="n">
-        <v>1088.96</v>
+        <v>1088.95</v>
       </c>
       <c r="D181" t="n">
-        <v>1079.61</v>
+        <v>1079.6</v>
       </c>
       <c r="E181" t="n">
-        <v>1098.31</v>
+        <v>1098.3</v>
       </c>
       <c r="F181" t="n">
         <v>7597</v>
@@ -24886,13 +24886,13 @@
         </is>
       </c>
       <c r="C183" t="n">
-        <v>1069.18</v>
+        <v>1069.17</v>
       </c>
       <c r="D183" t="n">
-        <v>1059.24</v>
+        <v>1059.23</v>
       </c>
       <c r="E183" t="n">
-        <v>1079.13</v>
+        <v>1079.11</v>
       </c>
       <c r="F183" t="n">
         <v>6965</v>
@@ -25037,13 +25037,13 @@
         </is>
       </c>
       <c r="C184" t="n">
-        <v>1066.33</v>
+        <v>1066.3</v>
       </c>
       <c r="D184" t="n">
-        <v>1054.82</v>
+        <v>1054.79</v>
       </c>
       <c r="E184" t="n">
-        <v>1077.85</v>
+        <v>1077.82</v>
       </c>
       <c r="F184" t="n">
         <v>5745</v>
@@ -25188,13 +25188,13 @@
         </is>
       </c>
       <c r="C185" t="n">
-        <v>1064.8</v>
+        <v>1064.78</v>
       </c>
       <c r="D185" t="n">
-        <v>1049.52</v>
+        <v>1049.5</v>
       </c>
       <c r="E185" t="n">
-        <v>1080.08</v>
+        <v>1080.06</v>
       </c>
       <c r="F185" t="n">
         <v>1743</v>
@@ -25339,13 +25339,13 @@
         </is>
       </c>
       <c r="C186" t="n">
-        <v>1060.65</v>
+        <v>1060.62</v>
       </c>
       <c r="D186" t="n">
-        <v>1048.62</v>
+        <v>1048.6</v>
       </c>
       <c r="E186" t="n">
-        <v>1072.67</v>
+        <v>1072.65</v>
       </c>
       <c r="F186" t="n">
         <v>3924</v>
@@ -25490,13 +25490,13 @@
         </is>
       </c>
       <c r="C187" t="n">
-        <v>1054.8</v>
+        <v>1054.78</v>
       </c>
       <c r="D187" t="n">
-        <v>1043.11</v>
+        <v>1043.1</v>
       </c>
       <c r="E187" t="n">
-        <v>1066.48</v>
+        <v>1066.47</v>
       </c>
       <c r="F187" t="n">
         <v>4658</v>
@@ -25641,13 +25641,13 @@
         </is>
       </c>
       <c r="C188" t="n">
-        <v>1040.1</v>
+        <v>1040.08</v>
       </c>
       <c r="D188" t="n">
-        <v>1028.65</v>
+        <v>1028.64</v>
       </c>
       <c r="E188" t="n">
-        <v>1051.55</v>
+        <v>1051.53</v>
       </c>
       <c r="F188" t="n">
         <v>4845</v>
@@ -25792,13 +25792,13 @@
         </is>
       </c>
       <c r="C189" t="n">
-        <v>1022.91</v>
+        <v>1022.9</v>
       </c>
       <c r="D189" t="n">
-        <v>1009.28</v>
+        <v>1009.27</v>
       </c>
       <c r="E189" t="n">
-        <v>1036.54</v>
+        <v>1036.53</v>
       </c>
       <c r="F189" t="n">
         <v>2658</v>
@@ -25943,13 +25943,13 @@
         </is>
       </c>
       <c r="C190" t="n">
-        <v>1020.86</v>
+        <v>1020.84</v>
       </c>
       <c r="D190" t="n">
-        <v>1009.94</v>
+        <v>1009.92</v>
       </c>
       <c r="E190" t="n">
-        <v>1031.79</v>
+        <v>1031.77</v>
       </c>
       <c r="F190" t="n">
         <v>6310</v>
@@ -26094,13 +26094,13 @@
         </is>
       </c>
       <c r="C191" t="n">
-        <v>994.3049999999999</v>
+        <v>994.294</v>
       </c>
       <c r="D191" t="n">
-        <v>981.684</v>
+        <v>981.675</v>
       </c>
       <c r="E191" t="n">
-        <v>1006.92</v>
+        <v>1006.91</v>
       </c>
       <c r="F191" t="n">
         <v>4914</v>
@@ -26245,13 +26245,13 @@
         </is>
       </c>
       <c r="C192" t="n">
-        <v>990.131</v>
+        <v>990.1130000000001</v>
       </c>
       <c r="D192" t="n">
-        <v>977.7</v>
+        <v>977.683</v>
       </c>
       <c r="E192" t="n">
-        <v>1002.56</v>
+        <v>1002.54</v>
       </c>
       <c r="F192" t="n">
         <v>4203</v>
@@ -26396,13 +26396,13 @@
         </is>
       </c>
       <c r="C193" t="n">
-        <v>978.949</v>
+        <v>978.92</v>
       </c>
       <c r="D193" t="n">
-        <v>965.3440000000001</v>
+        <v>965.317</v>
       </c>
       <c r="E193" t="n">
-        <v>992.554</v>
+        <v>992.524</v>
       </c>
       <c r="F193" t="n">
         <v>3412</v>
@@ -26547,13 +26547,13 @@
         </is>
       </c>
       <c r="C194" t="n">
-        <v>971.096</v>
+        <v>971.0650000000001</v>
       </c>
       <c r="D194" t="n">
-        <v>955.196</v>
+        <v>955.1660000000001</v>
       </c>
       <c r="E194" t="n">
-        <v>986.996</v>
+        <v>986.963</v>
       </c>
       <c r="F194" t="n">
         <v>2391</v>
@@ -26698,13 +26698,13 @@
         </is>
       </c>
       <c r="C195" t="n">
-        <v>951.361</v>
+        <v>951.347</v>
       </c>
       <c r="D195" t="n">
-        <v>938.552</v>
+        <v>938.54</v>
       </c>
       <c r="E195" t="n">
-        <v>964.17</v>
+        <v>964.155</v>
       </c>
       <c r="F195" t="n">
         <v>3287</v>
@@ -27795,37 +27795,29 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>kimi-k2-0905-preview</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="C18" t="n">
-        <v>32</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+          <t>deepseek-v3.1</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>qwen3.5-122b-a10b</t>
+          <t>kimi-k2-0905-preview</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>122</v>
+        <v>1000</v>
       </c>
       <c r="C19" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -27834,22 +27826,30 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>override</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>deepseek-v3.1</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
+          <t>qwen3.5-122b-a10b</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>122</v>
+      </c>
+      <c r="C20" t="n">
+        <v>10</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>name_parsing</t>
         </is>
       </c>
     </row>
@@ -28008,18 +28008,18 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>qwen3.5-27b</t>
+          <t>qwen3-235b-a22b-no-thinking</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>27</v>
+        <v>235</v>
       </c>
       <c r="C29" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>dense</t>
+          <t>moe</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -28031,18 +28031,18 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>qwen3-235b-a22b-no-thinking</t>
+          <t>qwen3.5-27b</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>235</v>
+        <v>27</v>
       </c>
       <c r="C30" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>moe</t>
+          <t>dense</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -28336,46 +28336,46 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>trinity-large</t>
+          <t>qwen3-235b-a22b</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>70</v>
+        <v>235</v>
       </c>
       <c r="C45" t="n">
-        <v>70</v>
+        <v>22</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>dense</t>
+          <t>moe</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>name_parsing</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>qwen3-235b-a22b</t>
+          <t>trinity-large-preview</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>235</v>
+        <v>70</v>
       </c>
       <c r="C46" t="n">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>moe</t>
+          <t>dense</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>override</t>
         </is>
       </c>
     </row>
@@ -28870,18 +28870,18 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>molmo-2-8b</t>
+          <t>qwen3-30b-a3b</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="C71" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>dense</t>
+          <t>moe</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -28893,18 +28893,18 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>qwen3-30b-a3b</t>
+          <t>molmo-2-8b</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="C72" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>moe</t>
+          <t>dense</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">

--- a/arena_enrichment/output/arena_leaderboard_enriched.xlsx
+++ b/arena_enrichment/output/arena_leaderboard_enriched.xlsx
@@ -675,16 +675,16 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>1470.88</v>
+        <v>1471.18</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1462.92</v>
+        <v>1463.75</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1478.83</v>
+        <v>1478.61</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>5326</v>
+        <v>6274</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
@@ -746,16 +746,16 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>1455.5</v>
+        <v>1455.54</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1450.05</v>
+        <v>1450.21</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1460.94</v>
+        <v>1460.88</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>14093</v>
+        <v>14988</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
@@ -897,16 +897,16 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>1451.7</v>
+        <v>1450.55</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1446.67</v>
+        <v>1445.88</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1456.74</v>
+        <v>1455.23</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>17735</v>
+        <v>21678</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
@@ -1048,16 +1048,16 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>1450.51</v>
+        <v>1450.43</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1442.89</v>
+        <v>1442.77</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1458.12</v>
+        <v>1458.1</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>5957</v>
+        <v>5839</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
@@ -1199,16 +1199,16 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1446.75</v>
+        <v>1445.5</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1441.53</v>
+        <v>1440.37</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1451.96</v>
+        <v>1450.63</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>15408</v>
+        <v>16360</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
@@ -1350,13 +1350,13 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>1442.61</v>
+        <v>1442.57</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>1436.48</v>
+        <v>1436.45</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1448.73</v>
+        <v>1448.69</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>12180</v>
@@ -1421,16 +1421,16 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>1438.47</v>
+        <v>1438.84</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>1430.85</v>
+        <v>1431.15</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1446.09</v>
+        <v>1446.52</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>5927</v>
+        <v>5795</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
@@ -1572,16 +1572,16 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>1432.5</v>
+        <v>1431.93</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1425.89</v>
+        <v>1425.32</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1439.11</v>
+        <v>1438.54</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>8241</v>
+        <v>8234</v>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
@@ -1723,16 +1723,16 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>1430.28</v>
+        <v>1429.72</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>1426.76</v>
+        <v>1426.22</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1433.8</v>
+        <v>1433.22</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>46203</v>
+        <v>47037</v>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
@@ -1874,16 +1874,16 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>1425.74</v>
+        <v>1425.67</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>1421.8</v>
+        <v>1421.73</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1429.68</v>
+        <v>1429.6</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>35917</v>
+        <v>35904</v>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
@@ -1945,16 +1945,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1424.73</v>
+        <v>1424.67</v>
       </c>
       <c r="D12" t="n">
-        <v>1418.2</v>
+        <v>1418.13</v>
       </c>
       <c r="E12" t="n">
-        <v>1431.26</v>
+        <v>1431.2</v>
       </c>
       <c r="F12" t="n">
-        <v>9146</v>
+        <v>9140</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -2016,16 +2016,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1423.8</v>
+        <v>1423.36</v>
       </c>
       <c r="D13" t="n">
-        <v>1420.01</v>
+        <v>1419.59</v>
       </c>
       <c r="E13" t="n">
-        <v>1427.6</v>
+        <v>1427.13</v>
       </c>
       <c r="F13" t="n">
-        <v>41182</v>
+        <v>42036</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -2087,16 +2087,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1422.95</v>
+        <v>1422.98</v>
       </c>
       <c r="D14" t="n">
-        <v>1420.15</v>
+        <v>1420.2</v>
       </c>
       <c r="E14" t="n">
-        <v>1425.75</v>
+        <v>1425.76</v>
       </c>
       <c r="F14" t="n">
-        <v>82043</v>
+        <v>82850</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -2234,20 +2234,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>deepseek-v3.2-exp</t>
+          <t>deepseek-v3.2-thinking</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1422.77</v>
+        <v>1422.86</v>
       </c>
       <c r="D15" t="n">
-        <v>1416.37</v>
+        <v>1419</v>
       </c>
       <c r="E15" t="n">
-        <v>1429.18</v>
+        <v>1426.73</v>
       </c>
       <c r="F15" t="n">
-        <v>12019</v>
+        <v>36441</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -2305,20 +2305,20 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>deepseek-v3.2-thinking</t>
+          <t>deepseek-v3.2-exp</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1422.63</v>
+        <v>1422.61</v>
       </c>
       <c r="D16" t="n">
-        <v>1418.75</v>
+        <v>1416.2</v>
       </c>
       <c r="E16" t="n">
-        <v>1426.52</v>
+        <v>1429.01</v>
       </c>
       <c r="F16" t="n">
-        <v>35638</v>
+        <v>12013</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -2380,16 +2380,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1421.62</v>
+        <v>1421.66</v>
       </c>
       <c r="D17" t="n">
-        <v>1415.98</v>
+        <v>1416.02</v>
       </c>
       <c r="E17" t="n">
-        <v>1427.27</v>
+        <v>1427.31</v>
       </c>
       <c r="F17" t="n">
-        <v>18595</v>
+        <v>18590</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -2447,68 +2447,148 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>deepseek-v3.1</t>
+          <t>qwen3.5-122b-a10b</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1417.79</v>
+        <v>1417.76</v>
       </c>
       <c r="D18" t="n">
-        <v>1411.79</v>
+        <v>1412.24</v>
       </c>
       <c r="E18" t="n">
-        <v>1423.8</v>
+        <v>1423.28</v>
       </c>
       <c r="F18" t="n">
-        <v>15074</v>
+        <v>13066</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>DeepSeek</t>
+          <t>Alibaba</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+          <t>Apache 2.0</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>122</v>
+      </c>
+      <c r="J18" t="n">
+        <v>10</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
-      <c r="W18" t="inlineStr"/>
-      <c r="X18" t="inlineStr"/>
-      <c r="Y18" t="inlineStr"/>
-      <c r="Z18" t="inlineStr"/>
-      <c r="AA18" t="inlineStr"/>
-      <c r="AB18" t="inlineStr"/>
-      <c r="AC18" t="inlineStr"/>
-      <c r="AD18" t="inlineStr"/>
-      <c r="AE18" t="inlineStr"/>
-      <c r="AF18" t="inlineStr"/>
-      <c r="AG18" t="inlineStr"/>
+          <t>name_parsing</t>
+        </is>
+      </c>
+      <c r="M18" t="n">
+        <v>244</v>
+      </c>
+      <c r="N18" t="n">
+        <v>305</v>
+      </c>
+      <c r="O18" t="n">
+        <v>122</v>
+      </c>
+      <c r="P18" t="n">
+        <v>152.5</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>61</v>
+      </c>
+      <c r="R18" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="S18" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T18" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U18" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V18" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W18" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X18" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y18" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z18" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA18" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB18" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AC18" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AD18" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE18" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF18" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AG18" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>B200 SXM</t>
         </is>
       </c>
     </row>
@@ -2531,7 +2611,7 @@
         <v>1424.21</v>
       </c>
       <c r="F19" t="n">
-        <v>11870</v>
+        <v>11862</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -2669,148 +2749,68 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>qwen3.5-122b-a10b</t>
+          <t>deepseek-v3.1</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1417.71</v>
+        <v>1417.64</v>
       </c>
       <c r="D20" t="n">
-        <v>1412.07</v>
+        <v>1411.64</v>
       </c>
       <c r="E20" t="n">
-        <v>1423.35</v>
+        <v>1423.64</v>
       </c>
       <c r="F20" t="n">
-        <v>12139</v>
+        <v>15068</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alibaba</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>122</v>
-      </c>
-      <c r="J20" t="n">
-        <v>10</v>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>name_parsing</t>
-        </is>
-      </c>
-      <c r="M20" t="n">
-        <v>244</v>
-      </c>
-      <c r="N20" t="n">
-        <v>305</v>
-      </c>
-      <c r="O20" t="n">
-        <v>122</v>
-      </c>
-      <c r="P20" t="n">
-        <v>152.5</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>61</v>
-      </c>
-      <c r="R20" t="n">
-        <v>76.2</v>
-      </c>
-      <c r="S20" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T20" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U20" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="V20" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W20" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X20" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Y20" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z20" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AA20" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB20" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AC20" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AD20" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AE20" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AF20" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AG20" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr"/>
+      <c r="AB20" t="inlineStr"/>
+      <c r="AC20" t="inlineStr"/>
+      <c r="AD20" t="inlineStr"/>
+      <c r="AE20" t="inlineStr"/>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="inlineStr"/>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>B200 SXM</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -2824,16 +2824,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1416.92</v>
+        <v>1416.75</v>
       </c>
       <c r="D21" t="n">
-        <v>1412.08</v>
+        <v>1411.91</v>
       </c>
       <c r="E21" t="n">
-        <v>1421.76</v>
+        <v>1421.59</v>
       </c>
       <c r="F21" t="n">
-        <v>27869</v>
+        <v>27861</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -2975,16 +2975,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1416.79</v>
+        <v>1416.75</v>
       </c>
       <c r="D22" t="n">
-        <v>1410.2</v>
+        <v>1410.16</v>
       </c>
       <c r="E22" t="n">
-        <v>1423.38</v>
+        <v>1423.34</v>
       </c>
       <c r="F22" t="n">
-        <v>11824</v>
+        <v>11825</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -3046,16 +3046,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1416.46</v>
+        <v>1416.17</v>
       </c>
       <c r="D23" t="n">
-        <v>1406.51</v>
+        <v>1406.22</v>
       </c>
       <c r="E23" t="n">
-        <v>1426.41</v>
+        <v>1426.12</v>
       </c>
       <c r="F23" t="n">
-        <v>3491</v>
+        <v>3488</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -3117,16 +3117,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1415.87</v>
+        <v>1415.72</v>
       </c>
       <c r="D24" t="n">
-        <v>1406.27</v>
+        <v>1406.12</v>
       </c>
       <c r="E24" t="n">
-        <v>1425.47</v>
+        <v>1425.32</v>
       </c>
       <c r="F24" t="n">
-        <v>3724</v>
+        <v>3722</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -3188,16 +3188,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1415.62</v>
+        <v>1415.59</v>
       </c>
       <c r="D25" t="n">
-        <v>1409.16</v>
+        <v>1409.13</v>
       </c>
       <c r="E25" t="n">
-        <v>1422.07</v>
+        <v>1422.05</v>
       </c>
       <c r="F25" t="n">
-        <v>11610</v>
+        <v>11608</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -3339,16 +3339,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1414.52</v>
+        <v>1415.47</v>
       </c>
       <c r="D26" t="n">
-        <v>1410.74</v>
+        <v>1411.71</v>
       </c>
       <c r="E26" t="n">
-        <v>1418.29</v>
+        <v>1419.22</v>
       </c>
       <c r="F26" t="n">
-        <v>38277</v>
+        <v>39232</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -3490,16 +3490,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1410.84</v>
+        <v>1410.75</v>
       </c>
       <c r="D27" t="n">
-        <v>1405.98</v>
+        <v>1405.89</v>
       </c>
       <c r="E27" t="n">
-        <v>1415.7</v>
+        <v>1415.61</v>
       </c>
       <c r="F27" t="n">
-        <v>24514</v>
+        <v>24507</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -3637,68 +3637,148 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>minimax-m2.7</t>
+          <t>qwen3-235b-a22b-no-thinking</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1404.38</v>
+        <v>1402.55</v>
       </c>
       <c r="D28" t="n">
-        <v>1396.99</v>
+        <v>1398.06</v>
       </c>
       <c r="E28" t="n">
-        <v>1411.77</v>
+        <v>1407.04</v>
       </c>
       <c r="F28" t="n">
-        <v>6784</v>
+        <v>38470</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>MiniMax</t>
+          <t>Alibaba</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Modified MIT</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
+          <t>Apache 2.0</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>235</v>
+      </c>
+      <c r="J28" t="n">
+        <v>22</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr"/>
-      <c r="S28" t="inlineStr"/>
-      <c r="T28" t="inlineStr"/>
-      <c r="U28" t="inlineStr"/>
-      <c r="V28" t="inlineStr"/>
-      <c r="W28" t="inlineStr"/>
-      <c r="X28" t="inlineStr"/>
-      <c r="Y28" t="inlineStr"/>
-      <c r="Z28" t="inlineStr"/>
-      <c r="AA28" t="inlineStr"/>
-      <c r="AB28" t="inlineStr"/>
-      <c r="AC28" t="inlineStr"/>
-      <c r="AD28" t="inlineStr"/>
-      <c r="AE28" t="inlineStr"/>
-      <c r="AF28" t="inlineStr"/>
-      <c r="AG28" t="inlineStr"/>
+          <t>name_parsing</t>
+        </is>
+      </c>
+      <c r="M28" t="n">
+        <v>470</v>
+      </c>
+      <c r="N28" t="n">
+        <v>587.5</v>
+      </c>
+      <c r="O28" t="n">
+        <v>235</v>
+      </c>
+      <c r="P28" t="n">
+        <v>293.8</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>117.5</v>
+      </c>
+      <c r="R28" t="n">
+        <v>146.9</v>
+      </c>
+      <c r="S28" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T28" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U28" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V28" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W28" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X28" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y28" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z28" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA28" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AB28" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AC28" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD28" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE28" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF28" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AG28" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
     </row>
@@ -3708,20 +3788,20 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>minimax-m2.5</t>
+          <t>minimax-m2.7</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1403.38</v>
+        <v>1401.86</v>
       </c>
       <c r="D29" t="n">
-        <v>1398.31</v>
+        <v>1394.82</v>
       </c>
       <c r="E29" t="n">
-        <v>1408.44</v>
+        <v>1408.9</v>
       </c>
       <c r="F29" t="n">
-        <v>17217</v>
+        <v>7635</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -3779,148 +3859,68 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>qwen3-235b-a22b-no-thinking</t>
+          <t>minimax-m2.5</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1402.62</v>
+        <v>1401.83</v>
       </c>
       <c r="D30" t="n">
-        <v>1398.13</v>
+        <v>1396.83</v>
       </c>
       <c r="E30" t="n">
-        <v>1407.1</v>
+        <v>1406.82</v>
       </c>
       <c r="F30" t="n">
-        <v>38476</v>
+        <v>18224</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alibaba</t>
+          <t>MiniMax</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
-        </is>
-      </c>
-      <c r="I30" t="n">
-        <v>235</v>
-      </c>
-      <c r="J30" t="n">
-        <v>22</v>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+          <t>Modified MIT</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
-          <t>name_parsing</t>
-        </is>
-      </c>
-      <c r="M30" t="n">
-        <v>470</v>
-      </c>
-      <c r="N30" t="n">
-        <v>587.5</v>
-      </c>
-      <c r="O30" t="n">
-        <v>235</v>
-      </c>
-      <c r="P30" t="n">
-        <v>293.8</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>117.5</v>
-      </c>
-      <c r="R30" t="n">
-        <v>146.9</v>
-      </c>
-      <c r="S30" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T30" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U30" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="V30" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W30" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X30" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Y30" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z30" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AA30" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AB30" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AC30" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AD30" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AE30" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AF30" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AG30" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr"/>
+      <c r="AB30" t="inlineStr"/>
+      <c r="AC30" t="inlineStr"/>
+      <c r="AD30" t="inlineStr"/>
+      <c r="AE30" t="inlineStr"/>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="inlineStr"/>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -3934,16 +3934,16 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1402.09</v>
+        <v>1401.61</v>
       </c>
       <c r="D31" t="n">
-        <v>1396.37</v>
+        <v>1396.01</v>
       </c>
       <c r="E31" t="n">
-        <v>1407.81</v>
+        <v>1407.21</v>
       </c>
       <c r="F31" t="n">
-        <v>11893</v>
+        <v>12770</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -4085,16 +4085,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1401.53</v>
+        <v>1401.34</v>
       </c>
       <c r="D32" t="n">
-        <v>1396.76</v>
+        <v>1396.58</v>
       </c>
       <c r="E32" t="n">
-        <v>1406.29</v>
+        <v>1406.11</v>
       </c>
       <c r="F32" t="n">
-        <v>23076</v>
+        <v>23060</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -4236,16 +4236,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1400.96</v>
+        <v>1400.94</v>
       </c>
       <c r="D33" t="n">
-        <v>1394.59</v>
+        <v>1394.58</v>
       </c>
       <c r="E33" t="n">
-        <v>1407.32</v>
+        <v>1407.3</v>
       </c>
       <c r="F33" t="n">
-        <v>11481</v>
+        <v>11476</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -4387,13 +4387,13 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1399.67</v>
+        <v>1399.57</v>
       </c>
       <c r="D34" t="n">
-        <v>1393.15</v>
+        <v>1393.06</v>
       </c>
       <c r="E34" t="n">
-        <v>1406.18</v>
+        <v>1406.09</v>
       </c>
       <c r="F34" t="n">
         <v>9061</v>
@@ -4538,13 +4538,13 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1397.5</v>
+        <v>1397.48</v>
       </c>
       <c r="D35" t="n">
-        <v>1392.64</v>
+        <v>1392.62</v>
       </c>
       <c r="E35" t="n">
-        <v>1402.36</v>
+        <v>1402.34</v>
       </c>
       <c r="F35" t="n">
         <v>18524</v>
@@ -4689,16 +4689,16 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1395.54</v>
+        <v>1396</v>
       </c>
       <c r="D36" t="n">
-        <v>1389.91</v>
+        <v>1390.5</v>
       </c>
       <c r="E36" t="n">
-        <v>1401.17</v>
+        <v>1401.51</v>
       </c>
       <c r="F36" t="n">
-        <v>12328</v>
+        <v>13268</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -4840,16 +4840,16 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1395.36</v>
+        <v>1395.51</v>
       </c>
       <c r="D37" t="n">
-        <v>1388.6</v>
+        <v>1388.75</v>
       </c>
       <c r="E37" t="n">
-        <v>1402.13</v>
+        <v>1402.28</v>
       </c>
       <c r="F37" t="n">
-        <v>8024</v>
+        <v>8021</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -4991,16 +4991,16 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1394.59</v>
+        <v>1394.49</v>
       </c>
       <c r="D38" t="n">
-        <v>1390.74</v>
+        <v>1390.64</v>
       </c>
       <c r="E38" t="n">
-        <v>1398.44</v>
+        <v>1398.34</v>
       </c>
       <c r="F38" t="n">
-        <v>45800</v>
+        <v>45799</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -5142,16 +5142,16 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1392.1</v>
+        <v>1391.14</v>
       </c>
       <c r="D39" t="n">
-        <v>1388.01</v>
+        <v>1387.09</v>
       </c>
       <c r="E39" t="n">
-        <v>1396.19</v>
+        <v>1395.19</v>
       </c>
       <c r="F39" t="n">
-        <v>30218</v>
+        <v>31132</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -5213,16 +5213,16 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1391.58</v>
+        <v>1390.99</v>
       </c>
       <c r="D40" t="n">
-        <v>1386.69</v>
+        <v>1386.17</v>
       </c>
       <c r="E40" t="n">
-        <v>1396.47</v>
+        <v>1395.81</v>
       </c>
       <c r="F40" t="n">
-        <v>18567</v>
+        <v>19379</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -5293,7 +5293,7 @@
         <v>1392.29</v>
       </c>
       <c r="F41" t="n">
-        <v>25962</v>
+        <v>25958</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -5435,16 +5435,16 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1387.08</v>
+        <v>1386.85</v>
       </c>
       <c r="D42" t="n">
-        <v>1380.81</v>
+        <v>1380.58</v>
       </c>
       <c r="E42" t="n">
-        <v>1393.36</v>
+        <v>1393.12</v>
       </c>
       <c r="F42" t="n">
-        <v>11018</v>
+        <v>11021</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -5506,16 +5506,16 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1385.59</v>
+        <v>1385.3</v>
       </c>
       <c r="D43" t="n">
-        <v>1380.33</v>
+        <v>1380.05</v>
       </c>
       <c r="E43" t="n">
-        <v>1390.85</v>
+        <v>1390.55</v>
       </c>
       <c r="F43" t="n">
-        <v>17231</v>
+        <v>17234</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -5577,16 +5577,16 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1383.04</v>
+        <v>1383.02</v>
       </c>
       <c r="D44" t="n">
-        <v>1378.18</v>
+        <v>1378.15</v>
       </c>
       <c r="E44" t="n">
-        <v>1387.9</v>
+        <v>1387.88</v>
       </c>
       <c r="F44" t="n">
-        <v>23941</v>
+        <v>23932</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -5728,16 +5728,16 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1377.71</v>
+        <v>1377.55</v>
       </c>
       <c r="D45" t="n">
-        <v>1366.43</v>
+        <v>1366.27</v>
       </c>
       <c r="E45" t="n">
-        <v>1388.99</v>
+        <v>1388.84</v>
       </c>
       <c r="F45" t="n">
-        <v>2816</v>
+        <v>2817</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -5795,24 +5795,24 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>qwen3-235b-a22b</t>
+          <t>trinity-large-preview</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1374.43</v>
+        <v>1374.49</v>
       </c>
       <c r="D46" t="n">
-        <v>1369.75</v>
+        <v>1368.99</v>
       </c>
       <c r="E46" t="n">
-        <v>1379.11</v>
+        <v>1379.98</v>
       </c>
       <c r="F46" t="n">
-        <v>26425</v>
+        <v>14164</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alibaba</t>
+          <t>Arcee AI</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -5821,52 +5821,52 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>235</v>
+        <v>70</v>
       </c>
       <c r="J46" t="n">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>moe</t>
+          <t>dense</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>override</t>
         </is>
       </c>
       <c r="M46" t="n">
-        <v>470</v>
+        <v>140</v>
       </c>
       <c r="N46" t="n">
-        <v>587.5</v>
+        <v>175</v>
       </c>
       <c r="O46" t="n">
-        <v>235</v>
+        <v>70</v>
       </c>
       <c r="P46" t="n">
-        <v>293.8</v>
+        <v>87.5</v>
       </c>
       <c r="Q46" t="n">
-        <v>117.5</v>
+        <v>35</v>
       </c>
       <c r="R46" t="n">
-        <v>146.9</v>
+        <v>43.8</v>
       </c>
       <c r="S46" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="T46" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U46" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="T46" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U46" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="V46" s="5" t="inlineStr">
@@ -5879,9 +5879,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="X46" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="X46" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Y46" s="5" t="inlineStr">
@@ -5889,24 +5889,24 @@
           <t>No</t>
         </is>
       </c>
-      <c r="Z46" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AA46" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AB46" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AC46" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="Z46" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AA46" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB46" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AC46" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AD46" s="6" t="inlineStr">
@@ -5914,14 +5914,14 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="AE46" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AF46" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AE46" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AF46" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AG46" s="6" t="inlineStr">
@@ -5931,12 +5931,12 @@
       </c>
       <c r="AH46" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>B200 SXM</t>
         </is>
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>RTX PRO 6000</t>
         </is>
       </c>
     </row>
@@ -5946,24 +5946,24 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>trinity-large-preview</t>
+          <t>qwen3-235b-a22b</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1374.31</v>
+        <v>1374.35</v>
       </c>
       <c r="D47" t="n">
-        <v>1368.7</v>
+        <v>1369.67</v>
       </c>
       <c r="E47" t="n">
-        <v>1379.92</v>
+        <v>1379.03</v>
       </c>
       <c r="F47" t="n">
-        <v>13315</v>
+        <v>26423</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Arcee AI</t>
+          <t>Alibaba</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -5972,52 +5972,52 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>70</v>
+        <v>235</v>
       </c>
       <c r="J47" t="n">
-        <v>70</v>
+        <v>22</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>dense</t>
+          <t>moe</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>name_parsing</t>
         </is>
       </c>
       <c r="M47" t="n">
-        <v>140</v>
+        <v>470</v>
       </c>
       <c r="N47" t="n">
-        <v>175</v>
+        <v>587.5</v>
       </c>
       <c r="O47" t="n">
-        <v>70</v>
+        <v>235</v>
       </c>
       <c r="P47" t="n">
-        <v>87.5</v>
+        <v>293.8</v>
       </c>
       <c r="Q47" t="n">
-        <v>35</v>
+        <v>117.5</v>
       </c>
       <c r="R47" t="n">
-        <v>43.8</v>
+        <v>146.9</v>
       </c>
       <c r="S47" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="T47" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="U47" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="T47" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U47" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="V47" s="5" t="inlineStr">
@@ -6030,9 +6030,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="X47" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="X47" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="Y47" s="5" t="inlineStr">
@@ -6040,24 +6040,24 @@
           <t>No</t>
         </is>
       </c>
-      <c r="Z47" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AA47" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB47" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AC47" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="Z47" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA47" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AB47" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AC47" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AD47" s="6" t="inlineStr">
@@ -6065,14 +6065,14 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="AE47" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AF47" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AE47" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF47" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AG47" s="6" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="AH47" t="inlineStr">
         <is>
-          <t>B200 SXM</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>RTX PRO 6000</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
     </row>
@@ -6101,16 +6101,16 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1372.76</v>
+        <v>1372.81</v>
       </c>
       <c r="D48" t="n">
-        <v>1368.52</v>
+        <v>1368.58</v>
       </c>
       <c r="E48" t="n">
-        <v>1376.99</v>
+        <v>1377.04</v>
       </c>
       <c r="F48" t="n">
-        <v>31387</v>
+        <v>31372</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -6172,16 +6172,16 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1369.03</v>
+        <v>1368.78</v>
       </c>
       <c r="D49" t="n">
-        <v>1363.22</v>
+        <v>1362.97</v>
       </c>
       <c r="E49" t="n">
-        <v>1374.85</v>
+        <v>1374.59</v>
       </c>
       <c r="F49" t="n">
-        <v>13837</v>
+        <v>13836</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -6323,16 +6323,16 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1368.16</v>
+        <v>1367.72</v>
       </c>
       <c r="D50" t="n">
-        <v>1362.34</v>
+        <v>1361.89</v>
       </c>
       <c r="E50" t="n">
-        <v>1373.98</v>
+        <v>1373.54</v>
       </c>
       <c r="F50" t="n">
-        <v>11829</v>
+        <v>11819</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -6394,16 +6394,16 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1365.11</v>
+        <v>1365.05</v>
       </c>
       <c r="D51" t="n">
-        <v>1361.46</v>
+        <v>1361.4</v>
       </c>
       <c r="E51" t="n">
-        <v>1368.77</v>
+        <v>1368.71</v>
       </c>
       <c r="F51" t="n">
-        <v>47852</v>
+        <v>47842</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -6545,16 +6545,16 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1363.35</v>
+        <v>1363.16</v>
       </c>
       <c r="D52" t="n">
-        <v>1359.09</v>
+        <v>1358.9</v>
       </c>
       <c r="E52" t="n">
-        <v>1367.6</v>
+        <v>1367.41</v>
       </c>
       <c r="F52" t="n">
-        <v>35518</v>
+        <v>35505</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -6616,16 +6616,16 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1361.07</v>
+        <v>1360.55</v>
       </c>
       <c r="D53" t="n">
-        <v>1353.78</v>
+        <v>1353.29</v>
       </c>
       <c r="E53" t="n">
-        <v>1368.37</v>
+        <v>1367.82</v>
       </c>
       <c r="F53" t="n">
-        <v>7449</v>
+        <v>7435</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1358.15</v>
+        <v>1358.11</v>
       </c>
       <c r="D54" t="n">
-        <v>1353.43</v>
+        <v>1353.39</v>
       </c>
       <c r="E54" t="n">
-        <v>1362.86</v>
+        <v>1362.83</v>
       </c>
       <c r="F54" t="n">
         <v>21770</v>
@@ -6918,16 +6918,16 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1356.93</v>
+        <v>1356.91</v>
       </c>
       <c r="D55" t="n">
-        <v>1351.75</v>
+        <v>1351.72</v>
       </c>
       <c r="E55" t="n">
-        <v>1362.12</v>
+        <v>1362.09</v>
       </c>
       <c r="F55" t="n">
-        <v>17843</v>
+        <v>17850</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -6989,16 +6989,16 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1356.3</v>
+        <v>1356.2</v>
       </c>
       <c r="D56" t="n">
-        <v>1347.94</v>
+        <v>1347.85</v>
       </c>
       <c r="E56" t="n">
-        <v>1364.65</v>
+        <v>1364.55</v>
       </c>
       <c r="F56" t="n">
-        <v>5356</v>
+        <v>5357</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -7140,16 +7140,16 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1353.77</v>
+        <v>1353.6</v>
       </c>
       <c r="D57" t="n">
-        <v>1349.44</v>
+        <v>1349.26</v>
       </c>
       <c r="E57" t="n">
-        <v>1358.11</v>
+        <v>1357.93</v>
       </c>
       <c r="F57" t="n">
-        <v>30903</v>
+        <v>30883</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -7291,16 +7291,16 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1353.31</v>
+        <v>1353.32</v>
       </c>
       <c r="D58" t="n">
         <v>1349.88</v>
       </c>
       <c r="E58" t="n">
-        <v>1356.74</v>
+        <v>1356.75</v>
       </c>
       <c r="F58" t="n">
-        <v>56670</v>
+        <v>56663</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -7362,16 +7362,16 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1353.08</v>
+        <v>1352.98</v>
       </c>
       <c r="D59" t="n">
-        <v>1344.75</v>
+        <v>1344.66</v>
       </c>
       <c r="E59" t="n">
-        <v>1361.41</v>
+        <v>1361.31</v>
       </c>
       <c r="F59" t="n">
-        <v>4980</v>
+        <v>4983</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -7433,16 +7433,16 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1347.59</v>
+        <v>1347.58</v>
       </c>
       <c r="D60" t="n">
-        <v>1340.21</v>
+        <v>1340.2</v>
       </c>
       <c r="E60" t="n">
-        <v>1354.97</v>
+        <v>1354.96</v>
       </c>
       <c r="F60" t="n">
-        <v>6587</v>
+        <v>6585</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -7504,13 +7504,13 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1347</v>
+        <v>1346.95</v>
       </c>
       <c r="D61" t="n">
-        <v>1337.54</v>
+        <v>1337.49</v>
       </c>
       <c r="E61" t="n">
-        <v>1356.47</v>
+        <v>1356.42</v>
       </c>
       <c r="F61" t="n">
         <v>3926</v>
@@ -7655,13 +7655,13 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1346.83</v>
+        <v>1346.81</v>
       </c>
       <c r="D62" t="n">
-        <v>1335.13</v>
+        <v>1335.12</v>
       </c>
       <c r="E62" t="n">
-        <v>1358.53</v>
+        <v>1358.51</v>
       </c>
       <c r="F62" t="n">
         <v>2549</v>
@@ -7806,16 +7806,16 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1346.39</v>
+        <v>1346.53</v>
       </c>
       <c r="D63" t="n">
-        <v>1338.67</v>
+        <v>1338.8</v>
       </c>
       <c r="E63" t="n">
-        <v>1354.11</v>
+        <v>1354.25</v>
       </c>
       <c r="F63" t="n">
-        <v>6919</v>
+        <v>6908</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -7957,16 +7957,16 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1346.2</v>
+        <v>1346.03</v>
       </c>
       <c r="D64" t="n">
-        <v>1338.97</v>
+        <v>1338.8</v>
       </c>
       <c r="E64" t="n">
-        <v>1353.43</v>
+        <v>1353.25</v>
       </c>
       <c r="F64" t="n">
-        <v>7081</v>
+        <v>7080</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -8028,13 +8028,13 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1342.82</v>
+        <v>1342.77</v>
       </c>
       <c r="D65" t="n">
-        <v>1332.87</v>
+        <v>1332.82</v>
       </c>
       <c r="E65" t="n">
-        <v>1352.77</v>
+        <v>1352.72</v>
       </c>
       <c r="F65" t="n">
         <v>3366</v>
@@ -8179,13 +8179,13 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1341.41</v>
+        <v>1341.42</v>
       </c>
       <c r="D66" t="n">
-        <v>1331.9</v>
+        <v>1331.91</v>
       </c>
       <c r="E66" t="n">
-        <v>1350.93</v>
+        <v>1350.94</v>
       </c>
       <c r="F66" t="n">
         <v>3829</v>
@@ -8330,13 +8330,13 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1335.65</v>
+        <v>1335.61</v>
       </c>
       <c r="D67" t="n">
-        <v>1331.23</v>
+        <v>1331.19</v>
       </c>
       <c r="E67" t="n">
-        <v>1340.07</v>
+        <v>1340.03</v>
       </c>
       <c r="F67" t="n">
         <v>25522</v>
@@ -8481,13 +8481,13 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1334.25</v>
+        <v>1334.24</v>
       </c>
       <c r="D68" t="n">
-        <v>1330.57</v>
+        <v>1330.56</v>
       </c>
       <c r="E68" t="n">
-        <v>1337.93</v>
+        <v>1337.92</v>
       </c>
       <c r="F68" t="n">
         <v>41375</v>
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1332.45</v>
+        <v>1332.44</v>
       </c>
       <c r="D69" t="n">
-        <v>1328.89</v>
+        <v>1328.87</v>
       </c>
       <c r="E69" t="n">
-        <v>1336.02</v>
+        <v>1336.01</v>
       </c>
       <c r="F69" t="n">
         <v>59656</v>
@@ -8783,16 +8783,16 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1330.9</v>
+        <v>1330.72</v>
       </c>
       <c r="D70" t="n">
-        <v>1324.8</v>
+        <v>1324.62</v>
       </c>
       <c r="E70" t="n">
-        <v>1337</v>
+        <v>1336.82</v>
       </c>
       <c r="F70" t="n">
-        <v>12291</v>
+        <v>12285</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -8930,40 +8930,40 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>llama-3.3-nemotron-49b-super-v1</t>
+          <t>qwen3-30b-a3b</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1327.38</v>
+        <v>1327.36</v>
       </c>
       <c r="D71" t="n">
-        <v>1315.21</v>
+        <v>1322.65</v>
       </c>
       <c r="E71" t="n">
-        <v>1339.55</v>
+        <v>1332.07</v>
       </c>
       <c r="F71" t="n">
-        <v>2218</v>
+        <v>26646</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Alibaba</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Apache 2.0</t>
         </is>
       </c>
       <c r="I71" t="n">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="J71" t="n">
-        <v>49</v>
+        <v>3</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>dense</t>
+          <t>moe</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -8972,26 +8972,26 @@
         </is>
       </c>
       <c r="M71" t="n">
-        <v>98</v>
+        <v>60</v>
       </c>
       <c r="N71" t="n">
-        <v>122.5</v>
+        <v>75</v>
       </c>
       <c r="O71" t="n">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="P71" t="n">
-        <v>61.2</v>
+        <v>37.5</v>
       </c>
       <c r="Q71" t="n">
-        <v>24.5</v>
+        <v>15</v>
       </c>
       <c r="R71" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="S71" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+        <v>18.8</v>
+      </c>
+      <c r="S71" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="T71" s="6" t="inlineStr">
@@ -9004,9 +9004,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="V71" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="V71" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W71" s="6" t="inlineStr">
@@ -9066,7 +9066,7 @@
       </c>
       <c r="AH71" t="inlineStr">
         <is>
-          <t>H200 SXM</t>
+          <t>H100 SXM</t>
         </is>
       </c>
       <c r="AI71" t="inlineStr">
@@ -9081,40 +9081,40 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>qwen3-30b-a3b</t>
+          <t>llama-3.3-nemotron-49b-super-v1</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1327.33</v>
+        <v>1327.36</v>
       </c>
       <c r="D72" t="n">
-        <v>1322.61</v>
+        <v>1315.19</v>
       </c>
       <c r="E72" t="n">
-        <v>1332.04</v>
+        <v>1339.52</v>
       </c>
       <c r="F72" t="n">
-        <v>26648</v>
+        <v>2218</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alibaba</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="I72" t="n">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="J72" t="n">
-        <v>3</v>
+        <v>49</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>moe</t>
+          <t>dense</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -9123,26 +9123,26 @@
         </is>
       </c>
       <c r="M72" t="n">
-        <v>60</v>
+        <v>98</v>
       </c>
       <c r="N72" t="n">
-        <v>75</v>
+        <v>122.5</v>
       </c>
       <c r="O72" t="n">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="P72" t="n">
-        <v>37.5</v>
+        <v>61.2</v>
       </c>
       <c r="Q72" t="n">
-        <v>15</v>
+        <v>24.5</v>
       </c>
       <c r="R72" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="S72" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+        <v>30.6</v>
+      </c>
+      <c r="S72" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="T72" s="6" t="inlineStr">
@@ -9155,9 +9155,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="V72" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="V72" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="W72" s="6" t="inlineStr">
@@ -9217,7 +9217,7 @@
       </c>
       <c r="AH72" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>H200 SXM</t>
         </is>
       </c>
       <c r="AI72" t="inlineStr">
@@ -9236,13 +9236,13 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1326.95</v>
+        <v>1326.84</v>
       </c>
       <c r="D73" t="n">
-        <v>1305.57</v>
+        <v>1305.46</v>
       </c>
       <c r="E73" t="n">
-        <v>1348.34</v>
+        <v>1348.23</v>
       </c>
       <c r="F73" t="n">
         <v>806</v>
@@ -9387,16 +9387,16 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1326.67</v>
+        <v>1326.66</v>
       </c>
       <c r="D74" t="n">
-        <v>1322.43</v>
+        <v>1322.42</v>
       </c>
       <c r="E74" t="n">
-        <v>1330.9</v>
+        <v>1330.89</v>
       </c>
       <c r="F74" t="n">
-        <v>40222</v>
+        <v>40214</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -9538,13 +9538,13 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>1323.07</v>
+        <v>1323.03</v>
       </c>
       <c r="D75" t="n">
-        <v>1314.81</v>
+        <v>1314.77</v>
       </c>
       <c r="E75" t="n">
-        <v>1331.34</v>
+        <v>1331.3</v>
       </c>
       <c r="F75" t="n">
         <v>6795</v>
@@ -9609,16 +9609,16 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>1322.03</v>
+        <v>1321.92</v>
       </c>
       <c r="D76" t="n">
-        <v>1317.34</v>
+        <v>1317.23</v>
       </c>
       <c r="E76" t="n">
-        <v>1326.73</v>
+        <v>1326.62</v>
       </c>
       <c r="F76" t="n">
-        <v>30494</v>
+        <v>30488</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -9760,13 +9760,13 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1320.78</v>
+        <v>1320.63</v>
       </c>
       <c r="D77" t="n">
-        <v>1313.6</v>
+        <v>1313.45</v>
       </c>
       <c r="E77" t="n">
-        <v>1327.97</v>
+        <v>1327.81</v>
       </c>
       <c r="F77" t="n">
         <v>7221</v>
@@ -9831,13 +9831,13 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1318.03</v>
+        <v>1318.04</v>
       </c>
       <c r="D78" t="n">
-        <v>1312.89</v>
+        <v>1312.9</v>
       </c>
       <c r="E78" t="n">
-        <v>1323.16</v>
+        <v>1323.17</v>
       </c>
       <c r="F78" t="n">
         <v>22723</v>
@@ -9982,16 +9982,16 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>1317.94</v>
+        <v>1317.97</v>
       </c>
       <c r="D79" t="n">
-        <v>1314.51</v>
+        <v>1314.53</v>
       </c>
       <c r="E79" t="n">
-        <v>1321.38</v>
+        <v>1321.4</v>
       </c>
       <c r="F79" t="n">
-        <v>54888</v>
+        <v>54884</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -10133,16 +10133,16 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1317.71</v>
+        <v>1317.67</v>
       </c>
       <c r="D80" t="n">
-        <v>1311.36</v>
+        <v>1311.32</v>
       </c>
       <c r="E80" t="n">
-        <v>1324.06</v>
+        <v>1324.02</v>
       </c>
       <c r="F80" t="n">
-        <v>10701</v>
+        <v>10695</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -10280,148 +10280,68 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>nvidia-nemotron-3-nano-30b-a3b-bf16</t>
+          <t>qwen-max-0919</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1317.49</v>
+        <v>1317.45</v>
       </c>
       <c r="D81" t="n">
-        <v>1311.91</v>
+        <v>1311.76</v>
       </c>
       <c r="E81" t="n">
-        <v>1323.07</v>
+        <v>1323.14</v>
       </c>
       <c r="F81" t="n">
-        <v>15589</v>
+        <v>16478</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Alibaba</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>NVIDIA Open Model</t>
-        </is>
-      </c>
-      <c r="I81" t="n">
-        <v>30</v>
-      </c>
-      <c r="J81" t="n">
-        <v>3</v>
-      </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+          <t>Qwen</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr">
         <is>
-          <t>name_parsing</t>
-        </is>
-      </c>
-      <c r="M81" t="n">
-        <v>60</v>
-      </c>
-      <c r="N81" t="n">
-        <v>75</v>
-      </c>
-      <c r="O81" t="n">
-        <v>30</v>
-      </c>
-      <c r="P81" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="Q81" t="n">
-        <v>15</v>
-      </c>
-      <c r="R81" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="S81" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="T81" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="U81" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="V81" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W81" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X81" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Y81" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z81" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AA81" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB81" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AC81" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AD81" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AE81" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AF81" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AG81" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" t="inlineStr"/>
+      <c r="P81" t="inlineStr"/>
+      <c r="Q81" t="inlineStr"/>
+      <c r="R81" t="inlineStr"/>
+      <c r="S81" t="inlineStr"/>
+      <c r="T81" t="inlineStr"/>
+      <c r="U81" t="inlineStr"/>
+      <c r="V81" t="inlineStr"/>
+      <c r="W81" t="inlineStr"/>
+      <c r="X81" t="inlineStr"/>
+      <c r="Y81" t="inlineStr"/>
+      <c r="Z81" t="inlineStr"/>
+      <c r="AA81" t="inlineStr"/>
+      <c r="AB81" t="inlineStr"/>
+      <c r="AC81" t="inlineStr"/>
+      <c r="AD81" t="inlineStr"/>
+      <c r="AE81" t="inlineStr"/>
+      <c r="AF81" t="inlineStr"/>
+      <c r="AG81" t="inlineStr"/>
       <c r="AH81" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -10431,68 +10351,148 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>qwen-max-0919</t>
+          <t>nvidia-nemotron-3-nano-30b-a3b-bf16</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>1317.48</v>
+        <v>1317.41</v>
       </c>
       <c r="D82" t="n">
-        <v>1311.8</v>
+        <v>1311.83</v>
       </c>
       <c r="E82" t="n">
-        <v>1323.17</v>
+        <v>1322.99</v>
       </c>
       <c r="F82" t="n">
-        <v>16478</v>
+        <v>15590</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alibaba</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Qwen</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
+          <t>NVIDIA Open Model</t>
+        </is>
+      </c>
+      <c r="I82" t="n">
+        <v>30</v>
+      </c>
+      <c r="J82" t="n">
+        <v>3</v>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="M82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
-      <c r="O82" t="inlineStr"/>
-      <c r="P82" t="inlineStr"/>
-      <c r="Q82" t="inlineStr"/>
-      <c r="R82" t="inlineStr"/>
-      <c r="S82" t="inlineStr"/>
-      <c r="T82" t="inlineStr"/>
-      <c r="U82" t="inlineStr"/>
-      <c r="V82" t="inlineStr"/>
-      <c r="W82" t="inlineStr"/>
-      <c r="X82" t="inlineStr"/>
-      <c r="Y82" t="inlineStr"/>
-      <c r="Z82" t="inlineStr"/>
-      <c r="AA82" t="inlineStr"/>
-      <c r="AB82" t="inlineStr"/>
-      <c r="AC82" t="inlineStr"/>
-      <c r="AD82" t="inlineStr"/>
-      <c r="AE82" t="inlineStr"/>
-      <c r="AF82" t="inlineStr"/>
-      <c r="AG82" t="inlineStr"/>
+          <t>name_parsing</t>
+        </is>
+      </c>
+      <c r="M82" t="n">
+        <v>60</v>
+      </c>
+      <c r="N82" t="n">
+        <v>75</v>
+      </c>
+      <c r="O82" t="n">
+        <v>30</v>
+      </c>
+      <c r="P82" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>15</v>
+      </c>
+      <c r="R82" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="S82" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T82" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U82" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V82" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W82" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X82" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y82" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z82" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AA82" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB82" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AC82" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AD82" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE82" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AF82" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AG82" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AH82" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>H100 SXM</t>
         </is>
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>H100 SXM</t>
         </is>
       </c>
     </row>
@@ -10506,13 +10506,13 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>1314.06</v>
+        <v>1314.01</v>
       </c>
       <c r="D83" t="n">
-        <v>1309.53</v>
+        <v>1309.49</v>
       </c>
       <c r="E83" t="n">
-        <v>1318.58</v>
+        <v>1318.54</v>
       </c>
       <c r="F83" t="n">
         <v>24739</v>
@@ -10657,13 +10657,13 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>1313.36</v>
+        <v>1313.34</v>
       </c>
       <c r="D84" t="n">
-        <v>1309.46</v>
+        <v>1309.44</v>
       </c>
       <c r="E84" t="n">
-        <v>1317.27</v>
+        <v>1317.24</v>
       </c>
       <c r="F84" t="n">
         <v>45459</v>
@@ -10808,13 +10808,13 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>1306.63</v>
+        <v>1306.59</v>
       </c>
       <c r="D85" t="n">
-        <v>1301.94</v>
+        <v>1301.91</v>
       </c>
       <c r="E85" t="n">
-        <v>1311.31</v>
+        <v>1311.28</v>
       </c>
       <c r="F85" t="n">
         <v>24572</v>
@@ -10879,13 +10879,13 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>1305.52</v>
+        <v>1305.53</v>
       </c>
       <c r="D86" t="n">
-        <v>1299.85</v>
+        <v>1299.86</v>
       </c>
       <c r="E86" t="n">
-        <v>1311.18</v>
+        <v>1311.19</v>
       </c>
       <c r="F86" t="n">
         <v>19621</v>
@@ -11030,16 +11030,16 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>1305.35</v>
+        <v>1305.34</v>
       </c>
       <c r="D87" t="n">
-        <v>1297.17</v>
+        <v>1297.16</v>
       </c>
       <c r="E87" t="n">
-        <v>1313.52</v>
+        <v>1313.51</v>
       </c>
       <c r="F87" t="n">
-        <v>5987</v>
+        <v>5986</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -11181,13 +11181,13 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>1304.68</v>
+        <v>1304.66</v>
       </c>
       <c r="D88" t="n">
-        <v>1300.27</v>
+        <v>1300.25</v>
       </c>
       <c r="E88" t="n">
-        <v>1309.08</v>
+        <v>1309.06</v>
       </c>
       <c r="F88" t="n">
         <v>28073</v>
@@ -11252,13 +11252,13 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>1302.8</v>
+        <v>1302.81</v>
       </c>
       <c r="D89" t="n">
-        <v>1293.48</v>
+        <v>1293.49</v>
       </c>
       <c r="E89" t="n">
-        <v>1312.11</v>
+        <v>1312.12</v>
       </c>
       <c r="F89" t="n">
         <v>4171</v>
@@ -11403,16 +11403,16 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>1302.77</v>
+        <v>1302.67</v>
       </c>
       <c r="D90" t="n">
-        <v>1298.27</v>
+        <v>1298.18</v>
       </c>
       <c r="E90" t="n">
-        <v>1307.26</v>
+        <v>1307.16</v>
       </c>
       <c r="F90" t="n">
-        <v>33474</v>
+        <v>33462</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -11554,13 +11554,13 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>1302.33</v>
+        <v>1302.3</v>
       </c>
       <c r="D91" t="n">
-        <v>1298.29</v>
+        <v>1298.26</v>
       </c>
       <c r="E91" t="n">
-        <v>1306.38</v>
+        <v>1306.34</v>
       </c>
       <c r="F91" t="n">
         <v>39406</v>
@@ -11708,10 +11708,10 @@
         <v>1298.46</v>
       </c>
       <c r="D92" t="n">
-        <v>1290.71</v>
+        <v>1290.7</v>
       </c>
       <c r="E92" t="n">
-        <v>1306.22</v>
+        <v>1306.21</v>
       </c>
       <c r="F92" t="n">
         <v>7140</v>
@@ -11856,13 +11856,13 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>1292.81</v>
+        <v>1292.79</v>
       </c>
       <c r="D93" t="n">
-        <v>1289.1</v>
+        <v>1289.09</v>
       </c>
       <c r="E93" t="n">
-        <v>1296.52</v>
+        <v>1296.5</v>
       </c>
       <c r="F93" t="n">
         <v>55240</v>
@@ -12007,13 +12007,13 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1288.23</v>
+        <v>1288.21</v>
       </c>
       <c r="D94" t="n">
-        <v>1280.93</v>
+        <v>1280.91</v>
       </c>
       <c r="E94" t="n">
-        <v>1295.53</v>
+        <v>1295.51</v>
       </c>
       <c r="F94" t="n">
         <v>8662</v>
@@ -12078,13 +12078,13 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1287.64</v>
+        <v>1287.67</v>
       </c>
       <c r="D95" t="n">
-        <v>1284.29</v>
+        <v>1284.32</v>
       </c>
       <c r="E95" t="n">
-        <v>1290.99</v>
+        <v>1291.02</v>
       </c>
       <c r="F95" t="n">
         <v>75754</v>
@@ -12229,16 +12229,16 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>1287.03</v>
+        <v>1286.74</v>
       </c>
       <c r="D96" t="n">
-        <v>1278.69</v>
+        <v>1278.4</v>
       </c>
       <c r="E96" t="n">
-        <v>1295.37</v>
+        <v>1295.09</v>
       </c>
       <c r="F96" t="n">
-        <v>5743</v>
+        <v>5747</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
@@ -12380,13 +12380,13 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1285.81</v>
+        <v>1285.78</v>
       </c>
       <c r="D97" t="n">
-        <v>1275.33</v>
+        <v>1275.3</v>
       </c>
       <c r="E97" t="n">
-        <v>1296.28</v>
+        <v>1296.25</v>
       </c>
       <c r="F97" t="n">
         <v>2846</v>
@@ -12531,13 +12531,13 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>1285.44</v>
+        <v>1285.35</v>
       </c>
       <c r="D98" t="n">
-        <v>1278.22</v>
+        <v>1278.13</v>
       </c>
       <c r="E98" t="n">
-        <v>1292.67</v>
+        <v>1292.57</v>
       </c>
       <c r="F98" t="n">
         <v>8544</v>
@@ -12682,13 +12682,13 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>1285.32</v>
+        <v>1285.3</v>
       </c>
       <c r="D99" t="n">
-        <v>1275.35</v>
+        <v>1275.33</v>
       </c>
       <c r="E99" t="n">
-        <v>1295.29</v>
+        <v>1295.28</v>
       </c>
       <c r="F99" t="n">
         <v>3749</v>
@@ -12833,13 +12833,13 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>1278.88</v>
+        <v>1278.9</v>
       </c>
       <c r="D100" t="n">
-        <v>1272.02</v>
+        <v>1272.04</v>
       </c>
       <c r="E100" t="n">
-        <v>1285.74</v>
+        <v>1285.75</v>
       </c>
       <c r="F100" t="n">
         <v>10072</v>
@@ -12984,13 +12984,13 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1276.24</v>
+        <v>1276.21</v>
       </c>
       <c r="D101" t="n">
-        <v>1270.92</v>
+        <v>1270.88</v>
       </c>
       <c r="E101" t="n">
-        <v>1281.57</v>
+        <v>1281.54</v>
       </c>
       <c r="F101" t="n">
         <v>19659</v>
@@ -13135,13 +13135,13 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>1275.51</v>
+        <v>1275.47</v>
       </c>
       <c r="D102" t="n">
-        <v>1268.94</v>
+        <v>1268.91</v>
       </c>
       <c r="E102" t="n">
-        <v>1282.08</v>
+        <v>1282.04</v>
       </c>
       <c r="F102" t="n">
         <v>9866</v>
@@ -13286,7 +13286,7 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>1275.19</v>
+        <v>1275.18</v>
       </c>
       <c r="D103" t="n">
         <v>1271.61</v>
@@ -13437,13 +13437,13 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>1273.47</v>
+        <v>1273.45</v>
       </c>
       <c r="D104" t="n">
-        <v>1267.59</v>
+        <v>1267.56</v>
       </c>
       <c r="E104" t="n">
-        <v>1279.36</v>
+        <v>1279.34</v>
       </c>
       <c r="F104" t="n">
         <v>14681</v>
@@ -13588,13 +13588,13 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>1269.93</v>
+        <v>1269.9</v>
       </c>
       <c r="D105" t="n">
-        <v>1261.81</v>
+        <v>1261.78</v>
       </c>
       <c r="E105" t="n">
-        <v>1278.05</v>
+        <v>1278.02</v>
       </c>
       <c r="F105" t="n">
         <v>5432</v>
@@ -13739,10 +13739,10 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>1266.3</v>
+        <v>1266.29</v>
       </c>
       <c r="D106" t="n">
-        <v>1261.44</v>
+        <v>1261.43</v>
       </c>
       <c r="E106" t="n">
         <v>1271.16</v>
@@ -13890,13 +13890,13 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>1265.11</v>
+        <v>1265.14</v>
       </c>
       <c r="D107" t="n">
-        <v>1261.32</v>
+        <v>1261.35</v>
       </c>
       <c r="E107" t="n">
-        <v>1268.9</v>
+        <v>1268.93</v>
       </c>
       <c r="F107" t="n">
         <v>54611</v>
@@ -14041,13 +14041,13 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>1263.45</v>
+        <v>1263.44</v>
       </c>
       <c r="D108" t="n">
-        <v>1257.17</v>
+        <v>1257.16</v>
       </c>
       <c r="E108" t="n">
-        <v>1269.73</v>
+        <v>1269.72</v>
       </c>
       <c r="F108" t="n">
         <v>15147</v>
@@ -14192,13 +14192,13 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>1260.76</v>
+        <v>1260.72</v>
       </c>
       <c r="D109" t="n">
-        <v>1256.44</v>
+        <v>1256.4</v>
       </c>
       <c r="E109" t="n">
-        <v>1265.08</v>
+        <v>1265.04</v>
       </c>
       <c r="F109" t="n">
         <v>77554</v>
@@ -14263,13 +14263,13 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>1260.75</v>
+        <v>1260.71</v>
       </c>
       <c r="D110" t="n">
-        <v>1255.81</v>
+        <v>1255.78</v>
       </c>
       <c r="E110" t="n">
-        <v>1265.68</v>
+        <v>1265.65</v>
       </c>
       <c r="F110" t="n">
         <v>37325</v>
@@ -14414,13 +14414,13 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>1255.46</v>
+        <v>1255.44</v>
       </c>
       <c r="D111" t="n">
-        <v>1250.9</v>
+        <v>1250.87</v>
       </c>
       <c r="E111" t="n">
-        <v>1260.03</v>
+        <v>1260.01</v>
       </c>
       <c r="F111" t="n">
         <v>24126</v>
@@ -14565,13 +14565,13 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>1251.17</v>
+        <v>1251.14</v>
       </c>
       <c r="D112" t="n">
-        <v>1240.38</v>
+        <v>1240.35</v>
       </c>
       <c r="E112" t="n">
-        <v>1261.96</v>
+        <v>1261.93</v>
       </c>
       <c r="F112" t="n">
         <v>3334</v>
@@ -14716,13 +14716,13 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>1249.1</v>
+        <v>1249.08</v>
       </c>
       <c r="D113" t="n">
-        <v>1242.51</v>
+        <v>1242.48</v>
       </c>
       <c r="E113" t="n">
-        <v>1255.7</v>
+        <v>1255.67</v>
       </c>
       <c r="F113" t="n">
         <v>10140</v>
@@ -14870,7 +14870,7 @@
         <v>1238.42</v>
       </c>
       <c r="D114" t="n">
-        <v>1231.2</v>
+        <v>1231.19</v>
       </c>
       <c r="E114" t="n">
         <v>1245.64</v>
@@ -14938,13 +14938,13 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>1236.61</v>
+        <v>1236.59</v>
       </c>
       <c r="D115" t="n">
-        <v>1227.52</v>
+        <v>1227.49</v>
       </c>
       <c r="E115" t="n">
-        <v>1245.71</v>
+        <v>1245.68</v>
       </c>
       <c r="F115" t="n">
         <v>4781</v>
@@ -15089,13 +15089,13 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>1233.01</v>
+        <v>1232.99</v>
       </c>
       <c r="D116" t="n">
-        <v>1227.46</v>
+        <v>1227.43</v>
       </c>
       <c r="E116" t="n">
-        <v>1238.57</v>
+        <v>1238.54</v>
       </c>
       <c r="F116" t="n">
         <v>26195</v>
@@ -15240,13 +15240,13 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>1232.06</v>
+        <v>1232.04</v>
       </c>
       <c r="D117" t="n">
-        <v>1226.79</v>
+        <v>1226.76</v>
       </c>
       <c r="E117" t="n">
-        <v>1237.34</v>
+        <v>1237.32</v>
       </c>
       <c r="F117" t="n">
         <v>39302</v>
@@ -15391,13 +15391,13 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>1228.25</v>
+        <v>1228.22</v>
       </c>
       <c r="D118" t="n">
-        <v>1223.7</v>
+        <v>1223.67</v>
       </c>
       <c r="E118" t="n">
-        <v>1232.8</v>
+        <v>1232.77</v>
       </c>
       <c r="F118" t="n">
         <v>51416</v>
@@ -15542,13 +15542,13 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>1225.73</v>
+        <v>1225.69</v>
       </c>
       <c r="D119" t="n">
-        <v>1220.94</v>
+        <v>1220.91</v>
       </c>
       <c r="E119" t="n">
-        <v>1230.51</v>
+        <v>1230.47</v>
       </c>
       <c r="F119" t="n">
         <v>54036</v>
@@ -15616,7 +15616,7 @@
         <v>1222.26</v>
       </c>
       <c r="D120" t="n">
-        <v>1215.31</v>
+        <v>1215.3</v>
       </c>
       <c r="E120" t="n">
         <v>1229.22</v>
@@ -15764,13 +15764,13 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>1222.25</v>
+        <v>1222.24</v>
       </c>
       <c r="D121" t="n">
         <v>1218.52</v>
       </c>
       <c r="E121" t="n">
-        <v>1225.98</v>
+        <v>1225.97</v>
       </c>
       <c r="F121" t="n">
         <v>104642</v>
@@ -15915,13 +15915,13 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>1220.35</v>
+        <v>1220.32</v>
       </c>
       <c r="D122" t="n">
-        <v>1209.67</v>
+        <v>1209.63</v>
       </c>
       <c r="E122" t="n">
-        <v>1231.04</v>
+        <v>1231</v>
       </c>
       <c r="F122" t="n">
         <v>2896</v>
@@ -16066,13 +16066,13 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>1212.41</v>
+        <v>1212.37</v>
       </c>
       <c r="D123" t="n">
-        <v>1207.37</v>
+        <v>1207.33</v>
       </c>
       <c r="E123" t="n">
-        <v>1217.44</v>
+        <v>1217.4</v>
       </c>
       <c r="F123" t="n">
         <v>24146</v>
@@ -16217,13 +16217,13 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>1211.56</v>
+        <v>1211.53</v>
       </c>
       <c r="D124" t="n">
-        <v>1200.75</v>
+        <v>1200.72</v>
       </c>
       <c r="E124" t="n">
-        <v>1222.37</v>
+        <v>1222.34</v>
       </c>
       <c r="F124" t="n">
         <v>4652</v>
@@ -16368,13 +16368,13 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>1211.03</v>
+        <v>1211.01</v>
       </c>
       <c r="D125" t="n">
-        <v>1206.91</v>
+        <v>1206.88</v>
       </c>
       <c r="E125" t="n">
-        <v>1215.16</v>
+        <v>1215.13</v>
       </c>
       <c r="F125" t="n">
         <v>49605</v>
@@ -16519,13 +16519,13 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>1207.34</v>
+        <v>1207.32</v>
       </c>
       <c r="D126" t="n">
-        <v>1196.23</v>
+        <v>1196.21</v>
       </c>
       <c r="E126" t="n">
-        <v>1218.46</v>
+        <v>1218.43</v>
       </c>
       <c r="F126" t="n">
         <v>3090</v>
@@ -16670,13 +16670,13 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>1202.67</v>
+        <v>1202.64</v>
       </c>
       <c r="D127" t="n">
-        <v>1196.55</v>
+        <v>1196.52</v>
       </c>
       <c r="E127" t="n">
-        <v>1208.79</v>
+        <v>1208.76</v>
       </c>
       <c r="F127" t="n">
         <v>21741</v>
@@ -16821,13 +16821,13 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>1198.6</v>
+        <v>1198.64</v>
       </c>
       <c r="D128" t="n">
-        <v>1194.53</v>
+        <v>1194.57</v>
       </c>
       <c r="E128" t="n">
-        <v>1202.67</v>
+        <v>1202.7</v>
       </c>
       <c r="F128" t="n">
         <v>46616</v>
@@ -16972,13 +16972,13 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>1196.8</v>
+        <v>1196.77</v>
       </c>
       <c r="D129" t="n">
-        <v>1191.65</v>
+        <v>1191.61</v>
       </c>
       <c r="E129" t="n">
-        <v>1201.95</v>
+        <v>1201.92</v>
       </c>
       <c r="F129" t="n">
         <v>25055</v>
@@ -17123,13 +17123,13 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>1195.93</v>
+        <v>1195.9</v>
       </c>
       <c r="D130" t="n">
-        <v>1191.66</v>
+        <v>1191.63</v>
       </c>
       <c r="E130" t="n">
-        <v>1200.2</v>
+        <v>1200.17</v>
       </c>
       <c r="F130" t="n">
         <v>73503</v>
@@ -17274,13 +17274,13 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>1193.86</v>
+        <v>1193.84</v>
       </c>
       <c r="D131" t="n">
-        <v>1187.75</v>
+        <v>1187.72</v>
       </c>
       <c r="E131" t="n">
-        <v>1199.98</v>
+        <v>1199.95</v>
       </c>
       <c r="F131" t="n">
         <v>32191</v>
@@ -17345,13 +17345,13 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>1190.43</v>
+        <v>1190.4</v>
       </c>
       <c r="D132" t="n">
-        <v>1183.26</v>
+        <v>1183.23</v>
       </c>
       <c r="E132" t="n">
-        <v>1197.61</v>
+        <v>1197.58</v>
       </c>
       <c r="F132" t="n">
         <v>9901</v>
@@ -17496,13 +17496,13 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>1189.79</v>
+        <v>1189.77</v>
       </c>
       <c r="D133" t="n">
-        <v>1182.67</v>
+        <v>1182.64</v>
       </c>
       <c r="E133" t="n">
-        <v>1196.92</v>
+        <v>1196.89</v>
       </c>
       <c r="F133" t="n">
         <v>17839</v>
@@ -17647,13 +17647,13 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>1183.46</v>
+        <v>1183.43</v>
       </c>
       <c r="D134" t="n">
-        <v>1174</v>
+        <v>1173.97</v>
       </c>
       <c r="E134" t="n">
-        <v>1192.91</v>
+        <v>1192.88</v>
       </c>
       <c r="F134" t="n">
         <v>8214</v>
@@ -17798,13 +17798,13 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>1183.18</v>
+        <v>1183.15</v>
       </c>
       <c r="D135" t="n">
-        <v>1171.67</v>
+        <v>1171.64</v>
       </c>
       <c r="E135" t="n">
-        <v>1194.69</v>
+        <v>1194.67</v>
       </c>
       <c r="F135" t="n">
         <v>4932</v>
@@ -17949,13 +17949,13 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>1182.73</v>
+        <v>1182.71</v>
       </c>
       <c r="D136" t="n">
-        <v>1175.9</v>
+        <v>1175.88</v>
       </c>
       <c r="E136" t="n">
-        <v>1189.57</v>
+        <v>1189.54</v>
       </c>
       <c r="F136" t="n">
         <v>15483</v>
@@ -18100,13 +18100,13 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>1181.06</v>
+        <v>1181.03</v>
       </c>
       <c r="D137" t="n">
-        <v>1173.05</v>
+        <v>1173.03</v>
       </c>
       <c r="E137" t="n">
-        <v>1189.06</v>
+        <v>1189.04</v>
       </c>
       <c r="F137" t="n">
         <v>12637</v>
@@ -18171,13 +18171,13 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>1181.01</v>
+        <v>1180.99</v>
       </c>
       <c r="D138" t="n">
-        <v>1171.33</v>
+        <v>1171.31</v>
       </c>
       <c r="E138" t="n">
-        <v>1190.69</v>
+        <v>1190.67</v>
       </c>
       <c r="F138" t="n">
         <v>7968</v>
@@ -18242,13 +18242,13 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>1180.95</v>
+        <v>1180.94</v>
       </c>
       <c r="D139" t="n">
         <v>1172.26</v>
       </c>
       <c r="E139" t="n">
-        <v>1189.64</v>
+        <v>1189.63</v>
       </c>
       <c r="F139" t="n">
         <v>6638</v>
@@ -18393,13 +18393,13 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>1179.71</v>
+        <v>1179.75</v>
       </c>
       <c r="D140" t="n">
-        <v>1173.64</v>
+        <v>1173.68</v>
       </c>
       <c r="E140" t="n">
-        <v>1185.78</v>
+        <v>1185.82</v>
       </c>
       <c r="F140" t="n">
         <v>23893</v>
@@ -18544,13 +18544,13 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>1178.28</v>
+        <v>1178.25</v>
       </c>
       <c r="D141" t="n">
-        <v>1172.36</v>
+        <v>1172.34</v>
       </c>
       <c r="E141" t="n">
-        <v>1184.19</v>
+        <v>1184.17</v>
       </c>
       <c r="F141" t="n">
         <v>32832</v>
@@ -18615,13 +18615,13 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>1177.91</v>
+        <v>1177.89</v>
       </c>
       <c r="D142" t="n">
-        <v>1166.7</v>
+        <v>1166.68</v>
       </c>
       <c r="E142" t="n">
-        <v>1189.11</v>
+        <v>1189.09</v>
       </c>
       <c r="F142" t="n">
         <v>3188</v>
@@ -18766,13 +18766,13 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>1176.78</v>
+        <v>1176.74</v>
       </c>
       <c r="D143" t="n">
-        <v>1166.96</v>
+        <v>1166.92</v>
       </c>
       <c r="E143" t="n">
-        <v>1186.61</v>
+        <v>1186.56</v>
       </c>
       <c r="F143" t="n">
         <v>6535</v>
@@ -18917,13 +18917,13 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>1173.98</v>
+        <v>1173.96</v>
       </c>
       <c r="D144" t="n">
-        <v>1163.55</v>
+        <v>1163.54</v>
       </c>
       <c r="E144" t="n">
-        <v>1184.41</v>
+        <v>1184.39</v>
       </c>
       <c r="F144" t="n">
         <v>5006</v>
@@ -19068,13 +19068,13 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>1171.56</v>
+        <v>1171.53</v>
       </c>
       <c r="D145" t="n">
-        <v>1165.35</v>
+        <v>1165.32</v>
       </c>
       <c r="E145" t="n">
-        <v>1177.77</v>
+        <v>1177.74</v>
       </c>
       <c r="F145" t="n">
         <v>22479</v>
@@ -19219,13 +19219,13 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>1170.47</v>
+        <v>1170.43</v>
       </c>
       <c r="D146" t="n">
-        <v>1163.05</v>
+        <v>1163.02</v>
       </c>
       <c r="E146" t="n">
-        <v>1177.88</v>
+        <v>1177.85</v>
       </c>
       <c r="F146" t="n">
         <v>16056</v>
@@ -19370,13 +19370,13 @@
         </is>
       </c>
       <c r="C147" t="n">
-        <v>1169.94</v>
+        <v>1169.91</v>
       </c>
       <c r="D147" t="n">
-        <v>1164.03</v>
+        <v>1164</v>
       </c>
       <c r="E147" t="n">
-        <v>1175.86</v>
+        <v>1175.83</v>
       </c>
       <c r="F147" t="n">
         <v>17766</v>
@@ -19521,13 +19521,13 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>1169.61</v>
+        <v>1169.58</v>
       </c>
       <c r="D148" t="n">
-        <v>1164.1</v>
+        <v>1164.07</v>
       </c>
       <c r="E148" t="n">
-        <v>1175.11</v>
+        <v>1175.08</v>
       </c>
       <c r="F148" t="n">
         <v>38492</v>
@@ -19672,13 +19672,13 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>1166.32</v>
+        <v>1166.29</v>
       </c>
       <c r="D149" t="n">
-        <v>1158.25</v>
+        <v>1158.21</v>
       </c>
       <c r="E149" t="n">
-        <v>1174.39</v>
+        <v>1174.36</v>
       </c>
       <c r="F149" t="n">
         <v>10224</v>
@@ -19823,13 +19823,13 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>1165.69</v>
+        <v>1165.67</v>
       </c>
       <c r="D150" t="n">
-        <v>1158</v>
+        <v>1157.98</v>
       </c>
       <c r="E150" t="n">
-        <v>1173.39</v>
+        <v>1173.37</v>
       </c>
       <c r="F150" t="n">
         <v>7936</v>
@@ -19974,13 +19974,13 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>1163.53</v>
+        <v>1163.5</v>
       </c>
       <c r="D151" t="n">
-        <v>1151.6</v>
+        <v>1151.56</v>
       </c>
       <c r="E151" t="n">
-        <v>1175.47</v>
+        <v>1175.44</v>
       </c>
       <c r="F151" t="n">
         <v>3777</v>
@@ -20125,13 +20125,13 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>1155.82</v>
+        <v>1155.74</v>
       </c>
       <c r="D152" t="n">
-        <v>1144.32</v>
+        <v>1144.23</v>
       </c>
       <c r="E152" t="n">
-        <v>1167.32</v>
+        <v>1167.24</v>
       </c>
       <c r="F152" t="n">
         <v>3231</v>
@@ -20276,13 +20276,13 @@
         </is>
       </c>
       <c r="C153" t="n">
-        <v>1154.91</v>
+        <v>1154.89</v>
       </c>
       <c r="D153" t="n">
-        <v>1146.52</v>
+        <v>1146.5</v>
       </c>
       <c r="E153" t="n">
-        <v>1163.3</v>
+        <v>1163.28</v>
       </c>
       <c r="F153" t="n">
         <v>6837</v>
@@ -20427,13 +20427,13 @@
         </is>
       </c>
       <c r="C154" t="n">
-        <v>1154.04</v>
+        <v>1153.98</v>
       </c>
       <c r="D154" t="n">
-        <v>1141.42</v>
+        <v>1141.36</v>
       </c>
       <c r="E154" t="n">
-        <v>1166.66</v>
+        <v>1166.6</v>
       </c>
       <c r="F154" t="n">
         <v>3585</v>
@@ -20578,13 +20578,13 @@
         </is>
       </c>
       <c r="C155" t="n">
-        <v>1151.11</v>
+        <v>1151.08</v>
       </c>
       <c r="D155" t="n">
-        <v>1137.91</v>
+        <v>1137.87</v>
       </c>
       <c r="E155" t="n">
-        <v>1164.32</v>
+        <v>1164.28</v>
       </c>
       <c r="F155" t="n">
         <v>4155</v>
@@ -20729,13 +20729,13 @@
         </is>
       </c>
       <c r="C156" t="n">
-        <v>1150.78</v>
+        <v>1150.76</v>
       </c>
       <c r="D156" t="n">
-        <v>1135.39</v>
+        <v>1135.36</v>
       </c>
       <c r="E156" t="n">
-        <v>1166.17</v>
+        <v>1166.14</v>
       </c>
       <c r="F156" t="n">
         <v>1679</v>
@@ -20880,13 +20880,13 @@
         </is>
       </c>
       <c r="C157" t="n">
-        <v>1148.88</v>
+        <v>1148.86</v>
       </c>
       <c r="D157" t="n">
-        <v>1136.58</v>
+        <v>1136.57</v>
       </c>
       <c r="E157" t="n">
-        <v>1161.18</v>
+        <v>1161.16</v>
       </c>
       <c r="F157" t="n">
         <v>2572</v>
@@ -21031,13 +21031,13 @@
         </is>
       </c>
       <c r="C158" t="n">
-        <v>1148.37</v>
+        <v>1148.33</v>
       </c>
       <c r="D158" t="n">
-        <v>1141.71</v>
+        <v>1141.67</v>
       </c>
       <c r="E158" t="n">
-        <v>1155.02</v>
+        <v>1154.98</v>
       </c>
       <c r="F158" t="n">
         <v>19402</v>
@@ -21182,13 +21182,13 @@
         </is>
       </c>
       <c r="C159" t="n">
-        <v>1147.98</v>
+        <v>1147.96</v>
       </c>
       <c r="D159" t="n">
-        <v>1138.72</v>
+        <v>1138.69</v>
       </c>
       <c r="E159" t="n">
-        <v>1157.24</v>
+        <v>1157.22</v>
       </c>
       <c r="F159" t="n">
         <v>7044</v>
@@ -21333,13 +21333,13 @@
         </is>
       </c>
       <c r="C160" t="n">
-        <v>1145.83</v>
+        <v>1145.82</v>
       </c>
       <c r="D160" t="n">
-        <v>1128.71</v>
+        <v>1128.7</v>
       </c>
       <c r="E160" t="n">
-        <v>1162.96</v>
+        <v>1162.94</v>
       </c>
       <c r="F160" t="n">
         <v>1295</v>
@@ -21484,13 +21484,13 @@
         </is>
       </c>
       <c r="C161" t="n">
-        <v>1142.64</v>
+        <v>1142.62</v>
       </c>
       <c r="D161" t="n">
-        <v>1132.74</v>
+        <v>1132.72</v>
       </c>
       <c r="E161" t="n">
-        <v>1152.54</v>
+        <v>1152.51</v>
       </c>
       <c r="F161" t="n">
         <v>4737</v>
@@ -21635,13 +21635,13 @@
         </is>
       </c>
       <c r="C162" t="n">
-        <v>1141.93</v>
+        <v>1141.9</v>
       </c>
       <c r="D162" t="n">
-        <v>1135.5</v>
+        <v>1135.47</v>
       </c>
       <c r="E162" t="n">
-        <v>1148.37</v>
+        <v>1148.34</v>
       </c>
       <c r="F162" t="n">
         <v>12297</v>
@@ -21786,13 +21786,13 @@
         </is>
       </c>
       <c r="C163" t="n">
-        <v>1140.32</v>
+        <v>1140.29</v>
       </c>
       <c r="D163" t="n">
-        <v>1133.59</v>
+        <v>1133.56</v>
       </c>
       <c r="E163" t="n">
-        <v>1147.05</v>
+        <v>1147.02</v>
       </c>
       <c r="F163" t="n">
         <v>19174</v>
@@ -21937,13 +21937,13 @@
         </is>
       </c>
       <c r="C164" t="n">
-        <v>1139.69</v>
+        <v>1139.66</v>
       </c>
       <c r="D164" t="n">
-        <v>1132.97</v>
+        <v>1132.95</v>
       </c>
       <c r="E164" t="n">
-        <v>1146.4</v>
+        <v>1146.38</v>
       </c>
       <c r="F164" t="n">
         <v>19367</v>
@@ -22088,13 +22088,13 @@
         </is>
       </c>
       <c r="C165" t="n">
-        <v>1137.35</v>
+        <v>1137.32</v>
       </c>
       <c r="D165" t="n">
-        <v>1126.38</v>
+        <v>1126.36</v>
       </c>
       <c r="E165" t="n">
-        <v>1148.31</v>
+        <v>1148.29</v>
       </c>
       <c r="F165" t="n">
         <v>4964</v>
@@ -22239,13 +22239,13 @@
         </is>
       </c>
       <c r="C166" t="n">
-        <v>1135.36</v>
+        <v>1135.38</v>
       </c>
       <c r="D166" t="n">
-        <v>1125.85</v>
+        <v>1125.87</v>
       </c>
       <c r="E166" t="n">
-        <v>1144.87</v>
+        <v>1144.89</v>
       </c>
       <c r="F166" t="n">
         <v>8925</v>
@@ -22390,13 +22390,13 @@
         </is>
       </c>
       <c r="C167" t="n">
-        <v>1135.35</v>
+        <v>1135.32</v>
       </c>
       <c r="D167" t="n">
-        <v>1126.44</v>
+        <v>1126.42</v>
       </c>
       <c r="E167" t="n">
-        <v>1144.25</v>
+        <v>1144.23</v>
       </c>
       <c r="F167" t="n">
         <v>7366</v>
@@ -22541,13 +22541,13 @@
         </is>
       </c>
       <c r="C168" t="n">
-        <v>1129.78</v>
+        <v>1129.74</v>
       </c>
       <c r="D168" t="n">
-        <v>1120.93</v>
+        <v>1120.89</v>
       </c>
       <c r="E168" t="n">
-        <v>1138.63</v>
+        <v>1138.59</v>
       </c>
       <c r="F168" t="n">
         <v>11118</v>
@@ -22692,13 +22692,13 @@
         </is>
       </c>
       <c r="C169" t="n">
-        <v>1128.03</v>
+        <v>1128.01</v>
       </c>
       <c r="D169" t="n">
-        <v>1120.61</v>
+        <v>1120.59</v>
       </c>
       <c r="E169" t="n">
-        <v>1135.46</v>
+        <v>1135.44</v>
       </c>
       <c r="F169" t="n">
         <v>20685</v>
@@ -22843,13 +22843,13 @@
         </is>
       </c>
       <c r="C170" t="n">
-        <v>1127.22</v>
+        <v>1127.18</v>
       </c>
       <c r="D170" t="n">
-        <v>1120.82</v>
+        <v>1120.79</v>
       </c>
       <c r="E170" t="n">
-        <v>1133.62</v>
+        <v>1133.58</v>
       </c>
       <c r="F170" t="n">
         <v>20118</v>
@@ -22994,13 +22994,13 @@
         </is>
       </c>
       <c r="C171" t="n">
-        <v>1126.06</v>
+        <v>1126.03</v>
       </c>
       <c r="D171" t="n">
-        <v>1113.91</v>
+        <v>1113.88</v>
       </c>
       <c r="E171" t="n">
-        <v>1138.21</v>
+        <v>1138.17</v>
       </c>
       <c r="F171" t="n">
         <v>2921</v>
@@ -23145,13 +23145,13 @@
         </is>
       </c>
       <c r="C172" t="n">
-        <v>1125.65</v>
+        <v>1125.62</v>
       </c>
       <c r="D172" t="n">
-        <v>1109.98</v>
+        <v>1109.95</v>
       </c>
       <c r="E172" t="n">
-        <v>1141.32</v>
+        <v>1141.28</v>
       </c>
       <c r="F172" t="n">
         <v>1785</v>
@@ -23296,13 +23296,13 @@
         </is>
       </c>
       <c r="C173" t="n">
-        <v>1119.75</v>
+        <v>1119.73</v>
       </c>
       <c r="D173" t="n">
-        <v>1108.75</v>
+        <v>1108.73</v>
       </c>
       <c r="E173" t="n">
-        <v>1130.76</v>
+        <v>1130.73</v>
       </c>
       <c r="F173" t="n">
         <v>5182</v>
@@ -23447,13 +23447,13 @@
         </is>
       </c>
       <c r="C174" t="n">
-        <v>1117.93</v>
+        <v>1117.91</v>
       </c>
       <c r="D174" t="n">
-        <v>1099.73</v>
+        <v>1099.71</v>
       </c>
       <c r="E174" t="n">
-        <v>1136.14</v>
+        <v>1136.11</v>
       </c>
       <c r="F174" t="n">
         <v>1143</v>
@@ -23598,13 +23598,13 @@
         </is>
       </c>
       <c r="C175" t="n">
-        <v>1113.58</v>
+        <v>1113.63</v>
       </c>
       <c r="D175" t="n">
-        <v>1105.84</v>
+        <v>1105.89</v>
       </c>
       <c r="E175" t="n">
-        <v>1121.32</v>
+        <v>1121.37</v>
       </c>
       <c r="F175" t="n">
         <v>10854</v>
@@ -23749,13 +23749,13 @@
         </is>
       </c>
       <c r="C176" t="n">
-        <v>1113.41</v>
+        <v>1113.39</v>
       </c>
       <c r="D176" t="n">
-        <v>1104.23</v>
+        <v>1104.21</v>
       </c>
       <c r="E176" t="n">
-        <v>1122.59</v>
+        <v>1122.56</v>
       </c>
       <c r="F176" t="n">
         <v>6923</v>
@@ -23900,13 +23900,13 @@
         </is>
       </c>
       <c r="C177" t="n">
-        <v>1113.18</v>
+        <v>1113.16</v>
       </c>
       <c r="D177" t="n">
-        <v>1098.77</v>
+        <v>1098.75</v>
       </c>
       <c r="E177" t="n">
-        <v>1127.59</v>
+        <v>1127.57</v>
       </c>
       <c r="F177" t="n">
         <v>2199</v>
@@ -24051,13 +24051,13 @@
         </is>
       </c>
       <c r="C178" t="n">
-        <v>1110.22</v>
+        <v>1110.19</v>
       </c>
       <c r="D178" t="n">
-        <v>1102.35</v>
+        <v>1102.31</v>
       </c>
       <c r="E178" t="n">
-        <v>1118.1</v>
+        <v>1118.07</v>
       </c>
       <c r="F178" t="n">
         <v>8045</v>
@@ -24202,13 +24202,13 @@
         </is>
       </c>
       <c r="C179" t="n">
-        <v>1108.38</v>
+        <v>1108.36</v>
       </c>
       <c r="D179" t="n">
-        <v>1099.09</v>
+        <v>1099.07</v>
       </c>
       <c r="E179" t="n">
-        <v>1117.68</v>
+        <v>1117.66</v>
       </c>
       <c r="F179" t="n">
         <v>8977</v>
@@ -24353,13 +24353,13 @@
         </is>
       </c>
       <c r="C180" t="n">
-        <v>1106.94</v>
+        <v>1106.91</v>
       </c>
       <c r="D180" t="n">
-        <v>1099.88</v>
+        <v>1099.85</v>
       </c>
       <c r="E180" t="n">
-        <v>1114</v>
+        <v>1113.97</v>
       </c>
       <c r="F180" t="n">
         <v>14148</v>
@@ -24504,13 +24504,13 @@
         </is>
       </c>
       <c r="C181" t="n">
-        <v>1090.95</v>
+        <v>1090.98</v>
       </c>
       <c r="D181" t="n">
-        <v>1079.44</v>
+        <v>1079.47</v>
       </c>
       <c r="E181" t="n">
-        <v>1102.46</v>
+        <v>1102.49</v>
       </c>
       <c r="F181" t="n">
         <v>4780</v>
@@ -24655,13 +24655,13 @@
         </is>
       </c>
       <c r="C182" t="n">
-        <v>1088.95</v>
+        <v>1088.93</v>
       </c>
       <c r="D182" t="n">
-        <v>1079.6</v>
+        <v>1079.58</v>
       </c>
       <c r="E182" t="n">
-        <v>1098.3</v>
+        <v>1098.28</v>
       </c>
       <c r="F182" t="n">
         <v>7597</v>
@@ -24806,13 +24806,13 @@
         </is>
       </c>
       <c r="C183" t="n">
-        <v>1073.31</v>
+        <v>1073.26</v>
       </c>
       <c r="D183" t="n">
-        <v>1062.12</v>
+        <v>1062.07</v>
       </c>
       <c r="E183" t="n">
-        <v>1084.49</v>
+        <v>1084.44</v>
       </c>
       <c r="F183" t="n">
         <v>6328</v>
@@ -24957,13 +24957,13 @@
         </is>
       </c>
       <c r="C184" t="n">
-        <v>1069.17</v>
+        <v>1069.15</v>
       </c>
       <c r="D184" t="n">
-        <v>1059.23</v>
+        <v>1059.21</v>
       </c>
       <c r="E184" t="n">
-        <v>1079.11</v>
+        <v>1079.09</v>
       </c>
       <c r="F184" t="n">
         <v>6965</v>
@@ -25108,13 +25108,13 @@
         </is>
       </c>
       <c r="C185" t="n">
-        <v>1066.3</v>
+        <v>1066.32</v>
       </c>
       <c r="D185" t="n">
-        <v>1054.79</v>
+        <v>1054.81</v>
       </c>
       <c r="E185" t="n">
-        <v>1077.82</v>
+        <v>1077.84</v>
       </c>
       <c r="F185" t="n">
         <v>5745</v>
@@ -25561,13 +25561,13 @@
         </is>
       </c>
       <c r="C188" t="n">
-        <v>1054.78</v>
+        <v>1054.76</v>
       </c>
       <c r="D188" t="n">
-        <v>1043.1</v>
+        <v>1043.07</v>
       </c>
       <c r="E188" t="n">
-        <v>1066.47</v>
+        <v>1066.44</v>
       </c>
       <c r="F188" t="n">
         <v>4658</v>
@@ -25712,13 +25712,13 @@
         </is>
       </c>
       <c r="C189" t="n">
-        <v>1040.08</v>
+        <v>1040.07</v>
       </c>
       <c r="D189" t="n">
-        <v>1028.64</v>
+        <v>1028.63</v>
       </c>
       <c r="E189" t="n">
-        <v>1051.53</v>
+        <v>1051.51</v>
       </c>
       <c r="F189" t="n">
         <v>4845</v>
@@ -25863,13 +25863,13 @@
         </is>
       </c>
       <c r="C190" t="n">
-        <v>1022.9</v>
+        <v>1022.88</v>
       </c>
       <c r="D190" t="n">
-        <v>1009.27</v>
+        <v>1009.25</v>
       </c>
       <c r="E190" t="n">
-        <v>1036.53</v>
+        <v>1036.5</v>
       </c>
       <c r="F190" t="n">
         <v>2658</v>
@@ -26017,10 +26017,10 @@
         <v>1020.84</v>
       </c>
       <c r="D191" t="n">
-        <v>1009.92</v>
+        <v>1009.91</v>
       </c>
       <c r="E191" t="n">
-        <v>1031.77</v>
+        <v>1031.76</v>
       </c>
       <c r="F191" t="n">
         <v>6310</v>
@@ -26165,13 +26165,13 @@
         </is>
       </c>
       <c r="C192" t="n">
-        <v>994.294</v>
+        <v>994.266</v>
       </c>
       <c r="D192" t="n">
-        <v>981.675</v>
+        <v>981.649</v>
       </c>
       <c r="E192" t="n">
-        <v>1006.91</v>
+        <v>1006.88</v>
       </c>
       <c r="F192" t="n">
         <v>4914</v>
@@ -26316,10 +26316,10 @@
         </is>
       </c>
       <c r="C193" t="n">
-        <v>990.1130000000001</v>
+        <v>990.109</v>
       </c>
       <c r="D193" t="n">
-        <v>977.683</v>
+        <v>977.681</v>
       </c>
       <c r="E193" t="n">
         <v>1002.54</v>
@@ -26467,13 +26467,13 @@
         </is>
       </c>
       <c r="C194" t="n">
-        <v>978.92</v>
+        <v>978.933</v>
       </c>
       <c r="D194" t="n">
-        <v>965.317</v>
+        <v>965.332</v>
       </c>
       <c r="E194" t="n">
-        <v>992.524</v>
+        <v>992.533</v>
       </c>
       <c r="F194" t="n">
         <v>3412</v>
@@ -26618,13 +26618,13 @@
         </is>
       </c>
       <c r="C195" t="n">
-        <v>971.0650000000001</v>
+        <v>971.095</v>
       </c>
       <c r="D195" t="n">
-        <v>955.1660000000001</v>
+        <v>955.2</v>
       </c>
       <c r="E195" t="n">
-        <v>986.963</v>
+        <v>986.99</v>
       </c>
       <c r="F195" t="n">
         <v>2391</v>
@@ -26769,13 +26769,13 @@
         </is>
       </c>
       <c r="C196" t="n">
-        <v>951.347</v>
+        <v>951.327</v>
       </c>
       <c r="D196" t="n">
-        <v>938.54</v>
+        <v>938.522</v>
       </c>
       <c r="E196" t="n">
-        <v>964.155</v>
+        <v>964.1319999999999</v>
       </c>
       <c r="F196" t="n">
         <v>3287</v>
@@ -27821,7 +27821,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>deepseek-v3.2-exp</t>
+          <t>deepseek-v3.2-thinking</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -27836,7 +27836,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>deepseek-v3.2-thinking</t>
+          <t>deepseek-v3.2-exp</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -27866,15 +27866,23 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>deepseek-v3.1</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
+          <t>qwen3.5-122b-a10b</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>122</v>
+      </c>
+      <c r="C18" t="n">
+        <v>10</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>name_parsing</t>
         </is>
       </c>
     </row>
@@ -27904,23 +27912,15 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>qwen3.5-122b-a10b</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>122</v>
-      </c>
-      <c r="C20" t="n">
-        <v>10</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+          <t>deepseek-v3.1</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -28064,22 +28064,30 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>minimax-m2.7</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
+          <t>qwen3-235b-a22b-no-thinking</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>235</v>
+      </c>
+      <c r="C28" t="n">
+        <v>22</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>name_parsing</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>minimax-m2.5</t>
+          <t>minimax-m2.7</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -28094,23 +28102,15 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>qwen3-235b-a22b-no-thinking</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>235</v>
-      </c>
-      <c r="C30" t="n">
-        <v>22</v>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+          <t>minimax-m2.5</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -28422,46 +28422,46 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>qwen3-235b-a22b</t>
+          <t>trinity-large-preview</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>235</v>
+        <v>70</v>
       </c>
       <c r="C46" t="n">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>moe</t>
+          <t>dense</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>override</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>trinity-large-preview</t>
+          <t>qwen3-235b-a22b</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>70</v>
+        <v>235</v>
       </c>
       <c r="C47" t="n">
-        <v>70</v>
+        <v>22</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>dense</t>
+          <t>moe</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>name_parsing</t>
         </is>
       </c>
     </row>
@@ -28933,18 +28933,18 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>llama-3.3-nemotron-49b-super-v1</t>
+          <t>qwen3-30b-a3b</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="C71" t="n">
-        <v>49</v>
+        <v>3</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>dense</t>
+          <t>moe</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -28956,18 +28956,18 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>qwen3-30b-a3b</t>
+          <t>llama-3.3-nemotron-49b-super-v1</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="C72" t="n">
-        <v>3</v>
+        <v>49</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>moe</t>
+          <t>dense</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -29147,38 +29147,38 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>nvidia-nemotron-3-nano-30b-a3b-bf16</t>
-        </is>
-      </c>
-      <c r="B81" t="n">
-        <v>30</v>
-      </c>
-      <c r="C81" t="n">
-        <v>3</v>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+          <t>qwen-max-0919</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr"/>
+      <c r="C81" t="inlineStr"/>
+      <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>qwen-max-0919</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr"/>
-      <c r="C82" t="inlineStr"/>
-      <c r="D82" t="inlineStr"/>
+          <t>nvidia-nemotron-3-nano-30b-a3b-bf16</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>30</v>
+      </c>
+      <c r="C82" t="n">
+        <v>3</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>name_parsing</t>
         </is>
       </c>
     </row>

--- a/arena_enrichment/output/arena_leaderboard_enriched.xlsx
+++ b/arena_enrichment/output/arena_leaderboard_enriched.xlsx
@@ -675,16 +675,16 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>1471.18</v>
+        <v>1471.59</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1463.75</v>
+        <v>1464.55</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1478.61</v>
+        <v>1478.63</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>6274</v>
+        <v>7179</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
@@ -746,16 +746,16 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>1455.54</v>
+        <v>1456.03</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1450.21</v>
+        <v>1450.8</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1460.88</v>
+        <v>1461.27</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>14988</v>
+        <v>15839</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
@@ -893,148 +893,148 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>kimi-k2.5-thinking</t>
+          <t>gemma-4-31b</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>1450.55</v>
+        <v>1451.48</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1445.88</v>
+        <v>1443.81</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1455.23</v>
+        <v>1459.15</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>21678</v>
+        <v>5827</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Moonshot</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Modified MIT</t>
+          <t>Apache 2.0</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>1000</v>
+        <v>31</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>moe</t>
+          <t>dense</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>name_parsing</t>
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>2000</v>
+        <v>62</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>2500</v>
+        <v>77.5</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>1000</v>
+        <v>31</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>1250</v>
+        <v>38.8</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>500</v>
+        <v>15.5</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>625</v>
-      </c>
-      <c r="S4" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T4" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U4" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="V4" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W4" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X4" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Y4" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z4" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AA4" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AB4" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AC4" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AD4" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AE4" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AF4" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AG4" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+        <v>19.4</v>
+      </c>
+      <c r="S4" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T4" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U4" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V4" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y4" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AA4" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB4" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AC4" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AD4" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE4" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AF4" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AG4" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AH4" s="2" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>H100 SXM</t>
         </is>
       </c>
       <c r="AI4" s="2" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>H100 SXM</t>
         </is>
       </c>
     </row>
@@ -1044,148 +1044,148 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>gemma-4-31b</t>
+          <t>kimi-k2.5-thinking</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>1450.43</v>
+        <v>1450.89</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1442.77</v>
+        <v>1446.27</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1458.1</v>
+        <v>1455.52</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>5839</v>
+        <v>22439</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Moonshot</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
+          <t>Modified MIT</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>31</v>
+        <v>1000</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>dense</t>
+          <t>moe</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>override</t>
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>62</v>
+        <v>2000</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>77.5</v>
+        <v>2500</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>31</v>
+        <v>1000</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>38.8</v>
+        <v>1250</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>15.5</v>
+        <v>500</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="S5" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="T5" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="U5" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="V5" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W5" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X5" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Y5" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AA5" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB5" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AC5" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AD5" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AE5" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AF5" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AG5" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
+        <v>625</v>
+      </c>
+      <c r="S5" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T5" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U5" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V5" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W5" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X5" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y5" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z5" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA5" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AB5" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AC5" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD5" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE5" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF5" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AG5" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AH5" s="2" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
       <c r="AI5" s="2" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
     </row>
@@ -1199,16 +1199,16 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1445.5</v>
+        <v>1445.9</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1440.37</v>
+        <v>1440.86</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1450.63</v>
+        <v>1450.94</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>16360</v>
+        <v>17212</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
@@ -1350,16 +1350,16 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>1442.57</v>
+        <v>1442.89</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>1436.45</v>
+        <v>1436.77</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1448.69</v>
+        <v>1449.01</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>12180</v>
+        <v>12149</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
@@ -1421,16 +1421,16 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>1438.84</v>
+        <v>1438.96</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>1431.15</v>
+        <v>1431.27</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1446.52</v>
+        <v>1446.65</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>5795</v>
+        <v>5782</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
@@ -1572,16 +1572,16 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>1431.93</v>
+        <v>1432.48</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1425.32</v>
+        <v>1425.87</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1438.54</v>
+        <v>1439.1</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>8234</v>
+        <v>8217</v>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
@@ -1723,16 +1723,16 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>1429.72</v>
+        <v>1430.27</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>1426.22</v>
+        <v>1426.79</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1433.22</v>
+        <v>1433.76</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>47037</v>
+        <v>47731</v>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
@@ -1874,16 +1874,16 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>1425.67</v>
+        <v>1425.86</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>1421.73</v>
+        <v>1421.91</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1429.6</v>
+        <v>1429.81</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>35904</v>
+        <v>35734</v>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
@@ -1945,16 +1945,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1424.67</v>
+        <v>1424.58</v>
       </c>
       <c r="D12" t="n">
-        <v>1418.13</v>
+        <v>1418.02</v>
       </c>
       <c r="E12" t="n">
-        <v>1431.2</v>
+        <v>1431.13</v>
       </c>
       <c r="F12" t="n">
-        <v>9140</v>
+        <v>9078</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -2016,16 +2016,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1423.36</v>
+        <v>1424.21</v>
       </c>
       <c r="D13" t="n">
-        <v>1419.59</v>
+        <v>1420.47</v>
       </c>
       <c r="E13" t="n">
-        <v>1427.13</v>
+        <v>1427.96</v>
       </c>
       <c r="F13" t="n">
-        <v>42036</v>
+        <v>42815</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -2087,16 +2087,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1422.98</v>
+        <v>1423.5</v>
       </c>
       <c r="D14" t="n">
-        <v>1420.2</v>
+        <v>1420.72</v>
       </c>
       <c r="E14" t="n">
-        <v>1425.76</v>
+        <v>1426.28</v>
       </c>
       <c r="F14" t="n">
-        <v>82850</v>
+        <v>83341</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -2234,20 +2234,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>deepseek-v3.2-thinking</t>
+          <t>deepseek-v3.2-exp</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1422.86</v>
+        <v>1423.15</v>
       </c>
       <c r="D15" t="n">
-        <v>1419</v>
+        <v>1416.74</v>
       </c>
       <c r="E15" t="n">
-        <v>1426.73</v>
+        <v>1429.57</v>
       </c>
       <c r="F15" t="n">
-        <v>36441</v>
+        <v>11952</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -2305,20 +2305,20 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>deepseek-v3.2-exp</t>
+          <t>deepseek-v3.2-thinking</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>1422.61</v>
       </c>
       <c r="D16" t="n">
-        <v>1416.2</v>
+        <v>1418.78</v>
       </c>
       <c r="E16" t="n">
-        <v>1429.01</v>
+        <v>1426.45</v>
       </c>
       <c r="F16" t="n">
-        <v>12013</v>
+        <v>37197</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -2380,16 +2380,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1421.66</v>
+        <v>1421.98</v>
       </c>
       <c r="D17" t="n">
-        <v>1416.02</v>
+        <v>1416.33</v>
       </c>
       <c r="E17" t="n">
-        <v>1427.31</v>
+        <v>1427.64</v>
       </c>
       <c r="F17" t="n">
-        <v>18590</v>
+        <v>18480</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -2451,16 +2451,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1417.76</v>
+        <v>1418.4</v>
       </c>
       <c r="D18" t="n">
-        <v>1412.24</v>
+        <v>1413</v>
       </c>
       <c r="E18" t="n">
-        <v>1423.28</v>
+        <v>1423.8</v>
       </c>
       <c r="F18" t="n">
-        <v>13066</v>
+        <v>14023</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -2598,148 +2598,68 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>kimi-k2-0905-preview</t>
+          <t>deepseek-v3.1</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1417.73</v>
+        <v>1418.03</v>
       </c>
       <c r="D19" t="n">
-        <v>1411.25</v>
+        <v>1412.02</v>
       </c>
       <c r="E19" t="n">
-        <v>1424.21</v>
+        <v>1424.04</v>
       </c>
       <c r="F19" t="n">
-        <v>11862</v>
+        <v>14995</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Moonshot</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Modified MIT</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J19" t="n">
-        <v>32</v>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>override</t>
-        </is>
-      </c>
-      <c r="M19" t="n">
-        <v>2000</v>
-      </c>
-      <c r="N19" t="n">
-        <v>2500</v>
-      </c>
-      <c r="O19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="P19" t="n">
-        <v>1250</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>500</v>
-      </c>
-      <c r="R19" t="n">
-        <v>625</v>
-      </c>
-      <c r="S19" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T19" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U19" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="V19" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W19" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X19" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Y19" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z19" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AA19" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AB19" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AC19" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AD19" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AE19" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AF19" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AG19" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr"/>
+      <c r="AB19" t="inlineStr"/>
+      <c r="AC19" t="inlineStr"/>
+      <c r="AD19" t="inlineStr"/>
+      <c r="AE19" t="inlineStr"/>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="inlineStr"/>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -2749,68 +2669,148 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>deepseek-v3.1</t>
+          <t>kimi-k2-0905-preview</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1417.64</v>
+        <v>1417.87</v>
       </c>
       <c r="D20" t="n">
-        <v>1411.64</v>
+        <v>1411.38</v>
       </c>
       <c r="E20" t="n">
-        <v>1423.64</v>
+        <v>1424.36</v>
       </c>
       <c r="F20" t="n">
-        <v>15068</v>
+        <v>11805</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>DeepSeek</t>
+          <t>Moonshot</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
+          <t>Modified MIT</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J20" t="n">
+        <v>32</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr"/>
-      <c r="W20" t="inlineStr"/>
-      <c r="X20" t="inlineStr"/>
-      <c r="Y20" t="inlineStr"/>
-      <c r="Z20" t="inlineStr"/>
-      <c r="AA20" t="inlineStr"/>
-      <c r="AB20" t="inlineStr"/>
-      <c r="AC20" t="inlineStr"/>
-      <c r="AD20" t="inlineStr"/>
-      <c r="AE20" t="inlineStr"/>
-      <c r="AF20" t="inlineStr"/>
-      <c r="AG20" t="inlineStr"/>
+          <t>override</t>
+        </is>
+      </c>
+      <c r="M20" t="n">
+        <v>2000</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2500</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1250</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>500</v>
+      </c>
+      <c r="R20" t="n">
+        <v>625</v>
+      </c>
+      <c r="S20" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T20" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U20" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V20" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W20" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X20" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y20" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z20" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA20" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AB20" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AC20" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD20" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE20" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF20" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AG20" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
     </row>
@@ -2824,16 +2824,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1416.75</v>
+        <v>1417.4</v>
       </c>
       <c r="D21" t="n">
-        <v>1411.91</v>
+        <v>1412.55</v>
       </c>
       <c r="E21" t="n">
-        <v>1421.59</v>
+        <v>1422.26</v>
       </c>
       <c r="F21" t="n">
-        <v>27861</v>
+        <v>27669</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -2975,16 +2975,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1416.75</v>
+        <v>1417.09</v>
       </c>
       <c r="D22" t="n">
-        <v>1410.16</v>
+        <v>1410.48</v>
       </c>
       <c r="E22" t="n">
-        <v>1423.34</v>
+        <v>1423.7</v>
       </c>
       <c r="F22" t="n">
-        <v>11825</v>
+        <v>11762</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -3046,16 +3046,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1416.17</v>
+        <v>1416.95</v>
       </c>
       <c r="D23" t="n">
-        <v>1406.22</v>
+        <v>1406.99</v>
       </c>
       <c r="E23" t="n">
-        <v>1426.12</v>
+        <v>1426.92</v>
       </c>
       <c r="F23" t="n">
-        <v>3488</v>
+        <v>3475</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -3117,16 +3117,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1415.72</v>
+        <v>1416.06</v>
       </c>
       <c r="D24" t="n">
-        <v>1406.12</v>
+        <v>1406.45</v>
       </c>
       <c r="E24" t="n">
-        <v>1425.32</v>
+        <v>1425.67</v>
       </c>
       <c r="F24" t="n">
-        <v>3722</v>
+        <v>3713</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -3188,16 +3188,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1415.59</v>
+        <v>1415.89</v>
       </c>
       <c r="D25" t="n">
-        <v>1409.13</v>
+        <v>1409.4</v>
       </c>
       <c r="E25" t="n">
-        <v>1422.05</v>
+        <v>1422.37</v>
       </c>
       <c r="F25" t="n">
-        <v>11608</v>
+        <v>11533</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -3339,16 +3339,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1415.47</v>
+        <v>1415.41</v>
       </c>
       <c r="D26" t="n">
-        <v>1411.71</v>
+        <v>1411.69</v>
       </c>
       <c r="E26" t="n">
-        <v>1419.22</v>
+        <v>1419.13</v>
       </c>
       <c r="F26" t="n">
-        <v>39232</v>
+        <v>40077</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -3490,16 +3490,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1410.75</v>
+        <v>1411.16</v>
       </c>
       <c r="D27" t="n">
-        <v>1405.89</v>
+        <v>1406.28</v>
       </c>
       <c r="E27" t="n">
-        <v>1415.61</v>
+        <v>1416.04</v>
       </c>
       <c r="F27" t="n">
-        <v>24507</v>
+        <v>24356</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -3637,20 +3637,20 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>qwen3-235b-a22b-no-thinking</t>
+          <t>qwen3.5-27b</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1402.55</v>
+        <v>1403.43</v>
       </c>
       <c r="D28" t="n">
-        <v>1398.06</v>
+        <v>1397.96</v>
       </c>
       <c r="E28" t="n">
-        <v>1407.04</v>
+        <v>1408.89</v>
       </c>
       <c r="F28" t="n">
-        <v>38470</v>
+        <v>13687</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -3663,14 +3663,14 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>235</v>
+        <v>27</v>
       </c>
       <c r="J28" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>moe</t>
+          <t>dense</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3679,76 +3679,76 @@
         </is>
       </c>
       <c r="M28" t="n">
-        <v>470</v>
+        <v>54</v>
       </c>
       <c r="N28" t="n">
-        <v>587.5</v>
+        <v>67.5</v>
       </c>
       <c r="O28" t="n">
-        <v>235</v>
+        <v>27</v>
       </c>
       <c r="P28" t="n">
-        <v>293.8</v>
+        <v>33.8</v>
       </c>
       <c r="Q28" t="n">
-        <v>117.5</v>
+        <v>13.5</v>
       </c>
       <c r="R28" t="n">
-        <v>146.9</v>
-      </c>
-      <c r="S28" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T28" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U28" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="V28" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W28" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X28" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Y28" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z28" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AA28" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AB28" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AC28" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+        <v>16.9</v>
+      </c>
+      <c r="S28" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T28" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U28" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V28" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W28" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X28" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y28" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z28" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AA28" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB28" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AC28" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AD28" s="6" t="inlineStr">
@@ -3756,14 +3756,14 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="AE28" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AF28" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AE28" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AF28" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AG28" s="6" t="inlineStr">
@@ -3773,12 +3773,12 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>H100 SXM</t>
         </is>
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>H100 SXM</t>
         </is>
       </c>
     </row>
@@ -3792,16 +3792,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1401.86</v>
+        <v>1403.24</v>
       </c>
       <c r="D29" t="n">
-        <v>1394.82</v>
+        <v>1396.48</v>
       </c>
       <c r="E29" t="n">
-        <v>1408.9</v>
+        <v>1409.99</v>
       </c>
       <c r="F29" t="n">
-        <v>7635</v>
+        <v>8484</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -3859,68 +3859,148 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>minimax-m2.5</t>
+          <t>qwen3-235b-a22b-no-thinking</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1401.83</v>
+        <v>1403.21</v>
       </c>
       <c r="D30" t="n">
-        <v>1396.83</v>
+        <v>1398.72</v>
       </c>
       <c r="E30" t="n">
-        <v>1406.82</v>
+        <v>1407.71</v>
       </c>
       <c r="F30" t="n">
-        <v>18224</v>
+        <v>38253</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>MiniMax</t>
+          <t>Alibaba</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Modified MIT</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
+          <t>Apache 2.0</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>235</v>
+      </c>
+      <c r="J30" t="n">
+        <v>22</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr"/>
-      <c r="S30" t="inlineStr"/>
-      <c r="T30" t="inlineStr"/>
-      <c r="U30" t="inlineStr"/>
-      <c r="V30" t="inlineStr"/>
-      <c r="W30" t="inlineStr"/>
-      <c r="X30" t="inlineStr"/>
-      <c r="Y30" t="inlineStr"/>
-      <c r="Z30" t="inlineStr"/>
-      <c r="AA30" t="inlineStr"/>
-      <c r="AB30" t="inlineStr"/>
-      <c r="AC30" t="inlineStr"/>
-      <c r="AD30" t="inlineStr"/>
-      <c r="AE30" t="inlineStr"/>
-      <c r="AF30" t="inlineStr"/>
-      <c r="AG30" t="inlineStr"/>
+          <t>name_parsing</t>
+        </is>
+      </c>
+      <c r="M30" t="n">
+        <v>470</v>
+      </c>
+      <c r="N30" t="n">
+        <v>587.5</v>
+      </c>
+      <c r="O30" t="n">
+        <v>235</v>
+      </c>
+      <c r="P30" t="n">
+        <v>293.8</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>117.5</v>
+      </c>
+      <c r="R30" t="n">
+        <v>146.9</v>
+      </c>
+      <c r="S30" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T30" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U30" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V30" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W30" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X30" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y30" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z30" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA30" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AB30" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AC30" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD30" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE30" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF30" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AG30" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
     </row>
@@ -3930,148 +4010,68 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>qwen3.5-27b</t>
+          <t>minimax-m2.5</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1401.61</v>
+        <v>1403.02</v>
       </c>
       <c r="D31" t="n">
-        <v>1396.01</v>
+        <v>1398.11</v>
       </c>
       <c r="E31" t="n">
-        <v>1407.21</v>
+        <v>1407.93</v>
       </c>
       <c r="F31" t="n">
-        <v>12770</v>
+        <v>19156</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alibaba</t>
+          <t>MiniMax</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
-        </is>
-      </c>
-      <c r="I31" t="n">
-        <v>27</v>
-      </c>
-      <c r="J31" t="n">
-        <v>27</v>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>dense</t>
-        </is>
-      </c>
+          <t>Modified MIT</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
-          <t>name_parsing</t>
-        </is>
-      </c>
-      <c r="M31" t="n">
-        <v>54</v>
-      </c>
-      <c r="N31" t="n">
-        <v>67.5</v>
-      </c>
-      <c r="O31" t="n">
-        <v>27</v>
-      </c>
-      <c r="P31" t="n">
-        <v>33.8</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="R31" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="S31" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="T31" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="U31" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="V31" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W31" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X31" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Y31" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z31" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AA31" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB31" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AC31" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AD31" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AE31" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AF31" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AG31" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="inlineStr"/>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr"/>
+      <c r="AB31" t="inlineStr"/>
+      <c r="AC31" t="inlineStr"/>
+      <c r="AD31" t="inlineStr"/>
+      <c r="AE31" t="inlineStr"/>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="inlineStr"/>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -4085,16 +4085,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1401.34</v>
+        <v>1401.85</v>
       </c>
       <c r="D32" t="n">
-        <v>1396.58</v>
+        <v>1397.07</v>
       </c>
       <c r="E32" t="n">
-        <v>1406.11</v>
+        <v>1406.63</v>
       </c>
       <c r="F32" t="n">
-        <v>23060</v>
+        <v>22909</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -4236,16 +4236,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1400.94</v>
+        <v>1401.52</v>
       </c>
       <c r="D33" t="n">
-        <v>1394.58</v>
+        <v>1395.15</v>
       </c>
       <c r="E33" t="n">
-        <v>1407.3</v>
+        <v>1407.89</v>
       </c>
       <c r="F33" t="n">
-        <v>11476</v>
+        <v>11418</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -4387,16 +4387,16 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1399.57</v>
+        <v>1399.73</v>
       </c>
       <c r="D34" t="n">
-        <v>1393.06</v>
+        <v>1393.21</v>
       </c>
       <c r="E34" t="n">
-        <v>1406.09</v>
+        <v>1406.26</v>
       </c>
       <c r="F34" t="n">
-        <v>9061</v>
+        <v>9013</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -4538,13 +4538,13 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1397.48</v>
+        <v>1397.8</v>
       </c>
       <c r="D35" t="n">
-        <v>1392.62</v>
+        <v>1392.94</v>
       </c>
       <c r="E35" t="n">
-        <v>1402.34</v>
+        <v>1402.66</v>
       </c>
       <c r="F35" t="n">
         <v>18524</v>
@@ -4685,20 +4685,20 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>qwen3.5-35b-a3b</t>
+          <t>qwen3-vl-235b-a22b-thinking</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1396</v>
+        <v>1395.89</v>
       </c>
       <c r="D36" t="n">
-        <v>1390.5</v>
+        <v>1389.1</v>
       </c>
       <c r="E36" t="n">
-        <v>1401.51</v>
+        <v>1402.67</v>
       </c>
       <c r="F36" t="n">
-        <v>13268</v>
+        <v>7960</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -4711,10 +4711,10 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>35</v>
+        <v>235</v>
       </c>
       <c r="J36" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -4727,36 +4727,36 @@
         </is>
       </c>
       <c r="M36" t="n">
-        <v>70</v>
+        <v>470</v>
       </c>
       <c r="N36" t="n">
-        <v>87.5</v>
+        <v>587.5</v>
       </c>
       <c r="O36" t="n">
-        <v>35</v>
+        <v>235</v>
       </c>
       <c r="P36" t="n">
-        <v>43.8</v>
+        <v>293.8</v>
       </c>
       <c r="Q36" t="n">
-        <v>17.5</v>
+        <v>117.5</v>
       </c>
       <c r="R36" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="S36" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="T36" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="U36" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+        <v>146.9</v>
+      </c>
+      <c r="S36" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T36" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U36" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="V36" s="5" t="inlineStr">
@@ -4764,39 +4764,39 @@
           <t>No</t>
         </is>
       </c>
-      <c r="W36" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X36" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Y36" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z36" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AA36" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB36" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AC36" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="W36" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X36" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y36" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z36" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA36" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AB36" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AC36" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AD36" s="6" t="inlineStr">
@@ -4804,14 +4804,14 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="AE36" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AF36" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AE36" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF36" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AG36" s="6" t="inlineStr">
@@ -4821,12 +4821,12 @@
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>RTX PRO 6000</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
     </row>
@@ -4836,20 +4836,20 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>qwen3-vl-235b-a22b-thinking</t>
+          <t>qwen3.5-35b-a3b</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1395.51</v>
+        <v>1395.86</v>
       </c>
       <c r="D37" t="n">
-        <v>1388.75</v>
+        <v>1390.48</v>
       </c>
       <c r="E37" t="n">
-        <v>1402.28</v>
+        <v>1401.23</v>
       </c>
       <c r="F37" t="n">
-        <v>8021</v>
+        <v>14275</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -4862,10 +4862,10 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>235</v>
+        <v>35</v>
       </c>
       <c r="J37" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -4878,36 +4878,36 @@
         </is>
       </c>
       <c r="M37" t="n">
-        <v>470</v>
+        <v>70</v>
       </c>
       <c r="N37" t="n">
-        <v>587.5</v>
+        <v>87.5</v>
       </c>
       <c r="O37" t="n">
-        <v>235</v>
+        <v>35</v>
       </c>
       <c r="P37" t="n">
-        <v>293.8</v>
+        <v>43.8</v>
       </c>
       <c r="Q37" t="n">
-        <v>117.5</v>
+        <v>17.5</v>
       </c>
       <c r="R37" t="n">
-        <v>146.9</v>
-      </c>
-      <c r="S37" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T37" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U37" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+        <v>21.9</v>
+      </c>
+      <c r="S37" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T37" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U37" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="V37" s="5" t="inlineStr">
@@ -4915,39 +4915,39 @@
           <t>No</t>
         </is>
       </c>
-      <c r="W37" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X37" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Y37" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z37" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AA37" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AB37" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AC37" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="W37" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X37" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y37" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z37" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AA37" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB37" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AC37" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AD37" s="6" t="inlineStr">
@@ -4955,14 +4955,14 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="AE37" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AF37" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AE37" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AF37" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AG37" s="6" t="inlineStr">
@@ -4972,12 +4972,12 @@
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>RTX PRO 6000</t>
         </is>
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>H100 SXM</t>
         </is>
       </c>
     </row>
@@ -4991,16 +4991,16 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1394.49</v>
+        <v>1395.24</v>
       </c>
       <c r="D38" t="n">
-        <v>1390.64</v>
+        <v>1391.38</v>
       </c>
       <c r="E38" t="n">
-        <v>1398.34</v>
+        <v>1399.1</v>
       </c>
       <c r="F38" t="n">
-        <v>45799</v>
+        <v>45555</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -5138,29 +5138,29 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>mimo-v2-flash (non-thinking)</t>
+          <t>step-3.5-flash</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1391.14</v>
+        <v>1392.41</v>
       </c>
       <c r="D39" t="n">
-        <v>1387.09</v>
+        <v>1387.65</v>
       </c>
       <c r="E39" t="n">
-        <v>1395.19</v>
+        <v>1397.17</v>
       </c>
       <c r="F39" t="n">
-        <v>31132</v>
+        <v>20186</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Xiaomi</t>
+          <t>StepFun</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Apache 2.0</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5209,29 +5209,29 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>step-3.5-flash</t>
+          <t>mimo-v2-flash (non-thinking)</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1390.99</v>
+        <v>1392.12</v>
       </c>
       <c r="D40" t="n">
-        <v>1386.17</v>
+        <v>1388.1</v>
       </c>
       <c r="E40" t="n">
-        <v>1395.81</v>
+        <v>1396.14</v>
       </c>
       <c r="F40" t="n">
-        <v>19379</v>
+        <v>31981</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>StepFun</t>
+          <t>Xiaomi</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5284,16 +5284,16 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1387.36</v>
+        <v>1387.49</v>
       </c>
       <c r="D41" t="n">
-        <v>1382.43</v>
+        <v>1382.54</v>
       </c>
       <c r="E41" t="n">
-        <v>1392.29</v>
+        <v>1392.44</v>
       </c>
       <c r="F41" t="n">
-        <v>25958</v>
+        <v>25768</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -5435,16 +5435,16 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1386.85</v>
+        <v>1387.35</v>
       </c>
       <c r="D42" t="n">
-        <v>1380.58</v>
+        <v>1381.07</v>
       </c>
       <c r="E42" t="n">
-        <v>1393.12</v>
+        <v>1393.63</v>
       </c>
       <c r="F42" t="n">
-        <v>11021</v>
+        <v>10994</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -5506,16 +5506,16 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1385.3</v>
+        <v>1385.49</v>
       </c>
       <c r="D43" t="n">
-        <v>1380.05</v>
+        <v>1380.23</v>
       </c>
       <c r="E43" t="n">
-        <v>1390.55</v>
+        <v>1390.75</v>
       </c>
       <c r="F43" t="n">
-        <v>17234</v>
+        <v>17175</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -5577,16 +5577,16 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1383.02</v>
+        <v>1383.63</v>
       </c>
       <c r="D44" t="n">
-        <v>1378.15</v>
+        <v>1378.75</v>
       </c>
       <c r="E44" t="n">
-        <v>1387.88</v>
+        <v>1388.51</v>
       </c>
       <c r="F44" t="n">
-        <v>23932</v>
+        <v>23783</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -5728,16 +5728,16 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1377.55</v>
+        <v>1377.51</v>
       </c>
       <c r="D45" t="n">
-        <v>1366.27</v>
+        <v>1366.22</v>
       </c>
       <c r="E45" t="n">
-        <v>1388.84</v>
+        <v>1388.8</v>
       </c>
       <c r="F45" t="n">
-        <v>2817</v>
+        <v>2807</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -5799,16 +5799,16 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1374.49</v>
+        <v>1375.5</v>
       </c>
       <c r="D46" t="n">
-        <v>1368.99</v>
+        <v>1370.1</v>
       </c>
       <c r="E46" t="n">
-        <v>1379.98</v>
+        <v>1380.9</v>
       </c>
       <c r="F46" t="n">
-        <v>14164</v>
+        <v>15015</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -5950,16 +5950,16 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1374.35</v>
+        <v>1374.83</v>
       </c>
       <c r="D47" t="n">
-        <v>1369.67</v>
+        <v>1370.14</v>
       </c>
       <c r="E47" t="n">
-        <v>1379.03</v>
+        <v>1379.52</v>
       </c>
       <c r="F47" t="n">
-        <v>26423</v>
+        <v>26285</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -6101,16 +6101,16 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1372.81</v>
+        <v>1373.18</v>
       </c>
       <c r="D48" t="n">
-        <v>1368.58</v>
+        <v>1368.94</v>
       </c>
       <c r="E48" t="n">
-        <v>1377.04</v>
+        <v>1377.43</v>
       </c>
       <c r="F48" t="n">
-        <v>31372</v>
+        <v>31149</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -6172,16 +6172,16 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1368.78</v>
+        <v>1369.29</v>
       </c>
       <c r="D49" t="n">
-        <v>1362.97</v>
+        <v>1363.45</v>
       </c>
       <c r="E49" t="n">
-        <v>1374.59</v>
+        <v>1375.13</v>
       </c>
       <c r="F49" t="n">
-        <v>13836</v>
+        <v>13717</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -6323,16 +6323,16 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1367.72</v>
+        <v>1368.03</v>
       </c>
       <c r="D50" t="n">
-        <v>1361.89</v>
+        <v>1362.2</v>
       </c>
       <c r="E50" t="n">
-        <v>1373.54</v>
+        <v>1373.87</v>
       </c>
       <c r="F50" t="n">
-        <v>11819</v>
+        <v>11778</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -6394,16 +6394,16 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1365.05</v>
+        <v>1365.58</v>
       </c>
       <c r="D51" t="n">
-        <v>1361.4</v>
+        <v>1361.92</v>
       </c>
       <c r="E51" t="n">
-        <v>1368.71</v>
+        <v>1369.24</v>
       </c>
       <c r="F51" t="n">
-        <v>47842</v>
+        <v>47584</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -6545,16 +6545,16 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1363.16</v>
+        <v>1363.63</v>
       </c>
       <c r="D52" t="n">
-        <v>1358.9</v>
+        <v>1359.37</v>
       </c>
       <c r="E52" t="n">
-        <v>1367.41</v>
+        <v>1367.9</v>
       </c>
       <c r="F52" t="n">
-        <v>35505</v>
+        <v>35260</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -6616,16 +6616,16 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1360.55</v>
+        <v>1361.33</v>
       </c>
       <c r="D53" t="n">
-        <v>1353.29</v>
+        <v>1354.06</v>
       </c>
       <c r="E53" t="n">
-        <v>1367.82</v>
+        <v>1368.61</v>
       </c>
       <c r="F53" t="n">
-        <v>7435</v>
+        <v>7413</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1358.11</v>
+        <v>1358.4</v>
       </c>
       <c r="D54" t="n">
-        <v>1353.39</v>
+        <v>1353.68</v>
       </c>
       <c r="E54" t="n">
-        <v>1362.83</v>
+        <v>1363.12</v>
       </c>
       <c r="F54" t="n">
         <v>21770</v>
@@ -6918,16 +6918,16 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1356.91</v>
+        <v>1357.28</v>
       </c>
       <c r="D55" t="n">
-        <v>1351.72</v>
+        <v>1352.08</v>
       </c>
       <c r="E55" t="n">
-        <v>1362.09</v>
+        <v>1362.48</v>
       </c>
       <c r="F55" t="n">
-        <v>17850</v>
+        <v>17729</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -6989,16 +6989,16 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1356.2</v>
+        <v>1356.9</v>
       </c>
       <c r="D56" t="n">
-        <v>1347.85</v>
+        <v>1348.54</v>
       </c>
       <c r="E56" t="n">
-        <v>1364.55</v>
+        <v>1365.27</v>
       </c>
       <c r="F56" t="n">
-        <v>5357</v>
+        <v>5337</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -7136,148 +7136,68 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>gpt-oss-120b</t>
+          <t>command-a-03-2025</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1353.6</v>
+        <v>1353.62</v>
       </c>
       <c r="D57" t="n">
-        <v>1349.26</v>
+        <v>1350.18</v>
       </c>
       <c r="E57" t="n">
-        <v>1357.93</v>
+        <v>1357.06</v>
       </c>
       <c r="F57" t="n">
-        <v>30883</v>
+        <v>56351</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Cohere</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
-        </is>
-      </c>
-      <c r="I57" t="n">
-        <v>117</v>
-      </c>
-      <c r="J57" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+          <t>CC-BY-NC-4.0</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr">
         <is>
-          <t>override</t>
-        </is>
-      </c>
-      <c r="M57" t="n">
-        <v>234</v>
-      </c>
-      <c r="N57" t="n">
-        <v>292.5</v>
-      </c>
-      <c r="O57" t="n">
-        <v>117</v>
-      </c>
-      <c r="P57" t="n">
-        <v>146.2</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>58.5</v>
-      </c>
-      <c r="R57" t="n">
-        <v>73.09999999999999</v>
-      </c>
-      <c r="S57" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T57" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U57" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="V57" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W57" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X57" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Y57" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z57" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AA57" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB57" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AC57" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AD57" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AE57" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AF57" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AG57" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr"/>
+      <c r="R57" t="inlineStr"/>
+      <c r="S57" t="inlineStr"/>
+      <c r="T57" t="inlineStr"/>
+      <c r="U57" t="inlineStr"/>
+      <c r="V57" t="inlineStr"/>
+      <c r="W57" t="inlineStr"/>
+      <c r="X57" t="inlineStr"/>
+      <c r="Y57" t="inlineStr"/>
+      <c r="Z57" t="inlineStr"/>
+      <c r="AA57" t="inlineStr"/>
+      <c r="AB57" t="inlineStr"/>
+      <c r="AC57" t="inlineStr"/>
+      <c r="AD57" t="inlineStr"/>
+      <c r="AE57" t="inlineStr"/>
+      <c r="AF57" t="inlineStr"/>
+      <c r="AG57" t="inlineStr"/>
       <c r="AH57" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>B200 SXM</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -7287,68 +7207,148 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>command-a-03-2025</t>
+          <t>gpt-oss-120b</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1353.32</v>
+        <v>1353.37</v>
       </c>
       <c r="D58" t="n">
-        <v>1349.88</v>
+        <v>1349.02</v>
       </c>
       <c r="E58" t="n">
-        <v>1356.75</v>
+        <v>1357.72</v>
       </c>
       <c r="F58" t="n">
-        <v>56663</v>
+        <v>30675</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cohere</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>CC-BY-NC-4.0</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
+          <t>Apache 2.0</t>
+        </is>
+      </c>
+      <c r="I58" t="n">
+        <v>117</v>
+      </c>
+      <c r="J58" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
-      <c r="O58" t="inlineStr"/>
-      <c r="P58" t="inlineStr"/>
-      <c r="Q58" t="inlineStr"/>
-      <c r="R58" t="inlineStr"/>
-      <c r="S58" t="inlineStr"/>
-      <c r="T58" t="inlineStr"/>
-      <c r="U58" t="inlineStr"/>
-      <c r="V58" t="inlineStr"/>
-      <c r="W58" t="inlineStr"/>
-      <c r="X58" t="inlineStr"/>
-      <c r="Y58" t="inlineStr"/>
-      <c r="Z58" t="inlineStr"/>
-      <c r="AA58" t="inlineStr"/>
-      <c r="AB58" t="inlineStr"/>
-      <c r="AC58" t="inlineStr"/>
-      <c r="AD58" t="inlineStr"/>
-      <c r="AE58" t="inlineStr"/>
-      <c r="AF58" t="inlineStr"/>
-      <c r="AG58" t="inlineStr"/>
+          <t>override</t>
+        </is>
+      </c>
+      <c r="M58" t="n">
+        <v>234</v>
+      </c>
+      <c r="N58" t="n">
+        <v>292.5</v>
+      </c>
+      <c r="O58" t="n">
+        <v>117</v>
+      </c>
+      <c r="P58" t="n">
+        <v>146.2</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="R58" t="n">
+        <v>73.09999999999999</v>
+      </c>
+      <c r="S58" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T58" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U58" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V58" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W58" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X58" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y58" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z58" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA58" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB58" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AC58" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AD58" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE58" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF58" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AG58" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AH58" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
       <c r="AI58" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>B200 SXM</t>
         </is>
       </c>
     </row>
@@ -7362,16 +7362,16 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1352.98</v>
+        <v>1353.25</v>
       </c>
       <c r="D59" t="n">
-        <v>1344.66</v>
+        <v>1344.91</v>
       </c>
       <c r="E59" t="n">
-        <v>1361.31</v>
+        <v>1361.59</v>
       </c>
       <c r="F59" t="n">
-        <v>4983</v>
+        <v>4969</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -7433,16 +7433,16 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1347.58</v>
+        <v>1347.85</v>
       </c>
       <c r="D60" t="n">
-        <v>1340.2</v>
+        <v>1340.46</v>
       </c>
       <c r="E60" t="n">
-        <v>1354.96</v>
+        <v>1355.25</v>
       </c>
       <c r="F60" t="n">
-        <v>6585</v>
+        <v>6555</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -7504,13 +7504,13 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1346.95</v>
+        <v>1347.26</v>
       </c>
       <c r="D61" t="n">
-        <v>1337.49</v>
+        <v>1337.8</v>
       </c>
       <c r="E61" t="n">
-        <v>1356.42</v>
+        <v>1356.72</v>
       </c>
       <c r="F61" t="n">
         <v>3926</v>
@@ -7655,13 +7655,13 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1346.81</v>
+        <v>1347.15</v>
       </c>
       <c r="D62" t="n">
-        <v>1335.12</v>
+        <v>1335.45</v>
       </c>
       <c r="E62" t="n">
-        <v>1358.51</v>
+        <v>1358.85</v>
       </c>
       <c r="F62" t="n">
         <v>2549</v>
@@ -7806,16 +7806,16 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1346.53</v>
+        <v>1346.34</v>
       </c>
       <c r="D63" t="n">
-        <v>1338.8</v>
+        <v>1338.6</v>
       </c>
       <c r="E63" t="n">
-        <v>1354.25</v>
+        <v>1354.09</v>
       </c>
       <c r="F63" t="n">
-        <v>6908</v>
+        <v>6875</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -7957,16 +7957,16 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1346.03</v>
+        <v>1346.18</v>
       </c>
       <c r="D64" t="n">
-        <v>1338.8</v>
+        <v>1338.92</v>
       </c>
       <c r="E64" t="n">
-        <v>1353.25</v>
+        <v>1353.44</v>
       </c>
       <c r="F64" t="n">
-        <v>7080</v>
+        <v>7017</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -8028,16 +8028,16 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1342.77</v>
+        <v>1342.95</v>
       </c>
       <c r="D65" t="n">
-        <v>1332.82</v>
+        <v>1332.98</v>
       </c>
       <c r="E65" t="n">
-        <v>1352.72</v>
+        <v>1352.92</v>
       </c>
       <c r="F65" t="n">
-        <v>3366</v>
+        <v>3347</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -8179,13 +8179,13 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1341.42</v>
+        <v>1341.69</v>
       </c>
       <c r="D66" t="n">
-        <v>1331.91</v>
+        <v>1332.17</v>
       </c>
       <c r="E66" t="n">
-        <v>1350.94</v>
+        <v>1351.2</v>
       </c>
       <c r="F66" t="n">
         <v>3829</v>
@@ -8330,16 +8330,16 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1335.61</v>
+        <v>1336.09</v>
       </c>
       <c r="D67" t="n">
-        <v>1331.19</v>
+        <v>1331.66</v>
       </c>
       <c r="E67" t="n">
-        <v>1340.03</v>
+        <v>1340.52</v>
       </c>
       <c r="F67" t="n">
-        <v>25522</v>
+        <v>25412</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -8481,13 +8481,13 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1334.24</v>
+        <v>1334.54</v>
       </c>
       <c r="D68" t="n">
-        <v>1330.56</v>
+        <v>1330.86</v>
       </c>
       <c r="E68" t="n">
-        <v>1337.92</v>
+        <v>1338.22</v>
       </c>
       <c r="F68" t="n">
         <v>41375</v>
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1332.44</v>
+        <v>1332.73</v>
       </c>
       <c r="D69" t="n">
-        <v>1328.87</v>
+        <v>1329.16</v>
       </c>
       <c r="E69" t="n">
-        <v>1336.01</v>
+        <v>1336.3</v>
       </c>
       <c r="F69" t="n">
         <v>59656</v>
@@ -8783,16 +8783,16 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1330.72</v>
+        <v>1330.8</v>
       </c>
       <c r="D70" t="n">
-        <v>1324.62</v>
+        <v>1324.69</v>
       </c>
       <c r="E70" t="n">
-        <v>1336.82</v>
+        <v>1336.9</v>
       </c>
       <c r="F70" t="n">
-        <v>12285</v>
+        <v>12244</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -8930,40 +8930,40 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>qwen3-30b-a3b</t>
+          <t>llama-3.3-nemotron-49b-super-v1</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1327.36</v>
+        <v>1327.67</v>
       </c>
       <c r="D71" t="n">
-        <v>1322.65</v>
+        <v>1315.5</v>
       </c>
       <c r="E71" t="n">
-        <v>1332.07</v>
+        <v>1339.84</v>
       </c>
       <c r="F71" t="n">
-        <v>26646</v>
+        <v>2218</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alibaba</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="I71" t="n">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="J71" t="n">
-        <v>3</v>
+        <v>49</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>moe</t>
+          <t>dense</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -8972,26 +8972,26 @@
         </is>
       </c>
       <c r="M71" t="n">
-        <v>60</v>
+        <v>98</v>
       </c>
       <c r="N71" t="n">
-        <v>75</v>
+        <v>122.5</v>
       </c>
       <c r="O71" t="n">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="P71" t="n">
-        <v>37.5</v>
+        <v>61.2</v>
       </c>
       <c r="Q71" t="n">
-        <v>15</v>
+        <v>24.5</v>
       </c>
       <c r="R71" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="S71" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+        <v>30.6</v>
+      </c>
+      <c r="S71" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="T71" s="6" t="inlineStr">
@@ -9004,9 +9004,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="V71" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="V71" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="W71" s="6" t="inlineStr">
@@ -9066,7 +9066,7 @@
       </c>
       <c r="AH71" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>H200 SXM</t>
         </is>
       </c>
       <c r="AI71" t="inlineStr">
@@ -9081,40 +9081,40 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>llama-3.3-nemotron-49b-super-v1</t>
+          <t>qwen3-30b-a3b</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1327.36</v>
+        <v>1327.52</v>
       </c>
       <c r="D72" t="n">
-        <v>1315.19</v>
+        <v>1322.79</v>
       </c>
       <c r="E72" t="n">
-        <v>1339.52</v>
+        <v>1332.24</v>
       </c>
       <c r="F72" t="n">
-        <v>2218</v>
+        <v>26510</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Alibaba</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Apache 2.0</t>
         </is>
       </c>
       <c r="I72" t="n">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="J72" t="n">
-        <v>49</v>
+        <v>3</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>dense</t>
+          <t>moe</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -9123,26 +9123,26 @@
         </is>
       </c>
       <c r="M72" t="n">
-        <v>98</v>
+        <v>60</v>
       </c>
       <c r="N72" t="n">
-        <v>122.5</v>
+        <v>75</v>
       </c>
       <c r="O72" t="n">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="P72" t="n">
-        <v>61.2</v>
+        <v>37.5</v>
       </c>
       <c r="Q72" t="n">
-        <v>24.5</v>
+        <v>15</v>
       </c>
       <c r="R72" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="S72" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+        <v>18.8</v>
+      </c>
+      <c r="S72" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="T72" s="6" t="inlineStr">
@@ -9155,9 +9155,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="V72" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="V72" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W72" s="6" t="inlineStr">
@@ -9217,7 +9217,7 @@
       </c>
       <c r="AH72" t="inlineStr">
         <is>
-          <t>H200 SXM</t>
+          <t>H100 SXM</t>
         </is>
       </c>
       <c r="AI72" t="inlineStr">
@@ -9236,16 +9236,16 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1326.84</v>
+        <v>1327.44</v>
       </c>
       <c r="D73" t="n">
-        <v>1305.46</v>
+        <v>1306.02</v>
       </c>
       <c r="E73" t="n">
-        <v>1348.23</v>
+        <v>1348.86</v>
       </c>
       <c r="F73" t="n">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -9387,16 +9387,16 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1326.66</v>
+        <v>1326.84</v>
       </c>
       <c r="D74" t="n">
-        <v>1322.42</v>
+        <v>1322.6</v>
       </c>
       <c r="E74" t="n">
-        <v>1330.89</v>
+        <v>1331.08</v>
       </c>
       <c r="F74" t="n">
-        <v>40214</v>
+        <v>40010</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -9538,13 +9538,13 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>1323.03</v>
+        <v>1323.32</v>
       </c>
       <c r="D75" t="n">
-        <v>1314.77</v>
+        <v>1315.06</v>
       </c>
       <c r="E75" t="n">
-        <v>1331.3</v>
+        <v>1331.58</v>
       </c>
       <c r="F75" t="n">
         <v>6795</v>
@@ -9609,16 +9609,16 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>1321.92</v>
+        <v>1322.42</v>
       </c>
       <c r="D76" t="n">
-        <v>1317.23</v>
+        <v>1317.72</v>
       </c>
       <c r="E76" t="n">
-        <v>1326.62</v>
+        <v>1327.12</v>
       </c>
       <c r="F76" t="n">
-        <v>30488</v>
+        <v>30316</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -9760,16 +9760,16 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1320.63</v>
+        <v>1320.86</v>
       </c>
       <c r="D77" t="n">
-        <v>1313.45</v>
+        <v>1313.65</v>
       </c>
       <c r="E77" t="n">
-        <v>1327.81</v>
+        <v>1328.08</v>
       </c>
       <c r="F77" t="n">
-        <v>7221</v>
+        <v>7157</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -9827,68 +9827,68 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>gemma-3n-e4b-it</t>
+          <t>llama-3.3-70b-instruct</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1318.04</v>
+        <v>1318.11</v>
       </c>
       <c r="D78" t="n">
-        <v>1312.9</v>
+        <v>1314.67</v>
       </c>
       <c r="E78" t="n">
-        <v>1323.17</v>
+        <v>1321.55</v>
       </c>
       <c r="F78" t="n">
-        <v>22723</v>
+        <v>54757</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Gemma</t>
+          <t>Llama-3.3</t>
         </is>
       </c>
       <c r="I78" t="n">
-        <v>8.4</v>
+        <v>70</v>
       </c>
       <c r="J78" t="n">
-        <v>4</v>
+        <v>70</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>moe</t>
+          <t>dense</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>aa_single_scrape</t>
+          <t>name_parsing</t>
         </is>
       </c>
       <c r="M78" t="n">
-        <v>16.8</v>
+        <v>140</v>
       </c>
       <c r="N78" t="n">
-        <v>21</v>
+        <v>175</v>
       </c>
       <c r="O78" t="n">
-        <v>8.4</v>
+        <v>70</v>
       </c>
       <c r="P78" t="n">
-        <v>10.5</v>
+        <v>87.5</v>
       </c>
       <c r="Q78" t="n">
-        <v>4.2</v>
+        <v>35</v>
       </c>
       <c r="R78" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="S78" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+        <v>43.8</v>
+      </c>
+      <c r="S78" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="T78" s="6" t="inlineStr">
@@ -9901,14 +9901,14 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="V78" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W78" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="V78" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W78" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="X78" s="6" t="inlineStr">
@@ -9916,9 +9916,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="Y78" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="Y78" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="Z78" s="6" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="AH78" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>B200 SXM</t>
         </is>
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>RTX PRO 6000</t>
         </is>
       </c>
     </row>
@@ -9978,68 +9978,68 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>llama-3.3-70b-instruct</t>
+          <t>gemma-3n-e4b-it</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>1317.97</v>
+        <v>1318.1</v>
       </c>
       <c r="D79" t="n">
-        <v>1314.53</v>
+        <v>1312.96</v>
       </c>
       <c r="E79" t="n">
-        <v>1321.4</v>
+        <v>1323.25</v>
       </c>
       <c r="F79" t="n">
-        <v>54884</v>
+        <v>22620</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Llama-3.3</t>
+          <t>Gemma</t>
         </is>
       </c>
       <c r="I79" t="n">
-        <v>70</v>
+        <v>8.4</v>
       </c>
       <c r="J79" t="n">
-        <v>70</v>
+        <v>4</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>dense</t>
+          <t>moe</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>aa_single_scrape</t>
         </is>
       </c>
       <c r="M79" t="n">
-        <v>140</v>
+        <v>16.8</v>
       </c>
       <c r="N79" t="n">
-        <v>175</v>
+        <v>21</v>
       </c>
       <c r="O79" t="n">
-        <v>70</v>
+        <v>8.4</v>
       </c>
       <c r="P79" t="n">
-        <v>87.5</v>
+        <v>10.5</v>
       </c>
       <c r="Q79" t="n">
-        <v>35</v>
+        <v>4.2</v>
       </c>
       <c r="R79" t="n">
-        <v>43.8</v>
-      </c>
-      <c r="S79" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+        <v>5.2</v>
+      </c>
+      <c r="S79" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="T79" s="6" t="inlineStr">
@@ -10052,14 +10052,14 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="V79" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W79" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="V79" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W79" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="X79" s="6" t="inlineStr">
@@ -10067,9 +10067,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="Y79" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="Y79" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Z79" s="6" t="inlineStr">
@@ -10114,12 +10114,12 @@
       </c>
       <c r="AH79" t="inlineStr">
         <is>
-          <t>B200 SXM</t>
+          <t>H100 SXM</t>
         </is>
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>RTX PRO 6000</t>
+          <t>H100 SXM</t>
         </is>
       </c>
     </row>
@@ -10129,148 +10129,68 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>gpt-oss-20b</t>
+          <t>qwen-max-0919</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1317.67</v>
+        <v>1317.74</v>
       </c>
       <c r="D80" t="n">
-        <v>1311.32</v>
+        <v>1312.05</v>
       </c>
       <c r="E80" t="n">
-        <v>1324.02</v>
+        <v>1323.43</v>
       </c>
       <c r="F80" t="n">
-        <v>10695</v>
+        <v>16478</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Alibaba</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
-        </is>
-      </c>
-      <c r="I80" t="n">
-        <v>21</v>
-      </c>
-      <c r="J80" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+          <t>Qwen</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr">
         <is>
-          <t>override</t>
-        </is>
-      </c>
-      <c r="M80" t="n">
-        <v>42</v>
-      </c>
-      <c r="N80" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="O80" t="n">
-        <v>21</v>
-      </c>
-      <c r="P80" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="Q80" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="R80" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="S80" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="T80" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="U80" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="V80" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W80" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X80" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Y80" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z80" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AA80" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB80" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AC80" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AD80" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AE80" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AF80" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AG80" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
+      <c r="O80" t="inlineStr"/>
+      <c r="P80" t="inlineStr"/>
+      <c r="Q80" t="inlineStr"/>
+      <c r="R80" t="inlineStr"/>
+      <c r="S80" t="inlineStr"/>
+      <c r="T80" t="inlineStr"/>
+      <c r="U80" t="inlineStr"/>
+      <c r="V80" t="inlineStr"/>
+      <c r="W80" t="inlineStr"/>
+      <c r="X80" t="inlineStr"/>
+      <c r="Y80" t="inlineStr"/>
+      <c r="Z80" t="inlineStr"/>
+      <c r="AA80" t="inlineStr"/>
+      <c r="AB80" t="inlineStr"/>
+      <c r="AC80" t="inlineStr"/>
+      <c r="AD80" t="inlineStr"/>
+      <c r="AE80" t="inlineStr"/>
+      <c r="AF80" t="inlineStr"/>
+      <c r="AG80" t="inlineStr"/>
       <c r="AH80" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="AI80" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -10280,68 +10200,148 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>qwen-max-0919</t>
+          <t>gpt-oss-20b</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1317.45</v>
+        <v>1317.56</v>
       </c>
       <c r="D81" t="n">
-        <v>1311.76</v>
+        <v>1311.2</v>
       </c>
       <c r="E81" t="n">
-        <v>1323.14</v>
+        <v>1323.92</v>
       </c>
       <c r="F81" t="n">
-        <v>16478</v>
+        <v>10639</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alibaba</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Qwen</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
+          <t>Apache 2.0</t>
+        </is>
+      </c>
+      <c r="I81" t="n">
+        <v>21</v>
+      </c>
+      <c r="J81" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="M81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
-      <c r="O81" t="inlineStr"/>
-      <c r="P81" t="inlineStr"/>
-      <c r="Q81" t="inlineStr"/>
-      <c r="R81" t="inlineStr"/>
-      <c r="S81" t="inlineStr"/>
-      <c r="T81" t="inlineStr"/>
-      <c r="U81" t="inlineStr"/>
-      <c r="V81" t="inlineStr"/>
-      <c r="W81" t="inlineStr"/>
-      <c r="X81" t="inlineStr"/>
-      <c r="Y81" t="inlineStr"/>
-      <c r="Z81" t="inlineStr"/>
-      <c r="AA81" t="inlineStr"/>
-      <c r="AB81" t="inlineStr"/>
-      <c r="AC81" t="inlineStr"/>
-      <c r="AD81" t="inlineStr"/>
-      <c r="AE81" t="inlineStr"/>
-      <c r="AF81" t="inlineStr"/>
-      <c r="AG81" t="inlineStr"/>
+          <t>override</t>
+        </is>
+      </c>
+      <c r="M81" t="n">
+        <v>42</v>
+      </c>
+      <c r="N81" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="O81" t="n">
+        <v>21</v>
+      </c>
+      <c r="P81" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="R81" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="S81" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T81" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U81" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V81" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W81" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X81" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y81" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z81" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AA81" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB81" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AC81" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AD81" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE81" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AF81" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AG81" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AH81" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>H100 SXM</t>
         </is>
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>H100 SXM</t>
         </is>
       </c>
     </row>
@@ -10361,10 +10361,10 @@
         <v>1311.83</v>
       </c>
       <c r="E82" t="n">
-        <v>1322.99</v>
+        <v>1323</v>
       </c>
       <c r="F82" t="n">
-        <v>15590</v>
+        <v>15543</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -10506,13 +10506,13 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>1314.01</v>
+        <v>1314.28</v>
       </c>
       <c r="D83" t="n">
-        <v>1309.49</v>
+        <v>1309.75</v>
       </c>
       <c r="E83" t="n">
-        <v>1318.54</v>
+        <v>1318.81</v>
       </c>
       <c r="F83" t="n">
         <v>24739</v>
@@ -10657,13 +10657,13 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>1313.34</v>
+        <v>1313.65</v>
       </c>
       <c r="D84" t="n">
-        <v>1309.44</v>
+        <v>1309.75</v>
       </c>
       <c r="E84" t="n">
-        <v>1317.24</v>
+        <v>1317.55</v>
       </c>
       <c r="F84" t="n">
         <v>45459</v>
@@ -10808,13 +10808,13 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>1306.59</v>
+        <v>1306.89</v>
       </c>
       <c r="D85" t="n">
-        <v>1301.91</v>
+        <v>1302.21</v>
       </c>
       <c r="E85" t="n">
-        <v>1311.28</v>
+        <v>1311.58</v>
       </c>
       <c r="F85" t="n">
         <v>24572</v>
@@ -10879,13 +10879,13 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>1305.53</v>
+        <v>1305.84</v>
       </c>
       <c r="D86" t="n">
-        <v>1299.86</v>
+        <v>1300.17</v>
       </c>
       <c r="E86" t="n">
-        <v>1311.19</v>
+        <v>1311.5</v>
       </c>
       <c r="F86" t="n">
         <v>19621</v>
@@ -11030,16 +11030,16 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>1305.34</v>
+        <v>1305.45</v>
       </c>
       <c r="D87" t="n">
-        <v>1297.16</v>
+        <v>1297.26</v>
       </c>
       <c r="E87" t="n">
-        <v>1313.51</v>
+        <v>1313.65</v>
       </c>
       <c r="F87" t="n">
-        <v>5986</v>
+        <v>5967</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -11181,13 +11181,13 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>1304.66</v>
+        <v>1304.97</v>
       </c>
       <c r="D88" t="n">
-        <v>1300.25</v>
+        <v>1300.56</v>
       </c>
       <c r="E88" t="n">
-        <v>1309.06</v>
+        <v>1309.37</v>
       </c>
       <c r="F88" t="n">
         <v>28073</v>
@@ -11248,36 +11248,36 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>gemma-3-4b-it</t>
+          <t>mistral-small-3.1-24b-instruct-2503</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>1302.81</v>
+        <v>1303.25</v>
       </c>
       <c r="D89" t="n">
-        <v>1293.49</v>
+        <v>1298.75</v>
       </c>
       <c r="E89" t="n">
-        <v>1312.12</v>
+        <v>1307.75</v>
       </c>
       <c r="F89" t="n">
-        <v>4171</v>
+        <v>33249</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Mistral</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Gemma</t>
+          <t>Apache 2.0</t>
         </is>
       </c>
       <c r="I89" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="J89" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
@@ -11290,22 +11290,22 @@
         </is>
       </c>
       <c r="M89" t="n">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="N89" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="O89" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="P89" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="Q89" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="R89" t="n">
-        <v>2.5</v>
+        <v>15</v>
       </c>
       <c r="S89" s="6" t="inlineStr">
         <is>
@@ -11399,36 +11399,36 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>mistral-small-3.1-24b-instruct-2503</t>
+          <t>gemma-3-4b-it</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>1302.67</v>
+        <v>1303.08</v>
       </c>
       <c r="D90" t="n">
-        <v>1298.18</v>
+        <v>1293.76</v>
       </c>
       <c r="E90" t="n">
-        <v>1307.16</v>
+        <v>1312.4</v>
       </c>
       <c r="F90" t="n">
-        <v>33462</v>
+        <v>4171</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Mistral</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
+          <t>Gemma</t>
         </is>
       </c>
       <c r="I90" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="J90" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
@@ -11441,22 +11441,22 @@
         </is>
       </c>
       <c r="M90" t="n">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="N90" t="n">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="O90" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="P90" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="Q90" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="R90" t="n">
-        <v>15</v>
+        <v>2.5</v>
       </c>
       <c r="S90" s="6" t="inlineStr">
         <is>
@@ -11554,13 +11554,13 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>1302.3</v>
+        <v>1302.59</v>
       </c>
       <c r="D91" t="n">
-        <v>1298.26</v>
+        <v>1298.55</v>
       </c>
       <c r="E91" t="n">
-        <v>1306.34</v>
+        <v>1306.64</v>
       </c>
       <c r="F91" t="n">
         <v>39406</v>
@@ -11705,13 +11705,13 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>1298.46</v>
+        <v>1298.71</v>
       </c>
       <c r="D92" t="n">
-        <v>1290.7</v>
+        <v>1290.95</v>
       </c>
       <c r="E92" t="n">
-        <v>1306.21</v>
+        <v>1306.47</v>
       </c>
       <c r="F92" t="n">
         <v>7140</v>
@@ -11856,13 +11856,13 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>1292.79</v>
+        <v>1293.07</v>
       </c>
       <c r="D93" t="n">
-        <v>1289.09</v>
+        <v>1289.36</v>
       </c>
       <c r="E93" t="n">
-        <v>1296.5</v>
+        <v>1296.78</v>
       </c>
       <c r="F93" t="n">
         <v>55240</v>
@@ -12007,13 +12007,13 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1288.21</v>
+        <v>1288.54</v>
       </c>
       <c r="D94" t="n">
-        <v>1280.91</v>
+        <v>1281.24</v>
       </c>
       <c r="E94" t="n">
-        <v>1295.51</v>
+        <v>1295.84</v>
       </c>
       <c r="F94" t="n">
         <v>8662</v>
@@ -12078,13 +12078,13 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1287.67</v>
+        <v>1288.02</v>
       </c>
       <c r="D95" t="n">
-        <v>1284.32</v>
+        <v>1284.67</v>
       </c>
       <c r="E95" t="n">
-        <v>1291.02</v>
+        <v>1291.37</v>
       </c>
       <c r="F95" t="n">
         <v>75754</v>
@@ -12229,16 +12229,16 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>1286.74</v>
+        <v>1286.82</v>
       </c>
       <c r="D96" t="n">
-        <v>1278.4</v>
+        <v>1278.43</v>
       </c>
       <c r="E96" t="n">
-        <v>1295.09</v>
+        <v>1295.21</v>
       </c>
       <c r="F96" t="n">
-        <v>5747</v>
+        <v>5691</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
@@ -12380,13 +12380,13 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1285.78</v>
+        <v>1286.02</v>
       </c>
       <c r="D97" t="n">
-        <v>1275.3</v>
+        <v>1275.55</v>
       </c>
       <c r="E97" t="n">
-        <v>1296.25</v>
+        <v>1296.5</v>
       </c>
       <c r="F97" t="n">
         <v>2846</v>
@@ -12527,36 +12527,36 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>olmo-3.1-32b-think</t>
+          <t>llama-3.1-nemotron-51b-instruct</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>1285.35</v>
+        <v>1285.61</v>
       </c>
       <c r="D98" t="n">
-        <v>1278.13</v>
+        <v>1275.64</v>
       </c>
       <c r="E98" t="n">
-        <v>1292.57</v>
+        <v>1295.59</v>
       </c>
       <c r="F98" t="n">
-        <v>8544</v>
+        <v>3749</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Ai2</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
+          <t>Llama 3.1</t>
         </is>
       </c>
       <c r="I98" t="n">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="J98" t="n">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
@@ -12569,26 +12569,26 @@
         </is>
       </c>
       <c r="M98" t="n">
-        <v>64</v>
+        <v>102</v>
       </c>
       <c r="N98" t="n">
-        <v>80</v>
+        <v>127.5</v>
       </c>
       <c r="O98" t="n">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="P98" t="n">
-        <v>40</v>
+        <v>63.8</v>
       </c>
       <c r="Q98" t="n">
-        <v>16</v>
+        <v>25.5</v>
       </c>
       <c r="R98" t="n">
-        <v>20</v>
-      </c>
-      <c r="S98" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+        <v>31.9</v>
+      </c>
+      <c r="S98" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="T98" s="6" t="inlineStr">
@@ -12601,9 +12601,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="V98" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="V98" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="W98" s="6" t="inlineStr">
@@ -12663,7 +12663,7 @@
       </c>
       <c r="AH98" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>H200 SXM</t>
         </is>
       </c>
       <c r="AI98" t="inlineStr">
@@ -12678,36 +12678,36 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>llama-3.1-nemotron-51b-instruct</t>
+          <t>olmo-3.1-32b-think</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>1285.3</v>
+        <v>1285.46</v>
       </c>
       <c r="D99" t="n">
-        <v>1275.33</v>
+        <v>1278.22</v>
       </c>
       <c r="E99" t="n">
-        <v>1295.28</v>
+        <v>1292.7</v>
       </c>
       <c r="F99" t="n">
-        <v>3749</v>
+        <v>8512</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Ai2</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Llama 3.1</t>
+          <t>Apache 2.0</t>
         </is>
       </c>
       <c r="I99" t="n">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="J99" t="n">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
@@ -12720,26 +12720,26 @@
         </is>
       </c>
       <c r="M99" t="n">
-        <v>102</v>
+        <v>64</v>
       </c>
       <c r="N99" t="n">
-        <v>127.5</v>
+        <v>80</v>
       </c>
       <c r="O99" t="n">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="P99" t="n">
-        <v>63.8</v>
+        <v>40</v>
       </c>
       <c r="Q99" t="n">
-        <v>25.5</v>
+        <v>16</v>
       </c>
       <c r="R99" t="n">
-        <v>31.9</v>
-      </c>
-      <c r="S99" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+        <v>20</v>
+      </c>
+      <c r="S99" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="T99" s="6" t="inlineStr">
@@ -12752,9 +12752,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="V99" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="V99" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W99" s="6" t="inlineStr">
@@ -12814,7 +12814,7 @@
       </c>
       <c r="AH99" t="inlineStr">
         <is>
-          <t>H200 SXM</t>
+          <t>H100 SXM</t>
         </is>
       </c>
       <c r="AI99" t="inlineStr">
@@ -12833,13 +12833,13 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>1278.9</v>
+        <v>1279.24</v>
       </c>
       <c r="D100" t="n">
-        <v>1272.04</v>
+        <v>1272.38</v>
       </c>
       <c r="E100" t="n">
-        <v>1285.75</v>
+        <v>1286.1</v>
       </c>
       <c r="F100" t="n">
         <v>10072</v>
@@ -12984,13 +12984,13 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1276.21</v>
+        <v>1276.49</v>
       </c>
       <c r="D101" t="n">
-        <v>1270.88</v>
+        <v>1271.17</v>
       </c>
       <c r="E101" t="n">
-        <v>1281.54</v>
+        <v>1281.82</v>
       </c>
       <c r="F101" t="n">
         <v>19659</v>
@@ -13135,13 +13135,13 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>1275.47</v>
+        <v>1275.75</v>
       </c>
       <c r="D102" t="n">
-        <v>1268.91</v>
+        <v>1269.18</v>
       </c>
       <c r="E102" t="n">
-        <v>1282.04</v>
+        <v>1282.32</v>
       </c>
       <c r="F102" t="n">
         <v>9866</v>
@@ -13286,13 +13286,13 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>1275.18</v>
+        <v>1275.49</v>
       </c>
       <c r="D103" t="n">
-        <v>1271.61</v>
+        <v>1271.92</v>
       </c>
       <c r="E103" t="n">
-        <v>1278.76</v>
+        <v>1279.07</v>
       </c>
       <c r="F103" t="n">
         <v>156876</v>
@@ -13437,13 +13437,13 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>1273.45</v>
+        <v>1273.77</v>
       </c>
       <c r="D104" t="n">
-        <v>1267.56</v>
+        <v>1267.88</v>
       </c>
       <c r="E104" t="n">
-        <v>1279.34</v>
+        <v>1279.66</v>
       </c>
       <c r="F104" t="n">
         <v>14681</v>
@@ -13588,13 +13588,13 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>1269.9</v>
+        <v>1270.19</v>
       </c>
       <c r="D105" t="n">
-        <v>1261.78</v>
+        <v>1262.07</v>
       </c>
       <c r="E105" t="n">
-        <v>1278.02</v>
+        <v>1278.31</v>
       </c>
       <c r="F105" t="n">
         <v>5432</v>
@@ -13739,13 +13739,13 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>1266.29</v>
+        <v>1266.58</v>
       </c>
       <c r="D106" t="n">
-        <v>1261.43</v>
+        <v>1261.72</v>
       </c>
       <c r="E106" t="n">
-        <v>1271.16</v>
+        <v>1271.45</v>
       </c>
       <c r="F106" t="n">
         <v>27124</v>
@@ -13890,13 +13890,13 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>1265.14</v>
+        <v>1265.5</v>
       </c>
       <c r="D107" t="n">
-        <v>1261.35</v>
+        <v>1261.7</v>
       </c>
       <c r="E107" t="n">
-        <v>1268.93</v>
+        <v>1269.29</v>
       </c>
       <c r="F107" t="n">
         <v>54611</v>
@@ -14041,13 +14041,13 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>1263.44</v>
+        <v>1263.81</v>
       </c>
       <c r="D108" t="n">
-        <v>1257.16</v>
+        <v>1257.53</v>
       </c>
       <c r="E108" t="n">
-        <v>1269.72</v>
+        <v>1270.09</v>
       </c>
       <c r="F108" t="n">
         <v>15147</v>
@@ -14188,68 +14188,148 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>command-r-plus</t>
+          <t>qwen2-72b-instruct</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>1260.72</v>
+        <v>1261.02</v>
       </c>
       <c r="D109" t="n">
-        <v>1256.4</v>
+        <v>1256.09</v>
       </c>
       <c r="E109" t="n">
-        <v>1265.04</v>
+        <v>1265.96</v>
       </c>
       <c r="F109" t="n">
-        <v>77554</v>
+        <v>37325</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Cohere</t>
+          <t>Alibaba</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>CC-BY-NC-4.0</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
+          <t>Qianwen LICENSE</t>
+        </is>
+      </c>
+      <c r="I109" t="n">
+        <v>72</v>
+      </c>
+      <c r="J109" t="n">
+        <v>72</v>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>dense</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="M109" t="inlineStr"/>
-      <c r="N109" t="inlineStr"/>
-      <c r="O109" t="inlineStr"/>
-      <c r="P109" t="inlineStr"/>
-      <c r="Q109" t="inlineStr"/>
-      <c r="R109" t="inlineStr"/>
-      <c r="S109" t="inlineStr"/>
-      <c r="T109" t="inlineStr"/>
-      <c r="U109" t="inlineStr"/>
-      <c r="V109" t="inlineStr"/>
-      <c r="W109" t="inlineStr"/>
-      <c r="X109" t="inlineStr"/>
-      <c r="Y109" t="inlineStr"/>
-      <c r="Z109" t="inlineStr"/>
-      <c r="AA109" t="inlineStr"/>
-      <c r="AB109" t="inlineStr"/>
-      <c r="AC109" t="inlineStr"/>
-      <c r="AD109" t="inlineStr"/>
-      <c r="AE109" t="inlineStr"/>
-      <c r="AF109" t="inlineStr"/>
-      <c r="AG109" t="inlineStr"/>
+          <t>name_parsing</t>
+        </is>
+      </c>
+      <c r="M109" t="n">
+        <v>144</v>
+      </c>
+      <c r="N109" t="n">
+        <v>180</v>
+      </c>
+      <c r="O109" t="n">
+        <v>72</v>
+      </c>
+      <c r="P109" t="n">
+        <v>90</v>
+      </c>
+      <c r="Q109" t="n">
+        <v>36</v>
+      </c>
+      <c r="R109" t="n">
+        <v>45</v>
+      </c>
+      <c r="S109" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T109" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U109" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V109" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W109" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X109" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y109" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z109" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AA109" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB109" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AC109" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AD109" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE109" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AF109" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AG109" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AH109" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>B200 SXM</t>
         </is>
       </c>
       <c r="AI109" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>RTX PRO 6000</t>
         </is>
       </c>
     </row>
@@ -14259,148 +14339,68 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>qwen2-72b-instruct</t>
+          <t>command-r-plus</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>1260.71</v>
+        <v>1261.02</v>
       </c>
       <c r="D110" t="n">
-        <v>1255.78</v>
+        <v>1256.7</v>
       </c>
       <c r="E110" t="n">
-        <v>1265.65</v>
+        <v>1265.34</v>
       </c>
       <c r="F110" t="n">
-        <v>37325</v>
+        <v>77554</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alibaba</t>
+          <t>Cohere</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Qianwen LICENSE</t>
-        </is>
-      </c>
-      <c r="I110" t="n">
-        <v>72</v>
-      </c>
-      <c r="J110" t="n">
-        <v>72</v>
-      </c>
-      <c r="K110" t="inlineStr">
-        <is>
-          <t>dense</t>
-        </is>
-      </c>
+          <t>CC-BY-NC-4.0</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
       <c r="L110" t="inlineStr">
         <is>
-          <t>name_parsing</t>
-        </is>
-      </c>
-      <c r="M110" t="n">
-        <v>144</v>
-      </c>
-      <c r="N110" t="n">
-        <v>180</v>
-      </c>
-      <c r="O110" t="n">
-        <v>72</v>
-      </c>
-      <c r="P110" t="n">
-        <v>90</v>
-      </c>
-      <c r="Q110" t="n">
-        <v>36</v>
-      </c>
-      <c r="R110" t="n">
-        <v>45</v>
-      </c>
-      <c r="S110" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T110" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="U110" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="V110" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W110" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X110" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Y110" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z110" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AA110" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB110" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AC110" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AD110" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AE110" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AF110" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AG110" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
+      <c r="O110" t="inlineStr"/>
+      <c r="P110" t="inlineStr"/>
+      <c r="Q110" t="inlineStr"/>
+      <c r="R110" t="inlineStr"/>
+      <c r="S110" t="inlineStr"/>
+      <c r="T110" t="inlineStr"/>
+      <c r="U110" t="inlineStr"/>
+      <c r="V110" t="inlineStr"/>
+      <c r="W110" t="inlineStr"/>
+      <c r="X110" t="inlineStr"/>
+      <c r="Y110" t="inlineStr"/>
+      <c r="Z110" t="inlineStr"/>
+      <c r="AA110" t="inlineStr"/>
+      <c r="AB110" t="inlineStr"/>
+      <c r="AC110" t="inlineStr"/>
+      <c r="AD110" t="inlineStr"/>
+      <c r="AE110" t="inlineStr"/>
+      <c r="AF110" t="inlineStr"/>
+      <c r="AG110" t="inlineStr"/>
       <c r="AH110" t="inlineStr">
         <is>
-          <t>B200 SXM</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="AI110" t="inlineStr">
         <is>
-          <t>RTX PRO 6000</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -14414,13 +14414,13 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>1255.44</v>
+        <v>1255.75</v>
       </c>
       <c r="D111" t="n">
-        <v>1250.87</v>
+        <v>1251.18</v>
       </c>
       <c r="E111" t="n">
-        <v>1260.01</v>
+        <v>1260.32</v>
       </c>
       <c r="F111" t="n">
         <v>24126</v>
@@ -14565,13 +14565,13 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>1251.14</v>
+        <v>1251.43</v>
       </c>
       <c r="D112" t="n">
-        <v>1240.35</v>
+        <v>1240.64</v>
       </c>
       <c r="E112" t="n">
-        <v>1261.93</v>
+        <v>1262.23</v>
       </c>
       <c r="F112" t="n">
         <v>3334</v>
@@ -14716,13 +14716,13 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>1249.08</v>
+        <v>1249.39</v>
       </c>
       <c r="D113" t="n">
-        <v>1242.48</v>
+        <v>1242.8</v>
       </c>
       <c r="E113" t="n">
-        <v>1255.67</v>
+        <v>1255.98</v>
       </c>
       <c r="F113" t="n">
         <v>10140</v>
@@ -14867,13 +14867,13 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>1238.42</v>
+        <v>1238.74</v>
       </c>
       <c r="D114" t="n">
-        <v>1231.19</v>
+        <v>1231.52</v>
       </c>
       <c r="E114" t="n">
-        <v>1245.64</v>
+        <v>1245.97</v>
       </c>
       <c r="F114" t="n">
         <v>8858</v>
@@ -14938,13 +14938,13 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>1236.59</v>
+        <v>1236.9</v>
       </c>
       <c r="D115" t="n">
-        <v>1227.49</v>
+        <v>1227.8</v>
       </c>
       <c r="E115" t="n">
-        <v>1245.68</v>
+        <v>1245.99</v>
       </c>
       <c r="F115" t="n">
         <v>4781</v>
@@ -15089,13 +15089,13 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>1232.99</v>
+        <v>1233.3</v>
       </c>
       <c r="D116" t="n">
-        <v>1227.43</v>
+        <v>1227.75</v>
       </c>
       <c r="E116" t="n">
-        <v>1238.54</v>
+        <v>1238.86</v>
       </c>
       <c r="F116" t="n">
         <v>26195</v>
@@ -15240,13 +15240,13 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>1232.04</v>
+        <v>1232.36</v>
       </c>
       <c r="D117" t="n">
-        <v>1226.76</v>
+        <v>1227.09</v>
       </c>
       <c r="E117" t="n">
-        <v>1237.32</v>
+        <v>1237.64</v>
       </c>
       <c r="F117" t="n">
         <v>39302</v>
@@ -15391,13 +15391,13 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>1228.22</v>
+        <v>1228.54</v>
       </c>
       <c r="D118" t="n">
-        <v>1223.67</v>
+        <v>1223.99</v>
       </c>
       <c r="E118" t="n">
-        <v>1232.77</v>
+        <v>1233.09</v>
       </c>
       <c r="F118" t="n">
         <v>51416</v>
@@ -15542,13 +15542,13 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>1225.69</v>
+        <v>1225.99</v>
       </c>
       <c r="D119" t="n">
-        <v>1220.91</v>
+        <v>1221.21</v>
       </c>
       <c r="E119" t="n">
-        <v>1230.47</v>
+        <v>1230.78</v>
       </c>
       <c r="F119" t="n">
         <v>54036</v>
@@ -15609,29 +15609,29 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>c4ai-aya-expanse-8b</t>
+          <t>llama-3-8b-instruct</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>1222.26</v>
+        <v>1222.55</v>
       </c>
       <c r="D120" t="n">
-        <v>1215.3</v>
+        <v>1218.82</v>
       </c>
       <c r="E120" t="n">
-        <v>1229.22</v>
+        <v>1226.28</v>
       </c>
       <c r="F120" t="n">
-        <v>9818</v>
+        <v>104642</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Cohere</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>CC-BY-NC-4.0</t>
+          <t>Llama 3 Community</t>
         </is>
       </c>
       <c r="I120" t="n">
@@ -15760,29 +15760,29 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>llama-3-8b-instruct</t>
+          <t>c4ai-aya-expanse-8b</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>1222.24</v>
+        <v>1222.54</v>
       </c>
       <c r="D121" t="n">
-        <v>1218.52</v>
+        <v>1215.58</v>
       </c>
       <c r="E121" t="n">
-        <v>1225.97</v>
+        <v>1229.49</v>
       </c>
       <c r="F121" t="n">
-        <v>104642</v>
+        <v>9818</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>Cohere</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Llama 3 Community</t>
+          <t>CC-BY-NC-4.0</t>
         </is>
       </c>
       <c r="I121" t="n">
@@ -15915,13 +15915,13 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>1220.32</v>
+        <v>1220.56</v>
       </c>
       <c r="D122" t="n">
-        <v>1209.63</v>
+        <v>1209.88</v>
       </c>
       <c r="E122" t="n">
-        <v>1231</v>
+        <v>1231.25</v>
       </c>
       <c r="F122" t="n">
         <v>2896</v>
@@ -16066,13 +16066,13 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>1212.37</v>
+        <v>1212.63</v>
       </c>
       <c r="D123" t="n">
-        <v>1207.33</v>
+        <v>1207.59</v>
       </c>
       <c r="E123" t="n">
-        <v>1217.4</v>
+        <v>1217.66</v>
       </c>
       <c r="F123" t="n">
         <v>24146</v>
@@ -16217,13 +16217,13 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>1211.53</v>
+        <v>1211.85</v>
       </c>
       <c r="D124" t="n">
-        <v>1200.72</v>
+        <v>1201.04</v>
       </c>
       <c r="E124" t="n">
-        <v>1222.34</v>
+        <v>1222.66</v>
       </c>
       <c r="F124" t="n">
         <v>4652</v>
@@ -16368,13 +16368,13 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>1211.01</v>
+        <v>1211.27</v>
       </c>
       <c r="D125" t="n">
-        <v>1206.88</v>
+        <v>1207.14</v>
       </c>
       <c r="E125" t="n">
-        <v>1215.13</v>
+        <v>1215.39</v>
       </c>
       <c r="F125" t="n">
         <v>49605</v>
@@ -16519,13 +16519,13 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>1207.32</v>
+        <v>1207.61</v>
       </c>
       <c r="D126" t="n">
-        <v>1196.21</v>
+        <v>1196.5</v>
       </c>
       <c r="E126" t="n">
-        <v>1218.43</v>
+        <v>1218.72</v>
       </c>
       <c r="F126" t="n">
         <v>3090</v>
@@ -16670,13 +16670,13 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>1202.64</v>
+        <v>1202.95</v>
       </c>
       <c r="D127" t="n">
-        <v>1196.52</v>
+        <v>1196.83</v>
       </c>
       <c r="E127" t="n">
-        <v>1208.76</v>
+        <v>1209.07</v>
       </c>
       <c r="F127" t="n">
         <v>21741</v>
@@ -16821,13 +16821,13 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>1198.64</v>
+        <v>1198.95</v>
       </c>
       <c r="D128" t="n">
-        <v>1194.57</v>
+        <v>1194.89</v>
       </c>
       <c r="E128" t="n">
-        <v>1202.7</v>
+        <v>1203.02</v>
       </c>
       <c r="F128" t="n">
         <v>46616</v>
@@ -16972,13 +16972,13 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>1196.77</v>
+        <v>1197.06</v>
       </c>
       <c r="D129" t="n">
-        <v>1191.61</v>
+        <v>1191.91</v>
       </c>
       <c r="E129" t="n">
-        <v>1201.92</v>
+        <v>1202.22</v>
       </c>
       <c r="F129" t="n">
         <v>25055</v>
@@ -17123,13 +17123,13 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>1195.9</v>
+        <v>1196.2</v>
       </c>
       <c r="D130" t="n">
-        <v>1191.63</v>
+        <v>1191.93</v>
       </c>
       <c r="E130" t="n">
-        <v>1200.17</v>
+        <v>1200.47</v>
       </c>
       <c r="F130" t="n">
         <v>73503</v>
@@ -17274,13 +17274,13 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>1193.84</v>
+        <v>1194.18</v>
       </c>
       <c r="D131" t="n">
-        <v>1187.72</v>
+        <v>1188.06</v>
       </c>
       <c r="E131" t="n">
-        <v>1199.95</v>
+        <v>1200.3</v>
       </c>
       <c r="F131" t="n">
         <v>32191</v>
@@ -17345,13 +17345,13 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>1190.4</v>
+        <v>1190.65</v>
       </c>
       <c r="D132" t="n">
-        <v>1183.23</v>
+        <v>1183.47</v>
       </c>
       <c r="E132" t="n">
-        <v>1197.58</v>
+        <v>1197.83</v>
       </c>
       <c r="F132" t="n">
         <v>9901</v>
@@ -17496,13 +17496,13 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>1189.77</v>
+        <v>1190.07</v>
       </c>
       <c r="D133" t="n">
-        <v>1182.64</v>
+        <v>1182.95</v>
       </c>
       <c r="E133" t="n">
-        <v>1196.89</v>
+        <v>1197.2</v>
       </c>
       <c r="F133" t="n">
         <v>17839</v>
@@ -17647,13 +17647,13 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>1183.43</v>
+        <v>1183.73</v>
       </c>
       <c r="D134" t="n">
-        <v>1173.97</v>
+        <v>1174.27</v>
       </c>
       <c r="E134" t="n">
-        <v>1192.88</v>
+        <v>1193.19</v>
       </c>
       <c r="F134" t="n">
         <v>8214</v>
@@ -17798,13 +17798,13 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>1183.15</v>
+        <v>1183.5</v>
       </c>
       <c r="D135" t="n">
-        <v>1171.64</v>
+        <v>1171.99</v>
       </c>
       <c r="E135" t="n">
-        <v>1194.67</v>
+        <v>1195.02</v>
       </c>
       <c r="F135" t="n">
         <v>4932</v>
@@ -17949,13 +17949,13 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>1182.71</v>
+        <v>1183</v>
       </c>
       <c r="D136" t="n">
-        <v>1175.88</v>
+        <v>1176.17</v>
       </c>
       <c r="E136" t="n">
-        <v>1189.54</v>
+        <v>1189.83</v>
       </c>
       <c r="F136" t="n">
         <v>15483</v>
@@ -18100,13 +18100,13 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>1181.03</v>
+        <v>1181.37</v>
       </c>
       <c r="D137" t="n">
-        <v>1173.03</v>
+        <v>1173.37</v>
       </c>
       <c r="E137" t="n">
-        <v>1189.04</v>
+        <v>1189.37</v>
       </c>
       <c r="F137" t="n">
         <v>12637</v>
@@ -18171,13 +18171,13 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>1180.99</v>
+        <v>1181.35</v>
       </c>
       <c r="D138" t="n">
-        <v>1171.31</v>
+        <v>1171.67</v>
       </c>
       <c r="E138" t="n">
-        <v>1190.67</v>
+        <v>1191.03</v>
       </c>
       <c r="F138" t="n">
         <v>7968</v>
@@ -18242,13 +18242,13 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>1180.94</v>
+        <v>1181.31</v>
       </c>
       <c r="D139" t="n">
-        <v>1172.26</v>
+        <v>1172.62</v>
       </c>
       <c r="E139" t="n">
-        <v>1189.63</v>
+        <v>1190</v>
       </c>
       <c r="F139" t="n">
         <v>6638</v>
@@ -18393,13 +18393,13 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>1179.75</v>
+        <v>1180.17</v>
       </c>
       <c r="D140" t="n">
-        <v>1173.68</v>
+        <v>1174.1</v>
       </c>
       <c r="E140" t="n">
-        <v>1185.82</v>
+        <v>1186.24</v>
       </c>
       <c r="F140" t="n">
         <v>23893</v>
@@ -18544,13 +18544,13 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>1178.25</v>
+        <v>1178.6</v>
       </c>
       <c r="D141" t="n">
-        <v>1172.34</v>
+        <v>1172.68</v>
       </c>
       <c r="E141" t="n">
-        <v>1184.17</v>
+        <v>1184.51</v>
       </c>
       <c r="F141" t="n">
         <v>32832</v>
@@ -18615,13 +18615,13 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>1177.89</v>
+        <v>1178.16</v>
       </c>
       <c r="D142" t="n">
-        <v>1166.68</v>
+        <v>1166.95</v>
       </c>
       <c r="E142" t="n">
-        <v>1189.09</v>
+        <v>1189.36</v>
       </c>
       <c r="F142" t="n">
         <v>3188</v>
@@ -18766,13 +18766,13 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>1176.74</v>
+        <v>1177.02</v>
       </c>
       <c r="D143" t="n">
-        <v>1166.92</v>
+        <v>1167.2</v>
       </c>
       <c r="E143" t="n">
-        <v>1186.56</v>
+        <v>1186.85</v>
       </c>
       <c r="F143" t="n">
         <v>6535</v>
@@ -18917,13 +18917,13 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>1173.96</v>
+        <v>1174.32</v>
       </c>
       <c r="D144" t="n">
-        <v>1163.54</v>
+        <v>1163.89</v>
       </c>
       <c r="E144" t="n">
-        <v>1184.39</v>
+        <v>1184.74</v>
       </c>
       <c r="F144" t="n">
         <v>5006</v>
@@ -19068,13 +19068,13 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>1171.53</v>
+        <v>1171.84</v>
       </c>
       <c r="D145" t="n">
-        <v>1165.32</v>
+        <v>1165.63</v>
       </c>
       <c r="E145" t="n">
-        <v>1177.74</v>
+        <v>1178.05</v>
       </c>
       <c r="F145" t="n">
         <v>22479</v>
@@ -19219,13 +19219,13 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>1170.43</v>
+        <v>1170.65</v>
       </c>
       <c r="D146" t="n">
-        <v>1163.02</v>
+        <v>1163.24</v>
       </c>
       <c r="E146" t="n">
-        <v>1177.85</v>
+        <v>1178.07</v>
       </c>
       <c r="F146" t="n">
         <v>16056</v>
@@ -19370,13 +19370,13 @@
         </is>
       </c>
       <c r="C147" t="n">
-        <v>1169.91</v>
+        <v>1170.21</v>
       </c>
       <c r="D147" t="n">
-        <v>1164</v>
+        <v>1164.3</v>
       </c>
       <c r="E147" t="n">
-        <v>1175.83</v>
+        <v>1176.13</v>
       </c>
       <c r="F147" t="n">
         <v>17766</v>
@@ -19521,13 +19521,13 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>1169.58</v>
+        <v>1169.85</v>
       </c>
       <c r="D148" t="n">
-        <v>1164.07</v>
+        <v>1164.35</v>
       </c>
       <c r="E148" t="n">
-        <v>1175.08</v>
+        <v>1175.36</v>
       </c>
       <c r="F148" t="n">
         <v>38492</v>
@@ -19672,13 +19672,13 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>1166.29</v>
+        <v>1166.57</v>
       </c>
       <c r="D149" t="n">
-        <v>1158.21</v>
+        <v>1158.5</v>
       </c>
       <c r="E149" t="n">
-        <v>1174.36</v>
+        <v>1174.65</v>
       </c>
       <c r="F149" t="n">
         <v>10224</v>
@@ -19823,13 +19823,13 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>1165.67</v>
+        <v>1165.98</v>
       </c>
       <c r="D150" t="n">
-        <v>1157.98</v>
+        <v>1158.28</v>
       </c>
       <c r="E150" t="n">
-        <v>1173.37</v>
+        <v>1173.67</v>
       </c>
       <c r="F150" t="n">
         <v>7936</v>
@@ -19974,13 +19974,13 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>1163.5</v>
+        <v>1163.77</v>
       </c>
       <c r="D151" t="n">
-        <v>1151.56</v>
+        <v>1151.83</v>
       </c>
       <c r="E151" t="n">
-        <v>1175.44</v>
+        <v>1175.71</v>
       </c>
       <c r="F151" t="n">
         <v>3777</v>
@@ -20125,13 +20125,13 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>1155.74</v>
+        <v>1155.86</v>
       </c>
       <c r="D152" t="n">
-        <v>1144.23</v>
+        <v>1144.36</v>
       </c>
       <c r="E152" t="n">
-        <v>1167.24</v>
+        <v>1167.36</v>
       </c>
       <c r="F152" t="n">
         <v>3231</v>
@@ -20276,13 +20276,13 @@
         </is>
       </c>
       <c r="C153" t="n">
-        <v>1154.89</v>
+        <v>1155.23</v>
       </c>
       <c r="D153" t="n">
-        <v>1146.5</v>
+        <v>1146.84</v>
       </c>
       <c r="E153" t="n">
-        <v>1163.28</v>
+        <v>1163.62</v>
       </c>
       <c r="F153" t="n">
         <v>6837</v>
@@ -20427,13 +20427,13 @@
         </is>
       </c>
       <c r="C154" t="n">
-        <v>1153.98</v>
+        <v>1154.27</v>
       </c>
       <c r="D154" t="n">
-        <v>1141.36</v>
+        <v>1141.65</v>
       </c>
       <c r="E154" t="n">
-        <v>1166.6</v>
+        <v>1166.89</v>
       </c>
       <c r="F154" t="n">
         <v>3585</v>
@@ -20578,13 +20578,13 @@
         </is>
       </c>
       <c r="C155" t="n">
-        <v>1151.08</v>
+        <v>1151.39</v>
       </c>
       <c r="D155" t="n">
-        <v>1137.87</v>
+        <v>1138.19</v>
       </c>
       <c r="E155" t="n">
-        <v>1164.28</v>
+        <v>1164.6</v>
       </c>
       <c r="F155" t="n">
         <v>4155</v>
@@ -20729,13 +20729,13 @@
         </is>
       </c>
       <c r="C156" t="n">
-        <v>1150.76</v>
+        <v>1151.08</v>
       </c>
       <c r="D156" t="n">
-        <v>1135.36</v>
+        <v>1135.69</v>
       </c>
       <c r="E156" t="n">
-        <v>1166.14</v>
+        <v>1166.47</v>
       </c>
       <c r="F156" t="n">
         <v>1679</v>
@@ -20880,13 +20880,13 @@
         </is>
       </c>
       <c r="C157" t="n">
-        <v>1148.86</v>
+        <v>1149.21</v>
       </c>
       <c r="D157" t="n">
-        <v>1136.57</v>
+        <v>1136.92</v>
       </c>
       <c r="E157" t="n">
-        <v>1161.16</v>
+        <v>1161.51</v>
       </c>
       <c r="F157" t="n">
         <v>2572</v>
@@ -21031,13 +21031,13 @@
         </is>
       </c>
       <c r="C158" t="n">
-        <v>1148.33</v>
+        <v>1148.62</v>
       </c>
       <c r="D158" t="n">
-        <v>1141.67</v>
+        <v>1141.96</v>
       </c>
       <c r="E158" t="n">
-        <v>1154.98</v>
+        <v>1155.27</v>
       </c>
       <c r="F158" t="n">
         <v>19402</v>
@@ -21182,13 +21182,13 @@
         </is>
       </c>
       <c r="C159" t="n">
-        <v>1147.96</v>
+        <v>1148.28</v>
       </c>
       <c r="D159" t="n">
-        <v>1138.69</v>
+        <v>1139.02</v>
       </c>
       <c r="E159" t="n">
-        <v>1157.22</v>
+        <v>1157.54</v>
       </c>
       <c r="F159" t="n">
         <v>7044</v>
@@ -21333,13 +21333,13 @@
         </is>
       </c>
       <c r="C160" t="n">
-        <v>1145.82</v>
+        <v>1146.21</v>
       </c>
       <c r="D160" t="n">
-        <v>1128.7</v>
+        <v>1129.08</v>
       </c>
       <c r="E160" t="n">
-        <v>1162.94</v>
+        <v>1163.33</v>
       </c>
       <c r="F160" t="n">
         <v>1295</v>
@@ -21484,13 +21484,13 @@
         </is>
       </c>
       <c r="C161" t="n">
-        <v>1142.62</v>
+        <v>1142.91</v>
       </c>
       <c r="D161" t="n">
-        <v>1132.72</v>
+        <v>1133.01</v>
       </c>
       <c r="E161" t="n">
-        <v>1152.51</v>
+        <v>1152.81</v>
       </c>
       <c r="F161" t="n">
         <v>4737</v>
@@ -21635,13 +21635,13 @@
         </is>
       </c>
       <c r="C162" t="n">
-        <v>1141.9</v>
+        <v>1142.21</v>
       </c>
       <c r="D162" t="n">
-        <v>1135.47</v>
+        <v>1135.77</v>
       </c>
       <c r="E162" t="n">
-        <v>1148.34</v>
+        <v>1148.64</v>
       </c>
       <c r="F162" t="n">
         <v>12297</v>
@@ -21786,13 +21786,13 @@
         </is>
       </c>
       <c r="C163" t="n">
-        <v>1140.29</v>
+        <v>1140.57</v>
       </c>
       <c r="D163" t="n">
-        <v>1133.56</v>
+        <v>1133.84</v>
       </c>
       <c r="E163" t="n">
-        <v>1147.02</v>
+        <v>1147.3</v>
       </c>
       <c r="F163" t="n">
         <v>19174</v>
@@ -21937,13 +21937,13 @@
         </is>
       </c>
       <c r="C164" t="n">
-        <v>1139.66</v>
+        <v>1140.02</v>
       </c>
       <c r="D164" t="n">
-        <v>1132.95</v>
+        <v>1133.3</v>
       </c>
       <c r="E164" t="n">
-        <v>1146.38</v>
+        <v>1146.73</v>
       </c>
       <c r="F164" t="n">
         <v>19367</v>
@@ -22088,13 +22088,13 @@
         </is>
       </c>
       <c r="C165" t="n">
-        <v>1137.32</v>
+        <v>1137.7</v>
       </c>
       <c r="D165" t="n">
-        <v>1126.36</v>
+        <v>1126.73</v>
       </c>
       <c r="E165" t="n">
-        <v>1148.29</v>
+        <v>1148.66</v>
       </c>
       <c r="F165" t="n">
         <v>4964</v>
@@ -22239,13 +22239,13 @@
         </is>
       </c>
       <c r="C166" t="n">
-        <v>1135.38</v>
+        <v>1135.78</v>
       </c>
       <c r="D166" t="n">
-        <v>1125.87</v>
+        <v>1126.27</v>
       </c>
       <c r="E166" t="n">
-        <v>1144.89</v>
+        <v>1145.28</v>
       </c>
       <c r="F166" t="n">
         <v>8925</v>
@@ -22390,13 +22390,13 @@
         </is>
       </c>
       <c r="C167" t="n">
-        <v>1135.32</v>
+        <v>1135.64</v>
       </c>
       <c r="D167" t="n">
-        <v>1126.42</v>
+        <v>1126.73</v>
       </c>
       <c r="E167" t="n">
-        <v>1144.23</v>
+        <v>1144.55</v>
       </c>
       <c r="F167" t="n">
         <v>7366</v>
@@ -22541,13 +22541,13 @@
         </is>
       </c>
       <c r="C168" t="n">
-        <v>1129.74</v>
+        <v>1130.03</v>
       </c>
       <c r="D168" t="n">
-        <v>1120.89</v>
+        <v>1121.19</v>
       </c>
       <c r="E168" t="n">
-        <v>1138.59</v>
+        <v>1138.88</v>
       </c>
       <c r="F168" t="n">
         <v>11118</v>
@@ -22692,13 +22692,13 @@
         </is>
       </c>
       <c r="C169" t="n">
-        <v>1128.01</v>
+        <v>1128.36</v>
       </c>
       <c r="D169" t="n">
-        <v>1120.59</v>
+        <v>1120.93</v>
       </c>
       <c r="E169" t="n">
-        <v>1135.44</v>
+        <v>1135.79</v>
       </c>
       <c r="F169" t="n">
         <v>20685</v>
@@ -22843,13 +22843,13 @@
         </is>
       </c>
       <c r="C170" t="n">
-        <v>1127.18</v>
+        <v>1127.46</v>
       </c>
       <c r="D170" t="n">
-        <v>1120.79</v>
+        <v>1121.06</v>
       </c>
       <c r="E170" t="n">
-        <v>1133.58</v>
+        <v>1133.86</v>
       </c>
       <c r="F170" t="n">
         <v>20118</v>
@@ -22994,13 +22994,13 @@
         </is>
       </c>
       <c r="C171" t="n">
-        <v>1126.03</v>
+        <v>1126.36</v>
       </c>
       <c r="D171" t="n">
-        <v>1113.88</v>
+        <v>1114.21</v>
       </c>
       <c r="E171" t="n">
-        <v>1138.17</v>
+        <v>1138.5</v>
       </c>
       <c r="F171" t="n">
         <v>2921</v>
@@ -23145,13 +23145,13 @@
         </is>
       </c>
       <c r="C172" t="n">
-        <v>1125.62</v>
+        <v>1125.93</v>
       </c>
       <c r="D172" t="n">
-        <v>1109.95</v>
+        <v>1110.26</v>
       </c>
       <c r="E172" t="n">
-        <v>1141.28</v>
+        <v>1141.59</v>
       </c>
       <c r="F172" t="n">
         <v>1785</v>
@@ -23296,13 +23296,13 @@
         </is>
       </c>
       <c r="C173" t="n">
-        <v>1119.73</v>
+        <v>1120.09</v>
       </c>
       <c r="D173" t="n">
-        <v>1108.73</v>
+        <v>1109.09</v>
       </c>
       <c r="E173" t="n">
-        <v>1130.73</v>
+        <v>1131.09</v>
       </c>
       <c r="F173" t="n">
         <v>5182</v>
@@ -23447,13 +23447,13 @@
         </is>
       </c>
       <c r="C174" t="n">
-        <v>1117.91</v>
+        <v>1118.22</v>
       </c>
       <c r="D174" t="n">
-        <v>1099.71</v>
+        <v>1100.01</v>
       </c>
       <c r="E174" t="n">
-        <v>1136.11</v>
+        <v>1136.42</v>
       </c>
       <c r="F174" t="n">
         <v>1143</v>
@@ -23598,13 +23598,13 @@
         </is>
       </c>
       <c r="C175" t="n">
-        <v>1113.63</v>
+        <v>1114.05</v>
       </c>
       <c r="D175" t="n">
-        <v>1105.89</v>
+        <v>1106.32</v>
       </c>
       <c r="E175" t="n">
-        <v>1121.37</v>
+        <v>1121.79</v>
       </c>
       <c r="F175" t="n">
         <v>10854</v>
@@ -23749,13 +23749,13 @@
         </is>
       </c>
       <c r="C176" t="n">
-        <v>1113.39</v>
+        <v>1113.74</v>
       </c>
       <c r="D176" t="n">
-        <v>1104.21</v>
+        <v>1104.57</v>
       </c>
       <c r="E176" t="n">
-        <v>1122.56</v>
+        <v>1122.92</v>
       </c>
       <c r="F176" t="n">
         <v>6923</v>
@@ -23900,13 +23900,13 @@
         </is>
       </c>
       <c r="C177" t="n">
-        <v>1113.16</v>
+        <v>1113.48</v>
       </c>
       <c r="D177" t="n">
-        <v>1098.75</v>
+        <v>1099.07</v>
       </c>
       <c r="E177" t="n">
-        <v>1127.57</v>
+        <v>1127.89</v>
       </c>
       <c r="F177" t="n">
         <v>2199</v>
@@ -24051,13 +24051,13 @@
         </is>
       </c>
       <c r="C178" t="n">
-        <v>1110.19</v>
+        <v>1110.49</v>
       </c>
       <c r="D178" t="n">
-        <v>1102.31</v>
+        <v>1102.61</v>
       </c>
       <c r="E178" t="n">
-        <v>1118.07</v>
+        <v>1118.36</v>
       </c>
       <c r="F178" t="n">
         <v>8045</v>
@@ -24202,13 +24202,13 @@
         </is>
       </c>
       <c r="C179" t="n">
-        <v>1108.36</v>
+        <v>1108.73</v>
       </c>
       <c r="D179" t="n">
-        <v>1099.07</v>
+        <v>1099.43</v>
       </c>
       <c r="E179" t="n">
-        <v>1117.66</v>
+        <v>1118.03</v>
       </c>
       <c r="F179" t="n">
         <v>8977</v>
@@ -24353,13 +24353,13 @@
         </is>
       </c>
       <c r="C180" t="n">
-        <v>1106.91</v>
+        <v>1107.17</v>
       </c>
       <c r="D180" t="n">
-        <v>1099.85</v>
+        <v>1100.12</v>
       </c>
       <c r="E180" t="n">
-        <v>1113.97</v>
+        <v>1114.23</v>
       </c>
       <c r="F180" t="n">
         <v>14148</v>
@@ -24504,13 +24504,13 @@
         </is>
       </c>
       <c r="C181" t="n">
-        <v>1090.98</v>
+        <v>1091.39</v>
       </c>
       <c r="D181" t="n">
-        <v>1079.47</v>
+        <v>1079.88</v>
       </c>
       <c r="E181" t="n">
-        <v>1102.49</v>
+        <v>1102.9</v>
       </c>
       <c r="F181" t="n">
         <v>4780</v>
@@ -24655,13 +24655,13 @@
         </is>
       </c>
       <c r="C182" t="n">
-        <v>1088.93</v>
+        <v>1089.31</v>
       </c>
       <c r="D182" t="n">
-        <v>1079.58</v>
+        <v>1079.96</v>
       </c>
       <c r="E182" t="n">
-        <v>1098.28</v>
+        <v>1098.66</v>
       </c>
       <c r="F182" t="n">
         <v>7597</v>
@@ -24806,13 +24806,13 @@
         </is>
       </c>
       <c r="C183" t="n">
-        <v>1073.26</v>
+        <v>1073.49</v>
       </c>
       <c r="D183" t="n">
-        <v>1062.07</v>
+        <v>1062.3</v>
       </c>
       <c r="E183" t="n">
-        <v>1084.44</v>
+        <v>1084.68</v>
       </c>
       <c r="F183" t="n">
         <v>6328</v>
@@ -24957,13 +24957,13 @@
         </is>
       </c>
       <c r="C184" t="n">
-        <v>1069.15</v>
+        <v>1069.49</v>
       </c>
       <c r="D184" t="n">
-        <v>1059.21</v>
+        <v>1059.55</v>
       </c>
       <c r="E184" t="n">
-        <v>1079.09</v>
+        <v>1079.43</v>
       </c>
       <c r="F184" t="n">
         <v>6965</v>
@@ -25108,13 +25108,13 @@
         </is>
       </c>
       <c r="C185" t="n">
-        <v>1066.32</v>
+        <v>1066.83</v>
       </c>
       <c r="D185" t="n">
-        <v>1054.81</v>
+        <v>1055.31</v>
       </c>
       <c r="E185" t="n">
-        <v>1077.84</v>
+        <v>1078.34</v>
       </c>
       <c r="F185" t="n">
         <v>5745</v>
@@ -25259,13 +25259,13 @@
         </is>
       </c>
       <c r="C186" t="n">
-        <v>1064.78</v>
+        <v>1065.21</v>
       </c>
       <c r="D186" t="n">
-        <v>1049.5</v>
+        <v>1049.93</v>
       </c>
       <c r="E186" t="n">
-        <v>1080.06</v>
+        <v>1080.49</v>
       </c>
       <c r="F186" t="n">
         <v>1743</v>
@@ -25410,13 +25410,13 @@
         </is>
       </c>
       <c r="C187" t="n">
-        <v>1060.62</v>
+        <v>1061.04</v>
       </c>
       <c r="D187" t="n">
-        <v>1048.6</v>
+        <v>1049.02</v>
       </c>
       <c r="E187" t="n">
-        <v>1072.65</v>
+        <v>1073.07</v>
       </c>
       <c r="F187" t="n">
         <v>3924</v>
@@ -25561,13 +25561,13 @@
         </is>
       </c>
       <c r="C188" t="n">
-        <v>1054.76</v>
+        <v>1055.11</v>
       </c>
       <c r="D188" t="n">
-        <v>1043.07</v>
+        <v>1043.43</v>
       </c>
       <c r="E188" t="n">
-        <v>1066.44</v>
+        <v>1066.8</v>
       </c>
       <c r="F188" t="n">
         <v>4658</v>
@@ -25712,13 +25712,13 @@
         </is>
       </c>
       <c r="C189" t="n">
-        <v>1040.07</v>
+        <v>1040.45</v>
       </c>
       <c r="D189" t="n">
-        <v>1028.63</v>
+        <v>1029.01</v>
       </c>
       <c r="E189" t="n">
-        <v>1051.51</v>
+        <v>1051.89</v>
       </c>
       <c r="F189" t="n">
         <v>4845</v>
@@ -25863,13 +25863,13 @@
         </is>
       </c>
       <c r="C190" t="n">
-        <v>1022.88</v>
+        <v>1023.23</v>
       </c>
       <c r="D190" t="n">
-        <v>1009.25</v>
+        <v>1009.6</v>
       </c>
       <c r="E190" t="n">
-        <v>1036.5</v>
+        <v>1036.86</v>
       </c>
       <c r="F190" t="n">
         <v>2658</v>
@@ -26014,13 +26014,13 @@
         </is>
       </c>
       <c r="C191" t="n">
-        <v>1020.84</v>
+        <v>1021.25</v>
       </c>
       <c r="D191" t="n">
-        <v>1009.91</v>
+        <v>1010.33</v>
       </c>
       <c r="E191" t="n">
-        <v>1031.76</v>
+        <v>1032.17</v>
       </c>
       <c r="F191" t="n">
         <v>6310</v>
@@ -26165,13 +26165,13 @@
         </is>
       </c>
       <c r="C192" t="n">
-        <v>994.266</v>
+        <v>994.593</v>
       </c>
       <c r="D192" t="n">
-        <v>981.649</v>
+        <v>981.975</v>
       </c>
       <c r="E192" t="n">
-        <v>1006.88</v>
+        <v>1007.21</v>
       </c>
       <c r="F192" t="n">
         <v>4914</v>
@@ -26316,13 +26316,13 @@
         </is>
       </c>
       <c r="C193" t="n">
-        <v>990.109</v>
+        <v>990.491</v>
       </c>
       <c r="D193" t="n">
-        <v>977.681</v>
+        <v>978.063</v>
       </c>
       <c r="E193" t="n">
-        <v>1002.54</v>
+        <v>1002.92</v>
       </c>
       <c r="F193" t="n">
         <v>4203</v>
@@ -26467,13 +26467,13 @@
         </is>
       </c>
       <c r="C194" t="n">
-        <v>978.933</v>
+        <v>979.4109999999999</v>
       </c>
       <c r="D194" t="n">
-        <v>965.332</v>
+        <v>965.8099999999999</v>
       </c>
       <c r="E194" t="n">
-        <v>992.533</v>
+        <v>993.0119999999999</v>
       </c>
       <c r="F194" t="n">
         <v>3412</v>
@@ -26618,13 +26618,13 @@
         </is>
       </c>
       <c r="C195" t="n">
-        <v>971.095</v>
+        <v>971.598</v>
       </c>
       <c r="D195" t="n">
-        <v>955.2</v>
+        <v>955.704</v>
       </c>
       <c r="E195" t="n">
-        <v>986.99</v>
+        <v>987.4930000000001</v>
       </c>
       <c r="F195" t="n">
         <v>2391</v>
@@ -26769,13 +26769,13 @@
         </is>
       </c>
       <c r="C196" t="n">
-        <v>951.327</v>
+        <v>951.675</v>
       </c>
       <c r="D196" t="n">
-        <v>938.522</v>
+        <v>938.871</v>
       </c>
       <c r="E196" t="n">
-        <v>964.1319999999999</v>
+        <v>964.479</v>
       </c>
       <c r="F196" t="n">
         <v>3287</v>
@@ -26994,7 +26994,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -27029,7 +27029,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -27064,7 +27064,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -27099,7 +27099,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -27134,7 +27134,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -27173,7 +27173,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -27208,7 +27208,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -27243,7 +27243,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -27278,7 +27278,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -27313,7 +27313,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -27348,7 +27348,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -27383,7 +27383,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -27418,7 +27418,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -27453,7 +27453,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -27488,7 +27488,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -27600,46 +27600,46 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>kimi-k2.5-thinking</t>
+          <t>gemma-4-31b</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1000</v>
+        <v>31</v>
       </c>
       <c r="C4" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>moe</t>
+          <t>dense</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>name_parsing</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>gemma-4-31b</t>
+          <t>kimi-k2.5-thinking</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>31</v>
+        <v>1000</v>
       </c>
       <c r="C5" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>dense</t>
+          <t>moe</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>override</t>
         </is>
       </c>
     </row>
@@ -27821,7 +27821,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>deepseek-v3.2-thinking</t>
+          <t>deepseek-v3.2-exp</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -27836,7 +27836,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>deepseek-v3.2-exp</t>
+          <t>deepseek-v3.2-thinking</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -27889,38 +27889,38 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>kimi-k2-0905-preview</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="C19" t="n">
-        <v>32</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+          <t>deepseek-v3.1</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>deepseek-v3.1</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
+          <t>kimi-k2-0905-preview</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C20" t="n">
+        <v>32</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>override</t>
         </is>
       </c>
     </row>
@@ -28064,18 +28064,18 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>qwen3-235b-a22b-no-thinking</t>
+          <t>qwen3.5-27b</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>235</v>
+        <v>27</v>
       </c>
       <c r="C28" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>moe</t>
+          <t>dense</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -28102,38 +28102,38 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>minimax-m2.5</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
+          <t>qwen3-235b-a22b-no-thinking</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>235</v>
+      </c>
+      <c r="C30" t="n">
+        <v>22</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>name_parsing</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>qwen3.5-27b</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>27</v>
-      </c>
-      <c r="C31" t="n">
-        <v>27</v>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>dense</t>
-        </is>
-      </c>
+          <t>minimax-m2.5</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -28232,14 +28232,14 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>qwen3.5-35b-a3b</t>
+          <t>qwen3-vl-235b-a22b-thinking</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>35</v>
+        <v>235</v>
       </c>
       <c r="C36" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -28255,14 +28255,14 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>qwen3-vl-235b-a22b-thinking</t>
+          <t>qwen3.5-35b-a3b</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>235</v>
+        <v>35</v>
       </c>
       <c r="C37" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -28301,7 +28301,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>mimo-v2-flash (non-thinking)</t>
+          <t>step-3.5-flash</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -28316,7 +28316,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>step-3.5-flash</t>
+          <t>mimo-v2-flash (non-thinking)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
@@ -28643,38 +28643,38 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>gpt-oss-120b</t>
-        </is>
-      </c>
-      <c r="B57" t="n">
-        <v>117</v>
-      </c>
-      <c r="C57" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+          <t>command-a-03-2025</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr"/>
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>command-a-03-2025</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr"/>
-      <c r="C58" t="inlineStr"/>
-      <c r="D58" t="inlineStr"/>
+          <t>gpt-oss-120b</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>117</v>
+      </c>
+      <c r="C58" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>override</t>
         </is>
       </c>
     </row>
@@ -28933,18 +28933,18 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>qwen3-30b-a3b</t>
+          <t>llama-3.3-nemotron-49b-super-v1</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="C71" t="n">
-        <v>3</v>
+        <v>49</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>moe</t>
+          <t>dense</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -28956,18 +28956,18 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>llama-3.3-nemotron-49b-super-v1</t>
+          <t>qwen3-30b-a3b</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="C72" t="n">
-        <v>49</v>
+        <v>3</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>dense</t>
+          <t>moe</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -29078,84 +29078,84 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>gemma-3n-e4b-it</t>
+          <t>llama-3.3-70b-instruct</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>8.4</v>
+        <v>70</v>
       </c>
       <c r="C78" t="n">
-        <v>4</v>
+        <v>70</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>moe</t>
+          <t>dense</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>aa_single_scrape</t>
+          <t>name_parsing</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>llama-3.3-70b-instruct</t>
+          <t>gemma-3n-e4b-it</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>70</v>
+        <v>8.4</v>
       </c>
       <c r="C79" t="n">
-        <v>70</v>
+        <v>4</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>dense</t>
+          <t>moe</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>aa_single_scrape</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>gpt-oss-20b</t>
-        </is>
-      </c>
-      <c r="B80" t="n">
-        <v>21</v>
-      </c>
-      <c r="C80" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+          <t>qwen-max-0919</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr"/>
+      <c r="C80" t="inlineStr"/>
+      <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>qwen-max-0919</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr"/>
-      <c r="C81" t="inlineStr"/>
-      <c r="D81" t="inlineStr"/>
+          <t>gpt-oss-20b</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>21</v>
+      </c>
+      <c r="C81" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>override</t>
         </is>
       </c>
     </row>
@@ -29307,14 +29307,14 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>gemma-3-4b-it</t>
+          <t>mistral-small-3.1-24b-instruct-2503</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="C89" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -29330,14 +29330,14 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>mistral-small-3.1-24b-instruct-2503</t>
+          <t>gemma-3-4b-it</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="C90" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -29506,14 +29506,14 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>olmo-3.1-32b-think</t>
+          <t>llama-3.1-nemotron-51b-instruct</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="C98" t="n">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -29529,14 +29529,14 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>llama-3.1-nemotron-51b-instruct</t>
+          <t>olmo-3.1-32b-think</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="C99" t="n">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -29759,38 +29759,38 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>command-r-plus</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr"/>
-      <c r="C109" t="inlineStr"/>
-      <c r="D109" t="inlineStr"/>
+          <t>qwen2-72b-instruct</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>72</v>
+      </c>
+      <c r="C109" t="n">
+        <v>72</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>dense</t>
+        </is>
+      </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>name_parsing</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>qwen2-72b-instruct</t>
-        </is>
-      </c>
-      <c r="B110" t="n">
-        <v>72</v>
-      </c>
-      <c r="C110" t="n">
-        <v>72</v>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>dense</t>
-        </is>
-      </c>
+          <t>command-r-plus</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr"/>
+      <c r="C110" t="inlineStr"/>
+      <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -29988,7 +29988,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>c4ai-aya-expanse-8b</t>
+          <t>llama-3-8b-instruct</t>
         </is>
       </c>
       <c r="B120" t="n">
@@ -30011,7 +30011,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>llama-3-8b-instruct</t>
+          <t>c4ai-aya-expanse-8b</t>
         </is>
       </c>
       <c r="B121" t="n">

--- a/arena_enrichment/output/arena_leaderboard_enriched.xlsx
+++ b/arena_enrichment/output/arena_leaderboard_enriched.xlsx
@@ -675,16 +675,16 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>1471.59</v>
+        <v>1468.84</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1464.55</v>
+        <v>1462.01</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1478.63</v>
+        <v>1475.66</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>7179</v>
+        <v>7927</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
@@ -746,16 +746,16 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>1456.03</v>
+        <v>1457.05</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1450.8</v>
+        <v>1451.88</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1461.27</v>
+        <v>1462.22</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>15839</v>
+        <v>16528</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
@@ -897,16 +897,16 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>1451.48</v>
+        <v>1451.35</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1443.81</v>
+        <v>1443.68</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1459.15</v>
+        <v>1459.01</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>5827</v>
+        <v>5822</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
@@ -1048,16 +1048,16 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>1450.89</v>
+        <v>1450.68</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1446.27</v>
+        <v>1446.1</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1455.52</v>
+        <v>1455.26</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>22439</v>
+        <v>23091</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
@@ -1199,16 +1199,16 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1445.9</v>
+        <v>1446.78</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1440.86</v>
+        <v>1441.83</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1450.94</v>
+        <v>1451.74</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>17212</v>
+        <v>17989</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
@@ -1350,16 +1350,16 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>1442.89</v>
+        <v>1442.83</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>1436.77</v>
+        <v>1436.7</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1449.01</v>
+        <v>1448.96</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>12149</v>
+        <v>12138</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
@@ -1421,16 +1421,16 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>1438.96</v>
+        <v>1438.95</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>1431.27</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1446.65</v>
+        <v>1446.64</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>5782</v>
+        <v>5780</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
@@ -1572,16 +1572,16 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>1432.48</v>
+        <v>1432.38</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1425.87</v>
+        <v>1425.76</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1439.1</v>
+        <v>1438.99</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>8217</v>
+        <v>8208</v>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
@@ -1723,16 +1723,16 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>1430.27</v>
+        <v>1430.17</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>1426.79</v>
+        <v>1426.7</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1433.76</v>
+        <v>1433.63</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>47731</v>
+        <v>48416</v>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
@@ -1874,16 +1874,16 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>1425.86</v>
+        <v>1425.87</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>1421.91</v>
+        <v>1421.92</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>1429.81</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>35734</v>
+        <v>35724</v>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
@@ -1945,16 +1945,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1424.58</v>
+        <v>1424.52</v>
       </c>
       <c r="D12" t="n">
-        <v>1418.02</v>
+        <v>1417.96</v>
       </c>
       <c r="E12" t="n">
-        <v>1431.13</v>
+        <v>1431.07</v>
       </c>
       <c r="F12" t="n">
-        <v>9078</v>
+        <v>9080</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -2016,16 +2016,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1424.21</v>
+        <v>1424.08</v>
       </c>
       <c r="D13" t="n">
-        <v>1420.47</v>
+        <v>1420.36</v>
       </c>
       <c r="E13" t="n">
-        <v>1427.96</v>
+        <v>1427.79</v>
       </c>
       <c r="F13" t="n">
-        <v>42815</v>
+        <v>43509</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -2087,16 +2087,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1423.5</v>
+        <v>1423.09</v>
       </c>
       <c r="D14" t="n">
-        <v>1420.72</v>
+        <v>1420.33</v>
       </c>
       <c r="E14" t="n">
-        <v>1426.28</v>
+        <v>1425.86</v>
       </c>
       <c r="F14" t="n">
-        <v>83341</v>
+        <v>84048</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -2238,16 +2238,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1423.15</v>
+        <v>1422.96</v>
       </c>
       <c r="D15" t="n">
-        <v>1416.74</v>
+        <v>1416.55</v>
       </c>
       <c r="E15" t="n">
-        <v>1429.57</v>
+        <v>1429.38</v>
       </c>
       <c r="F15" t="n">
-        <v>11952</v>
+        <v>11950</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -2305,20 +2305,20 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>deepseek-v3.2-thinking</t>
+          <t>deepseek-r1-0528</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1422.61</v>
+        <v>1421.88</v>
       </c>
       <c r="D16" t="n">
-        <v>1418.78</v>
+        <v>1416.22</v>
       </c>
       <c r="E16" t="n">
-        <v>1426.45</v>
+        <v>1427.54</v>
       </c>
       <c r="F16" t="n">
-        <v>37197</v>
+        <v>18479</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -2376,20 +2376,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>deepseek-r1-0528</t>
+          <t>deepseek-v3.2-thinking</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1421.98</v>
+        <v>1421.82</v>
       </c>
       <c r="D17" t="n">
-        <v>1416.33</v>
+        <v>1418.02</v>
       </c>
       <c r="E17" t="n">
-        <v>1427.64</v>
+        <v>1425.63</v>
       </c>
       <c r="F17" t="n">
-        <v>18480</v>
+        <v>37837</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -2451,16 +2451,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1418.4</v>
+        <v>1419.01</v>
       </c>
       <c r="D18" t="n">
-        <v>1413</v>
+        <v>1413.71</v>
       </c>
       <c r="E18" t="n">
-        <v>1423.8</v>
+        <v>1424.31</v>
       </c>
       <c r="F18" t="n">
-        <v>14023</v>
+        <v>14744</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -2598,68 +2598,148 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>deepseek-v3.1</t>
+          <t>kimi-k2-0905-preview</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1418.03</v>
+        <v>1417.83</v>
       </c>
       <c r="D19" t="n">
-        <v>1412.02</v>
+        <v>1411.33</v>
       </c>
       <c r="E19" t="n">
-        <v>1424.04</v>
+        <v>1424.32</v>
       </c>
       <c r="F19" t="n">
-        <v>14995</v>
+        <v>11805</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>DeepSeek</t>
+          <t>Moonshot</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+          <t>Modified MIT</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J19" t="n">
+        <v>32</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr"/>
-      <c r="W19" t="inlineStr"/>
-      <c r="X19" t="inlineStr"/>
-      <c r="Y19" t="inlineStr"/>
-      <c r="Z19" t="inlineStr"/>
-      <c r="AA19" t="inlineStr"/>
-      <c r="AB19" t="inlineStr"/>
-      <c r="AC19" t="inlineStr"/>
-      <c r="AD19" t="inlineStr"/>
-      <c r="AE19" t="inlineStr"/>
-      <c r="AF19" t="inlineStr"/>
-      <c r="AG19" t="inlineStr"/>
+          <t>override</t>
+        </is>
+      </c>
+      <c r="M19" t="n">
+        <v>2000</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2500</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1250</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>500</v>
+      </c>
+      <c r="R19" t="n">
+        <v>625</v>
+      </c>
+      <c r="S19" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T19" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U19" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V19" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W19" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X19" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y19" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z19" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA19" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AB19" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AC19" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD19" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE19" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF19" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AG19" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
     </row>
@@ -2669,148 +2749,68 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>kimi-k2-0905-preview</t>
+          <t>deepseek-v3.1</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1417.87</v>
+        <v>1417.76</v>
       </c>
       <c r="D20" t="n">
-        <v>1411.38</v>
+        <v>1411.75</v>
       </c>
       <c r="E20" t="n">
-        <v>1424.36</v>
+        <v>1423.77</v>
       </c>
       <c r="F20" t="n">
-        <v>11805</v>
+        <v>14989</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Moonshot</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Modified MIT</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J20" t="n">
-        <v>32</v>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>override</t>
-        </is>
-      </c>
-      <c r="M20" t="n">
-        <v>2000</v>
-      </c>
-      <c r="N20" t="n">
-        <v>2500</v>
-      </c>
-      <c r="O20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="P20" t="n">
-        <v>1250</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>500</v>
-      </c>
-      <c r="R20" t="n">
-        <v>625</v>
-      </c>
-      <c r="S20" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T20" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U20" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="V20" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W20" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X20" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Y20" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z20" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AA20" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AB20" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AC20" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AD20" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AE20" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AF20" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AG20" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr"/>
+      <c r="AB20" t="inlineStr"/>
+      <c r="AC20" t="inlineStr"/>
+      <c r="AD20" t="inlineStr"/>
+      <c r="AE20" t="inlineStr"/>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="inlineStr"/>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -2824,16 +2824,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1417.4</v>
+        <v>1417.29</v>
       </c>
       <c r="D21" t="n">
-        <v>1412.55</v>
+        <v>1412.44</v>
       </c>
       <c r="E21" t="n">
-        <v>1422.26</v>
+        <v>1422.15</v>
       </c>
       <c r="F21" t="n">
-        <v>27669</v>
+        <v>27662</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -2975,16 +2975,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1417.09</v>
+        <v>1416.92</v>
       </c>
       <c r="D22" t="n">
-        <v>1410.48</v>
+        <v>1410.31</v>
       </c>
       <c r="E22" t="n">
-        <v>1423.7</v>
+        <v>1423.53</v>
       </c>
       <c r="F22" t="n">
-        <v>11762</v>
+        <v>11761</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -3046,16 +3046,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1416.95</v>
+        <v>1416.9</v>
       </c>
       <c r="D23" t="n">
-        <v>1406.99</v>
+        <v>1406.93</v>
       </c>
       <c r="E23" t="n">
-        <v>1426.92</v>
+        <v>1426.86</v>
       </c>
       <c r="F23" t="n">
-        <v>3475</v>
+        <v>3473</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -3117,13 +3117,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1416.06</v>
+        <v>1415.96</v>
       </c>
       <c r="D24" t="n">
-        <v>1406.45</v>
+        <v>1406.35</v>
       </c>
       <c r="E24" t="n">
-        <v>1425.67</v>
+        <v>1425.57</v>
       </c>
       <c r="F24" t="n">
         <v>3713</v>
@@ -3188,16 +3188,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1415.89</v>
+        <v>1415.78</v>
       </c>
       <c r="D25" t="n">
-        <v>1409.4</v>
+        <v>1409.29</v>
       </c>
       <c r="E25" t="n">
-        <v>1422.37</v>
+        <v>1422.26</v>
       </c>
       <c r="F25" t="n">
-        <v>11533</v>
+        <v>11536</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -3339,16 +3339,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1415.41</v>
+        <v>1415.04</v>
       </c>
       <c r="D26" t="n">
-        <v>1411.69</v>
+        <v>1411.34</v>
       </c>
       <c r="E26" t="n">
-        <v>1419.13</v>
+        <v>1418.73</v>
       </c>
       <c r="F26" t="n">
-        <v>40077</v>
+        <v>40823</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -3490,13 +3490,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1411.16</v>
+        <v>1411.07</v>
       </c>
       <c r="D27" t="n">
-        <v>1406.28</v>
+        <v>1406.19</v>
       </c>
       <c r="E27" t="n">
-        <v>1416.04</v>
+        <v>1415.95</v>
       </c>
       <c r="F27" t="n">
         <v>24356</v>
@@ -3641,16 +3641,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1403.43</v>
+        <v>1404.03</v>
       </c>
       <c r="D28" t="n">
-        <v>1397.96</v>
+        <v>1398.68</v>
       </c>
       <c r="E28" t="n">
-        <v>1408.89</v>
+        <v>1409.38</v>
       </c>
       <c r="F28" t="n">
-        <v>13687</v>
+        <v>14416</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -3788,68 +3788,148 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>minimax-m2.7</t>
+          <t>qwen3-235b-a22b-no-thinking</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1403.24</v>
+        <v>1403.06</v>
       </c>
       <c r="D29" t="n">
-        <v>1396.48</v>
+        <v>1398.56</v>
       </c>
       <c r="E29" t="n">
-        <v>1409.99</v>
+        <v>1407.55</v>
       </c>
       <c r="F29" t="n">
-        <v>8484</v>
+        <v>38249</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>MiniMax</t>
+          <t>Alibaba</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Modified MIT</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
+          <t>Apache 2.0</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>235</v>
+      </c>
+      <c r="J29" t="n">
+        <v>22</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr"/>
-      <c r="S29" t="inlineStr"/>
-      <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr"/>
-      <c r="V29" t="inlineStr"/>
-      <c r="W29" t="inlineStr"/>
-      <c r="X29" t="inlineStr"/>
-      <c r="Y29" t="inlineStr"/>
-      <c r="Z29" t="inlineStr"/>
-      <c r="AA29" t="inlineStr"/>
-      <c r="AB29" t="inlineStr"/>
-      <c r="AC29" t="inlineStr"/>
-      <c r="AD29" t="inlineStr"/>
-      <c r="AE29" t="inlineStr"/>
-      <c r="AF29" t="inlineStr"/>
-      <c r="AG29" t="inlineStr"/>
+          <t>name_parsing</t>
+        </is>
+      </c>
+      <c r="M29" t="n">
+        <v>470</v>
+      </c>
+      <c r="N29" t="n">
+        <v>587.5</v>
+      </c>
+      <c r="O29" t="n">
+        <v>235</v>
+      </c>
+      <c r="P29" t="n">
+        <v>293.8</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>117.5</v>
+      </c>
+      <c r="R29" t="n">
+        <v>146.9</v>
+      </c>
+      <c r="S29" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T29" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U29" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V29" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W29" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X29" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y29" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z29" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA29" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AB29" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AC29" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD29" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE29" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF29" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AG29" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
     </row>
@@ -3859,148 +3939,68 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>qwen3-235b-a22b-no-thinking</t>
+          <t>minimax-m2.7</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1403.21</v>
+        <v>1402.86</v>
       </c>
       <c r="D30" t="n">
-        <v>1398.72</v>
+        <v>1396.32</v>
       </c>
       <c r="E30" t="n">
-        <v>1407.71</v>
+        <v>1409.41</v>
       </c>
       <c r="F30" t="n">
-        <v>38253</v>
+        <v>9172</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alibaba</t>
+          <t>MiniMax</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
-        </is>
-      </c>
-      <c r="I30" t="n">
-        <v>235</v>
-      </c>
-      <c r="J30" t="n">
-        <v>22</v>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+          <t>Modified MIT</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
-          <t>name_parsing</t>
-        </is>
-      </c>
-      <c r="M30" t="n">
-        <v>470</v>
-      </c>
-      <c r="N30" t="n">
-        <v>587.5</v>
-      </c>
-      <c r="O30" t="n">
-        <v>235</v>
-      </c>
-      <c r="P30" t="n">
-        <v>293.8</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>117.5</v>
-      </c>
-      <c r="R30" t="n">
-        <v>146.9</v>
-      </c>
-      <c r="S30" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T30" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U30" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="V30" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W30" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X30" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Y30" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z30" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AA30" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AB30" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AC30" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AD30" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AE30" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AF30" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AG30" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr"/>
+      <c r="AB30" t="inlineStr"/>
+      <c r="AC30" t="inlineStr"/>
+      <c r="AD30" t="inlineStr"/>
+      <c r="AE30" t="inlineStr"/>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="inlineStr"/>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -4010,68 +4010,148 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>minimax-m2.5</t>
+          <t>qwen3-next-80b-a3b-instruct</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1403.02</v>
+        <v>1401.65</v>
       </c>
       <c r="D31" t="n">
-        <v>1398.11</v>
+        <v>1396.87</v>
       </c>
       <c r="E31" t="n">
-        <v>1407.93</v>
+        <v>1406.43</v>
       </c>
       <c r="F31" t="n">
-        <v>19156</v>
+        <v>22912</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>MiniMax</t>
+          <t>Alibaba</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Modified MIT</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
+          <t>Apache 2.0</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>80</v>
+      </c>
+      <c r="J31" t="n">
+        <v>3</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr"/>
-      <c r="R31" t="inlineStr"/>
-      <c r="S31" t="inlineStr"/>
-      <c r="T31" t="inlineStr"/>
-      <c r="U31" t="inlineStr"/>
-      <c r="V31" t="inlineStr"/>
-      <c r="W31" t="inlineStr"/>
-      <c r="X31" t="inlineStr"/>
-      <c r="Y31" t="inlineStr"/>
-      <c r="Z31" t="inlineStr"/>
-      <c r="AA31" t="inlineStr"/>
-      <c r="AB31" t="inlineStr"/>
-      <c r="AC31" t="inlineStr"/>
-      <c r="AD31" t="inlineStr"/>
-      <c r="AE31" t="inlineStr"/>
-      <c r="AF31" t="inlineStr"/>
-      <c r="AG31" t="inlineStr"/>
+          <t>name_parsing</t>
+        </is>
+      </c>
+      <c r="M31" t="n">
+        <v>160</v>
+      </c>
+      <c r="N31" t="n">
+        <v>200</v>
+      </c>
+      <c r="O31" t="n">
+        <v>80</v>
+      </c>
+      <c r="P31" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>40</v>
+      </c>
+      <c r="R31" t="n">
+        <v>50</v>
+      </c>
+      <c r="S31" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T31" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U31" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V31" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W31" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X31" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y31" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z31" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AA31" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB31" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AC31" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AD31" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE31" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AF31" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AG31" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>B300 SXM</t>
         </is>
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>H200 SXM</t>
         </is>
       </c>
     </row>
@@ -4081,36 +4161,36 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>qwen3-next-80b-a3b-instruct</t>
+          <t>longcat-flash-chat</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1401.85</v>
+        <v>1401.26</v>
       </c>
       <c r="D32" t="n">
-        <v>1397.07</v>
+        <v>1394.89</v>
       </c>
       <c r="E32" t="n">
-        <v>1406.63</v>
+        <v>1407.63</v>
       </c>
       <c r="F32" t="n">
-        <v>22909</v>
+        <v>11420</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alibaba</t>
+          <t>Meituan</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>80</v>
+        <v>560</v>
       </c>
       <c r="J32" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -4119,26 +4199,26 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>override</t>
         </is>
       </c>
       <c r="M32" t="n">
-        <v>160</v>
+        <v>1120</v>
       </c>
       <c r="N32" t="n">
-        <v>200</v>
+        <v>1400</v>
       </c>
       <c r="O32" t="n">
-        <v>80</v>
+        <v>560</v>
       </c>
       <c r="P32" t="n">
-        <v>100</v>
+        <v>700</v>
       </c>
       <c r="Q32" t="n">
-        <v>40</v>
+        <v>280</v>
       </c>
       <c r="R32" t="n">
-        <v>50</v>
+        <v>350</v>
       </c>
       <c r="S32" s="5" t="inlineStr">
         <is>
@@ -4150,9 +4230,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="U32" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="U32" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="V32" s="5" t="inlineStr">
@@ -4165,9 +4245,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="X32" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="X32" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="Y32" s="5" t="inlineStr">
@@ -4175,14 +4255,14 @@
           <t>No</t>
         </is>
       </c>
-      <c r="Z32" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AA32" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="Z32" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA32" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AB32" s="5" t="inlineStr">
@@ -4190,39 +4270,39 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AC32" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AD32" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AE32" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AF32" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AG32" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AC32" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD32" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE32" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF32" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AG32" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>B300 SXM</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>H200 SXM</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
     </row>
@@ -4232,148 +4312,68 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>longcat-flash-chat</t>
+          <t>minimax-m2.5</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1401.52</v>
+        <v>1401.01</v>
       </c>
       <c r="D33" t="n">
-        <v>1395.15</v>
+        <v>1396.17</v>
       </c>
       <c r="E33" t="n">
-        <v>1407.89</v>
+        <v>1405.86</v>
       </c>
       <c r="F33" t="n">
-        <v>11418</v>
+        <v>19891</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Meituan</t>
+          <t>MiniMax</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="I33" t="n">
-        <v>560</v>
-      </c>
-      <c r="J33" t="n">
-        <v>27</v>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+          <t>Modified MIT</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
-          <t>override</t>
-        </is>
-      </c>
-      <c r="M33" t="n">
-        <v>1120</v>
-      </c>
-      <c r="N33" t="n">
-        <v>1400</v>
-      </c>
-      <c r="O33" t="n">
-        <v>560</v>
-      </c>
-      <c r="P33" t="n">
-        <v>700</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>280</v>
-      </c>
-      <c r="R33" t="n">
-        <v>350</v>
-      </c>
-      <c r="S33" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T33" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U33" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="V33" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W33" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X33" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Y33" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z33" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AA33" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AB33" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AC33" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AD33" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AE33" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AF33" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AG33" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr"/>
+      <c r="W33" t="inlineStr"/>
+      <c r="X33" t="inlineStr"/>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr"/>
+      <c r="AA33" t="inlineStr"/>
+      <c r="AB33" t="inlineStr"/>
+      <c r="AC33" t="inlineStr"/>
+      <c r="AD33" t="inlineStr"/>
+      <c r="AE33" t="inlineStr"/>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="inlineStr"/>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -4387,16 +4387,16 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1399.73</v>
+        <v>1399.45</v>
       </c>
       <c r="D34" t="n">
-        <v>1393.21</v>
+        <v>1392.92</v>
       </c>
       <c r="E34" t="n">
-        <v>1406.26</v>
+        <v>1405.98</v>
       </c>
       <c r="F34" t="n">
-        <v>9013</v>
+        <v>9008</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -4538,13 +4538,13 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1397.8</v>
+        <v>1397.7</v>
       </c>
       <c r="D35" t="n">
-        <v>1392.94</v>
+        <v>1392.84</v>
       </c>
       <c r="E35" t="n">
-        <v>1402.66</v>
+        <v>1402.56</v>
       </c>
       <c r="F35" t="n">
         <v>18524</v>
@@ -4689,13 +4689,13 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1395.89</v>
+        <v>1395.84</v>
       </c>
       <c r="D36" t="n">
-        <v>1389.1</v>
+        <v>1389.05</v>
       </c>
       <c r="E36" t="n">
-        <v>1402.67</v>
+        <v>1402.62</v>
       </c>
       <c r="F36" t="n">
         <v>7960</v>
@@ -4840,16 +4840,16 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1395.86</v>
+        <v>1395.63</v>
       </c>
       <c r="D37" t="n">
-        <v>1390.48</v>
+        <v>1390.37</v>
       </c>
       <c r="E37" t="n">
-        <v>1401.23</v>
+        <v>1400.9</v>
       </c>
       <c r="F37" t="n">
-        <v>14275</v>
+        <v>15041</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -4991,16 +4991,16 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1395.24</v>
+        <v>1395.07</v>
       </c>
       <c r="D38" t="n">
-        <v>1391.38</v>
+        <v>1391.21</v>
       </c>
       <c r="E38" t="n">
-        <v>1399.1</v>
+        <v>1398.93</v>
       </c>
       <c r="F38" t="n">
-        <v>45555</v>
+        <v>45547</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -5142,16 +5142,16 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1392.41</v>
+        <v>1392.72</v>
       </c>
       <c r="D39" t="n">
-        <v>1387.65</v>
+        <v>1388.02</v>
       </c>
       <c r="E39" t="n">
-        <v>1397.17</v>
+        <v>1397.42</v>
       </c>
       <c r="F39" t="n">
-        <v>20186</v>
+        <v>20897</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -5213,16 +5213,16 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1392.12</v>
+        <v>1392.65</v>
       </c>
       <c r="D40" t="n">
-        <v>1388.1</v>
+        <v>1388.66</v>
       </c>
       <c r="E40" t="n">
-        <v>1396.14</v>
+        <v>1396.63</v>
       </c>
       <c r="F40" t="n">
-        <v>31981</v>
+        <v>32693</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -5284,16 +5284,16 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1387.49</v>
+        <v>1387.39</v>
       </c>
       <c r="D41" t="n">
-        <v>1382.54</v>
+        <v>1382.45</v>
       </c>
       <c r="E41" t="n">
-        <v>1392.44</v>
+        <v>1392.34</v>
       </c>
       <c r="F41" t="n">
-        <v>25768</v>
+        <v>25766</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -5435,16 +5435,16 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1387.35</v>
+        <v>1387.38</v>
       </c>
       <c r="D42" t="n">
-        <v>1381.07</v>
+        <v>1381.1</v>
       </c>
       <c r="E42" t="n">
-        <v>1393.63</v>
+        <v>1393.66</v>
       </c>
       <c r="F42" t="n">
-        <v>10994</v>
+        <v>10983</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -5506,16 +5506,16 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1385.49</v>
+        <v>1385.5</v>
       </c>
       <c r="D43" t="n">
-        <v>1380.23</v>
+        <v>1380.24</v>
       </c>
       <c r="E43" t="n">
-        <v>1390.75</v>
+        <v>1390.76</v>
       </c>
       <c r="F43" t="n">
-        <v>17175</v>
+        <v>17159</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -5577,16 +5577,16 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1383.63</v>
+        <v>1383.47</v>
       </c>
       <c r="D44" t="n">
-        <v>1378.75</v>
+        <v>1378.6</v>
       </c>
       <c r="E44" t="n">
-        <v>1388.51</v>
+        <v>1388.35</v>
       </c>
       <c r="F44" t="n">
-        <v>23783</v>
+        <v>23776</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -5728,16 +5728,16 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1377.51</v>
+        <v>1377.55</v>
       </c>
       <c r="D45" t="n">
-        <v>1366.22</v>
+        <v>1366.26</v>
       </c>
       <c r="E45" t="n">
-        <v>1388.8</v>
+        <v>1388.84</v>
       </c>
       <c r="F45" t="n">
-        <v>2807</v>
+        <v>2805</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -5799,16 +5799,16 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1375.5</v>
+        <v>1375.72</v>
       </c>
       <c r="D46" t="n">
-        <v>1370.1</v>
+        <v>1370.41</v>
       </c>
       <c r="E46" t="n">
-        <v>1380.9</v>
+        <v>1381.02</v>
       </c>
       <c r="F46" t="n">
-        <v>15015</v>
+        <v>15782</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -5950,16 +5950,16 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1374.83</v>
+        <v>1374.69</v>
       </c>
       <c r="D47" t="n">
-        <v>1370.14</v>
+        <v>1370.01</v>
       </c>
       <c r="E47" t="n">
-        <v>1379.52</v>
+        <v>1379.38</v>
       </c>
       <c r="F47" t="n">
-        <v>26285</v>
+        <v>26284</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -6101,16 +6101,16 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1373.18</v>
+        <v>1372.98</v>
       </c>
       <c r="D48" t="n">
-        <v>1368.94</v>
+        <v>1368.73</v>
       </c>
       <c r="E48" t="n">
-        <v>1377.43</v>
+        <v>1377.22</v>
       </c>
       <c r="F48" t="n">
-        <v>31149</v>
+        <v>31139</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -6172,16 +6172,16 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1369.29</v>
+        <v>1369.32</v>
       </c>
       <c r="D49" t="n">
-        <v>1363.45</v>
+        <v>1363.48</v>
       </c>
       <c r="E49" t="n">
-        <v>1375.13</v>
+        <v>1375.16</v>
       </c>
       <c r="F49" t="n">
-        <v>13717</v>
+        <v>13715</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -6323,16 +6323,16 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1368.03</v>
+        <v>1367.95</v>
       </c>
       <c r="D50" t="n">
-        <v>1362.2</v>
+        <v>1362.12</v>
       </c>
       <c r="E50" t="n">
-        <v>1373.87</v>
+        <v>1373.78</v>
       </c>
       <c r="F50" t="n">
-        <v>11778</v>
+        <v>11771</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -6394,13 +6394,13 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1365.58</v>
+        <v>1365.59</v>
       </c>
       <c r="D51" t="n">
-        <v>1361.92</v>
+        <v>1361.93</v>
       </c>
       <c r="E51" t="n">
-        <v>1369.24</v>
+        <v>1369.26</v>
       </c>
       <c r="F51" t="n">
         <v>47584</v>
@@ -6545,16 +6545,16 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1363.63</v>
+        <v>1363.46</v>
       </c>
       <c r="D52" t="n">
-        <v>1359.37</v>
+        <v>1359.2</v>
       </c>
       <c r="E52" t="n">
-        <v>1367.9</v>
+        <v>1367.73</v>
       </c>
       <c r="F52" t="n">
-        <v>35260</v>
+        <v>35265</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -6616,16 +6616,16 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1361.33</v>
+        <v>1361.16</v>
       </c>
       <c r="D53" t="n">
-        <v>1354.06</v>
+        <v>1353.89</v>
       </c>
       <c r="E53" t="n">
-        <v>1368.61</v>
+        <v>1368.43</v>
       </c>
       <c r="F53" t="n">
-        <v>7413</v>
+        <v>7410</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1358.4</v>
+        <v>1358.3</v>
       </c>
       <c r="D54" t="n">
-        <v>1353.68</v>
+        <v>1353.58</v>
       </c>
       <c r="E54" t="n">
-        <v>1363.12</v>
+        <v>1363.02</v>
       </c>
       <c r="F54" t="n">
         <v>21770</v>
@@ -6918,16 +6918,16 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1357.28</v>
+        <v>1357.22</v>
       </c>
       <c r="D55" t="n">
-        <v>1352.08</v>
+        <v>1352.02</v>
       </c>
       <c r="E55" t="n">
-        <v>1362.48</v>
+        <v>1362.42</v>
       </c>
       <c r="F55" t="n">
-        <v>17729</v>
+        <v>17725</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -6989,13 +6989,13 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1356.9</v>
+        <v>1356.75</v>
       </c>
       <c r="D56" t="n">
-        <v>1348.54</v>
+        <v>1348.39</v>
       </c>
       <c r="E56" t="n">
-        <v>1365.27</v>
+        <v>1365.11</v>
       </c>
       <c r="F56" t="n">
         <v>5337</v>
@@ -7140,16 +7140,16 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1353.62</v>
+        <v>1353.56</v>
       </c>
       <c r="D57" t="n">
-        <v>1350.18</v>
+        <v>1350.13</v>
       </c>
       <c r="E57" t="n">
-        <v>1357.06</v>
+        <v>1357</v>
       </c>
       <c r="F57" t="n">
-        <v>56351</v>
+        <v>56352</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -7211,16 +7211,16 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1353.37</v>
+        <v>1353.33</v>
       </c>
       <c r="D58" t="n">
-        <v>1349.02</v>
+        <v>1348.98</v>
       </c>
       <c r="E58" t="n">
-        <v>1357.72</v>
+        <v>1357.68</v>
       </c>
       <c r="F58" t="n">
-        <v>30675</v>
+        <v>30681</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -7362,16 +7362,16 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1353.25</v>
+        <v>1353.18</v>
       </c>
       <c r="D59" t="n">
-        <v>1344.91</v>
+        <v>1344.84</v>
       </c>
       <c r="E59" t="n">
-        <v>1361.59</v>
+        <v>1361.53</v>
       </c>
       <c r="F59" t="n">
-        <v>4969</v>
+        <v>4966</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -7433,16 +7433,16 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1347.85</v>
+        <v>1347.74</v>
       </c>
       <c r="D60" t="n">
-        <v>1340.46</v>
+        <v>1340.34</v>
       </c>
       <c r="E60" t="n">
-        <v>1355.25</v>
+        <v>1355.14</v>
       </c>
       <c r="F60" t="n">
-        <v>6555</v>
+        <v>6560</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -7504,13 +7504,13 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1347.26</v>
+        <v>1347.12</v>
       </c>
       <c r="D61" t="n">
-        <v>1337.8</v>
+        <v>1337.66</v>
       </c>
       <c r="E61" t="n">
-        <v>1356.72</v>
+        <v>1356.58</v>
       </c>
       <c r="F61" t="n">
         <v>3926</v>
@@ -7655,13 +7655,13 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1347.15</v>
+        <v>1347.05</v>
       </c>
       <c r="D62" t="n">
-        <v>1335.45</v>
+        <v>1335.35</v>
       </c>
       <c r="E62" t="n">
-        <v>1358.85</v>
+        <v>1358.74</v>
       </c>
       <c r="F62" t="n">
         <v>2549</v>
@@ -7806,16 +7806,16 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1346.34</v>
+        <v>1346.2</v>
       </c>
       <c r="D63" t="n">
-        <v>1338.6</v>
+        <v>1338.46</v>
       </c>
       <c r="E63" t="n">
-        <v>1354.09</v>
+        <v>1353.94</v>
       </c>
       <c r="F63" t="n">
-        <v>6875</v>
+        <v>6877</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -7957,16 +7957,16 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1346.18</v>
+        <v>1346.01</v>
       </c>
       <c r="D64" t="n">
-        <v>1338.92</v>
+        <v>1338.75</v>
       </c>
       <c r="E64" t="n">
-        <v>1353.44</v>
+        <v>1353.27</v>
       </c>
       <c r="F64" t="n">
-        <v>7017</v>
+        <v>7019</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -8028,16 +8028,16 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1342.95</v>
+        <v>1342.87</v>
       </c>
       <c r="D65" t="n">
-        <v>1332.98</v>
+        <v>1332.9</v>
       </c>
       <c r="E65" t="n">
-        <v>1352.92</v>
+        <v>1352.85</v>
       </c>
       <c r="F65" t="n">
-        <v>3347</v>
+        <v>3346</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -8179,13 +8179,13 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1341.69</v>
+        <v>1341.67</v>
       </c>
       <c r="D66" t="n">
-        <v>1332.17</v>
+        <v>1332.16</v>
       </c>
       <c r="E66" t="n">
-        <v>1351.2</v>
+        <v>1351.18</v>
       </c>
       <c r="F66" t="n">
         <v>3829</v>
@@ -8330,16 +8330,16 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1336.09</v>
+        <v>1335.93</v>
       </c>
       <c r="D67" t="n">
-        <v>1331.66</v>
+        <v>1331.51</v>
       </c>
       <c r="E67" t="n">
-        <v>1340.52</v>
+        <v>1340.36</v>
       </c>
       <c r="F67" t="n">
-        <v>25412</v>
+        <v>25411</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -8481,13 +8481,13 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1334.54</v>
+        <v>1334.55</v>
       </c>
       <c r="D68" t="n">
-        <v>1330.86</v>
+        <v>1330.87</v>
       </c>
       <c r="E68" t="n">
-        <v>1338.22</v>
+        <v>1338.23</v>
       </c>
       <c r="F68" t="n">
         <v>41375</v>
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1332.73</v>
+        <v>1332.74</v>
       </c>
       <c r="D69" t="n">
-        <v>1329.16</v>
+        <v>1329.17</v>
       </c>
       <c r="E69" t="n">
-        <v>1336.3</v>
+        <v>1336.31</v>
       </c>
       <c r="F69" t="n">
         <v>59656</v>
@@ -8783,16 +8783,16 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1330.8</v>
+        <v>1330.65</v>
       </c>
       <c r="D70" t="n">
-        <v>1324.69</v>
+        <v>1324.54</v>
       </c>
       <c r="E70" t="n">
-        <v>1336.9</v>
+        <v>1336.76</v>
       </c>
       <c r="F70" t="n">
-        <v>12244</v>
+        <v>12241</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -8934,13 +8934,13 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1327.67</v>
+        <v>1327.55</v>
       </c>
       <c r="D71" t="n">
-        <v>1315.5</v>
+        <v>1315.38</v>
       </c>
       <c r="E71" t="n">
-        <v>1339.84</v>
+        <v>1339.71</v>
       </c>
       <c r="F71" t="n">
         <v>2218</v>
@@ -9081,24 +9081,24 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>qwen3-30b-a3b</t>
+          <t>molmo-2-8b</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1327.52</v>
+        <v>1327.4</v>
       </c>
       <c r="D72" t="n">
-        <v>1322.79</v>
+        <v>1305.98</v>
       </c>
       <c r="E72" t="n">
-        <v>1332.24</v>
+        <v>1348.81</v>
       </c>
       <c r="F72" t="n">
-        <v>26510</v>
+        <v>804</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alibaba</t>
+          <t>Ai2</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -9107,14 +9107,14 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="J72" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>moe</t>
+          <t>dense</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -9123,22 +9123,22 @@
         </is>
       </c>
       <c r="M72" t="n">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="N72" t="n">
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="O72" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="P72" t="n">
-        <v>37.5</v>
+        <v>10</v>
       </c>
       <c r="Q72" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="R72" t="n">
-        <v>18.8</v>
+        <v>5</v>
       </c>
       <c r="S72" s="6" t="inlineStr">
         <is>
@@ -9232,24 +9232,24 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>molmo-2-8b</t>
+          <t>qwen3-30b-a3b</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1327.44</v>
+        <v>1327.32</v>
       </c>
       <c r="D73" t="n">
-        <v>1306.02</v>
+        <v>1322.6</v>
       </c>
       <c r="E73" t="n">
-        <v>1348.86</v>
+        <v>1332.05</v>
       </c>
       <c r="F73" t="n">
-        <v>804</v>
+        <v>26510</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Ai2</t>
+          <t>Alibaba</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -9258,14 +9258,14 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="J73" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>dense</t>
+          <t>moe</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -9274,22 +9274,22 @@
         </is>
       </c>
       <c r="M73" t="n">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="N73" t="n">
-        <v>20</v>
+        <v>75</v>
       </c>
       <c r="O73" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="P73" t="n">
-        <v>10</v>
+        <v>37.5</v>
       </c>
       <c r="Q73" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="R73" t="n">
-        <v>5</v>
+        <v>18.8</v>
       </c>
       <c r="S73" s="6" t="inlineStr">
         <is>
@@ -9387,16 +9387,16 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1326.84</v>
+        <v>1326.95</v>
       </c>
       <c r="D74" t="n">
-        <v>1322.6</v>
+        <v>1322.71</v>
       </c>
       <c r="E74" t="n">
-        <v>1331.08</v>
+        <v>1331.2</v>
       </c>
       <c r="F74" t="n">
-        <v>40010</v>
+        <v>40009</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -9538,13 +9538,13 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>1323.32</v>
+        <v>1323.21</v>
       </c>
       <c r="D75" t="n">
-        <v>1315.06</v>
+        <v>1314.95</v>
       </c>
       <c r="E75" t="n">
-        <v>1331.58</v>
+        <v>1331.48</v>
       </c>
       <c r="F75" t="n">
         <v>6795</v>
@@ -9609,16 +9609,16 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>1322.42</v>
+        <v>1322.33</v>
       </c>
       <c r="D76" t="n">
-        <v>1317.72</v>
+        <v>1317.62</v>
       </c>
       <c r="E76" t="n">
-        <v>1327.12</v>
+        <v>1327.03</v>
       </c>
       <c r="F76" t="n">
-        <v>30316</v>
+        <v>30321</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -9760,13 +9760,13 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1320.86</v>
+        <v>1320.63</v>
       </c>
       <c r="D77" t="n">
-        <v>1313.65</v>
+        <v>1313.41</v>
       </c>
       <c r="E77" t="n">
-        <v>1328.08</v>
+        <v>1327.84</v>
       </c>
       <c r="F77" t="n">
         <v>7157</v>
@@ -9827,68 +9827,68 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>llama-3.3-70b-instruct</t>
+          <t>gemma-3n-e4b-it</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1318.11</v>
+        <v>1318.09</v>
       </c>
       <c r="D78" t="n">
-        <v>1314.67</v>
+        <v>1312.95</v>
       </c>
       <c r="E78" t="n">
-        <v>1321.55</v>
+        <v>1323.23</v>
       </c>
       <c r="F78" t="n">
-        <v>54757</v>
+        <v>22621</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Llama-3.3</t>
+          <t>Gemma</t>
         </is>
       </c>
       <c r="I78" t="n">
-        <v>70</v>
+        <v>8.4</v>
       </c>
       <c r="J78" t="n">
-        <v>70</v>
+        <v>4</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>dense</t>
+          <t>moe</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>aa_single_scrape</t>
         </is>
       </c>
       <c r="M78" t="n">
-        <v>140</v>
+        <v>16.8</v>
       </c>
       <c r="N78" t="n">
-        <v>175</v>
+        <v>21</v>
       </c>
       <c r="O78" t="n">
-        <v>70</v>
+        <v>8.4</v>
       </c>
       <c r="P78" t="n">
-        <v>87.5</v>
+        <v>10.5</v>
       </c>
       <c r="Q78" t="n">
-        <v>35</v>
+        <v>4.2</v>
       </c>
       <c r="R78" t="n">
-        <v>43.8</v>
-      </c>
-      <c r="S78" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+        <v>5.2</v>
+      </c>
+      <c r="S78" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="T78" s="6" t="inlineStr">
@@ -9901,14 +9901,14 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="V78" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W78" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="V78" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W78" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="X78" s="6" t="inlineStr">
@@ -9916,9 +9916,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="Y78" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="Y78" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Z78" s="6" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="AH78" t="inlineStr">
         <is>
-          <t>B200 SXM</t>
+          <t>H100 SXM</t>
         </is>
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>RTX PRO 6000</t>
+          <t>H100 SXM</t>
         </is>
       </c>
     </row>
@@ -9978,68 +9978,68 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>gemma-3n-e4b-it</t>
+          <t>llama-3.3-70b-instruct</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>1318.1</v>
+        <v>1318.09</v>
       </c>
       <c r="D79" t="n">
-        <v>1312.96</v>
+        <v>1314.65</v>
       </c>
       <c r="E79" t="n">
-        <v>1323.25</v>
+        <v>1321.53</v>
       </c>
       <c r="F79" t="n">
-        <v>22620</v>
+        <v>54758</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Gemma</t>
+          <t>Llama-3.3</t>
         </is>
       </c>
       <c r="I79" t="n">
-        <v>8.4</v>
+        <v>70</v>
       </c>
       <c r="J79" t="n">
-        <v>4</v>
+        <v>70</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>moe</t>
+          <t>dense</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>aa_single_scrape</t>
+          <t>name_parsing</t>
         </is>
       </c>
       <c r="M79" t="n">
-        <v>16.8</v>
+        <v>140</v>
       </c>
       <c r="N79" t="n">
-        <v>21</v>
+        <v>175</v>
       </c>
       <c r="O79" t="n">
-        <v>8.4</v>
+        <v>70</v>
       </c>
       <c r="P79" t="n">
-        <v>10.5</v>
+        <v>87.5</v>
       </c>
       <c r="Q79" t="n">
-        <v>4.2</v>
+        <v>35</v>
       </c>
       <c r="R79" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="S79" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+        <v>43.8</v>
+      </c>
+      <c r="S79" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="T79" s="6" t="inlineStr">
@@ -10052,14 +10052,14 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="V79" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W79" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="V79" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W79" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="X79" s="6" t="inlineStr">
@@ -10067,9 +10067,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="Y79" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="Y79" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="Z79" s="6" t="inlineStr">
@@ -10114,12 +10114,12 @@
       </c>
       <c r="AH79" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>B200 SXM</t>
         </is>
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>RTX PRO 6000</t>
         </is>
       </c>
     </row>
@@ -10133,13 +10133,13 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1317.74</v>
+        <v>1317.67</v>
       </c>
       <c r="D80" t="n">
-        <v>1312.05</v>
+        <v>1311.98</v>
       </c>
       <c r="E80" t="n">
-        <v>1323.43</v>
+        <v>1323.36</v>
       </c>
       <c r="F80" t="n">
         <v>16478</v>
@@ -10204,16 +10204,16 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1317.56</v>
+        <v>1317.47</v>
       </c>
       <c r="D81" t="n">
-        <v>1311.2</v>
+        <v>1311.11</v>
       </c>
       <c r="E81" t="n">
-        <v>1323.92</v>
+        <v>1323.83</v>
       </c>
       <c r="F81" t="n">
-        <v>10639</v>
+        <v>10638</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -10355,16 +10355,16 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>1317.41</v>
+        <v>1317.21</v>
       </c>
       <c r="D82" t="n">
-        <v>1311.83</v>
+        <v>1311.63</v>
       </c>
       <c r="E82" t="n">
-        <v>1323</v>
+        <v>1322.79</v>
       </c>
       <c r="F82" t="n">
-        <v>15543</v>
+        <v>15538</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -10506,13 +10506,13 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>1314.28</v>
+        <v>1314.19</v>
       </c>
       <c r="D83" t="n">
-        <v>1309.75</v>
+        <v>1309.66</v>
       </c>
       <c r="E83" t="n">
-        <v>1318.81</v>
+        <v>1318.72</v>
       </c>
       <c r="F83" t="n">
         <v>24739</v>
@@ -10657,13 +10657,13 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>1313.65</v>
+        <v>1313.6</v>
       </c>
       <c r="D84" t="n">
-        <v>1309.75</v>
+        <v>1309.7</v>
       </c>
       <c r="E84" t="n">
-        <v>1317.55</v>
+        <v>1317.51</v>
       </c>
       <c r="F84" t="n">
         <v>45459</v>
@@ -10808,13 +10808,13 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>1306.89</v>
+        <v>1306.79</v>
       </c>
       <c r="D85" t="n">
-        <v>1302.21</v>
+        <v>1302.11</v>
       </c>
       <c r="E85" t="n">
-        <v>1311.58</v>
+        <v>1311.48</v>
       </c>
       <c r="F85" t="n">
         <v>24572</v>
@@ -10879,13 +10879,13 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>1305.84</v>
+        <v>1305.79</v>
       </c>
       <c r="D86" t="n">
-        <v>1300.17</v>
+        <v>1300.12</v>
       </c>
       <c r="E86" t="n">
-        <v>1311.5</v>
+        <v>1311.45</v>
       </c>
       <c r="F86" t="n">
         <v>19621</v>
@@ -11030,16 +11030,16 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>1305.45</v>
+        <v>1305.25</v>
       </c>
       <c r="D87" t="n">
-        <v>1297.26</v>
+        <v>1297.06</v>
       </c>
       <c r="E87" t="n">
-        <v>1313.65</v>
+        <v>1313.44</v>
       </c>
       <c r="F87" t="n">
-        <v>5967</v>
+        <v>5969</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -11181,13 +11181,13 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>1304.97</v>
+        <v>1304.91</v>
       </c>
       <c r="D88" t="n">
-        <v>1300.56</v>
+        <v>1300.5</v>
       </c>
       <c r="E88" t="n">
-        <v>1309.37</v>
+        <v>1309.32</v>
       </c>
       <c r="F88" t="n">
         <v>28073</v>
@@ -11252,16 +11252,16 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>1303.25</v>
+        <v>1303.17</v>
       </c>
       <c r="D89" t="n">
-        <v>1298.75</v>
+        <v>1298.66</v>
       </c>
       <c r="E89" t="n">
-        <v>1307.75</v>
+        <v>1307.67</v>
       </c>
       <c r="F89" t="n">
-        <v>33249</v>
+        <v>33245</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -11403,13 +11403,13 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>1303.08</v>
+        <v>1303.06</v>
       </c>
       <c r="D90" t="n">
-        <v>1293.76</v>
+        <v>1293.74</v>
       </c>
       <c r="E90" t="n">
-        <v>1312.4</v>
+        <v>1312.38</v>
       </c>
       <c r="F90" t="n">
         <v>4171</v>
@@ -11554,13 +11554,13 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>1302.59</v>
+        <v>1302.5</v>
       </c>
       <c r="D91" t="n">
-        <v>1298.55</v>
+        <v>1298.46</v>
       </c>
       <c r="E91" t="n">
-        <v>1306.64</v>
+        <v>1306.55</v>
       </c>
       <c r="F91" t="n">
         <v>39406</v>
@@ -11705,13 +11705,13 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>1298.71</v>
+        <v>1298.64</v>
       </c>
       <c r="D92" t="n">
-        <v>1290.95</v>
+        <v>1290.88</v>
       </c>
       <c r="E92" t="n">
-        <v>1306.47</v>
+        <v>1306.4</v>
       </c>
       <c r="F92" t="n">
         <v>7140</v>
@@ -11856,13 +11856,13 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>1293.07</v>
+        <v>1293.03</v>
       </c>
       <c r="D93" t="n">
-        <v>1289.36</v>
+        <v>1289.32</v>
       </c>
       <c r="E93" t="n">
-        <v>1296.78</v>
+        <v>1296.74</v>
       </c>
       <c r="F93" t="n">
         <v>55240</v>
@@ -12007,13 +12007,13 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1288.54</v>
+        <v>1288.47</v>
       </c>
       <c r="D94" t="n">
-        <v>1281.24</v>
+        <v>1281.16</v>
       </c>
       <c r="E94" t="n">
-        <v>1295.84</v>
+        <v>1295.77</v>
       </c>
       <c r="F94" t="n">
         <v>8662</v>
@@ -12078,13 +12078,13 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1288.02</v>
+        <v>1287.96</v>
       </c>
       <c r="D95" t="n">
-        <v>1284.67</v>
+        <v>1284.6</v>
       </c>
       <c r="E95" t="n">
-        <v>1291.37</v>
+        <v>1291.31</v>
       </c>
       <c r="F95" t="n">
         <v>75754</v>
@@ -12229,16 +12229,16 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>1286.82</v>
+        <v>1286.61</v>
       </c>
       <c r="D96" t="n">
-        <v>1278.43</v>
+        <v>1278.22</v>
       </c>
       <c r="E96" t="n">
-        <v>1295.21</v>
+        <v>1295</v>
       </c>
       <c r="F96" t="n">
-        <v>5691</v>
+        <v>5695</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
@@ -12380,13 +12380,13 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1286.02</v>
+        <v>1286.01</v>
       </c>
       <c r="D97" t="n">
-        <v>1275.55</v>
+        <v>1275.53</v>
       </c>
       <c r="E97" t="n">
-        <v>1296.5</v>
+        <v>1296.48</v>
       </c>
       <c r="F97" t="n">
         <v>2846</v>
@@ -12682,16 +12682,16 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>1285.46</v>
+        <v>1285.55</v>
       </c>
       <c r="D99" t="n">
-        <v>1278.22</v>
+        <v>1278.31</v>
       </c>
       <c r="E99" t="n">
-        <v>1292.7</v>
+        <v>1292.79</v>
       </c>
       <c r="F99" t="n">
-        <v>8512</v>
+        <v>8508</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -12833,13 +12833,13 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>1279.24</v>
+        <v>1279.17</v>
       </c>
       <c r="D100" t="n">
-        <v>1272.38</v>
+        <v>1272.31</v>
       </c>
       <c r="E100" t="n">
-        <v>1286.1</v>
+        <v>1286.02</v>
       </c>
       <c r="F100" t="n">
         <v>10072</v>
@@ -12984,13 +12984,13 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1276.49</v>
+        <v>1276.52</v>
       </c>
       <c r="D101" t="n">
-        <v>1271.17</v>
+        <v>1271.19</v>
       </c>
       <c r="E101" t="n">
-        <v>1281.82</v>
+        <v>1281.84</v>
       </c>
       <c r="F101" t="n">
         <v>19659</v>
@@ -13135,13 +13135,13 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>1275.75</v>
+        <v>1275.76</v>
       </c>
       <c r="D102" t="n">
-        <v>1269.18</v>
+        <v>1269.19</v>
       </c>
       <c r="E102" t="n">
-        <v>1282.32</v>
+        <v>1282.33</v>
       </c>
       <c r="F102" t="n">
         <v>9866</v>
@@ -13289,10 +13289,10 @@
         <v>1275.49</v>
       </c>
       <c r="D103" t="n">
-        <v>1271.92</v>
+        <v>1271.91</v>
       </c>
       <c r="E103" t="n">
-        <v>1279.07</v>
+        <v>1279.06</v>
       </c>
       <c r="F103" t="n">
         <v>156876</v>
@@ -13437,13 +13437,13 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>1273.77</v>
+        <v>1273.71</v>
       </c>
       <c r="D104" t="n">
-        <v>1267.88</v>
+        <v>1267.82</v>
       </c>
       <c r="E104" t="n">
-        <v>1279.66</v>
+        <v>1279.6</v>
       </c>
       <c r="F104" t="n">
         <v>14681</v>
@@ -13588,13 +13588,13 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>1270.19</v>
+        <v>1270.13</v>
       </c>
       <c r="D105" t="n">
-        <v>1262.07</v>
+        <v>1262.01</v>
       </c>
       <c r="E105" t="n">
-        <v>1278.31</v>
+        <v>1278.25</v>
       </c>
       <c r="F105" t="n">
         <v>5432</v>
@@ -13739,13 +13739,13 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>1266.58</v>
+        <v>1266.56</v>
       </c>
       <c r="D106" t="n">
-        <v>1261.72</v>
+        <v>1261.69</v>
       </c>
       <c r="E106" t="n">
-        <v>1271.45</v>
+        <v>1271.42</v>
       </c>
       <c r="F106" t="n">
         <v>27124</v>
@@ -13890,13 +13890,13 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>1265.5</v>
+        <v>1265.43</v>
       </c>
       <c r="D107" t="n">
-        <v>1261.7</v>
+        <v>1261.64</v>
       </c>
       <c r="E107" t="n">
-        <v>1269.29</v>
+        <v>1269.22</v>
       </c>
       <c r="F107" t="n">
         <v>54611</v>
@@ -14041,13 +14041,13 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>1263.81</v>
+        <v>1263.76</v>
       </c>
       <c r="D108" t="n">
-        <v>1257.53</v>
+        <v>1257.48</v>
       </c>
       <c r="E108" t="n">
-        <v>1270.09</v>
+        <v>1270.04</v>
       </c>
       <c r="F108" t="n">
         <v>15147</v>
@@ -14188,148 +14188,68 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>qwen2-72b-instruct</t>
+          <t>command-r-plus</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>1261.02</v>
+        <v>1261.03</v>
       </c>
       <c r="D109" t="n">
-        <v>1256.09</v>
+        <v>1256.71</v>
       </c>
       <c r="E109" t="n">
-        <v>1265.96</v>
+        <v>1265.35</v>
       </c>
       <c r="F109" t="n">
-        <v>37325</v>
+        <v>77554</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alibaba</t>
+          <t>Cohere</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Qianwen LICENSE</t>
-        </is>
-      </c>
-      <c r="I109" t="n">
-        <v>72</v>
-      </c>
-      <c r="J109" t="n">
-        <v>72</v>
-      </c>
-      <c r="K109" t="inlineStr">
-        <is>
-          <t>dense</t>
-        </is>
-      </c>
+          <t>CC-BY-NC-4.0</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
       <c r="L109" t="inlineStr">
         <is>
-          <t>name_parsing</t>
-        </is>
-      </c>
-      <c r="M109" t="n">
-        <v>144</v>
-      </c>
-      <c r="N109" t="n">
-        <v>180</v>
-      </c>
-      <c r="O109" t="n">
-        <v>72</v>
-      </c>
-      <c r="P109" t="n">
-        <v>90</v>
-      </c>
-      <c r="Q109" t="n">
-        <v>36</v>
-      </c>
-      <c r="R109" t="n">
-        <v>45</v>
-      </c>
-      <c r="S109" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T109" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="U109" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="V109" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W109" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X109" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Y109" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z109" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AA109" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB109" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AC109" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AD109" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AE109" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AF109" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AG109" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
+      <c r="O109" t="inlineStr"/>
+      <c r="P109" t="inlineStr"/>
+      <c r="Q109" t="inlineStr"/>
+      <c r="R109" t="inlineStr"/>
+      <c r="S109" t="inlineStr"/>
+      <c r="T109" t="inlineStr"/>
+      <c r="U109" t="inlineStr"/>
+      <c r="V109" t="inlineStr"/>
+      <c r="W109" t="inlineStr"/>
+      <c r="X109" t="inlineStr"/>
+      <c r="Y109" t="inlineStr"/>
+      <c r="Z109" t="inlineStr"/>
+      <c r="AA109" t="inlineStr"/>
+      <c r="AB109" t="inlineStr"/>
+      <c r="AC109" t="inlineStr"/>
+      <c r="AD109" t="inlineStr"/>
+      <c r="AE109" t="inlineStr"/>
+      <c r="AF109" t="inlineStr"/>
+      <c r="AG109" t="inlineStr"/>
       <c r="AH109" t="inlineStr">
         <is>
-          <t>B200 SXM</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="AI109" t="inlineStr">
         <is>
-          <t>RTX PRO 6000</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -14339,68 +14259,148 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>command-r-plus</t>
+          <t>qwen2-72b-instruct</t>
         </is>
       </c>
       <c r="C110" t="n">
         <v>1261.02</v>
       </c>
       <c r="D110" t="n">
-        <v>1256.7</v>
+        <v>1256.08</v>
       </c>
       <c r="E110" t="n">
-        <v>1265.34</v>
+        <v>1265.96</v>
       </c>
       <c r="F110" t="n">
-        <v>77554</v>
+        <v>37325</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Cohere</t>
+          <t>Alibaba</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>CC-BY-NC-4.0</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr"/>
-      <c r="J110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
+          <t>Qianwen LICENSE</t>
+        </is>
+      </c>
+      <c r="I110" t="n">
+        <v>72</v>
+      </c>
+      <c r="J110" t="n">
+        <v>72</v>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>dense</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="M110" t="inlineStr"/>
-      <c r="N110" t="inlineStr"/>
-      <c r="O110" t="inlineStr"/>
-      <c r="P110" t="inlineStr"/>
-      <c r="Q110" t="inlineStr"/>
-      <c r="R110" t="inlineStr"/>
-      <c r="S110" t="inlineStr"/>
-      <c r="T110" t="inlineStr"/>
-      <c r="U110" t="inlineStr"/>
-      <c r="V110" t="inlineStr"/>
-      <c r="W110" t="inlineStr"/>
-      <c r="X110" t="inlineStr"/>
-      <c r="Y110" t="inlineStr"/>
-      <c r="Z110" t="inlineStr"/>
-      <c r="AA110" t="inlineStr"/>
-      <c r="AB110" t="inlineStr"/>
-      <c r="AC110" t="inlineStr"/>
-      <c r="AD110" t="inlineStr"/>
-      <c r="AE110" t="inlineStr"/>
-      <c r="AF110" t="inlineStr"/>
-      <c r="AG110" t="inlineStr"/>
+          <t>name_parsing</t>
+        </is>
+      </c>
+      <c r="M110" t="n">
+        <v>144</v>
+      </c>
+      <c r="N110" t="n">
+        <v>180</v>
+      </c>
+      <c r="O110" t="n">
+        <v>72</v>
+      </c>
+      <c r="P110" t="n">
+        <v>90</v>
+      </c>
+      <c r="Q110" t="n">
+        <v>36</v>
+      </c>
+      <c r="R110" t="n">
+        <v>45</v>
+      </c>
+      <c r="S110" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T110" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U110" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V110" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W110" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X110" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y110" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z110" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AA110" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB110" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AC110" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AD110" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE110" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AF110" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AG110" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AH110" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>B200 SXM</t>
         </is>
       </c>
       <c r="AI110" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>RTX PRO 6000</t>
         </is>
       </c>
     </row>
@@ -14414,13 +14414,13 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>1255.75</v>
+        <v>1255.7</v>
       </c>
       <c r="D111" t="n">
-        <v>1251.18</v>
+        <v>1251.13</v>
       </c>
       <c r="E111" t="n">
-        <v>1260.32</v>
+        <v>1260.27</v>
       </c>
       <c r="F111" t="n">
         <v>24126</v>
@@ -14565,13 +14565,13 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>1251.43</v>
+        <v>1251.42</v>
       </c>
       <c r="D112" t="n">
-        <v>1240.64</v>
+        <v>1240.63</v>
       </c>
       <c r="E112" t="n">
-        <v>1262.23</v>
+        <v>1262.21</v>
       </c>
       <c r="F112" t="n">
         <v>3334</v>
@@ -14716,13 +14716,13 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>1249.39</v>
+        <v>1249.4</v>
       </c>
       <c r="D113" t="n">
         <v>1242.8</v>
       </c>
       <c r="E113" t="n">
-        <v>1255.98</v>
+        <v>1255.99</v>
       </c>
       <c r="F113" t="n">
         <v>10140</v>
@@ -14867,13 +14867,13 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>1238.74</v>
+        <v>1238.68</v>
       </c>
       <c r="D114" t="n">
-        <v>1231.52</v>
+        <v>1231.46</v>
       </c>
       <c r="E114" t="n">
-        <v>1245.97</v>
+        <v>1245.91</v>
       </c>
       <c r="F114" t="n">
         <v>8858</v>
@@ -14938,13 +14938,13 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>1236.9</v>
+        <v>1236.83</v>
       </c>
       <c r="D115" t="n">
-        <v>1227.8</v>
+        <v>1227.74</v>
       </c>
       <c r="E115" t="n">
-        <v>1245.99</v>
+        <v>1245.93</v>
       </c>
       <c r="F115" t="n">
         <v>4781</v>
@@ -15089,13 +15089,13 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>1233.3</v>
+        <v>1233.29</v>
       </c>
       <c r="D116" t="n">
-        <v>1227.75</v>
+        <v>1227.74</v>
       </c>
       <c r="E116" t="n">
-        <v>1238.86</v>
+        <v>1238.85</v>
       </c>
       <c r="F116" t="n">
         <v>26195</v>
@@ -15240,13 +15240,13 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>1232.36</v>
+        <v>1232.37</v>
       </c>
       <c r="D117" t="n">
         <v>1227.09</v>
       </c>
       <c r="E117" t="n">
-        <v>1237.64</v>
+        <v>1237.65</v>
       </c>
       <c r="F117" t="n">
         <v>39302</v>
@@ -15391,13 +15391,13 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>1228.54</v>
+        <v>1228.55</v>
       </c>
       <c r="D118" t="n">
-        <v>1223.99</v>
+        <v>1224</v>
       </c>
       <c r="E118" t="n">
-        <v>1233.09</v>
+        <v>1233.1</v>
       </c>
       <c r="F118" t="n">
         <v>51416</v>
@@ -15542,13 +15542,13 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>1225.99</v>
+        <v>1226.01</v>
       </c>
       <c r="D119" t="n">
-        <v>1221.21</v>
+        <v>1221.23</v>
       </c>
       <c r="E119" t="n">
-        <v>1230.78</v>
+        <v>1230.79</v>
       </c>
       <c r="F119" t="n">
         <v>54036</v>
@@ -15616,7 +15616,7 @@
         <v>1222.55</v>
       </c>
       <c r="D120" t="n">
-        <v>1218.82</v>
+        <v>1218.83</v>
       </c>
       <c r="E120" t="n">
         <v>1226.28</v>
@@ -15764,13 +15764,13 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>1222.54</v>
+        <v>1222.51</v>
       </c>
       <c r="D121" t="n">
-        <v>1215.58</v>
+        <v>1215.54</v>
       </c>
       <c r="E121" t="n">
-        <v>1229.49</v>
+        <v>1229.47</v>
       </c>
       <c r="F121" t="n">
         <v>9818</v>
@@ -15915,13 +15915,13 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>1220.56</v>
+        <v>1220.53</v>
       </c>
       <c r="D122" t="n">
-        <v>1209.88</v>
+        <v>1209.85</v>
       </c>
       <c r="E122" t="n">
-        <v>1231.25</v>
+        <v>1231.22</v>
       </c>
       <c r="F122" t="n">
         <v>2896</v>
@@ -16072,7 +16072,7 @@
         <v>1207.59</v>
       </c>
       <c r="E123" t="n">
-        <v>1217.66</v>
+        <v>1217.67</v>
       </c>
       <c r="F123" t="n">
         <v>24146</v>
@@ -16217,13 +16217,13 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>1211.85</v>
+        <v>1211.87</v>
       </c>
       <c r="D124" t="n">
-        <v>1201.04</v>
+        <v>1201.06</v>
       </c>
       <c r="E124" t="n">
-        <v>1222.66</v>
+        <v>1222.67</v>
       </c>
       <c r="F124" t="n">
         <v>4652</v>
@@ -16368,13 +16368,13 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>1211.27</v>
+        <v>1211.2</v>
       </c>
       <c r="D125" t="n">
-        <v>1207.14</v>
+        <v>1207.08</v>
       </c>
       <c r="E125" t="n">
-        <v>1215.39</v>
+        <v>1215.33</v>
       </c>
       <c r="F125" t="n">
         <v>49605</v>
@@ -16519,13 +16519,13 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>1207.61</v>
+        <v>1207.63</v>
       </c>
       <c r="D126" t="n">
-        <v>1196.5</v>
+        <v>1196.52</v>
       </c>
       <c r="E126" t="n">
-        <v>1218.72</v>
+        <v>1218.74</v>
       </c>
       <c r="F126" t="n">
         <v>3090</v>
@@ -16670,13 +16670,13 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>1202.95</v>
+        <v>1202.97</v>
       </c>
       <c r="D127" t="n">
-        <v>1196.83</v>
+        <v>1196.85</v>
       </c>
       <c r="E127" t="n">
-        <v>1209.07</v>
+        <v>1209.09</v>
       </c>
       <c r="F127" t="n">
         <v>21741</v>
@@ -16821,13 +16821,13 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>1198.95</v>
+        <v>1198.89</v>
       </c>
       <c r="D128" t="n">
-        <v>1194.89</v>
+        <v>1194.82</v>
       </c>
       <c r="E128" t="n">
-        <v>1203.02</v>
+        <v>1202.96</v>
       </c>
       <c r="F128" t="n">
         <v>46616</v>
@@ -16972,13 +16972,13 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>1197.06</v>
+        <v>1197.08</v>
       </c>
       <c r="D129" t="n">
-        <v>1191.91</v>
+        <v>1191.93</v>
       </c>
       <c r="E129" t="n">
-        <v>1202.22</v>
+        <v>1202.24</v>
       </c>
       <c r="F129" t="n">
         <v>25055</v>
@@ -17123,13 +17123,13 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>1196.2</v>
+        <v>1196.22</v>
       </c>
       <c r="D130" t="n">
-        <v>1191.93</v>
+        <v>1191.95</v>
       </c>
       <c r="E130" t="n">
-        <v>1200.47</v>
+        <v>1200.49</v>
       </c>
       <c r="F130" t="n">
         <v>73503</v>
@@ -17277,7 +17277,7 @@
         <v>1194.18</v>
       </c>
       <c r="D131" t="n">
-        <v>1188.06</v>
+        <v>1188.07</v>
       </c>
       <c r="E131" t="n">
         <v>1200.3</v>
@@ -17345,13 +17345,13 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>1190.65</v>
+        <v>1190.66</v>
       </c>
       <c r="D132" t="n">
-        <v>1183.47</v>
+        <v>1183.48</v>
       </c>
       <c r="E132" t="n">
-        <v>1197.83</v>
+        <v>1197.84</v>
       </c>
       <c r="F132" t="n">
         <v>9901</v>
@@ -17496,13 +17496,13 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>1190.07</v>
+        <v>1190.09</v>
       </c>
       <c r="D133" t="n">
-        <v>1182.95</v>
+        <v>1182.96</v>
       </c>
       <c r="E133" t="n">
-        <v>1197.2</v>
+        <v>1197.22</v>
       </c>
       <c r="F133" t="n">
         <v>17839</v>
@@ -17647,13 +17647,13 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>1183.73</v>
+        <v>1183.75</v>
       </c>
       <c r="D134" t="n">
-        <v>1174.27</v>
+        <v>1174.3</v>
       </c>
       <c r="E134" t="n">
-        <v>1193.19</v>
+        <v>1193.21</v>
       </c>
       <c r="F134" t="n">
         <v>8214</v>
@@ -17798,7 +17798,7 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>1183.5</v>
+        <v>1183.51</v>
       </c>
       <c r="D135" t="n">
         <v>1171.99</v>
@@ -17949,13 +17949,13 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>1183</v>
+        <v>1183.01</v>
       </c>
       <c r="D136" t="n">
-        <v>1176.17</v>
+        <v>1176.18</v>
       </c>
       <c r="E136" t="n">
-        <v>1189.83</v>
+        <v>1189.84</v>
       </c>
       <c r="F136" t="n">
         <v>15483</v>
@@ -18100,13 +18100,13 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>1181.37</v>
+        <v>1181.38</v>
       </c>
       <c r="D137" t="n">
-        <v>1173.37</v>
+        <v>1173.38</v>
       </c>
       <c r="E137" t="n">
-        <v>1189.37</v>
+        <v>1189.39</v>
       </c>
       <c r="F137" t="n">
         <v>12637</v>
@@ -18242,13 +18242,13 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>1181.31</v>
+        <v>1181.3</v>
       </c>
       <c r="D139" t="n">
         <v>1172.62</v>
       </c>
       <c r="E139" t="n">
-        <v>1190</v>
+        <v>1189.99</v>
       </c>
       <c r="F139" t="n">
         <v>6638</v>
@@ -18393,13 +18393,13 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>1180.17</v>
+        <v>1180.09</v>
       </c>
       <c r="D140" t="n">
-        <v>1174.1</v>
+        <v>1174.02</v>
       </c>
       <c r="E140" t="n">
-        <v>1186.24</v>
+        <v>1186.17</v>
       </c>
       <c r="F140" t="n">
         <v>23893</v>
@@ -18544,13 +18544,13 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>1178.6</v>
+        <v>1178.61</v>
       </c>
       <c r="D141" t="n">
-        <v>1172.68</v>
+        <v>1172.69</v>
       </c>
       <c r="E141" t="n">
-        <v>1184.51</v>
+        <v>1184.52</v>
       </c>
       <c r="F141" t="n">
         <v>32832</v>
@@ -18615,13 +18615,13 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>1178.16</v>
+        <v>1178.18</v>
       </c>
       <c r="D142" t="n">
-        <v>1166.95</v>
+        <v>1166.98</v>
       </c>
       <c r="E142" t="n">
-        <v>1189.36</v>
+        <v>1189.39</v>
       </c>
       <c r="F142" t="n">
         <v>3188</v>
@@ -18766,13 +18766,13 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>1177.02</v>
+        <v>1177.05</v>
       </c>
       <c r="D143" t="n">
-        <v>1167.2</v>
+        <v>1167.23</v>
       </c>
       <c r="E143" t="n">
-        <v>1186.85</v>
+        <v>1186.88</v>
       </c>
       <c r="F143" t="n">
         <v>6535</v>
@@ -18920,10 +18920,10 @@
         <v>1174.32</v>
       </c>
       <c r="D144" t="n">
-        <v>1163.89</v>
+        <v>1163.9</v>
       </c>
       <c r="E144" t="n">
-        <v>1184.74</v>
+        <v>1184.75</v>
       </c>
       <c r="F144" t="n">
         <v>5006</v>
@@ -19068,13 +19068,13 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>1171.84</v>
+        <v>1171.86</v>
       </c>
       <c r="D145" t="n">
-        <v>1165.63</v>
+        <v>1165.65</v>
       </c>
       <c r="E145" t="n">
-        <v>1178.05</v>
+        <v>1178.08</v>
       </c>
       <c r="F145" t="n">
         <v>22479</v>
@@ -19219,13 +19219,13 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>1170.65</v>
+        <v>1170.72</v>
       </c>
       <c r="D146" t="n">
-        <v>1163.24</v>
+        <v>1163.31</v>
       </c>
       <c r="E146" t="n">
-        <v>1178.07</v>
+        <v>1178.14</v>
       </c>
       <c r="F146" t="n">
         <v>16056</v>
@@ -19370,13 +19370,13 @@
         </is>
       </c>
       <c r="C147" t="n">
-        <v>1170.21</v>
+        <v>1170.23</v>
       </c>
       <c r="D147" t="n">
-        <v>1164.3</v>
+        <v>1164.31</v>
       </c>
       <c r="E147" t="n">
-        <v>1176.13</v>
+        <v>1176.14</v>
       </c>
       <c r="F147" t="n">
         <v>17766</v>
@@ -19521,13 +19521,13 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>1169.85</v>
+        <v>1169.89</v>
       </c>
       <c r="D148" t="n">
-        <v>1164.35</v>
+        <v>1164.38</v>
       </c>
       <c r="E148" t="n">
-        <v>1175.36</v>
+        <v>1175.4</v>
       </c>
       <c r="F148" t="n">
         <v>38492</v>
@@ -19672,13 +19672,13 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>1166.57</v>
+        <v>1166.61</v>
       </c>
       <c r="D149" t="n">
-        <v>1158.5</v>
+        <v>1158.53</v>
       </c>
       <c r="E149" t="n">
-        <v>1174.65</v>
+        <v>1174.68</v>
       </c>
       <c r="F149" t="n">
         <v>10224</v>
@@ -19823,10 +19823,10 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>1165.98</v>
+        <v>1165.97</v>
       </c>
       <c r="D150" t="n">
-        <v>1158.28</v>
+        <v>1158.27</v>
       </c>
       <c r="E150" t="n">
         <v>1173.67</v>
@@ -19974,13 +19974,13 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>1163.77</v>
+        <v>1163.81</v>
       </c>
       <c r="D151" t="n">
-        <v>1151.83</v>
+        <v>1151.87</v>
       </c>
       <c r="E151" t="n">
-        <v>1175.71</v>
+        <v>1175.74</v>
       </c>
       <c r="F151" t="n">
         <v>3777</v>
@@ -20125,13 +20125,13 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>1155.86</v>
+        <v>1155.91</v>
       </c>
       <c r="D152" t="n">
-        <v>1144.36</v>
+        <v>1144.41</v>
       </c>
       <c r="E152" t="n">
-        <v>1167.36</v>
+        <v>1167.41</v>
       </c>
       <c r="F152" t="n">
         <v>3231</v>
@@ -20282,7 +20282,7 @@
         <v>1146.84</v>
       </c>
       <c r="E153" t="n">
-        <v>1163.62</v>
+        <v>1163.63</v>
       </c>
       <c r="F153" t="n">
         <v>6837</v>
@@ -20427,13 +20427,13 @@
         </is>
       </c>
       <c r="C154" t="n">
-        <v>1154.27</v>
+        <v>1154.29</v>
       </c>
       <c r="D154" t="n">
-        <v>1141.65</v>
+        <v>1141.67</v>
       </c>
       <c r="E154" t="n">
-        <v>1166.89</v>
+        <v>1166.91</v>
       </c>
       <c r="F154" t="n">
         <v>3585</v>
@@ -20578,13 +20578,13 @@
         </is>
       </c>
       <c r="C155" t="n">
-        <v>1151.39</v>
+        <v>1151.41</v>
       </c>
       <c r="D155" t="n">
-        <v>1138.19</v>
+        <v>1138.2</v>
       </c>
       <c r="E155" t="n">
-        <v>1164.6</v>
+        <v>1164.61</v>
       </c>
       <c r="F155" t="n">
         <v>4155</v>
@@ -20729,13 +20729,13 @@
         </is>
       </c>
       <c r="C156" t="n">
-        <v>1151.08</v>
+        <v>1151.09</v>
       </c>
       <c r="D156" t="n">
-        <v>1135.69</v>
+        <v>1135.71</v>
       </c>
       <c r="E156" t="n">
-        <v>1166.47</v>
+        <v>1166.48</v>
       </c>
       <c r="F156" t="n">
         <v>1679</v>
@@ -20880,7 +20880,7 @@
         </is>
       </c>
       <c r="C157" t="n">
-        <v>1149.21</v>
+        <v>1149.22</v>
       </c>
       <c r="D157" t="n">
         <v>1136.92</v>
@@ -21031,13 +21031,13 @@
         </is>
       </c>
       <c r="C158" t="n">
-        <v>1148.62</v>
+        <v>1148.65</v>
       </c>
       <c r="D158" t="n">
-        <v>1141.96</v>
+        <v>1141.99</v>
       </c>
       <c r="E158" t="n">
-        <v>1155.27</v>
+        <v>1155.3</v>
       </c>
       <c r="F158" t="n">
         <v>19402</v>
@@ -21182,13 +21182,13 @@
         </is>
       </c>
       <c r="C159" t="n">
-        <v>1148.28</v>
+        <v>1148.3</v>
       </c>
       <c r="D159" t="n">
-        <v>1139.02</v>
+        <v>1139.04</v>
       </c>
       <c r="E159" t="n">
-        <v>1157.54</v>
+        <v>1157.55</v>
       </c>
       <c r="F159" t="n">
         <v>7044</v>
@@ -21333,13 +21333,13 @@
         </is>
       </c>
       <c r="C160" t="n">
-        <v>1146.21</v>
+        <v>1146.19</v>
       </c>
       <c r="D160" t="n">
         <v>1129.08</v>
       </c>
       <c r="E160" t="n">
-        <v>1163.33</v>
+        <v>1163.31</v>
       </c>
       <c r="F160" t="n">
         <v>1295</v>
@@ -21484,13 +21484,13 @@
         </is>
       </c>
       <c r="C161" t="n">
-        <v>1142.91</v>
+        <v>1142.93</v>
       </c>
       <c r="D161" t="n">
-        <v>1133.01</v>
+        <v>1133.04</v>
       </c>
       <c r="E161" t="n">
-        <v>1152.81</v>
+        <v>1152.83</v>
       </c>
       <c r="F161" t="n">
         <v>4737</v>
@@ -21635,13 +21635,13 @@
         </is>
       </c>
       <c r="C162" t="n">
-        <v>1142.21</v>
+        <v>1142.22</v>
       </c>
       <c r="D162" t="n">
-        <v>1135.77</v>
+        <v>1135.78</v>
       </c>
       <c r="E162" t="n">
-        <v>1148.64</v>
+        <v>1148.65</v>
       </c>
       <c r="F162" t="n">
         <v>12297</v>
@@ -21786,13 +21786,13 @@
         </is>
       </c>
       <c r="C163" t="n">
-        <v>1140.57</v>
+        <v>1140.61</v>
       </c>
       <c r="D163" t="n">
-        <v>1133.84</v>
+        <v>1133.88</v>
       </c>
       <c r="E163" t="n">
-        <v>1147.3</v>
+        <v>1147.34</v>
       </c>
       <c r="F163" t="n">
         <v>19174</v>
@@ -21940,7 +21940,7 @@
         <v>1140.02</v>
       </c>
       <c r="D164" t="n">
-        <v>1133.3</v>
+        <v>1133.31</v>
       </c>
       <c r="E164" t="n">
         <v>1146.73</v>
@@ -22088,13 +22088,13 @@
         </is>
       </c>
       <c r="C165" t="n">
-        <v>1137.7</v>
+        <v>1137.69</v>
       </c>
       <c r="D165" t="n">
-        <v>1126.73</v>
+        <v>1126.72</v>
       </c>
       <c r="E165" t="n">
-        <v>1148.66</v>
+        <v>1148.65</v>
       </c>
       <c r="F165" t="n">
         <v>4964</v>
@@ -22239,13 +22239,13 @@
         </is>
       </c>
       <c r="C166" t="n">
-        <v>1135.78</v>
+        <v>1135.71</v>
       </c>
       <c r="D166" t="n">
-        <v>1126.27</v>
+        <v>1126.2</v>
       </c>
       <c r="E166" t="n">
-        <v>1145.28</v>
+        <v>1145.21</v>
       </c>
       <c r="F166" t="n">
         <v>8925</v>
@@ -22390,13 +22390,13 @@
         </is>
       </c>
       <c r="C167" t="n">
-        <v>1135.64</v>
+        <v>1135.66</v>
       </c>
       <c r="D167" t="n">
-        <v>1126.73</v>
+        <v>1126.76</v>
       </c>
       <c r="E167" t="n">
-        <v>1144.55</v>
+        <v>1144.57</v>
       </c>
       <c r="F167" t="n">
         <v>7366</v>
@@ -22541,13 +22541,13 @@
         </is>
       </c>
       <c r="C168" t="n">
-        <v>1130.03</v>
+        <v>1130.06</v>
       </c>
       <c r="D168" t="n">
-        <v>1121.19</v>
+        <v>1121.21</v>
       </c>
       <c r="E168" t="n">
-        <v>1138.88</v>
+        <v>1138.91</v>
       </c>
       <c r="F168" t="n">
         <v>11118</v>
@@ -22843,13 +22843,13 @@
         </is>
       </c>
       <c r="C170" t="n">
-        <v>1127.46</v>
+        <v>1127.49</v>
       </c>
       <c r="D170" t="n">
-        <v>1121.06</v>
+        <v>1121.09</v>
       </c>
       <c r="E170" t="n">
-        <v>1133.86</v>
+        <v>1133.89</v>
       </c>
       <c r="F170" t="n">
         <v>20118</v>
@@ -22997,10 +22997,10 @@
         <v>1126.36</v>
       </c>
       <c r="D171" t="n">
-        <v>1114.21</v>
+        <v>1114.22</v>
       </c>
       <c r="E171" t="n">
-        <v>1138.5</v>
+        <v>1138.51</v>
       </c>
       <c r="F171" t="n">
         <v>2921</v>
@@ -23145,13 +23145,13 @@
         </is>
       </c>
       <c r="C172" t="n">
-        <v>1125.93</v>
+        <v>1125.95</v>
       </c>
       <c r="D172" t="n">
-        <v>1110.26</v>
+        <v>1110.28</v>
       </c>
       <c r="E172" t="n">
-        <v>1141.59</v>
+        <v>1141.61</v>
       </c>
       <c r="F172" t="n">
         <v>1785</v>
@@ -23302,7 +23302,7 @@
         <v>1109.09</v>
       </c>
       <c r="E173" t="n">
-        <v>1131.09</v>
+        <v>1131.08</v>
       </c>
       <c r="F173" t="n">
         <v>5182</v>
@@ -23450,7 +23450,7 @@
         <v>1118.22</v>
       </c>
       <c r="D174" t="n">
-        <v>1100.01</v>
+        <v>1100.02</v>
       </c>
       <c r="E174" t="n">
         <v>1136.42</v>
@@ -23598,13 +23598,13 @@
         </is>
       </c>
       <c r="C175" t="n">
-        <v>1114.05</v>
+        <v>1113.99</v>
       </c>
       <c r="D175" t="n">
-        <v>1106.32</v>
+        <v>1106.25</v>
       </c>
       <c r="E175" t="n">
-        <v>1121.79</v>
+        <v>1121.73</v>
       </c>
       <c r="F175" t="n">
         <v>10854</v>
@@ -23900,13 +23900,13 @@
         </is>
       </c>
       <c r="C177" t="n">
-        <v>1113.48</v>
+        <v>1113.49</v>
       </c>
       <c r="D177" t="n">
-        <v>1099.07</v>
+        <v>1099.08</v>
       </c>
       <c r="E177" t="n">
-        <v>1127.89</v>
+        <v>1127.9</v>
       </c>
       <c r="F177" t="n">
         <v>2199</v>
@@ -24051,10 +24051,10 @@
         </is>
       </c>
       <c r="C178" t="n">
-        <v>1110.49</v>
+        <v>1110.48</v>
       </c>
       <c r="D178" t="n">
-        <v>1102.61</v>
+        <v>1102.6</v>
       </c>
       <c r="E178" t="n">
         <v>1118.36</v>
@@ -24202,13 +24202,13 @@
         </is>
       </c>
       <c r="C179" t="n">
-        <v>1108.73</v>
+        <v>1108.72</v>
       </c>
       <c r="D179" t="n">
         <v>1099.43</v>
       </c>
       <c r="E179" t="n">
-        <v>1118.03</v>
+        <v>1118.02</v>
       </c>
       <c r="F179" t="n">
         <v>8977</v>
@@ -24353,13 +24353,13 @@
         </is>
       </c>
       <c r="C180" t="n">
-        <v>1107.17</v>
+        <v>1107.22</v>
       </c>
       <c r="D180" t="n">
-        <v>1100.12</v>
+        <v>1100.16</v>
       </c>
       <c r="E180" t="n">
-        <v>1114.23</v>
+        <v>1114.28</v>
       </c>
       <c r="F180" t="n">
         <v>14148</v>
@@ -24504,13 +24504,13 @@
         </is>
       </c>
       <c r="C181" t="n">
-        <v>1091.39</v>
+        <v>1091.33</v>
       </c>
       <c r="D181" t="n">
-        <v>1079.88</v>
+        <v>1079.82</v>
       </c>
       <c r="E181" t="n">
-        <v>1102.9</v>
+        <v>1102.84</v>
       </c>
       <c r="F181" t="n">
         <v>4780</v>
@@ -24655,13 +24655,13 @@
         </is>
       </c>
       <c r="C182" t="n">
-        <v>1089.31</v>
+        <v>1089.3</v>
       </c>
       <c r="D182" t="n">
-        <v>1079.96</v>
+        <v>1079.95</v>
       </c>
       <c r="E182" t="n">
-        <v>1098.66</v>
+        <v>1098.65</v>
       </c>
       <c r="F182" t="n">
         <v>7597</v>
@@ -24806,13 +24806,13 @@
         </is>
       </c>
       <c r="C183" t="n">
-        <v>1073.49</v>
+        <v>1073.54</v>
       </c>
       <c r="D183" t="n">
-        <v>1062.3</v>
+        <v>1062.36</v>
       </c>
       <c r="E183" t="n">
-        <v>1084.68</v>
+        <v>1084.73</v>
       </c>
       <c r="F183" t="n">
         <v>6328</v>
@@ -24957,10 +24957,10 @@
         </is>
       </c>
       <c r="C184" t="n">
-        <v>1069.49</v>
+        <v>1069.5</v>
       </c>
       <c r="D184" t="n">
-        <v>1059.55</v>
+        <v>1059.56</v>
       </c>
       <c r="E184" t="n">
         <v>1079.43</v>
@@ -25108,13 +25108,13 @@
         </is>
       </c>
       <c r="C185" t="n">
-        <v>1066.83</v>
+        <v>1066.76</v>
       </c>
       <c r="D185" t="n">
-        <v>1055.31</v>
+        <v>1055.25</v>
       </c>
       <c r="E185" t="n">
-        <v>1078.34</v>
+        <v>1078.27</v>
       </c>
       <c r="F185" t="n">
         <v>5745</v>
@@ -25259,13 +25259,13 @@
         </is>
       </c>
       <c r="C186" t="n">
-        <v>1065.21</v>
+        <v>1065.18</v>
       </c>
       <c r="D186" t="n">
-        <v>1049.93</v>
+        <v>1049.91</v>
       </c>
       <c r="E186" t="n">
-        <v>1080.49</v>
+        <v>1080.45</v>
       </c>
       <c r="F186" t="n">
         <v>1743</v>
@@ -25410,13 +25410,13 @@
         </is>
       </c>
       <c r="C187" t="n">
-        <v>1061.04</v>
+        <v>1061.02</v>
       </c>
       <c r="D187" t="n">
-        <v>1049.02</v>
+        <v>1049</v>
       </c>
       <c r="E187" t="n">
-        <v>1073.07</v>
+        <v>1073.04</v>
       </c>
       <c r="F187" t="n">
         <v>3924</v>
@@ -25564,10 +25564,10 @@
         <v>1055.11</v>
       </c>
       <c r="D188" t="n">
-        <v>1043.43</v>
+        <v>1043.42</v>
       </c>
       <c r="E188" t="n">
-        <v>1066.8</v>
+        <v>1066.79</v>
       </c>
       <c r="F188" t="n">
         <v>4658</v>
@@ -25712,13 +25712,13 @@
         </is>
       </c>
       <c r="C189" t="n">
-        <v>1040.45</v>
+        <v>1040.44</v>
       </c>
       <c r="D189" t="n">
-        <v>1029.01</v>
+        <v>1029</v>
       </c>
       <c r="E189" t="n">
-        <v>1051.89</v>
+        <v>1051.88</v>
       </c>
       <c r="F189" t="n">
         <v>4845</v>
@@ -26014,13 +26014,13 @@
         </is>
       </c>
       <c r="C191" t="n">
-        <v>1021.25</v>
+        <v>1021.23</v>
       </c>
       <c r="D191" t="n">
-        <v>1010.33</v>
+        <v>1010.31</v>
       </c>
       <c r="E191" t="n">
-        <v>1032.17</v>
+        <v>1032.14</v>
       </c>
       <c r="F191" t="n">
         <v>6310</v>
@@ -26165,13 +26165,13 @@
         </is>
       </c>
       <c r="C192" t="n">
-        <v>994.593</v>
+        <v>994.607</v>
       </c>
       <c r="D192" t="n">
-        <v>981.975</v>
+        <v>981.9930000000001</v>
       </c>
       <c r="E192" t="n">
-        <v>1007.21</v>
+        <v>1007.22</v>
       </c>
       <c r="F192" t="n">
         <v>4914</v>
@@ -26316,13 +26316,13 @@
         </is>
       </c>
       <c r="C193" t="n">
-        <v>990.491</v>
+        <v>990.487</v>
       </c>
       <c r="D193" t="n">
-        <v>978.063</v>
+        <v>978.062</v>
       </c>
       <c r="E193" t="n">
-        <v>1002.92</v>
+        <v>1002.91</v>
       </c>
       <c r="F193" t="n">
         <v>4203</v>
@@ -26467,13 +26467,13 @@
         </is>
       </c>
       <c r="C194" t="n">
-        <v>979.4109999999999</v>
+        <v>979.359</v>
       </c>
       <c r="D194" t="n">
-        <v>965.8099999999999</v>
+        <v>965.763</v>
       </c>
       <c r="E194" t="n">
-        <v>993.0119999999999</v>
+        <v>992.954</v>
       </c>
       <c r="F194" t="n">
         <v>3412</v>
@@ -26618,13 +26618,13 @@
         </is>
       </c>
       <c r="C195" t="n">
-        <v>971.598</v>
+        <v>971.542</v>
       </c>
       <c r="D195" t="n">
-        <v>955.704</v>
+        <v>955.653</v>
       </c>
       <c r="E195" t="n">
-        <v>987.4930000000001</v>
+        <v>987.4299999999999</v>
       </c>
       <c r="F195" t="n">
         <v>2391</v>
@@ -26769,13 +26769,13 @@
         </is>
       </c>
       <c r="C196" t="n">
-        <v>951.675</v>
+        <v>951.681</v>
       </c>
       <c r="D196" t="n">
-        <v>938.871</v>
+        <v>938.881</v>
       </c>
       <c r="E196" t="n">
-        <v>964.479</v>
+        <v>964.48</v>
       </c>
       <c r="F196" t="n">
         <v>3287</v>
@@ -27836,7 +27836,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>deepseek-v3.2-thinking</t>
+          <t>deepseek-r1-0528</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -27851,7 +27851,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>deepseek-r1-0528</t>
+          <t>deepseek-v3.2-thinking</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -27889,38 +27889,38 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>deepseek-v3.1</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
+          <t>kimi-k2-0905-preview</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C19" t="n">
+        <v>32</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>override</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>kimi-k2-0905-preview</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="C20" t="n">
-        <v>32</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+          <t>deepseek-v3.1</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -28087,67 +28087,75 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>minimax-m2.7</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
+          <t>qwen3-235b-a22b-no-thinking</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>235</v>
+      </c>
+      <c r="C29" t="n">
+        <v>22</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>name_parsing</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>qwen3-235b-a22b-no-thinking</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>235</v>
-      </c>
-      <c r="C30" t="n">
-        <v>22</v>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+          <t>minimax-m2.7</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>minimax-m2.5</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
+          <t>qwen3-next-80b-a3b-instruct</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>80</v>
+      </c>
+      <c r="C31" t="n">
+        <v>3</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>name_parsing</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>qwen3-next-80b-a3b-instruct</t>
+          <t>longcat-flash-chat</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>80</v>
+        <v>560</v>
       </c>
       <c r="C32" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -28156,30 +28164,22 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>override</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>longcat-flash-chat</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>560</v>
-      </c>
-      <c r="C33" t="n">
-        <v>27</v>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+          <t>minimax-m2.5</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -28956,18 +28956,18 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>qwen3-30b-a3b</t>
+          <t>molmo-2-8b</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="C72" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>moe</t>
+          <t>dense</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -28979,18 +28979,18 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>molmo-2-8b</t>
+          <t>qwen3-30b-a3b</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="C73" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>dense</t>
+          <t>moe</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -29078,46 +29078,46 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>llama-3.3-70b-instruct</t>
+          <t>gemma-3n-e4b-it</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>70</v>
+        <v>8.4</v>
       </c>
       <c r="C78" t="n">
-        <v>70</v>
+        <v>4</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>dense</t>
+          <t>moe</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>aa_single_scrape</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>gemma-3n-e4b-it</t>
+          <t>llama-3.3-70b-instruct</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>8.4</v>
+        <v>70</v>
       </c>
       <c r="C79" t="n">
-        <v>4</v>
+        <v>70</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>moe</t>
+          <t>dense</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>aa_single_scrape</t>
+          <t>name_parsing</t>
         </is>
       </c>
     </row>
@@ -29759,38 +29759,38 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>qwen2-72b-instruct</t>
-        </is>
-      </c>
-      <c r="B109" t="n">
-        <v>72</v>
-      </c>
-      <c r="C109" t="n">
-        <v>72</v>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>dense</t>
-        </is>
-      </c>
+          <t>command-r-plus</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr"/>
+      <c r="C109" t="inlineStr"/>
+      <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>command-r-plus</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr"/>
-      <c r="C110" t="inlineStr"/>
-      <c r="D110" t="inlineStr"/>
+          <t>qwen2-72b-instruct</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>72</v>
+      </c>
+      <c r="C110" t="n">
+        <v>72</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>dense</t>
+        </is>
+      </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>name_parsing</t>
         </is>
       </c>
     </row>

--- a/arena_enrichment/output/arena_leaderboard_enriched.xlsx
+++ b/arena_enrichment/output/arena_leaderboard_enriched.xlsx
@@ -675,16 +675,16 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>1469.63</v>
+        <v>1469.87</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1463.09</v>
+        <v>1463.47</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1476.16</v>
+        <v>1476.28</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>9028</v>
+        <v>9670</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
@@ -746,16 +746,16 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>1463.18</v>
+        <v>1463.08</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1454.44</v>
+        <v>1454.32</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1471.91</v>
+        <v>1471.84</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>4163</v>
+        <v>4175</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
@@ -897,16 +897,16 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>1462.22</v>
+        <v>1462.08</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1452.97</v>
+        <v>1452.85</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1471.48</v>
+        <v>1471.3</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>3783</v>
+        <v>3823</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
@@ -968,16 +968,16 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>1458.18</v>
+        <v>1459.18</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1449.63</v>
+        <v>1451.07</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1466.74</v>
+        <v>1467.29</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>4355</v>
+        <v>4901</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
@@ -1119,16 +1119,16 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1457.15</v>
+        <v>1457</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1452.13</v>
+        <v>1452.08</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1462.17</v>
+        <v>1461.92</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>17733</v>
+        <v>18455</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
@@ -1270,13 +1270,13 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>1451.18</v>
+        <v>1450.98</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>1443.52</v>
+        <v>1443.32</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1458.84</v>
+        <v>1458.63</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>5818</v>
@@ -1421,16 +1421,16 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>1449.16</v>
+        <v>1448.77</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>1444.67</v>
+        <v>1444.33</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1453.66</v>
+        <v>1453.21</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>24213</v>
+        <v>24838</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
@@ -1572,16 +1572,16 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>1446.09</v>
+        <v>1446.68</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1441.25</v>
+        <v>1441.89</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1450.92</v>
+        <v>1451.47</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>19254</v>
+        <v>19928</v>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
@@ -1723,16 +1723,16 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>1442.78</v>
+        <v>1442.5</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>1436.66</v>
+        <v>1436.39</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1448.9</v>
+        <v>1448.62</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>12138</v>
+        <v>12143</v>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
@@ -1794,16 +1794,16 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>1439.44</v>
+        <v>1439.53</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>1430.14</v>
+        <v>1430.21</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1448.74</v>
+        <v>1448.86</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>3607</v>
+        <v>3605</v>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
@@ -1865,16 +1865,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1438.84</v>
+        <v>1438.4</v>
       </c>
       <c r="D12" t="n">
-        <v>1431.17</v>
+        <v>1430.72</v>
       </c>
       <c r="E12" t="n">
-        <v>1446.52</v>
+        <v>1446.07</v>
       </c>
       <c r="F12" t="n">
-        <v>5778</v>
+        <v>5781</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -2016,16 +2016,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1433.09</v>
+        <v>1432.59</v>
       </c>
       <c r="D13" t="n">
-        <v>1423.63</v>
+        <v>1423.15</v>
       </c>
       <c r="E13" t="n">
-        <v>1442.55</v>
+        <v>1442.03</v>
       </c>
       <c r="F13" t="n">
-        <v>3497</v>
+        <v>3510</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -2167,16 +2167,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1432.12</v>
+        <v>1431.58</v>
       </c>
       <c r="D14" t="n">
-        <v>1425.51</v>
+        <v>1424.97</v>
       </c>
       <c r="E14" t="n">
-        <v>1438.74</v>
+        <v>1438.19</v>
       </c>
       <c r="F14" t="n">
-        <v>8205</v>
+        <v>8206</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -2318,16 +2318,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1429.9</v>
+        <v>1429.88</v>
       </c>
       <c r="D15" t="n">
-        <v>1426.47</v>
+        <v>1426.49</v>
       </c>
       <c r="E15" t="n">
-        <v>1433.32</v>
+        <v>1433.28</v>
       </c>
       <c r="F15" t="n">
-        <v>49631</v>
+        <v>50311</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -2469,16 +2469,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1425.76</v>
+        <v>1425.64</v>
       </c>
       <c r="D16" t="n">
-        <v>1421.82</v>
+        <v>1421.7</v>
       </c>
       <c r="E16" t="n">
-        <v>1429.7</v>
+        <v>1429.58</v>
       </c>
       <c r="F16" t="n">
-        <v>35711</v>
+        <v>35713</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -2540,16 +2540,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1424.5</v>
+        <v>1424.44</v>
       </c>
       <c r="D17" t="n">
-        <v>1417.95</v>
+        <v>1417.89</v>
       </c>
       <c r="E17" t="n">
-        <v>1431.06</v>
+        <v>1430.99</v>
       </c>
       <c r="F17" t="n">
-        <v>9078</v>
+        <v>9083</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -2611,16 +2611,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1424.39</v>
+        <v>1424.2</v>
       </c>
       <c r="D18" t="n">
-        <v>1420.73</v>
+        <v>1420.54</v>
       </c>
       <c r="E18" t="n">
-        <v>1428.05</v>
+        <v>1427.86</v>
       </c>
       <c r="F18" t="n">
-        <v>44738</v>
+        <v>44831</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -2682,16 +2682,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1423.15</v>
+        <v>1422.93</v>
       </c>
       <c r="D19" t="n">
-        <v>1416.73</v>
+        <v>1416.53</v>
       </c>
       <c r="E19" t="n">
-        <v>1429.56</v>
+        <v>1429.34</v>
       </c>
       <c r="F19" t="n">
-        <v>11949</v>
+        <v>11953</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -2753,16 +2753,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1422.93</v>
+        <v>1422.52</v>
       </c>
       <c r="D20" t="n">
-        <v>1420.19</v>
+        <v>1419.79</v>
       </c>
       <c r="E20" t="n">
-        <v>1425.67</v>
+        <v>1425.25</v>
       </c>
       <c r="F20" t="n">
-        <v>85263</v>
+        <v>85971</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -2904,16 +2904,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1422.39</v>
+        <v>1422.02</v>
       </c>
       <c r="D21" t="n">
-        <v>1418.64</v>
+        <v>1418.28</v>
       </c>
       <c r="E21" t="n">
-        <v>1426.14</v>
+        <v>1425.76</v>
       </c>
       <c r="F21" t="n">
-        <v>38982</v>
+        <v>39104</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -2975,16 +2975,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1421.87</v>
+        <v>1421.79</v>
       </c>
       <c r="D22" t="n">
-        <v>1416.21</v>
+        <v>1416.13</v>
       </c>
       <c r="E22" t="n">
-        <v>1427.52</v>
+        <v>1427.44</v>
       </c>
       <c r="F22" t="n">
-        <v>18474</v>
+        <v>18472</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -3042,36 +3042,36 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>qwen3.5-122b-a10b</t>
+          <t>kimi-k2-0905-preview</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1418.3</v>
+        <v>1417.98</v>
       </c>
       <c r="D23" t="n">
-        <v>1413.15</v>
+        <v>1411.49</v>
       </c>
       <c r="E23" t="n">
-        <v>1423.44</v>
+        <v>1424.47</v>
       </c>
       <c r="F23" t="n">
-        <v>16040</v>
+        <v>11805</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alibaba</t>
+          <t>Moonshot</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
+          <t>Modified MIT</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>122</v>
+        <v>1000</v>
       </c>
       <c r="J23" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -3080,26 +3080,26 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>override</t>
         </is>
       </c>
       <c r="M23" t="n">
-        <v>244</v>
+        <v>2000</v>
       </c>
       <c r="N23" t="n">
-        <v>305</v>
+        <v>2500</v>
       </c>
       <c r="O23" t="n">
-        <v>122</v>
+        <v>1000</v>
       </c>
       <c r="P23" t="n">
-        <v>152.5</v>
+        <v>1250</v>
       </c>
       <c r="Q23" t="n">
-        <v>61</v>
+        <v>500</v>
       </c>
       <c r="R23" t="n">
-        <v>76.2</v>
+        <v>625</v>
       </c>
       <c r="S23" s="6" t="inlineStr">
         <is>
@@ -3111,9 +3111,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="U23" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="U23" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="V23" s="6" t="inlineStr">
@@ -3126,9 +3126,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="X23" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="X23" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="Y23" s="6" t="inlineStr">
@@ -3141,9 +3141,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AA23" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AA23" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AB23" s="6" t="inlineStr">
@@ -3151,14 +3151,14 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AC23" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AD23" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AC23" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD23" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AE23" s="6" t="inlineStr">
@@ -3166,14 +3166,14 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AF23" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AG23" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AF23" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AG23" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
@@ -3183,7 +3183,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>B200 SXM</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
     </row>
@@ -3193,36 +3193,36 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>kimi-k2-0905-preview</t>
+          <t>qwen3.5-122b-a10b</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1418.05</v>
+        <v>1417.86</v>
       </c>
       <c r="D24" t="n">
-        <v>1411.55</v>
+        <v>1412.8</v>
       </c>
       <c r="E24" t="n">
-        <v>1424.54</v>
+        <v>1422.91</v>
       </c>
       <c r="F24" t="n">
-        <v>11800</v>
+        <v>16762</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Moonshot</t>
+          <t>Alibaba</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Modified MIT</t>
+          <t>Apache 2.0</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1000</v>
+        <v>122</v>
       </c>
       <c r="J24" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -3231,26 +3231,26 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>name_parsing</t>
         </is>
       </c>
       <c r="M24" t="n">
-        <v>2000</v>
+        <v>244</v>
       </c>
       <c r="N24" t="n">
-        <v>2500</v>
+        <v>305</v>
       </c>
       <c r="O24" t="n">
-        <v>1000</v>
+        <v>122</v>
       </c>
       <c r="P24" t="n">
-        <v>1250</v>
+        <v>152.5</v>
       </c>
       <c r="Q24" t="n">
-        <v>500</v>
+        <v>61</v>
       </c>
       <c r="R24" t="n">
-        <v>625</v>
+        <v>76.2</v>
       </c>
       <c r="S24" s="6" t="inlineStr">
         <is>
@@ -3262,9 +3262,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="U24" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="U24" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="V24" s="6" t="inlineStr">
@@ -3277,9 +3277,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="X24" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="X24" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Y24" s="6" t="inlineStr">
@@ -3292,9 +3292,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AA24" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AA24" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AB24" s="6" t="inlineStr">
@@ -3302,14 +3302,14 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AC24" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AD24" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AC24" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AD24" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AE24" s="6" t="inlineStr">
@@ -3317,14 +3317,14 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AF24" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AG24" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AF24" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AG24" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AH24" t="inlineStr">
@@ -3334,7 +3334,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>B200 SXM</t>
         </is>
       </c>
     </row>
@@ -3348,16 +3348,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1417.68</v>
+        <v>1417.53</v>
       </c>
       <c r="D25" t="n">
-        <v>1411.67</v>
+        <v>1411.52</v>
       </c>
       <c r="E25" t="n">
-        <v>1423.69</v>
+        <v>1423.54</v>
       </c>
       <c r="F25" t="n">
-        <v>14992</v>
+        <v>14997</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -3415,148 +3415,68 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>kimi-k2-0711-preview</t>
+          <t>deepseek-v3.1-terminus-thinking</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1417.29</v>
+        <v>1417.13</v>
       </c>
       <c r="D26" t="n">
-        <v>1412.44</v>
+        <v>1407.15</v>
       </c>
       <c r="E26" t="n">
-        <v>1422.14</v>
+        <v>1427.11</v>
       </c>
       <c r="F26" t="n">
-        <v>27668</v>
+        <v>3467</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Moonshot</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Modified MIT</t>
-        </is>
-      </c>
-      <c r="I26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J26" t="n">
-        <v>32</v>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
-          <t>override</t>
-        </is>
-      </c>
-      <c r="M26" t="n">
-        <v>2000</v>
-      </c>
-      <c r="N26" t="n">
-        <v>2500</v>
-      </c>
-      <c r="O26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="P26" t="n">
-        <v>1250</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>500</v>
-      </c>
-      <c r="R26" t="n">
-        <v>625</v>
-      </c>
-      <c r="S26" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T26" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U26" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="V26" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W26" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X26" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Y26" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z26" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AA26" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AB26" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AC26" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AD26" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AE26" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AF26" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AG26" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr"/>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr"/>
+      <c r="AB26" t="inlineStr"/>
+      <c r="AC26" t="inlineStr"/>
+      <c r="AD26" t="inlineStr"/>
+      <c r="AE26" t="inlineStr"/>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="inlineStr"/>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -3566,68 +3486,148 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>deepseek-v3.1-terminus-thinking</t>
+          <t>kimi-k2-0711-preview</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1417.15</v>
+        <v>1417.11</v>
       </c>
       <c r="D27" t="n">
-        <v>1407.17</v>
+        <v>1412.25</v>
       </c>
       <c r="E27" t="n">
-        <v>1427.12</v>
+        <v>1421.96</v>
       </c>
       <c r="F27" t="n">
-        <v>3469</v>
+        <v>27661</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>DeepSeek</t>
+          <t>Moonshot</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
+          <t>Modified MIT</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J27" t="n">
+        <v>32</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr"/>
-      <c r="S27" t="inlineStr"/>
-      <c r="T27" t="inlineStr"/>
-      <c r="U27" t="inlineStr"/>
-      <c r="V27" t="inlineStr"/>
-      <c r="W27" t="inlineStr"/>
-      <c r="X27" t="inlineStr"/>
-      <c r="Y27" t="inlineStr"/>
-      <c r="Z27" t="inlineStr"/>
-      <c r="AA27" t="inlineStr"/>
-      <c r="AB27" t="inlineStr"/>
-      <c r="AC27" t="inlineStr"/>
-      <c r="AD27" t="inlineStr"/>
-      <c r="AE27" t="inlineStr"/>
-      <c r="AF27" t="inlineStr"/>
-      <c r="AG27" t="inlineStr"/>
+          <t>override</t>
+        </is>
+      </c>
+      <c r="M27" t="n">
+        <v>2000</v>
+      </c>
+      <c r="N27" t="n">
+        <v>2500</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1250</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>500</v>
+      </c>
+      <c r="R27" t="n">
+        <v>625</v>
+      </c>
+      <c r="S27" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T27" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U27" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V27" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W27" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X27" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y27" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z27" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA27" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AB27" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AC27" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD27" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE27" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF27" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AG27" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
     </row>
@@ -3641,16 +3641,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1416.78</v>
+        <v>1416.72</v>
       </c>
       <c r="D28" t="n">
-        <v>1410.17</v>
+        <v>1410.11</v>
       </c>
       <c r="E28" t="n">
-        <v>1423.39</v>
+        <v>1423.33</v>
       </c>
       <c r="F28" t="n">
-        <v>11759</v>
+        <v>11762</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -3712,13 +3712,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1415.87</v>
+        <v>1415.76</v>
       </c>
       <c r="D29" t="n">
-        <v>1406.26</v>
+        <v>1406.15</v>
       </c>
       <c r="E29" t="n">
-        <v>1425.48</v>
+        <v>1425.37</v>
       </c>
       <c r="F29" t="n">
         <v>3713</v>
@@ -3783,16 +3783,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1415.6</v>
+        <v>1415.47</v>
       </c>
       <c r="D30" t="n">
-        <v>1409.12</v>
+        <v>1408.98</v>
       </c>
       <c r="E30" t="n">
-        <v>1422.09</v>
+        <v>1421.95</v>
       </c>
       <c r="F30" t="n">
-        <v>11528</v>
+        <v>11529</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -3934,16 +3934,16 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1415.14</v>
+        <v>1414.62</v>
       </c>
       <c r="D31" t="n">
-        <v>1411.46</v>
+        <v>1410.95</v>
       </c>
       <c r="E31" t="n">
-        <v>1418.81</v>
+        <v>1418.29</v>
       </c>
       <c r="F31" t="n">
-        <v>41361</v>
+        <v>41363</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -4085,13 +4085,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1411.06</v>
+        <v>1410.97</v>
       </c>
       <c r="D32" t="n">
-        <v>1406.18</v>
+        <v>1406.09</v>
       </c>
       <c r="E32" t="n">
-        <v>1415.94</v>
+        <v>1415.85</v>
       </c>
       <c r="F32" t="n">
         <v>24352</v>
@@ -4236,16 +4236,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1405.09</v>
+        <v>1404.63</v>
       </c>
       <c r="D33" t="n">
-        <v>1399.89</v>
+        <v>1399.5</v>
       </c>
       <c r="E33" t="n">
-        <v>1410.28</v>
+        <v>1409.75</v>
       </c>
       <c r="F33" t="n">
-        <v>15682</v>
+        <v>16330</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -4387,16 +4387,16 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1403.48</v>
+        <v>1404.1</v>
       </c>
       <c r="D34" t="n">
-        <v>1397.2</v>
+        <v>1397.96</v>
       </c>
       <c r="E34" t="n">
-        <v>1409.76</v>
+        <v>1410.24</v>
       </c>
       <c r="F34" t="n">
-        <v>10307</v>
+        <v>10943</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -4458,16 +4458,16 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1402.96</v>
+        <v>1402.9</v>
       </c>
       <c r="D35" t="n">
-        <v>1398.47</v>
+        <v>1398.4</v>
       </c>
       <c r="E35" t="n">
-        <v>1407.46</v>
+        <v>1407.4</v>
       </c>
       <c r="F35" t="n">
-        <v>38253</v>
+        <v>38251</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -4609,16 +4609,16 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1401.5</v>
+        <v>1401.45</v>
       </c>
       <c r="D36" t="n">
-        <v>1396.72</v>
+        <v>1396.67</v>
       </c>
       <c r="E36" t="n">
-        <v>1406.28</v>
+        <v>1406.23</v>
       </c>
       <c r="F36" t="n">
-        <v>22907</v>
+        <v>22912</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -4760,16 +4760,16 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1401.25</v>
+        <v>1401.08</v>
       </c>
       <c r="D37" t="n">
-        <v>1394.89</v>
+        <v>1394.72</v>
       </c>
       <c r="E37" t="n">
-        <v>1407.62</v>
+        <v>1407.45</v>
       </c>
       <c r="F37" t="n">
-        <v>11417</v>
+        <v>11416</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -4907,68 +4907,148 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>minimax-m2.5</t>
+          <t>qwen3-235b-a22b-thinking-2507</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1399.45</v>
+        <v>1399.15</v>
       </c>
       <c r="D38" t="n">
-        <v>1394.71</v>
+        <v>1392.62</v>
       </c>
       <c r="E38" t="n">
-        <v>1404.19</v>
+        <v>1405.67</v>
       </c>
       <c r="F38" t="n">
-        <v>21236</v>
+        <v>9008</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>MiniMax</t>
+          <t>Alibaba</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Modified MIT</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
+          <t>Apache 2.0</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>235</v>
+      </c>
+      <c r="J38" t="n">
+        <v>22</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr"/>
-      <c r="R38" t="inlineStr"/>
-      <c r="S38" t="inlineStr"/>
-      <c r="T38" t="inlineStr"/>
-      <c r="U38" t="inlineStr"/>
-      <c r="V38" t="inlineStr"/>
-      <c r="W38" t="inlineStr"/>
-      <c r="X38" t="inlineStr"/>
-      <c r="Y38" t="inlineStr"/>
-      <c r="Z38" t="inlineStr"/>
-      <c r="AA38" t="inlineStr"/>
-      <c r="AB38" t="inlineStr"/>
-      <c r="AC38" t="inlineStr"/>
-      <c r="AD38" t="inlineStr"/>
-      <c r="AE38" t="inlineStr"/>
-      <c r="AF38" t="inlineStr"/>
-      <c r="AG38" t="inlineStr"/>
+          <t>name_parsing</t>
+        </is>
+      </c>
+      <c r="M38" t="n">
+        <v>470</v>
+      </c>
+      <c r="N38" t="n">
+        <v>587.5</v>
+      </c>
+      <c r="O38" t="n">
+        <v>235</v>
+      </c>
+      <c r="P38" t="n">
+        <v>293.8</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>117.5</v>
+      </c>
+      <c r="R38" t="n">
+        <v>146.9</v>
+      </c>
+      <c r="S38" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T38" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U38" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V38" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W38" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X38" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y38" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z38" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA38" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AB38" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AC38" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD38" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE38" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF38" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AG38" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
     </row>
@@ -4978,148 +5058,68 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>qwen3-235b-a22b-thinking-2507</t>
+          <t>minimax-m2.5</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1399.35</v>
+        <v>1398.32</v>
       </c>
       <c r="D39" t="n">
-        <v>1392.82</v>
+        <v>1393.63</v>
       </c>
       <c r="E39" t="n">
-        <v>1405.88</v>
+        <v>1403</v>
       </c>
       <c r="F39" t="n">
-        <v>9008</v>
+        <v>21952</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alibaba</t>
+          <t>MiniMax</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
-        </is>
-      </c>
-      <c r="I39" t="n">
-        <v>235</v>
-      </c>
-      <c r="J39" t="n">
-        <v>22</v>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+          <t>Modified MIT</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
-          <t>name_parsing</t>
-        </is>
-      </c>
-      <c r="M39" t="n">
-        <v>470</v>
-      </c>
-      <c r="N39" t="n">
-        <v>587.5</v>
-      </c>
-      <c r="O39" t="n">
-        <v>235</v>
-      </c>
-      <c r="P39" t="n">
-        <v>293.8</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>117.5</v>
-      </c>
-      <c r="R39" t="n">
-        <v>146.9</v>
-      </c>
-      <c r="S39" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T39" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U39" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="V39" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W39" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X39" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Y39" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z39" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AA39" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AB39" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AC39" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AD39" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AE39" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AF39" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AG39" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr"/>
+      <c r="V39" t="inlineStr"/>
+      <c r="W39" t="inlineStr"/>
+      <c r="X39" t="inlineStr"/>
+      <c r="Y39" t="inlineStr"/>
+      <c r="Z39" t="inlineStr"/>
+      <c r="AA39" t="inlineStr"/>
+      <c r="AB39" t="inlineStr"/>
+      <c r="AC39" t="inlineStr"/>
+      <c r="AD39" t="inlineStr"/>
+      <c r="AE39" t="inlineStr"/>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="inlineStr"/>
       <c r="AH39" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -5133,13 +5133,13 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1397.66</v>
+        <v>1397.61</v>
       </c>
       <c r="D40" t="n">
-        <v>1392.8</v>
+        <v>1392.75</v>
       </c>
       <c r="E40" t="n">
-        <v>1402.52</v>
+        <v>1402.48</v>
       </c>
       <c r="F40" t="n">
         <v>18524</v>
@@ -5280,20 +5280,20 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>qwen3-vl-235b-a22b-thinking</t>
+          <t>qwen3.5-35b-a3b</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1395.84</v>
+        <v>1396.19</v>
       </c>
       <c r="D41" t="n">
-        <v>1389.05</v>
+        <v>1391.12</v>
       </c>
       <c r="E41" t="n">
-        <v>1402.63</v>
+        <v>1401.27</v>
       </c>
       <c r="F41" t="n">
-        <v>7947</v>
+        <v>16914</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -5306,10 +5306,10 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>235</v>
+        <v>35</v>
       </c>
       <c r="J41" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -5322,36 +5322,36 @@
         </is>
       </c>
       <c r="M41" t="n">
-        <v>470</v>
+        <v>70</v>
       </c>
       <c r="N41" t="n">
-        <v>587.5</v>
+        <v>87.5</v>
       </c>
       <c r="O41" t="n">
-        <v>235</v>
+        <v>35</v>
       </c>
       <c r="P41" t="n">
-        <v>293.8</v>
+        <v>43.8</v>
       </c>
       <c r="Q41" t="n">
-        <v>117.5</v>
+        <v>17.5</v>
       </c>
       <c r="R41" t="n">
-        <v>146.9</v>
-      </c>
-      <c r="S41" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T41" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U41" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
+        <v>21.9</v>
+      </c>
+      <c r="S41" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T41" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U41" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="V41" s="6" t="inlineStr">
@@ -5359,39 +5359,39 @@
           <t>No</t>
         </is>
       </c>
-      <c r="W41" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X41" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Y41" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z41" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AA41" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AB41" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AC41" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="W41" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X41" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y41" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z41" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AA41" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB41" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AC41" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AD41" s="5" t="inlineStr">
@@ -5399,14 +5399,14 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="AE41" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AF41" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AE41" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AF41" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AG41" s="5" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>RTX PRO 6000</t>
         </is>
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>H100 SXM</t>
         </is>
       </c>
     </row>
@@ -5431,20 +5431,20 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>qwen3.5-35b-a3b</t>
+          <t>qwen3-vl-235b-a22b-thinking</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1395.36</v>
+        <v>1395.74</v>
       </c>
       <c r="D42" t="n">
-        <v>1390.21</v>
+        <v>1388.95</v>
       </c>
       <c r="E42" t="n">
-        <v>1400.5</v>
+        <v>1402.53</v>
       </c>
       <c r="F42" t="n">
-        <v>16250</v>
+        <v>7951</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -5457,10 +5457,10 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>35</v>
+        <v>235</v>
       </c>
       <c r="J42" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -5473,36 +5473,36 @@
         </is>
       </c>
       <c r="M42" t="n">
-        <v>70</v>
+        <v>470</v>
       </c>
       <c r="N42" t="n">
-        <v>87.5</v>
+        <v>587.5</v>
       </c>
       <c r="O42" t="n">
-        <v>35</v>
+        <v>235</v>
       </c>
       <c r="P42" t="n">
-        <v>43.8</v>
+        <v>293.8</v>
       </c>
       <c r="Q42" t="n">
-        <v>17.5</v>
+        <v>117.5</v>
       </c>
       <c r="R42" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="S42" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="T42" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="U42" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
+        <v>146.9</v>
+      </c>
+      <c r="S42" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T42" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U42" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="V42" s="6" t="inlineStr">
@@ -5510,39 +5510,39 @@
           <t>No</t>
         </is>
       </c>
-      <c r="W42" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X42" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Y42" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z42" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AA42" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB42" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AC42" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="W42" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X42" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y42" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z42" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA42" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AB42" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AC42" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AD42" s="5" t="inlineStr">
@@ -5550,14 +5550,14 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="AE42" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AF42" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AE42" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF42" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AG42" s="5" t="inlineStr">
@@ -5567,12 +5567,12 @@
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>RTX PRO 6000</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
     </row>
@@ -5586,16 +5586,16 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1395.04</v>
+        <v>1395</v>
       </c>
       <c r="D43" t="n">
-        <v>1391.17</v>
+        <v>1391.14</v>
       </c>
       <c r="E43" t="n">
-        <v>1398.9</v>
+        <v>1398.87</v>
       </c>
       <c r="F43" t="n">
-        <v>45546</v>
+        <v>45552</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -5737,16 +5737,16 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1392.82</v>
+        <v>1392.42</v>
       </c>
       <c r="D44" t="n">
-        <v>1388.89</v>
+        <v>1388.51</v>
       </c>
       <c r="E44" t="n">
-        <v>1396.75</v>
+        <v>1396.32</v>
       </c>
       <c r="F44" t="n">
-        <v>33906</v>
+        <v>34578</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -5808,16 +5808,16 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1392.42</v>
+        <v>1391.76</v>
       </c>
       <c r="D45" t="n">
-        <v>1387.81</v>
+        <v>1387.19</v>
       </c>
       <c r="E45" t="n">
-        <v>1397.02</v>
+        <v>1396.32</v>
       </c>
       <c r="F45" t="n">
-        <v>21987</v>
+        <v>22678</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -5875,68 +5875,148 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>mimo-v2-flash (thinking)</t>
+          <t>qwen3-coder-480b-a35b-instruct</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1387.43</v>
+        <v>1387.36</v>
       </c>
       <c r="D46" t="n">
-        <v>1381.15</v>
+        <v>1382.41</v>
       </c>
       <c r="E46" t="n">
-        <v>1393.7</v>
+        <v>1392.31</v>
       </c>
       <c r="F46" t="n">
-        <v>10980</v>
+        <v>25762</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Xiaomi</t>
+          <t>Alibaba</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
+          <t>Apache 2.0</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>480</v>
+      </c>
+      <c r="J46" t="n">
+        <v>35</v>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr"/>
-      <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="inlineStr"/>
-      <c r="R46" t="inlineStr"/>
-      <c r="S46" t="inlineStr"/>
-      <c r="T46" t="inlineStr"/>
-      <c r="U46" t="inlineStr"/>
-      <c r="V46" t="inlineStr"/>
-      <c r="W46" t="inlineStr"/>
-      <c r="X46" t="inlineStr"/>
-      <c r="Y46" t="inlineStr"/>
-      <c r="Z46" t="inlineStr"/>
-      <c r="AA46" t="inlineStr"/>
-      <c r="AB46" t="inlineStr"/>
-      <c r="AC46" t="inlineStr"/>
-      <c r="AD46" t="inlineStr"/>
-      <c r="AE46" t="inlineStr"/>
-      <c r="AF46" t="inlineStr"/>
-      <c r="AG46" t="inlineStr"/>
+          <t>name_parsing</t>
+        </is>
+      </c>
+      <c r="M46" t="n">
+        <v>960</v>
+      </c>
+      <c r="N46" t="n">
+        <v>1200</v>
+      </c>
+      <c r="O46" t="n">
+        <v>480</v>
+      </c>
+      <c r="P46" t="n">
+        <v>600</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>240</v>
+      </c>
+      <c r="R46" t="n">
+        <v>300</v>
+      </c>
+      <c r="S46" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T46" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U46" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V46" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W46" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X46" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y46" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z46" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA46" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AB46" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AC46" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD46" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE46" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF46" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AG46" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AH46" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
     </row>
@@ -5946,148 +6026,68 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>qwen3-coder-480b-a35b-instruct</t>
+          <t>mimo-v2-flash (thinking)</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1387.41</v>
+        <v>1387.34</v>
       </c>
       <c r="D47" t="n">
-        <v>1382.46</v>
+        <v>1381.07</v>
       </c>
       <c r="E47" t="n">
-        <v>1392.35</v>
+        <v>1393.61</v>
       </c>
       <c r="F47" t="n">
-        <v>25762</v>
+        <v>10988</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alibaba</t>
+          <t>Xiaomi</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
-        </is>
-      </c>
-      <c r="I47" t="n">
-        <v>480</v>
-      </c>
-      <c r="J47" t="n">
-        <v>35</v>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
-          <t>name_parsing</t>
-        </is>
-      </c>
-      <c r="M47" t="n">
-        <v>960</v>
-      </c>
-      <c r="N47" t="n">
-        <v>1200</v>
-      </c>
-      <c r="O47" t="n">
-        <v>480</v>
-      </c>
-      <c r="P47" t="n">
-        <v>600</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>240</v>
-      </c>
-      <c r="R47" t="n">
-        <v>300</v>
-      </c>
-      <c r="S47" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T47" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U47" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="V47" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W47" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X47" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Y47" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z47" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AA47" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AB47" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AC47" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AD47" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AE47" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AF47" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AG47" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr"/>
+      <c r="S47" t="inlineStr"/>
+      <c r="T47" t="inlineStr"/>
+      <c r="U47" t="inlineStr"/>
+      <c r="V47" t="inlineStr"/>
+      <c r="W47" t="inlineStr"/>
+      <c r="X47" t="inlineStr"/>
+      <c r="Y47" t="inlineStr"/>
+      <c r="Z47" t="inlineStr"/>
+      <c r="AA47" t="inlineStr"/>
+      <c r="AB47" t="inlineStr"/>
+      <c r="AC47" t="inlineStr"/>
+      <c r="AD47" t="inlineStr"/>
+      <c r="AE47" t="inlineStr"/>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="inlineStr"/>
       <c r="AH47" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -6101,16 +6101,16 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1385.32</v>
+        <v>1385.13</v>
       </c>
       <c r="D48" t="n">
-        <v>1380.06</v>
+        <v>1379.87</v>
       </c>
       <c r="E48" t="n">
-        <v>1390.58</v>
+        <v>1390.38</v>
       </c>
       <c r="F48" t="n">
-        <v>17150</v>
+        <v>17169</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -6172,16 +6172,16 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1383.3</v>
+        <v>1383.18</v>
       </c>
       <c r="D49" t="n">
-        <v>1378.42</v>
+        <v>1378.31</v>
       </c>
       <c r="E49" t="n">
-        <v>1388.18</v>
+        <v>1388.06</v>
       </c>
       <c r="F49" t="n">
-        <v>23768</v>
+        <v>23771</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -6323,16 +6323,16 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1377.78</v>
+        <v>1377.33</v>
       </c>
       <c r="D50" t="n">
-        <v>1366.49</v>
+        <v>1366.05</v>
       </c>
       <c r="E50" t="n">
-        <v>1389.06</v>
+        <v>1388.6</v>
       </c>
       <c r="F50" t="n">
-        <v>2806</v>
+        <v>2807</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -6394,16 +6394,16 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1374.6</v>
+        <v>1374.43</v>
       </c>
       <c r="D51" t="n">
-        <v>1369.91</v>
+        <v>1369.74</v>
       </c>
       <c r="E51" t="n">
-        <v>1379.29</v>
+        <v>1379.12</v>
       </c>
       <c r="F51" t="n">
-        <v>26285</v>
+        <v>26287</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -6545,16 +6545,16 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1374.55</v>
+        <v>1374.42</v>
       </c>
       <c r="D52" t="n">
-        <v>1369.39</v>
+        <v>1369.35</v>
       </c>
       <c r="E52" t="n">
-        <v>1379.71</v>
+        <v>1379.48</v>
       </c>
       <c r="F52" t="n">
-        <v>17170</v>
+        <v>17933</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -6696,16 +6696,16 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1372.97</v>
+        <v>1372.85</v>
       </c>
       <c r="D53" t="n">
-        <v>1368.73</v>
+        <v>1368.6</v>
       </c>
       <c r="E53" t="n">
-        <v>1377.22</v>
+        <v>1377.09</v>
       </c>
       <c r="F53" t="n">
-        <v>31136</v>
+        <v>31130</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -6767,16 +6767,16 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1369.21</v>
+        <v>1369.07</v>
       </c>
       <c r="D54" t="n">
-        <v>1363.37</v>
+        <v>1363.23</v>
       </c>
       <c r="E54" t="n">
-        <v>1375.05</v>
+        <v>1374.9</v>
       </c>
       <c r="F54" t="n">
-        <v>13718</v>
+        <v>13713</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -6918,16 +6918,16 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1368.07</v>
+        <v>1367.93</v>
       </c>
       <c r="D55" t="n">
-        <v>1362.24</v>
+        <v>1362.1</v>
       </c>
       <c r="E55" t="n">
-        <v>1373.89</v>
+        <v>1373.75</v>
       </c>
       <c r="F55" t="n">
-        <v>11769</v>
+        <v>11780</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -6989,10 +6989,10 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1365.59</v>
+        <v>1365.58</v>
       </c>
       <c r="D56" t="n">
-        <v>1361.93</v>
+        <v>1361.92</v>
       </c>
       <c r="E56" t="n">
         <v>1369.25</v>
@@ -7140,13 +7140,13 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1363.36</v>
+        <v>1363.32</v>
       </c>
       <c r="D57" t="n">
-        <v>1359.09</v>
+        <v>1359.05</v>
       </c>
       <c r="E57" t="n">
-        <v>1367.63</v>
+        <v>1367.59</v>
       </c>
       <c r="F57" t="n">
         <v>35252</v>
@@ -7211,16 +7211,16 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1361.31</v>
+        <v>1361.47</v>
       </c>
       <c r="D58" t="n">
-        <v>1354.04</v>
+        <v>1354.21</v>
       </c>
       <c r="E58" t="n">
-        <v>1368.58</v>
+        <v>1368.72</v>
       </c>
       <c r="F58" t="n">
-        <v>7408</v>
+        <v>7419</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -7362,13 +7362,13 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1358.23</v>
+        <v>1358.17</v>
       </c>
       <c r="D59" t="n">
-        <v>1353.51</v>
+        <v>1353.45</v>
       </c>
       <c r="E59" t="n">
-        <v>1362.95</v>
+        <v>1362.89</v>
       </c>
       <c r="F59" t="n">
         <v>21770</v>
@@ -7513,16 +7513,16 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1357.2</v>
+        <v>1357.05</v>
       </c>
       <c r="D60" t="n">
-        <v>1352</v>
+        <v>1351.85</v>
       </c>
       <c r="E60" t="n">
-        <v>1362.39</v>
+        <v>1362.24</v>
       </c>
       <c r="F60" t="n">
-        <v>17722</v>
+        <v>17723</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -7584,16 +7584,16 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1356.43</v>
+        <v>1356.41</v>
       </c>
       <c r="D61" t="n">
-        <v>1348.06</v>
+        <v>1348.05</v>
       </c>
       <c r="E61" t="n">
-        <v>1364.8</v>
+        <v>1364.76</v>
       </c>
       <c r="F61" t="n">
-        <v>5332</v>
+        <v>5334</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -7735,16 +7735,16 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1353.56</v>
+        <v>1353.52</v>
       </c>
       <c r="D62" t="n">
-        <v>1350.12</v>
+        <v>1350.08</v>
       </c>
       <c r="E62" t="n">
-        <v>1357</v>
+        <v>1356.96</v>
       </c>
       <c r="F62" t="n">
-        <v>56346</v>
+        <v>56341</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -7802,148 +7802,68 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>gpt-oss-120b</t>
+          <t>glm-4.5v</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1353.19</v>
+        <v>1353.07</v>
       </c>
       <c r="D63" t="n">
-        <v>1348.85</v>
+        <v>1344.73</v>
       </c>
       <c r="E63" t="n">
-        <v>1357.54</v>
+        <v>1361.41</v>
       </c>
       <c r="F63" t="n">
-        <v>30674</v>
+        <v>4969</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Z.ai</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
-        </is>
-      </c>
-      <c r="I63" t="n">
-        <v>117</v>
-      </c>
-      <c r="J63" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr">
         <is>
-          <t>override</t>
-        </is>
-      </c>
-      <c r="M63" t="n">
-        <v>234</v>
-      </c>
-      <c r="N63" t="n">
-        <v>292.5</v>
-      </c>
-      <c r="O63" t="n">
-        <v>117</v>
-      </c>
-      <c r="P63" t="n">
-        <v>146.2</v>
-      </c>
-      <c r="Q63" t="n">
-        <v>58.5</v>
-      </c>
-      <c r="R63" t="n">
-        <v>73.09999999999999</v>
-      </c>
-      <c r="S63" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T63" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U63" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="V63" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W63" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X63" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Y63" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z63" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AA63" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB63" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AC63" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AD63" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AE63" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AF63" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AG63" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr"/>
+      <c r="P63" t="inlineStr"/>
+      <c r="Q63" t="inlineStr"/>
+      <c r="R63" t="inlineStr"/>
+      <c r="S63" t="inlineStr"/>
+      <c r="T63" t="inlineStr"/>
+      <c r="U63" t="inlineStr"/>
+      <c r="V63" t="inlineStr"/>
+      <c r="W63" t="inlineStr"/>
+      <c r="X63" t="inlineStr"/>
+      <c r="Y63" t="inlineStr"/>
+      <c r="Z63" t="inlineStr"/>
+      <c r="AA63" t="inlineStr"/>
+      <c r="AB63" t="inlineStr"/>
+      <c r="AC63" t="inlineStr"/>
+      <c r="AD63" t="inlineStr"/>
+      <c r="AE63" t="inlineStr"/>
+      <c r="AF63" t="inlineStr"/>
+      <c r="AG63" t="inlineStr"/>
       <c r="AH63" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>B200 SXM</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -7953,68 +7873,148 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>glm-4.5v</t>
+          <t>gpt-oss-120b</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1353.13</v>
+        <v>1353.04</v>
       </c>
       <c r="D64" t="n">
-        <v>1344.79</v>
+        <v>1348.69</v>
       </c>
       <c r="E64" t="n">
-        <v>1361.47</v>
+        <v>1357.39</v>
       </c>
       <c r="F64" t="n">
-        <v>4968</v>
+        <v>30677</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Z.ai</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
+          <t>Apache 2.0</t>
+        </is>
+      </c>
+      <c r="I64" t="n">
+        <v>117</v>
+      </c>
+      <c r="J64" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
-      <c r="O64" t="inlineStr"/>
-      <c r="P64" t="inlineStr"/>
-      <c r="Q64" t="inlineStr"/>
-      <c r="R64" t="inlineStr"/>
-      <c r="S64" t="inlineStr"/>
-      <c r="T64" t="inlineStr"/>
-      <c r="U64" t="inlineStr"/>
-      <c r="V64" t="inlineStr"/>
-      <c r="W64" t="inlineStr"/>
-      <c r="X64" t="inlineStr"/>
-      <c r="Y64" t="inlineStr"/>
-      <c r="Z64" t="inlineStr"/>
-      <c r="AA64" t="inlineStr"/>
-      <c r="AB64" t="inlineStr"/>
-      <c r="AC64" t="inlineStr"/>
-      <c r="AD64" t="inlineStr"/>
-      <c r="AE64" t="inlineStr"/>
-      <c r="AF64" t="inlineStr"/>
-      <c r="AG64" t="inlineStr"/>
+          <t>override</t>
+        </is>
+      </c>
+      <c r="M64" t="n">
+        <v>234</v>
+      </c>
+      <c r="N64" t="n">
+        <v>292.5</v>
+      </c>
+      <c r="O64" t="n">
+        <v>117</v>
+      </c>
+      <c r="P64" t="n">
+        <v>146.2</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="R64" t="n">
+        <v>73.09999999999999</v>
+      </c>
+      <c r="S64" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T64" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U64" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V64" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W64" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X64" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y64" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z64" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA64" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB64" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AC64" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AD64" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE64" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF64" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AG64" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AH64" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>B200 SXM</t>
         </is>
       </c>
     </row>
@@ -8028,16 +8028,16 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1347.7</v>
+        <v>1347.65</v>
       </c>
       <c r="D65" t="n">
-        <v>1340.3</v>
+        <v>1340.25</v>
       </c>
       <c r="E65" t="n">
-        <v>1355.1</v>
+        <v>1355.05</v>
       </c>
       <c r="F65" t="n">
-        <v>6560</v>
+        <v>6558</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -8095,36 +8095,36 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>qwen3-32b</t>
+          <t>llama-3.1-nemotron-ultra-253b-v1</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1347.04</v>
+        <v>1346.96</v>
       </c>
       <c r="D66" t="n">
-        <v>1337.58</v>
+        <v>1335.27</v>
       </c>
       <c r="E66" t="n">
-        <v>1356.5</v>
+        <v>1358.66</v>
       </c>
       <c r="F66" t="n">
-        <v>3926</v>
+        <v>2549</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alibaba</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
+          <t>Nvidia Open Model</t>
         </is>
       </c>
       <c r="I66" t="n">
-        <v>32</v>
+        <v>253</v>
       </c>
       <c r="J66" t="n">
-        <v>32</v>
+        <v>253</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
@@ -8137,76 +8137,76 @@
         </is>
       </c>
       <c r="M66" t="n">
-        <v>64</v>
+        <v>506</v>
       </c>
       <c r="N66" t="n">
-        <v>80</v>
+        <v>632.5</v>
       </c>
       <c r="O66" t="n">
-        <v>32</v>
+        <v>253</v>
       </c>
       <c r="P66" t="n">
-        <v>40</v>
+        <v>316.2</v>
       </c>
       <c r="Q66" t="n">
-        <v>16</v>
+        <v>126.5</v>
       </c>
       <c r="R66" t="n">
-        <v>20</v>
-      </c>
-      <c r="S66" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="T66" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="U66" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="V66" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W66" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X66" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Y66" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z66" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AA66" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB66" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AC66" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
+        <v>158.1</v>
+      </c>
+      <c r="S66" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T66" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U66" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V66" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W66" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X66" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y66" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z66" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA66" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AB66" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AC66" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AD66" s="5" t="inlineStr">
@@ -8214,14 +8214,14 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="AE66" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AF66" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AE66" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF66" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AG66" s="5" t="inlineStr">
@@ -8231,12 +8231,12 @@
       </c>
       <c r="AH66" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
       <c r="AI66" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
     </row>
@@ -8246,36 +8246,36 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>llama-3.1-nemotron-ultra-253b-v1</t>
+          <t>qwen3-32b</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1347.02</v>
+        <v>1346.95</v>
       </c>
       <c r="D67" t="n">
-        <v>1335.32</v>
+        <v>1337.49</v>
       </c>
       <c r="E67" t="n">
-        <v>1358.72</v>
+        <v>1356.42</v>
       </c>
       <c r="F67" t="n">
-        <v>2549</v>
+        <v>3926</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Alibaba</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Nvidia Open Model</t>
+          <t>Apache 2.0</t>
         </is>
       </c>
       <c r="I67" t="n">
-        <v>253</v>
+        <v>32</v>
       </c>
       <c r="J67" t="n">
-        <v>253</v>
+        <v>32</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
@@ -8288,76 +8288,76 @@
         </is>
       </c>
       <c r="M67" t="n">
-        <v>506</v>
+        <v>64</v>
       </c>
       <c r="N67" t="n">
-        <v>632.5</v>
+        <v>80</v>
       </c>
       <c r="O67" t="n">
-        <v>253</v>
+        <v>32</v>
       </c>
       <c r="P67" t="n">
-        <v>316.2</v>
+        <v>40</v>
       </c>
       <c r="Q67" t="n">
-        <v>126.5</v>
+        <v>16</v>
       </c>
       <c r="R67" t="n">
-        <v>158.1</v>
-      </c>
-      <c r="S67" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T67" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U67" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="V67" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W67" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X67" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Y67" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z67" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AA67" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AB67" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AC67" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
+        <v>20</v>
+      </c>
+      <c r="S67" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T67" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U67" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V67" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W67" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X67" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y67" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z67" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AA67" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB67" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AC67" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AD67" s="5" t="inlineStr">
@@ -8365,14 +8365,14 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="AE67" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AF67" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AE67" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AF67" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AG67" s="5" t="inlineStr">
@@ -8382,12 +8382,12 @@
       </c>
       <c r="AH67" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>H100 SXM</t>
         </is>
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>H100 SXM</t>
         </is>
       </c>
     </row>
@@ -8401,13 +8401,13 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1346.02</v>
+        <v>1346</v>
       </c>
       <c r="D68" t="n">
-        <v>1338.28</v>
+        <v>1338.27</v>
       </c>
       <c r="E68" t="n">
-        <v>1353.76</v>
+        <v>1353.74</v>
       </c>
       <c r="F68" t="n">
         <v>6876</v>
@@ -8552,16 +8552,16 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1345.81</v>
+        <v>1345.78</v>
       </c>
       <c r="D69" t="n">
-        <v>1338.55</v>
+        <v>1338.51</v>
       </c>
       <c r="E69" t="n">
-        <v>1353.07</v>
+        <v>1353.04</v>
       </c>
       <c r="F69" t="n">
-        <v>7018</v>
+        <v>7016</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -8623,16 +8623,16 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1342.71</v>
+        <v>1342.76</v>
       </c>
       <c r="D70" t="n">
-        <v>1332.74</v>
+        <v>1332.79</v>
       </c>
       <c r="E70" t="n">
-        <v>1352.69</v>
+        <v>1352.74</v>
       </c>
       <c r="F70" t="n">
-        <v>3347</v>
+        <v>3345</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -8774,13 +8774,13 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1341.68</v>
+        <v>1341.64</v>
       </c>
       <c r="D71" t="n">
-        <v>1332.17</v>
+        <v>1332.13</v>
       </c>
       <c r="E71" t="n">
-        <v>1351.19</v>
+        <v>1351.15</v>
       </c>
       <c r="F71" t="n">
         <v>3829</v>
@@ -8925,16 +8925,16 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1335.85</v>
+        <v>1335.79</v>
       </c>
       <c r="D72" t="n">
-        <v>1331.42</v>
+        <v>1331.36</v>
       </c>
       <c r="E72" t="n">
-        <v>1340.28</v>
+        <v>1340.22</v>
       </c>
       <c r="F72" t="n">
-        <v>25406</v>
+        <v>25405</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -9082,7 +9082,7 @@
         <v>1330.87</v>
       </c>
       <c r="E73" t="n">
-        <v>1338.24</v>
+        <v>1338.25</v>
       </c>
       <c r="F73" t="n">
         <v>41375</v>
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1332.74</v>
+        <v>1332.73</v>
       </c>
       <c r="D74" t="n">
-        <v>1329.17</v>
+        <v>1329.16</v>
       </c>
       <c r="E74" t="n">
-        <v>1336.32</v>
+        <v>1336.31</v>
       </c>
       <c r="F74" t="n">
         <v>59656</v>
@@ -9378,16 +9378,16 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>1330.67</v>
+        <v>1330.54</v>
       </c>
       <c r="D75" t="n">
-        <v>1324.57</v>
+        <v>1324.44</v>
       </c>
       <c r="E75" t="n">
-        <v>1336.77</v>
+        <v>1336.63</v>
       </c>
       <c r="F75" t="n">
-        <v>12238</v>
+        <v>12251</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -9529,16 +9529,16 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>1327.77</v>
+        <v>1327.9</v>
       </c>
       <c r="D76" t="n">
-        <v>1306.36</v>
+        <v>1306.49</v>
       </c>
       <c r="E76" t="n">
-        <v>1349.18</v>
+        <v>1349.31</v>
       </c>
       <c r="F76" t="n">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -9680,13 +9680,13 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1327.49</v>
+        <v>1327.44</v>
       </c>
       <c r="D77" t="n">
-        <v>1315.33</v>
+        <v>1315.27</v>
       </c>
       <c r="E77" t="n">
-        <v>1339.66</v>
+        <v>1339.6</v>
       </c>
       <c r="F77" t="n">
         <v>2218</v>
@@ -9831,16 +9831,16 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1327.23</v>
+        <v>1327.15</v>
       </c>
       <c r="D78" t="n">
-        <v>1322.51</v>
+        <v>1322.42</v>
       </c>
       <c r="E78" t="n">
-        <v>1331.95</v>
+        <v>1331.87</v>
       </c>
       <c r="F78" t="n">
-        <v>26507</v>
+        <v>26506</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -9982,16 +9982,16 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>1326.81</v>
+        <v>1326.79</v>
       </c>
       <c r="D79" t="n">
-        <v>1322.56</v>
+        <v>1322.55</v>
       </c>
       <c r="E79" t="n">
-        <v>1331.05</v>
+        <v>1331.04</v>
       </c>
       <c r="F79" t="n">
-        <v>40010</v>
+        <v>40008</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -10133,13 +10133,13 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1323.15</v>
+        <v>1323.09</v>
       </c>
       <c r="D80" t="n">
-        <v>1314.88</v>
+        <v>1314.82</v>
       </c>
       <c r="E80" t="n">
-        <v>1331.41</v>
+        <v>1331.36</v>
       </c>
       <c r="F80" t="n">
         <v>6795</v>
@@ -10204,16 +10204,16 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1322.37</v>
+        <v>1322.27</v>
       </c>
       <c r="D81" t="n">
-        <v>1317.67</v>
+        <v>1317.57</v>
       </c>
       <c r="E81" t="n">
-        <v>1327.07</v>
+        <v>1326.97</v>
       </c>
       <c r="F81" t="n">
-        <v>30319</v>
+        <v>30323</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -10355,13 +10355,13 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>1320.62</v>
+        <v>1320.54</v>
       </c>
       <c r="D82" t="n">
-        <v>1313.41</v>
+        <v>1313.32</v>
       </c>
       <c r="E82" t="n">
-        <v>1327.83</v>
+        <v>1327.75</v>
       </c>
       <c r="F82" t="n">
         <v>7158</v>
@@ -10426,13 +10426,13 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>1318.12</v>
+        <v>1318.08</v>
       </c>
       <c r="D83" t="n">
-        <v>1314.68</v>
+        <v>1314.63</v>
       </c>
       <c r="E83" t="n">
-        <v>1321.57</v>
+        <v>1321.53</v>
       </c>
       <c r="F83" t="n">
         <v>54756</v>
@@ -10577,16 +10577,16 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>1318.05</v>
+        <v>1318.02</v>
       </c>
       <c r="D84" t="n">
-        <v>1312.91</v>
+        <v>1312.88</v>
       </c>
       <c r="E84" t="n">
-        <v>1323.19</v>
+        <v>1323.16</v>
       </c>
       <c r="F84" t="n">
-        <v>22616</v>
+        <v>22619</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -10728,13 +10728,13 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>1317.63</v>
+        <v>1317.59</v>
       </c>
       <c r="D85" t="n">
-        <v>1311.94</v>
+        <v>1311.9</v>
       </c>
       <c r="E85" t="n">
-        <v>1323.32</v>
+        <v>1323.29</v>
       </c>
       <c r="F85" t="n">
         <v>16478</v>
@@ -10799,16 +10799,16 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>1317.33</v>
+        <v>1317.21</v>
       </c>
       <c r="D86" t="n">
-        <v>1310.97</v>
+        <v>1310.85</v>
       </c>
       <c r="E86" t="n">
-        <v>1323.69</v>
+        <v>1323.58</v>
       </c>
       <c r="F86" t="n">
-        <v>10640</v>
+        <v>10638</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -10950,16 +10950,16 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>1317.09</v>
+        <v>1316.71</v>
       </c>
       <c r="D87" t="n">
-        <v>1311.52</v>
+        <v>1311.14</v>
       </c>
       <c r="E87" t="n">
-        <v>1322.67</v>
+        <v>1322.29</v>
       </c>
       <c r="F87" t="n">
-        <v>15526</v>
+        <v>15535</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -11101,13 +11101,13 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>1314.11</v>
+        <v>1314.05</v>
       </c>
       <c r="D88" t="n">
-        <v>1309.58</v>
+        <v>1309.52</v>
       </c>
       <c r="E88" t="n">
-        <v>1318.64</v>
+        <v>1318.59</v>
       </c>
       <c r="F88" t="n">
         <v>24739</v>
@@ -11252,13 +11252,13 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>1313.58</v>
+        <v>1313.57</v>
       </c>
       <c r="D89" t="n">
-        <v>1309.68</v>
+        <v>1309.65</v>
       </c>
       <c r="E89" t="n">
-        <v>1317.49</v>
+        <v>1317.48</v>
       </c>
       <c r="F89" t="n">
         <v>45459</v>
@@ -11403,13 +11403,13 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>1306.74</v>
+        <v>1306.69</v>
       </c>
       <c r="D90" t="n">
-        <v>1302.05</v>
+        <v>1301.99</v>
       </c>
       <c r="E90" t="n">
-        <v>1311.43</v>
+        <v>1311.38</v>
       </c>
       <c r="F90" t="n">
         <v>24572</v>
@@ -11474,13 +11474,13 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>1305.8</v>
+        <v>1305.76</v>
       </c>
       <c r="D91" t="n">
-        <v>1300.13</v>
+        <v>1300.09</v>
       </c>
       <c r="E91" t="n">
-        <v>1311.47</v>
+        <v>1311.43</v>
       </c>
       <c r="F91" t="n">
         <v>19621</v>
@@ -11625,13 +11625,13 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>1305.36</v>
+        <v>1305.2</v>
       </c>
       <c r="D92" t="n">
-        <v>1297.17</v>
+        <v>1297.02</v>
       </c>
       <c r="E92" t="n">
-        <v>1313.55</v>
+        <v>1313.39</v>
       </c>
       <c r="F92" t="n">
         <v>5965</v>
@@ -11776,13 +11776,13 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>1304.88</v>
+        <v>1304.86</v>
       </c>
       <c r="D93" t="n">
-        <v>1300.47</v>
+        <v>1300.45</v>
       </c>
       <c r="E93" t="n">
-        <v>1309.3</v>
+        <v>1309.28</v>
       </c>
       <c r="F93" t="n">
         <v>28073</v>
@@ -11843,36 +11843,36 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>mistral-small-3.1-24b-instruct-2503</t>
+          <t>gemma-3-4b-it</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1303.1</v>
+        <v>1303.04</v>
       </c>
       <c r="D94" t="n">
-        <v>1298.6</v>
+        <v>1293.72</v>
       </c>
       <c r="E94" t="n">
-        <v>1307.6</v>
+        <v>1312.36</v>
       </c>
       <c r="F94" t="n">
-        <v>33239</v>
+        <v>4171</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Mistral</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
+          <t>Gemma</t>
         </is>
       </c>
       <c r="I94" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="J94" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
@@ -11885,22 +11885,22 @@
         </is>
       </c>
       <c r="M94" t="n">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="N94" t="n">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="O94" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="P94" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="Q94" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="R94" t="n">
-        <v>15</v>
+        <v>2.5</v>
       </c>
       <c r="S94" s="5" t="inlineStr">
         <is>
@@ -11994,36 +11994,36 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>gemma-3-4b-it</t>
+          <t>mistral-small-3.1-24b-instruct-2503</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1303.07</v>
+        <v>1303.02</v>
       </c>
       <c r="D95" t="n">
-        <v>1293.75</v>
+        <v>1298.51</v>
       </c>
       <c r="E95" t="n">
-        <v>1312.39</v>
+        <v>1307.52</v>
       </c>
       <c r="F95" t="n">
-        <v>4171</v>
+        <v>33241</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Mistral</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Gemma</t>
+          <t>Apache 2.0</t>
         </is>
       </c>
       <c r="I95" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="J95" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
@@ -12036,22 +12036,22 @@
         </is>
       </c>
       <c r="M95" t="n">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="N95" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="O95" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="P95" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="Q95" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="R95" t="n">
-        <v>2.5</v>
+        <v>15</v>
       </c>
       <c r="S95" s="5" t="inlineStr">
         <is>
@@ -12149,13 +12149,13 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>1302.45</v>
+        <v>1302.41</v>
       </c>
       <c r="D96" t="n">
-        <v>1298.4</v>
+        <v>1298.36</v>
       </c>
       <c r="E96" t="n">
-        <v>1306.5</v>
+        <v>1306.46</v>
       </c>
       <c r="F96" t="n">
         <v>39406</v>
@@ -12300,13 +12300,13 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1298.61</v>
+        <v>1298.56</v>
       </c>
       <c r="D97" t="n">
-        <v>1290.85</v>
+        <v>1290.8</v>
       </c>
       <c r="E97" t="n">
-        <v>1306.37</v>
+        <v>1306.32</v>
       </c>
       <c r="F97" t="n">
         <v>7140</v>
@@ -12451,13 +12451,13 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>1293.01</v>
+        <v>1292.96</v>
       </c>
       <c r="D98" t="n">
-        <v>1289.3</v>
+        <v>1289.24</v>
       </c>
       <c r="E98" t="n">
-        <v>1296.73</v>
+        <v>1296.67</v>
       </c>
       <c r="F98" t="n">
         <v>55240</v>
@@ -12602,13 +12602,13 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>1288.45</v>
+        <v>1288.43</v>
       </c>
       <c r="D99" t="n">
-        <v>1281.15</v>
+        <v>1281.13</v>
       </c>
       <c r="E99" t="n">
-        <v>1295.76</v>
+        <v>1295.74</v>
       </c>
       <c r="F99" t="n">
         <v>8662</v>
@@ -12673,13 +12673,13 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>1288</v>
+        <v>1287.99</v>
       </c>
       <c r="D100" t="n">
-        <v>1284.64</v>
+        <v>1284.63</v>
       </c>
       <c r="E100" t="n">
-        <v>1291.36</v>
+        <v>1291.35</v>
       </c>
       <c r="F100" t="n">
         <v>75754</v>
@@ -12824,16 +12824,16 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1286.78</v>
+        <v>1286.77</v>
       </c>
       <c r="D101" t="n">
-        <v>1278.39</v>
+        <v>1278.38</v>
       </c>
       <c r="E101" t="n">
         <v>1295.17</v>
       </c>
       <c r="F101" t="n">
-        <v>5690</v>
+        <v>5689</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
@@ -12975,13 +12975,13 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>1285.97</v>
+        <v>1285.92</v>
       </c>
       <c r="D102" t="n">
-        <v>1275.5</v>
+        <v>1275.45</v>
       </c>
       <c r="E102" t="n">
-        <v>1296.45</v>
+        <v>1296.4</v>
       </c>
       <c r="F102" t="n">
         <v>2846</v>
@@ -13126,10 +13126,10 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>1285.62</v>
+        <v>1285.61</v>
       </c>
       <c r="D103" t="n">
-        <v>1275.64</v>
+        <v>1275.63</v>
       </c>
       <c r="E103" t="n">
         <v>1295.59</v>
@@ -13277,16 +13277,16 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>1285.48</v>
+        <v>1285.06</v>
       </c>
       <c r="D104" t="n">
-        <v>1278.24</v>
+        <v>1277.83</v>
       </c>
       <c r="E104" t="n">
-        <v>1292.71</v>
+        <v>1292.29</v>
       </c>
       <c r="F104" t="n">
-        <v>8504</v>
+        <v>8514</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
@@ -13428,13 +13428,13 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>1279.19</v>
+        <v>1279.15</v>
       </c>
       <c r="D105" t="n">
-        <v>1272.33</v>
+        <v>1272.29</v>
       </c>
       <c r="E105" t="n">
-        <v>1286.05</v>
+        <v>1286.01</v>
       </c>
       <c r="F105" t="n">
         <v>10072</v>
@@ -13579,13 +13579,13 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>1276.51</v>
+        <v>1276.49</v>
       </c>
       <c r="D106" t="n">
-        <v>1271.18</v>
+        <v>1271.17</v>
       </c>
       <c r="E106" t="n">
-        <v>1281.83</v>
+        <v>1281.82</v>
       </c>
       <c r="F106" t="n">
         <v>19659</v>
@@ -13730,13 +13730,13 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>1275.74</v>
+        <v>1275.72</v>
       </c>
       <c r="D107" t="n">
-        <v>1269.17</v>
+        <v>1269.15</v>
       </c>
       <c r="E107" t="n">
-        <v>1282.31</v>
+        <v>1282.3</v>
       </c>
       <c r="F107" t="n">
         <v>9866</v>
@@ -13881,10 +13881,10 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>1275.51</v>
+        <v>1275.5</v>
       </c>
       <c r="D108" t="n">
-        <v>1271.93</v>
+        <v>1271.92</v>
       </c>
       <c r="E108" t="n">
         <v>1279.09</v>
@@ -14032,13 +14032,13 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>1273.68</v>
+        <v>1273.66</v>
       </c>
       <c r="D109" t="n">
-        <v>1267.79</v>
+        <v>1267.77</v>
       </c>
       <c r="E109" t="n">
-        <v>1279.57</v>
+        <v>1279.55</v>
       </c>
       <c r="F109" t="n">
         <v>14681</v>
@@ -14183,13 +14183,13 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>1270.09</v>
+        <v>1270.06</v>
       </c>
       <c r="D110" t="n">
-        <v>1261.97</v>
+        <v>1261.93</v>
       </c>
       <c r="E110" t="n">
-        <v>1278.21</v>
+        <v>1278.18</v>
       </c>
       <c r="F110" t="n">
         <v>5432</v>
@@ -14334,13 +14334,13 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>1266.56</v>
+        <v>1266.53</v>
       </c>
       <c r="D111" t="n">
-        <v>1261.69</v>
+        <v>1261.66</v>
       </c>
       <c r="E111" t="n">
-        <v>1271.42</v>
+        <v>1271.4</v>
       </c>
       <c r="F111" t="n">
         <v>27124</v>
@@ -14488,7 +14488,7 @@
         <v>1265.47</v>
       </c>
       <c r="D112" t="n">
-        <v>1261.68</v>
+        <v>1261.67</v>
       </c>
       <c r="E112" t="n">
         <v>1269.27</v>
@@ -14639,7 +14639,7 @@
         <v>1263.79</v>
       </c>
       <c r="D113" t="n">
-        <v>1257.5</v>
+        <v>1257.51</v>
       </c>
       <c r="E113" t="n">
         <v>1270.07</v>
@@ -14787,10 +14787,10 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>1261.02</v>
+        <v>1261.01</v>
       </c>
       <c r="D114" t="n">
-        <v>1256.7</v>
+        <v>1256.69</v>
       </c>
       <c r="E114" t="n">
         <v>1265.34</v>
@@ -14858,13 +14858,13 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>1261.01</v>
+        <v>1260.98</v>
       </c>
       <c r="D115" t="n">
-        <v>1256.07</v>
+        <v>1256.04</v>
       </c>
       <c r="E115" t="n">
-        <v>1265.95</v>
+        <v>1265.93</v>
       </c>
       <c r="F115" t="n">
         <v>37325</v>
@@ -15009,13 +15009,13 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>1255.68</v>
+        <v>1255.65</v>
       </c>
       <c r="D116" t="n">
-        <v>1251.11</v>
+        <v>1251.08</v>
       </c>
       <c r="E116" t="n">
-        <v>1260.25</v>
+        <v>1260.23</v>
       </c>
       <c r="F116" t="n">
         <v>24126</v>
@@ -15160,13 +15160,13 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>1251.39</v>
+        <v>1251.35</v>
       </c>
       <c r="D117" t="n">
-        <v>1240.6</v>
+        <v>1240.55</v>
       </c>
       <c r="E117" t="n">
-        <v>1262.18</v>
+        <v>1262.14</v>
       </c>
       <c r="F117" t="n">
         <v>3334</v>
@@ -15462,13 +15462,13 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>1238.69</v>
+        <v>1238.68</v>
       </c>
       <c r="D119" t="n">
-        <v>1231.47</v>
+        <v>1231.45</v>
       </c>
       <c r="E119" t="n">
-        <v>1245.91</v>
+        <v>1245.9</v>
       </c>
       <c r="F119" t="n">
         <v>8858</v>
@@ -15533,13 +15533,13 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>1236.81</v>
+        <v>1236.79</v>
       </c>
       <c r="D120" t="n">
-        <v>1227.71</v>
+        <v>1227.69</v>
       </c>
       <c r="E120" t="n">
-        <v>1245.91</v>
+        <v>1245.88</v>
       </c>
       <c r="F120" t="n">
         <v>4781</v>
@@ -15684,13 +15684,13 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>1233.29</v>
+        <v>1233.26</v>
       </c>
       <c r="D121" t="n">
-        <v>1227.73</v>
+        <v>1227.71</v>
       </c>
       <c r="E121" t="n">
-        <v>1238.84</v>
+        <v>1238.82</v>
       </c>
       <c r="F121" t="n">
         <v>26195</v>
@@ -15989,7 +15989,7 @@
         <v>1228.55</v>
       </c>
       <c r="D123" t="n">
-        <v>1224</v>
+        <v>1223.99</v>
       </c>
       <c r="E123" t="n">
         <v>1233.11</v>
@@ -16137,13 +16137,13 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>1226</v>
+        <v>1225.99</v>
       </c>
       <c r="D124" t="n">
-        <v>1221.22</v>
+        <v>1221.21</v>
       </c>
       <c r="E124" t="n">
-        <v>1230.79</v>
+        <v>1230.78</v>
       </c>
       <c r="F124" t="n">
         <v>54036</v>
@@ -16359,13 +16359,13 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>1222.5</v>
+        <v>1222.47</v>
       </c>
       <c r="D126" t="n">
-        <v>1215.54</v>
+        <v>1215.51</v>
       </c>
       <c r="E126" t="n">
-        <v>1229.47</v>
+        <v>1229.44</v>
       </c>
       <c r="F126" t="n">
         <v>9818</v>
@@ -16510,13 +16510,13 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>1220.49</v>
+        <v>1220.43</v>
       </c>
       <c r="D127" t="n">
-        <v>1209.8</v>
+        <v>1209.74</v>
       </c>
       <c r="E127" t="n">
-        <v>1231.17</v>
+        <v>1231.11</v>
       </c>
       <c r="F127" t="n">
         <v>2896</v>
@@ -16661,13 +16661,13 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>1212.6</v>
+        <v>1212.56</v>
       </c>
       <c r="D128" t="n">
-        <v>1207.56</v>
+        <v>1207.52</v>
       </c>
       <c r="E128" t="n">
-        <v>1217.63</v>
+        <v>1217.6</v>
       </c>
       <c r="F128" t="n">
         <v>24146</v>
@@ -16812,13 +16812,13 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>1211.88</v>
+        <v>1211.89</v>
       </c>
       <c r="D129" t="n">
-        <v>1201.07</v>
+        <v>1201.08</v>
       </c>
       <c r="E129" t="n">
-        <v>1222.68</v>
+        <v>1222.69</v>
       </c>
       <c r="F129" t="n">
         <v>4652</v>
@@ -16963,13 +16963,13 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>1211.16</v>
+        <v>1211.09</v>
       </c>
       <c r="D130" t="n">
-        <v>1207.03</v>
+        <v>1206.96</v>
       </c>
       <c r="E130" t="n">
-        <v>1215.29</v>
+        <v>1215.23</v>
       </c>
       <c r="F130" t="n">
         <v>49605</v>
@@ -17117,7 +17117,7 @@
         <v>1207.64</v>
       </c>
       <c r="D131" t="n">
-        <v>1196.52</v>
+        <v>1196.53</v>
       </c>
       <c r="E131" t="n">
         <v>1218.75</v>
@@ -17416,13 +17416,13 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>1198.94</v>
+        <v>1198.92</v>
       </c>
       <c r="D133" t="n">
-        <v>1194.87</v>
+        <v>1194.85</v>
       </c>
       <c r="E133" t="n">
-        <v>1203.01</v>
+        <v>1203</v>
       </c>
       <c r="F133" t="n">
         <v>46616</v>
@@ -17567,10 +17567,10 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>1197.08</v>
+        <v>1197.07</v>
       </c>
       <c r="D134" t="n">
-        <v>1191.92</v>
+        <v>1191.91</v>
       </c>
       <c r="E134" t="n">
         <v>1202.23</v>
@@ -17721,7 +17721,7 @@
         <v>1196.22</v>
       </c>
       <c r="D135" t="n">
-        <v>1191.95</v>
+        <v>1191.94</v>
       </c>
       <c r="E135" t="n">
         <v>1200.49</v>
@@ -17869,7 +17869,7 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>1194.19</v>
+        <v>1194.2</v>
       </c>
       <c r="D136" t="n">
         <v>1188.08</v>
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>1190.63</v>
+        <v>1190.59</v>
       </c>
       <c r="D137" t="n">
-        <v>1183.45</v>
+        <v>1183.41</v>
       </c>
       <c r="E137" t="n">
-        <v>1197.81</v>
+        <v>1197.77</v>
       </c>
       <c r="F137" t="n">
         <v>9901</v>
@@ -18091,7 +18091,7 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>1190.1</v>
+        <v>1190.09</v>
       </c>
       <c r="D138" t="n">
         <v>1182.97</v>
@@ -18245,10 +18245,10 @@
         <v>1183.76</v>
       </c>
       <c r="D139" t="n">
-        <v>1174.3</v>
+        <v>1174.31</v>
       </c>
       <c r="E139" t="n">
-        <v>1193.21</v>
+        <v>1193.22</v>
       </c>
       <c r="F139" t="n">
         <v>8214</v>
@@ -18393,13 +18393,13 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>1183.52</v>
+        <v>1183.53</v>
       </c>
       <c r="D140" t="n">
-        <v>1172.01</v>
+        <v>1172.02</v>
       </c>
       <c r="E140" t="n">
-        <v>1195.03</v>
+        <v>1195.04</v>
       </c>
       <c r="F140" t="n">
         <v>4932</v>
@@ -18544,13 +18544,13 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>1183</v>
+        <v>1182.98</v>
       </c>
       <c r="D141" t="n">
-        <v>1176.17</v>
+        <v>1176.15</v>
       </c>
       <c r="E141" t="n">
-        <v>1189.83</v>
+        <v>1189.82</v>
       </c>
       <c r="F141" t="n">
         <v>15483</v>
@@ -18695,13 +18695,13 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>1181.4</v>
+        <v>1181.41</v>
       </c>
       <c r="D142" t="n">
-        <v>1173.39</v>
+        <v>1173.41</v>
       </c>
       <c r="E142" t="n">
-        <v>1189.4</v>
+        <v>1189.42</v>
       </c>
       <c r="F142" t="n">
         <v>12637</v>
@@ -18766,13 +18766,13 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>1181.38</v>
+        <v>1181.39</v>
       </c>
       <c r="D143" t="n">
-        <v>1171.7</v>
+        <v>1171.72</v>
       </c>
       <c r="E143" t="n">
-        <v>1191.05</v>
+        <v>1191.07</v>
       </c>
       <c r="F143" t="n">
         <v>7968</v>
@@ -18837,13 +18837,13 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>1181.34</v>
+        <v>1181.36</v>
       </c>
       <c r="D144" t="n">
-        <v>1172.65</v>
+        <v>1172.68</v>
       </c>
       <c r="E144" t="n">
-        <v>1190.03</v>
+        <v>1190.05</v>
       </c>
       <c r="F144" t="n">
         <v>6638</v>
@@ -18988,13 +18988,13 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>1180.18</v>
+        <v>1180.2</v>
       </c>
       <c r="D145" t="n">
-        <v>1174.1</v>
+        <v>1174.12</v>
       </c>
       <c r="E145" t="n">
-        <v>1186.25</v>
+        <v>1186.28</v>
       </c>
       <c r="F145" t="n">
         <v>23893</v>
@@ -19139,13 +19139,13 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>1178.62</v>
+        <v>1178.64</v>
       </c>
       <c r="D146" t="n">
-        <v>1172.71</v>
+        <v>1172.72</v>
       </c>
       <c r="E146" t="n">
-        <v>1184.54</v>
+        <v>1184.56</v>
       </c>
       <c r="F146" t="n">
         <v>32832</v>
@@ -19361,13 +19361,13 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>1177.04</v>
+        <v>1177.03</v>
       </c>
       <c r="D148" t="n">
-        <v>1167.22</v>
+        <v>1167.21</v>
       </c>
       <c r="E148" t="n">
-        <v>1186.86</v>
+        <v>1186.85</v>
       </c>
       <c r="F148" t="n">
         <v>6535</v>
@@ -19512,13 +19512,13 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>1174.35</v>
+        <v>1174.37</v>
       </c>
       <c r="D149" t="n">
-        <v>1163.92</v>
+        <v>1163.95</v>
       </c>
       <c r="E149" t="n">
-        <v>1184.77</v>
+        <v>1184.79</v>
       </c>
       <c r="F149" t="n">
         <v>5006</v>
@@ -19663,13 +19663,13 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>1171.87</v>
+        <v>1171.88</v>
       </c>
       <c r="D150" t="n">
         <v>1165.66</v>
       </c>
       <c r="E150" t="n">
-        <v>1178.08</v>
+        <v>1178.09</v>
       </c>
       <c r="F150" t="n">
         <v>22479</v>
@@ -19814,13 +19814,13 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>1170.71</v>
+        <v>1170.73</v>
       </c>
       <c r="D151" t="n">
-        <v>1163.3</v>
+        <v>1163.31</v>
       </c>
       <c r="E151" t="n">
-        <v>1178.13</v>
+        <v>1178.14</v>
       </c>
       <c r="F151" t="n">
         <v>16056</v>
@@ -19965,13 +19965,13 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>1170.22</v>
+        <v>1170.21</v>
       </c>
       <c r="D152" t="n">
-        <v>1164.3</v>
+        <v>1164.29</v>
       </c>
       <c r="E152" t="n">
-        <v>1176.14</v>
+        <v>1176.13</v>
       </c>
       <c r="F152" t="n">
         <v>17766</v>
@@ -20116,13 +20116,13 @@
         </is>
       </c>
       <c r="C153" t="n">
-        <v>1169.89</v>
+        <v>1169.9</v>
       </c>
       <c r="D153" t="n">
-        <v>1164.38</v>
+        <v>1164.4</v>
       </c>
       <c r="E153" t="n">
-        <v>1175.4</v>
+        <v>1175.41</v>
       </c>
       <c r="F153" t="n">
         <v>38492</v>
@@ -20267,10 +20267,10 @@
         </is>
       </c>
       <c r="C154" t="n">
-        <v>1166.6</v>
+        <v>1166.61</v>
       </c>
       <c r="D154" t="n">
-        <v>1158.53</v>
+        <v>1158.54</v>
       </c>
       <c r="E154" t="n">
         <v>1174.68</v>
@@ -20418,13 +20418,13 @@
         </is>
       </c>
       <c r="C155" t="n">
-        <v>1165.97</v>
+        <v>1165.95</v>
       </c>
       <c r="D155" t="n">
-        <v>1158.27</v>
+        <v>1158.25</v>
       </c>
       <c r="E155" t="n">
-        <v>1173.67</v>
+        <v>1173.65</v>
       </c>
       <c r="F155" t="n">
         <v>7936</v>
@@ -20569,7 +20569,7 @@
         </is>
       </c>
       <c r="C156" t="n">
-        <v>1163.8</v>
+        <v>1163.79</v>
       </c>
       <c r="D156" t="n">
         <v>1151.86</v>
@@ -20720,13 +20720,13 @@
         </is>
       </c>
       <c r="C157" t="n">
-        <v>1155.8</v>
+        <v>1155.7</v>
       </c>
       <c r="D157" t="n">
-        <v>1144.29</v>
+        <v>1144.2</v>
       </c>
       <c r="E157" t="n">
-        <v>1167.3</v>
+        <v>1167.21</v>
       </c>
       <c r="F157" t="n">
         <v>3231</v>
@@ -20871,13 +20871,13 @@
         </is>
       </c>
       <c r="C158" t="n">
-        <v>1155.25</v>
+        <v>1155.27</v>
       </c>
       <c r="D158" t="n">
-        <v>1146.86</v>
+        <v>1146.88</v>
       </c>
       <c r="E158" t="n">
-        <v>1163.65</v>
+        <v>1163.66</v>
       </c>
       <c r="F158" t="n">
         <v>6837</v>
@@ -21022,13 +21022,13 @@
         </is>
       </c>
       <c r="C159" t="n">
-        <v>1154.25</v>
+        <v>1154.22</v>
       </c>
       <c r="D159" t="n">
-        <v>1141.63</v>
+        <v>1141.6</v>
       </c>
       <c r="E159" t="n">
-        <v>1166.87</v>
+        <v>1166.84</v>
       </c>
       <c r="F159" t="n">
         <v>3585</v>
@@ -21173,13 +21173,13 @@
         </is>
       </c>
       <c r="C160" t="n">
-        <v>1151.41</v>
+        <v>1151.4</v>
       </c>
       <c r="D160" t="n">
         <v>1138.2</v>
       </c>
       <c r="E160" t="n">
-        <v>1164.61</v>
+        <v>1164.6</v>
       </c>
       <c r="F160" t="n">
         <v>4155</v>
@@ -21324,10 +21324,10 @@
         </is>
       </c>
       <c r="C161" t="n">
-        <v>1151.1</v>
+        <v>1151.11</v>
       </c>
       <c r="D161" t="n">
-        <v>1135.72</v>
+        <v>1135.73</v>
       </c>
       <c r="E161" t="n">
         <v>1166.49</v>
@@ -21475,13 +21475,13 @@
         </is>
       </c>
       <c r="C162" t="n">
-        <v>1149.24</v>
+        <v>1149.25</v>
       </c>
       <c r="D162" t="n">
-        <v>1136.95</v>
+        <v>1136.96</v>
       </c>
       <c r="E162" t="n">
-        <v>1161.53</v>
+        <v>1161.54</v>
       </c>
       <c r="F162" t="n">
         <v>2572</v>
@@ -21626,13 +21626,13 @@
         </is>
       </c>
       <c r="C163" t="n">
-        <v>1148.64</v>
+        <v>1148.63</v>
       </c>
       <c r="D163" t="n">
         <v>1141.98</v>
       </c>
       <c r="E163" t="n">
-        <v>1155.3</v>
+        <v>1155.29</v>
       </c>
       <c r="F163" t="n">
         <v>19402</v>
@@ -21777,13 +21777,13 @@
         </is>
       </c>
       <c r="C164" t="n">
-        <v>1148.31</v>
+        <v>1148.32</v>
       </c>
       <c r="D164" t="n">
-        <v>1139.05</v>
+        <v>1139.06</v>
       </c>
       <c r="E164" t="n">
-        <v>1157.57</v>
+        <v>1157.58</v>
       </c>
       <c r="F164" t="n">
         <v>7044</v>
@@ -21928,13 +21928,13 @@
         </is>
       </c>
       <c r="C165" t="n">
-        <v>1146.23</v>
+        <v>1146.25</v>
       </c>
       <c r="D165" t="n">
-        <v>1129.11</v>
+        <v>1129.14</v>
       </c>
       <c r="E165" t="n">
-        <v>1163.34</v>
+        <v>1163.36</v>
       </c>
       <c r="F165" t="n">
         <v>1295</v>
@@ -22082,10 +22082,10 @@
         <v>1142.94</v>
       </c>
       <c r="D166" t="n">
-        <v>1133.04</v>
+        <v>1133.05</v>
       </c>
       <c r="E166" t="n">
-        <v>1152.83</v>
+        <v>1152.84</v>
       </c>
       <c r="F166" t="n">
         <v>4737</v>
@@ -22233,10 +22233,10 @@
         <v>1142.21</v>
       </c>
       <c r="D167" t="n">
-        <v>1135.78</v>
+        <v>1135.77</v>
       </c>
       <c r="E167" t="n">
-        <v>1148.65</v>
+        <v>1148.64</v>
       </c>
       <c r="F167" t="n">
         <v>12297</v>
@@ -22381,13 +22381,13 @@
         </is>
       </c>
       <c r="C168" t="n">
-        <v>1140.61</v>
+        <v>1140.63</v>
       </c>
       <c r="D168" t="n">
-        <v>1133.88</v>
+        <v>1133.9</v>
       </c>
       <c r="E168" t="n">
-        <v>1147.34</v>
+        <v>1147.36</v>
       </c>
       <c r="F168" t="n">
         <v>19174</v>
@@ -22532,13 +22532,13 @@
         </is>
       </c>
       <c r="C169" t="n">
-        <v>1140.04</v>
+        <v>1140.05</v>
       </c>
       <c r="D169" t="n">
-        <v>1133.32</v>
+        <v>1133.33</v>
       </c>
       <c r="E169" t="n">
-        <v>1146.75</v>
+        <v>1146.76</v>
       </c>
       <c r="F169" t="n">
         <v>19367</v>
@@ -22686,10 +22686,10 @@
         <v>1137.71</v>
       </c>
       <c r="D170" t="n">
-        <v>1126.74</v>
+        <v>1126.75</v>
       </c>
       <c r="E170" t="n">
-        <v>1148.67</v>
+        <v>1148.68</v>
       </c>
       <c r="F170" t="n">
         <v>4964</v>
@@ -22834,7 +22834,7 @@
         </is>
       </c>
       <c r="C171" t="n">
-        <v>1135.76</v>
+        <v>1135.77</v>
       </c>
       <c r="D171" t="n">
         <v>1126.26</v>
@@ -22985,13 +22985,13 @@
         </is>
       </c>
       <c r="C172" t="n">
-        <v>1135.67</v>
+        <v>1135.69</v>
       </c>
       <c r="D172" t="n">
-        <v>1126.77</v>
+        <v>1126.78</v>
       </c>
       <c r="E172" t="n">
-        <v>1144.58</v>
+        <v>1144.59</v>
       </c>
       <c r="F172" t="n">
         <v>7366</v>
@@ -23136,13 +23136,13 @@
         </is>
       </c>
       <c r="C173" t="n">
-        <v>1130.05</v>
+        <v>1130.04</v>
       </c>
       <c r="D173" t="n">
         <v>1121.2</v>
       </c>
       <c r="E173" t="n">
-        <v>1138.9</v>
+        <v>1138.89</v>
       </c>
       <c r="F173" t="n">
         <v>11118</v>
@@ -23287,13 +23287,13 @@
         </is>
       </c>
       <c r="C174" t="n">
-        <v>1128.38</v>
+        <v>1128.4</v>
       </c>
       <c r="D174" t="n">
-        <v>1120.95</v>
+        <v>1120.97</v>
       </c>
       <c r="E174" t="n">
-        <v>1135.81</v>
+        <v>1135.83</v>
       </c>
       <c r="F174" t="n">
         <v>20685</v>
@@ -23441,7 +23441,7 @@
         <v>1127.47</v>
       </c>
       <c r="D175" t="n">
-        <v>1121.08</v>
+        <v>1121.07</v>
       </c>
       <c r="E175" t="n">
         <v>1133.87</v>
@@ -23589,13 +23589,13 @@
         </is>
       </c>
       <c r="C176" t="n">
-        <v>1126.36</v>
+        <v>1126.35</v>
       </c>
       <c r="D176" t="n">
-        <v>1114.22</v>
+        <v>1114.21</v>
       </c>
       <c r="E176" t="n">
-        <v>1138.51</v>
+        <v>1138.5</v>
       </c>
       <c r="F176" t="n">
         <v>2921</v>
@@ -23743,7 +23743,7 @@
         <v>1125.94</v>
       </c>
       <c r="D177" t="n">
-        <v>1110.28</v>
+        <v>1110.29</v>
       </c>
       <c r="E177" t="n">
         <v>1141.6</v>
@@ -23891,13 +23891,13 @@
         </is>
       </c>
       <c r="C178" t="n">
-        <v>1120.11</v>
+        <v>1120.12</v>
       </c>
       <c r="D178" t="n">
-        <v>1109.11</v>
+        <v>1109.12</v>
       </c>
       <c r="E178" t="n">
-        <v>1131.1</v>
+        <v>1131.11</v>
       </c>
       <c r="F178" t="n">
         <v>5182</v>
@@ -24042,13 +24042,13 @@
         </is>
       </c>
       <c r="C179" t="n">
-        <v>1118.23</v>
+        <v>1118.22</v>
       </c>
       <c r="D179" t="n">
         <v>1100.03</v>
       </c>
       <c r="E179" t="n">
-        <v>1136.42</v>
+        <v>1136.41</v>
       </c>
       <c r="F179" t="n">
         <v>1143</v>
@@ -24193,13 +24193,13 @@
         </is>
       </c>
       <c r="C180" t="n">
-        <v>1114.09</v>
+        <v>1114.13</v>
       </c>
       <c r="D180" t="n">
-        <v>1106.35</v>
+        <v>1106.39</v>
       </c>
       <c r="E180" t="n">
-        <v>1121.83</v>
+        <v>1121.87</v>
       </c>
       <c r="F180" t="n">
         <v>10854</v>
@@ -24344,13 +24344,13 @@
         </is>
       </c>
       <c r="C181" t="n">
-        <v>1113.76</v>
+        <v>1113.78</v>
       </c>
       <c r="D181" t="n">
-        <v>1104.59</v>
+        <v>1104.6</v>
       </c>
       <c r="E181" t="n">
-        <v>1122.94</v>
+        <v>1122.95</v>
       </c>
       <c r="F181" t="n">
         <v>6923</v>
@@ -24646,13 +24646,13 @@
         </is>
       </c>
       <c r="C183" t="n">
-        <v>1110.47</v>
+        <v>1110.44</v>
       </c>
       <c r="D183" t="n">
-        <v>1102.59</v>
+        <v>1102.56</v>
       </c>
       <c r="E183" t="n">
-        <v>1118.34</v>
+        <v>1118.32</v>
       </c>
       <c r="F183" t="n">
         <v>8045</v>
@@ -24797,13 +24797,13 @@
         </is>
       </c>
       <c r="C184" t="n">
-        <v>1108.74</v>
+        <v>1108.76</v>
       </c>
       <c r="D184" t="n">
-        <v>1099.45</v>
+        <v>1099.46</v>
       </c>
       <c r="E184" t="n">
-        <v>1118.04</v>
+        <v>1118.05</v>
       </c>
       <c r="F184" t="n">
         <v>8977</v>
@@ -24948,13 +24948,13 @@
         </is>
       </c>
       <c r="C185" t="n">
-        <v>1107.22</v>
+        <v>1107.24</v>
       </c>
       <c r="D185" t="n">
-        <v>1100.17</v>
+        <v>1100.18</v>
       </c>
       <c r="E185" t="n">
-        <v>1114.28</v>
+        <v>1114.3</v>
       </c>
       <c r="F185" t="n">
         <v>14148</v>
@@ -25099,13 +25099,13 @@
         </is>
       </c>
       <c r="C186" t="n">
-        <v>1091.4</v>
+        <v>1091.42</v>
       </c>
       <c r="D186" t="n">
-        <v>1079.89</v>
+        <v>1079.91</v>
       </c>
       <c r="E186" t="n">
-        <v>1102.91</v>
+        <v>1102.93</v>
       </c>
       <c r="F186" t="n">
         <v>4780</v>
@@ -25250,13 +25250,13 @@
         </is>
       </c>
       <c r="C187" t="n">
-        <v>1089.33</v>
+        <v>1089.34</v>
       </c>
       <c r="D187" t="n">
-        <v>1079.98</v>
+        <v>1079.99</v>
       </c>
       <c r="E187" t="n">
-        <v>1098.67</v>
+        <v>1098.69</v>
       </c>
       <c r="F187" t="n">
         <v>7597</v>
@@ -25401,13 +25401,13 @@
         </is>
       </c>
       <c r="C188" t="n">
-        <v>1073.51</v>
+        <v>1073.49</v>
       </c>
       <c r="D188" t="n">
-        <v>1062.33</v>
+        <v>1062.31</v>
       </c>
       <c r="E188" t="n">
-        <v>1084.69</v>
+        <v>1084.68</v>
       </c>
       <c r="F188" t="n">
         <v>6328</v>
@@ -25552,13 +25552,13 @@
         </is>
       </c>
       <c r="C189" t="n">
-        <v>1069.51</v>
+        <v>1069.53</v>
       </c>
       <c r="D189" t="n">
-        <v>1059.58</v>
+        <v>1059.59</v>
       </c>
       <c r="E189" t="n">
-        <v>1079.45</v>
+        <v>1079.46</v>
       </c>
       <c r="F189" t="n">
         <v>6965</v>
@@ -25703,13 +25703,13 @@
         </is>
       </c>
       <c r="C190" t="n">
-        <v>1066.85</v>
+        <v>1066.91</v>
       </c>
       <c r="D190" t="n">
-        <v>1055.35</v>
+        <v>1055.4</v>
       </c>
       <c r="E190" t="n">
-        <v>1078.36</v>
+        <v>1078.41</v>
       </c>
       <c r="F190" t="n">
         <v>5745</v>
@@ -25854,13 +25854,13 @@
         </is>
       </c>
       <c r="C191" t="n">
-        <v>1065.24</v>
+        <v>1065.27</v>
       </c>
       <c r="D191" t="n">
-        <v>1049.97</v>
+        <v>1050.01</v>
       </c>
       <c r="E191" t="n">
-        <v>1080.51</v>
+        <v>1080.54</v>
       </c>
       <c r="F191" t="n">
         <v>1743</v>
@@ -26005,13 +26005,13 @@
         </is>
       </c>
       <c r="C192" t="n">
-        <v>1061.07</v>
+        <v>1061.11</v>
       </c>
       <c r="D192" t="n">
-        <v>1049.06</v>
+        <v>1049.09</v>
       </c>
       <c r="E192" t="n">
-        <v>1073.09</v>
+        <v>1073.12</v>
       </c>
       <c r="F192" t="n">
         <v>3924</v>
@@ -26307,13 +26307,13 @@
         </is>
       </c>
       <c r="C194" t="n">
-        <v>1040.48</v>
+        <v>1040.5</v>
       </c>
       <c r="D194" t="n">
-        <v>1029.04</v>
+        <v>1029.07</v>
       </c>
       <c r="E194" t="n">
-        <v>1051.91</v>
+        <v>1051.94</v>
       </c>
       <c r="F194" t="n">
         <v>4845</v>
@@ -26461,10 +26461,10 @@
         <v>1023.25</v>
       </c>
       <c r="D195" t="n">
-        <v>1009.62</v>
+        <v>1009.63</v>
       </c>
       <c r="E195" t="n">
-        <v>1036.87</v>
+        <v>1036.88</v>
       </c>
       <c r="F195" t="n">
         <v>2658</v>
@@ -26609,13 +26609,13 @@
         </is>
       </c>
       <c r="C196" t="n">
-        <v>1021.27</v>
+        <v>1021.3</v>
       </c>
       <c r="D196" t="n">
-        <v>1010.36</v>
+        <v>1010.39</v>
       </c>
       <c r="E196" t="n">
-        <v>1032.19</v>
+        <v>1032.21</v>
       </c>
       <c r="F196" t="n">
         <v>6310</v>
@@ -26760,10 +26760,10 @@
         </is>
       </c>
       <c r="C197" t="n">
-        <v>994.615</v>
+        <v>994.62</v>
       </c>
       <c r="D197" t="n">
-        <v>982.003</v>
+        <v>982.011</v>
       </c>
       <c r="E197" t="n">
         <v>1007.23</v>
@@ -26911,13 +26911,13 @@
         </is>
       </c>
       <c r="C198" t="n">
-        <v>990.535</v>
+        <v>990.574</v>
       </c>
       <c r="D198" t="n">
-        <v>978.114</v>
+        <v>978.1559999999999</v>
       </c>
       <c r="E198" t="n">
-        <v>1002.96</v>
+        <v>1002.99</v>
       </c>
       <c r="F198" t="n">
         <v>4203</v>
@@ -27062,13 +27062,13 @@
         </is>
       </c>
       <c r="C199" t="n">
-        <v>979.438</v>
+        <v>979.482</v>
       </c>
       <c r="D199" t="n">
-        <v>965.847</v>
+        <v>965.895</v>
       </c>
       <c r="E199" t="n">
-        <v>993.03</v>
+        <v>993.0700000000001</v>
       </c>
       <c r="F199" t="n">
         <v>3412</v>
@@ -27213,13 +27213,13 @@
         </is>
       </c>
       <c r="C200" t="n">
-        <v>971.65</v>
+        <v>971.723</v>
       </c>
       <c r="D200" t="n">
-        <v>955.768</v>
+        <v>955.846</v>
       </c>
       <c r="E200" t="n">
-        <v>987.532</v>
+        <v>987.599</v>
       </c>
       <c r="F200" t="n">
         <v>2391</v>
@@ -27364,13 +27364,13 @@
         </is>
       </c>
       <c r="C201" t="n">
-        <v>951.702</v>
+        <v>951.717</v>
       </c>
       <c r="D201" t="n">
-        <v>938.907</v>
+        <v>938.926</v>
       </c>
       <c r="E201" t="n">
-        <v>964.497</v>
+        <v>964.5069999999999</v>
       </c>
       <c r="F201" t="n">
         <v>3287</v>
@@ -28560,14 +28560,14 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>qwen3.5-122b-a10b</t>
+          <t>kimi-k2-0905-preview</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>122</v>
+        <v>1000</v>
       </c>
       <c r="C23" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -28576,21 +28576,21 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>override</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>kimi-k2-0905-preview</t>
+          <t>qwen3.5-122b-a10b</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1000</v>
+        <v>122</v>
       </c>
       <c r="C24" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -28599,7 +28599,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>name_parsing</t>
         </is>
       </c>
     </row>
@@ -28621,38 +28621,38 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>kimi-k2-0711-preview</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="C26" t="n">
-        <v>32</v>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+          <t>deepseek-v3.1-terminus-thinking</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>deepseek-v3.1-terminus-thinking</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
+          <t>kimi-k2-0711-preview</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C27" t="n">
+        <v>32</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>override</t>
         </is>
       </c>
     </row>
@@ -28865,38 +28865,38 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>minimax-m2.5</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr"/>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
+          <t>qwen3-235b-a22b-thinking-2507</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>235</v>
+      </c>
+      <c r="C38" t="n">
+        <v>22</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>name_parsing</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>qwen3-235b-a22b-thinking-2507</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>235</v>
-      </c>
-      <c r="C39" t="n">
-        <v>22</v>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+          <t>minimax-m2.5</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -28926,14 +28926,14 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>qwen3-vl-235b-a22b-thinking</t>
+          <t>qwen3.5-35b-a3b</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>235</v>
+        <v>35</v>
       </c>
       <c r="C41" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -28949,14 +28949,14 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>qwen3.5-35b-a3b</t>
+          <t>qwen3-vl-235b-a22b-thinking</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>35</v>
+        <v>235</v>
       </c>
       <c r="C42" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -29025,38 +29025,38 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>mimo-v2-flash (thinking)</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr"/>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
+          <t>qwen3-coder-480b-a35b-instruct</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>480</v>
+      </c>
+      <c r="C46" t="n">
+        <v>35</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>name_parsing</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>qwen3-coder-480b-a35b-instruct</t>
-        </is>
-      </c>
-      <c r="B47" t="n">
-        <v>480</v>
-      </c>
-      <c r="C47" t="n">
-        <v>35</v>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+          <t>mimo-v2-flash (thinking)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr"/>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -29352,38 +29352,38 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>gpt-oss-120b</t>
-        </is>
-      </c>
-      <c r="B63" t="n">
-        <v>117</v>
-      </c>
-      <c r="C63" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+          <t>glm-4.5v</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr"/>
+      <c r="C63" t="inlineStr"/>
+      <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>glm-4.5v</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr"/>
-      <c r="C64" t="inlineStr"/>
-      <c r="D64" t="inlineStr"/>
+          <t>gpt-oss-120b</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>117</v>
+      </c>
+      <c r="C64" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>override</t>
         </is>
       </c>
     </row>
@@ -29405,14 +29405,14 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>qwen3-32b</t>
+          <t>llama-3.1-nemotron-ultra-253b-v1</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>32</v>
+        <v>253</v>
       </c>
       <c r="C66" t="n">
-        <v>32</v>
+        <v>253</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -29428,14 +29428,14 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>llama-3.1-nemotron-ultra-253b-v1</t>
+          <t>qwen3-32b</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>253</v>
+        <v>32</v>
       </c>
       <c r="C67" t="n">
-        <v>253</v>
+        <v>32</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -30001,14 +30001,14 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>mistral-small-3.1-24b-instruct-2503</t>
+          <t>gemma-3-4b-it</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="C94" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -30024,14 +30024,14 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>gemma-3-4b-it</t>
+          <t>mistral-small-3.1-24b-instruct-2503</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="C95" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>

--- a/arena_enrichment/output/arena_leaderboard_enriched.xlsx
+++ b/arena_enrichment/output/arena_leaderboard_enriched.xlsx
@@ -675,16 +675,16 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>1469.87</v>
+        <v>1469.08</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1463.47</v>
+        <v>1462.8</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1476.28</v>
+        <v>1475.36</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>9670</v>
+        <v>10217</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
@@ -746,16 +746,16 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>1465.38</v>
+        <v>1463.6</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1455.47</v>
+        <v>1454.64</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1475.28</v>
+        <v>1472.56</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>3375</v>
+        <v>4153</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
@@ -817,16 +817,16 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>1463.08</v>
+        <v>1463.54</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1454.32</v>
+        <v>1454.77</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1471.84</v>
+        <v>1472.3</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>4175</v>
+        <v>4178</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
@@ -968,16 +968,16 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>1462.08</v>
+        <v>1461.94</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1452.85</v>
+        <v>1452.71</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1471.3</v>
+        <v>1471.17</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>3823</v>
+        <v>3814</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
@@ -1039,16 +1039,16 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1459.18</v>
+        <v>1460.71</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1451.07</v>
+        <v>1452.95</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1467.29</v>
+        <v>1468.47</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>4901</v>
+        <v>5404</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
@@ -1190,16 +1190,16 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>1457</v>
+        <v>1456.98</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>1452.08</v>
+        <v>1452.12</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1461.92</v>
+        <v>1461.84</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>18455</v>
+        <v>18992</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
@@ -1341,16 +1341,16 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>1450.98</v>
+        <v>1450.95</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>1443.32</v>
+        <v>1443.3</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1458.63</v>
+        <v>1458.61</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>5818</v>
+        <v>5812</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
@@ -1492,16 +1492,16 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>1448.77</v>
+        <v>1449.33</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1444.33</v>
+        <v>1444.93</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1453.21</v>
+        <v>1453.73</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>24838</v>
+        <v>25331</v>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
@@ -1643,16 +1643,16 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>1446.68</v>
+        <v>1446.52</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>1441.89</v>
+        <v>1441.77</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1451.47</v>
+        <v>1451.26</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>19928</v>
+        <v>20465</v>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
@@ -1794,16 +1794,16 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>1442.5</v>
+        <v>1442.55</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>1436.39</v>
+        <v>1436.43</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1448.62</v>
+        <v>1448.66</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>12143</v>
+        <v>12144</v>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
@@ -1865,16 +1865,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1439.53</v>
+        <v>1439.49</v>
       </c>
       <c r="D12" t="n">
-        <v>1430.21</v>
+        <v>1430.18</v>
       </c>
       <c r="E12" t="n">
-        <v>1448.86</v>
+        <v>1448.81</v>
       </c>
       <c r="F12" t="n">
-        <v>3605</v>
+        <v>3607</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1936,16 +1936,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1438.4</v>
+        <v>1438.33</v>
       </c>
       <c r="D13" t="n">
-        <v>1430.72</v>
+        <v>1430.66</v>
       </c>
       <c r="E13" t="n">
-        <v>1446.07</v>
+        <v>1446</v>
       </c>
       <c r="F13" t="n">
-        <v>5781</v>
+        <v>5775</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -2087,16 +2087,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1432.59</v>
+        <v>1432.42</v>
       </c>
       <c r="D14" t="n">
-        <v>1423.15</v>
+        <v>1423</v>
       </c>
       <c r="E14" t="n">
-        <v>1442.03</v>
+        <v>1441.85</v>
       </c>
       <c r="F14" t="n">
-        <v>3510</v>
+        <v>3514</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -2238,16 +2238,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1431.58</v>
+        <v>1431.92</v>
       </c>
       <c r="D15" t="n">
-        <v>1424.97</v>
+        <v>1425.31</v>
       </c>
       <c r="E15" t="n">
-        <v>1438.19</v>
+        <v>1438.53</v>
       </c>
       <c r="F15" t="n">
-        <v>8206</v>
+        <v>8198</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -2389,16 +2389,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1429.88</v>
+        <v>1430.44</v>
       </c>
       <c r="D16" t="n">
-        <v>1426.49</v>
+        <v>1427.06</v>
       </c>
       <c r="E16" t="n">
-        <v>1433.28</v>
+        <v>1433.83</v>
       </c>
       <c r="F16" t="n">
-        <v>50311</v>
+        <v>50809</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -2540,16 +2540,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1425.64</v>
+        <v>1425.74</v>
       </c>
       <c r="D17" t="n">
-        <v>1421.7</v>
+        <v>1421.8</v>
       </c>
       <c r="E17" t="n">
-        <v>1429.58</v>
+        <v>1429.68</v>
       </c>
       <c r="F17" t="n">
-        <v>35713</v>
+        <v>35712</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -2611,16 +2611,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1424.44</v>
+        <v>1424.51</v>
       </c>
       <c r="D18" t="n">
-        <v>1417.89</v>
+        <v>1417.96</v>
       </c>
       <c r="E18" t="n">
-        <v>1430.99</v>
+        <v>1431.06</v>
       </c>
       <c r="F18" t="n">
-        <v>9083</v>
+        <v>9074</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -2678,24 +2678,24 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>mimo-v2.5</t>
+          <t>deepseek-v3.2</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1424.27</v>
+        <v>1424.1</v>
       </c>
       <c r="D19" t="n">
-        <v>1414.5</v>
+        <v>1420.45</v>
       </c>
       <c r="E19" t="n">
-        <v>1434.04</v>
+        <v>1427.76</v>
       </c>
       <c r="F19" t="n">
-        <v>3442</v>
+        <v>44813</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Xiaomi</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2749,24 +2749,24 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>deepseek-v3.2</t>
+          <t>mimo-v2.5</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1424.2</v>
+        <v>1423.17</v>
       </c>
       <c r="D20" t="n">
-        <v>1420.54</v>
+        <v>1414.35</v>
       </c>
       <c r="E20" t="n">
-        <v>1427.86</v>
+        <v>1431.99</v>
       </c>
       <c r="F20" t="n">
-        <v>44831</v>
+        <v>4246</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>DeepSeek</t>
+          <t>Xiaomi</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2824,16 +2824,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1422.93</v>
+        <v>1422.83</v>
       </c>
       <c r="D21" t="n">
-        <v>1416.53</v>
+        <v>1416.42</v>
       </c>
       <c r="E21" t="n">
-        <v>1429.34</v>
+        <v>1429.23</v>
       </c>
       <c r="F21" t="n">
-        <v>11953</v>
+        <v>11949</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -2895,16 +2895,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1422.52</v>
+        <v>1422.57</v>
       </c>
       <c r="D22" t="n">
-        <v>1419.79</v>
+        <v>1419.85</v>
       </c>
       <c r="E22" t="n">
-        <v>1425.25</v>
+        <v>1425.29</v>
       </c>
       <c r="F22" t="n">
-        <v>85971</v>
+        <v>86482</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -3046,16 +3046,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1422.02</v>
+        <v>1421.91</v>
       </c>
       <c r="D23" t="n">
-        <v>1418.28</v>
+        <v>1418.17</v>
       </c>
       <c r="E23" t="n">
-        <v>1425.76</v>
+        <v>1425.65</v>
       </c>
       <c r="F23" t="n">
-        <v>39104</v>
+        <v>39086</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -3117,16 +3117,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1421.79</v>
+        <v>1421.89</v>
       </c>
       <c r="D24" t="n">
-        <v>1416.13</v>
+        <v>1416.23</v>
       </c>
       <c r="E24" t="n">
-        <v>1427.44</v>
+        <v>1427.55</v>
       </c>
       <c r="F24" t="n">
-        <v>18472</v>
+        <v>18470</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -3188,16 +3188,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1417.98</v>
+        <v>1417.97</v>
       </c>
       <c r="D25" t="n">
-        <v>1411.49</v>
+        <v>1411.48</v>
       </c>
       <c r="E25" t="n">
         <v>1424.47</v>
       </c>
       <c r="F25" t="n">
-        <v>11805</v>
+        <v>11799</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -3335,148 +3335,68 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>qwen3.5-122b-a10b</t>
+          <t>deepseek-v3.1</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1417.86</v>
+        <v>1417.58</v>
       </c>
       <c r="D26" t="n">
-        <v>1412.8</v>
+        <v>1411.57</v>
       </c>
       <c r="E26" t="n">
-        <v>1422.91</v>
+        <v>1423.59</v>
       </c>
       <c r="F26" t="n">
-        <v>16762</v>
+        <v>14991</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alibaba</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
-        </is>
-      </c>
-      <c r="I26" t="n">
-        <v>122</v>
-      </c>
-      <c r="J26" t="n">
-        <v>10</v>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
-          <t>name_parsing</t>
-        </is>
-      </c>
-      <c r="M26" t="n">
-        <v>244</v>
-      </c>
-      <c r="N26" t="n">
-        <v>305</v>
-      </c>
-      <c r="O26" t="n">
-        <v>122</v>
-      </c>
-      <c r="P26" t="n">
-        <v>152.5</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>61</v>
-      </c>
-      <c r="R26" t="n">
-        <v>76.2</v>
-      </c>
-      <c r="S26" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T26" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U26" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="V26" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W26" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X26" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Y26" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z26" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AA26" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB26" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AC26" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AD26" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AE26" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AF26" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AG26" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr"/>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr"/>
+      <c r="AB26" t="inlineStr"/>
+      <c r="AC26" t="inlineStr"/>
+      <c r="AD26" t="inlineStr"/>
+      <c r="AE26" t="inlineStr"/>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="inlineStr"/>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>B200 SXM</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -3486,68 +3406,148 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>deepseek-v3.1</t>
+          <t>qwen3.5-122b-a10b</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1417.53</v>
+        <v>1417.52</v>
       </c>
       <c r="D27" t="n">
-        <v>1411.52</v>
+        <v>1412.51</v>
       </c>
       <c r="E27" t="n">
-        <v>1423.54</v>
+        <v>1422.53</v>
       </c>
       <c r="F27" t="n">
-        <v>14997</v>
+        <v>17294</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>DeepSeek</t>
+          <t>Alibaba</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
+          <t>Apache 2.0</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>122</v>
+      </c>
+      <c r="J27" t="n">
+        <v>10</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr"/>
-      <c r="S27" t="inlineStr"/>
-      <c r="T27" t="inlineStr"/>
-      <c r="U27" t="inlineStr"/>
-      <c r="V27" t="inlineStr"/>
-      <c r="W27" t="inlineStr"/>
-      <c r="X27" t="inlineStr"/>
-      <c r="Y27" t="inlineStr"/>
-      <c r="Z27" t="inlineStr"/>
-      <c r="AA27" t="inlineStr"/>
-      <c r="AB27" t="inlineStr"/>
-      <c r="AC27" t="inlineStr"/>
-      <c r="AD27" t="inlineStr"/>
-      <c r="AE27" t="inlineStr"/>
-      <c r="AF27" t="inlineStr"/>
-      <c r="AG27" t="inlineStr"/>
+          <t>name_parsing</t>
+        </is>
+      </c>
+      <c r="M27" t="n">
+        <v>244</v>
+      </c>
+      <c r="N27" t="n">
+        <v>305</v>
+      </c>
+      <c r="O27" t="n">
+        <v>122</v>
+      </c>
+      <c r="P27" t="n">
+        <v>152.5</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>61</v>
+      </c>
+      <c r="R27" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="S27" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T27" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U27" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V27" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W27" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X27" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y27" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z27" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA27" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB27" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AC27" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AD27" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE27" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF27" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AG27" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>B200 SXM</t>
         </is>
       </c>
     </row>
@@ -3561,16 +3561,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1417.13</v>
+        <v>1417.15</v>
       </c>
       <c r="D28" t="n">
-        <v>1407.15</v>
+        <v>1407.17</v>
       </c>
       <c r="E28" t="n">
-        <v>1427.11</v>
+        <v>1427.12</v>
       </c>
       <c r="F28" t="n">
-        <v>3467</v>
+        <v>3468</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -3632,16 +3632,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1417.11</v>
+        <v>1417.14</v>
       </c>
       <c r="D29" t="n">
-        <v>1412.25</v>
+        <v>1412.29</v>
       </c>
       <c r="E29" t="n">
-        <v>1421.96</v>
+        <v>1422</v>
       </c>
       <c r="F29" t="n">
-        <v>27661</v>
+        <v>27653</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -3783,13 +3783,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1416.72</v>
+        <v>1416.74</v>
       </c>
       <c r="D30" t="n">
-        <v>1410.11</v>
+        <v>1410.14</v>
       </c>
       <c r="E30" t="n">
-        <v>1423.33</v>
+        <v>1423.35</v>
       </c>
       <c r="F30" t="n">
         <v>11762</v>
@@ -3854,16 +3854,16 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1415.76</v>
+        <v>1415.72</v>
       </c>
       <c r="D31" t="n">
-        <v>1406.15</v>
+        <v>1406.11</v>
       </c>
       <c r="E31" t="n">
-        <v>1425.37</v>
+        <v>1425.33</v>
       </c>
       <c r="F31" t="n">
-        <v>3713</v>
+        <v>3712</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
         <v>1421.95</v>
       </c>
       <c r="F32" t="n">
-        <v>11529</v>
+        <v>11528</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -4076,16 +4076,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1414.62</v>
+        <v>1414.71</v>
       </c>
       <c r="D33" t="n">
-        <v>1410.95</v>
+        <v>1411.04</v>
       </c>
       <c r="E33" t="n">
-        <v>1418.29</v>
+        <v>1418.38</v>
       </c>
       <c r="F33" t="n">
-        <v>41363</v>
+        <v>41339</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -4227,16 +4227,16 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1410.97</v>
+        <v>1411.04</v>
       </c>
       <c r="D34" t="n">
-        <v>1406.09</v>
+        <v>1406.16</v>
       </c>
       <c r="E34" t="n">
-        <v>1415.85</v>
+        <v>1415.92</v>
       </c>
       <c r="F34" t="n">
-        <v>24352</v>
+        <v>24349</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -4378,16 +4378,16 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1404.63</v>
+        <v>1404.56</v>
       </c>
       <c r="D35" t="n">
-        <v>1399.5</v>
+        <v>1399.48</v>
       </c>
       <c r="E35" t="n">
-        <v>1409.75</v>
+        <v>1409.63</v>
       </c>
       <c r="F35" t="n">
-        <v>16330</v>
+        <v>16816</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -4529,16 +4529,16 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1404.1</v>
+        <v>1403.87</v>
       </c>
       <c r="D36" t="n">
-        <v>1397.96</v>
+        <v>1397.85</v>
       </c>
       <c r="E36" t="n">
-        <v>1410.24</v>
+        <v>1409.89</v>
       </c>
       <c r="F36" t="n">
-        <v>10943</v>
+        <v>11500</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -4600,16 +4600,16 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1402.9</v>
+        <v>1402.88</v>
       </c>
       <c r="D37" t="n">
-        <v>1398.4</v>
+        <v>1398.39</v>
       </c>
       <c r="E37" t="n">
-        <v>1407.4</v>
+        <v>1407.38</v>
       </c>
       <c r="F37" t="n">
-        <v>38251</v>
+        <v>38247</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -4751,16 +4751,16 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1401.45</v>
+        <v>1401.49</v>
       </c>
       <c r="D38" t="n">
-        <v>1396.67</v>
+        <v>1396.71</v>
       </c>
       <c r="E38" t="n">
-        <v>1406.23</v>
+        <v>1406.27</v>
       </c>
       <c r="F38" t="n">
-        <v>22912</v>
+        <v>22902</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -4902,16 +4902,16 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1401.08</v>
+        <v>1401.22</v>
       </c>
       <c r="D39" t="n">
-        <v>1394.72</v>
+        <v>1394.85</v>
       </c>
       <c r="E39" t="n">
-        <v>1407.45</v>
+        <v>1407.59</v>
       </c>
       <c r="F39" t="n">
-        <v>11416</v>
+        <v>11407</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -5053,16 +5053,16 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1399.15</v>
+        <v>1399.2</v>
       </c>
       <c r="D40" t="n">
-        <v>1392.62</v>
+        <v>1392.67</v>
       </c>
       <c r="E40" t="n">
-        <v>1405.67</v>
+        <v>1405.72</v>
       </c>
       <c r="F40" t="n">
-        <v>9008</v>
+        <v>9007</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -5204,16 +5204,16 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1398.32</v>
+        <v>1398.45</v>
       </c>
       <c r="D41" t="n">
-        <v>1393.63</v>
+        <v>1393.82</v>
       </c>
       <c r="E41" t="n">
-        <v>1403</v>
+        <v>1403.09</v>
       </c>
       <c r="F41" t="n">
-        <v>21952</v>
+        <v>22531</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -5275,7 +5275,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1397.61</v>
+        <v>1397.62</v>
       </c>
       <c r="D42" t="n">
         <v>1392.75</v>
@@ -5426,16 +5426,16 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1396.19</v>
+        <v>1396</v>
       </c>
       <c r="D43" t="n">
-        <v>1391.12</v>
+        <v>1390.99</v>
       </c>
       <c r="E43" t="n">
-        <v>1401.27</v>
+        <v>1401.01</v>
       </c>
       <c r="F43" t="n">
-        <v>16914</v>
+        <v>17504</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -5577,16 +5577,16 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1395.74</v>
+        <v>1395.8</v>
       </c>
       <c r="D44" t="n">
-        <v>1388.95</v>
+        <v>1389.01</v>
       </c>
       <c r="E44" t="n">
-        <v>1402.53</v>
+        <v>1402.59</v>
       </c>
       <c r="F44" t="n">
-        <v>7951</v>
+        <v>7949</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -5737,7 +5737,7 @@
         <v>1398.87</v>
       </c>
       <c r="F45" t="n">
-        <v>45552</v>
+        <v>45545</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -5879,16 +5879,16 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1392.42</v>
+        <v>1392.51</v>
       </c>
       <c r="D46" t="n">
-        <v>1388.51</v>
+        <v>1388.63</v>
       </c>
       <c r="E46" t="n">
-        <v>1396.32</v>
+        <v>1396.39</v>
       </c>
       <c r="F46" t="n">
-        <v>34578</v>
+        <v>35121</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -5950,16 +5950,16 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1391.76</v>
+        <v>1391.39</v>
       </c>
       <c r="D47" t="n">
-        <v>1387.19</v>
+        <v>1386.87</v>
       </c>
       <c r="E47" t="n">
-        <v>1396.32</v>
+        <v>1395.91</v>
       </c>
       <c r="F47" t="n">
-        <v>22678</v>
+        <v>23164</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -6017,148 +6017,68 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>qwen3-coder-480b-a35b-instruct</t>
+          <t>mimo-v2-flash (thinking)</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1387.36</v>
+        <v>1387.41</v>
       </c>
       <c r="D48" t="n">
-        <v>1382.41</v>
+        <v>1381.14</v>
       </c>
       <c r="E48" t="n">
-        <v>1392.31</v>
+        <v>1393.68</v>
       </c>
       <c r="F48" t="n">
-        <v>25762</v>
+        <v>10981</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alibaba</t>
+          <t>Xiaomi</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
-        </is>
-      </c>
-      <c r="I48" t="n">
-        <v>480</v>
-      </c>
-      <c r="J48" t="n">
-        <v>35</v>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
-          <t>name_parsing</t>
-        </is>
-      </c>
-      <c r="M48" t="n">
-        <v>960</v>
-      </c>
-      <c r="N48" t="n">
-        <v>1200</v>
-      </c>
-      <c r="O48" t="n">
-        <v>480</v>
-      </c>
-      <c r="P48" t="n">
-        <v>600</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>240</v>
-      </c>
-      <c r="R48" t="n">
-        <v>300</v>
-      </c>
-      <c r="S48" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T48" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U48" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="V48" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W48" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X48" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Y48" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z48" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AA48" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AB48" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AC48" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AD48" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AE48" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AF48" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AG48" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr"/>
+      <c r="S48" t="inlineStr"/>
+      <c r="T48" t="inlineStr"/>
+      <c r="U48" t="inlineStr"/>
+      <c r="V48" t="inlineStr"/>
+      <c r="W48" t="inlineStr"/>
+      <c r="X48" t="inlineStr"/>
+      <c r="Y48" t="inlineStr"/>
+      <c r="Z48" t="inlineStr"/>
+      <c r="AA48" t="inlineStr"/>
+      <c r="AB48" t="inlineStr"/>
+      <c r="AC48" t="inlineStr"/>
+      <c r="AD48" t="inlineStr"/>
+      <c r="AE48" t="inlineStr"/>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="inlineStr"/>
       <c r="AH48" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -6168,68 +6088,148 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>mimo-v2-flash (thinking)</t>
+          <t>qwen3-coder-480b-a35b-instruct</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1387.34</v>
+        <v>1387.41</v>
       </c>
       <c r="D49" t="n">
-        <v>1381.07</v>
+        <v>1382.46</v>
       </c>
       <c r="E49" t="n">
-        <v>1393.61</v>
+        <v>1392.36</v>
       </c>
       <c r="F49" t="n">
-        <v>10988</v>
+        <v>25758</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Xiaomi</t>
+          <t>Alibaba</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
+          <t>Apache 2.0</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
+        <v>480</v>
+      </c>
+      <c r="J49" t="n">
+        <v>35</v>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr"/>
-      <c r="R49" t="inlineStr"/>
-      <c r="S49" t="inlineStr"/>
-      <c r="T49" t="inlineStr"/>
-      <c r="U49" t="inlineStr"/>
-      <c r="V49" t="inlineStr"/>
-      <c r="W49" t="inlineStr"/>
-      <c r="X49" t="inlineStr"/>
-      <c r="Y49" t="inlineStr"/>
-      <c r="Z49" t="inlineStr"/>
-      <c r="AA49" t="inlineStr"/>
-      <c r="AB49" t="inlineStr"/>
-      <c r="AC49" t="inlineStr"/>
-      <c r="AD49" t="inlineStr"/>
-      <c r="AE49" t="inlineStr"/>
-      <c r="AF49" t="inlineStr"/>
-      <c r="AG49" t="inlineStr"/>
+          <t>name_parsing</t>
+        </is>
+      </c>
+      <c r="M49" t="n">
+        <v>960</v>
+      </c>
+      <c r="N49" t="n">
+        <v>1200</v>
+      </c>
+      <c r="O49" t="n">
+        <v>480</v>
+      </c>
+      <c r="P49" t="n">
+        <v>600</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>240</v>
+      </c>
+      <c r="R49" t="n">
+        <v>300</v>
+      </c>
+      <c r="S49" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T49" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U49" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V49" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W49" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X49" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y49" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z49" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA49" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AB49" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AC49" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD49" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE49" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF49" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AG49" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AH49" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
     </row>
@@ -6243,16 +6243,16 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1385.13</v>
+        <v>1385.1</v>
       </c>
       <c r="D50" t="n">
-        <v>1379.87</v>
+        <v>1379.85</v>
       </c>
       <c r="E50" t="n">
-        <v>1390.38</v>
+        <v>1390.35</v>
       </c>
       <c r="F50" t="n">
-        <v>17169</v>
+        <v>17165</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -6314,16 +6314,16 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1383.18</v>
+        <v>1383.26</v>
       </c>
       <c r="D51" t="n">
-        <v>1378.31</v>
+        <v>1378.38</v>
       </c>
       <c r="E51" t="n">
-        <v>1388.06</v>
+        <v>1388.14</v>
       </c>
       <c r="F51" t="n">
-        <v>23771</v>
+        <v>23769</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -6465,16 +6465,16 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1377.33</v>
+        <v>1377.37</v>
       </c>
       <c r="D52" t="n">
-        <v>1366.05</v>
+        <v>1366.1</v>
       </c>
       <c r="E52" t="n">
-        <v>1388.6</v>
+        <v>1388.65</v>
       </c>
       <c r="F52" t="n">
-        <v>2807</v>
+        <v>2808</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -6532,24 +6532,24 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>qwen3-235b-a22b</t>
+          <t>trinity-large-preview</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1374.43</v>
+        <v>1374.83</v>
       </c>
       <c r="D53" t="n">
-        <v>1369.74</v>
+        <v>1369.84</v>
       </c>
       <c r="E53" t="n">
-        <v>1379.12</v>
+        <v>1379.83</v>
       </c>
       <c r="F53" t="n">
-        <v>26287</v>
+        <v>18558</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alibaba</t>
+          <t>Arcee AI</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -6558,52 +6558,52 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>235</v>
+        <v>70</v>
       </c>
       <c r="J53" t="n">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>moe</t>
+          <t>dense</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>override</t>
         </is>
       </c>
       <c r="M53" t="n">
-        <v>470</v>
+        <v>140</v>
       </c>
       <c r="N53" t="n">
-        <v>587.5</v>
+        <v>175</v>
       </c>
       <c r="O53" t="n">
-        <v>235</v>
+        <v>70</v>
       </c>
       <c r="P53" t="n">
-        <v>293.8</v>
+        <v>87.5</v>
       </c>
       <c r="Q53" t="n">
-        <v>117.5</v>
+        <v>35</v>
       </c>
       <c r="R53" t="n">
-        <v>146.9</v>
+        <v>43.8</v>
       </c>
       <c r="S53" s="6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="T53" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U53" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="T53" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U53" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="V53" s="6" t="inlineStr">
@@ -6616,9 +6616,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="X53" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="X53" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Y53" s="6" t="inlineStr">
@@ -6626,24 +6626,24 @@
           <t>No</t>
         </is>
       </c>
-      <c r="Z53" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AA53" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AB53" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AC53" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="Z53" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AA53" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB53" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AC53" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AD53" s="5" t="inlineStr">
@@ -6651,14 +6651,14 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="AE53" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AF53" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AE53" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AF53" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AG53" s="5" t="inlineStr">
@@ -6668,12 +6668,12 @@
       </c>
       <c r="AH53" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>B200 SXM</t>
         </is>
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>RTX PRO 6000</t>
         </is>
       </c>
     </row>
@@ -6683,24 +6683,24 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>trinity-large-preview</t>
+          <t>qwen3-235b-a22b</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1374.42</v>
+        <v>1374.56</v>
       </c>
       <c r="D54" t="n">
-        <v>1369.35</v>
+        <v>1369.87</v>
       </c>
       <c r="E54" t="n">
-        <v>1379.48</v>
+        <v>1379.25</v>
       </c>
       <c r="F54" t="n">
-        <v>17933</v>
+        <v>26283</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Arcee AI</t>
+          <t>Alibaba</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -6709,52 +6709,52 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>70</v>
+        <v>235</v>
       </c>
       <c r="J54" t="n">
-        <v>70</v>
+        <v>22</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>dense</t>
+          <t>moe</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>name_parsing</t>
         </is>
       </c>
       <c r="M54" t="n">
-        <v>140</v>
+        <v>470</v>
       </c>
       <c r="N54" t="n">
-        <v>175</v>
+        <v>587.5</v>
       </c>
       <c r="O54" t="n">
-        <v>70</v>
+        <v>235</v>
       </c>
       <c r="P54" t="n">
-        <v>87.5</v>
+        <v>293.8</v>
       </c>
       <c r="Q54" t="n">
-        <v>35</v>
+        <v>117.5</v>
       </c>
       <c r="R54" t="n">
-        <v>43.8</v>
+        <v>146.9</v>
       </c>
       <c r="S54" s="6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="T54" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="U54" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="T54" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U54" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="V54" s="6" t="inlineStr">
@@ -6767,9 +6767,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="X54" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="X54" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="Y54" s="6" t="inlineStr">
@@ -6777,24 +6777,24 @@
           <t>No</t>
         </is>
       </c>
-      <c r="Z54" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AA54" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB54" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AC54" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="Z54" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA54" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AB54" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AC54" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AD54" s="5" t="inlineStr">
@@ -6802,14 +6802,14 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="AE54" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AF54" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AE54" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF54" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AG54" s="5" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="AH54" t="inlineStr">
         <is>
-          <t>B200 SXM</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>RTX PRO 6000</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
     </row>
@@ -6838,16 +6838,16 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1372.85</v>
+        <v>1372.86</v>
       </c>
       <c r="D55" t="n">
-        <v>1368.6</v>
+        <v>1368.62</v>
       </c>
       <c r="E55" t="n">
-        <v>1377.09</v>
+        <v>1377.11</v>
       </c>
       <c r="F55" t="n">
-        <v>31130</v>
+        <v>31131</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -6909,16 +6909,16 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1369.07</v>
+        <v>1369.15</v>
       </c>
       <c r="D56" t="n">
-        <v>1363.23</v>
+        <v>1363.31</v>
       </c>
       <c r="E56" t="n">
-        <v>1374.9</v>
+        <v>1374.99</v>
       </c>
       <c r="F56" t="n">
-        <v>13713</v>
+        <v>13715</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -7060,16 +7060,16 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1367.93</v>
+        <v>1367.89</v>
       </c>
       <c r="D57" t="n">
-        <v>1362.1</v>
+        <v>1362.07</v>
       </c>
       <c r="E57" t="n">
-        <v>1373.75</v>
+        <v>1373.72</v>
       </c>
       <c r="F57" t="n">
-        <v>11780</v>
+        <v>11763</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -7131,16 +7131,16 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1365.58</v>
+        <v>1365.56</v>
       </c>
       <c r="D58" t="n">
-        <v>1361.92</v>
+        <v>1361.9</v>
       </c>
       <c r="E58" t="n">
-        <v>1369.25</v>
+        <v>1369.23</v>
       </c>
       <c r="F58" t="n">
-        <v>47577</v>
+        <v>47574</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -7282,16 +7282,16 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1363.32</v>
+        <v>1363.31</v>
       </c>
       <c r="D59" t="n">
-        <v>1359.05</v>
+        <v>1359.04</v>
       </c>
       <c r="E59" t="n">
-        <v>1367.59</v>
+        <v>1367.57</v>
       </c>
       <c r="F59" t="n">
-        <v>35252</v>
+        <v>35238</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -7353,16 +7353,16 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1361.47</v>
+        <v>1361.12</v>
       </c>
       <c r="D60" t="n">
-        <v>1354.21</v>
+        <v>1353.86</v>
       </c>
       <c r="E60" t="n">
-        <v>1368.72</v>
+        <v>1368.38</v>
       </c>
       <c r="F60" t="n">
-        <v>7419</v>
+        <v>7413</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -7504,10 +7504,10 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1358.17</v>
+        <v>1358.16</v>
       </c>
       <c r="D61" t="n">
-        <v>1353.45</v>
+        <v>1353.44</v>
       </c>
       <c r="E61" t="n">
         <v>1362.89</v>
@@ -7655,16 +7655,16 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1357.05</v>
+        <v>1357.1</v>
       </c>
       <c r="D62" t="n">
-        <v>1351.85</v>
+        <v>1351.9</v>
       </c>
       <c r="E62" t="n">
-        <v>1362.24</v>
+        <v>1362.3</v>
       </c>
       <c r="F62" t="n">
-        <v>17723</v>
+        <v>17720</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -7726,16 +7726,16 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1356.41</v>
+        <v>1356.57</v>
       </c>
       <c r="D63" t="n">
-        <v>1348.05</v>
+        <v>1348.21</v>
       </c>
       <c r="E63" t="n">
-        <v>1364.76</v>
+        <v>1364.92</v>
       </c>
       <c r="F63" t="n">
-        <v>5334</v>
+        <v>5336</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -7877,16 +7877,16 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1353.52</v>
+        <v>1353.47</v>
       </c>
       <c r="D64" t="n">
-        <v>1350.08</v>
+        <v>1350.03</v>
       </c>
       <c r="E64" t="n">
-        <v>1356.96</v>
+        <v>1356.91</v>
       </c>
       <c r="F64" t="n">
-        <v>56341</v>
+        <v>56326</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -7948,13 +7948,13 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1353.07</v>
+        <v>1353.15</v>
       </c>
       <c r="D65" t="n">
-        <v>1344.73</v>
+        <v>1344.82</v>
       </c>
       <c r="E65" t="n">
-        <v>1361.41</v>
+        <v>1361.49</v>
       </c>
       <c r="F65" t="n">
         <v>4969</v>
@@ -8019,16 +8019,16 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1353.04</v>
+        <v>1352.94</v>
       </c>
       <c r="D66" t="n">
-        <v>1348.69</v>
+        <v>1348.6</v>
       </c>
       <c r="E66" t="n">
-        <v>1357.39</v>
+        <v>1357.29</v>
       </c>
       <c r="F66" t="n">
-        <v>30677</v>
+        <v>30664</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -8170,16 +8170,16 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1347.65</v>
+        <v>1347.7</v>
       </c>
       <c r="D67" t="n">
-        <v>1340.25</v>
+        <v>1340.3</v>
       </c>
       <c r="E67" t="n">
-        <v>1355.05</v>
+        <v>1355.09</v>
       </c>
       <c r="F67" t="n">
-        <v>6558</v>
+        <v>6557</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -8241,13 +8241,13 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1346.96</v>
+        <v>1346.98</v>
       </c>
       <c r="D68" t="n">
-        <v>1335.27</v>
+        <v>1335.28</v>
       </c>
       <c r="E68" t="n">
-        <v>1358.66</v>
+        <v>1358.67</v>
       </c>
       <c r="F68" t="n">
         <v>2549</v>
@@ -8392,13 +8392,13 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1346.95</v>
+        <v>1346.97</v>
       </c>
       <c r="D69" t="n">
-        <v>1337.49</v>
+        <v>1337.5</v>
       </c>
       <c r="E69" t="n">
-        <v>1356.42</v>
+        <v>1356.43</v>
       </c>
       <c r="F69" t="n">
         <v>3926</v>
@@ -8543,16 +8543,16 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1346</v>
+        <v>1346.24</v>
       </c>
       <c r="D70" t="n">
-        <v>1338.27</v>
+        <v>1338.49</v>
       </c>
       <c r="E70" t="n">
-        <v>1353.74</v>
+        <v>1353.98</v>
       </c>
       <c r="F70" t="n">
-        <v>6876</v>
+        <v>6872</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -8697,13 +8697,13 @@
         <v>1345.78</v>
       </c>
       <c r="D71" t="n">
-        <v>1338.51</v>
+        <v>1338.52</v>
       </c>
       <c r="E71" t="n">
         <v>1353.04</v>
       </c>
       <c r="F71" t="n">
-        <v>7016</v>
+        <v>7014</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -8765,13 +8765,13 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1342.76</v>
+        <v>1342.8</v>
       </c>
       <c r="D72" t="n">
-        <v>1332.79</v>
+        <v>1332.83</v>
       </c>
       <c r="E72" t="n">
-        <v>1352.74</v>
+        <v>1352.78</v>
       </c>
       <c r="F72" t="n">
         <v>3345</v>
@@ -8916,13 +8916,13 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1341.64</v>
+        <v>1341.66</v>
       </c>
       <c r="D73" t="n">
-        <v>1332.13</v>
+        <v>1332.15</v>
       </c>
       <c r="E73" t="n">
-        <v>1351.15</v>
+        <v>1351.17</v>
       </c>
       <c r="F73" t="n">
         <v>3829</v>
@@ -9067,13 +9067,13 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1335.79</v>
+        <v>1335.81</v>
       </c>
       <c r="D74" t="n">
-        <v>1331.36</v>
+        <v>1331.38</v>
       </c>
       <c r="E74" t="n">
-        <v>1340.22</v>
+        <v>1340.24</v>
       </c>
       <c r="F74" t="n">
         <v>25405</v>
@@ -9218,13 +9218,13 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>1334.56</v>
+        <v>1334.53</v>
       </c>
       <c r="D75" t="n">
-        <v>1330.87</v>
+        <v>1330.84</v>
       </c>
       <c r="E75" t="n">
-        <v>1338.25</v>
+        <v>1338.22</v>
       </c>
       <c r="F75" t="n">
         <v>41375</v>
@@ -9369,13 +9369,13 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>1332.73</v>
+        <v>1332.7</v>
       </c>
       <c r="D76" t="n">
-        <v>1329.16</v>
+        <v>1329.13</v>
       </c>
       <c r="E76" t="n">
-        <v>1336.31</v>
+        <v>1336.28</v>
       </c>
       <c r="F76" t="n">
         <v>59656</v>
@@ -9520,16 +9520,16 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1330.54</v>
+        <v>1330.62</v>
       </c>
       <c r="D77" t="n">
-        <v>1324.44</v>
+        <v>1324.53</v>
       </c>
       <c r="E77" t="n">
-        <v>1336.63</v>
+        <v>1336.72</v>
       </c>
       <c r="F77" t="n">
-        <v>12251</v>
+        <v>12236</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -9671,16 +9671,16 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1327.9</v>
+        <v>1328.43</v>
       </c>
       <c r="D78" t="n">
-        <v>1306.49</v>
+        <v>1307.03</v>
       </c>
       <c r="E78" t="n">
-        <v>1349.31</v>
+        <v>1349.83</v>
       </c>
       <c r="F78" t="n">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -9825,10 +9825,10 @@
         <v>1327.44</v>
       </c>
       <c r="D79" t="n">
-        <v>1315.27</v>
+        <v>1315.28</v>
       </c>
       <c r="E79" t="n">
-        <v>1339.6</v>
+        <v>1339.61</v>
       </c>
       <c r="F79" t="n">
         <v>2218</v>
@@ -9973,16 +9973,16 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1327.15</v>
+        <v>1327.22</v>
       </c>
       <c r="D80" t="n">
-        <v>1322.42</v>
+        <v>1322.5</v>
       </c>
       <c r="E80" t="n">
-        <v>1331.87</v>
+        <v>1331.95</v>
       </c>
       <c r="F80" t="n">
-        <v>26506</v>
+        <v>26501</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -10124,16 +10124,16 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1326.79</v>
+        <v>1326.85</v>
       </c>
       <c r="D81" t="n">
-        <v>1322.55</v>
+        <v>1322.61</v>
       </c>
       <c r="E81" t="n">
-        <v>1331.04</v>
+        <v>1331.1</v>
       </c>
       <c r="F81" t="n">
-        <v>40008</v>
+        <v>40004</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -10275,13 +10275,13 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>1323.09</v>
+        <v>1323.08</v>
       </c>
       <c r="D82" t="n">
-        <v>1314.82</v>
+        <v>1314.81</v>
       </c>
       <c r="E82" t="n">
-        <v>1331.36</v>
+        <v>1331.35</v>
       </c>
       <c r="F82" t="n">
         <v>6795</v>
@@ -10346,16 +10346,16 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>1322.27</v>
+        <v>1322.33</v>
       </c>
       <c r="D83" t="n">
-        <v>1317.57</v>
+        <v>1317.62</v>
       </c>
       <c r="E83" t="n">
-        <v>1326.97</v>
+        <v>1327.03</v>
       </c>
       <c r="F83" t="n">
-        <v>30323</v>
+        <v>30314</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -10497,16 +10497,16 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>1320.54</v>
+        <v>1320.59</v>
       </c>
       <c r="D84" t="n">
-        <v>1313.32</v>
+        <v>1313.38</v>
       </c>
       <c r="E84" t="n">
-        <v>1327.75</v>
+        <v>1327.81</v>
       </c>
       <c r="F84" t="n">
-        <v>7158</v>
+        <v>7152</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -10568,16 +10568,16 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>1318.08</v>
+        <v>1318.09</v>
       </c>
       <c r="D85" t="n">
-        <v>1314.63</v>
+        <v>1314.64</v>
       </c>
       <c r="E85" t="n">
-        <v>1321.53</v>
+        <v>1321.54</v>
       </c>
       <c r="F85" t="n">
-        <v>54756</v>
+        <v>54750</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -10719,16 +10719,16 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>1318.02</v>
+        <v>1317.98</v>
       </c>
       <c r="D86" t="n">
-        <v>1312.88</v>
+        <v>1312.84</v>
       </c>
       <c r="E86" t="n">
-        <v>1323.16</v>
+        <v>1323.12</v>
       </c>
       <c r="F86" t="n">
-        <v>22619</v>
+        <v>22613</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -10870,13 +10870,13 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>1317.59</v>
+        <v>1317.58</v>
       </c>
       <c r="D87" t="n">
-        <v>1311.9</v>
+        <v>1311.89</v>
       </c>
       <c r="E87" t="n">
-        <v>1323.29</v>
+        <v>1323.27</v>
       </c>
       <c r="F87" t="n">
         <v>16478</v>
@@ -10941,16 +10941,16 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>1317.21</v>
+        <v>1317.2</v>
       </c>
       <c r="D88" t="n">
-        <v>1310.85</v>
+        <v>1310.83</v>
       </c>
       <c r="E88" t="n">
-        <v>1323.58</v>
+        <v>1323.56</v>
       </c>
       <c r="F88" t="n">
-        <v>10638</v>
+        <v>10635</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -11092,16 +11092,16 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>1316.71</v>
+        <v>1316.84</v>
       </c>
       <c r="D89" t="n">
-        <v>1311.14</v>
+        <v>1311.26</v>
       </c>
       <c r="E89" t="n">
-        <v>1322.29</v>
+        <v>1322.41</v>
       </c>
       <c r="F89" t="n">
-        <v>15535</v>
+        <v>15527</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -11243,13 +11243,13 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>1314.05</v>
+        <v>1314.04</v>
       </c>
       <c r="D90" t="n">
-        <v>1309.52</v>
+        <v>1309.51</v>
       </c>
       <c r="E90" t="n">
-        <v>1318.59</v>
+        <v>1318.58</v>
       </c>
       <c r="F90" t="n">
         <v>24739</v>
@@ -11394,13 +11394,13 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>1313.57</v>
+        <v>1313.55</v>
       </c>
       <c r="D91" t="n">
-        <v>1309.65</v>
+        <v>1309.64</v>
       </c>
       <c r="E91" t="n">
-        <v>1317.48</v>
+        <v>1317.46</v>
       </c>
       <c r="F91" t="n">
         <v>45459</v>
@@ -11545,13 +11545,13 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>1306.69</v>
+        <v>1306.67</v>
       </c>
       <c r="D92" t="n">
-        <v>1301.99</v>
+        <v>1301.98</v>
       </c>
       <c r="E92" t="n">
-        <v>1311.38</v>
+        <v>1311.37</v>
       </c>
       <c r="F92" t="n">
         <v>24572</v>
@@ -11616,13 +11616,13 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>1305.76</v>
+        <v>1305.75</v>
       </c>
       <c r="D93" t="n">
-        <v>1300.09</v>
+        <v>1300.08</v>
       </c>
       <c r="E93" t="n">
-        <v>1311.43</v>
+        <v>1311.42</v>
       </c>
       <c r="F93" t="n">
         <v>19621</v>
@@ -11773,10 +11773,10 @@
         <v>1297.02</v>
       </c>
       <c r="E94" t="n">
-        <v>1313.39</v>
+        <v>1313.38</v>
       </c>
       <c r="F94" t="n">
-        <v>5965</v>
+        <v>5967</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -11918,13 +11918,13 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1304.86</v>
+        <v>1304.85</v>
       </c>
       <c r="D95" t="n">
-        <v>1300.45</v>
+        <v>1300.44</v>
       </c>
       <c r="E95" t="n">
-        <v>1309.28</v>
+        <v>1309.27</v>
       </c>
       <c r="F95" t="n">
         <v>28073</v>
@@ -11985,36 +11985,36 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>gemma-3-4b-it</t>
+          <t>mistral-small-3.1-24b-instruct-2503</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>1303.04</v>
+        <v>1303.05</v>
       </c>
       <c r="D96" t="n">
-        <v>1293.72</v>
+        <v>1298.55</v>
       </c>
       <c r="E96" t="n">
-        <v>1312.36</v>
+        <v>1307.56</v>
       </c>
       <c r="F96" t="n">
-        <v>4171</v>
+        <v>33239</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Mistral</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Gemma</t>
+          <t>Apache 2.0</t>
         </is>
       </c>
       <c r="I96" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="J96" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="K96" t="inlineStr">
         <is>
@@ -12027,22 +12027,22 @@
         </is>
       </c>
       <c r="M96" t="n">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="N96" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="O96" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="P96" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="Q96" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="R96" t="n">
-        <v>2.5</v>
+        <v>15</v>
       </c>
       <c r="S96" s="5" t="inlineStr">
         <is>
@@ -12136,36 +12136,36 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>mistral-small-3.1-24b-instruct-2503</t>
+          <t>gemma-3-4b-it</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1303.02</v>
+        <v>1303.05</v>
       </c>
       <c r="D97" t="n">
-        <v>1298.51</v>
+        <v>1293.73</v>
       </c>
       <c r="E97" t="n">
-        <v>1307.52</v>
+        <v>1312.37</v>
       </c>
       <c r="F97" t="n">
-        <v>33241</v>
+        <v>4171</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Mistral</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
+          <t>Gemma</t>
         </is>
       </c>
       <c r="I97" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="J97" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="K97" t="inlineStr">
         <is>
@@ -12178,22 +12178,22 @@
         </is>
       </c>
       <c r="M97" t="n">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="N97" t="n">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="O97" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="P97" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="Q97" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="R97" t="n">
-        <v>15</v>
+        <v>2.5</v>
       </c>
       <c r="S97" s="5" t="inlineStr">
         <is>
@@ -12291,10 +12291,10 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>1302.41</v>
+        <v>1302.4</v>
       </c>
       <c r="D98" t="n">
-        <v>1298.36</v>
+        <v>1298.35</v>
       </c>
       <c r="E98" t="n">
         <v>1306.46</v>
@@ -12593,13 +12593,13 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>1292.96</v>
+        <v>1292.94</v>
       </c>
       <c r="D100" t="n">
-        <v>1289.24</v>
+        <v>1289.22</v>
       </c>
       <c r="E100" t="n">
-        <v>1296.67</v>
+        <v>1296.65</v>
       </c>
       <c r="F100" t="n">
         <v>55240</v>
@@ -12744,13 +12744,13 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1288.43</v>
+        <v>1288.42</v>
       </c>
       <c r="D101" t="n">
-        <v>1281.13</v>
+        <v>1281.11</v>
       </c>
       <c r="E101" t="n">
-        <v>1295.74</v>
+        <v>1295.72</v>
       </c>
       <c r="F101" t="n">
         <v>8662</v>
@@ -12966,16 +12966,16 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>1286.77</v>
+        <v>1286.91</v>
       </c>
       <c r="D103" t="n">
-        <v>1278.38</v>
+        <v>1278.52</v>
       </c>
       <c r="E103" t="n">
-        <v>1295.17</v>
+        <v>1295.31</v>
       </c>
       <c r="F103" t="n">
-        <v>5689</v>
+        <v>5687</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
@@ -13117,13 +13117,13 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>1285.92</v>
+        <v>1285.9</v>
       </c>
       <c r="D104" t="n">
-        <v>1275.45</v>
+        <v>1275.42</v>
       </c>
       <c r="E104" t="n">
-        <v>1296.4</v>
+        <v>1296.37</v>
       </c>
       <c r="F104" t="n">
         <v>2846</v>
@@ -13268,13 +13268,13 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>1285.61</v>
+        <v>1285.58</v>
       </c>
       <c r="D105" t="n">
-        <v>1275.63</v>
+        <v>1275.6</v>
       </c>
       <c r="E105" t="n">
-        <v>1295.59</v>
+        <v>1295.55</v>
       </c>
       <c r="F105" t="n">
         <v>3749</v>
@@ -13419,16 +13419,16 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>1285.06</v>
+        <v>1285.12</v>
       </c>
       <c r="D106" t="n">
-        <v>1277.83</v>
+        <v>1277.88</v>
       </c>
       <c r="E106" t="n">
-        <v>1292.29</v>
+        <v>1292.35</v>
       </c>
       <c r="F106" t="n">
-        <v>8514</v>
+        <v>8511</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
@@ -13570,13 +13570,13 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>1279.15</v>
+        <v>1279.13</v>
       </c>
       <c r="D107" t="n">
-        <v>1272.29</v>
+        <v>1272.27</v>
       </c>
       <c r="E107" t="n">
-        <v>1286.01</v>
+        <v>1285.99</v>
       </c>
       <c r="F107" t="n">
         <v>10072</v>
@@ -13721,13 +13721,13 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>1276.49</v>
+        <v>1276.45</v>
       </c>
       <c r="D108" t="n">
-        <v>1271.17</v>
+        <v>1271.13</v>
       </c>
       <c r="E108" t="n">
-        <v>1281.82</v>
+        <v>1281.78</v>
       </c>
       <c r="F108" t="n">
         <v>19659</v>
@@ -13872,13 +13872,13 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>1275.72</v>
+        <v>1275.69</v>
       </c>
       <c r="D109" t="n">
-        <v>1269.15</v>
+        <v>1269.12</v>
       </c>
       <c r="E109" t="n">
-        <v>1282.3</v>
+        <v>1282.26</v>
       </c>
       <c r="F109" t="n">
         <v>9866</v>
@@ -14023,13 +14023,13 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>1275.5</v>
+        <v>1275.48</v>
       </c>
       <c r="D110" t="n">
-        <v>1271.92</v>
+        <v>1271.9</v>
       </c>
       <c r="E110" t="n">
-        <v>1279.09</v>
+        <v>1279.06</v>
       </c>
       <c r="F110" t="n">
         <v>156876</v>
@@ -14174,13 +14174,13 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>1273.66</v>
+        <v>1273.65</v>
       </c>
       <c r="D111" t="n">
-        <v>1267.77</v>
+        <v>1267.76</v>
       </c>
       <c r="E111" t="n">
-        <v>1279.55</v>
+        <v>1279.54</v>
       </c>
       <c r="F111" t="n">
         <v>14681</v>
@@ -14325,13 +14325,13 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>1270.06</v>
+        <v>1270.04</v>
       </c>
       <c r="D112" t="n">
-        <v>1261.93</v>
+        <v>1261.92</v>
       </c>
       <c r="E112" t="n">
-        <v>1278.18</v>
+        <v>1278.16</v>
       </c>
       <c r="F112" t="n">
         <v>5432</v>
@@ -14476,13 +14476,13 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>1266.53</v>
+        <v>1266.51</v>
       </c>
       <c r="D113" t="n">
-        <v>1261.66</v>
+        <v>1261.64</v>
       </c>
       <c r="E113" t="n">
-        <v>1271.4</v>
+        <v>1271.38</v>
       </c>
       <c r="F113" t="n">
         <v>27124</v>
@@ -14778,13 +14778,13 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>1263.79</v>
+        <v>1263.76</v>
       </c>
       <c r="D115" t="n">
-        <v>1257.51</v>
+        <v>1257.48</v>
       </c>
       <c r="E115" t="n">
-        <v>1270.07</v>
+        <v>1270.04</v>
       </c>
       <c r="F115" t="n">
         <v>15147</v>
@@ -14929,13 +14929,13 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>1261.01</v>
+        <v>1260.97</v>
       </c>
       <c r="D116" t="n">
-        <v>1256.69</v>
+        <v>1256.64</v>
       </c>
       <c r="E116" t="n">
-        <v>1265.34</v>
+        <v>1265.29</v>
       </c>
       <c r="F116" t="n">
         <v>77554</v>
@@ -15000,13 +15000,13 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>1260.98</v>
+        <v>1260.94</v>
       </c>
       <c r="D117" t="n">
-        <v>1256.04</v>
+        <v>1256</v>
       </c>
       <c r="E117" t="n">
-        <v>1265.93</v>
+        <v>1265.88</v>
       </c>
       <c r="F117" t="n">
         <v>37325</v>
@@ -15151,13 +15151,13 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>1255.65</v>
+        <v>1255.64</v>
       </c>
       <c r="D118" t="n">
-        <v>1251.08</v>
+        <v>1251.07</v>
       </c>
       <c r="E118" t="n">
-        <v>1260.23</v>
+        <v>1260.22</v>
       </c>
       <c r="F118" t="n">
         <v>24126</v>
@@ -15302,13 +15302,13 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>1251.35</v>
+        <v>1251.33</v>
       </c>
       <c r="D119" t="n">
-        <v>1240.55</v>
+        <v>1240.54</v>
       </c>
       <c r="E119" t="n">
-        <v>1262.14</v>
+        <v>1262.12</v>
       </c>
       <c r="F119" t="n">
         <v>3334</v>
@@ -15453,13 +15453,13 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>1249.4</v>
+        <v>1249.36</v>
       </c>
       <c r="D120" t="n">
-        <v>1242.8</v>
+        <v>1242.77</v>
       </c>
       <c r="E120" t="n">
-        <v>1256</v>
+        <v>1255.96</v>
       </c>
       <c r="F120" t="n">
         <v>10140</v>
@@ -15604,13 +15604,13 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>1238.68</v>
+        <v>1238.67</v>
       </c>
       <c r="D121" t="n">
-        <v>1231.45</v>
+        <v>1231.44</v>
       </c>
       <c r="E121" t="n">
-        <v>1245.9</v>
+        <v>1245.89</v>
       </c>
       <c r="F121" t="n">
         <v>8858</v>
@@ -15675,13 +15675,13 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>1236.79</v>
+        <v>1236.77</v>
       </c>
       <c r="D122" t="n">
-        <v>1227.69</v>
+        <v>1227.68</v>
       </c>
       <c r="E122" t="n">
-        <v>1245.88</v>
+        <v>1245.87</v>
       </c>
       <c r="F122" t="n">
         <v>4781</v>
@@ -15826,13 +15826,13 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>1233.26</v>
+        <v>1233.22</v>
       </c>
       <c r="D123" t="n">
-        <v>1227.71</v>
+        <v>1227.66</v>
       </c>
       <c r="E123" t="n">
-        <v>1238.82</v>
+        <v>1238.78</v>
       </c>
       <c r="F123" t="n">
         <v>26195</v>
@@ -15977,13 +15977,13 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>1232.38</v>
+        <v>1232.34</v>
       </c>
       <c r="D124" t="n">
-        <v>1227.1</v>
+        <v>1227.07</v>
       </c>
       <c r="E124" t="n">
-        <v>1237.66</v>
+        <v>1237.62</v>
       </c>
       <c r="F124" t="n">
         <v>39302</v>
@@ -16128,13 +16128,13 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>1228.55</v>
+        <v>1228.5</v>
       </c>
       <c r="D125" t="n">
-        <v>1223.99</v>
+        <v>1223.95</v>
       </c>
       <c r="E125" t="n">
-        <v>1233.11</v>
+        <v>1233.06</v>
       </c>
       <c r="F125" t="n">
         <v>51416</v>
@@ -16279,13 +16279,13 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>1225.99</v>
+        <v>1225.94</v>
       </c>
       <c r="D126" t="n">
-        <v>1221.21</v>
+        <v>1221.16</v>
       </c>
       <c r="E126" t="n">
-        <v>1230.78</v>
+        <v>1230.73</v>
       </c>
       <c r="F126" t="n">
         <v>54036</v>
@@ -16350,13 +16350,13 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>1222.58</v>
+        <v>1222.55</v>
       </c>
       <c r="D127" t="n">
-        <v>1218.84</v>
+        <v>1218.82</v>
       </c>
       <c r="E127" t="n">
-        <v>1226.31</v>
+        <v>1226.28</v>
       </c>
       <c r="F127" t="n">
         <v>104642</v>
@@ -16501,13 +16501,13 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>1222.47</v>
+        <v>1222.46</v>
       </c>
       <c r="D128" t="n">
-        <v>1215.51</v>
+        <v>1215.5</v>
       </c>
       <c r="E128" t="n">
-        <v>1229.44</v>
+        <v>1229.42</v>
       </c>
       <c r="F128" t="n">
         <v>9818</v>
@@ -16652,13 +16652,13 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>1220.43</v>
+        <v>1220.4</v>
       </c>
       <c r="D129" t="n">
-        <v>1209.74</v>
+        <v>1209.72</v>
       </c>
       <c r="E129" t="n">
-        <v>1231.11</v>
+        <v>1231.09</v>
       </c>
       <c r="F129" t="n">
         <v>2896</v>
@@ -16803,13 +16803,13 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>1212.56</v>
+        <v>1212.53</v>
       </c>
       <c r="D130" t="n">
-        <v>1207.52</v>
+        <v>1207.49</v>
       </c>
       <c r="E130" t="n">
-        <v>1217.6</v>
+        <v>1217.56</v>
       </c>
       <c r="F130" t="n">
         <v>24146</v>
@@ -16954,13 +16954,13 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>1211.89</v>
+        <v>1211.84</v>
       </c>
       <c r="D131" t="n">
-        <v>1201.08</v>
+        <v>1201.04</v>
       </c>
       <c r="E131" t="n">
-        <v>1222.69</v>
+        <v>1222.65</v>
       </c>
       <c r="F131" t="n">
         <v>4652</v>
@@ -17105,13 +17105,13 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>1211.09</v>
+        <v>1211.08</v>
       </c>
       <c r="D132" t="n">
-        <v>1206.96</v>
+        <v>1206.95</v>
       </c>
       <c r="E132" t="n">
-        <v>1215.23</v>
+        <v>1215.21</v>
       </c>
       <c r="F132" t="n">
         <v>49605</v>
@@ -17256,13 +17256,13 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>1207.64</v>
+        <v>1207.6</v>
       </c>
       <c r="D133" t="n">
-        <v>1196.53</v>
+        <v>1196.49</v>
       </c>
       <c r="E133" t="n">
-        <v>1218.75</v>
+        <v>1218.71</v>
       </c>
       <c r="F133" t="n">
         <v>3090</v>
@@ -17407,13 +17407,13 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>1202.97</v>
+        <v>1202.92</v>
       </c>
       <c r="D134" t="n">
-        <v>1196.85</v>
+        <v>1196.8</v>
       </c>
       <c r="E134" t="n">
-        <v>1209.09</v>
+        <v>1209.05</v>
       </c>
       <c r="F134" t="n">
         <v>21741</v>
@@ -17558,13 +17558,13 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>1198.92</v>
+        <v>1198.93</v>
       </c>
       <c r="D135" t="n">
-        <v>1194.85</v>
+        <v>1194.86</v>
       </c>
       <c r="E135" t="n">
-        <v>1203</v>
+        <v>1203.01</v>
       </c>
       <c r="F135" t="n">
         <v>46616</v>
@@ -17709,13 +17709,13 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>1197.07</v>
+        <v>1197.03</v>
       </c>
       <c r="D136" t="n">
-        <v>1191.91</v>
+        <v>1191.87</v>
       </c>
       <c r="E136" t="n">
-        <v>1202.23</v>
+        <v>1202.19</v>
       </c>
       <c r="F136" t="n">
         <v>25055</v>
@@ -17860,13 +17860,13 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>1196.22</v>
+        <v>1196.17</v>
       </c>
       <c r="D137" t="n">
-        <v>1191.94</v>
+        <v>1191.9</v>
       </c>
       <c r="E137" t="n">
-        <v>1200.49</v>
+        <v>1200.44</v>
       </c>
       <c r="F137" t="n">
         <v>73503</v>
@@ -18011,13 +18011,13 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>1194.2</v>
+        <v>1194.15</v>
       </c>
       <c r="D138" t="n">
-        <v>1188.08</v>
+        <v>1188.03</v>
       </c>
       <c r="E138" t="n">
-        <v>1200.31</v>
+        <v>1200.26</v>
       </c>
       <c r="F138" t="n">
         <v>32191</v>
@@ -18082,13 +18082,13 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>1190.59</v>
+        <v>1190.56</v>
       </c>
       <c r="D139" t="n">
-        <v>1183.41</v>
+        <v>1183.38</v>
       </c>
       <c r="E139" t="n">
-        <v>1197.77</v>
+        <v>1197.74</v>
       </c>
       <c r="F139" t="n">
         <v>9901</v>
@@ -18233,13 +18233,13 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>1190.09</v>
+        <v>1190.05</v>
       </c>
       <c r="D140" t="n">
-        <v>1182.97</v>
+        <v>1182.93</v>
       </c>
       <c r="E140" t="n">
-        <v>1197.22</v>
+        <v>1197.18</v>
       </c>
       <c r="F140" t="n">
         <v>17839</v>
@@ -18384,13 +18384,13 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>1183.76</v>
+        <v>1183.72</v>
       </c>
       <c r="D141" t="n">
-        <v>1174.31</v>
+        <v>1174.27</v>
       </c>
       <c r="E141" t="n">
-        <v>1193.22</v>
+        <v>1193.18</v>
       </c>
       <c r="F141" t="n">
         <v>8214</v>
@@ -18535,13 +18535,13 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>1183.53</v>
+        <v>1183.48</v>
       </c>
       <c r="D142" t="n">
-        <v>1172.02</v>
+        <v>1171.97</v>
       </c>
       <c r="E142" t="n">
-        <v>1195.04</v>
+        <v>1194.98</v>
       </c>
       <c r="F142" t="n">
         <v>4932</v>
@@ -18686,13 +18686,13 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>1182.98</v>
+        <v>1182.95</v>
       </c>
       <c r="D143" t="n">
-        <v>1176.15</v>
+        <v>1176.11</v>
       </c>
       <c r="E143" t="n">
-        <v>1189.82</v>
+        <v>1189.78</v>
       </c>
       <c r="F143" t="n">
         <v>15483</v>
@@ -18837,13 +18837,13 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>1181.41</v>
+        <v>1181.37</v>
       </c>
       <c r="D144" t="n">
-        <v>1173.41</v>
+        <v>1173.37</v>
       </c>
       <c r="E144" t="n">
-        <v>1189.42</v>
+        <v>1189.37</v>
       </c>
       <c r="F144" t="n">
         <v>12637</v>
@@ -18908,13 +18908,13 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>1181.39</v>
+        <v>1181.35</v>
       </c>
       <c r="D145" t="n">
-        <v>1171.72</v>
+        <v>1171.67</v>
       </c>
       <c r="E145" t="n">
-        <v>1191.07</v>
+        <v>1191.02</v>
       </c>
       <c r="F145" t="n">
         <v>7968</v>
@@ -18979,13 +18979,13 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>1181.36</v>
+        <v>1181.33</v>
       </c>
       <c r="D146" t="n">
-        <v>1172.68</v>
+        <v>1172.64</v>
       </c>
       <c r="E146" t="n">
-        <v>1190.05</v>
+        <v>1190.01</v>
       </c>
       <c r="F146" t="n">
         <v>6638</v>
@@ -19130,13 +19130,13 @@
         </is>
       </c>
       <c r="C147" t="n">
-        <v>1180.2</v>
+        <v>1180.19</v>
       </c>
       <c r="D147" t="n">
         <v>1174.12</v>
       </c>
       <c r="E147" t="n">
-        <v>1186.28</v>
+        <v>1186.27</v>
       </c>
       <c r="F147" t="n">
         <v>23893</v>
@@ -19281,13 +19281,13 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>1178.64</v>
+        <v>1178.59</v>
       </c>
       <c r="D148" t="n">
-        <v>1172.72</v>
+        <v>1172.68</v>
       </c>
       <c r="E148" t="n">
-        <v>1184.56</v>
+        <v>1184.51</v>
       </c>
       <c r="F148" t="n">
         <v>32832</v>
@@ -19352,13 +19352,13 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>1178.18</v>
+        <v>1178.15</v>
       </c>
       <c r="D149" t="n">
-        <v>1166.98</v>
+        <v>1166.95</v>
       </c>
       <c r="E149" t="n">
-        <v>1189.39</v>
+        <v>1189.36</v>
       </c>
       <c r="F149" t="n">
         <v>3188</v>
@@ -19503,13 +19503,13 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>1177.03</v>
+        <v>1176.98</v>
       </c>
       <c r="D150" t="n">
-        <v>1167.21</v>
+        <v>1167.16</v>
       </c>
       <c r="E150" t="n">
-        <v>1186.85</v>
+        <v>1186.8</v>
       </c>
       <c r="F150" t="n">
         <v>6535</v>
@@ -19654,13 +19654,13 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>1174.37</v>
+        <v>1174.33</v>
       </c>
       <c r="D151" t="n">
-        <v>1163.95</v>
+        <v>1163.9</v>
       </c>
       <c r="E151" t="n">
-        <v>1184.79</v>
+        <v>1184.75</v>
       </c>
       <c r="F151" t="n">
         <v>5006</v>
@@ -19805,13 +19805,13 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>1171.88</v>
+        <v>1171.84</v>
       </c>
       <c r="D152" t="n">
-        <v>1165.66</v>
+        <v>1165.62</v>
       </c>
       <c r="E152" t="n">
-        <v>1178.09</v>
+        <v>1178.05</v>
       </c>
       <c r="F152" t="n">
         <v>22479</v>
@@ -19956,13 +19956,13 @@
         </is>
       </c>
       <c r="C153" t="n">
-        <v>1170.73</v>
+        <v>1170.7</v>
       </c>
       <c r="D153" t="n">
-        <v>1163.31</v>
+        <v>1163.29</v>
       </c>
       <c r="E153" t="n">
-        <v>1178.14</v>
+        <v>1178.12</v>
       </c>
       <c r="F153" t="n">
         <v>16056</v>
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="C154" t="n">
-        <v>1170.21</v>
+        <v>1170.17</v>
       </c>
       <c r="D154" t="n">
-        <v>1164.29</v>
+        <v>1164.25</v>
       </c>
       <c r="E154" t="n">
-        <v>1176.13</v>
+        <v>1176.09</v>
       </c>
       <c r="F154" t="n">
         <v>17766</v>
@@ -20258,13 +20258,13 @@
         </is>
       </c>
       <c r="C155" t="n">
-        <v>1169.9</v>
+        <v>1169.87</v>
       </c>
       <c r="D155" t="n">
-        <v>1164.4</v>
+        <v>1164.36</v>
       </c>
       <c r="E155" t="n">
-        <v>1175.41</v>
+        <v>1175.38</v>
       </c>
       <c r="F155" t="n">
         <v>38492</v>
@@ -20409,13 +20409,13 @@
         </is>
       </c>
       <c r="C156" t="n">
-        <v>1166.61</v>
+        <v>1166.57</v>
       </c>
       <c r="D156" t="n">
-        <v>1158.54</v>
+        <v>1158.5</v>
       </c>
       <c r="E156" t="n">
-        <v>1174.68</v>
+        <v>1174.64</v>
       </c>
       <c r="F156" t="n">
         <v>10224</v>
@@ -20560,13 +20560,13 @@
         </is>
       </c>
       <c r="C157" t="n">
-        <v>1165.95</v>
+        <v>1165.91</v>
       </c>
       <c r="D157" t="n">
-        <v>1158.25</v>
+        <v>1158.21</v>
       </c>
       <c r="E157" t="n">
-        <v>1173.65</v>
+        <v>1173.61</v>
       </c>
       <c r="F157" t="n">
         <v>7936</v>
@@ -20711,13 +20711,13 @@
         </is>
       </c>
       <c r="C158" t="n">
-        <v>1163.79</v>
+        <v>1163.76</v>
       </c>
       <c r="D158" t="n">
-        <v>1151.86</v>
+        <v>1151.82</v>
       </c>
       <c r="E158" t="n">
-        <v>1175.73</v>
+        <v>1175.69</v>
       </c>
       <c r="F158" t="n">
         <v>3777</v>
@@ -20862,13 +20862,13 @@
         </is>
       </c>
       <c r="C159" t="n">
-        <v>1155.7</v>
+        <v>1155.66</v>
       </c>
       <c r="D159" t="n">
-        <v>1144.2</v>
+        <v>1144.16</v>
       </c>
       <c r="E159" t="n">
-        <v>1167.21</v>
+        <v>1167.16</v>
       </c>
       <c r="F159" t="n">
         <v>3231</v>
@@ -21013,13 +21013,13 @@
         </is>
       </c>
       <c r="C160" t="n">
-        <v>1155.27</v>
+        <v>1155.23</v>
       </c>
       <c r="D160" t="n">
-        <v>1146.88</v>
+        <v>1146.84</v>
       </c>
       <c r="E160" t="n">
-        <v>1163.66</v>
+        <v>1163.62</v>
       </c>
       <c r="F160" t="n">
         <v>6837</v>
@@ -21164,13 +21164,13 @@
         </is>
       </c>
       <c r="C161" t="n">
-        <v>1154.22</v>
+        <v>1154.15</v>
       </c>
       <c r="D161" t="n">
-        <v>1141.6</v>
+        <v>1141.54</v>
       </c>
       <c r="E161" t="n">
-        <v>1166.84</v>
+        <v>1166.77</v>
       </c>
       <c r="F161" t="n">
         <v>3585</v>
@@ -21315,13 +21315,13 @@
         </is>
       </c>
       <c r="C162" t="n">
-        <v>1151.4</v>
+        <v>1151.35</v>
       </c>
       <c r="D162" t="n">
-        <v>1138.2</v>
+        <v>1138.15</v>
       </c>
       <c r="E162" t="n">
-        <v>1164.6</v>
+        <v>1164.55</v>
       </c>
       <c r="F162" t="n">
         <v>4155</v>
@@ -21466,13 +21466,13 @@
         </is>
       </c>
       <c r="C163" t="n">
-        <v>1151.11</v>
+        <v>1151.07</v>
       </c>
       <c r="D163" t="n">
-        <v>1135.73</v>
+        <v>1135.69</v>
       </c>
       <c r="E163" t="n">
-        <v>1166.49</v>
+        <v>1166.44</v>
       </c>
       <c r="F163" t="n">
         <v>1679</v>
@@ -21617,13 +21617,13 @@
         </is>
       </c>
       <c r="C164" t="n">
-        <v>1149.25</v>
+        <v>1149.21</v>
       </c>
       <c r="D164" t="n">
-        <v>1136.96</v>
+        <v>1136.92</v>
       </c>
       <c r="E164" t="n">
-        <v>1161.54</v>
+        <v>1161.49</v>
       </c>
       <c r="F164" t="n">
         <v>2572</v>
@@ -21768,13 +21768,13 @@
         </is>
       </c>
       <c r="C165" t="n">
-        <v>1148.63</v>
+        <v>1148.59</v>
       </c>
       <c r="D165" t="n">
-        <v>1141.98</v>
+        <v>1141.93</v>
       </c>
       <c r="E165" t="n">
-        <v>1155.29</v>
+        <v>1155.25</v>
       </c>
       <c r="F165" t="n">
         <v>19402</v>
@@ -21919,13 +21919,13 @@
         </is>
       </c>
       <c r="C166" t="n">
-        <v>1148.32</v>
+        <v>1148.28</v>
       </c>
       <c r="D166" t="n">
-        <v>1139.06</v>
+        <v>1139.02</v>
       </c>
       <c r="E166" t="n">
-        <v>1157.58</v>
+        <v>1157.53</v>
       </c>
       <c r="F166" t="n">
         <v>7044</v>
@@ -22070,13 +22070,13 @@
         </is>
       </c>
       <c r="C167" t="n">
-        <v>1146.25</v>
+        <v>1146.2</v>
       </c>
       <c r="D167" t="n">
-        <v>1129.14</v>
+        <v>1129.09</v>
       </c>
       <c r="E167" t="n">
-        <v>1163.36</v>
+        <v>1163.31</v>
       </c>
       <c r="F167" t="n">
         <v>1295</v>
@@ -22221,13 +22221,13 @@
         </is>
       </c>
       <c r="C168" t="n">
-        <v>1142.94</v>
+        <v>1142.91</v>
       </c>
       <c r="D168" t="n">
-        <v>1133.05</v>
+        <v>1133.01</v>
       </c>
       <c r="E168" t="n">
-        <v>1152.84</v>
+        <v>1152.8</v>
       </c>
       <c r="F168" t="n">
         <v>4737</v>
@@ -22372,13 +22372,13 @@
         </is>
       </c>
       <c r="C169" t="n">
-        <v>1142.21</v>
+        <v>1142.16</v>
       </c>
       <c r="D169" t="n">
-        <v>1135.77</v>
+        <v>1135.73</v>
       </c>
       <c r="E169" t="n">
-        <v>1148.64</v>
+        <v>1148.6</v>
       </c>
       <c r="F169" t="n">
         <v>12297</v>
@@ -22523,13 +22523,13 @@
         </is>
       </c>
       <c r="C170" t="n">
-        <v>1140.63</v>
+        <v>1140.6</v>
       </c>
       <c r="D170" t="n">
-        <v>1133.9</v>
+        <v>1133.87</v>
       </c>
       <c r="E170" t="n">
-        <v>1147.36</v>
+        <v>1147.33</v>
       </c>
       <c r="F170" t="n">
         <v>19174</v>
@@ -22674,13 +22674,13 @@
         </is>
       </c>
       <c r="C171" t="n">
-        <v>1140.05</v>
+        <v>1140</v>
       </c>
       <c r="D171" t="n">
-        <v>1133.33</v>
+        <v>1133.29</v>
       </c>
       <c r="E171" t="n">
-        <v>1146.76</v>
+        <v>1146.71</v>
       </c>
       <c r="F171" t="n">
         <v>19367</v>
@@ -22825,13 +22825,13 @@
         </is>
       </c>
       <c r="C172" t="n">
-        <v>1137.71</v>
+        <v>1137.66</v>
       </c>
       <c r="D172" t="n">
-        <v>1126.75</v>
+        <v>1126.7</v>
       </c>
       <c r="E172" t="n">
-        <v>1148.68</v>
+        <v>1148.62</v>
       </c>
       <c r="F172" t="n">
         <v>4964</v>
@@ -22976,13 +22976,13 @@
         </is>
       </c>
       <c r="C173" t="n">
-        <v>1135.77</v>
+        <v>1135.75</v>
       </c>
       <c r="D173" t="n">
-        <v>1126.26</v>
+        <v>1126.24</v>
       </c>
       <c r="E173" t="n">
-        <v>1145.27</v>
+        <v>1145.25</v>
       </c>
       <c r="F173" t="n">
         <v>8925</v>
@@ -23127,13 +23127,13 @@
         </is>
       </c>
       <c r="C174" t="n">
-        <v>1135.69</v>
+        <v>1135.65</v>
       </c>
       <c r="D174" t="n">
-        <v>1126.78</v>
+        <v>1126.74</v>
       </c>
       <c r="E174" t="n">
-        <v>1144.59</v>
+        <v>1144.55</v>
       </c>
       <c r="F174" t="n">
         <v>7366</v>
@@ -23278,13 +23278,13 @@
         </is>
       </c>
       <c r="C175" t="n">
-        <v>1130.04</v>
+        <v>1130</v>
       </c>
       <c r="D175" t="n">
-        <v>1121.2</v>
+        <v>1121.15</v>
       </c>
       <c r="E175" t="n">
-        <v>1138.89</v>
+        <v>1138.84</v>
       </c>
       <c r="F175" t="n">
         <v>11118</v>
@@ -23429,13 +23429,13 @@
         </is>
       </c>
       <c r="C176" t="n">
-        <v>1128.4</v>
+        <v>1128.35</v>
       </c>
       <c r="D176" t="n">
-        <v>1120.97</v>
+        <v>1120.93</v>
       </c>
       <c r="E176" t="n">
-        <v>1135.83</v>
+        <v>1135.78</v>
       </c>
       <c r="F176" t="n">
         <v>20685</v>
@@ -23580,13 +23580,13 @@
         </is>
       </c>
       <c r="C177" t="n">
-        <v>1127.47</v>
+        <v>1127.43</v>
       </c>
       <c r="D177" t="n">
-        <v>1121.07</v>
+        <v>1121.03</v>
       </c>
       <c r="E177" t="n">
-        <v>1133.87</v>
+        <v>1133.83</v>
       </c>
       <c r="F177" t="n">
         <v>20118</v>
@@ -23731,13 +23731,13 @@
         </is>
       </c>
       <c r="C178" t="n">
-        <v>1126.35</v>
+        <v>1126.3</v>
       </c>
       <c r="D178" t="n">
-        <v>1114.21</v>
+        <v>1114.16</v>
       </c>
       <c r="E178" t="n">
-        <v>1138.5</v>
+        <v>1138.44</v>
       </c>
       <c r="F178" t="n">
         <v>2921</v>
@@ -23882,13 +23882,13 @@
         </is>
       </c>
       <c r="C179" t="n">
-        <v>1125.94</v>
+        <v>1125.89</v>
       </c>
       <c r="D179" t="n">
-        <v>1110.29</v>
+        <v>1110.24</v>
       </c>
       <c r="E179" t="n">
-        <v>1141.6</v>
+        <v>1141.54</v>
       </c>
       <c r="F179" t="n">
         <v>1785</v>
@@ -24033,13 +24033,13 @@
         </is>
       </c>
       <c r="C180" t="n">
-        <v>1120.12</v>
+        <v>1120.07</v>
       </c>
       <c r="D180" t="n">
-        <v>1109.12</v>
+        <v>1109.07</v>
       </c>
       <c r="E180" t="n">
-        <v>1131.11</v>
+        <v>1131.06</v>
       </c>
       <c r="F180" t="n">
         <v>5182</v>
@@ -24184,13 +24184,13 @@
         </is>
       </c>
       <c r="C181" t="n">
-        <v>1118.22</v>
+        <v>1118.18</v>
       </c>
       <c r="D181" t="n">
-        <v>1100.03</v>
+        <v>1099.99</v>
       </c>
       <c r="E181" t="n">
-        <v>1136.41</v>
+        <v>1136.37</v>
       </c>
       <c r="F181" t="n">
         <v>1143</v>
@@ -24335,13 +24335,13 @@
         </is>
       </c>
       <c r="C182" t="n">
-        <v>1114.13</v>
+        <v>1114.12</v>
       </c>
       <c r="D182" t="n">
         <v>1106.39</v>
       </c>
       <c r="E182" t="n">
-        <v>1121.87</v>
+        <v>1121.86</v>
       </c>
       <c r="F182" t="n">
         <v>10854</v>
@@ -24486,13 +24486,13 @@
         </is>
       </c>
       <c r="C183" t="n">
-        <v>1113.78</v>
+        <v>1113.73</v>
       </c>
       <c r="D183" t="n">
-        <v>1104.6</v>
+        <v>1104.56</v>
       </c>
       <c r="E183" t="n">
-        <v>1122.95</v>
+        <v>1122.9</v>
       </c>
       <c r="F183" t="n">
         <v>6923</v>
@@ -24637,13 +24637,13 @@
         </is>
       </c>
       <c r="C184" t="n">
-        <v>1113.5</v>
+        <v>1113.46</v>
       </c>
       <c r="D184" t="n">
-        <v>1099.09</v>
+        <v>1099.05</v>
       </c>
       <c r="E184" t="n">
-        <v>1127.9</v>
+        <v>1127.86</v>
       </c>
       <c r="F184" t="n">
         <v>2199</v>
@@ -24788,13 +24788,13 @@
         </is>
       </c>
       <c r="C185" t="n">
-        <v>1110.44</v>
+        <v>1110.4</v>
       </c>
       <c r="D185" t="n">
-        <v>1102.56</v>
+        <v>1102.52</v>
       </c>
       <c r="E185" t="n">
-        <v>1118.32</v>
+        <v>1118.28</v>
       </c>
       <c r="F185" t="n">
         <v>8045</v>
@@ -24939,13 +24939,13 @@
         </is>
       </c>
       <c r="C186" t="n">
-        <v>1108.76</v>
+        <v>1108.71</v>
       </c>
       <c r="D186" t="n">
-        <v>1099.46</v>
+        <v>1099.41</v>
       </c>
       <c r="E186" t="n">
-        <v>1118.05</v>
+        <v>1118</v>
       </c>
       <c r="F186" t="n">
         <v>8977</v>
@@ -25090,13 +25090,13 @@
         </is>
       </c>
       <c r="C187" t="n">
-        <v>1107.24</v>
+        <v>1107.21</v>
       </c>
       <c r="D187" t="n">
-        <v>1100.18</v>
+        <v>1100.15</v>
       </c>
       <c r="E187" t="n">
-        <v>1114.3</v>
+        <v>1114.27</v>
       </c>
       <c r="F187" t="n">
         <v>14148</v>
@@ -25241,13 +25241,13 @@
         </is>
       </c>
       <c r="C188" t="n">
-        <v>1091.42</v>
+        <v>1091.4</v>
       </c>
       <c r="D188" t="n">
-        <v>1079.91</v>
+        <v>1079.89</v>
       </c>
       <c r="E188" t="n">
-        <v>1102.93</v>
+        <v>1102.9</v>
       </c>
       <c r="F188" t="n">
         <v>4780</v>
@@ -25392,13 +25392,13 @@
         </is>
       </c>
       <c r="C189" t="n">
-        <v>1089.34</v>
+        <v>1089.28</v>
       </c>
       <c r="D189" t="n">
-        <v>1079.99</v>
+        <v>1079.94</v>
       </c>
       <c r="E189" t="n">
-        <v>1098.69</v>
+        <v>1098.63</v>
       </c>
       <c r="F189" t="n">
         <v>7597</v>
@@ -25543,13 +25543,13 @@
         </is>
       </c>
       <c r="C190" t="n">
-        <v>1073.49</v>
+        <v>1073.45</v>
       </c>
       <c r="D190" t="n">
-        <v>1062.31</v>
+        <v>1062.27</v>
       </c>
       <c r="E190" t="n">
-        <v>1084.68</v>
+        <v>1084.63</v>
       </c>
       <c r="F190" t="n">
         <v>6328</v>
@@ -25694,13 +25694,13 @@
         </is>
       </c>
       <c r="C191" t="n">
-        <v>1069.53</v>
+        <v>1069.48</v>
       </c>
       <c r="D191" t="n">
-        <v>1059.59</v>
+        <v>1059.55</v>
       </c>
       <c r="E191" t="n">
-        <v>1079.46</v>
+        <v>1079.41</v>
       </c>
       <c r="F191" t="n">
         <v>6965</v>
@@ -25845,13 +25845,13 @@
         </is>
       </c>
       <c r="C192" t="n">
-        <v>1066.91</v>
+        <v>1066.86</v>
       </c>
       <c r="D192" t="n">
-        <v>1055.4</v>
+        <v>1055.36</v>
       </c>
       <c r="E192" t="n">
-        <v>1078.41</v>
+        <v>1078.36</v>
       </c>
       <c r="F192" t="n">
         <v>5745</v>
@@ -25996,13 +25996,13 @@
         </is>
       </c>
       <c r="C193" t="n">
-        <v>1065.27</v>
+        <v>1065.23</v>
       </c>
       <c r="D193" t="n">
-        <v>1050.01</v>
+        <v>1049.96</v>
       </c>
       <c r="E193" t="n">
-        <v>1080.54</v>
+        <v>1080.49</v>
       </c>
       <c r="F193" t="n">
         <v>1743</v>
@@ -26147,13 +26147,13 @@
         </is>
       </c>
       <c r="C194" t="n">
-        <v>1061.11</v>
+        <v>1061.06</v>
       </c>
       <c r="D194" t="n">
-        <v>1049.09</v>
+        <v>1049.05</v>
       </c>
       <c r="E194" t="n">
-        <v>1073.12</v>
+        <v>1073.08</v>
       </c>
       <c r="F194" t="n">
         <v>3924</v>
@@ -26298,13 +26298,13 @@
         </is>
       </c>
       <c r="C195" t="n">
-        <v>1055.12</v>
+        <v>1055.07</v>
       </c>
       <c r="D195" t="n">
-        <v>1043.44</v>
+        <v>1043.38</v>
       </c>
       <c r="E195" t="n">
-        <v>1066.8</v>
+        <v>1066.75</v>
       </c>
       <c r="F195" t="n">
         <v>4658</v>
@@ -26449,13 +26449,13 @@
         </is>
       </c>
       <c r="C196" t="n">
-        <v>1040.5</v>
+        <v>1040.46</v>
       </c>
       <c r="D196" t="n">
-        <v>1029.07</v>
+        <v>1029.03</v>
       </c>
       <c r="E196" t="n">
-        <v>1051.94</v>
+        <v>1051.89</v>
       </c>
       <c r="F196" t="n">
         <v>4845</v>
@@ -26600,13 +26600,13 @@
         </is>
       </c>
       <c r="C197" t="n">
-        <v>1023.25</v>
+        <v>1023.2</v>
       </c>
       <c r="D197" t="n">
-        <v>1009.63</v>
+        <v>1009.58</v>
       </c>
       <c r="E197" t="n">
-        <v>1036.88</v>
+        <v>1036.82</v>
       </c>
       <c r="F197" t="n">
         <v>2658</v>
@@ -26751,13 +26751,13 @@
         </is>
       </c>
       <c r="C198" t="n">
-        <v>1021.3</v>
+        <v>1021.25</v>
       </c>
       <c r="D198" t="n">
-        <v>1010.39</v>
+        <v>1010.34</v>
       </c>
       <c r="E198" t="n">
-        <v>1032.21</v>
+        <v>1032.16</v>
       </c>
       <c r="F198" t="n">
         <v>6310</v>
@@ -26902,13 +26902,13 @@
         </is>
       </c>
       <c r="C199" t="n">
-        <v>994.62</v>
+        <v>994.573</v>
       </c>
       <c r="D199" t="n">
-        <v>982.011</v>
+        <v>981.968</v>
       </c>
       <c r="E199" t="n">
-        <v>1007.23</v>
+        <v>1007.18</v>
       </c>
       <c r="F199" t="n">
         <v>4914</v>
@@ -27053,13 +27053,13 @@
         </is>
       </c>
       <c r="C200" t="n">
-        <v>990.574</v>
+        <v>990.538</v>
       </c>
       <c r="D200" t="n">
-        <v>978.1559999999999</v>
+        <v>978.123</v>
       </c>
       <c r="E200" t="n">
-        <v>1002.99</v>
+        <v>1002.95</v>
       </c>
       <c r="F200" t="n">
         <v>4203</v>
@@ -27204,13 +27204,13 @@
         </is>
       </c>
       <c r="C201" t="n">
-        <v>979.482</v>
+        <v>979.4349999999999</v>
       </c>
       <c r="D201" t="n">
-        <v>965.895</v>
+        <v>965.852</v>
       </c>
       <c r="E201" t="n">
-        <v>993.0700000000001</v>
+        <v>993.019</v>
       </c>
       <c r="F201" t="n">
         <v>3412</v>
@@ -27355,13 +27355,13 @@
         </is>
       </c>
       <c r="C202" t="n">
-        <v>971.723</v>
+        <v>971.686</v>
       </c>
       <c r="D202" t="n">
-        <v>955.846</v>
+        <v>955.816</v>
       </c>
       <c r="E202" t="n">
-        <v>987.599</v>
+        <v>987.557</v>
       </c>
       <c r="F202" t="n">
         <v>2391</v>
@@ -27506,13 +27506,13 @@
         </is>
       </c>
       <c r="C203" t="n">
-        <v>951.717</v>
+        <v>951.674</v>
       </c>
       <c r="D203" t="n">
-        <v>938.926</v>
+        <v>938.888</v>
       </c>
       <c r="E203" t="n">
-        <v>964.5069999999999</v>
+        <v>964.46</v>
       </c>
       <c r="F203" t="n">
         <v>3287</v>
@@ -28634,7 +28634,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>mimo-v2.5</t>
+          <t>deepseek-v3.2</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -28649,7 +28649,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>deepseek-v3.2</t>
+          <t>mimo-v2.5</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
@@ -28755,38 +28755,38 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>qwen3.5-122b-a10b</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>122</v>
-      </c>
-      <c r="C26" t="n">
-        <v>10</v>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+          <t>deepseek-v3.1</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>deepseek-v3.1</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
+          <t>qwen3.5-122b-a10b</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>122</v>
+      </c>
+      <c r="C27" t="n">
+        <v>10</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>name_parsing</t>
         </is>
       </c>
     </row>
@@ -29197,38 +29197,38 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>qwen3-coder-480b-a35b-instruct</t>
-        </is>
-      </c>
-      <c r="B48" t="n">
-        <v>480</v>
-      </c>
-      <c r="C48" t="n">
-        <v>35</v>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+          <t>mimo-v2-flash (thinking)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr"/>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>mimo-v2-flash (thinking)</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr"/>
-      <c r="C49" t="inlineStr"/>
-      <c r="D49" t="inlineStr"/>
+          <t>qwen3-coder-480b-a35b-instruct</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>480</v>
+      </c>
+      <c r="C49" t="n">
+        <v>35</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>name_parsing</t>
         </is>
       </c>
     </row>
@@ -29288,46 +29288,46 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>qwen3-235b-a22b</t>
+          <t>trinity-large-preview</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>235</v>
+        <v>70</v>
       </c>
       <c r="C53" t="n">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>moe</t>
+          <t>dense</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>override</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>trinity-large-preview</t>
+          <t>qwen3-235b-a22b</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>70</v>
+        <v>235</v>
       </c>
       <c r="C54" t="n">
-        <v>70</v>
+        <v>22</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>dense</t>
+          <t>moe</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>name_parsing</t>
         </is>
       </c>
     </row>
@@ -30173,14 +30173,14 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>gemma-3-4b-it</t>
+          <t>mistral-small-3.1-24b-instruct-2503</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="C96" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -30196,14 +30196,14 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>mistral-small-3.1-24b-instruct-2503</t>
+          <t>gemma-3-4b-it</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="C97" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>

--- a/arena_enrichment/output/arena_leaderboard_enriched.xlsx
+++ b/arena_enrichment/output/arena_leaderboard_enriched.xlsx
@@ -7969,123 +7969,43 @@
           <t>MIT</t>
         </is>
       </c>
-      <c r="I65" t="n">
-        <v>107</v>
-      </c>
-      <c r="J65" t="n">
-        <v>107</v>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>dense</t>
-        </is>
-      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr">
         <is>
-          <t>aa_single_scrape</t>
-        </is>
-      </c>
-      <c r="M65" t="n">
-        <v>214</v>
-      </c>
-      <c r="N65" t="n">
-        <v>267.5</v>
-      </c>
-      <c r="O65" t="n">
-        <v>107</v>
-      </c>
-      <c r="P65" t="n">
-        <v>133.8</v>
-      </c>
-      <c r="Q65" t="n">
-        <v>53.5</v>
-      </c>
-      <c r="R65" t="n">
-        <v>66.90000000000001</v>
-      </c>
-      <c r="S65" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T65" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U65" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="V65" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W65" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X65" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Y65" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z65" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AA65" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB65" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AC65" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AD65" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AE65" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AF65" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AG65" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr"/>
+      <c r="P65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr"/>
+      <c r="R65" t="inlineStr"/>
+      <c r="S65" t="inlineStr"/>
+      <c r="T65" t="inlineStr"/>
+      <c r="U65" t="inlineStr"/>
+      <c r="V65" t="inlineStr"/>
+      <c r="W65" t="inlineStr"/>
+      <c r="X65" t="inlineStr"/>
+      <c r="Y65" t="inlineStr"/>
+      <c r="Z65" t="inlineStr"/>
+      <c r="AA65" t="inlineStr"/>
+      <c r="AB65" t="inlineStr"/>
+      <c r="AC65" t="inlineStr"/>
+      <c r="AD65" t="inlineStr"/>
+      <c r="AE65" t="inlineStr"/>
+      <c r="AF65" t="inlineStr"/>
+      <c r="AG65" t="inlineStr"/>
       <c r="AH65" t="inlineStr">
         <is>
-          <t>B300 SXM</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="AI65" t="inlineStr">
         <is>
-          <t>H200 SXM</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -15021,123 +14941,43 @@
           <t>DeepSeek License</t>
         </is>
       </c>
-      <c r="I117" t="n">
-        <v>236</v>
-      </c>
-      <c r="J117" t="n">
-        <v>21</v>
-      </c>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
       <c r="L117" t="inlineStr">
         <is>
-          <t>aa_single_scrape</t>
-        </is>
-      </c>
-      <c r="M117" t="n">
-        <v>472</v>
-      </c>
-      <c r="N117" t="n">
-        <v>590</v>
-      </c>
-      <c r="O117" t="n">
-        <v>236</v>
-      </c>
-      <c r="P117" t="n">
-        <v>295</v>
-      </c>
-      <c r="Q117" t="n">
-        <v>118</v>
-      </c>
-      <c r="R117" t="n">
-        <v>147.5</v>
-      </c>
-      <c r="S117" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T117" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U117" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="V117" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W117" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X117" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Y117" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z117" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AA117" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AB117" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AC117" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AD117" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AE117" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AF117" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AG117" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr"/>
+      <c r="N117" t="inlineStr"/>
+      <c r="O117" t="inlineStr"/>
+      <c r="P117" t="inlineStr"/>
+      <c r="Q117" t="inlineStr"/>
+      <c r="R117" t="inlineStr"/>
+      <c r="S117" t="inlineStr"/>
+      <c r="T117" t="inlineStr"/>
+      <c r="U117" t="inlineStr"/>
+      <c r="V117" t="inlineStr"/>
+      <c r="W117" t="inlineStr"/>
+      <c r="X117" t="inlineStr"/>
+      <c r="Y117" t="inlineStr"/>
+      <c r="Z117" t="inlineStr"/>
+      <c r="AA117" t="inlineStr"/>
+      <c r="AB117" t="inlineStr"/>
+      <c r="AC117" t="inlineStr"/>
+      <c r="AD117" t="inlineStr"/>
+      <c r="AE117" t="inlineStr"/>
+      <c r="AF117" t="inlineStr"/>
+      <c r="AG117" t="inlineStr"/>
       <c r="AH117" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="AI117" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -29749,20 +29589,12 @@
           <t>intellect-3</t>
         </is>
       </c>
-      <c r="B65" t="n">
-        <v>107</v>
-      </c>
-      <c r="C65" t="n">
-        <v>107</v>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>dense</t>
-        </is>
-      </c>
+      <c r="B65" t="inlineStr"/>
+      <c r="C65" t="inlineStr"/>
+      <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>aa_single_scrape</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -30865,20 +30697,12 @@
           <t>deepseek-coder-v2</t>
         </is>
       </c>
-      <c r="B117" t="n">
-        <v>236</v>
-      </c>
-      <c r="C117" t="n">
-        <v>21</v>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+      <c r="B117" t="inlineStr"/>
+      <c r="C117" t="inlineStr"/>
+      <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr">
         <is>
-          <t>aa_single_scrape</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>

--- a/arena_enrichment/output/arena_leaderboard_enriched.xlsx
+++ b/arena_enrichment/output/arena_leaderboard_enriched.xlsx
@@ -7969,43 +7969,123 @@
           <t>MIT</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
+      <c r="I65" t="n">
+        <v>107</v>
+      </c>
+      <c r="J65" t="n">
+        <v>107</v>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>dense</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
-      <c r="O65" t="inlineStr"/>
-      <c r="P65" t="inlineStr"/>
-      <c r="Q65" t="inlineStr"/>
-      <c r="R65" t="inlineStr"/>
-      <c r="S65" t="inlineStr"/>
-      <c r="T65" t="inlineStr"/>
-      <c r="U65" t="inlineStr"/>
-      <c r="V65" t="inlineStr"/>
-      <c r="W65" t="inlineStr"/>
-      <c r="X65" t="inlineStr"/>
-      <c r="Y65" t="inlineStr"/>
-      <c r="Z65" t="inlineStr"/>
-      <c r="AA65" t="inlineStr"/>
-      <c r="AB65" t="inlineStr"/>
-      <c r="AC65" t="inlineStr"/>
-      <c r="AD65" t="inlineStr"/>
-      <c r="AE65" t="inlineStr"/>
-      <c r="AF65" t="inlineStr"/>
-      <c r="AG65" t="inlineStr"/>
+          <t>aa_single_scrape</t>
+        </is>
+      </c>
+      <c r="M65" t="n">
+        <v>214</v>
+      </c>
+      <c r="N65" t="n">
+        <v>267.5</v>
+      </c>
+      <c r="O65" t="n">
+        <v>107</v>
+      </c>
+      <c r="P65" t="n">
+        <v>133.8</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="R65" t="n">
+        <v>66.90000000000001</v>
+      </c>
+      <c r="S65" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T65" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U65" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V65" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W65" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X65" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y65" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z65" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AA65" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB65" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AC65" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AD65" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE65" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AF65" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AG65" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AH65" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>B300 SXM</t>
         </is>
       </c>
       <c r="AI65" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>H200 SXM</t>
         </is>
       </c>
     </row>
@@ -14941,43 +15021,123 @@
           <t>DeepSeek License</t>
         </is>
       </c>
-      <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
+      <c r="I117" t="n">
+        <v>236</v>
+      </c>
+      <c r="J117" t="n">
+        <v>21</v>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="M117" t="inlineStr"/>
-      <c r="N117" t="inlineStr"/>
-      <c r="O117" t="inlineStr"/>
-      <c r="P117" t="inlineStr"/>
-      <c r="Q117" t="inlineStr"/>
-      <c r="R117" t="inlineStr"/>
-      <c r="S117" t="inlineStr"/>
-      <c r="T117" t="inlineStr"/>
-      <c r="U117" t="inlineStr"/>
-      <c r="V117" t="inlineStr"/>
-      <c r="W117" t="inlineStr"/>
-      <c r="X117" t="inlineStr"/>
-      <c r="Y117" t="inlineStr"/>
-      <c r="Z117" t="inlineStr"/>
-      <c r="AA117" t="inlineStr"/>
-      <c r="AB117" t="inlineStr"/>
-      <c r="AC117" t="inlineStr"/>
-      <c r="AD117" t="inlineStr"/>
-      <c r="AE117" t="inlineStr"/>
-      <c r="AF117" t="inlineStr"/>
-      <c r="AG117" t="inlineStr"/>
+          <t>aa_single_scrape</t>
+        </is>
+      </c>
+      <c r="M117" t="n">
+        <v>472</v>
+      </c>
+      <c r="N117" t="n">
+        <v>590</v>
+      </c>
+      <c r="O117" t="n">
+        <v>236</v>
+      </c>
+      <c r="P117" t="n">
+        <v>295</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>118</v>
+      </c>
+      <c r="R117" t="n">
+        <v>147.5</v>
+      </c>
+      <c r="S117" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T117" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U117" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V117" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W117" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X117" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y117" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z117" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA117" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AB117" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AC117" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD117" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE117" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF117" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AG117" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AH117" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
       <c r="AI117" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
     </row>
@@ -29589,12 +29749,20 @@
           <t>intellect-3</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr"/>
-      <c r="C65" t="inlineStr"/>
-      <c r="D65" t="inlineStr"/>
+      <c r="B65" t="n">
+        <v>107</v>
+      </c>
+      <c r="C65" t="n">
+        <v>107</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>dense</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>aa_single_scrape</t>
         </is>
       </c>
     </row>
@@ -30697,12 +30865,20 @@
           <t>deepseek-coder-v2</t>
         </is>
       </c>
-      <c r="B117" t="inlineStr"/>
-      <c r="C117" t="inlineStr"/>
-      <c r="D117" t="inlineStr"/>
+      <c r="B117" t="n">
+        <v>236</v>
+      </c>
+      <c r="C117" t="n">
+        <v>21</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>aa_single_scrape</t>
         </is>
       </c>
     </row>

--- a/arena_enrichment/output/arena_leaderboard_enriched.xlsx
+++ b/arena_enrichment/output/arena_leaderboard_enriched.xlsx
@@ -675,16 +675,16 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>1470.52</v>
+        <v>1471.22</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1464.41</v>
+        <v>1465.15</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1476.63</v>
+        <v>1477.28</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>11071</v>
+        <v>11347</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
@@ -746,16 +746,16 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>1463.32</v>
+        <v>1463.4</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1455.16</v>
+        <v>1455.9</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1471.47</v>
+        <v>1470.91</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>5037</v>
+        <v>6039</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
@@ -817,16 +817,16 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>1463.03</v>
+        <v>1462.93</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1454.26</v>
+        <v>1454.14</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1471.81</v>
+        <v>1471.71</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>4176</v>
+        <v>4160</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
@@ -968,16 +968,16 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>1461.72</v>
+        <v>1462.01</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1452.5</v>
+        <v>1452.76</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1470.95</v>
+        <v>1471.25</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>3820</v>
+        <v>3808</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
@@ -1039,16 +1039,16 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1460.05</v>
+        <v>1460.81</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1452.75</v>
+        <v>1453.88</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1467.35</v>
+        <v>1467.74</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>6168</v>
+        <v>6936</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
@@ -1190,16 +1190,16 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>1456.32</v>
+        <v>1456.45</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>1451.55</v>
+        <v>1451.71</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1461.1</v>
+        <v>1461.18</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>19980</v>
+        <v>20291</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
@@ -1341,16 +1341,16 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>1450.99</v>
+        <v>1451.05</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>1443.34</v>
+        <v>1443.42</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1458.64</v>
+        <v>1458.68</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>5810</v>
+        <v>5829</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
@@ -1492,16 +1492,16 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>1449.5</v>
+        <v>1449.09</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1445.14</v>
+        <v>1444.8</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1453.86</v>
+        <v>1453.38</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>26123</v>
+        <v>27087</v>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
@@ -1643,16 +1643,16 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>1447.12</v>
+        <v>1445.14</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>1442.44</v>
+        <v>1440.54</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1451.79</v>
+        <v>1449.75</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>21382</v>
+        <v>22296</v>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
@@ -1794,16 +1794,16 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>1442.51</v>
+        <v>1442.48</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>1436.4</v>
+        <v>1436.37</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1448.63</v>
+        <v>1448.59</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>12143</v>
+        <v>12145</v>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
@@ -1865,16 +1865,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1438.75</v>
+        <v>1439.4</v>
       </c>
       <c r="D12" t="n">
-        <v>1429.43</v>
+        <v>1430.08</v>
       </c>
       <c r="E12" t="n">
-        <v>1448.08</v>
+        <v>1448.72</v>
       </c>
       <c r="F12" t="n">
-        <v>3603</v>
+        <v>3604</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1936,16 +1936,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1438.05</v>
+        <v>1437.95</v>
       </c>
       <c r="D13" t="n">
-        <v>1430.39</v>
+        <v>1430.28</v>
       </c>
       <c r="E13" t="n">
-        <v>1445.72</v>
+        <v>1445.61</v>
       </c>
       <c r="F13" t="n">
-        <v>5777</v>
+        <v>5782</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -2087,16 +2087,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1432.33</v>
+        <v>1432.38</v>
       </c>
       <c r="D14" t="n">
-        <v>1422.91</v>
+        <v>1422.94</v>
       </c>
       <c r="E14" t="n">
-        <v>1441.75</v>
+        <v>1441.82</v>
       </c>
       <c r="F14" t="n">
-        <v>3512</v>
+        <v>3505</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -2238,16 +2238,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1431.88</v>
+        <v>1431.71</v>
       </c>
       <c r="D15" t="n">
-        <v>1425.28</v>
+        <v>1425.11</v>
       </c>
       <c r="E15" t="n">
-        <v>1438.49</v>
+        <v>1438.31</v>
       </c>
       <c r="F15" t="n">
-        <v>8198</v>
+        <v>8205</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -2389,16 +2389,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1430.3</v>
+        <v>1429.91</v>
       </c>
       <c r="D16" t="n">
-        <v>1426.95</v>
+        <v>1426.59</v>
       </c>
       <c r="E16" t="n">
-        <v>1433.66</v>
+        <v>1433.24</v>
       </c>
       <c r="F16" t="n">
-        <v>51723</v>
+        <v>52748</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -2540,16 +2540,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1425.72</v>
+        <v>1425.56</v>
       </c>
       <c r="D17" t="n">
-        <v>1421.78</v>
+        <v>1421.62</v>
       </c>
       <c r="E17" t="n">
-        <v>1429.65</v>
+        <v>1429.49</v>
       </c>
       <c r="F17" t="n">
-        <v>35707</v>
+        <v>35690</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -2611,16 +2611,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1424.45</v>
+        <v>1424.51</v>
       </c>
       <c r="D18" t="n">
-        <v>1417.9</v>
+        <v>1417.95</v>
       </c>
       <c r="E18" t="n">
-        <v>1431</v>
+        <v>1431.06</v>
       </c>
       <c r="F18" t="n">
-        <v>9079</v>
+        <v>9070</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -2678,24 +2678,24 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>mimo-v2.5</t>
+          <t>deepseek-v3.2</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1424.37</v>
+        <v>1423.95</v>
       </c>
       <c r="D19" t="n">
-        <v>1416.32</v>
+        <v>1420.31</v>
       </c>
       <c r="E19" t="n">
-        <v>1432.43</v>
+        <v>1427.59</v>
       </c>
       <c r="F19" t="n">
-        <v>5131</v>
+        <v>44813</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Xiaomi</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2749,24 +2749,24 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>deepseek-v3.2</t>
+          <t>mimo-v2.5</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1423.97</v>
+        <v>1423.39</v>
       </c>
       <c r="D20" t="n">
-        <v>1420.32</v>
+        <v>1415.95</v>
       </c>
       <c r="E20" t="n">
-        <v>1427.62</v>
+        <v>1430.83</v>
       </c>
       <c r="F20" t="n">
-        <v>44809</v>
+        <v>6105</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>DeepSeek</t>
+          <t>Xiaomi</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2824,16 +2824,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1422.77</v>
+        <v>1422.84</v>
       </c>
       <c r="D21" t="n">
-        <v>1416.36</v>
+        <v>1416.43</v>
       </c>
       <c r="E21" t="n">
-        <v>1429.17</v>
+        <v>1429.25</v>
       </c>
       <c r="F21" t="n">
-        <v>11944</v>
+        <v>11940</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -2895,16 +2895,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1422.39</v>
+        <v>1422.66</v>
       </c>
       <c r="D22" t="n">
-        <v>1419.69</v>
+        <v>1419.98</v>
       </c>
       <c r="E22" t="n">
-        <v>1425.09</v>
+        <v>1425.35</v>
       </c>
       <c r="F22" t="n">
-        <v>87368</v>
+        <v>88345</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -3046,16 +3046,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1421.91</v>
+        <v>1421.96</v>
       </c>
       <c r="D23" t="n">
-        <v>1418.17</v>
+        <v>1418.23</v>
       </c>
       <c r="E23" t="n">
-        <v>1425.64</v>
+        <v>1425.69</v>
       </c>
       <c r="F23" t="n">
-        <v>39077</v>
+        <v>39063</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -3117,16 +3117,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1421.86</v>
+        <v>1421.89</v>
       </c>
       <c r="D24" t="n">
-        <v>1416.2</v>
+        <v>1416.23</v>
       </c>
       <c r="E24" t="n">
-        <v>1427.52</v>
+        <v>1427.55</v>
       </c>
       <c r="F24" t="n">
-        <v>18469</v>
+        <v>18465</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -3188,16 +3188,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1418.83</v>
+        <v>1419.79</v>
       </c>
       <c r="D25" t="n">
-        <v>1409.02</v>
+        <v>1411.22</v>
       </c>
       <c r="E25" t="n">
-        <v>1428.64</v>
+        <v>1428.36</v>
       </c>
       <c r="F25" t="n">
-        <v>3321</v>
+        <v>4349</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -3259,16 +3259,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1417.9</v>
+        <v>1417.99</v>
       </c>
       <c r="D26" t="n">
-        <v>1412.98</v>
+        <v>1413.16</v>
       </c>
       <c r="E26" t="n">
         <v>1422.83</v>
       </c>
       <c r="F26" t="n">
-        <v>18236</v>
+        <v>19200</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -3410,16 +3410,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1417.88</v>
+        <v>1417.71</v>
       </c>
       <c r="D27" t="n">
-        <v>1411.39</v>
+        <v>1411.22</v>
       </c>
       <c r="E27" t="n">
-        <v>1424.38</v>
+        <v>1424.21</v>
       </c>
       <c r="F27" t="n">
-        <v>11792</v>
+        <v>11795</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -3561,16 +3561,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1417.55</v>
+        <v>1417.46</v>
       </c>
       <c r="D28" t="n">
-        <v>1411.54</v>
+        <v>1411.45</v>
       </c>
       <c r="E28" t="n">
-        <v>1423.56</v>
+        <v>1423.46</v>
       </c>
       <c r="F28" t="n">
-        <v>14989</v>
+        <v>14987</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -3628,68 +3628,148 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>deepseek-v3.1-terminus-thinking</t>
+          <t>kimi-k2-0711-preview</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1417.13</v>
+        <v>1417.03</v>
       </c>
       <c r="D29" t="n">
-        <v>1407.16</v>
+        <v>1412.18</v>
       </c>
       <c r="E29" t="n">
-        <v>1427.11</v>
+        <v>1421.89</v>
       </c>
       <c r="F29" t="n">
-        <v>3468</v>
+        <v>27645</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>DeepSeek</t>
+          <t>Moonshot</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
+          <t>Modified MIT</t>
+        </is>
+   